--- a/Alola_Paths_and_Challenges.xlsx
+++ b/Alola_Paths_and_Challenges.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F377"/>
+  <dimension ref="A1:F380"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -615,7 +615,7 @@
         <v>Inkay</v>
       </c>
       <c r="E11" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F11" t="str">
         <v>12.50%</v>
@@ -635,7 +635,7 @@
         <v>Slowpoke</v>
       </c>
       <c r="E12" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F12" t="str">
         <v>12.50%</v>
@@ -655,7 +655,7 @@
         <v>Wingull</v>
       </c>
       <c r="E13" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F13" t="str">
         <v>12.50%</v>
@@ -675,7 +675,7 @@
         <v>Alolan Meowth</v>
       </c>
       <c r="E14" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F14" t="str">
         <v>12.50%</v>
@@ -695,7 +695,7 @@
         <v>Magnemite</v>
       </c>
       <c r="E15" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F15" t="str">
         <v>12.50%</v>
@@ -715,7 +715,7 @@
         <v>Alolan Grimer</v>
       </c>
       <c r="E16" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F16" t="str">
         <v>12.50%</v>
@@ -735,7 +735,7 @@
         <v>Tentacool</v>
       </c>
       <c r="E17" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F17" t="str">
         <v>12.50%</v>
@@ -755,7 +755,7 @@
         <v>Finneon</v>
       </c>
       <c r="E18" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F18" t="str">
         <v>12.50%</v>
@@ -775,7 +775,7 @@
         <v>Rattata</v>
       </c>
       <c r="E19" t="str">
-        <v>4-9</v>
+        <v>2-7</v>
       </c>
       <c r="F19" t="str">
         <v>20.00%</v>
@@ -795,7 +795,7 @@
         <v>Metapod</v>
       </c>
       <c r="E20" t="str">
-        <v>4-9</v>
+        <v>2-7</v>
       </c>
       <c r="F20" t="str">
         <v>20.00%</v>
@@ -815,7 +815,7 @@
         <v>Bonsly</v>
       </c>
       <c r="E21" t="str">
-        <v>4-9</v>
+        <v>2-7</v>
       </c>
       <c r="F21" t="str">
         <v>20.00%</v>
@@ -835,7 +835,7 @@
         <v>Munchlax</v>
       </c>
       <c r="E22" t="str">
-        <v>4-9</v>
+        <v>2-7</v>
       </c>
       <c r="F22" t="str">
         <v>20.00%</v>
@@ -855,7 +855,7 @@
         <v>Rockruff</v>
       </c>
       <c r="E23" t="str">
-        <v>4-9</v>
+        <v>2-7</v>
       </c>
       <c r="F23" t="str">
         <v>20.00%</v>
@@ -875,7 +875,7 @@
         <v>Zorua</v>
       </c>
       <c r="E24" t="str">
-        <v>5-10</v>
+        <v>2-7</v>
       </c>
       <c r="F24" t="str">
         <v>33.33%</v>
@@ -895,7 +895,7 @@
         <v>Gastly</v>
       </c>
       <c r="E25" t="str">
-        <v>5-10</v>
+        <v>2-7</v>
       </c>
       <c r="F25" t="str">
         <v>33.33%</v>
@@ -915,7 +915,7 @@
         <v>Drifloon</v>
       </c>
       <c r="E26" t="str">
-        <v>5-10</v>
+        <v>2-7</v>
       </c>
       <c r="F26" t="str">
         <v>33.33%</v>
@@ -935,7 +935,7 @@
         <v>Rowlet</v>
       </c>
       <c r="E27" t="str">
-        <v>7-12</v>
+        <v>2-7</v>
       </c>
       <c r="F27" t="str">
         <v>33.33%</v>
@@ -955,7 +955,7 @@
         <v>Litten</v>
       </c>
       <c r="E28" t="str">
-        <v>7-12</v>
+        <v>2-7</v>
       </c>
       <c r="F28" t="str">
         <v>33.33%</v>
@@ -975,7 +975,7 @@
         <v>Popplio</v>
       </c>
       <c r="E29" t="str">
-        <v>7-12</v>
+        <v>2-7</v>
       </c>
       <c r="F29" t="str">
         <v>33.33%</v>
@@ -995,7 +995,7 @@
         <v>Luvdisc</v>
       </c>
       <c r="E30" t="str">
-        <v>8-13</v>
+        <v>4-9</v>
       </c>
       <c r="F30" t="str">
         <v>20.00%</v>
@@ -1015,7 +1015,7 @@
         <v>Corsola</v>
       </c>
       <c r="E31" t="str">
-        <v>8-13</v>
+        <v>4-9</v>
       </c>
       <c r="F31" t="str">
         <v>20.00%</v>
@@ -1035,7 +1035,7 @@
         <v>Remoraid</v>
       </c>
       <c r="E32" t="str">
-        <v>8-13</v>
+        <v>4-9</v>
       </c>
       <c r="F32" t="str">
         <v>20.00%</v>
@@ -1055,7 +1055,7 @@
         <v>Magikarp</v>
       </c>
       <c r="E33" t="str">
-        <v>8-13</v>
+        <v>4-9</v>
       </c>
       <c r="F33" t="str">
         <v>20.00%</v>
@@ -1075,7 +1075,7 @@
         <v>Clamperl</v>
       </c>
       <c r="E34" t="str">
-        <v>8-13</v>
+        <v>4-9</v>
       </c>
       <c r="F34" t="str">
         <v>20.00%</v>
@@ -1095,7 +1095,7 @@
         <v>Furfrou</v>
       </c>
       <c r="E35" t="str">
-        <v>9-14</v>
+        <v>4-9</v>
       </c>
       <c r="F35" t="str">
         <v>20.00%</v>
@@ -1115,7 +1115,7 @@
         <v>Hypno</v>
       </c>
       <c r="E36" t="str">
-        <v>9-14</v>
+        <v>4-9</v>
       </c>
       <c r="F36" t="str">
         <v>20.00%</v>
@@ -1135,7 +1135,7 @@
         <v>Abra</v>
       </c>
       <c r="E37" t="str">
-        <v>9-14</v>
+        <v>4-9</v>
       </c>
       <c r="F37" t="str">
         <v>20.00%</v>
@@ -1155,7 +1155,7 @@
         <v>Mime Jr.</v>
       </c>
       <c r="E38" t="str">
-        <v>9-14</v>
+        <v>4-9</v>
       </c>
       <c r="F38" t="str">
         <v>20.00%</v>
@@ -1175,7 +1175,7 @@
         <v>Bewear</v>
       </c>
       <c r="E39" t="str">
-        <v>9-14</v>
+        <v>4-9</v>
       </c>
       <c r="F39" t="str">
         <v>20.00%</v>
@@ -1195,7 +1195,7 @@
         <v>Machop</v>
       </c>
       <c r="E40" t="str">
-        <v>10-15</v>
+        <v>5-10</v>
       </c>
       <c r="F40" t="str">
         <v>50.00%</v>
@@ -1215,7 +1215,7 @@
         <v>Hawlucha</v>
       </c>
       <c r="E41" t="str">
-        <v>10-15</v>
+        <v>5-10</v>
       </c>
       <c r="F41" t="str">
         <v>50.00%</v>
@@ -1235,7 +1235,7 @@
         <v>Drowzee</v>
       </c>
       <c r="E42" t="str">
-        <v>12-17</v>
+        <v>5-10</v>
       </c>
       <c r="F42" t="str">
         <v>14.29%</v>
@@ -1255,7 +1255,7 @@
         <v>Makuhita</v>
       </c>
       <c r="E43" t="str">
-        <v>12-17</v>
+        <v>5-10</v>
       </c>
       <c r="F43" t="str">
         <v>14.29%</v>
@@ -1275,7 +1275,7 @@
         <v>Spearow</v>
       </c>
       <c r="E44" t="str">
-        <v>12-17</v>
+        <v>5-10</v>
       </c>
       <c r="F44" t="str">
         <v>14.29%</v>
@@ -1295,7 +1295,7 @@
         <v>Cutiefly</v>
       </c>
       <c r="E45" t="str">
-        <v>12-17</v>
+        <v>5-10</v>
       </c>
       <c r="F45" t="str">
         <v>14.29%</v>
@@ -1315,7 +1315,7 @@
         <v>Ekans</v>
       </c>
       <c r="E46" t="str">
-        <v>12-17</v>
+        <v>5-10</v>
       </c>
       <c r="F46" t="str">
         <v>14.29%</v>
@@ -1335,7 +1335,7 @@
         <v>Growlithe</v>
       </c>
       <c r="E47" t="str">
-        <v>12-17</v>
+        <v>5-10</v>
       </c>
       <c r="F47" t="str">
         <v>14.29%</v>
@@ -1355,7 +1355,7 @@
         <v>Smeargle</v>
       </c>
       <c r="E48" t="str">
-        <v>12-17</v>
+        <v>5-10</v>
       </c>
       <c r="F48" t="str">
         <v>14.29%</v>
@@ -1375,7 +1375,7 @@
         <v>Crabrawler</v>
       </c>
       <c r="E49" t="str">
-        <v>13-18</v>
+        <v>5-10</v>
       </c>
       <c r="F49" t="str">
         <v>100.00%</v>
@@ -1386,7 +1386,7 @@
         <v>11</v>
       </c>
       <c r="B50" t="str">
-        <v>Captain Ilima (Boss)</v>
+        <v>Captain Ilima</v>
       </c>
       <c r="C50" t="str">
         <v>Boss Battle</v>
@@ -1395,7 +1395,7 @@
         <v>Boss</v>
       </c>
       <c r="E50" t="str">
-        <v>15-20</v>
+        <v>7-12</v>
       </c>
       <c r="F50" t="str">
         <v>-</v>
@@ -1415,7 +1415,7 @@
         <v>Gastly</v>
       </c>
       <c r="E51" t="str">
-        <v>15-20</v>
+        <v>9-14</v>
       </c>
       <c r="F51" t="str">
         <v>20.00%</v>
@@ -1435,7 +1435,7 @@
         <v>Drifloon</v>
       </c>
       <c r="E52" t="str">
-        <v>15-20</v>
+        <v>9-14</v>
       </c>
       <c r="F52" t="str">
         <v>20.00%</v>
@@ -1455,7 +1455,7 @@
         <v>Zubat</v>
       </c>
       <c r="E53" t="str">
-        <v>15-20</v>
+        <v>9-14</v>
       </c>
       <c r="F53" t="str">
         <v>20.00%</v>
@@ -1475,7 +1475,7 @@
         <v>Murkrow</v>
       </c>
       <c r="E54" t="str">
-        <v>15-20</v>
+        <v>9-14</v>
       </c>
       <c r="F54" t="str">
         <v>20.00%</v>
@@ -1495,7 +1495,7 @@
         <v>Misdreavus</v>
       </c>
       <c r="E55" t="str">
-        <v>15-20</v>
+        <v>9-14</v>
       </c>
       <c r="F55" t="str">
         <v>20.00%</v>
@@ -1515,7 +1515,7 @@
         <v>Zubat</v>
       </c>
       <c r="E56" t="str">
-        <v>17-22</v>
+        <v>10-15</v>
       </c>
       <c r="F56" t="str">
         <v>25.00%</v>
@@ -1535,7 +1535,7 @@
         <v>Noibat</v>
       </c>
       <c r="E57" t="str">
-        <v>17-22</v>
+        <v>10-15</v>
       </c>
       <c r="F57" t="str">
         <v>25.00%</v>
@@ -1555,7 +1555,7 @@
         <v>Alolan Diglett</v>
       </c>
       <c r="E58" t="str">
-        <v>17-22</v>
+        <v>10-15</v>
       </c>
       <c r="F58" t="str">
         <v>25.00%</v>
@@ -1575,7 +1575,7 @@
         <v>Pheromosa</v>
       </c>
       <c r="E59" t="str">
-        <v>17-22</v>
+        <v>10-15</v>
       </c>
       <c r="F59" t="str">
         <v>25.00%</v>
@@ -1595,7 +1595,7 @@
         <v>Roggenrola</v>
       </c>
       <c r="E60" t="str">
-        <v>18-23</v>
+        <v>12-17</v>
       </c>
       <c r="F60" t="str">
         <v>25.00%</v>
@@ -1615,7 +1615,7 @@
         <v>Carbink</v>
       </c>
       <c r="E61" t="str">
-        <v>18-23</v>
+        <v>12-17</v>
       </c>
       <c r="F61" t="str">
         <v>25.00%</v>
@@ -1635,7 +1635,7 @@
         <v>Spinda</v>
       </c>
       <c r="E62" t="str">
-        <v>18-23</v>
+        <v>12-17</v>
       </c>
       <c r="F62" t="str">
         <v>25.00%</v>
@@ -1655,7 +1655,7 @@
         <v>Necrozma</v>
       </c>
       <c r="E63" t="str">
-        <v>18-23</v>
+        <v>12-17</v>
       </c>
       <c r="F63" t="str">
         <v>25.00%</v>
@@ -1675,7 +1675,7 @@
         <v>Mawile</v>
       </c>
       <c r="E64" t="str">
-        <v>19-24</v>
+        <v>12-17</v>
       </c>
       <c r="F64" t="str">
         <v>100.00%</v>
@@ -1695,7 +1695,7 @@
         <v>Zubat</v>
       </c>
       <c r="E65" t="str">
-        <v>20-25</v>
+        <v>13-18</v>
       </c>
       <c r="F65" t="str">
         <v>9.09%</v>
@@ -1715,7 +1715,7 @@
         <v>Alolan Diglett</v>
       </c>
       <c r="E66" t="str">
-        <v>20-25</v>
+        <v>13-18</v>
       </c>
       <c r="F66" t="str">
         <v>9.09%</v>
@@ -1735,7 +1735,7 @@
         <v>Magikarp</v>
       </c>
       <c r="E67" t="str">
-        <v>20-25</v>
+        <v>13-18</v>
       </c>
       <c r="F67" t="str">
         <v>9.09%</v>
@@ -1755,7 +1755,7 @@
         <v>Delibird</v>
       </c>
       <c r="E68" t="str">
-        <v>20-25</v>
+        <v>13-18</v>
       </c>
       <c r="F68" t="str">
         <v>9.09%</v>
@@ -1775,7 +1775,7 @@
         <v>Zubat</v>
       </c>
       <c r="E69" t="str">
-        <v>20-25</v>
+        <v>13-18</v>
       </c>
       <c r="F69" t="str">
         <v>9.09%</v>
@@ -1795,7 +1795,7 @@
         <v>Psyduck</v>
       </c>
       <c r="E70" t="str">
-        <v>20-25</v>
+        <v>13-18</v>
       </c>
       <c r="F70" t="str">
         <v>9.09%</v>
@@ -1815,7 +1815,7 @@
         <v>Delibird</v>
       </c>
       <c r="E71" t="str">
-        <v>20-25</v>
+        <v>13-18</v>
       </c>
       <c r="F71" t="str">
         <v>9.09%</v>
@@ -1835,7 +1835,7 @@
         <v>Psyduck</v>
       </c>
       <c r="E72" t="str">
-        <v>20-25</v>
+        <v>13-18</v>
       </c>
       <c r="F72" t="str">
         <v>9.09%</v>
@@ -1855,7 +1855,7 @@
         <v>Barboach</v>
       </c>
       <c r="E73" t="str">
-        <v>20-25</v>
+        <v>13-18</v>
       </c>
       <c r="F73" t="str">
         <v>9.09%</v>
@@ -1875,7 +1875,7 @@
         <v>Smoochum</v>
       </c>
       <c r="E74" t="str">
-        <v>20-25</v>
+        <v>13-18</v>
       </c>
       <c r="F74" t="str">
         <v>9.09%</v>
@@ -1895,7 +1895,7 @@
         <v>Seel</v>
       </c>
       <c r="E75" t="str">
-        <v>20-25</v>
+        <v>13-18</v>
       </c>
       <c r="F75" t="str">
         <v>9.09%</v>
@@ -1906,59 +1906,59 @@
         <v>17</v>
       </c>
       <c r="B76" t="str">
-        <v>Kahuna Hala</v>
+        <v>Route 3</v>
       </c>
       <c r="C76" t="str">
-        <v>Kahuna Hala</v>
+        <v>North</v>
       </c>
       <c r="D76" t="str">
-        <v>Boss</v>
+        <v>Mankey</v>
       </c>
       <c r="E76" t="str">
-        <v>21-26</v>
+        <v>15-20</v>
       </c>
       <c r="F76" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B77" t="str">
-        <v>Heahea Beach</v>
+        <v>Route 3</v>
       </c>
       <c r="C77" t="str">
-        <v>Main Area</v>
+        <v>North</v>
       </c>
       <c r="D77" t="str">
-        <v>Gumshoos</v>
+        <v>Delibird</v>
       </c>
       <c r="E77" t="str">
-        <v>23-28</v>
+        <v>15-20</v>
       </c>
       <c r="F77" t="str">
-        <v>9.09%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B78" t="str">
-        <v>Heahea Beach</v>
+        <v>Route 3</v>
       </c>
       <c r="C78" t="str">
-        <v>Main Area</v>
+        <v>North</v>
       </c>
       <c r="D78" t="str">
-        <v>Raticate</v>
+        <v>Bagon</v>
       </c>
       <c r="E78" t="str">
-        <v>23-28</v>
+        <v>15-20</v>
       </c>
       <c r="F78" t="str">
-        <v>9.09%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="79">
@@ -1966,24 +1966,24 @@
         <v>18</v>
       </c>
       <c r="B79" t="str">
-        <v>Heahea Beach</v>
+        <v>Kahuna Hala</v>
       </c>
       <c r="C79" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D79" t="str">
-        <v>Vikavolt</v>
+        <v>Boss</v>
       </c>
       <c r="E79" t="str">
-        <v>23-28</v>
+        <v>17-22</v>
       </c>
       <c r="F79" t="str">
-        <v>9.09%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B80" t="str">
         <v>Heahea Beach</v>
@@ -1992,10 +1992,10 @@
         <v>Main Area</v>
       </c>
       <c r="D80" t="str">
-        <v>Ribombee</v>
+        <v>Gumshoos</v>
       </c>
       <c r="E80" t="str">
-        <v>23-28</v>
+        <v>18-23</v>
       </c>
       <c r="F80" t="str">
         <v>9.09%</v>
@@ -2003,7 +2003,7 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B81" t="str">
         <v>Heahea Beach</v>
@@ -2012,10 +2012,10 @@
         <v>Main Area</v>
       </c>
       <c r="D81" t="str">
-        <v>Araquanid</v>
+        <v>Raticate</v>
       </c>
       <c r="E81" t="str">
-        <v>23-28</v>
+        <v>18-23</v>
       </c>
       <c r="F81" t="str">
         <v>9.09%</v>
@@ -2023,7 +2023,7 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B82" t="str">
         <v>Heahea Beach</v>
@@ -2032,10 +2032,10 @@
         <v>Main Area</v>
       </c>
       <c r="D82" t="str">
-        <v>Lurantis</v>
+        <v>Vikavolt</v>
       </c>
       <c r="E82" t="str">
-        <v>23-28</v>
+        <v>18-23</v>
       </c>
       <c r="F82" t="str">
         <v>9.09%</v>
@@ -2043,7 +2043,7 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B83" t="str">
         <v>Heahea Beach</v>
@@ -2052,10 +2052,10 @@
         <v>Main Area</v>
       </c>
       <c r="D83" t="str">
-        <v>Salazzle</v>
+        <v>Ribombee</v>
       </c>
       <c r="E83" t="str">
-        <v>23-28</v>
+        <v>18-23</v>
       </c>
       <c r="F83" t="str">
         <v>9.09%</v>
@@ -2063,7 +2063,7 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B84" t="str">
         <v>Heahea Beach</v>
@@ -2072,10 +2072,10 @@
         <v>Main Area</v>
       </c>
       <c r="D84" t="str">
-        <v>Marowak</v>
+        <v>Araquanid</v>
       </c>
       <c r="E84" t="str">
-        <v>23-28</v>
+        <v>18-23</v>
       </c>
       <c r="F84" t="str">
         <v>9.09%</v>
@@ -2083,7 +2083,7 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B85" t="str">
         <v>Heahea Beach</v>
@@ -2092,10 +2092,10 @@
         <v>Main Area</v>
       </c>
       <c r="D85" t="str">
-        <v>Kommo-o</v>
+        <v>Lurantis</v>
       </c>
       <c r="E85" t="str">
-        <v>23-28</v>
+        <v>18-23</v>
       </c>
       <c r="F85" t="str">
         <v>9.09%</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B86" t="str">
         <v>Heahea Beach</v>
@@ -2112,10 +2112,10 @@
         <v>Main Area</v>
       </c>
       <c r="D86" t="str">
-        <v>Togedemaru</v>
+        <v>Salazzle</v>
       </c>
       <c r="E86" t="str">
-        <v>23-28</v>
+        <v>18-23</v>
       </c>
       <c r="F86" t="str">
         <v>9.09%</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B87" t="str">
         <v>Heahea Beach</v>
@@ -2132,10 +2132,10 @@
         <v>Main Area</v>
       </c>
       <c r="D87" t="str">
-        <v>Mimikyu</v>
+        <v>Marowak</v>
       </c>
       <c r="E87" t="str">
-        <v>23-28</v>
+        <v>18-23</v>
       </c>
       <c r="F87" t="str">
         <v>9.09%</v>
@@ -2146,19 +2146,19 @@
         <v>19</v>
       </c>
       <c r="B88" t="str">
-        <v>Route 4</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C88" t="str">
         <v>Main Area</v>
       </c>
       <c r="D88" t="str">
-        <v>Pikipek</v>
+        <v>Kommo-o</v>
       </c>
       <c r="E88" t="str">
-        <v>24-29</v>
+        <v>18-23</v>
       </c>
       <c r="F88" t="str">
-        <v>12.50%</v>
+        <v>9.09%</v>
       </c>
     </row>
     <row r="89">
@@ -2166,19 +2166,19 @@
         <v>19</v>
       </c>
       <c r="B89" t="str">
-        <v>Route 4</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C89" t="str">
         <v>Main Area</v>
       </c>
       <c r="D89" t="str">
-        <v>Alolan Rattata</v>
+        <v>Togedemaru</v>
       </c>
       <c r="E89" t="str">
-        <v>24-29</v>
+        <v>18-23</v>
       </c>
       <c r="F89" t="str">
-        <v>12.50%</v>
+        <v>9.09%</v>
       </c>
     </row>
     <row r="90">
@@ -2186,24 +2186,24 @@
         <v>19</v>
       </c>
       <c r="B90" t="str">
-        <v>Route 4</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C90" t="str">
         <v>Main Area</v>
       </c>
       <c r="D90" t="str">
-        <v>Grubbin</v>
+        <v>Mimikyu</v>
       </c>
       <c r="E90" t="str">
-        <v>24-29</v>
+        <v>18-23</v>
       </c>
       <c r="F90" t="str">
-        <v>12.50%</v>
+        <v>9.09%</v>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B91" t="str">
         <v>Route 4</v>
@@ -2212,10 +2212,10 @@
         <v>Main Area</v>
       </c>
       <c r="D91" t="str">
-        <v>Crabrawler</v>
+        <v>Pikipek</v>
       </c>
       <c r="E91" t="str">
-        <v>24-29</v>
+        <v>20-25</v>
       </c>
       <c r="F91" t="str">
         <v>12.50%</v>
@@ -2223,7 +2223,7 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B92" t="str">
         <v>Route 4</v>
@@ -2232,10 +2232,10 @@
         <v>Main Area</v>
       </c>
       <c r="D92" t="str">
-        <v>Lillipup</v>
+        <v>Alolan Rattata</v>
       </c>
       <c r="E92" t="str">
-        <v>24-29</v>
+        <v>20-25</v>
       </c>
       <c r="F92" t="str">
         <v>12.50%</v>
@@ -2243,7 +2243,7 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B93" t="str">
         <v>Route 4</v>
@@ -2252,10 +2252,10 @@
         <v>Main Area</v>
       </c>
       <c r="D93" t="str">
-        <v>Eevee</v>
+        <v>Grubbin</v>
       </c>
       <c r="E93" t="str">
-        <v>24-29</v>
+        <v>20-25</v>
       </c>
       <c r="F93" t="str">
         <v>12.50%</v>
@@ -2263,7 +2263,7 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B94" t="str">
         <v>Route 4</v>
@@ -2272,10 +2272,10 @@
         <v>Main Area</v>
       </c>
       <c r="D94" t="str">
-        <v>Igglybuff</v>
+        <v>Crabrawler</v>
       </c>
       <c r="E94" t="str">
-        <v>24-29</v>
+        <v>20-25</v>
       </c>
       <c r="F94" t="str">
         <v>12.50%</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B95" t="str">
         <v>Route 4</v>
@@ -2292,10 +2292,10 @@
         <v>Main Area</v>
       </c>
       <c r="D95" t="str">
-        <v>Mudbray</v>
+        <v>Lillipup</v>
       </c>
       <c r="E95" t="str">
-        <v>24-29</v>
+        <v>20-25</v>
       </c>
       <c r="F95" t="str">
         <v>12.50%</v>
@@ -2306,19 +2306,19 @@
         <v>20</v>
       </c>
       <c r="B96" t="str">
-        <v>Paniola Ranch</v>
+        <v>Route 4</v>
       </c>
       <c r="C96" t="str">
         <v>Main Area</v>
       </c>
       <c r="D96" t="str">
-        <v>Lillipup</v>
+        <v>Eevee</v>
       </c>
       <c r="E96" t="str">
-        <v>25-30</v>
+        <v>20-25</v>
       </c>
       <c r="F96" t="str">
-        <v>16.67%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="97">
@@ -2326,19 +2326,19 @@
         <v>20</v>
       </c>
       <c r="B97" t="str">
-        <v>Paniola Ranch</v>
+        <v>Route 4</v>
       </c>
       <c r="C97" t="str">
         <v>Main Area</v>
       </c>
       <c r="D97" t="str">
-        <v>Eevee</v>
+        <v>Igglybuff</v>
       </c>
       <c r="E97" t="str">
-        <v>25-30</v>
+        <v>20-25</v>
       </c>
       <c r="F97" t="str">
-        <v>16.67%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="98">
@@ -2346,7 +2346,7 @@
         <v>20</v>
       </c>
       <c r="B98" t="str">
-        <v>Paniola Ranch</v>
+        <v>Route 4</v>
       </c>
       <c r="C98" t="str">
         <v>Main Area</v>
@@ -2355,15 +2355,15 @@
         <v>Mudbray</v>
       </c>
       <c r="E98" t="str">
-        <v>25-30</v>
+        <v>20-25</v>
       </c>
       <c r="F98" t="str">
-        <v>16.67%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B99" t="str">
         <v>Paniola Ranch</v>
@@ -2372,10 +2372,10 @@
         <v>Main Area</v>
       </c>
       <c r="D99" t="str">
-        <v>Mareep</v>
+        <v>Lillipup</v>
       </c>
       <c r="E99" t="str">
-        <v>25-30</v>
+        <v>21-26</v>
       </c>
       <c r="F99" t="str">
         <v>16.67%</v>
@@ -2383,7 +2383,7 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B100" t="str">
         <v>Paniola Ranch</v>
@@ -2392,10 +2392,10 @@
         <v>Main Area</v>
       </c>
       <c r="D100" t="str">
-        <v>Tauros</v>
+        <v>Eevee</v>
       </c>
       <c r="E100" t="str">
-        <v>25-30</v>
+        <v>21-26</v>
       </c>
       <c r="F100" t="str">
         <v>16.67%</v>
@@ -2403,7 +2403,7 @@
     </row>
     <row r="101">
       <c r="A101">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B101" t="str">
         <v>Paniola Ranch</v>
@@ -2412,10 +2412,10 @@
         <v>Main Area</v>
       </c>
       <c r="D101" t="str">
-        <v>Miltank</v>
+        <v>Mudbray</v>
       </c>
       <c r="E101" t="str">
-        <v>25-30</v>
+        <v>21-26</v>
       </c>
       <c r="F101" t="str">
         <v>16.67%</v>
@@ -2426,59 +2426,59 @@
         <v>21</v>
       </c>
       <c r="B102" t="str">
-        <v>Daycare</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C102" t="str">
-        <v>Daycare</v>
+        <v>Main Area</v>
       </c>
       <c r="D102" t="str">
-        <v>NPC</v>
+        <v>Mareep</v>
       </c>
       <c r="E102" t="str">
-        <v>-</v>
+        <v>21-26</v>
       </c>
       <c r="F102" t="str">
-        <v>-</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="103">
       <c r="A103">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B103" t="str">
-        <v>Route 5</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C103" t="str">
         <v>Main Area</v>
       </c>
       <c r="D103" t="str">
-        <v>Pikipek</v>
+        <v>Tauros</v>
       </c>
       <c r="E103" t="str">
-        <v>28-33</v>
+        <v>21-26</v>
       </c>
       <c r="F103" t="str">
-        <v>12.50%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="104">
       <c r="A104">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B104" t="str">
-        <v>Route 5</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C104" t="str">
         <v>Main Area</v>
       </c>
       <c r="D104" t="str">
-        <v>Metapod</v>
+        <v>Miltank</v>
       </c>
       <c r="E104" t="str">
-        <v>28-33</v>
+        <v>21-26</v>
       </c>
       <c r="F104" t="str">
-        <v>12.50%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="105">
@@ -2486,24 +2486,24 @@
         <v>22</v>
       </c>
       <c r="B105" t="str">
-        <v>Route 5</v>
+        <v>Daycare</v>
       </c>
       <c r="C105" t="str">
-        <v>Main Area</v>
+        <v>NPC</v>
       </c>
       <c r="D105" t="str">
-        <v>Grubbin</v>
+        <v>NPC</v>
       </c>
       <c r="E105" t="str">
-        <v>28-33</v>
+        <v>-</v>
       </c>
       <c r="F105" t="str">
-        <v>12.50%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="106">
       <c r="A106">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B106" t="str">
         <v>Route 5</v>
@@ -2512,10 +2512,10 @@
         <v>Main Area</v>
       </c>
       <c r="D106" t="str">
-        <v>Crabrawler</v>
+        <v>Pikipek</v>
       </c>
       <c r="E106" t="str">
-        <v>28-33</v>
+        <v>25-30</v>
       </c>
       <c r="F106" t="str">
         <v>12.50%</v>
@@ -2523,7 +2523,7 @@
     </row>
     <row r="107">
       <c r="A107">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B107" t="str">
         <v>Route 5</v>
@@ -2532,10 +2532,10 @@
         <v>Main Area</v>
       </c>
       <c r="D107" t="str">
-        <v>Noibat</v>
+        <v>Metapod</v>
       </c>
       <c r="E107" t="str">
-        <v>28-33</v>
+        <v>25-30</v>
       </c>
       <c r="F107" t="str">
         <v>12.50%</v>
@@ -2543,7 +2543,7 @@
     </row>
     <row r="108">
       <c r="A108">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B108" t="str">
         <v>Route 5</v>
@@ -2552,10 +2552,10 @@
         <v>Main Area</v>
       </c>
       <c r="D108" t="str">
-        <v>Lillipup</v>
+        <v>Grubbin</v>
       </c>
       <c r="E108" t="str">
-        <v>28-33</v>
+        <v>25-30</v>
       </c>
       <c r="F108" t="str">
         <v>12.50%</v>
@@ -2563,7 +2563,7 @@
     </row>
     <row r="109">
       <c r="A109">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B109" t="str">
         <v>Route 5</v>
@@ -2572,10 +2572,10 @@
         <v>Main Area</v>
       </c>
       <c r="D109" t="str">
-        <v>Fomantis</v>
+        <v>Crabrawler</v>
       </c>
       <c r="E109" t="str">
-        <v>28-33</v>
+        <v>25-30</v>
       </c>
       <c r="F109" t="str">
         <v>12.50%</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="110">
       <c r="A110">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B110" t="str">
         <v>Route 5</v>
@@ -2592,10 +2592,10 @@
         <v>Main Area</v>
       </c>
       <c r="D110" t="str">
-        <v>Bounsweet</v>
+        <v>Noibat</v>
       </c>
       <c r="E110" t="str">
-        <v>28-33</v>
+        <v>25-30</v>
       </c>
       <c r="F110" t="str">
         <v>12.50%</v>
@@ -2606,16 +2606,16 @@
         <v>23</v>
       </c>
       <c r="B111" t="str">
-        <v>Brooklet Hill</v>
+        <v>Route 5</v>
       </c>
       <c r="C111" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D111" t="str">
-        <v>Magikarp</v>
+        <v>Lillipup</v>
       </c>
       <c r="E111" t="str">
-        <v>29-34</v>
+        <v>25-30</v>
       </c>
       <c r="F111" t="str">
         <v>12.50%</v>
@@ -2626,16 +2626,16 @@
         <v>23</v>
       </c>
       <c r="B112" t="str">
-        <v>Brooklet Hill</v>
+        <v>Route 5</v>
       </c>
       <c r="C112" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D112" t="str">
-        <v>Psyduck</v>
+        <v>Fomantis</v>
       </c>
       <c r="E112" t="str">
-        <v>29-34</v>
+        <v>25-30</v>
       </c>
       <c r="F112" t="str">
         <v>12.50%</v>
@@ -2646,16 +2646,16 @@
         <v>23</v>
       </c>
       <c r="B113" t="str">
-        <v>Brooklet Hill</v>
+        <v>Route 5</v>
       </c>
       <c r="C113" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D113" t="str">
-        <v>Surskit</v>
+        <v>Bounsweet</v>
       </c>
       <c r="E113" t="str">
-        <v>29-34</v>
+        <v>25-30</v>
       </c>
       <c r="F113" t="str">
         <v>12.50%</v>
@@ -2663,7 +2663,7 @@
     </row>
     <row r="114">
       <c r="A114">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B114" t="str">
         <v>Brooklet Hill</v>
@@ -2672,10 +2672,10 @@
         <v>North</v>
       </c>
       <c r="D114" t="str">
-        <v>Dewpider</v>
+        <v>Magikarp</v>
       </c>
       <c r="E114" t="str">
-        <v>29-34</v>
+        <v>26-31</v>
       </c>
       <c r="F114" t="str">
         <v>12.50%</v>
@@ -2683,7 +2683,7 @@
     </row>
     <row r="115">
       <c r="A115">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B115" t="str">
         <v>Brooklet Hill</v>
@@ -2692,10 +2692,10 @@
         <v>North</v>
       </c>
       <c r="D115" t="str">
-        <v>Poliwag</v>
+        <v>Psyduck</v>
       </c>
       <c r="E115" t="str">
-        <v>29-34</v>
+        <v>26-31</v>
       </c>
       <c r="F115" t="str">
         <v>12.50%</v>
@@ -2703,7 +2703,7 @@
     </row>
     <row r="116">
       <c r="A116">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B116" t="str">
         <v>Brooklet Hill</v>
@@ -2715,7 +2715,7 @@
         <v>Surskit</v>
       </c>
       <c r="E116" t="str">
-        <v>29-34</v>
+        <v>26-31</v>
       </c>
       <c r="F116" t="str">
         <v>12.50%</v>
@@ -2723,7 +2723,7 @@
     </row>
     <row r="117">
       <c r="A117">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B117" t="str">
         <v>Brooklet Hill</v>
@@ -2735,7 +2735,7 @@
         <v>Dewpider</v>
       </c>
       <c r="E117" t="str">
-        <v>29-34</v>
+        <v>26-31</v>
       </c>
       <c r="F117" t="str">
         <v>12.50%</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="118">
       <c r="A118">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B118" t="str">
         <v>Brooklet Hill</v>
@@ -2752,10 +2752,10 @@
         <v>North</v>
       </c>
       <c r="D118" t="str">
-        <v>Morelull</v>
+        <v>Poliwag</v>
       </c>
       <c r="E118" t="str">
-        <v>29-34</v>
+        <v>26-31</v>
       </c>
       <c r="F118" t="str">
         <v>12.50%</v>
@@ -2769,16 +2769,16 @@
         <v>Brooklet Hill</v>
       </c>
       <c r="C119" t="str">
-        <v>South</v>
+        <v>North</v>
       </c>
       <c r="D119" t="str">
-        <v>Wingull</v>
+        <v>Surskit</v>
       </c>
       <c r="E119" t="str">
-        <v>30-35</v>
+        <v>26-31</v>
       </c>
       <c r="F119" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="120">
@@ -2789,16 +2789,16 @@
         <v>Brooklet Hill</v>
       </c>
       <c r="C120" t="str">
-        <v>South</v>
+        <v>North</v>
       </c>
       <c r="D120" t="str">
-        <v>Lillipup</v>
+        <v>Dewpider</v>
       </c>
       <c r="E120" t="str">
-        <v>30-35</v>
+        <v>26-31</v>
       </c>
       <c r="F120" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="121">
@@ -2809,21 +2809,21 @@
         <v>Brooklet Hill</v>
       </c>
       <c r="C121" t="str">
-        <v>South</v>
+        <v>North</v>
       </c>
       <c r="D121" t="str">
-        <v>Psyduck</v>
+        <v>Morelull</v>
       </c>
       <c r="E121" t="str">
-        <v>30-35</v>
+        <v>26-31</v>
       </c>
       <c r="F121" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="122">
       <c r="A122">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B122" t="str">
         <v>Brooklet Hill</v>
@@ -2832,10 +2832,10 @@
         <v>South</v>
       </c>
       <c r="D122" t="str">
-        <v>Paras</v>
+        <v>Wingull</v>
       </c>
       <c r="E122" t="str">
-        <v>30-35</v>
+        <v>26-31</v>
       </c>
       <c r="F122" t="str">
         <v>14.29%</v>
@@ -2843,7 +2843,7 @@
     </row>
     <row r="123">
       <c r="A123">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B123" t="str">
         <v>Brooklet Hill</v>
@@ -2852,10 +2852,10 @@
         <v>South</v>
       </c>
       <c r="D123" t="str">
-        <v>Poliwag</v>
+        <v>Lillipup</v>
       </c>
       <c r="E123" t="str">
-        <v>30-35</v>
+        <v>26-31</v>
       </c>
       <c r="F123" t="str">
         <v>14.29%</v>
@@ -2863,7 +2863,7 @@
     </row>
     <row r="124">
       <c r="A124">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B124" t="str">
         <v>Brooklet Hill</v>
@@ -2872,10 +2872,10 @@
         <v>South</v>
       </c>
       <c r="D124" t="str">
-        <v>Goldeen</v>
+        <v>Psyduck</v>
       </c>
       <c r="E124" t="str">
-        <v>30-35</v>
+        <v>26-31</v>
       </c>
       <c r="F124" t="str">
         <v>14.29%</v>
@@ -2883,7 +2883,7 @@
     </row>
     <row r="125">
       <c r="A125">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B125" t="str">
         <v>Brooklet Hill</v>
@@ -2892,10 +2892,10 @@
         <v>South</v>
       </c>
       <c r="D125" t="str">
-        <v>Feebas</v>
+        <v>Paras</v>
       </c>
       <c r="E125" t="str">
-        <v>30-35</v>
+        <v>26-31</v>
       </c>
       <c r="F125" t="str">
         <v>14.29%</v>
@@ -2906,59 +2906,59 @@
         <v>25</v>
       </c>
       <c r="B126" t="str">
-        <v>Captain Lana (Boss)</v>
+        <v>Brooklet Hill</v>
       </c>
       <c r="C126" t="str">
-        <v>Boss Battle</v>
+        <v>South</v>
       </c>
       <c r="D126" t="str">
-        <v>Boss</v>
+        <v>Poliwag</v>
       </c>
       <c r="E126" t="str">
-        <v>33-38</v>
+        <v>26-31</v>
       </c>
       <c r="F126" t="str">
-        <v>-</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="127">
       <c r="A127">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B127" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Brooklet Hill</v>
       </c>
       <c r="C127" t="str">
-        <v>Main Area</v>
+        <v>South</v>
       </c>
       <c r="D127" t="str">
-        <v>Salandit</v>
+        <v>Goldeen</v>
       </c>
       <c r="E127" t="str">
-        <v>33-38</v>
+        <v>26-31</v>
       </c>
       <c r="F127" t="str">
-        <v>16.67%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="128">
       <c r="A128">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B128" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Brooklet Hill</v>
       </c>
       <c r="C128" t="str">
-        <v>Main Area</v>
+        <v>South</v>
       </c>
       <c r="D128" t="str">
-        <v>Fletchling</v>
+        <v>Feebas</v>
       </c>
       <c r="E128" t="str">
-        <v>33-38</v>
+        <v>26-31</v>
       </c>
       <c r="F128" t="str">
-        <v>16.67%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="129">
@@ -2966,24 +2966,24 @@
         <v>26</v>
       </c>
       <c r="B129" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Captain Lana</v>
       </c>
       <c r="C129" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D129" t="str">
-        <v>Cubone</v>
+        <v>Boss</v>
       </c>
       <c r="E129" t="str">
-        <v>33-38</v>
+        <v>28-33</v>
       </c>
       <c r="F129" t="str">
-        <v>16.67%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="130">
       <c r="A130">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B130" t="str">
         <v>Wela Volcano Park</v>
@@ -2992,10 +2992,10 @@
         <v>Main Area</v>
       </c>
       <c r="D130" t="str">
-        <v>Kangaskhan</v>
+        <v>Salandit</v>
       </c>
       <c r="E130" t="str">
-        <v>33-38</v>
+        <v>29-34</v>
       </c>
       <c r="F130" t="str">
         <v>16.67%</v>
@@ -3003,7 +3003,7 @@
     </row>
     <row r="131">
       <c r="A131">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B131" t="str">
         <v>Wela Volcano Park</v>
@@ -3012,10 +3012,10 @@
         <v>Main Area</v>
       </c>
       <c r="D131" t="str">
-        <v>Magby</v>
+        <v>Fletchling</v>
       </c>
       <c r="E131" t="str">
-        <v>33-38</v>
+        <v>29-34</v>
       </c>
       <c r="F131" t="str">
         <v>16.67%</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="132">
       <c r="A132">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B132" t="str">
         <v>Wela Volcano Park</v>
@@ -3032,10 +3032,10 @@
         <v>Main Area</v>
       </c>
       <c r="D132" t="str">
-        <v>Nihilego</v>
+        <v>Cubone</v>
       </c>
       <c r="E132" t="str">
-        <v>33-38</v>
+        <v>29-34</v>
       </c>
       <c r="F132" t="str">
         <v>16.67%</v>
@@ -3046,59 +3046,59 @@
         <v>27</v>
       </c>
       <c r="B133" t="str">
-        <v>Captain Kiawe (Boss)</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C133" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D133" t="str">
-        <v>Boss</v>
+        <v>Kangaskhan</v>
       </c>
       <c r="E133" t="str">
-        <v>35-40</v>
+        <v>29-34</v>
       </c>
       <c r="F133" t="str">
-        <v>-</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="134">
       <c r="A134">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B134" t="str">
-        <v>Route 8</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C134" t="str">
-        <v>Fossil Restoration Center</v>
+        <v>Main Area</v>
       </c>
       <c r="D134" t="str">
-        <v>Omanyte</v>
+        <v>Magby</v>
       </c>
       <c r="E134" t="str">
-        <v>35-40</v>
+        <v>29-34</v>
       </c>
       <c r="F134" t="str">
-        <v>10.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="135">
       <c r="A135">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B135" t="str">
-        <v>Route 8</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C135" t="str">
-        <v>Fossil Restoration Center</v>
+        <v>Main Area</v>
       </c>
       <c r="D135" t="str">
-        <v>Kabuto</v>
+        <v>Nihilego</v>
       </c>
       <c r="E135" t="str">
-        <v>35-40</v>
+        <v>29-34</v>
       </c>
       <c r="F135" t="str">
-        <v>10.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="136">
@@ -3106,24 +3106,24 @@
         <v>28</v>
       </c>
       <c r="B136" t="str">
-        <v>Route 8</v>
+        <v>Captain Kiawe</v>
       </c>
       <c r="C136" t="str">
-        <v>Fossil Restoration Center</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D136" t="str">
-        <v>Lileep</v>
+        <v>Boss</v>
       </c>
       <c r="E136" t="str">
-        <v>35-40</v>
+        <v>31-36</v>
       </c>
       <c r="F136" t="str">
-        <v>10.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="137">
       <c r="A137">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B137" t="str">
         <v>Route 8</v>
@@ -3132,10 +3132,10 @@
         <v>Fossil Restoration Center</v>
       </c>
       <c r="D137" t="str">
-        <v>Anorith</v>
+        <v>Omanyte</v>
       </c>
       <c r="E137" t="str">
-        <v>35-40</v>
+        <v>33-38</v>
       </c>
       <c r="F137" t="str">
         <v>10.00%</v>
@@ -3143,7 +3143,7 @@
     </row>
     <row r="138">
       <c r="A138">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B138" t="str">
         <v>Route 8</v>
@@ -3152,10 +3152,10 @@
         <v>Fossil Restoration Center</v>
       </c>
       <c r="D138" t="str">
-        <v>Cranidos</v>
+        <v>Kabuto</v>
       </c>
       <c r="E138" t="str">
-        <v>35-40</v>
+        <v>33-38</v>
       </c>
       <c r="F138" t="str">
         <v>10.00%</v>
@@ -3163,7 +3163,7 @@
     </row>
     <row r="139">
       <c r="A139">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B139" t="str">
         <v>Route 8</v>
@@ -3172,10 +3172,10 @@
         <v>Fossil Restoration Center</v>
       </c>
       <c r="D139" t="str">
-        <v>Shieldon</v>
+        <v>Lileep</v>
       </c>
       <c r="E139" t="str">
-        <v>35-40</v>
+        <v>33-38</v>
       </c>
       <c r="F139" t="str">
         <v>10.00%</v>
@@ -3183,7 +3183,7 @@
     </row>
     <row r="140">
       <c r="A140">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B140" t="str">
         <v>Route 8</v>
@@ -3192,10 +3192,10 @@
         <v>Fossil Restoration Center</v>
       </c>
       <c r="D140" t="str">
-        <v>Archen</v>
+        <v>Anorith</v>
       </c>
       <c r="E140" t="str">
-        <v>35-40</v>
+        <v>33-38</v>
       </c>
       <c r="F140" t="str">
         <v>10.00%</v>
@@ -3203,7 +3203,7 @@
     </row>
     <row r="141">
       <c r="A141">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B141" t="str">
         <v>Route 8</v>
@@ -3212,10 +3212,10 @@
         <v>Fossil Restoration Center</v>
       </c>
       <c r="D141" t="str">
-        <v>Tirtouga</v>
+        <v>Cranidos</v>
       </c>
       <c r="E141" t="str">
-        <v>35-40</v>
+        <v>33-38</v>
       </c>
       <c r="F141" t="str">
         <v>10.00%</v>
@@ -3223,7 +3223,7 @@
     </row>
     <row r="142">
       <c r="A142">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B142" t="str">
         <v>Route 8</v>
@@ -3232,10 +3232,10 @@
         <v>Fossil Restoration Center</v>
       </c>
       <c r="D142" t="str">
-        <v>Tyrunt</v>
+        <v>Shieldon</v>
       </c>
       <c r="E142" t="str">
-        <v>35-40</v>
+        <v>33-38</v>
       </c>
       <c r="F142" t="str">
         <v>10.00%</v>
@@ -3243,7 +3243,7 @@
     </row>
     <row r="143">
       <c r="A143">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B143" t="str">
         <v>Route 8</v>
@@ -3252,10 +3252,10 @@
         <v>Fossil Restoration Center</v>
       </c>
       <c r="D143" t="str">
-        <v>Amaura</v>
+        <v>Archen</v>
       </c>
       <c r="E143" t="str">
-        <v>35-40</v>
+        <v>33-38</v>
       </c>
       <c r="F143" t="str">
         <v>10.00%</v>
@@ -3269,16 +3269,16 @@
         <v>Route 8</v>
       </c>
       <c r="C144" t="str">
-        <v>Main</v>
+        <v>Fossil Restoration Center</v>
       </c>
       <c r="D144" t="str">
-        <v>Arbok</v>
+        <v>Tirtouga</v>
       </c>
       <c r="E144" t="str">
-        <v>36-41</v>
+        <v>33-38</v>
       </c>
       <c r="F144" t="str">
-        <v>20.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="145">
@@ -3289,16 +3289,16 @@
         <v>Route 8</v>
       </c>
       <c r="C145" t="str">
-        <v>Main</v>
+        <v>Fossil Restoration Center</v>
       </c>
       <c r="D145" t="str">
-        <v>Stufful</v>
+        <v>Tyrunt</v>
       </c>
       <c r="E145" t="str">
-        <v>36-41</v>
+        <v>33-38</v>
       </c>
       <c r="F145" t="str">
-        <v>20.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="146">
@@ -3309,21 +3309,21 @@
         <v>Route 8</v>
       </c>
       <c r="C146" t="str">
-        <v>Main</v>
+        <v>Fossil Restoration Center</v>
       </c>
       <c r="D146" t="str">
-        <v>Wimpod</v>
+        <v>Amaura</v>
       </c>
       <c r="E146" t="str">
-        <v>36-41</v>
+        <v>33-38</v>
       </c>
       <c r="F146" t="str">
-        <v>20.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="147">
       <c r="A147">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B147" t="str">
         <v>Route 8</v>
@@ -3332,10 +3332,10 @@
         <v>Main</v>
       </c>
       <c r="D147" t="str">
-        <v>Fletchinder</v>
+        <v>Arbok</v>
       </c>
       <c r="E147" t="str">
-        <v>36-41</v>
+        <v>33-38</v>
       </c>
       <c r="F147" t="str">
         <v>20.00%</v>
@@ -3343,7 +3343,7 @@
     </row>
     <row r="148">
       <c r="A148">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B148" t="str">
         <v>Route 8</v>
@@ -3352,10 +3352,10 @@
         <v>Main</v>
       </c>
       <c r="D148" t="str">
-        <v>Chinchou</v>
+        <v>Stufful</v>
       </c>
       <c r="E148" t="str">
-        <v>36-41</v>
+        <v>33-38</v>
       </c>
       <c r="F148" t="str">
         <v>20.00%</v>
@@ -3366,19 +3366,19 @@
         <v>30</v>
       </c>
       <c r="B149" t="str">
-        <v>Lush Jungle</v>
+        <v>Route 8</v>
       </c>
       <c r="C149" t="str">
-        <v>East Cave</v>
+        <v>Main</v>
       </c>
       <c r="D149" t="str">
-        <v>Golbat</v>
+        <v>Wimpod</v>
       </c>
       <c r="E149" t="str">
-        <v>38-43</v>
+        <v>33-38</v>
       </c>
       <c r="F149" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="150">
@@ -3386,19 +3386,19 @@
         <v>30</v>
       </c>
       <c r="B150" t="str">
-        <v>Lush Jungle</v>
+        <v>Route 8</v>
       </c>
       <c r="C150" t="str">
-        <v>East Cave</v>
+        <v>Main</v>
       </c>
       <c r="D150" t="str">
-        <v>Dugtrio</v>
+        <v>Fletchinder</v>
       </c>
       <c r="E150" t="str">
-        <v>38-43</v>
+        <v>33-38</v>
       </c>
       <c r="F150" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="151">
@@ -3406,24 +3406,24 @@
         <v>30</v>
       </c>
       <c r="B151" t="str">
-        <v>Lush Jungle</v>
+        <v>Route 8</v>
       </c>
       <c r="C151" t="str">
-        <v>East Cave</v>
+        <v>Main</v>
       </c>
       <c r="D151" t="str">
-        <v>Salandit</v>
+        <v>Chinchou</v>
       </c>
       <c r="E151" t="str">
-        <v>38-43</v>
+        <v>33-38</v>
       </c>
       <c r="F151" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="152">
       <c r="A152">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B152" t="str">
         <v>Lush Jungle</v>
@@ -3432,10 +3432,10 @@
         <v>East Cave</v>
       </c>
       <c r="D152" t="str">
-        <v>Larvesta</v>
+        <v>Golbat</v>
       </c>
       <c r="E152" t="str">
-        <v>38-43</v>
+        <v>34-39</v>
       </c>
       <c r="F152" t="str">
         <v>25.00%</v>
@@ -3449,16 +3449,16 @@
         <v>Lush Jungle</v>
       </c>
       <c r="C153" t="str">
-        <v>North</v>
+        <v>East Cave</v>
       </c>
       <c r="D153" t="str">
-        <v>Trumbeak</v>
+        <v>Dugtrio</v>
       </c>
       <c r="E153" t="str">
-        <v>39-44</v>
+        <v>34-39</v>
       </c>
       <c r="F153" t="str">
-        <v>14.29%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="154">
@@ -3469,16 +3469,16 @@
         <v>Lush Jungle</v>
       </c>
       <c r="C154" t="str">
-        <v>North</v>
+        <v>East Cave</v>
       </c>
       <c r="D154" t="str">
-        <v>Pinsir</v>
+        <v>Salandit</v>
       </c>
       <c r="E154" t="str">
-        <v>39-44</v>
+        <v>34-39</v>
       </c>
       <c r="F154" t="str">
-        <v>14.29%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="155">
@@ -3489,21 +3489,21 @@
         <v>Lush Jungle</v>
       </c>
       <c r="C155" t="str">
-        <v>North</v>
+        <v>East Cave</v>
       </c>
       <c r="D155" t="str">
-        <v>Steenee</v>
+        <v>Larvesta</v>
       </c>
       <c r="E155" t="str">
-        <v>39-44</v>
+        <v>34-39</v>
       </c>
       <c r="F155" t="str">
-        <v>14.29%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="156">
       <c r="A156">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B156" t="str">
         <v>Lush Jungle</v>
@@ -3512,10 +3512,10 @@
         <v>North</v>
       </c>
       <c r="D156" t="str">
-        <v>Comfey</v>
+        <v>Trumbeak</v>
       </c>
       <c r="E156" t="str">
-        <v>39-44</v>
+        <v>34-39</v>
       </c>
       <c r="F156" t="str">
         <v>14.29%</v>
@@ -3523,7 +3523,7 @@
     </row>
     <row r="157">
       <c r="A157">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B157" t="str">
         <v>Lush Jungle</v>
@@ -3532,10 +3532,10 @@
         <v>North</v>
       </c>
       <c r="D157" t="str">
-        <v>Hoothoot</v>
+        <v>Pinsir</v>
       </c>
       <c r="E157" t="str">
-        <v>39-44</v>
+        <v>34-39</v>
       </c>
       <c r="F157" t="str">
         <v>14.29%</v>
@@ -3543,7 +3543,7 @@
     </row>
     <row r="158">
       <c r="A158">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B158" t="str">
         <v>Lush Jungle</v>
@@ -3552,10 +3552,10 @@
         <v>North</v>
       </c>
       <c r="D158" t="str">
-        <v>Oranguru</v>
+        <v>Steenee</v>
       </c>
       <c r="E158" t="str">
-        <v>39-44</v>
+        <v>34-39</v>
       </c>
       <c r="F158" t="str">
         <v>14.29%</v>
@@ -3563,7 +3563,7 @@
     </row>
     <row r="159">
       <c r="A159">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B159" t="str">
         <v>Lush Jungle</v>
@@ -3572,10 +3572,10 @@
         <v>North</v>
       </c>
       <c r="D159" t="str">
-        <v>Passimian</v>
+        <v>Comfey</v>
       </c>
       <c r="E159" t="str">
-        <v>39-44</v>
+        <v>34-39</v>
       </c>
       <c r="F159" t="str">
         <v>14.29%</v>
@@ -3586,59 +3586,59 @@
         <v>32</v>
       </c>
       <c r="B160" t="str">
-        <v>Captain Mallow (Boss)</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C160" t="str">
-        <v>Boss Battle</v>
+        <v>North</v>
       </c>
       <c r="D160" t="str">
-        <v>Boss</v>
+        <v>Hoothoot</v>
       </c>
       <c r="E160" t="str">
-        <v>41-46</v>
+        <v>34-39</v>
       </c>
       <c r="F160" t="str">
-        <v>-</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="161">
       <c r="A161">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B161" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C161" t="str">
-        <v>Main Area</v>
+        <v>North</v>
       </c>
       <c r="D161" t="str">
-        <v>Zubat</v>
+        <v>Oranguru</v>
       </c>
       <c r="E161" t="str">
-        <v>41-46</v>
+        <v>34-39</v>
       </c>
       <c r="F161" t="str">
-        <v>25.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="162">
       <c r="A162">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B162" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C162" t="str">
-        <v>Main Area</v>
+        <v>North</v>
       </c>
       <c r="D162" t="str">
-        <v>Alolan Diglett</v>
+        <v>Passimian</v>
       </c>
       <c r="E162" t="str">
-        <v>41-46</v>
+        <v>34-39</v>
       </c>
       <c r="F162" t="str">
-        <v>25.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="163">
@@ -3646,24 +3646,24 @@
         <v>33</v>
       </c>
       <c r="B163" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Captain Mallow</v>
       </c>
       <c r="C163" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D163" t="str">
-        <v>Kecleon</v>
+        <v>Boss</v>
       </c>
       <c r="E163" t="str">
-        <v>41-46</v>
+        <v>36-41</v>
       </c>
       <c r="F163" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="164">
       <c r="A164">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B164" t="str">
         <v>Diglett's Tunnel</v>
@@ -3672,10 +3672,10 @@
         <v>Main Area</v>
       </c>
       <c r="D164" t="str">
-        <v>Larvitar</v>
+        <v>Zubat</v>
       </c>
       <c r="E164" t="str">
-        <v>41-46</v>
+        <v>38-43</v>
       </c>
       <c r="F164" t="str">
         <v>25.00%</v>
@@ -3686,19 +3686,19 @@
         <v>34</v>
       </c>
       <c r="B165" t="str">
-        <v>Konikoni City</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C165" t="str">
         <v>Main Area</v>
       </c>
       <c r="D165" t="str">
-        <v>Poliwhirl</v>
+        <v>Alolan Diglett</v>
       </c>
       <c r="E165" t="str">
-        <v>42-47</v>
+        <v>38-43</v>
       </c>
       <c r="F165" t="str">
-        <v>50.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="166">
@@ -3706,39 +3706,39 @@
         <v>34</v>
       </c>
       <c r="B166" t="str">
-        <v>Konikoni City</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C166" t="str">
         <v>Main Area</v>
       </c>
       <c r="D166" t="str">
-        <v>Ditto</v>
+        <v>Kecleon</v>
       </c>
       <c r="E166" t="str">
-        <v>42-47</v>
+        <v>38-43</v>
       </c>
       <c r="F166" t="str">
-        <v>50.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="167">
       <c r="A167">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B167" t="str">
-        <v>Memorial Hill</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C167" t="str">
-        <v>Main</v>
+        <v>Main Area</v>
       </c>
       <c r="D167" t="str">
-        <v>Zubat</v>
+        <v>Larvitar</v>
       </c>
       <c r="E167" t="str">
-        <v>44-49</v>
+        <v>38-43</v>
       </c>
       <c r="F167" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="168">
@@ -3746,19 +3746,19 @@
         <v>35</v>
       </c>
       <c r="B168" t="str">
-        <v>Memorial Hill</v>
+        <v>Konikoni City</v>
       </c>
       <c r="C168" t="str">
-        <v>Main</v>
+        <v>Main Area</v>
       </c>
       <c r="D168" t="str">
-        <v>Gastly</v>
+        <v>Poliwhirl</v>
       </c>
       <c r="E168" t="str">
-        <v>44-49</v>
+        <v>39-44</v>
       </c>
       <c r="F168" t="str">
-        <v>33.33%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="169">
@@ -3766,19 +3766,19 @@
         <v>35</v>
       </c>
       <c r="B169" t="str">
-        <v>Memorial Hill</v>
+        <v>Konikoni City</v>
       </c>
       <c r="C169" t="str">
-        <v>Main</v>
+        <v>Main Area</v>
       </c>
       <c r="D169" t="str">
-        <v>Phantump</v>
+        <v>Ditto</v>
       </c>
       <c r="E169" t="str">
-        <v>44-49</v>
+        <v>39-44</v>
       </c>
       <c r="F169" t="str">
-        <v>33.33%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="170">
@@ -3786,19 +3786,19 @@
         <v>36</v>
       </c>
       <c r="B170" t="str">
-        <v>Akala Outskirts</v>
+        <v>Memorial Hill</v>
       </c>
       <c r="C170" t="str">
-        <v>Main Area</v>
+        <v>Main</v>
       </c>
       <c r="D170" t="str">
-        <v>Gumshoos</v>
+        <v>Zubat</v>
       </c>
       <c r="E170" t="str">
-        <v>45-50</v>
+        <v>41-46</v>
       </c>
       <c r="F170" t="str">
-        <v>12.50%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="171">
@@ -3806,19 +3806,19 @@
         <v>36</v>
       </c>
       <c r="B171" t="str">
-        <v>Akala Outskirts</v>
+        <v>Memorial Hill</v>
       </c>
       <c r="C171" t="str">
-        <v>Main Area</v>
+        <v>Main</v>
       </c>
       <c r="D171" t="str">
-        <v>Wingull</v>
+        <v>Gastly</v>
       </c>
       <c r="E171" t="str">
-        <v>45-50</v>
+        <v>41-46</v>
       </c>
       <c r="F171" t="str">
-        <v>12.50%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="172">
@@ -3826,24 +3826,24 @@
         <v>36</v>
       </c>
       <c r="B172" t="str">
-        <v>Akala Outskirts</v>
+        <v>Memorial Hill</v>
       </c>
       <c r="C172" t="str">
-        <v>Main Area</v>
+        <v>Main</v>
       </c>
       <c r="D172" t="str">
-        <v>Magikarp</v>
+        <v>Phantump</v>
       </c>
       <c r="E172" t="str">
-        <v>45-50</v>
+        <v>41-46</v>
       </c>
       <c r="F172" t="str">
-        <v>12.50%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="173">
       <c r="A173">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B173" t="str">
         <v>Akala Outskirts</v>
@@ -3852,10 +3852,10 @@
         <v>Main Area</v>
       </c>
       <c r="D173" t="str">
-        <v>Stufful</v>
+        <v>Gumshoos</v>
       </c>
       <c r="E173" t="str">
-        <v>45-50</v>
+        <v>42-47</v>
       </c>
       <c r="F173" t="str">
         <v>12.50%</v>
@@ -3863,7 +3863,7 @@
     </row>
     <row r="174">
       <c r="A174">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B174" t="str">
         <v>Akala Outskirts</v>
@@ -3872,10 +3872,10 @@
         <v>Main Area</v>
       </c>
       <c r="D174" t="str">
-        <v>Chinchou</v>
+        <v>Wingull</v>
       </c>
       <c r="E174" t="str">
-        <v>45-50</v>
+        <v>42-47</v>
       </c>
       <c r="F174" t="str">
         <v>12.50%</v>
@@ -3883,7 +3883,7 @@
     </row>
     <row r="175">
       <c r="A175">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B175" t="str">
         <v>Akala Outskirts</v>
@@ -3892,10 +3892,10 @@
         <v>Main Area</v>
       </c>
       <c r="D175" t="str">
-        <v>Alolan Raticate</v>
+        <v>Magikarp</v>
       </c>
       <c r="E175" t="str">
-        <v>45-50</v>
+        <v>42-47</v>
       </c>
       <c r="F175" t="str">
         <v>12.50%</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="176">
       <c r="A176">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B176" t="str">
         <v>Akala Outskirts</v>
@@ -3912,10 +3912,10 @@
         <v>Main Area</v>
       </c>
       <c r="D176" t="str">
-        <v>Natu</v>
+        <v>Stufful</v>
       </c>
       <c r="E176" t="str">
-        <v>45-50</v>
+        <v>42-47</v>
       </c>
       <c r="F176" t="str">
         <v>12.50%</v>
@@ -3923,7 +3923,7 @@
     </row>
     <row r="177">
       <c r="A177">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B177" t="str">
         <v>Akala Outskirts</v>
@@ -3932,10 +3932,10 @@
         <v>Main Area</v>
       </c>
       <c r="D177" t="str">
-        <v>Nosepass</v>
+        <v>Chinchou</v>
       </c>
       <c r="E177" t="str">
-        <v>45-50</v>
+        <v>42-47</v>
       </c>
       <c r="F177" t="str">
         <v>12.50%</v>
@@ -3946,19 +3946,19 @@
         <v>37</v>
       </c>
       <c r="B178" t="str">
-        <v>Hano Beach</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C178" t="str">
         <v>Main Area</v>
       </c>
       <c r="D178" t="str">
-        <v>Staryu</v>
+        <v>Alolan Raticate</v>
       </c>
       <c r="E178" t="str">
-        <v>46-51</v>
+        <v>42-47</v>
       </c>
       <c r="F178" t="str">
-        <v>50.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="179">
@@ -3966,79 +3966,79 @@
         <v>37</v>
       </c>
       <c r="B179" t="str">
-        <v>Hano Beach</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C179" t="str">
         <v>Main Area</v>
       </c>
       <c r="D179" t="str">
-        <v>Sandygast</v>
+        <v>Natu</v>
       </c>
       <c r="E179" t="str">
-        <v>46-51</v>
+        <v>42-47</v>
       </c>
       <c r="F179" t="str">
-        <v>50.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="180">
       <c r="A180">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B180" t="str">
-        <v>Kahuna Olivia (Boss)</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C180" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D180" t="str">
-        <v>Boss</v>
+        <v>Nosepass</v>
       </c>
       <c r="E180" t="str">
-        <v>49-54</v>
+        <v>42-47</v>
       </c>
       <c r="F180" t="str">
-        <v>-</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="181">
       <c r="A181">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B181" t="str">
-        <v>Malie City</v>
+        <v>Hano Beach</v>
       </c>
       <c r="C181" t="str">
-        <v>Outer Cape</v>
+        <v>Main Area</v>
       </c>
       <c r="D181" t="str">
-        <v>Gumshoos</v>
+        <v>Staryu</v>
       </c>
       <c r="E181" t="str">
-        <v>49-54</v>
+        <v>44-49</v>
       </c>
       <c r="F181" t="str">
-        <v>16.67%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="182">
       <c r="A182">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B182" t="str">
-        <v>Malie City</v>
+        <v>Hano Beach</v>
       </c>
       <c r="C182" t="str">
-        <v>Outer Cape</v>
+        <v>Main Area</v>
       </c>
       <c r="D182" t="str">
-        <v>Alolan Raticate</v>
+        <v>Sandygast</v>
       </c>
       <c r="E182" t="str">
-        <v>49-54</v>
+        <v>44-49</v>
       </c>
       <c r="F182" t="str">
-        <v>16.67%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="183">
@@ -4046,24 +4046,24 @@
         <v>39</v>
       </c>
       <c r="B183" t="str">
-        <v>Malie City</v>
+        <v>Kahuna Olivia</v>
       </c>
       <c r="C183" t="str">
-        <v>Outer Cape</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D183" t="str">
-        <v>Magnemite</v>
+        <v>Boss</v>
       </c>
       <c r="E183" t="str">
-        <v>49-54</v>
+        <v>46-51</v>
       </c>
       <c r="F183" t="str">
-        <v>16.67%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="184">
       <c r="A184">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B184" t="str">
         <v>Malie City</v>
@@ -4072,10 +4072,10 @@
         <v>Outer Cape</v>
       </c>
       <c r="D184" t="str">
-        <v>Alolan Grimer</v>
+        <v>Gumshoos</v>
       </c>
       <c r="E184" t="str">
-        <v>49-54</v>
+        <v>47-52</v>
       </c>
       <c r="F184" t="str">
         <v>16.67%</v>
@@ -4083,7 +4083,7 @@
     </row>
     <row r="185">
       <c r="A185">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B185" t="str">
         <v>Malie City</v>
@@ -4092,10 +4092,10 @@
         <v>Outer Cape</v>
       </c>
       <c r="D185" t="str">
-        <v>Trubbish</v>
+        <v>Alolan Raticate</v>
       </c>
       <c r="E185" t="str">
-        <v>49-54</v>
+        <v>47-52</v>
       </c>
       <c r="F185" t="str">
         <v>16.67%</v>
@@ -4103,7 +4103,7 @@
     </row>
     <row r="186">
       <c r="A186">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B186" t="str">
         <v>Malie City</v>
@@ -4112,10 +4112,10 @@
         <v>Outer Cape</v>
       </c>
       <c r="D186" t="str">
-        <v>Minccino</v>
+        <v>Magnemite</v>
       </c>
       <c r="E186" t="str">
-        <v>49-54</v>
+        <v>47-52</v>
       </c>
       <c r="F186" t="str">
         <v>16.67%</v>
@@ -4126,16 +4126,16 @@
         <v>40</v>
       </c>
       <c r="B187" t="str">
-        <v>Malie Garden</v>
+        <v>Malie City</v>
       </c>
       <c r="C187" t="str">
-        <v>Main Area</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D187" t="str">
-        <v>Araquanid</v>
+        <v>Alolan Grimer</v>
       </c>
       <c r="E187" t="str">
-        <v>50-55</v>
+        <v>47-52</v>
       </c>
       <c r="F187" t="str">
         <v>16.67%</v>
@@ -4146,16 +4146,16 @@
         <v>40</v>
       </c>
       <c r="B188" t="str">
-        <v>Malie Garden</v>
+        <v>Malie City</v>
       </c>
       <c r="C188" t="str">
-        <v>Main Area</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D188" t="str">
-        <v>Poliwhirl</v>
+        <v>Trubbish</v>
       </c>
       <c r="E188" t="str">
-        <v>50-55</v>
+        <v>47-52</v>
       </c>
       <c r="F188" t="str">
         <v>16.67%</v>
@@ -4166,16 +4166,16 @@
         <v>40</v>
       </c>
       <c r="B189" t="str">
-        <v>Malie Garden</v>
+        <v>Malie City</v>
       </c>
       <c r="C189" t="str">
-        <v>Main Area</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D189" t="str">
-        <v>Gyarados</v>
+        <v>Minccino</v>
       </c>
       <c r="E189" t="str">
-        <v>50-55</v>
+        <v>47-52</v>
       </c>
       <c r="F189" t="str">
         <v>16.67%</v>
@@ -4183,7 +4183,7 @@
     </row>
     <row r="190">
       <c r="A190">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B190" t="str">
         <v>Malie Garden</v>
@@ -4192,10 +4192,10 @@
         <v>Main Area</v>
       </c>
       <c r="D190" t="str">
-        <v>Masquerain</v>
+        <v>Araquanid</v>
       </c>
       <c r="E190" t="str">
-        <v>50-55</v>
+        <v>49-54</v>
       </c>
       <c r="F190" t="str">
         <v>16.67%</v>
@@ -4203,7 +4203,7 @@
     </row>
     <row r="191">
       <c r="A191">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B191" t="str">
         <v>Malie Garden</v>
@@ -4212,10 +4212,10 @@
         <v>Main Area</v>
       </c>
       <c r="D191" t="str">
-        <v>Celesteela</v>
+        <v>Poliwhirl</v>
       </c>
       <c r="E191" t="str">
-        <v>50-55</v>
+        <v>49-54</v>
       </c>
       <c r="F191" t="str">
         <v>16.67%</v>
@@ -4223,7 +4223,7 @@
     </row>
     <row r="192">
       <c r="A192">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B192" t="str">
         <v>Malie Garden</v>
@@ -4232,10 +4232,10 @@
         <v>Main Area</v>
       </c>
       <c r="D192" t="str">
-        <v>Kartana</v>
+        <v>Gyarados</v>
       </c>
       <c r="E192" t="str">
-        <v>50-55</v>
+        <v>49-54</v>
       </c>
       <c r="F192" t="str">
         <v>16.67%</v>
@@ -4246,19 +4246,19 @@
         <v>41</v>
       </c>
       <c r="B193" t="str">
-        <v>Route 10</v>
+        <v>Malie Garden</v>
       </c>
       <c r="C193" t="str">
         <v>Main Area</v>
       </c>
       <c r="D193" t="str">
-        <v>Gumshoos</v>
+        <v>Masquerain</v>
       </c>
       <c r="E193" t="str">
-        <v>51-56</v>
+        <v>49-54</v>
       </c>
       <c r="F193" t="str">
-        <v>12.50%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="194">
@@ -4266,19 +4266,19 @@
         <v>41</v>
       </c>
       <c r="B194" t="str">
-        <v>Route 10</v>
+        <v>Malie Garden</v>
       </c>
       <c r="C194" t="str">
         <v>Main Area</v>
       </c>
       <c r="D194" t="str">
-        <v>Alolan Raticate</v>
+        <v>Celesteela</v>
       </c>
       <c r="E194" t="str">
-        <v>51-56</v>
+        <v>49-54</v>
       </c>
       <c r="F194" t="str">
-        <v>12.50%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="195">
@@ -4286,24 +4286,24 @@
         <v>41</v>
       </c>
       <c r="B195" t="str">
-        <v>Route 10</v>
+        <v>Malie Garden</v>
       </c>
       <c r="C195" t="str">
         <v>Main Area</v>
       </c>
       <c r="D195" t="str">
-        <v>Ledian</v>
+        <v>Kartana</v>
       </c>
       <c r="E195" t="str">
-        <v>51-56</v>
+        <v>49-54</v>
       </c>
       <c r="F195" t="str">
-        <v>12.50%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="196">
       <c r="A196">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B196" t="str">
         <v>Route 10</v>
@@ -4312,10 +4312,10 @@
         <v>Main Area</v>
       </c>
       <c r="D196" t="str">
-        <v>Ariados</v>
+        <v>Gumshoos</v>
       </c>
       <c r="E196" t="str">
-        <v>51-56</v>
+        <v>50-55</v>
       </c>
       <c r="F196" t="str">
         <v>12.50%</v>
@@ -4323,7 +4323,7 @@
     </row>
     <row r="197">
       <c r="A197">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B197" t="str">
         <v>Route 10</v>
@@ -4332,10 +4332,10 @@
         <v>Main Area</v>
       </c>
       <c r="D197" t="str">
-        <v>Crabrawler</v>
+        <v>Alolan Raticate</v>
       </c>
       <c r="E197" t="str">
-        <v>51-56</v>
+        <v>50-55</v>
       </c>
       <c r="F197" t="str">
         <v>12.50%</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="198">
       <c r="A198">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B198" t="str">
         <v>Route 10</v>
@@ -4352,10 +4352,10 @@
         <v>Main Area</v>
       </c>
       <c r="D198" t="str">
-        <v>Fearow</v>
+        <v>Ledian</v>
       </c>
       <c r="E198" t="str">
-        <v>51-56</v>
+        <v>50-55</v>
       </c>
       <c r="F198" t="str">
         <v>12.50%</v>
@@ -4363,7 +4363,7 @@
     </row>
     <row r="199">
       <c r="A199">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B199" t="str">
         <v>Route 10</v>
@@ -4372,10 +4372,10 @@
         <v>Main Area</v>
       </c>
       <c r="D199" t="str">
-        <v>Skarmory</v>
+        <v>Ariados</v>
       </c>
       <c r="E199" t="str">
-        <v>51-56</v>
+        <v>50-55</v>
       </c>
       <c r="F199" t="str">
         <v>12.50%</v>
@@ -4383,7 +4383,7 @@
     </row>
     <row r="200">
       <c r="A200">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B200" t="str">
         <v>Route 10</v>
@@ -4392,10 +4392,10 @@
         <v>Main Area</v>
       </c>
       <c r="D200" t="str">
-        <v>Pancham</v>
+        <v>Crabrawler</v>
       </c>
       <c r="E200" t="str">
-        <v>51-56</v>
+        <v>50-55</v>
       </c>
       <c r="F200" t="str">
         <v>12.50%</v>
@@ -4406,19 +4406,19 @@
         <v>42</v>
       </c>
       <c r="B201" t="str">
-        <v>Mount Hokulani</v>
+        <v>Route 10</v>
       </c>
       <c r="C201" t="str">
-        <v>East</v>
+        <v>Main Area</v>
       </c>
       <c r="D201" t="str">
-        <v>Cleffa</v>
+        <v>Fearow</v>
       </c>
       <c r="E201" t="str">
-        <v>52-57</v>
+        <v>50-55</v>
       </c>
       <c r="F201" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="202">
@@ -4426,19 +4426,19 @@
         <v>42</v>
       </c>
       <c r="B202" t="str">
-        <v>Mount Hokulani</v>
+        <v>Route 10</v>
       </c>
       <c r="C202" t="str">
-        <v>East</v>
+        <v>Main Area</v>
       </c>
       <c r="D202" t="str">
-        <v>Elgyem</v>
+        <v>Skarmory</v>
       </c>
       <c r="E202" t="str">
-        <v>52-57</v>
+        <v>50-55</v>
       </c>
       <c r="F202" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="203">
@@ -4446,19 +4446,19 @@
         <v>42</v>
       </c>
       <c r="B203" t="str">
-        <v>Mount Hokulani</v>
+        <v>Route 10</v>
       </c>
       <c r="C203" t="str">
-        <v>East</v>
+        <v>Main Area</v>
       </c>
       <c r="D203" t="str">
-        <v>Beldum</v>
+        <v>Pancham</v>
       </c>
       <c r="E203" t="str">
-        <v>52-57</v>
+        <v>50-55</v>
       </c>
       <c r="F203" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="204">
@@ -4469,76 +4469,76 @@
         <v>Mount Hokulani</v>
       </c>
       <c r="C204" t="str">
-        <v>West</v>
+        <v>East</v>
       </c>
       <c r="D204" t="str">
-        <v>Elekid</v>
+        <v>Cleffa</v>
       </c>
       <c r="E204" t="str">
-        <v>54-59</v>
+        <v>52-57</v>
       </c>
       <c r="F204" t="str">
-        <v>100.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="205">
       <c r="A205">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B205" t="str">
-        <v>Captain Sophocles (Boss)</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C205" t="str">
-        <v>Boss Battle</v>
+        <v>East</v>
       </c>
       <c r="D205" t="str">
-        <v>Boss</v>
+        <v>Elgyem</v>
       </c>
       <c r="E205" t="str">
-        <v>56-61</v>
+        <v>52-57</v>
       </c>
       <c r="F205" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="206">
       <c r="A206">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B206" t="str">
-        <v>Route 11</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C206" t="str">
-        <v>Main Area</v>
+        <v>East</v>
       </c>
       <c r="D206" t="str">
-        <v>Gumshoos</v>
+        <v>Beldum</v>
       </c>
       <c r="E206" t="str">
-        <v>56-61</v>
+        <v>52-57</v>
       </c>
       <c r="F206" t="str">
-        <v>14.29%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="207">
       <c r="A207">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B207" t="str">
-        <v>Route 11</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C207" t="str">
-        <v>Main Area</v>
+        <v>West</v>
       </c>
       <c r="D207" t="str">
-        <v>Alolan Raticate</v>
+        <v>Elekid</v>
       </c>
       <c r="E207" t="str">
-        <v>56-61</v>
+        <v>52-57</v>
       </c>
       <c r="F207" t="str">
-        <v>14.29%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="208">
@@ -4546,24 +4546,24 @@
         <v>45</v>
       </c>
       <c r="B208" t="str">
-        <v>Route 11</v>
+        <v>Captain Sophocles</v>
       </c>
       <c r="C208" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D208" t="str">
-        <v>Ariados</v>
+        <v>Boss</v>
       </c>
       <c r="E208" t="str">
-        <v>56-61</v>
+        <v>54-59</v>
       </c>
       <c r="F208" t="str">
-        <v>14.29%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="209">
       <c r="A209">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B209" t="str">
         <v>Route 11</v>
@@ -4572,10 +4572,10 @@
         <v>Main Area</v>
       </c>
       <c r="D209" t="str">
-        <v>Pancham</v>
+        <v>Gumshoos</v>
       </c>
       <c r="E209" t="str">
-        <v>56-61</v>
+        <v>55-60</v>
       </c>
       <c r="F209" t="str">
         <v>14.29%</v>
@@ -4583,7 +4583,7 @@
     </row>
     <row r="210">
       <c r="A210">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B210" t="str">
         <v>Route 11</v>
@@ -4592,10 +4592,10 @@
         <v>Main Area</v>
       </c>
       <c r="D210" t="str">
-        <v>Shiinotic</v>
+        <v>Alolan Raticate</v>
       </c>
       <c r="E210" t="str">
-        <v>56-61</v>
+        <v>55-60</v>
       </c>
       <c r="F210" t="str">
         <v>14.29%</v>
@@ -4603,7 +4603,7 @@
     </row>
     <row r="211">
       <c r="A211">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B211" t="str">
         <v>Route 11</v>
@@ -4612,10 +4612,10 @@
         <v>Main Area</v>
       </c>
       <c r="D211" t="str">
-        <v>Parasect</v>
+        <v>Ariados</v>
       </c>
       <c r="E211" t="str">
-        <v>56-61</v>
+        <v>55-60</v>
       </c>
       <c r="F211" t="str">
         <v>14.29%</v>
@@ -4623,7 +4623,7 @@
     </row>
     <row r="212">
       <c r="A212">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B212" t="str">
         <v>Route 11</v>
@@ -4632,10 +4632,10 @@
         <v>Main Area</v>
       </c>
       <c r="D212" t="str">
-        <v>Komala</v>
+        <v>Pancham</v>
       </c>
       <c r="E212" t="str">
-        <v>56-61</v>
+        <v>55-60</v>
       </c>
       <c r="F212" t="str">
         <v>14.29%</v>
@@ -4646,19 +4646,19 @@
         <v>46</v>
       </c>
       <c r="B213" t="str">
-        <v>Route 12</v>
+        <v>Route 11</v>
       </c>
       <c r="C213" t="str">
         <v>Main Area</v>
       </c>
       <c r="D213" t="str">
-        <v>Crabrawler</v>
+        <v>Shiinotic</v>
       </c>
       <c r="E213" t="str">
-        <v>57-62</v>
+        <v>55-60</v>
       </c>
       <c r="F213" t="str">
-        <v>12.50%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="214">
@@ -4666,19 +4666,19 @@
         <v>46</v>
       </c>
       <c r="B214" t="str">
-        <v>Route 12</v>
+        <v>Route 11</v>
       </c>
       <c r="C214" t="str">
         <v>Main Area</v>
       </c>
       <c r="D214" t="str">
-        <v>Mudbray</v>
+        <v>Parasect</v>
       </c>
       <c r="E214" t="str">
-        <v>57-62</v>
+        <v>55-60</v>
       </c>
       <c r="F214" t="str">
-        <v>12.50%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="215">
@@ -4686,24 +4686,24 @@
         <v>46</v>
       </c>
       <c r="B215" t="str">
-        <v>Route 12</v>
+        <v>Route 11</v>
       </c>
       <c r="C215" t="str">
         <v>Main Area</v>
       </c>
       <c r="D215" t="str">
-        <v>Elekid</v>
+        <v>Komala</v>
       </c>
       <c r="E215" t="str">
-        <v>57-62</v>
+        <v>55-60</v>
       </c>
       <c r="F215" t="str">
-        <v>12.50%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="216">
       <c r="A216">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B216" t="str">
         <v>Route 12</v>
@@ -4712,7 +4712,7 @@
         <v>Main Area</v>
       </c>
       <c r="D216" t="str">
-        <v>Torkoal</v>
+        <v>Crabrawler</v>
       </c>
       <c r="E216" t="str">
         <v>57-62</v>
@@ -4723,7 +4723,7 @@
     </row>
     <row r="217">
       <c r="A217">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B217" t="str">
         <v>Route 12</v>
@@ -4732,7 +4732,7 @@
         <v>Main Area</v>
       </c>
       <c r="D217" t="str">
-        <v>Houndoom</v>
+        <v>Mudbray</v>
       </c>
       <c r="E217" t="str">
         <v>57-62</v>
@@ -4743,7 +4743,7 @@
     </row>
     <row r="218">
       <c r="A218">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B218" t="str">
         <v>Route 12</v>
@@ -4752,7 +4752,7 @@
         <v>Main Area</v>
       </c>
       <c r="D218" t="str">
-        <v>Manectric</v>
+        <v>Elekid</v>
       </c>
       <c r="E218" t="str">
         <v>57-62</v>
@@ -4763,7 +4763,7 @@
     </row>
     <row r="219">
       <c r="A219">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B219" t="str">
         <v>Route 12</v>
@@ -4772,7 +4772,7 @@
         <v>Main Area</v>
       </c>
       <c r="D219" t="str">
-        <v>Alolan Geodude</v>
+        <v>Torkoal</v>
       </c>
       <c r="E219" t="str">
         <v>57-62</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="220">
       <c r="A220">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B220" t="str">
         <v>Route 12</v>
@@ -4792,7 +4792,7 @@
         <v>Main Area</v>
       </c>
       <c r="D220" t="str">
-        <v>Alolan Graveler</v>
+        <v>Houndoom</v>
       </c>
       <c r="E220" t="str">
         <v>57-62</v>
@@ -4806,19 +4806,19 @@
         <v>47</v>
       </c>
       <c r="B221" t="str">
-        <v>Blush Mountain</v>
+        <v>Route 12</v>
       </c>
       <c r="C221" t="str">
         <v>Main Area</v>
       </c>
       <c r="D221" t="str">
-        <v>Mudbray</v>
+        <v>Manectric</v>
       </c>
       <c r="E221" t="str">
-        <v>58-63</v>
+        <v>57-62</v>
       </c>
       <c r="F221" t="str">
-        <v>11.11%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="222">
@@ -4826,19 +4826,19 @@
         <v>47</v>
       </c>
       <c r="B222" t="str">
-        <v>Blush Mountain</v>
+        <v>Route 12</v>
       </c>
       <c r="C222" t="str">
         <v>Main Area</v>
       </c>
       <c r="D222" t="str">
-        <v>Torkoal</v>
+        <v>Alolan Geodude</v>
       </c>
       <c r="E222" t="str">
-        <v>58-63</v>
+        <v>57-62</v>
       </c>
       <c r="F222" t="str">
-        <v>11.11%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="223">
@@ -4846,24 +4846,24 @@
         <v>47</v>
       </c>
       <c r="B223" t="str">
-        <v>Blush Mountain</v>
+        <v>Route 12</v>
       </c>
       <c r="C223" t="str">
         <v>Main Area</v>
       </c>
       <c r="D223" t="str">
-        <v>Togedemaru</v>
+        <v>Alolan Graveler</v>
       </c>
       <c r="E223" t="str">
-        <v>58-63</v>
+        <v>57-62</v>
       </c>
       <c r="F223" t="str">
-        <v>11.11%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="224">
       <c r="A224">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B224" t="str">
         <v>Blush Mountain</v>
@@ -4872,7 +4872,7 @@
         <v>Main Area</v>
       </c>
       <c r="D224" t="str">
-        <v>Elekid</v>
+        <v>Mudbray</v>
       </c>
       <c r="E224" t="str">
         <v>58-63</v>
@@ -4883,7 +4883,7 @@
     </row>
     <row r="225">
       <c r="A225">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B225" t="str">
         <v>Blush Mountain</v>
@@ -4892,7 +4892,7 @@
         <v>Main Area</v>
       </c>
       <c r="D225" t="str">
-        <v>Alolan Geodude</v>
+        <v>Torkoal</v>
       </c>
       <c r="E225" t="str">
         <v>58-63</v>
@@ -4903,7 +4903,7 @@
     </row>
     <row r="226">
       <c r="A226">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B226" t="str">
         <v>Blush Mountain</v>
@@ -4912,7 +4912,7 @@
         <v>Main Area</v>
       </c>
       <c r="D226" t="str">
-        <v>Alolan Graveler</v>
+        <v>Togedemaru</v>
       </c>
       <c r="E226" t="str">
         <v>58-63</v>
@@ -4923,7 +4923,7 @@
     </row>
     <row r="227">
       <c r="A227">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B227" t="str">
         <v>Blush Mountain</v>
@@ -4932,7 +4932,7 @@
         <v>Main Area</v>
       </c>
       <c r="D227" t="str">
-        <v>Charjabug</v>
+        <v>Elekid</v>
       </c>
       <c r="E227" t="str">
         <v>58-63</v>
@@ -4943,7 +4943,7 @@
     </row>
     <row r="228">
       <c r="A228">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B228" t="str">
         <v>Blush Mountain</v>
@@ -4952,7 +4952,7 @@
         <v>Main Area</v>
       </c>
       <c r="D228" t="str">
-        <v>Turtonator</v>
+        <v>Alolan Geodude</v>
       </c>
       <c r="E228" t="str">
         <v>58-63</v>
@@ -4963,7 +4963,7 @@
     </row>
     <row r="229">
       <c r="A229">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B229" t="str">
         <v>Blush Mountain</v>
@@ -4972,7 +4972,7 @@
         <v>Main Area</v>
       </c>
       <c r="D229" t="str">
-        <v>Dedenne</v>
+        <v>Alolan Graveler</v>
       </c>
       <c r="E229" t="str">
         <v>58-63</v>
@@ -4986,19 +4986,19 @@
         <v>48</v>
       </c>
       <c r="B230" t="str">
-        <v>Haina Desert</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C230" t="str">
         <v>Main Area</v>
       </c>
       <c r="D230" t="str">
-        <v>Celesteela</v>
+        <v>Charjabug</v>
       </c>
       <c r="E230" t="str">
-        <v>60-65</v>
+        <v>58-63</v>
       </c>
       <c r="F230" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="231">
@@ -5006,19 +5006,19 @@
         <v>48</v>
       </c>
       <c r="B231" t="str">
-        <v>Haina Desert</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C231" t="str">
         <v>Main Area</v>
       </c>
       <c r="D231" t="str">
-        <v>Alolan Dugtrio</v>
+        <v>Turtonator</v>
       </c>
       <c r="E231" t="str">
-        <v>60-65</v>
+        <v>58-63</v>
       </c>
       <c r="F231" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="232">
@@ -5026,24 +5026,24 @@
         <v>48</v>
       </c>
       <c r="B232" t="str">
-        <v>Haina Desert</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C232" t="str">
         <v>Main Area</v>
       </c>
       <c r="D232" t="str">
-        <v>Sandile</v>
+        <v>Dedenne</v>
       </c>
       <c r="E232" t="str">
-        <v>60-65</v>
+        <v>58-63</v>
       </c>
       <c r="F232" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="233">
       <c r="A233">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B233" t="str">
         <v>Haina Desert</v>
@@ -5052,7 +5052,7 @@
         <v>Main Area</v>
       </c>
       <c r="D233" t="str">
-        <v>Krokorok</v>
+        <v>Celesteela</v>
       </c>
       <c r="E233" t="str">
         <v>60-65</v>
@@ -5066,19 +5066,19 @@
         <v>49</v>
       </c>
       <c r="B234" t="str">
-        <v>Tapu Village</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C234" t="str">
         <v>Main Area</v>
       </c>
       <c r="D234" t="str">
-        <v>Gumshoos</v>
+        <v>Alolan Dugtrio</v>
       </c>
       <c r="E234" t="str">
-        <v>61-66</v>
+        <v>60-65</v>
       </c>
       <c r="F234" t="str">
-        <v>9.09%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="235">
@@ -5086,19 +5086,19 @@
         <v>49</v>
       </c>
       <c r="B235" t="str">
-        <v>Tapu Village</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C235" t="str">
         <v>Main Area</v>
       </c>
       <c r="D235" t="str">
-        <v>Alolan Raticate</v>
+        <v>Sandile</v>
       </c>
       <c r="E235" t="str">
-        <v>61-66</v>
+        <v>60-65</v>
       </c>
       <c r="F235" t="str">
-        <v>9.09%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="236">
@@ -5106,24 +5106,24 @@
         <v>49</v>
       </c>
       <c r="B236" t="str">
-        <v>Tapu Village</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C236" t="str">
         <v>Main Area</v>
       </c>
       <c r="D236" t="str">
-        <v>Magikarp</v>
+        <v>Krokorok</v>
       </c>
       <c r="E236" t="str">
-        <v>61-66</v>
+        <v>60-65</v>
       </c>
       <c r="F236" t="str">
-        <v>9.09%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="237">
       <c r="A237">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B237" t="str">
         <v>Tapu Village</v>
@@ -5132,10 +5132,10 @@
         <v>Main Area</v>
       </c>
       <c r="D237" t="str">
-        <v>Phantump</v>
+        <v>Gumshoos</v>
       </c>
       <c r="E237" t="str">
-        <v>61-66</v>
+        <v>62-67</v>
       </c>
       <c r="F237" t="str">
         <v>9.09%</v>
@@ -5143,7 +5143,7 @@
     </row>
     <row r="238">
       <c r="A238">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B238" t="str">
         <v>Tapu Village</v>
@@ -5152,10 +5152,10 @@
         <v>Main Area</v>
       </c>
       <c r="D238" t="str">
-        <v>Pelipper</v>
+        <v>Alolan Raticate</v>
       </c>
       <c r="E238" t="str">
-        <v>61-66</v>
+        <v>62-67</v>
       </c>
       <c r="F238" t="str">
         <v>9.09%</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="239">
       <c r="A239">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B239" t="str">
         <v>Tapu Village</v>
@@ -5172,10 +5172,10 @@
         <v>Main Area</v>
       </c>
       <c r="D239" t="str">
-        <v>Graveler</v>
+        <v>Magikarp</v>
       </c>
       <c r="E239" t="str">
-        <v>61-66</v>
+        <v>62-67</v>
       </c>
       <c r="F239" t="str">
         <v>9.09%</v>
@@ -5183,7 +5183,7 @@
     </row>
     <row r="240">
       <c r="A240">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B240" t="str">
         <v>Tapu Village</v>
@@ -5192,10 +5192,10 @@
         <v>Main Area</v>
       </c>
       <c r="D240" t="str">
-        <v>Bruxish</v>
+        <v>Phantump</v>
       </c>
       <c r="E240" t="str">
-        <v>61-66</v>
+        <v>62-67</v>
       </c>
       <c r="F240" t="str">
         <v>9.09%</v>
@@ -5203,7 +5203,7 @@
     </row>
     <row r="241">
       <c r="A241">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B241" t="str">
         <v>Tapu Village</v>
@@ -5212,10 +5212,10 @@
         <v>Main Area</v>
       </c>
       <c r="D241" t="str">
-        <v>Absol</v>
+        <v>Pelipper</v>
       </c>
       <c r="E241" t="str">
-        <v>61-66</v>
+        <v>62-67</v>
       </c>
       <c r="F241" t="str">
         <v>9.09%</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="242">
       <c r="A242">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B242" t="str">
         <v>Tapu Village</v>
@@ -5232,10 +5232,10 @@
         <v>Main Area</v>
       </c>
       <c r="D242" t="str">
-        <v>Snorunt</v>
+        <v>Graveler</v>
       </c>
       <c r="E242" t="str">
-        <v>61-66</v>
+        <v>62-67</v>
       </c>
       <c r="F242" t="str">
         <v>9.09%</v>
@@ -5243,7 +5243,7 @@
     </row>
     <row r="243">
       <c r="A243">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B243" t="str">
         <v>Tapu Village</v>
@@ -5252,10 +5252,10 @@
         <v>Main Area</v>
       </c>
       <c r="D243" t="str">
-        <v>Alolan Sandshrew</v>
+        <v>Bruxish</v>
       </c>
       <c r="E243" t="str">
-        <v>61-66</v>
+        <v>62-67</v>
       </c>
       <c r="F243" t="str">
         <v>9.09%</v>
@@ -5263,7 +5263,7 @@
     </row>
     <row r="244">
       <c r="A244">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B244" t="str">
         <v>Tapu Village</v>
@@ -5272,10 +5272,10 @@
         <v>Main Area</v>
       </c>
       <c r="D244" t="str">
-        <v>Alolan Vulpix</v>
+        <v>Absol</v>
       </c>
       <c r="E244" t="str">
-        <v>61-66</v>
+        <v>62-67</v>
       </c>
       <c r="F244" t="str">
         <v>9.09%</v>
@@ -5286,19 +5286,19 @@
         <v>50</v>
       </c>
       <c r="B245" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C245" t="str">
-        <v>Abandoned Site</v>
+        <v>Main Area</v>
       </c>
       <c r="D245" t="str">
-        <v>Golbat</v>
+        <v>Snorunt</v>
       </c>
       <c r="E245" t="str">
         <v>62-67</v>
       </c>
       <c r="F245" t="str">
-        <v>20.00%</v>
+        <v>9.09%</v>
       </c>
     </row>
     <row r="246">
@@ -5306,19 +5306,19 @@
         <v>50</v>
       </c>
       <c r="B246" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C246" t="str">
-        <v>Abandoned Site</v>
+        <v>Main Area</v>
       </c>
       <c r="D246" t="str">
-        <v>Mimikyu</v>
+        <v>Alolan Sandshrew</v>
       </c>
       <c r="E246" t="str">
         <v>62-67</v>
       </c>
       <c r="F246" t="str">
-        <v>20.00%</v>
+        <v>9.09%</v>
       </c>
     </row>
     <row r="247">
@@ -5326,24 +5326,24 @@
         <v>50</v>
       </c>
       <c r="B247" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C247" t="str">
-        <v>Abandoned Site</v>
+        <v>Main Area</v>
       </c>
       <c r="D247" t="str">
-        <v>Haunter</v>
+        <v>Alolan Vulpix</v>
       </c>
       <c r="E247" t="str">
         <v>62-67</v>
       </c>
       <c r="F247" t="str">
-        <v>20.00%</v>
+        <v>9.09%</v>
       </c>
     </row>
     <row r="248">
       <c r="A248">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B248" t="str">
         <v>Thrifty Megamart</v>
@@ -5352,10 +5352,10 @@
         <v>Abandoned Site</v>
       </c>
       <c r="D248" t="str">
-        <v>Klefki</v>
+        <v>Golbat</v>
       </c>
       <c r="E248" t="str">
-        <v>62-67</v>
+        <v>63-68</v>
       </c>
       <c r="F248" t="str">
         <v>20.00%</v>
@@ -5363,7 +5363,7 @@
     </row>
     <row r="249">
       <c r="A249">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B249" t="str">
         <v>Thrifty Megamart</v>
@@ -5372,10 +5372,10 @@
         <v>Abandoned Site</v>
       </c>
       <c r="D249" t="str">
-        <v>Shuppet</v>
+        <v>Mimikyu</v>
       </c>
       <c r="E249" t="str">
-        <v>62-67</v>
+        <v>63-68</v>
       </c>
       <c r="F249" t="str">
         <v>20.00%</v>
@@ -5386,59 +5386,59 @@
         <v>51</v>
       </c>
       <c r="B250" t="str">
-        <v>Captain Acerola (Boss)</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C250" t="str">
-        <v>Boss Battle</v>
+        <v>Abandoned Site</v>
       </c>
       <c r="D250" t="str">
-        <v>Boss</v>
+        <v>Haunter</v>
       </c>
       <c r="E250" t="str">
-        <v>65-70</v>
+        <v>63-68</v>
       </c>
       <c r="F250" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="251">
       <c r="A251">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B251" t="str">
-        <v>Route 17</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C251" t="str">
-        <v>Northeast</v>
+        <v>Abandoned Site</v>
       </c>
       <c r="D251" t="str">
-        <v>Gumshoos</v>
+        <v>Klefki</v>
       </c>
       <c r="E251" t="str">
-        <v>65-70</v>
+        <v>63-68</v>
       </c>
       <c r="F251" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="252">
       <c r="A252">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B252" t="str">
-        <v>Route 17</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C252" t="str">
-        <v>Northeast</v>
+        <v>Abandoned Site</v>
       </c>
       <c r="D252" t="str">
-        <v>Alolan Raticate</v>
+        <v>Shuppet</v>
       </c>
       <c r="E252" t="str">
-        <v>65-70</v>
+        <v>63-68</v>
       </c>
       <c r="F252" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="253">
@@ -5446,24 +5446,24 @@
         <v>52</v>
       </c>
       <c r="B253" t="str">
-        <v>Route 17</v>
+        <v>Captain Acerola</v>
       </c>
       <c r="C253" t="str">
-        <v>Northeast</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D253" t="str">
-        <v>Fearow</v>
+        <v>Boss</v>
       </c>
       <c r="E253" t="str">
         <v>65-70</v>
       </c>
       <c r="F253" t="str">
-        <v>12.50%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="254">
       <c r="A254">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B254" t="str">
         <v>Route 17</v>
@@ -5472,10 +5472,10 @@
         <v>Northeast</v>
       </c>
       <c r="D254" t="str">
-        <v>Skarmory</v>
+        <v>Gumshoos</v>
       </c>
       <c r="E254" t="str">
-        <v>65-70</v>
+        <v>67-72</v>
       </c>
       <c r="F254" t="str">
         <v>12.50%</v>
@@ -5483,7 +5483,7 @@
     </row>
     <row r="255">
       <c r="A255">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B255" t="str">
         <v>Route 17</v>
@@ -5492,10 +5492,10 @@
         <v>Northeast</v>
       </c>
       <c r="D255" t="str">
-        <v>Pancham</v>
+        <v>Alolan Raticate</v>
       </c>
       <c r="E255" t="str">
-        <v>65-70</v>
+        <v>67-72</v>
       </c>
       <c r="F255" t="str">
         <v>12.50%</v>
@@ -5503,7 +5503,7 @@
     </row>
     <row r="256">
       <c r="A256">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B256" t="str">
         <v>Route 17</v>
@@ -5512,10 +5512,10 @@
         <v>Northeast</v>
       </c>
       <c r="D256" t="str">
-        <v>Alolan Graveler</v>
+        <v>Fearow</v>
       </c>
       <c r="E256" t="str">
-        <v>65-70</v>
+        <v>67-72</v>
       </c>
       <c r="F256" t="str">
         <v>12.50%</v>
@@ -5523,7 +5523,7 @@
     </row>
     <row r="257">
       <c r="A257">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B257" t="str">
         <v>Route 17</v>
@@ -5532,10 +5532,10 @@
         <v>Northeast</v>
       </c>
       <c r="D257" t="str">
-        <v>Scraggy</v>
+        <v>Skarmory</v>
       </c>
       <c r="E257" t="str">
-        <v>65-70</v>
+        <v>67-72</v>
       </c>
       <c r="F257" t="str">
         <v>12.50%</v>
@@ -5543,7 +5543,7 @@
     </row>
     <row r="258">
       <c r="A258">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B258" t="str">
         <v>Route 17</v>
@@ -5552,10 +5552,10 @@
         <v>Northeast</v>
       </c>
       <c r="D258" t="str">
-        <v>Bisharp</v>
+        <v>Pancham</v>
       </c>
       <c r="E258" t="str">
-        <v>65-70</v>
+        <v>67-72</v>
       </c>
       <c r="F258" t="str">
         <v>12.50%</v>
@@ -5566,59 +5566,59 @@
         <v>53</v>
       </c>
       <c r="B259" t="str">
-        <v>Kahuna Nanu (Boss)</v>
+        <v>Route 17</v>
       </c>
       <c r="C259" t="str">
-        <v>Boss Battle</v>
+        <v>Northeast</v>
       </c>
       <c r="D259" t="str">
-        <v>Boss</v>
+        <v>Alolan Graveler</v>
       </c>
       <c r="E259" t="str">
         <v>67-72</v>
       </c>
       <c r="F259" t="str">
-        <v>-</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="260">
       <c r="A260">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B260" t="str">
-        <v>Seafolk Village</v>
+        <v>Route 17</v>
       </c>
       <c r="C260" t="str">
-        <v>Main</v>
+        <v>Northeast</v>
       </c>
       <c r="D260" t="str">
-        <v>Magikarp</v>
+        <v>Scraggy</v>
       </c>
       <c r="E260" t="str">
         <v>67-72</v>
       </c>
       <c r="F260" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="261">
       <c r="A261">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B261" t="str">
-        <v>Seafolk Village</v>
+        <v>Route 17</v>
       </c>
       <c r="C261" t="str">
-        <v>Main</v>
+        <v>Northeast</v>
       </c>
       <c r="D261" t="str">
-        <v>Steenee</v>
+        <v>Bisharp</v>
       </c>
       <c r="E261" t="str">
         <v>67-72</v>
       </c>
       <c r="F261" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="262">
@@ -5626,24 +5626,24 @@
         <v>54</v>
       </c>
       <c r="B262" t="str">
-        <v>Seafolk Village</v>
+        <v>Kahuna Nanu</v>
       </c>
       <c r="C262" t="str">
-        <v>Main</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D262" t="str">
-        <v>Shellos</v>
+        <v>Boss</v>
       </c>
       <c r="E262" t="str">
-        <v>67-72</v>
+        <v>68-73</v>
       </c>
       <c r="F262" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="263">
       <c r="A263">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B263" t="str">
         <v>Seafolk Village</v>
@@ -5652,10 +5652,10 @@
         <v>Main</v>
       </c>
       <c r="D263" t="str">
-        <v>Dhelmise</v>
+        <v>Magikarp</v>
       </c>
       <c r="E263" t="str">
-        <v>67-72</v>
+        <v>70-75</v>
       </c>
       <c r="F263" t="str">
         <v>20.00%</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="264">
       <c r="A264">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B264" t="str">
         <v>Seafolk Village</v>
@@ -5672,10 +5672,10 @@
         <v>Main</v>
       </c>
       <c r="D264" t="str">
-        <v>Wailmer</v>
+        <v>Steenee</v>
       </c>
       <c r="E264" t="str">
-        <v>67-72</v>
+        <v>70-75</v>
       </c>
       <c r="F264" t="str">
         <v>20.00%</v>
@@ -5686,19 +5686,19 @@
         <v>55</v>
       </c>
       <c r="B265" t="str">
-        <v>Poni Wilds</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C265" t="str">
-        <v>Main Area</v>
+        <v>Main</v>
       </c>
       <c r="D265" t="str">
-        <v>Gumshoos</v>
+        <v>Shellos</v>
       </c>
       <c r="E265" t="str">
-        <v>68-73</v>
+        <v>70-75</v>
       </c>
       <c r="F265" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="266">
@@ -5706,19 +5706,19 @@
         <v>55</v>
       </c>
       <c r="B266" t="str">
-        <v>Poni Wilds</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C266" t="str">
-        <v>Main Area</v>
+        <v>Main</v>
       </c>
       <c r="D266" t="str">
-        <v>Alolan Raticate</v>
+        <v>Dhelmise</v>
       </c>
       <c r="E266" t="str">
-        <v>68-73</v>
+        <v>70-75</v>
       </c>
       <c r="F266" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="267">
@@ -5726,24 +5726,24 @@
         <v>55</v>
       </c>
       <c r="B267" t="str">
-        <v>Poni Wilds</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C267" t="str">
-        <v>Main Area</v>
+        <v>Main</v>
       </c>
       <c r="D267" t="str">
-        <v>Furfrou</v>
+        <v>Wailmer</v>
       </c>
       <c r="E267" t="str">
-        <v>68-73</v>
+        <v>70-75</v>
       </c>
       <c r="F267" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="268">
       <c r="A268">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B268" t="str">
         <v>Poni Wilds</v>
@@ -5752,10 +5752,10 @@
         <v>Main Area</v>
       </c>
       <c r="D268" t="str">
-        <v>Pelipper</v>
+        <v>Gumshoos</v>
       </c>
       <c r="E268" t="str">
-        <v>68-73</v>
+        <v>71-76</v>
       </c>
       <c r="F268" t="str">
         <v>11.11%</v>
@@ -5763,7 +5763,7 @@
     </row>
     <row r="269">
       <c r="A269">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B269" t="str">
         <v>Poni Wilds</v>
@@ -5772,10 +5772,10 @@
         <v>Main Area</v>
       </c>
       <c r="D269" t="str">
-        <v>Tentacruel</v>
+        <v>Alolan Raticate</v>
       </c>
       <c r="E269" t="str">
-        <v>68-73</v>
+        <v>71-76</v>
       </c>
       <c r="F269" t="str">
         <v>11.11%</v>
@@ -5783,7 +5783,7 @@
     </row>
     <row r="270">
       <c r="A270">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B270" t="str">
         <v>Poni Wilds</v>
@@ -5792,10 +5792,10 @@
         <v>Main Area</v>
       </c>
       <c r="D270" t="str">
-        <v>Granbull</v>
+        <v>Furfrou</v>
       </c>
       <c r="E270" t="str">
-        <v>68-73</v>
+        <v>71-76</v>
       </c>
       <c r="F270" t="str">
         <v>11.11%</v>
@@ -5803,7 +5803,7 @@
     </row>
     <row r="271">
       <c r="A271">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B271" t="str">
         <v>Poni Wilds</v>
@@ -5812,10 +5812,10 @@
         <v>Main Area</v>
       </c>
       <c r="D271" t="str">
-        <v>Gastrodon</v>
+        <v>Pelipper</v>
       </c>
       <c r="E271" t="str">
-        <v>68-73</v>
+        <v>71-76</v>
       </c>
       <c r="F271" t="str">
         <v>11.11%</v>
@@ -5823,7 +5823,7 @@
     </row>
     <row r="272">
       <c r="A272">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B272" t="str">
         <v>Poni Wilds</v>
@@ -5832,10 +5832,10 @@
         <v>Main Area</v>
       </c>
       <c r="D272" t="str">
-        <v>Lumineon</v>
+        <v>Tentacruel</v>
       </c>
       <c r="E272" t="str">
-        <v>68-73</v>
+        <v>71-76</v>
       </c>
       <c r="F272" t="str">
         <v>11.11%</v>
@@ -5843,7 +5843,7 @@
     </row>
     <row r="273">
       <c r="A273">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B273" t="str">
         <v>Poni Wilds</v>
@@ -5852,10 +5852,10 @@
         <v>Main Area</v>
       </c>
       <c r="D273" t="str">
-        <v>Lapras</v>
+        <v>Granbull</v>
       </c>
       <c r="E273" t="str">
-        <v>68-73</v>
+        <v>71-76</v>
       </c>
       <c r="F273" t="str">
         <v>11.11%</v>
@@ -5866,19 +5866,19 @@
         <v>56</v>
       </c>
       <c r="B274" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C274" t="str">
         <v>Main Area</v>
       </c>
       <c r="D274" t="str">
-        <v>Magikarp</v>
+        <v>Gastrodon</v>
       </c>
       <c r="E274" t="str">
-        <v>70-75</v>
+        <v>71-76</v>
       </c>
       <c r="F274" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="275">
@@ -5886,19 +5886,19 @@
         <v>56</v>
       </c>
       <c r="B275" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C275" t="str">
         <v>Main Area</v>
       </c>
       <c r="D275" t="str">
-        <v>Wimpod</v>
+        <v>Lumineon</v>
       </c>
       <c r="E275" t="str">
-        <v>70-75</v>
+        <v>71-76</v>
       </c>
       <c r="F275" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="276">
@@ -5906,24 +5906,24 @@
         <v>56</v>
       </c>
       <c r="B276" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C276" t="str">
         <v>Main Area</v>
       </c>
       <c r="D276" t="str">
-        <v>Relicanth</v>
+        <v>Lapras</v>
       </c>
       <c r="E276" t="str">
-        <v>70-75</v>
+        <v>71-76</v>
       </c>
       <c r="F276" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="277">
       <c r="A277">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B277" t="str">
         <v>Poni Breaker Coast</v>
@@ -5932,10 +5932,10 @@
         <v>Main Area</v>
       </c>
       <c r="D277" t="str">
-        <v>Wailmer</v>
+        <v>Magikarp</v>
       </c>
       <c r="E277" t="str">
-        <v>70-75</v>
+        <v>73-78</v>
       </c>
       <c r="F277" t="str">
         <v>16.67%</v>
@@ -5943,7 +5943,7 @@
     </row>
     <row r="278">
       <c r="A278">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B278" t="str">
         <v>Poni Breaker Coast</v>
@@ -5952,10 +5952,10 @@
         <v>Main Area</v>
       </c>
       <c r="D278" t="str">
-        <v>Carvanha</v>
+        <v>Wimpod</v>
       </c>
       <c r="E278" t="str">
-        <v>70-75</v>
+        <v>73-78</v>
       </c>
       <c r="F278" t="str">
         <v>16.67%</v>
@@ -5963,7 +5963,7 @@
     </row>
     <row r="279">
       <c r="A279">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B279" t="str">
         <v>Poni Breaker Coast</v>
@@ -5972,10 +5972,10 @@
         <v>Main Area</v>
       </c>
       <c r="D279" t="str">
-        <v>Sharpedo</v>
+        <v>Relicanth</v>
       </c>
       <c r="E279" t="str">
-        <v>70-75</v>
+        <v>73-78</v>
       </c>
       <c r="F279" t="str">
         <v>16.67%</v>
@@ -5986,16 +5986,16 @@
         <v>57</v>
       </c>
       <c r="B280" t="str">
-        <v>Exeggutor Island</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C280" t="str">
         <v>Main Area</v>
       </c>
       <c r="D280" t="str">
-        <v>Pelipper</v>
+        <v>Wailmer</v>
       </c>
       <c r="E280" t="str">
-        <v>71-76</v>
+        <v>73-78</v>
       </c>
       <c r="F280" t="str">
         <v>16.67%</v>
@@ -6006,16 +6006,16 @@
         <v>57</v>
       </c>
       <c r="B281" t="str">
-        <v>Exeggutor Island</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C281" t="str">
         <v>Main Area</v>
       </c>
       <c r="D281" t="str">
-        <v>Pinsir</v>
+        <v>Carvanha</v>
       </c>
       <c r="E281" t="str">
-        <v>71-76</v>
+        <v>73-78</v>
       </c>
       <c r="F281" t="str">
         <v>16.67%</v>
@@ -6026,16 +6026,16 @@
         <v>57</v>
       </c>
       <c r="B282" t="str">
-        <v>Exeggutor Island</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C282" t="str">
         <v>Main Area</v>
       </c>
       <c r="D282" t="str">
-        <v>Gastrodon</v>
+        <v>Sharpedo</v>
       </c>
       <c r="E282" t="str">
-        <v>71-76</v>
+        <v>73-78</v>
       </c>
       <c r="F282" t="str">
         <v>16.67%</v>
@@ -6043,7 +6043,7 @@
     </row>
     <row r="283">
       <c r="A283">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B283" t="str">
         <v>Exeggutor Island</v>
@@ -6052,10 +6052,10 @@
         <v>Main Area</v>
       </c>
       <c r="D283" t="str">
-        <v>Exeggcute</v>
+        <v>Pelipper</v>
       </c>
       <c r="E283" t="str">
-        <v>71-76</v>
+        <v>75-80</v>
       </c>
       <c r="F283" t="str">
         <v>16.67%</v>
@@ -6063,7 +6063,7 @@
     </row>
     <row r="284">
       <c r="A284">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B284" t="str">
         <v>Exeggutor Island</v>
@@ -6072,10 +6072,10 @@
         <v>Main Area</v>
       </c>
       <c r="D284" t="str">
-        <v>Tropius</v>
+        <v>Pinsir</v>
       </c>
       <c r="E284" t="str">
-        <v>71-76</v>
+        <v>75-80</v>
       </c>
       <c r="F284" t="str">
         <v>16.67%</v>
@@ -6083,7 +6083,7 @@
     </row>
     <row r="285">
       <c r="A285">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B285" t="str">
         <v>Exeggutor Island</v>
@@ -6092,10 +6092,10 @@
         <v>Main Area</v>
       </c>
       <c r="D285" t="str">
-        <v>Alolan Exeggutor</v>
+        <v>Gastrodon</v>
       </c>
       <c r="E285" t="str">
-        <v>71-76</v>
+        <v>75-80</v>
       </c>
       <c r="F285" t="str">
         <v>16.67%</v>
@@ -6106,59 +6106,59 @@
         <v>58</v>
       </c>
       <c r="B286" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C286" t="str">
-        <v>Inside</v>
+        <v>Main Area</v>
       </c>
       <c r="D286" t="str">
-        <v>Boldore</v>
+        <v>Exeggcute</v>
       </c>
       <c r="E286" t="str">
-        <v>72-77</v>
+        <v>75-80</v>
       </c>
       <c r="F286" t="str">
-        <v>100.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="287">
       <c r="A287">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B287" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C287" t="str">
-        <v>Northwest (Hidden Area)</v>
+        <v>Main Area</v>
       </c>
       <c r="D287" t="str">
-        <v>Corphish</v>
+        <v>Tropius</v>
       </c>
       <c r="E287" t="str">
-        <v>73-78</v>
+        <v>75-80</v>
       </c>
       <c r="F287" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="288">
       <c r="A288">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B288" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C288" t="str">
-        <v>Northwest (Hidden Area)</v>
+        <v>Main Area</v>
       </c>
       <c r="D288" t="str">
-        <v>Dratini</v>
+        <v>Alolan Exeggutor</v>
       </c>
       <c r="E288" t="str">
-        <v>73-78</v>
+        <v>75-80</v>
       </c>
       <c r="F288" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="289">
@@ -6169,16 +6169,16 @@
         <v>Vast Poni Canyon</v>
       </c>
       <c r="C289" t="str">
-        <v>Northwest (Hidden Area)</v>
+        <v>Inside</v>
       </c>
       <c r="D289" t="str">
-        <v>Golduck</v>
+        <v>Boldore</v>
       </c>
       <c r="E289" t="str">
-        <v>73-78</v>
+        <v>76-81</v>
       </c>
       <c r="F289" t="str">
-        <v>33.33%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="290">
@@ -6189,13 +6189,13 @@
         <v>Vast Poni Canyon</v>
       </c>
       <c r="C290" t="str">
-        <v>Outside</v>
+        <v>Northwest (Hidden Area)</v>
       </c>
       <c r="D290" t="str">
-        <v>Machoke</v>
+        <v>Corphish</v>
       </c>
       <c r="E290" t="str">
-        <v>75-80</v>
+        <v>76-81</v>
       </c>
       <c r="F290" t="str">
         <v>33.33%</v>
@@ -6209,13 +6209,13 @@
         <v>Vast Poni Canyon</v>
       </c>
       <c r="C291" t="str">
-        <v>Outside</v>
+        <v>Northwest (Hidden Area)</v>
       </c>
       <c r="D291" t="str">
-        <v>Mienfoo</v>
+        <v>Dratini</v>
       </c>
       <c r="E291" t="str">
-        <v>75-80</v>
+        <v>76-81</v>
       </c>
       <c r="F291" t="str">
         <v>33.33%</v>
@@ -6229,13 +6229,13 @@
         <v>Vast Poni Canyon</v>
       </c>
       <c r="C292" t="str">
-        <v>Outside</v>
+        <v>Northwest (Hidden Area)</v>
       </c>
       <c r="D292" t="str">
-        <v>Jangmo-o</v>
+        <v>Golduck</v>
       </c>
       <c r="E292" t="str">
-        <v>75-80</v>
+        <v>76-81</v>
       </c>
       <c r="F292" t="str">
         <v>33.33%</v>
@@ -6246,99 +6246,99 @@
         <v>61</v>
       </c>
       <c r="B293" t="str">
-        <v>Captain Kommo-o (Boss)</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C293" t="str">
-        <v>Boss Battle</v>
+        <v>Outside</v>
       </c>
       <c r="D293" t="str">
-        <v>Boss</v>
+        <v>Machoke</v>
       </c>
       <c r="E293" t="str">
-        <v>77-82</v>
+        <v>76-81</v>
       </c>
       <c r="F293" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="294">
       <c r="A294">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B294" t="str">
-        <v>Captain Mina</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C294" t="str">
-        <v>Captain Mina</v>
+        <v>Outside</v>
       </c>
       <c r="D294" t="str">
-        <v>Boss</v>
+        <v>Mienfoo</v>
       </c>
       <c r="E294" t="str">
-        <v>77-82</v>
+        <v>76-81</v>
       </c>
       <c r="F294" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="295">
       <c r="A295">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B295" t="str">
-        <v>Kahuna Hapu</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C295" t="str">
-        <v>Kahuna Hapu</v>
+        <v>Outside</v>
       </c>
       <c r="D295" t="str">
-        <v>Boss</v>
+        <v>Jangmo-o</v>
       </c>
       <c r="E295" t="str">
-        <v>78-83</v>
+        <v>76-81</v>
       </c>
       <c r="F295" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="296">
       <c r="A296">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B296" t="str">
-        <v>Mount Lanakila</v>
+        <v>Captain Kommo-o</v>
       </c>
       <c r="C296" t="str">
-        <v>Cave</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D296" t="str">
-        <v>Drampa</v>
+        <v>Boss</v>
       </c>
       <c r="E296" t="str">
-        <v>79-84</v>
+        <v>78-83</v>
       </c>
       <c r="F296" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="297">
       <c r="A297">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B297" t="str">
-        <v>Mount Lanakila</v>
+        <v>Captain Mina</v>
       </c>
       <c r="C297" t="str">
-        <v>Cave</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D297" t="str">
-        <v>Glalie</v>
+        <v>Boss</v>
       </c>
       <c r="E297" t="str">
         <v>79-84</v>
       </c>
       <c r="F297" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="298">
@@ -6346,19 +6346,19 @@
         <v>64</v>
       </c>
       <c r="B298" t="str">
-        <v>Mount Lanakila</v>
+        <v>Kahuna Hapu</v>
       </c>
       <c r="C298" t="str">
-        <v>Cave</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D298" t="str">
-        <v>Sneasel</v>
+        <v>Boss</v>
       </c>
       <c r="E298" t="str">
-        <v>79-84</v>
+        <v>81-86</v>
       </c>
       <c r="F298" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="299">
@@ -6366,79 +6366,79 @@
         <v>65</v>
       </c>
       <c r="B299" t="str">
-        <v>Alola Pokemon League</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C299" t="str">
-        <v>Elite Four</v>
+        <v>Cave</v>
       </c>
       <c r="D299" t="str">
-        <v>Boss</v>
+        <v>Drampa</v>
       </c>
       <c r="E299" t="str">
-        <v>81-86</v>
+        <v>83-88</v>
       </c>
       <c r="F299" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="300">
       <c r="A300">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B300" t="str">
-        <v>Champion Hau</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C300" t="str">
-        <v>Champion Hau</v>
+        <v>Cave</v>
       </c>
       <c r="D300" t="str">
-        <v>Boss</v>
+        <v>Glalie</v>
       </c>
       <c r="E300" t="str">
-        <v>82-87</v>
+        <v>83-88</v>
       </c>
       <c r="F300" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="301">
       <c r="A301">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B301" t="str">
-        <v>Poni Grove</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C301" t="str">
-        <v>Main Area</v>
+        <v>Cave</v>
       </c>
       <c r="D301" t="str">
-        <v>Alolan Raticate</v>
+        <v>Sneasel</v>
       </c>
       <c r="E301" t="str">
         <v>83-88</v>
       </c>
       <c r="F301" t="str">
-        <v>12.50%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="302">
       <c r="A302">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B302" t="str">
-        <v>Poni Grove</v>
+        <v>Alola Pokemon League</v>
       </c>
       <c r="C302" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D302" t="str">
-        <v>Buneary</v>
+        <v>Boss</v>
       </c>
       <c r="E302" t="str">
-        <v>83-88</v>
+        <v>84-89</v>
       </c>
       <c r="F302" t="str">
-        <v>12.50%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="303">
@@ -6446,24 +6446,24 @@
         <v>67</v>
       </c>
       <c r="B303" t="str">
-        <v>Poni Grove</v>
+        <v>Champion Hau</v>
       </c>
       <c r="C303" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D303" t="str">
-        <v>Granbull</v>
+        <v>Boss</v>
       </c>
       <c r="E303" t="str">
-        <v>83-88</v>
+        <v>86-91</v>
       </c>
       <c r="F303" t="str">
-        <v>12.50%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="304">
       <c r="A304">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B304" t="str">
         <v>Poni Grove</v>
@@ -6472,10 +6472,10 @@
         <v>Main Area</v>
       </c>
       <c r="D304" t="str">
-        <v>Zoroark</v>
+        <v>Alolan Raticate</v>
       </c>
       <c r="E304" t="str">
-        <v>83-88</v>
+        <v>87-92</v>
       </c>
       <c r="F304" t="str">
         <v>12.50%</v>
@@ -6483,7 +6483,7 @@
     </row>
     <row r="305">
       <c r="A305">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B305" t="str">
         <v>Poni Grove</v>
@@ -6492,10 +6492,10 @@
         <v>Main Area</v>
       </c>
       <c r="D305" t="str">
-        <v>Heracross</v>
+        <v>Buneary</v>
       </c>
       <c r="E305" t="str">
-        <v>83-88</v>
+        <v>87-92</v>
       </c>
       <c r="F305" t="str">
         <v>12.50%</v>
@@ -6503,7 +6503,7 @@
     </row>
     <row r="306">
       <c r="A306">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B306" t="str">
         <v>Poni Grove</v>
@@ -6512,10 +6512,10 @@
         <v>Main Area</v>
       </c>
       <c r="D306" t="str">
-        <v>Riolu</v>
+        <v>Granbull</v>
       </c>
       <c r="E306" t="str">
-        <v>83-88</v>
+        <v>87-92</v>
       </c>
       <c r="F306" t="str">
         <v>12.50%</v>
@@ -6523,7 +6523,7 @@
     </row>
     <row r="307">
       <c r="A307">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B307" t="str">
         <v>Poni Grove</v>
@@ -6532,10 +6532,10 @@
         <v>Main Area</v>
       </c>
       <c r="D307" t="str">
-        <v>Stakataka</v>
+        <v>Zoroark</v>
       </c>
       <c r="E307" t="str">
-        <v>83-88</v>
+        <v>87-92</v>
       </c>
       <c r="F307" t="str">
         <v>12.50%</v>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="308">
       <c r="A308">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B308" t="str">
         <v>Poni Grove</v>
@@ -6552,10 +6552,10 @@
         <v>Main Area</v>
       </c>
       <c r="D308" t="str">
-        <v>Blacephalon</v>
+        <v>Heracross</v>
       </c>
       <c r="E308" t="str">
-        <v>83-88</v>
+        <v>87-92</v>
       </c>
       <c r="F308" t="str">
         <v>12.50%</v>
@@ -6566,19 +6566,19 @@
         <v>68</v>
       </c>
       <c r="B309" t="str">
-        <v>Poni Plains</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C309" t="str">
-        <v>Center</v>
+        <v>Main Area</v>
       </c>
       <c r="D309" t="str">
-        <v>Trumbeak</v>
+        <v>Riolu</v>
       </c>
       <c r="E309" t="str">
-        <v>84-89</v>
+        <v>87-92</v>
       </c>
       <c r="F309" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="310">
@@ -6586,19 +6586,19 @@
         <v>68</v>
       </c>
       <c r="B310" t="str">
-        <v>Poni Plains</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C310" t="str">
-        <v>Center</v>
+        <v>Main Area</v>
       </c>
       <c r="D310" t="str">
-        <v>Gumshoos</v>
+        <v>Stakataka</v>
       </c>
       <c r="E310" t="str">
-        <v>84-89</v>
+        <v>87-92</v>
       </c>
       <c r="F310" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="311">
@@ -6606,24 +6606,24 @@
         <v>68</v>
       </c>
       <c r="B311" t="str">
-        <v>Poni Plains</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C311" t="str">
-        <v>Center</v>
+        <v>Main Area</v>
       </c>
       <c r="D311" t="str">
-        <v>Alolan Raticate</v>
+        <v>Blacephalon</v>
       </c>
       <c r="E311" t="str">
-        <v>84-89</v>
+        <v>87-92</v>
       </c>
       <c r="F311" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="312">
       <c r="A312">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B312" t="str">
         <v>Poni Plains</v>
@@ -6632,10 +6632,10 @@
         <v>Center</v>
       </c>
       <c r="D312" t="str">
-        <v>Hariyama</v>
+        <v>Trumbeak</v>
       </c>
       <c r="E312" t="str">
-        <v>84-89</v>
+        <v>89-94</v>
       </c>
       <c r="F312" t="str">
         <v>20.00%</v>
@@ -6643,7 +6643,7 @@
     </row>
     <row r="313">
       <c r="A313">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B313" t="str">
         <v>Poni Plains</v>
@@ -6652,10 +6652,10 @@
         <v>Center</v>
       </c>
       <c r="D313" t="str">
-        <v>Mudsdale</v>
+        <v>Gumshoos</v>
       </c>
       <c r="E313" t="str">
-        <v>84-89</v>
+        <v>89-94</v>
       </c>
       <c r="F313" t="str">
         <v>20.00%</v>
@@ -6666,16 +6666,16 @@
         <v>69</v>
       </c>
       <c r="B314" t="str">
-        <v>Resolution Cave</v>
+        <v>Poni Plains</v>
       </c>
       <c r="C314" t="str">
-        <v>Main Area</v>
+        <v>Center</v>
       </c>
       <c r="D314" t="str">
-        <v>Golbat</v>
+        <v>Alolan Raticate</v>
       </c>
       <c r="E314" t="str">
-        <v>86-91</v>
+        <v>89-94</v>
       </c>
       <c r="F314" t="str">
         <v>20.00%</v>
@@ -6686,16 +6686,16 @@
         <v>69</v>
       </c>
       <c r="B315" t="str">
-        <v>Resolution Cave</v>
+        <v>Poni Plains</v>
       </c>
       <c r="C315" t="str">
-        <v>Main Area</v>
+        <v>Center</v>
       </c>
       <c r="D315" t="str">
-        <v>Alolan Dugtrio</v>
+        <v>Hariyama</v>
       </c>
       <c r="E315" t="str">
-        <v>86-91</v>
+        <v>89-94</v>
       </c>
       <c r="F315" t="str">
         <v>20.00%</v>
@@ -6706,16 +6706,16 @@
         <v>69</v>
       </c>
       <c r="B316" t="str">
-        <v>Resolution Cave</v>
+        <v>Poni Plains</v>
       </c>
       <c r="C316" t="str">
-        <v>Main Area</v>
+        <v>Center</v>
       </c>
       <c r="D316" t="str">
-        <v>Noivern</v>
+        <v>Mudsdale</v>
       </c>
       <c r="E316" t="str">
-        <v>86-91</v>
+        <v>89-94</v>
       </c>
       <c r="F316" t="str">
         <v>20.00%</v>
@@ -6723,7 +6723,7 @@
     </row>
     <row r="317">
       <c r="A317">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B317" t="str">
         <v>Resolution Cave</v>
@@ -6732,10 +6732,10 @@
         <v>Main Area</v>
       </c>
       <c r="D317" t="str">
-        <v>Druddigon</v>
+        <v>Golbat</v>
       </c>
       <c r="E317" t="str">
-        <v>86-91</v>
+        <v>91-96</v>
       </c>
       <c r="F317" t="str">
         <v>20.00%</v>
@@ -6743,7 +6743,7 @@
     </row>
     <row r="318">
       <c r="A318">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B318" t="str">
         <v>Resolution Cave</v>
@@ -6752,10 +6752,10 @@
         <v>Main Area</v>
       </c>
       <c r="D318" t="str">
-        <v>Guzzlord</v>
+        <v>Alolan Dugtrio</v>
       </c>
       <c r="E318" t="str">
-        <v>86-91</v>
+        <v>91-96</v>
       </c>
       <c r="F318" t="str">
         <v>20.00%</v>
@@ -6766,19 +6766,19 @@
         <v>70</v>
       </c>
       <c r="B319" t="str">
-        <v>Mahalo Trail</v>
+        <v>Resolution Cave</v>
       </c>
       <c r="C319" t="str">
         <v>Main Area</v>
       </c>
       <c r="D319" t="str">
-        <v>Solgaleo</v>
+        <v>Noivern</v>
       </c>
       <c r="E319" t="str">
-        <v>87-92</v>
+        <v>91-96</v>
       </c>
       <c r="F319" t="str">
-        <v>50.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="320">
@@ -6786,39 +6786,39 @@
         <v>70</v>
       </c>
       <c r="B320" t="str">
-        <v>Mahalo Trail</v>
+        <v>Resolution Cave</v>
       </c>
       <c r="C320" t="str">
         <v>Main Area</v>
       </c>
       <c r="D320" t="str">
-        <v>Lunala</v>
+        <v>Druddigon</v>
       </c>
       <c r="E320" t="str">
-        <v>87-92</v>
+        <v>91-96</v>
       </c>
       <c r="F320" t="str">
-        <v>50.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="321">
       <c r="A321">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B321" t="str">
-        <v>Melemele Meadow</v>
+        <v>Resolution Cave</v>
       </c>
       <c r="C321" t="str">
         <v>Main Area</v>
       </c>
       <c r="D321" t="str">
-        <v>Caterpie</v>
+        <v>Guzzlord</v>
       </c>
       <c r="E321" t="str">
-        <v>88-93</v>
+        <v>91-96</v>
       </c>
       <c r="F321" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="322">
@@ -6826,19 +6826,19 @@
         <v>71</v>
       </c>
       <c r="B322" t="str">
-        <v>Melemele Meadow</v>
+        <v>Mahalo Trail</v>
       </c>
       <c r="C322" t="str">
         <v>Main Area</v>
       </c>
       <c r="D322" t="str">
-        <v>Metapod</v>
+        <v>Solgaleo</v>
       </c>
       <c r="E322" t="str">
-        <v>88-93</v>
+        <v>92-97</v>
       </c>
       <c r="F322" t="str">
-        <v>12.50%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="323">
@@ -6846,24 +6846,24 @@
         <v>71</v>
       </c>
       <c r="B323" t="str">
-        <v>Melemele Meadow</v>
+        <v>Mahalo Trail</v>
       </c>
       <c r="C323" t="str">
         <v>Main Area</v>
       </c>
       <c r="D323" t="str">
-        <v>Cutiefly</v>
+        <v>Lunala</v>
       </c>
       <c r="E323" t="str">
-        <v>88-93</v>
+        <v>92-97</v>
       </c>
       <c r="F323" t="str">
-        <v>12.50%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="324">
       <c r="A324">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B324" t="str">
         <v>Melemele Meadow</v>
@@ -6872,10 +6872,10 @@
         <v>Main Area</v>
       </c>
       <c r="D324" t="str">
-        <v>Butterfree</v>
+        <v>Caterpie</v>
       </c>
       <c r="E324" t="str">
-        <v>88-93</v>
+        <v>94-99</v>
       </c>
       <c r="F324" t="str">
         <v>12.50%</v>
@@ -6883,7 +6883,7 @@
     </row>
     <row r="325">
       <c r="A325">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B325" t="str">
         <v>Melemele Meadow</v>
@@ -6892,10 +6892,10 @@
         <v>Main Area</v>
       </c>
       <c r="D325" t="str">
-        <v>Flabébé</v>
+        <v>Metapod</v>
       </c>
       <c r="E325" t="str">
-        <v>88-93</v>
+        <v>94-99</v>
       </c>
       <c r="F325" t="str">
         <v>12.50%</v>
@@ -6903,7 +6903,7 @@
     </row>
     <row r="326">
       <c r="A326">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B326" t="str">
         <v>Melemele Meadow</v>
@@ -6912,10 +6912,10 @@
         <v>Main Area</v>
       </c>
       <c r="D326" t="str">
-        <v>Petilil</v>
+        <v>Cutiefly</v>
       </c>
       <c r="E326" t="str">
-        <v>88-93</v>
+        <v>94-99</v>
       </c>
       <c r="F326" t="str">
         <v>12.50%</v>
@@ -6923,7 +6923,7 @@
     </row>
     <row r="327">
       <c r="A327">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B327" t="str">
         <v>Melemele Meadow</v>
@@ -6932,10 +6932,10 @@
         <v>Main Area</v>
       </c>
       <c r="D327" t="str">
-        <v>Cottonee</v>
+        <v>Butterfree</v>
       </c>
       <c r="E327" t="str">
-        <v>88-93</v>
+        <v>94-99</v>
       </c>
       <c r="F327" t="str">
         <v>12.50%</v>
@@ -6943,7 +6943,7 @@
     </row>
     <row r="328">
       <c r="A328">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B328" t="str">
         <v>Melemele Meadow</v>
@@ -6952,10 +6952,10 @@
         <v>Main Area</v>
       </c>
       <c r="D328" t="str">
-        <v>Buzzwole</v>
+        <v>Flabébé</v>
       </c>
       <c r="E328" t="str">
-        <v>88-93</v>
+        <v>94-99</v>
       </c>
       <c r="F328" t="str">
         <v>12.50%</v>
@@ -6966,16 +6966,16 @@
         <v>72</v>
       </c>
       <c r="B329" t="str">
-        <v>Poké Pelago</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C329" t="str">
-        <v>Elite Four defeated 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D329" t="str">
-        <v>Gastly</v>
+        <v>Petilil</v>
       </c>
       <c r="E329" t="str">
-        <v>89-94</v>
+        <v>94-99</v>
       </c>
       <c r="F329" t="str">
         <v>12.50%</v>
@@ -6986,16 +6986,16 @@
         <v>72</v>
       </c>
       <c r="B330" t="str">
-        <v>Poké Pelago</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C330" t="str">
-        <v>Elite Four defeated 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D330" t="str">
-        <v>Spearow</v>
+        <v>Cottonee</v>
       </c>
       <c r="E330" t="str">
-        <v>89-94</v>
+        <v>94-99</v>
       </c>
       <c r="F330" t="str">
         <v>12.50%</v>
@@ -7006,16 +7006,16 @@
         <v>72</v>
       </c>
       <c r="B331" t="str">
-        <v>Poké Pelago</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C331" t="str">
-        <v>Elite Four defeated 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D331" t="str">
-        <v>Cutiefly</v>
+        <v>Buzzwole</v>
       </c>
       <c r="E331" t="str">
-        <v>89-94</v>
+        <v>94-99</v>
       </c>
       <c r="F331" t="str">
         <v>12.50%</v>
@@ -7023,7 +7023,7 @@
     </row>
     <row r="332">
       <c r="A332">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B332" t="str">
         <v>Poké Pelago</v>
@@ -7032,10 +7032,10 @@
         <v>Elite Four defeated 1</v>
       </c>
       <c r="D332" t="str">
-        <v>Corsola</v>
+        <v>Gastly</v>
       </c>
       <c r="E332" t="str">
-        <v>89-94</v>
+        <v>95-100</v>
       </c>
       <c r="F332" t="str">
         <v>12.50%</v>
@@ -7043,7 +7043,7 @@
     </row>
     <row r="333">
       <c r="A333">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B333" t="str">
         <v>Poké Pelago</v>
@@ -7052,10 +7052,10 @@
         <v>Elite Four defeated 1</v>
       </c>
       <c r="D333" t="str">
-        <v>Banette</v>
+        <v>Spearow</v>
       </c>
       <c r="E333" t="str">
-        <v>89-94</v>
+        <v>95-100</v>
       </c>
       <c r="F333" t="str">
         <v>12.50%</v>
@@ -7063,7 +7063,7 @@
     </row>
     <row r="334">
       <c r="A334">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B334" t="str">
         <v>Poké Pelago</v>
@@ -7072,10 +7072,10 @@
         <v>Elite Four defeated 1</v>
       </c>
       <c r="D334" t="str">
-        <v>Trevenant</v>
+        <v>Cutiefly</v>
       </c>
       <c r="E334" t="str">
-        <v>89-94</v>
+        <v>95-100</v>
       </c>
       <c r="F334" t="str">
         <v>12.50%</v>
@@ -7083,7 +7083,7 @@
     </row>
     <row r="335">
       <c r="A335">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B335" t="str">
         <v>Poké Pelago</v>
@@ -7092,10 +7092,10 @@
         <v>Elite Four defeated 1</v>
       </c>
       <c r="D335" t="str">
-        <v>Pyukumuku</v>
+        <v>Corsola</v>
       </c>
       <c r="E335" t="str">
-        <v>89-94</v>
+        <v>95-100</v>
       </c>
       <c r="F335" t="str">
         <v>12.50%</v>
@@ -7103,7 +7103,7 @@
     </row>
     <row r="336">
       <c r="A336">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B336" t="str">
         <v>Poké Pelago</v>
@@ -7112,10 +7112,10 @@
         <v>Elite Four defeated 1</v>
       </c>
       <c r="D336" t="str">
-        <v>Frillish</v>
+        <v>Banette</v>
       </c>
       <c r="E336" t="str">
-        <v>89-94</v>
+        <v>95-100</v>
       </c>
       <c r="F336" t="str">
         <v>12.50%</v>
@@ -7129,13 +7129,13 @@
         <v>Poké Pelago</v>
       </c>
       <c r="C337" t="str">
-        <v>Elite Four defeated 2</v>
+        <v>Elite Four defeated 1</v>
       </c>
       <c r="D337" t="str">
-        <v>Carbink</v>
+        <v>Trevenant</v>
       </c>
       <c r="E337" t="str">
-        <v>91-96</v>
+        <v>95-100</v>
       </c>
       <c r="F337" t="str">
         <v>12.50%</v>
@@ -7149,13 +7149,13 @@
         <v>Poké Pelago</v>
       </c>
       <c r="C338" t="str">
-        <v>Elite Four defeated 2</v>
+        <v>Elite Four defeated 1</v>
       </c>
       <c r="D338" t="str">
-        <v>Poliwag</v>
+        <v>Pyukumuku</v>
       </c>
       <c r="E338" t="str">
-        <v>91-96</v>
+        <v>95-100</v>
       </c>
       <c r="F338" t="str">
         <v>12.50%</v>
@@ -7169,13 +7169,13 @@
         <v>Poké Pelago</v>
       </c>
       <c r="C339" t="str">
-        <v>Elite Four defeated 2</v>
+        <v>Elite Four defeated 1</v>
       </c>
       <c r="D339" t="str">
-        <v>Murkrow</v>
+        <v>Frillish</v>
       </c>
       <c r="E339" t="str">
-        <v>91-96</v>
+        <v>95-100</v>
       </c>
       <c r="F339" t="str">
         <v>12.50%</v>
@@ -7183,7 +7183,7 @@
     </row>
     <row r="340">
       <c r="A340">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B340" t="str">
         <v>Poké Pelago</v>
@@ -7192,10 +7192,10 @@
         <v>Elite Four defeated 2</v>
       </c>
       <c r="D340" t="str">
-        <v>Pinsir</v>
+        <v>Carbink</v>
       </c>
       <c r="E340" t="str">
-        <v>91-96</v>
+        <v>95-100</v>
       </c>
       <c r="F340" t="str">
         <v>12.50%</v>
@@ -7203,7 +7203,7 @@
     </row>
     <row r="341">
       <c r="A341">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B341" t="str">
         <v>Poké Pelago</v>
@@ -7212,10 +7212,10 @@
         <v>Elite Four defeated 2</v>
       </c>
       <c r="D341" t="str">
-        <v>Electrike</v>
+        <v>Poliwag</v>
       </c>
       <c r="E341" t="str">
-        <v>91-96</v>
+        <v>95-100</v>
       </c>
       <c r="F341" t="str">
         <v>12.50%</v>
@@ -7223,7 +7223,7 @@
     </row>
     <row r="342">
       <c r="A342">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B342" t="str">
         <v>Poké Pelago</v>
@@ -7232,10 +7232,10 @@
         <v>Elite Four defeated 2</v>
       </c>
       <c r="D342" t="str">
-        <v>Litleo</v>
+        <v>Murkrow</v>
       </c>
       <c r="E342" t="str">
-        <v>91-96</v>
+        <v>95-100</v>
       </c>
       <c r="F342" t="str">
         <v>12.50%</v>
@@ -7243,7 +7243,7 @@
     </row>
     <row r="343">
       <c r="A343">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B343" t="str">
         <v>Poké Pelago</v>
@@ -7252,10 +7252,10 @@
         <v>Elite Four defeated 2</v>
       </c>
       <c r="D343" t="str">
-        <v>Mismagius</v>
+        <v>Pinsir</v>
       </c>
       <c r="E343" t="str">
-        <v>91-96</v>
+        <v>95-100</v>
       </c>
       <c r="F343" t="str">
         <v>12.50%</v>
@@ -7263,7 +7263,7 @@
     </row>
     <row r="344">
       <c r="A344">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B344" t="str">
         <v>Poké Pelago</v>
@@ -7272,10 +7272,10 @@
         <v>Elite Four defeated 2</v>
       </c>
       <c r="D344" t="str">
-        <v>Floette</v>
+        <v>Electrike</v>
       </c>
       <c r="E344" t="str">
-        <v>91-96</v>
+        <v>95-100</v>
       </c>
       <c r="F344" t="str">
         <v>12.50%</v>
@@ -7289,13 +7289,13 @@
         <v>Poké Pelago</v>
       </c>
       <c r="C345" t="str">
-        <v>Elite Four defeated 3</v>
+        <v>Elite Four defeated 2</v>
       </c>
       <c r="D345" t="str">
-        <v>Skarmory</v>
+        <v>Litleo</v>
       </c>
       <c r="E345" t="str">
-        <v>92-97</v>
+        <v>95-100</v>
       </c>
       <c r="F345" t="str">
         <v>12.50%</v>
@@ -7309,13 +7309,13 @@
         <v>Poké Pelago</v>
       </c>
       <c r="C346" t="str">
-        <v>Elite Four defeated 3</v>
+        <v>Elite Four defeated 2</v>
       </c>
       <c r="D346" t="str">
-        <v>Fletchling</v>
+        <v>Mismagius</v>
       </c>
       <c r="E346" t="str">
-        <v>92-97</v>
+        <v>95-100</v>
       </c>
       <c r="F346" t="str">
         <v>12.50%</v>
@@ -7329,13 +7329,13 @@
         <v>Poké Pelago</v>
       </c>
       <c r="C347" t="str">
-        <v>Elite Four defeated 3</v>
+        <v>Elite Four defeated 2</v>
       </c>
       <c r="D347" t="str">
-        <v>Hawlucha</v>
+        <v>Floette</v>
       </c>
       <c r="E347" t="str">
-        <v>92-97</v>
+        <v>95-100</v>
       </c>
       <c r="F347" t="str">
         <v>12.50%</v>
@@ -7343,7 +7343,7 @@
     </row>
     <row r="348">
       <c r="A348">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B348" t="str">
         <v>Poké Pelago</v>
@@ -7352,10 +7352,10 @@
         <v>Elite Four defeated 3</v>
       </c>
       <c r="D348" t="str">
-        <v>Lapras</v>
+        <v>Skarmory</v>
       </c>
       <c r="E348" t="str">
-        <v>92-97</v>
+        <v>95-100</v>
       </c>
       <c r="F348" t="str">
         <v>12.50%</v>
@@ -7363,7 +7363,7 @@
     </row>
     <row r="349">
       <c r="A349">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B349" t="str">
         <v>Poké Pelago</v>
@@ -7372,10 +7372,10 @@
         <v>Elite Four defeated 3</v>
       </c>
       <c r="D349" t="str">
-        <v>Jynx</v>
+        <v>Fletchling</v>
       </c>
       <c r="E349" t="str">
-        <v>92-97</v>
+        <v>95-100</v>
       </c>
       <c r="F349" t="str">
         <v>12.50%</v>
@@ -7383,7 +7383,7 @@
     </row>
     <row r="350">
       <c r="A350">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B350" t="str">
         <v>Poké Pelago</v>
@@ -7392,10 +7392,10 @@
         <v>Elite Four defeated 3</v>
       </c>
       <c r="D350" t="str">
-        <v>Emolga</v>
+        <v>Hawlucha</v>
       </c>
       <c r="E350" t="str">
-        <v>92-97</v>
+        <v>95-100</v>
       </c>
       <c r="F350" t="str">
         <v>12.50%</v>
@@ -7403,7 +7403,7 @@
     </row>
     <row r="351">
       <c r="A351">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B351" t="str">
         <v>Poké Pelago</v>
@@ -7412,10 +7412,10 @@
         <v>Elite Four defeated 3</v>
       </c>
       <c r="D351" t="str">
-        <v>Scyther</v>
+        <v>Lapras</v>
       </c>
       <c r="E351" t="str">
-        <v>92-97</v>
+        <v>95-100</v>
       </c>
       <c r="F351" t="str">
         <v>12.50%</v>
@@ -7423,7 +7423,7 @@
     </row>
     <row r="352">
       <c r="A352">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B352" t="str">
         <v>Poké Pelago</v>
@@ -7432,10 +7432,10 @@
         <v>Elite Four defeated 3</v>
       </c>
       <c r="D352" t="str">
-        <v>Talonflame</v>
+        <v>Jynx</v>
       </c>
       <c r="E352" t="str">
-        <v>92-97</v>
+        <v>95-100</v>
       </c>
       <c r="F352" t="str">
         <v>12.50%</v>
@@ -7449,13 +7449,13 @@
         <v>Poké Pelago</v>
       </c>
       <c r="C353" t="str">
-        <v>Elite Four defeated 4</v>
+        <v>Elite Four defeated 3</v>
       </c>
       <c r="D353" t="str">
-        <v>Tropius</v>
+        <v>Emolga</v>
       </c>
       <c r="E353" t="str">
-        <v>93-98</v>
+        <v>95-100</v>
       </c>
       <c r="F353" t="str">
         <v>12.50%</v>
@@ -7469,13 +7469,13 @@
         <v>Poké Pelago</v>
       </c>
       <c r="C354" t="str">
-        <v>Elite Four defeated 4</v>
+        <v>Elite Four defeated 3</v>
       </c>
       <c r="D354" t="str">
-        <v>Comfey</v>
+        <v>Scyther</v>
       </c>
       <c r="E354" t="str">
-        <v>93-98</v>
+        <v>95-100</v>
       </c>
       <c r="F354" t="str">
         <v>12.50%</v>
@@ -7489,13 +7489,13 @@
         <v>Poké Pelago</v>
       </c>
       <c r="C355" t="str">
-        <v>Elite Four defeated 4</v>
+        <v>Elite Four defeated 3</v>
       </c>
       <c r="D355" t="str">
-        <v>Hoothoot</v>
+        <v>Talonflame</v>
       </c>
       <c r="E355" t="str">
-        <v>93-98</v>
+        <v>95-100</v>
       </c>
       <c r="F355" t="str">
         <v>12.50%</v>
@@ -7503,7 +7503,7 @@
     </row>
     <row r="356">
       <c r="A356">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B356" t="str">
         <v>Poké Pelago</v>
@@ -7512,10 +7512,10 @@
         <v>Elite Four defeated 4</v>
       </c>
       <c r="D356" t="str">
-        <v>Seel</v>
+        <v>Tropius</v>
       </c>
       <c r="E356" t="str">
-        <v>93-98</v>
+        <v>95-100</v>
       </c>
       <c r="F356" t="str">
         <v>12.50%</v>
@@ -7523,7 +7523,7 @@
     </row>
     <row r="357">
       <c r="A357">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B357" t="str">
         <v>Poké Pelago</v>
@@ -7532,10 +7532,10 @@
         <v>Elite Four defeated 4</v>
       </c>
       <c r="D357" t="str">
-        <v>Snubbull</v>
+        <v>Comfey</v>
       </c>
       <c r="E357" t="str">
-        <v>93-98</v>
+        <v>95-100</v>
       </c>
       <c r="F357" t="str">
         <v>12.50%</v>
@@ -7543,7 +7543,7 @@
     </row>
     <row r="358">
       <c r="A358">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B358" t="str">
         <v>Poké Pelago</v>
@@ -7552,10 +7552,10 @@
         <v>Elite Four defeated 4</v>
       </c>
       <c r="D358" t="str">
-        <v>Metang</v>
+        <v>Hoothoot</v>
       </c>
       <c r="E358" t="str">
-        <v>93-98</v>
+        <v>95-100</v>
       </c>
       <c r="F358" t="str">
         <v>12.50%</v>
@@ -7563,7 +7563,7 @@
     </row>
     <row r="359">
       <c r="A359">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B359" t="str">
         <v>Poké Pelago</v>
@@ -7572,10 +7572,10 @@
         <v>Elite Four defeated 4</v>
       </c>
       <c r="D359" t="str">
-        <v>Houndour</v>
+        <v>Seel</v>
       </c>
       <c r="E359" t="str">
-        <v>93-98</v>
+        <v>95-100</v>
       </c>
       <c r="F359" t="str">
         <v>12.50%</v>
@@ -7583,7 +7583,7 @@
     </row>
     <row r="360">
       <c r="A360">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B360" t="str">
         <v>Poké Pelago</v>
@@ -7592,10 +7592,10 @@
         <v>Elite Four defeated 4</v>
       </c>
       <c r="D360" t="str">
-        <v>Lickitung</v>
+        <v>Snubbull</v>
       </c>
       <c r="E360" t="str">
-        <v>93-98</v>
+        <v>95-100</v>
       </c>
       <c r="F360" t="str">
         <v>12.50%</v>
@@ -7609,16 +7609,16 @@
         <v>Poké Pelago</v>
       </c>
       <c r="C361" t="str">
-        <v>Elite Four defeated 5</v>
+        <v>Elite Four defeated 4</v>
       </c>
       <c r="D361" t="str">
-        <v>Misdreavus</v>
+        <v>Metang</v>
       </c>
       <c r="E361" t="str">
-        <v>94-99</v>
+        <v>95-100</v>
       </c>
       <c r="F361" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="362">
@@ -7629,16 +7629,16 @@
         <v>Poké Pelago</v>
       </c>
       <c r="C362" t="str">
-        <v>Elite Four defeated 5</v>
+        <v>Elite Four defeated 4</v>
       </c>
       <c r="D362" t="str">
-        <v>Staryu</v>
+        <v>Houndour</v>
       </c>
       <c r="E362" t="str">
-        <v>94-99</v>
+        <v>95-100</v>
       </c>
       <c r="F362" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="363">
@@ -7649,21 +7649,21 @@
         <v>Poké Pelago</v>
       </c>
       <c r="C363" t="str">
-        <v>Elite Four defeated 5</v>
+        <v>Elite Four defeated 4</v>
       </c>
       <c r="D363" t="str">
-        <v>Klefki</v>
+        <v>Lickitung</v>
       </c>
       <c r="E363" t="str">
-        <v>94-99</v>
+        <v>95-100</v>
       </c>
       <c r="F363" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="364">
       <c r="A364">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B364" t="str">
         <v>Poké Pelago</v>
@@ -7672,10 +7672,10 @@
         <v>Elite Four defeated 5</v>
       </c>
       <c r="D364" t="str">
-        <v>Natu</v>
+        <v>Misdreavus</v>
       </c>
       <c r="E364" t="str">
-        <v>94-99</v>
+        <v>95-100</v>
       </c>
       <c r="F364" t="str">
         <v>14.29%</v>
@@ -7683,7 +7683,7 @@
     </row>
     <row r="365">
       <c r="A365">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B365" t="str">
         <v>Poké Pelago</v>
@@ -7692,10 +7692,10 @@
         <v>Elite Four defeated 5</v>
       </c>
       <c r="D365" t="str">
-        <v>Flaaffy</v>
+        <v>Staryu</v>
       </c>
       <c r="E365" t="str">
-        <v>94-99</v>
+        <v>95-100</v>
       </c>
       <c r="F365" t="str">
         <v>14.29%</v>
@@ -7703,7 +7703,7 @@
     </row>
     <row r="366">
       <c r="A366">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B366" t="str">
         <v>Poké Pelago</v>
@@ -7712,10 +7712,10 @@
         <v>Elite Four defeated 5</v>
       </c>
       <c r="D366" t="str">
-        <v>Drifblim</v>
+        <v>Klefki</v>
       </c>
       <c r="E366" t="str">
-        <v>94-99</v>
+        <v>95-100</v>
       </c>
       <c r="F366" t="str">
         <v>14.29%</v>
@@ -7723,7 +7723,7 @@
     </row>
     <row r="367">
       <c r="A367">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B367" t="str">
         <v>Poké Pelago</v>
@@ -7732,10 +7732,10 @@
         <v>Elite Four defeated 5</v>
       </c>
       <c r="D367" t="str">
-        <v>Honchkrow</v>
+        <v>Natu</v>
       </c>
       <c r="E367" t="str">
-        <v>94-99</v>
+        <v>95-100</v>
       </c>
       <c r="F367" t="str">
         <v>14.29%</v>
@@ -7749,16 +7749,16 @@
         <v>Poké Pelago</v>
       </c>
       <c r="C368" t="str">
-        <v>Elite Four defeated 6</v>
+        <v>Elite Four defeated 5</v>
       </c>
       <c r="D368" t="str">
-        <v>Pikipek</v>
+        <v>Flaaffy</v>
       </c>
       <c r="E368" t="str">
         <v>95-100</v>
       </c>
       <c r="F368" t="str">
-        <v>10.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="369">
@@ -7769,16 +7769,16 @@
         <v>Poké Pelago</v>
       </c>
       <c r="C369" t="str">
-        <v>Elite Four defeated 6</v>
+        <v>Elite Four defeated 5</v>
       </c>
       <c r="D369" t="str">
-        <v>Slowpoke</v>
+        <v>Drifblim</v>
       </c>
       <c r="E369" t="str">
         <v>95-100</v>
       </c>
       <c r="F369" t="str">
-        <v>10.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="370">
@@ -7789,21 +7789,21 @@
         <v>Poké Pelago</v>
       </c>
       <c r="C370" t="str">
-        <v>Elite Four defeated 6</v>
+        <v>Elite Four defeated 5</v>
       </c>
       <c r="D370" t="str">
-        <v>Wingull</v>
+        <v>Honchkrow</v>
       </c>
       <c r="E370" t="str">
         <v>95-100</v>
       </c>
       <c r="F370" t="str">
-        <v>10.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="371">
       <c r="A371">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B371" t="str">
         <v>Poké Pelago</v>
@@ -7812,7 +7812,7 @@
         <v>Elite Four defeated 6</v>
       </c>
       <c r="D371" t="str">
-        <v>Magnemite</v>
+        <v>Pikipek</v>
       </c>
       <c r="E371" t="str">
         <v>95-100</v>
@@ -7823,7 +7823,7 @@
     </row>
     <row r="372">
       <c r="A372">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B372" t="str">
         <v>Poké Pelago</v>
@@ -7832,7 +7832,7 @@
         <v>Elite Four defeated 6</v>
       </c>
       <c r="D372" t="str">
-        <v>Zubat</v>
+        <v>Slowpoke</v>
       </c>
       <c r="E372" t="str">
         <v>95-100</v>
@@ -7843,7 +7843,7 @@
     </row>
     <row r="373">
       <c r="A373">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B373" t="str">
         <v>Poké Pelago</v>
@@ -7852,7 +7852,7 @@
         <v>Elite Four defeated 6</v>
       </c>
       <c r="D373" t="str">
-        <v>Shellder</v>
+        <v>Wingull</v>
       </c>
       <c r="E373" t="str">
         <v>95-100</v>
@@ -7863,7 +7863,7 @@
     </row>
     <row r="374">
       <c r="A374">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B374" t="str">
         <v>Poké Pelago</v>
@@ -7872,7 +7872,7 @@
         <v>Elite Four defeated 6</v>
       </c>
       <c r="D374" t="str">
-        <v>Rufflet</v>
+        <v>Magnemite</v>
       </c>
       <c r="E374" t="str">
         <v>95-100</v>
@@ -7883,7 +7883,7 @@
     </row>
     <row r="375">
       <c r="A375">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B375" t="str">
         <v>Poké Pelago</v>
@@ -7892,7 +7892,7 @@
         <v>Elite Four defeated 6</v>
       </c>
       <c r="D375" t="str">
-        <v>Vullaby</v>
+        <v>Zubat</v>
       </c>
       <c r="E375" t="str">
         <v>95-100</v>
@@ -7903,7 +7903,7 @@
     </row>
     <row r="376">
       <c r="A376">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B376" t="str">
         <v>Poké Pelago</v>
@@ -7912,7 +7912,7 @@
         <v>Elite Four defeated 6</v>
       </c>
       <c r="D376" t="str">
-        <v>Kadabra</v>
+        <v>Shellder</v>
       </c>
       <c r="E376" t="str">
         <v>95-100</v>
@@ -7923,7 +7923,7 @@
     </row>
     <row r="377">
       <c r="A377">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B377" t="str">
         <v>Poké Pelago</v>
@@ -7932,7 +7932,7 @@
         <v>Elite Four defeated 6</v>
       </c>
       <c r="D377" t="str">
-        <v>Mr. Mime</v>
+        <v>Rufflet</v>
       </c>
       <c r="E377" t="str">
         <v>95-100</v>
@@ -7941,16 +7941,76 @@
         <v>10.00%</v>
       </c>
     </row>
+    <row r="378">
+      <c r="A378">
+        <v>78</v>
+      </c>
+      <c r="B378" t="str">
+        <v>Poké Pelago</v>
+      </c>
+      <c r="C378" t="str">
+        <v>Elite Four defeated 6</v>
+      </c>
+      <c r="D378" t="str">
+        <v>Vullaby</v>
+      </c>
+      <c r="E378" t="str">
+        <v>95-100</v>
+      </c>
+      <c r="F378" t="str">
+        <v>10.00%</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379">
+        <v>78</v>
+      </c>
+      <c r="B379" t="str">
+        <v>Poké Pelago</v>
+      </c>
+      <c r="C379" t="str">
+        <v>Elite Four defeated 6</v>
+      </c>
+      <c r="D379" t="str">
+        <v>Kadabra</v>
+      </c>
+      <c r="E379" t="str">
+        <v>95-100</v>
+      </c>
+      <c r="F379" t="str">
+        <v>10.00%</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380">
+        <v>78</v>
+      </c>
+      <c r="B380" t="str">
+        <v>Poké Pelago</v>
+      </c>
+      <c r="C380" t="str">
+        <v>Elite Four defeated 6</v>
+      </c>
+      <c r="D380" t="str">
+        <v>Mr. Mime</v>
+      </c>
+      <c r="E380" t="str">
+        <v>95-100</v>
+      </c>
+      <c r="F380" t="str">
+        <v>10.00%</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F377"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F380"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C65"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7968,10 +8028,10 @@
         <v>Challenge 1</v>
       </c>
       <c r="B2" t="str">
-        <v>Defeat Captain Ilima</v>
+        <v>Start the game</v>
       </c>
       <c r="C2" t="str">
-        <v>Hau'oli Cemetery</v>
+        <v>Route 1</v>
       </c>
     </row>
     <row r="3">
@@ -7979,10 +8039,10 @@
         <v>Challenge 2</v>
       </c>
       <c r="B3" t="str">
-        <v>Defeat Kahuna Hala</v>
+        <v>Defeat 10 Pokemon in Route 1</v>
       </c>
       <c r="C3" t="str">
-        <v>Heahea Beach</v>
+        <v>Hau'oli City</v>
       </c>
     </row>
     <row r="4">
@@ -7990,10 +8050,10 @@
         <v>Challenge 3</v>
       </c>
       <c r="B4" t="str">
-        <v>Reach Paniola Ranch</v>
+        <v>Defeat 5 Pokemon in Hau'oli City</v>
       </c>
       <c r="C4" t="str">
-        <v>Route 5</v>
+        <v>Route 2</v>
       </c>
     </row>
     <row r="5">
@@ -8001,10 +8061,10 @@
         <v>Challenge 4</v>
       </c>
       <c r="B5" t="str">
-        <v>Defeat Captain Lana</v>
+        <v>Defeat 10 Pokemon in Route 2</v>
       </c>
       <c r="C5" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Captain Ilima</v>
       </c>
     </row>
     <row r="6">
@@ -8012,10 +8072,10 @@
         <v>Challenge 5</v>
       </c>
       <c r="B6" t="str">
-        <v>Defeat Captain Kiawe</v>
+        <v>Defeat Captain Ilima</v>
       </c>
       <c r="C6" t="str">
-        <v>Route 8</v>
+        <v>Hau'oli Cemetery</v>
       </c>
     </row>
     <row r="7">
@@ -8023,10 +8083,10 @@
         <v>Challenge 6</v>
       </c>
       <c r="B7" t="str">
-        <v>Defeat Captain Mallow</v>
+        <v>Defeat 5 Pokemon in Hau'oli Cemetery</v>
       </c>
       <c r="C7" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Verdant Cavern</v>
       </c>
     </row>
     <row r="8">
@@ -8034,10 +8094,10 @@
         <v>Challenge 7</v>
       </c>
       <c r="B8" t="str">
-        <v>Defeat Kahuna Olivia</v>
+        <v>Defeat 10 Pokemon in Verdant Cavern</v>
       </c>
       <c r="C8" t="str">
-        <v>Malie City</v>
+        <v>Ten Carat Hill</v>
       </c>
     </row>
     <row r="9">
@@ -8045,10 +8105,10 @@
         <v>Challenge 8</v>
       </c>
       <c r="B9" t="str">
-        <v>Defeat Captain Sophocles</v>
+        <v>Defeat 5 Pokemon in Ten Carat Hill</v>
       </c>
       <c r="C9" t="str">
-        <v>Route 11</v>
+        <v>Seaward Cave</v>
       </c>
     </row>
     <row r="10">
@@ -8056,10 +8116,10 @@
         <v>Challenge 9</v>
       </c>
       <c r="B10" t="str">
-        <v>Defeat Captain Acerola</v>
+        <v>Defeat 5 Pokemon in Seaward Cave</v>
       </c>
       <c r="C10" t="str">
-        <v>Route 17</v>
+        <v>Route 3</v>
       </c>
     </row>
     <row r="11">
@@ -8067,10 +8127,10 @@
         <v>Challenge 10</v>
       </c>
       <c r="B11" t="str">
-        <v>Defeat Kahuna Nanu</v>
+        <v>Defeat 10 Pokemon in Route 3</v>
       </c>
       <c r="C11" t="str">
-        <v>Seafolk Village</v>
+        <v>Kahuna Hala</v>
       </c>
     </row>
     <row r="12">
@@ -8078,10 +8138,10 @@
         <v>Challenge 11</v>
       </c>
       <c r="B12" t="str">
-        <v>Defeat Captain Kommo-o</v>
+        <v>Defeat Kahuna Hala</v>
       </c>
       <c r="C12" t="str">
-        <v>Captain Mina</v>
+        <v>Heahea Beach</v>
       </c>
     </row>
     <row r="13">
@@ -8089,10 +8149,10 @@
         <v>Challenge 12</v>
       </c>
       <c r="B13" t="str">
-        <v>Defeat Captain Mina</v>
+        <v>Defeat 5 Pokemon in Heahea Beach</v>
       </c>
       <c r="C13" t="str">
-        <v>Kahuna Hapu</v>
+        <v>Route 4</v>
       </c>
     </row>
     <row r="14">
@@ -8100,10 +8160,10 @@
         <v>Challenge 13</v>
       </c>
       <c r="B14" t="str">
-        <v>Defeat Kahuna Hapu</v>
+        <v>Defeat 10 Pokemon in Route 4</v>
       </c>
       <c r="C14" t="str">
-        <v>Mount Lanakila</v>
+        <v>Paniola Ranch</v>
       </c>
     </row>
     <row r="15">
@@ -8111,10 +8171,10 @@
         <v>Challenge 14</v>
       </c>
       <c r="B15" t="str">
-        <v>Defeat Elite Four</v>
+        <v>Defeat 5 Pokemon in Paniola Ranch</v>
       </c>
       <c r="C15" t="str">
-        <v>Champion Hau</v>
+        <v>Daycare</v>
       </c>
     </row>
     <row r="16">
@@ -8122,70 +8182,554 @@
         <v>Challenge 15</v>
       </c>
       <c r="B16" t="str">
-        <v>Defeat Champion Hau</v>
+        <v>Reach Daycare</v>
       </c>
       <c r="C16" t="str">
-        <v>Poni Grove</v>
+        <v>Route 5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Extra Challenge $1</v>
+        <v>Challenge 16</v>
       </c>
       <c r="B17" t="str">
-        <v>Catch 10 Ultra Beasts (UM/US)</v>
+        <v>Defeat 5 Pokemon in Route 5</v>
       </c>
       <c r="C17" t="str">
-        <v>Ultra Space Paths</v>
+        <v>Brooklet Hill</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Extra Challenge $2</v>
+        <v>Challenge 17</v>
       </c>
       <c r="B18" t="str">
-        <v>Defeat Tapu Koko, Lele, Bulu, Fini</v>
+        <v>Defeat 10 Pokemon in Brooklet Hill</v>
       </c>
       <c r="C18" t="str">
-        <v>Tapu Shrine Paths</v>
+        <v>Captain Lana</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Extra Challenge $3</v>
+        <v>Challenge 18</v>
       </c>
       <c r="B19" t="str">
-        <v>Max Poké Pelago Islands</v>
+        <v>Defeat Captain Lana</v>
       </c>
       <c r="C19" t="str">
-        <v>Special encounters in Poké Pelago</v>
+        <v>Wela Volcano Park</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Extra Challenge $4</v>
+        <v>Challenge 19</v>
       </c>
       <c r="B20" t="str">
-        <v>Defeat Battle Tree Boss Red/Blue</v>
+        <v>Defeat 10 Pokemon in Wela Volcano Park</v>
       </c>
       <c r="C20" t="str">
-        <v>Battle Tree Master Ribbon</v>
+        <v>Captain Kiawe</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
+        <v>Challenge 20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Defeat Captain Kiawe</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Route 8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Challenge 21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Defeat 5 Pokemon in Route 8</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Lush Jungle</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Challenge 22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Defeat 10 Pokemon in Lush Jungle</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Captain Mallow</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Challenge 23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Defeat Captain Mallow</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Diglett's Tunnel</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Challenge 24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Defeat 5 Pokemon in Diglett's Tunnel</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Konikoni City</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Challenge 25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Defeat 5 Pokemon in Konikoni City</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Memorial Hill</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Challenge 26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Defeat 5 Pokemon in Memorial Hill</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Akala Outskirts</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Challenge 27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Defeat 5 Pokemon in Akala Outskirts</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Hano Beach</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Challenge 28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Defeat 5 Pokemon in Hano Beach</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Kahuna Olivia</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Challenge 29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Defeat Kahuna Olivia</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Malie City</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Challenge 30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Defeat 5 Pokemon in Malie City</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Malie Garden</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Challenge 31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Defeat 5 Pokemon in Malie Garden</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Route 10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Challenge 32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Defeat 5 Pokemon in Route 10</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Mount Hokulani</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Challenge 33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Defeat 10 Pokemon in Mount Hokulani</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Captain Sophocles</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Challenge 34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Defeat Captain Sophocles</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Route 11</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Challenge 35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Defeat 5 Pokemon in Route 11</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Route 12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Challenge 36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Defeat 5 Pokemon in Route 12</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Blush Mountain</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Challenge 37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Defeat 5 Pokemon in Blush Mountain</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Haina Desert</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Challenge 38</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Defeat 5 Pokemon in Haina Desert</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Tapu Village</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Challenge 39</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Defeat 5 Pokemon in Tapu Village</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Thrifty Megamart</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Challenge 40</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Defeat 10 Pokemon in Thrifty Megamart</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Captain Acerola</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Challenge 41</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Defeat Captain Acerola</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Route 17</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Challenge 42</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Defeat 10 Pokemon in Route 17</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Kahuna Nanu</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Challenge 43</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Defeat Kahuna Nanu</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Seafolk Village</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Challenge 44</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Defeat 5 Pokemon in Seafolk Village</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Poni Wilds</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Challenge 45</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Defeat 5 Pokemon in Poni Wilds</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Poni Breaker Coast</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Challenge 46</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Defeat 5 Pokemon in Poni Breaker Coast</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Exeggutor Island</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Challenge 47</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Defeat 5 Pokemon in Exeggutor Island</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Vast Poni Canyon</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Challenge 48</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Defeat 10 Pokemon in Vast Poni Canyon</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Captain Kommo-o</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Challenge 49</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Defeat Captain Kommo-o</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Captain Mina</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Challenge 50</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Defeat Captain Mina</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Kahuna Hapu</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Challenge 51</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Defeat Kahuna Hapu</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Mount Lanakila</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Challenge 52</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Defeat 15 Pokemon in Mount Lanakila</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Alola Pokemon League</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Challenge 53</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Defeat Alola Pokemon League</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Champion Hau</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Challenge 54</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Defeat Champion Hau</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Poni Grove</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Challenge 55</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Defeat 10 Pokemon in Poni Grove</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Poni Plains</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Challenge 56</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Defeat 10 Pokemon in Poni Plains</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Resolution Cave</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Challenge 57</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Defeat 5 Pokemon in Resolution Cave</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Mahalo Trail</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Challenge 58</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Defeat 5 Pokemon in Mahalo Trail</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Melemele Meadow</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Challenge 59</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Defeat 5 Pokemon in Melemele Meadow</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Poké Pelago</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Extra Challenge $1</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Catch 10 Ultra Beasts</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Ultra Space Paths</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Extra Challenge $2</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Defeat Tapu Koko, Lele, Bulu, Fini</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Tapu Shrine Paths</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Extra Challenge $3</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Max Poké Pelago Islands</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Special encounters in Poké Pelago</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Extra Challenge $4</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Defeat Battle Tree Boss Red/Blue</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Battle Tree Master Ribbon</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
         <v>Extra Challenge $5</v>
       </c>
-      <c r="B21" t="str">
-        <v>Collect 100 Totem Stickers (UM/US)</v>
-      </c>
-      <c r="C21" t="str">
+      <c r="B65" t="str">
+        <v>Collect 100 Totem Stickers</v>
+      </c>
+      <c r="C65" t="str">
         <v>Totem-Sized Pokemon</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C65"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Alola_Paths_and_Challenges.xlsx
+++ b/Alola_Paths_and_Challenges.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="Paths" sheetId="1" r:id="rId1"/>
     <sheet name="Challenges" sheetId="2" r:id="rId2"/>
+    <sheet name="Missing Pokemons" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -398,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F262"/>
+  <dimension ref="A1:F260"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -431,7 +432,7 @@
         <v>Professor Kukui</v>
       </c>
       <c r="D2" t="str">
-        <v>Popplio</v>
+        <v>Rowlet</v>
       </c>
       <c r="E2" t="str">
         <v>2-7</v>
@@ -471,7 +472,7 @@
         <v>Professor Kukui</v>
       </c>
       <c r="D4" t="str">
-        <v>Rowlet</v>
+        <v>Popplio</v>
       </c>
       <c r="E4" t="str">
         <v>2-7</v>
@@ -497,7 +498,7 @@
         <v>3-8</v>
       </c>
       <c r="F5" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +518,7 @@
         <v>3-8</v>
       </c>
       <c r="F6" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="7">
@@ -537,7 +538,7 @@
         <v>3-8</v>
       </c>
       <c r="F7" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="8">
@@ -557,7 +558,7 @@
         <v>3-8</v>
       </c>
       <c r="F8" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="9">
@@ -577,7 +578,7 @@
         <v>3-8</v>
       </c>
       <c r="F9" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="10">
@@ -597,7 +598,7 @@
         <v>3-8</v>
       </c>
       <c r="F10" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="11">
@@ -617,27 +618,27 @@
         <v>3-8</v>
       </c>
       <c r="F11" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="str">
         <v>Route 1</v>
       </c>
       <c r="C12" t="str">
-        <v>Hau'oli Outskirts</v>
+        <v>East</v>
       </c>
       <c r="D12" t="str">
-        <v>Inkay</v>
+        <v>Pikachu</v>
       </c>
       <c r="E12" t="str">
         <v>3-8</v>
       </c>
       <c r="F12" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="13">
@@ -651,10 +652,10 @@
         <v>Hau'oli Outskirts</v>
       </c>
       <c r="D13" t="str">
-        <v>Slowpoke</v>
+        <v>Inkay</v>
       </c>
       <c r="E13" t="str">
-        <v>3-8</v>
+        <v>4-9</v>
       </c>
       <c r="F13" t="str">
         <v>20.00%</v>
@@ -671,10 +672,10 @@
         <v>Hau'oli Outskirts</v>
       </c>
       <c r="D14" t="str">
-        <v>Alolan Meowth</v>
+        <v>Slowpoke</v>
       </c>
       <c r="E14" t="str">
-        <v>3-8</v>
+        <v>4-9</v>
       </c>
       <c r="F14" t="str">
         <v>20.00%</v>
@@ -691,10 +692,10 @@
         <v>Hau'oli Outskirts</v>
       </c>
       <c r="D15" t="str">
-        <v>Tentacool</v>
+        <v>Alolan Meowth</v>
       </c>
       <c r="E15" t="str">
-        <v>3-8</v>
+        <v>4-9</v>
       </c>
       <c r="F15" t="str">
         <v>20.00%</v>
@@ -711,10 +712,10 @@
         <v>Hau'oli Outskirts</v>
       </c>
       <c r="D16" t="str">
-        <v>Finneon</v>
+        <v>Tentacool</v>
       </c>
       <c r="E16" t="str">
-        <v>3-8</v>
+        <v>4-9</v>
       </c>
       <c r="F16" t="str">
         <v>20.00%</v>
@@ -722,22 +723,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" t="str">
         <v>Route 1</v>
       </c>
       <c r="C17" t="str">
-        <v>South</v>
+        <v>Hau'oli Outskirts</v>
       </c>
       <c r="D17" t="str">
-        <v>Bonsly</v>
+        <v>Finneon</v>
       </c>
       <c r="E17" t="str">
-        <v>3-8</v>
+        <v>4-9</v>
       </c>
       <c r="F17" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="18">
@@ -751,10 +752,10 @@
         <v>South</v>
       </c>
       <c r="D18" t="str">
-        <v>Munchlax</v>
+        <v>Bonsly</v>
       </c>
       <c r="E18" t="str">
-        <v>3-8</v>
+        <v>5-10</v>
       </c>
       <c r="F18" t="str">
         <v>33.33%</v>
@@ -771,10 +772,10 @@
         <v>South</v>
       </c>
       <c r="D19" t="str">
-        <v>Rockruff</v>
+        <v>Munchlax</v>
       </c>
       <c r="E19" t="str">
-        <v>3-8</v>
+        <v>5-10</v>
       </c>
       <c r="F19" t="str">
         <v>33.33%</v>
@@ -782,39 +783,39 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B20" t="str">
         <v>Route 1</v>
       </c>
       <c r="C20" t="str">
-        <v>Trainers' School</v>
+        <v>South</v>
       </c>
       <c r="D20" t="str">
-        <v>Zorua</v>
+        <v>Rockruff</v>
       </c>
       <c r="E20" t="str">
-        <v>3-8</v>
+        <v>5-10</v>
       </c>
       <c r="F20" t="str">
-        <v>100.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B21" t="str">
         <v>Route 1</v>
       </c>
       <c r="C21" t="str">
-        <v>Special Encounter</v>
+        <v>Trainers' School</v>
       </c>
       <c r="D21" t="str">
-        <v>Pikachu</v>
+        <v>Zorua</v>
       </c>
       <c r="E21" t="str">
-        <v>3-8</v>
+        <v>6-11</v>
       </c>
       <c r="F21" t="str">
         <v>100.00%</v>
@@ -822,7 +823,7 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B22" t="str">
         <v>Hau'oli City</v>
@@ -834,7 +835,7 @@
         <v>Luvdisc</v>
       </c>
       <c r="E22" t="str">
-        <v>4-9</v>
+        <v>7-12</v>
       </c>
       <c r="F22" t="str">
         <v>25.00%</v>
@@ -842,7 +843,7 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B23" t="str">
         <v>Hau'oli City</v>
@@ -854,7 +855,7 @@
         <v>Corsola</v>
       </c>
       <c r="E23" t="str">
-        <v>4-9</v>
+        <v>7-12</v>
       </c>
       <c r="F23" t="str">
         <v>25.00%</v>
@@ -862,7 +863,7 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B24" t="str">
         <v>Hau'oli City</v>
@@ -874,7 +875,7 @@
         <v>Remoraid</v>
       </c>
       <c r="E24" t="str">
-        <v>4-9</v>
+        <v>7-12</v>
       </c>
       <c r="F24" t="str">
         <v>25.00%</v>
@@ -882,7 +883,7 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B25" t="str">
         <v>Hau'oli City</v>
@@ -894,7 +895,7 @@
         <v>Clamperl</v>
       </c>
       <c r="E25" t="str">
-        <v>4-9</v>
+        <v>7-12</v>
       </c>
       <c r="F25" t="str">
         <v>25.00%</v>
@@ -902,7 +903,7 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B26" t="str">
         <v>Hau'oli City</v>
@@ -914,7 +915,7 @@
         <v>Furfrou</v>
       </c>
       <c r="E26" t="str">
-        <v>4-9</v>
+        <v>8-13</v>
       </c>
       <c r="F26" t="str">
         <v>20.00%</v>
@@ -922,7 +923,7 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B27" t="str">
         <v>Hau'oli City</v>
@@ -934,7 +935,7 @@
         <v>Hypno</v>
       </c>
       <c r="E27" t="str">
-        <v>4-9</v>
+        <v>8-13</v>
       </c>
       <c r="F27" t="str">
         <v>20.00%</v>
@@ -942,7 +943,7 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B28" t="str">
         <v>Hau'oli City</v>
@@ -954,7 +955,7 @@
         <v>Abra</v>
       </c>
       <c r="E28" t="str">
-        <v>4-9</v>
+        <v>8-13</v>
       </c>
       <c r="F28" t="str">
         <v>20.00%</v>
@@ -962,7 +963,7 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B29" t="str">
         <v>Hau'oli City</v>
@@ -974,7 +975,7 @@
         <v>Mime Jr.</v>
       </c>
       <c r="E29" t="str">
-        <v>4-9</v>
+        <v>8-13</v>
       </c>
       <c r="F29" t="str">
         <v>20.00%</v>
@@ -982,7 +983,7 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B30" t="str">
         <v>Hau'oli City</v>
@@ -994,7 +995,7 @@
         <v>Bewear</v>
       </c>
       <c r="E30" t="str">
-        <v>4-9</v>
+        <v>8-13</v>
       </c>
       <c r="F30" t="str">
         <v>20.00%</v>
@@ -1002,7 +1003,7 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B31" t="str">
         <v>Route 2</v>
@@ -1014,7 +1015,7 @@
         <v>Machop</v>
       </c>
       <c r="E31" t="str">
-        <v>6-11</v>
+        <v>9-14</v>
       </c>
       <c r="F31" t="str">
         <v>50.00%</v>
@@ -1022,7 +1023,7 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B32" t="str">
         <v>Route 2</v>
@@ -1034,7 +1035,7 @@
         <v>Hawlucha</v>
       </c>
       <c r="E32" t="str">
-        <v>6-11</v>
+        <v>9-14</v>
       </c>
       <c r="F32" t="str">
         <v>50.00%</v>
@@ -1042,7 +1043,7 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B33" t="str">
         <v>Route 2</v>
@@ -1054,7 +1055,7 @@
         <v>Drowzee</v>
       </c>
       <c r="E33" t="str">
-        <v>6-11</v>
+        <v>10-15</v>
       </c>
       <c r="F33" t="str">
         <v>16.67%</v>
@@ -1062,7 +1063,7 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B34" t="str">
         <v>Route 2</v>
@@ -1074,7 +1075,7 @@
         <v>Makuhita</v>
       </c>
       <c r="E34" t="str">
-        <v>6-11</v>
+        <v>10-15</v>
       </c>
       <c r="F34" t="str">
         <v>16.67%</v>
@@ -1082,7 +1083,7 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B35" t="str">
         <v>Route 2</v>
@@ -1094,7 +1095,7 @@
         <v>Spearow</v>
       </c>
       <c r="E35" t="str">
-        <v>6-11</v>
+        <v>10-15</v>
       </c>
       <c r="F35" t="str">
         <v>16.67%</v>
@@ -1102,7 +1103,7 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B36" t="str">
         <v>Route 2</v>
@@ -1114,7 +1115,7 @@
         <v>Ekans</v>
       </c>
       <c r="E36" t="str">
-        <v>6-11</v>
+        <v>10-15</v>
       </c>
       <c r="F36" t="str">
         <v>16.67%</v>
@@ -1122,7 +1123,7 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B37" t="str">
         <v>Route 2</v>
@@ -1134,7 +1135,7 @@
         <v>Growlithe</v>
       </c>
       <c r="E37" t="str">
-        <v>6-11</v>
+        <v>10-15</v>
       </c>
       <c r="F37" t="str">
         <v>16.67%</v>
@@ -1142,7 +1143,7 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B38" t="str">
         <v>Route 2</v>
@@ -1154,7 +1155,7 @@
         <v>Smeargle</v>
       </c>
       <c r="E38" t="str">
-        <v>6-11</v>
+        <v>10-15</v>
       </c>
       <c r="F38" t="str">
         <v>16.67%</v>
@@ -1162,7 +1163,7 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B39" t="str">
         <v>Captain Ilima</v>
@@ -1174,7 +1175,7 @@
         <v>Boss</v>
       </c>
       <c r="E39" t="str">
-        <v>7-12</v>
+        <v>11-16</v>
       </c>
       <c r="F39" t="str">
         <v>-</v>
@@ -1182,7 +1183,7 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B40" t="str">
         <v>Hau'oli Cemetery</v>
@@ -1194,7 +1195,7 @@
         <v>Gastly</v>
       </c>
       <c r="E40" t="str">
-        <v>8-13</v>
+        <v>12-17</v>
       </c>
       <c r="F40" t="str">
         <v>25.00%</v>
@@ -1202,7 +1203,7 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B41" t="str">
         <v>Hau'oli Cemetery</v>
@@ -1214,7 +1215,7 @@
         <v>Drifloon</v>
       </c>
       <c r="E41" t="str">
-        <v>8-13</v>
+        <v>12-17</v>
       </c>
       <c r="F41" t="str">
         <v>25.00%</v>
@@ -1222,7 +1223,7 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B42" t="str">
         <v>Hau'oli Cemetery</v>
@@ -1234,7 +1235,7 @@
         <v>Murkrow</v>
       </c>
       <c r="E42" t="str">
-        <v>8-13</v>
+        <v>12-17</v>
       </c>
       <c r="F42" t="str">
         <v>25.00%</v>
@@ -1242,7 +1243,7 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B43" t="str">
         <v>Hau'oli Cemetery</v>
@@ -1254,7 +1255,7 @@
         <v>Misdreavus</v>
       </c>
       <c r="E43" t="str">
-        <v>8-13</v>
+        <v>12-17</v>
       </c>
       <c r="F43" t="str">
         <v>25.00%</v>
@@ -1262,7 +1263,7 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B44" t="str">
         <v>Verdant Cavern</v>
@@ -1274,7 +1275,7 @@
         <v>Pheromosa</v>
       </c>
       <c r="E44" t="str">
-        <v>9-14</v>
+        <v>14-19</v>
       </c>
       <c r="F44" t="str">
         <v>100.00%</v>
@@ -1282,42 +1283,42 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B45" t="str">
         <v>Ten Carat Hill</v>
       </c>
       <c r="C45" t="str">
-        <v>Farthest Hollow</v>
+        <v>Inside</v>
       </c>
       <c r="D45" t="str">
-        <v>Roggenrola</v>
+        <v>Mawile</v>
       </c>
       <c r="E45" t="str">
-        <v>11-16</v>
+        <v>15-20</v>
       </c>
       <c r="F45" t="str">
-        <v>25.00%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B46" t="str">
         <v>Ten Carat Hill</v>
       </c>
       <c r="C46" t="str">
-        <v>Farthest Hollow</v>
+        <v>Inside</v>
       </c>
       <c r="D46" t="str">
-        <v>Carbink</v>
+        <v>Lycanroc</v>
       </c>
       <c r="E46" t="str">
-        <v>11-16</v>
+        <v>15-20</v>
       </c>
       <c r="F46" t="str">
-        <v>25.00%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="47">
@@ -1331,10 +1332,10 @@
         <v>Farthest Hollow</v>
       </c>
       <c r="D47" t="str">
-        <v>Spinda</v>
+        <v>Roggenrola</v>
       </c>
       <c r="E47" t="str">
-        <v>11-16</v>
+        <v>16-21</v>
       </c>
       <c r="F47" t="str">
         <v>25.00%</v>
@@ -1351,10 +1352,10 @@
         <v>Farthest Hollow</v>
       </c>
       <c r="D48" t="str">
-        <v>Necrozma</v>
+        <v>Carbink</v>
       </c>
       <c r="E48" t="str">
-        <v>11-16</v>
+        <v>16-21</v>
       </c>
       <c r="F48" t="str">
         <v>25.00%</v>
@@ -1362,47 +1363,47 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B49" t="str">
         <v>Ten Carat Hill</v>
       </c>
       <c r="C49" t="str">
-        <v>Inside</v>
+        <v>Farthest Hollow</v>
       </c>
       <c r="D49" t="str">
-        <v>Mawile</v>
+        <v>Spinda</v>
       </c>
       <c r="E49" t="str">
-        <v>11-16</v>
+        <v>16-21</v>
       </c>
       <c r="F49" t="str">
-        <v>100.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B50" t="str">
         <v>Ten Carat Hill</v>
       </c>
       <c r="C50" t="str">
-        <v>Special Encounter</v>
+        <v>Farthest Hollow</v>
       </c>
       <c r="D50" t="str">
-        <v>Lycanroc</v>
+        <v>Necrozma</v>
       </c>
       <c r="E50" t="str">
-        <v>11-16</v>
+        <v>16-21</v>
       </c>
       <c r="F50" t="str">
-        <v>100.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B51" t="str">
         <v>Seaward Cave</v>
@@ -1414,7 +1415,7 @@
         <v>Barboach</v>
       </c>
       <c r="E51" t="str">
-        <v>12-17</v>
+        <v>17-22</v>
       </c>
       <c r="F51" t="str">
         <v>33.33%</v>
@@ -1422,7 +1423,7 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B52" t="str">
         <v>Seaward Cave</v>
@@ -1434,7 +1435,7 @@
         <v>Smoochum</v>
       </c>
       <c r="E52" t="str">
-        <v>12-17</v>
+        <v>17-22</v>
       </c>
       <c r="F52" t="str">
         <v>33.33%</v>
@@ -1442,7 +1443,7 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B53" t="str">
         <v>Seaward Cave</v>
@@ -1454,7 +1455,7 @@
         <v>Seel</v>
       </c>
       <c r="E53" t="str">
-        <v>12-17</v>
+        <v>17-22</v>
       </c>
       <c r="F53" t="str">
         <v>33.33%</v>
@@ -1462,7 +1463,7 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B54" t="str">
         <v>Route 3</v>
@@ -1474,15 +1475,15 @@
         <v>Mankey</v>
       </c>
       <c r="E54" t="str">
-        <v>13-18</v>
+        <v>18-23</v>
       </c>
       <c r="F54" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B55" t="str">
         <v>Route 3</v>
@@ -1494,15 +1495,15 @@
         <v>Delibird</v>
       </c>
       <c r="E55" t="str">
-        <v>13-18</v>
+        <v>18-23</v>
       </c>
       <c r="F55" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B56" t="str">
         <v>Route 3</v>
@@ -1514,35 +1515,35 @@
         <v>Bagon</v>
       </c>
       <c r="E56" t="str">
-        <v>13-18</v>
+        <v>18-23</v>
       </c>
       <c r="F56" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B57" t="str">
         <v>Route 3</v>
       </c>
       <c r="C57" t="str">
-        <v>Special Encounter</v>
+        <v>North</v>
       </c>
       <c r="D57" t="str">
         <v>Oricorio</v>
       </c>
       <c r="E57" t="str">
-        <v>13-18</v>
+        <v>18-23</v>
       </c>
       <c r="F57" t="str">
-        <v>100.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B58" t="str">
         <v>Ruins of Conflict</v>
@@ -1554,7 +1555,7 @@
         <v>Tapu Koko</v>
       </c>
       <c r="E58" t="str">
-        <v>14-19</v>
+        <v>19-24</v>
       </c>
       <c r="F58" t="str">
         <v>100.00%</v>
@@ -1562,7 +1563,7 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B59" t="str">
         <v>Kahuna Hala</v>
@@ -1574,7 +1575,7 @@
         <v>Boss</v>
       </c>
       <c r="E59" t="str">
-        <v>16-21</v>
+        <v>20-25</v>
       </c>
       <c r="F59" t="str">
         <v>-</v>
@@ -1582,7 +1583,7 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B60" t="str">
         <v>Heahea Beach</v>
@@ -1594,7 +1595,7 @@
         <v>Vikavolt</v>
       </c>
       <c r="E60" t="str">
-        <v>17-22</v>
+        <v>21-26</v>
       </c>
       <c r="F60" t="str">
         <v>12.50%</v>
@@ -1602,7 +1603,7 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B61" t="str">
         <v>Heahea Beach</v>
@@ -1614,7 +1615,7 @@
         <v>Ribombee</v>
       </c>
       <c r="E61" t="str">
-        <v>17-22</v>
+        <v>21-26</v>
       </c>
       <c r="F61" t="str">
         <v>12.50%</v>
@@ -1622,7 +1623,7 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B62" t="str">
         <v>Heahea Beach</v>
@@ -1634,7 +1635,7 @@
         <v>Araquanid</v>
       </c>
       <c r="E62" t="str">
-        <v>17-22</v>
+        <v>21-26</v>
       </c>
       <c r="F62" t="str">
         <v>12.50%</v>
@@ -1642,7 +1643,7 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B63" t="str">
         <v>Heahea Beach</v>
@@ -1654,7 +1655,7 @@
         <v>Lurantis</v>
       </c>
       <c r="E63" t="str">
-        <v>17-22</v>
+        <v>21-26</v>
       </c>
       <c r="F63" t="str">
         <v>12.50%</v>
@@ -1662,7 +1663,7 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B64" t="str">
         <v>Heahea Beach</v>
@@ -1674,7 +1675,7 @@
         <v>Salazzle</v>
       </c>
       <c r="E64" t="str">
-        <v>17-22</v>
+        <v>21-26</v>
       </c>
       <c r="F64" t="str">
         <v>12.50%</v>
@@ -1682,7 +1683,7 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B65" t="str">
         <v>Heahea Beach</v>
@@ -1694,7 +1695,7 @@
         <v>Alolan Marowak</v>
       </c>
       <c r="E65" t="str">
-        <v>17-22</v>
+        <v>21-26</v>
       </c>
       <c r="F65" t="str">
         <v>12.50%</v>
@@ -1702,7 +1703,7 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B66" t="str">
         <v>Heahea Beach</v>
@@ -1714,7 +1715,7 @@
         <v>Kommo-o</v>
       </c>
       <c r="E66" t="str">
-        <v>17-22</v>
+        <v>21-26</v>
       </c>
       <c r="F66" t="str">
         <v>12.50%</v>
@@ -1722,7 +1723,7 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B67" t="str">
         <v>Heahea Beach</v>
@@ -1734,7 +1735,7 @@
         <v>Mimikyu</v>
       </c>
       <c r="E67" t="str">
-        <v>17-22</v>
+        <v>21-26</v>
       </c>
       <c r="F67" t="str">
         <v>12.50%</v>
@@ -1742,7 +1743,7 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B68" t="str">
         <v>Route 4</v>
@@ -1754,7 +1755,7 @@
         <v>Igglybuff</v>
       </c>
       <c r="E68" t="str">
-        <v>18-23</v>
+        <v>22-27</v>
       </c>
       <c r="F68" t="str">
         <v>100.00%</v>
@@ -1762,7 +1763,7 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B69" t="str">
         <v>Paniola Ranch</v>
@@ -1774,7 +1775,7 @@
         <v>Eevee</v>
       </c>
       <c r="E69" t="str">
-        <v>20-25</v>
+        <v>23-28</v>
       </c>
       <c r="F69" t="str">
         <v>25.00%</v>
@@ -1782,7 +1783,7 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B70" t="str">
         <v>Paniola Ranch</v>
@@ -1794,7 +1795,7 @@
         <v>Mareep</v>
       </c>
       <c r="E70" t="str">
-        <v>20-25</v>
+        <v>23-28</v>
       </c>
       <c r="F70" t="str">
         <v>25.00%</v>
@@ -1802,7 +1803,7 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B71" t="str">
         <v>Paniola Ranch</v>
@@ -1814,7 +1815,7 @@
         <v>Tauros</v>
       </c>
       <c r="E71" t="str">
-        <v>20-25</v>
+        <v>23-28</v>
       </c>
       <c r="F71" t="str">
         <v>25.00%</v>
@@ -1822,7 +1823,7 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B72" t="str">
         <v>Paniola Ranch</v>
@@ -1834,7 +1835,7 @@
         <v>Miltank</v>
       </c>
       <c r="E72" t="str">
-        <v>20-25</v>
+        <v>23-28</v>
       </c>
       <c r="F72" t="str">
         <v>25.00%</v>
@@ -1842,7 +1843,7 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B73" t="str">
         <v>Daycare</v>
@@ -1862,7 +1863,7 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B74" t="str">
         <v>Route 5</v>
@@ -1874,7 +1875,7 @@
         <v>Noibat</v>
       </c>
       <c r="E74" t="str">
-        <v>22-27</v>
+        <v>26-31</v>
       </c>
       <c r="F74" t="str">
         <v>33.33%</v>
@@ -1882,7 +1883,7 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B75" t="str">
         <v>Route 5</v>
@@ -1894,7 +1895,7 @@
         <v>Fomantis</v>
       </c>
       <c r="E75" t="str">
-        <v>22-27</v>
+        <v>26-31</v>
       </c>
       <c r="F75" t="str">
         <v>33.33%</v>
@@ -1902,7 +1903,7 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B76" t="str">
         <v>Route 5</v>
@@ -1914,7 +1915,7 @@
         <v>Bounsweet</v>
       </c>
       <c r="E76" t="str">
-        <v>22-27</v>
+        <v>26-31</v>
       </c>
       <c r="F76" t="str">
         <v>33.33%</v>
@@ -1922,7 +1923,7 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B77" t="str">
         <v>Brooklet Hill</v>
@@ -1934,7 +1935,7 @@
         <v>Magikarp</v>
       </c>
       <c r="E77" t="str">
-        <v>23-28</v>
+        <v>27-32</v>
       </c>
       <c r="F77" t="str">
         <v>20.00%</v>
@@ -1942,7 +1943,7 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B78" t="str">
         <v>Brooklet Hill</v>
@@ -1954,7 +1955,7 @@
         <v>Psyduck</v>
       </c>
       <c r="E78" t="str">
-        <v>23-28</v>
+        <v>27-32</v>
       </c>
       <c r="F78" t="str">
         <v>20.00%</v>
@@ -1962,7 +1963,7 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B79" t="str">
         <v>Brooklet Hill</v>
@@ -1974,7 +1975,7 @@
         <v>Surskit</v>
       </c>
       <c r="E79" t="str">
-        <v>23-28</v>
+        <v>27-32</v>
       </c>
       <c r="F79" t="str">
         <v>20.00%</v>
@@ -1982,7 +1983,7 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B80" t="str">
         <v>Brooklet Hill</v>
@@ -1994,7 +1995,7 @@
         <v>Dewpider</v>
       </c>
       <c r="E80" t="str">
-        <v>23-28</v>
+        <v>27-32</v>
       </c>
       <c r="F80" t="str">
         <v>20.00%</v>
@@ -2002,7 +2003,7 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B81" t="str">
         <v>Brooklet Hill</v>
@@ -2014,7 +2015,7 @@
         <v>Poliwag</v>
       </c>
       <c r="E81" t="str">
-        <v>23-28</v>
+        <v>27-32</v>
       </c>
       <c r="F81" t="str">
         <v>20.00%</v>
@@ -2022,7 +2023,7 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B82" t="str">
         <v>Brooklet Hill</v>
@@ -2034,7 +2035,7 @@
         <v>Wingull</v>
       </c>
       <c r="E82" t="str">
-        <v>23-28</v>
+        <v>28-33</v>
       </c>
       <c r="F82" t="str">
         <v>20.00%</v>
@@ -2042,7 +2043,7 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B83" t="str">
         <v>Brooklet Hill</v>
@@ -2054,7 +2055,7 @@
         <v>Lillipup</v>
       </c>
       <c r="E83" t="str">
-        <v>23-28</v>
+        <v>28-33</v>
       </c>
       <c r="F83" t="str">
         <v>20.00%</v>
@@ -2062,7 +2063,7 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B84" t="str">
         <v>Brooklet Hill</v>
@@ -2074,7 +2075,7 @@
         <v>Paras</v>
       </c>
       <c r="E84" t="str">
-        <v>23-28</v>
+        <v>28-33</v>
       </c>
       <c r="F84" t="str">
         <v>20.00%</v>
@@ -2082,7 +2083,7 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B85" t="str">
         <v>Brooklet Hill</v>
@@ -2094,7 +2095,7 @@
         <v>Goldeen</v>
       </c>
       <c r="E85" t="str">
-        <v>23-28</v>
+        <v>28-33</v>
       </c>
       <c r="F85" t="str">
         <v>20.00%</v>
@@ -2102,7 +2103,7 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B86" t="str">
         <v>Brooklet Hill</v>
@@ -2114,7 +2115,7 @@
         <v>Feebas</v>
       </c>
       <c r="E86" t="str">
-        <v>23-28</v>
+        <v>28-33</v>
       </c>
       <c r="F86" t="str">
         <v>20.00%</v>
@@ -2122,7 +2123,7 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B87" t="str">
         <v>Captain Lana</v>
@@ -2134,7 +2135,7 @@
         <v>Boss</v>
       </c>
       <c r="E87" t="str">
-        <v>25-30</v>
+        <v>29-34</v>
       </c>
       <c r="F87" t="str">
         <v>-</v>
@@ -2142,27 +2143,27 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B88" t="str">
-        <v>Route 6</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C88" t="str">
         <v>Main Area</v>
       </c>
       <c r="D88" t="str">
-        <v>Unknown</v>
+        <v>Cubone</v>
       </c>
       <c r="E88" t="str">
-        <v>26-31</v>
+        <v>30-35</v>
       </c>
       <c r="F88" t="str">
-        <v>100%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B89" t="str">
         <v>Wela Volcano Park</v>
@@ -2171,10 +2172,10 @@
         <v>Main Area</v>
       </c>
       <c r="D89" t="str">
-        <v>Cubone</v>
+        <v>Kangaskhan</v>
       </c>
       <c r="E89" t="str">
-        <v>27-32</v>
+        <v>30-35</v>
       </c>
       <c r="F89" t="str">
         <v>25.00%</v>
@@ -2182,7 +2183,7 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B90" t="str">
         <v>Wela Volcano Park</v>
@@ -2191,10 +2192,10 @@
         <v>Main Area</v>
       </c>
       <c r="D90" t="str">
-        <v>Kangaskhan</v>
+        <v>Magby</v>
       </c>
       <c r="E90" t="str">
-        <v>27-32</v>
+        <v>30-35</v>
       </c>
       <c r="F90" t="str">
         <v>25.00%</v>
@@ -2202,7 +2203,7 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B91" t="str">
         <v>Wela Volcano Park</v>
@@ -2211,10 +2212,10 @@
         <v>Main Area</v>
       </c>
       <c r="D91" t="str">
-        <v>Magby</v>
+        <v>Nihilego</v>
       </c>
       <c r="E91" t="str">
-        <v>27-32</v>
+        <v>30-35</v>
       </c>
       <c r="F91" t="str">
         <v>25.00%</v>
@@ -2222,59 +2223,59 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B92" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Captain Kiawe</v>
       </c>
       <c r="C92" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D92" t="str">
-        <v>Nihilego</v>
+        <v>Boss</v>
       </c>
       <c r="E92" t="str">
-        <v>27-32</v>
+        <v>31-36</v>
       </c>
       <c r="F92" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B93" t="str">
-        <v>Captain Kiawe</v>
+        <v>Route 7</v>
       </c>
       <c r="C93" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D93" t="str">
-        <v>Boss</v>
+        <v>Staryu</v>
       </c>
       <c r="E93" t="str">
-        <v>28-33</v>
+        <v>32-37</v>
       </c>
       <c r="F93" t="str">
-        <v>-</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B94" t="str">
         <v>Route 7</v>
       </c>
       <c r="C94" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D94" t="str">
-        <v>Staryu</v>
+        <v>Pyukumuku</v>
       </c>
       <c r="E94" t="str">
-        <v>30-35</v>
+        <v>32-37</v>
       </c>
       <c r="F94" t="str">
         <v>50.00%</v>
@@ -2282,79 +2283,79 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B95" t="str">
-        <v>Route 7</v>
+        <v>Route 8</v>
       </c>
       <c r="C95" t="str">
-        <v>Special Encounter</v>
+        <v>Main</v>
       </c>
       <c r="D95" t="str">
-        <v>Pyukumuku</v>
+        <v>Arbok</v>
       </c>
       <c r="E95" t="str">
-        <v>30-35</v>
+        <v>33-38</v>
       </c>
       <c r="F95" t="str">
-        <v>50.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B96" t="str">
         <v>Route 8</v>
       </c>
       <c r="C96" t="str">
-        <v>Fossil Restoration Center</v>
+        <v>Main</v>
       </c>
       <c r="D96" t="str">
-        <v>Omanyte</v>
+        <v>Wimpod</v>
       </c>
       <c r="E96" t="str">
-        <v>31-36</v>
+        <v>33-38</v>
       </c>
       <c r="F96" t="str">
-        <v>11.11%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="97">
       <c r="A97">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B97" t="str">
         <v>Route 8</v>
       </c>
       <c r="C97" t="str">
-        <v>Fossil Restoration Center</v>
+        <v>Main</v>
       </c>
       <c r="D97" t="str">
-        <v>Kabuto</v>
+        <v>Fletchinder</v>
       </c>
       <c r="E97" t="str">
-        <v>31-36</v>
+        <v>33-38</v>
       </c>
       <c r="F97" t="str">
-        <v>11.11%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B98" t="str">
         <v>Route 8</v>
       </c>
       <c r="C98" t="str">
-        <v>Fossil Restoration Center</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D98" t="str">
-        <v>Lileep</v>
+        <v>Omanyte</v>
       </c>
       <c r="E98" t="str">
-        <v>31-36</v>
+        <v>34-39</v>
       </c>
       <c r="F98" t="str">
         <v>11.11%</v>
@@ -2362,19 +2363,19 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B99" t="str">
         <v>Route 8</v>
       </c>
       <c r="C99" t="str">
-        <v>Fossil Restoration Center</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D99" t="str">
-        <v>Anorith</v>
+        <v>Kabuto</v>
       </c>
       <c r="E99" t="str">
-        <v>31-36</v>
+        <v>34-39</v>
       </c>
       <c r="F99" t="str">
         <v>11.11%</v>
@@ -2382,19 +2383,19 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B100" t="str">
         <v>Route 8</v>
       </c>
       <c r="C100" t="str">
-        <v>Fossil Restoration Center</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D100" t="str">
-        <v>Cranidos</v>
+        <v>Lileep</v>
       </c>
       <c r="E100" t="str">
-        <v>31-36</v>
+        <v>34-39</v>
       </c>
       <c r="F100" t="str">
         <v>11.11%</v>
@@ -2402,19 +2403,19 @@
     </row>
     <row r="101">
       <c r="A101">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B101" t="str">
         <v>Route 8</v>
       </c>
       <c r="C101" t="str">
-        <v>Fossil Restoration Center</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D101" t="str">
-        <v>Shieldon</v>
+        <v>Anorith</v>
       </c>
       <c r="E101" t="str">
-        <v>31-36</v>
+        <v>34-39</v>
       </c>
       <c r="F101" t="str">
         <v>11.11%</v>
@@ -2422,19 +2423,19 @@
     </row>
     <row r="102">
       <c r="A102">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B102" t="str">
         <v>Route 8</v>
       </c>
       <c r="C102" t="str">
-        <v>Fossil Restoration Center</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D102" t="str">
-        <v>Archen</v>
+        <v>Cranidos</v>
       </c>
       <c r="E102" t="str">
-        <v>31-36</v>
+        <v>34-39</v>
       </c>
       <c r="F102" t="str">
         <v>11.11%</v>
@@ -2442,19 +2443,19 @@
     </row>
     <row r="103">
       <c r="A103">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B103" t="str">
         <v>Route 8</v>
       </c>
       <c r="C103" t="str">
-        <v>Fossil Restoration Center</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D103" t="str">
-        <v>Tirtouga</v>
+        <v>Shieldon</v>
       </c>
       <c r="E103" t="str">
-        <v>31-36</v>
+        <v>34-39</v>
       </c>
       <c r="F103" t="str">
         <v>11.11%</v>
@@ -2462,19 +2463,19 @@
     </row>
     <row r="104">
       <c r="A104">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B104" t="str">
         <v>Route 8</v>
       </c>
       <c r="C104" t="str">
-        <v>Fossil Restoration Center</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D104" t="str">
-        <v>Tyrunt</v>
+        <v>Archen</v>
       </c>
       <c r="E104" t="str">
-        <v>31-36</v>
+        <v>34-39</v>
       </c>
       <c r="F104" t="str">
         <v>11.11%</v>
@@ -2482,127 +2483,127 @@
     </row>
     <row r="105">
       <c r="A105">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B105" t="str">
         <v>Route 8</v>
       </c>
       <c r="C105" t="str">
-        <v>Main</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D105" t="str">
-        <v>Arbok</v>
+        <v>Tirtouga</v>
       </c>
       <c r="E105" t="str">
-        <v>31-36</v>
+        <v>34-39</v>
       </c>
       <c r="F105" t="str">
-        <v>33.33%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="106">
       <c r="A106">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B106" t="str">
         <v>Route 8</v>
       </c>
       <c r="C106" t="str">
-        <v>Main</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D106" t="str">
-        <v>Wimpod</v>
+        <v>Tyrunt</v>
       </c>
       <c r="E106" t="str">
-        <v>31-36</v>
+        <v>34-39</v>
       </c>
       <c r="F106" t="str">
-        <v>33.33%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="107">
       <c r="A107">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B107" t="str">
         <v>Route 8</v>
       </c>
       <c r="C107" t="str">
-        <v>Main</v>
+        <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D107" t="str">
-        <v>Fletchinder</v>
+        <v>Amaura</v>
       </c>
       <c r="E107" t="str">
-        <v>31-36</v>
+        <v>34-39</v>
       </c>
       <c r="F107" t="str">
-        <v>33.33%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="108">
       <c r="A108">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B108" t="str">
         <v>Lush Jungle</v>
       </c>
       <c r="C108" t="str">
-        <v>East Cave</v>
+        <v>North</v>
       </c>
       <c r="D108" t="str">
-        <v>Golbat</v>
+        <v>Trumbeak</v>
       </c>
       <c r="E108" t="str">
-        <v>32-37</v>
+        <v>35-40</v>
       </c>
       <c r="F108" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="109">
       <c r="A109">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B109" t="str">
         <v>Lush Jungle</v>
       </c>
       <c r="C109" t="str">
-        <v>East Cave</v>
+        <v>North</v>
       </c>
       <c r="D109" t="str">
-        <v>Salandit</v>
+        <v>Steenee</v>
       </c>
       <c r="E109" t="str">
-        <v>32-37</v>
+        <v>35-40</v>
       </c>
       <c r="F109" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="110">
       <c r="A110">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B110" t="str">
         <v>Lush Jungle</v>
       </c>
       <c r="C110" t="str">
-        <v>East Cave</v>
+        <v>North</v>
       </c>
       <c r="D110" t="str">
-        <v>Larvesta</v>
+        <v>Comfey</v>
       </c>
       <c r="E110" t="str">
-        <v>32-37</v>
+        <v>35-40</v>
       </c>
       <c r="F110" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="111">
       <c r="A111">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B111" t="str">
         <v>Lush Jungle</v>
@@ -2611,10 +2612,10 @@
         <v>North</v>
       </c>
       <c r="D111" t="str">
-        <v>Trumbeak</v>
+        <v>Hoothoot</v>
       </c>
       <c r="E111" t="str">
-        <v>32-37</v>
+        <v>35-40</v>
       </c>
       <c r="F111" t="str">
         <v>16.67%</v>
@@ -2622,7 +2623,7 @@
     </row>
     <row r="112">
       <c r="A112">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B112" t="str">
         <v>Lush Jungle</v>
@@ -2631,10 +2632,10 @@
         <v>North</v>
       </c>
       <c r="D112" t="str">
-        <v>Steenee</v>
+        <v>Oranguru</v>
       </c>
       <c r="E112" t="str">
-        <v>32-37</v>
+        <v>35-40</v>
       </c>
       <c r="F112" t="str">
         <v>16.67%</v>
@@ -2642,7 +2643,7 @@
     </row>
     <row r="113">
       <c r="A113">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B113" t="str">
         <v>Lush Jungle</v>
@@ -2651,10 +2652,10 @@
         <v>North</v>
       </c>
       <c r="D113" t="str">
-        <v>Comfey</v>
+        <v>Bounsweet</v>
       </c>
       <c r="E113" t="str">
-        <v>32-37</v>
+        <v>35-40</v>
       </c>
       <c r="F113" t="str">
         <v>16.67%</v>
@@ -2662,147 +2663,147 @@
     </row>
     <row r="114">
       <c r="A114">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B114" t="str">
         <v>Lush Jungle</v>
       </c>
       <c r="C114" t="str">
-        <v>North</v>
+        <v>East Cave</v>
       </c>
       <c r="D114" t="str">
-        <v>Hoothoot</v>
+        <v>Golbat</v>
       </c>
       <c r="E114" t="str">
-        <v>32-37</v>
+        <v>36-41</v>
       </c>
       <c r="F114" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="115">
       <c r="A115">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B115" t="str">
         <v>Lush Jungle</v>
       </c>
       <c r="C115" t="str">
-        <v>North</v>
+        <v>East Cave</v>
       </c>
       <c r="D115" t="str">
-        <v>Oranguru</v>
+        <v>Salandit</v>
       </c>
       <c r="E115" t="str">
-        <v>32-37</v>
+        <v>36-41</v>
       </c>
       <c r="F115" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="116">
       <c r="A116">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B116" t="str">
         <v>Lush Jungle</v>
       </c>
       <c r="C116" t="str">
-        <v>North</v>
+        <v>East Cave</v>
       </c>
       <c r="D116" t="str">
-        <v>Passimian</v>
+        <v>Larvesta</v>
       </c>
       <c r="E116" t="str">
-        <v>32-37</v>
+        <v>36-41</v>
       </c>
       <c r="F116" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="117">
       <c r="A117">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B117" t="str">
         <v>Lush Jungle</v>
       </c>
       <c r="C117" t="str">
-        <v>Special Encounter</v>
+        <v>East Cave</v>
       </c>
       <c r="D117" t="str">
-        <v>Bounsweet</v>
+        <v>Oranguru</v>
       </c>
       <c r="E117" t="str">
-        <v>32-37</v>
+        <v>36-41</v>
       </c>
       <c r="F117" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="118">
       <c r="A118">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B118" t="str">
         <v>Lush Jungle</v>
       </c>
       <c r="C118" t="str">
-        <v>Special Encounter</v>
+        <v>East Cave</v>
       </c>
       <c r="D118" t="str">
-        <v>Oranguru</v>
+        <v>Passimian</v>
       </c>
       <c r="E118" t="str">
-        <v>32-37</v>
+        <v>36-41</v>
       </c>
       <c r="F118" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="119">
       <c r="A119">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B119" t="str">
-        <v>Lush Jungle</v>
+        <v>Captain Mallow</v>
       </c>
       <c r="C119" t="str">
-        <v>Special Encounter</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D119" t="str">
-        <v>Passimian</v>
+        <v>Boss</v>
       </c>
       <c r="E119" t="str">
-        <v>32-37</v>
+        <v>38-43</v>
       </c>
       <c r="F119" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="120">
       <c r="A120">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B120" t="str">
-        <v>Captain Mallow</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C120" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D120" t="str">
-        <v>Boss</v>
+        <v>Zubat</v>
       </c>
       <c r="E120" t="str">
-        <v>33-38</v>
+        <v>39-44</v>
       </c>
       <c r="F120" t="str">
-        <v>-</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="121">
       <c r="A121">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B121" t="str">
         <v>Diglett's Tunnel</v>
@@ -2811,10 +2812,10 @@
         <v>Main Area</v>
       </c>
       <c r="D121" t="str">
-        <v>Zubat</v>
+        <v>Alolan Diglett</v>
       </c>
       <c r="E121" t="str">
-        <v>35-40</v>
+        <v>39-44</v>
       </c>
       <c r="F121" t="str">
         <v>25.00%</v>
@@ -2822,7 +2823,7 @@
     </row>
     <row r="122">
       <c r="A122">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B122" t="str">
         <v>Diglett's Tunnel</v>
@@ -2831,10 +2832,10 @@
         <v>Main Area</v>
       </c>
       <c r="D122" t="str">
-        <v>Alolan Diglett</v>
+        <v>Kecleon</v>
       </c>
       <c r="E122" t="str">
-        <v>35-40</v>
+        <v>39-44</v>
       </c>
       <c r="F122" t="str">
         <v>25.00%</v>
@@ -2842,7 +2843,7 @@
     </row>
     <row r="123">
       <c r="A123">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B123" t="str">
         <v>Diglett's Tunnel</v>
@@ -2851,10 +2852,10 @@
         <v>Main Area</v>
       </c>
       <c r="D123" t="str">
-        <v>Kecleon</v>
+        <v>Larvitar</v>
       </c>
       <c r="E123" t="str">
-        <v>35-40</v>
+        <v>39-44</v>
       </c>
       <c r="F123" t="str">
         <v>25.00%</v>
@@ -2862,39 +2863,39 @@
     </row>
     <row r="124">
       <c r="A124">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B124" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Route 9</v>
       </c>
       <c r="C124" t="str">
         <v>Main Area</v>
       </c>
       <c r="D124" t="str">
-        <v>Larvitar</v>
+        <v>Corsola</v>
       </c>
       <c r="E124" t="str">
-        <v>35-40</v>
+        <v>40-45</v>
       </c>
       <c r="F124" t="str">
-        <v>25.00%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="125">
       <c r="A125">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B125" t="str">
         <v>Route 9</v>
       </c>
       <c r="C125" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D125" t="str">
-        <v>Corsola</v>
+        <v>Mareanie</v>
       </c>
       <c r="E125" t="str">
-        <v>36-41</v>
+        <v>40-45</v>
       </c>
       <c r="F125" t="str">
         <v>50.00%</v>
@@ -2902,19 +2903,19 @@
     </row>
     <row r="126">
       <c r="A126">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B126" t="str">
-        <v>Route 9</v>
+        <v>Konikoni City</v>
       </c>
       <c r="C126" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D126" t="str">
-        <v>Mareanie</v>
+        <v>Poliwhirl</v>
       </c>
       <c r="E126" t="str">
-        <v>36-41</v>
+        <v>41-46</v>
       </c>
       <c r="F126" t="str">
         <v>50.00%</v>
@@ -2922,7 +2923,7 @@
     </row>
     <row r="127">
       <c r="A127">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B127" t="str">
         <v>Konikoni City</v>
@@ -2931,10 +2932,10 @@
         <v>Main Area</v>
       </c>
       <c r="D127" t="str">
-        <v>Poliwhirl</v>
+        <v>Ditto</v>
       </c>
       <c r="E127" t="str">
-        <v>37-42</v>
+        <v>41-46</v>
       </c>
       <c r="F127" t="str">
         <v>50.00%</v>
@@ -2942,47 +2943,47 @@
     </row>
     <row r="128">
       <c r="A128">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B128" t="str">
-        <v>Konikoni City</v>
+        <v>Memorial Hill</v>
       </c>
       <c r="C128" t="str">
-        <v>Main Area</v>
+        <v>Main</v>
       </c>
       <c r="D128" t="str">
-        <v>Ditto</v>
+        <v>Phantump</v>
       </c>
       <c r="E128" t="str">
-        <v>37-42</v>
+        <v>42-47</v>
       </c>
       <c r="F128" t="str">
-        <v>50.00%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="129">
       <c r="A129">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B129" t="str">
-        <v>Memorial Hill</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C129" t="str">
-        <v>Main</v>
+        <v>Main Area</v>
       </c>
       <c r="D129" t="str">
-        <v>Phantump</v>
+        <v>Gumshoos</v>
       </c>
       <c r="E129" t="str">
-        <v>39-44</v>
+        <v>43-48</v>
       </c>
       <c r="F129" t="str">
-        <v>100.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="130">
       <c r="A130">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B130" t="str">
         <v>Akala Outskirts</v>
@@ -2991,10 +2992,10 @@
         <v>Main Area</v>
       </c>
       <c r="D130" t="str">
-        <v>Gumshoos</v>
+        <v>Wingull</v>
       </c>
       <c r="E130" t="str">
-        <v>40-45</v>
+        <v>43-48</v>
       </c>
       <c r="F130" t="str">
         <v>12.50%</v>
@@ -3002,7 +3003,7 @@
     </row>
     <row r="131">
       <c r="A131">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B131" t="str">
         <v>Akala Outskirts</v>
@@ -3011,10 +3012,10 @@
         <v>Main Area</v>
       </c>
       <c r="D131" t="str">
-        <v>Wingull</v>
+        <v>Magikarp</v>
       </c>
       <c r="E131" t="str">
-        <v>40-45</v>
+        <v>43-48</v>
       </c>
       <c r="F131" t="str">
         <v>12.50%</v>
@@ -3022,7 +3023,7 @@
     </row>
     <row r="132">
       <c r="A132">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B132" t="str">
         <v>Akala Outskirts</v>
@@ -3031,10 +3032,10 @@
         <v>Main Area</v>
       </c>
       <c r="D132" t="str">
-        <v>Magikarp</v>
+        <v>Stufful</v>
       </c>
       <c r="E132" t="str">
-        <v>40-45</v>
+        <v>43-48</v>
       </c>
       <c r="F132" t="str">
         <v>12.50%</v>
@@ -3042,7 +3043,7 @@
     </row>
     <row r="133">
       <c r="A133">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B133" t="str">
         <v>Akala Outskirts</v>
@@ -3051,10 +3052,10 @@
         <v>Main Area</v>
       </c>
       <c r="D133" t="str">
-        <v>Stufful</v>
+        <v>Chinchou</v>
       </c>
       <c r="E133" t="str">
-        <v>40-45</v>
+        <v>43-48</v>
       </c>
       <c r="F133" t="str">
         <v>12.50%</v>
@@ -3062,7 +3063,7 @@
     </row>
     <row r="134">
       <c r="A134">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B134" t="str">
         <v>Akala Outskirts</v>
@@ -3071,10 +3072,10 @@
         <v>Main Area</v>
       </c>
       <c r="D134" t="str">
-        <v>Chinchou</v>
+        <v>Alolan Raticate</v>
       </c>
       <c r="E134" t="str">
-        <v>40-45</v>
+        <v>43-48</v>
       </c>
       <c r="F134" t="str">
         <v>12.50%</v>
@@ -3082,7 +3083,7 @@
     </row>
     <row r="135">
       <c r="A135">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B135" t="str">
         <v>Akala Outskirts</v>
@@ -3091,10 +3092,10 @@
         <v>Main Area</v>
       </c>
       <c r="D135" t="str">
-        <v>Alolan Raticate</v>
+        <v>Natu</v>
       </c>
       <c r="E135" t="str">
-        <v>40-45</v>
+        <v>43-48</v>
       </c>
       <c r="F135" t="str">
         <v>12.50%</v>
@@ -3102,7 +3103,7 @@
     </row>
     <row r="136">
       <c r="A136">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B136" t="str">
         <v>Akala Outskirts</v>
@@ -3111,10 +3112,10 @@
         <v>Main Area</v>
       </c>
       <c r="D136" t="str">
-        <v>Natu</v>
+        <v>Nosepass</v>
       </c>
       <c r="E136" t="str">
-        <v>40-45</v>
+        <v>43-48</v>
       </c>
       <c r="F136" t="str">
         <v>12.50%</v>
@@ -3122,67 +3123,67 @@
     </row>
     <row r="137">
       <c r="A137">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B137" t="str">
-        <v>Akala Outskirts</v>
+        <v>Ruins of Life</v>
       </c>
       <c r="C137" t="str">
-        <v>Main Area</v>
+        <v>Special Encounter</v>
       </c>
       <c r="D137" t="str">
-        <v>Nosepass</v>
+        <v>Tapu Lele</v>
       </c>
       <c r="E137" t="str">
-        <v>40-45</v>
+        <v>44-49</v>
       </c>
       <c r="F137" t="str">
-        <v>12.50%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="138">
       <c r="A138">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B138" t="str">
-        <v>Ruins of Life</v>
+        <v>Kahuna Olivia</v>
       </c>
       <c r="C138" t="str">
-        <v>Special Encounter</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D138" t="str">
-        <v>Tapu Lele</v>
+        <v>Boss</v>
       </c>
       <c r="E138" t="str">
-        <v>41-46</v>
+        <v>45-50</v>
       </c>
       <c r="F138" t="str">
-        <v>100.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="139">
       <c r="A139">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B139" t="str">
-        <v>Kahuna Olivia</v>
+        <v>Hano Beach</v>
       </c>
       <c r="C139" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D139" t="str">
-        <v>Boss</v>
+        <v>Staryu</v>
       </c>
       <c r="E139" t="str">
-        <v>42-47</v>
+        <v>46-51</v>
       </c>
       <c r="F139" t="str">
-        <v>-</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="140">
       <c r="A140">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B140" t="str">
         <v>Hano Beach</v>
@@ -3191,10 +3192,10 @@
         <v>Main Area</v>
       </c>
       <c r="D140" t="str">
-        <v>Staryu</v>
+        <v>Sandygast</v>
       </c>
       <c r="E140" t="str">
-        <v>44-49</v>
+        <v>46-51</v>
       </c>
       <c r="F140" t="str">
         <v>50.00%</v>
@@ -3202,27 +3203,27 @@
     </row>
     <row r="141">
       <c r="A141">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B141" t="str">
-        <v>Hano Beach</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C141" t="str">
-        <v>Main Area</v>
+        <v>Special Encounter</v>
       </c>
       <c r="D141" t="str">
-        <v>Sandygast</v>
+        <v>Type: Null</v>
       </c>
       <c r="E141" t="str">
-        <v>44-49</v>
+        <v>47-52</v>
       </c>
       <c r="F141" t="str">
-        <v>50.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="142">
       <c r="A142">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B142" t="str">
         <v>Aether Paradise</v>
@@ -3231,10 +3232,10 @@
         <v>Special Encounter</v>
       </c>
       <c r="D142" t="str">
-        <v>Type: Null</v>
+        <v>Ditto</v>
       </c>
       <c r="E142" t="str">
-        <v>45-50</v>
+        <v>47-52</v>
       </c>
       <c r="F142" t="str">
         <v>33.33%</v>
@@ -3242,7 +3243,7 @@
     </row>
     <row r="143">
       <c r="A143">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B143" t="str">
         <v>Aether Paradise</v>
@@ -3251,10 +3252,10 @@
         <v>Special Encounter</v>
       </c>
       <c r="D143" t="str">
-        <v>Ditto</v>
+        <v>Porygon</v>
       </c>
       <c r="E143" t="str">
-        <v>45-50</v>
+        <v>47-52</v>
       </c>
       <c r="F143" t="str">
         <v>33.33%</v>
@@ -3262,27 +3263,27 @@
     </row>
     <row r="144">
       <c r="A144">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B144" t="str">
-        <v>Aether Paradise</v>
+        <v>Malie City</v>
       </c>
       <c r="C144" t="str">
-        <v>Special Encounter</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D144" t="str">
-        <v>Porygon</v>
+        <v>Magnemite</v>
       </c>
       <c r="E144" t="str">
-        <v>45-50</v>
+        <v>48-53</v>
       </c>
       <c r="F144" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="145">
       <c r="A145">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B145" t="str">
         <v>Malie City</v>
@@ -3291,10 +3292,10 @@
         <v>Outer Cape</v>
       </c>
       <c r="D145" t="str">
-        <v>Magnemite</v>
+        <v>Alolan Grimer</v>
       </c>
       <c r="E145" t="str">
-        <v>46-51</v>
+        <v>48-53</v>
       </c>
       <c r="F145" t="str">
         <v>25.00%</v>
@@ -3302,7 +3303,7 @@
     </row>
     <row r="146">
       <c r="A146">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B146" t="str">
         <v>Malie City</v>
@@ -3311,10 +3312,10 @@
         <v>Outer Cape</v>
       </c>
       <c r="D146" t="str">
-        <v>Alolan Grimer</v>
+        <v>Trubbish</v>
       </c>
       <c r="E146" t="str">
-        <v>46-51</v>
+        <v>48-53</v>
       </c>
       <c r="F146" t="str">
         <v>25.00%</v>
@@ -3322,7 +3323,7 @@
     </row>
     <row r="147">
       <c r="A147">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B147" t="str">
         <v>Malie City</v>
@@ -3331,10 +3332,10 @@
         <v>Outer Cape</v>
       </c>
       <c r="D147" t="str">
-        <v>Trubbish</v>
+        <v>Minccino</v>
       </c>
       <c r="E147" t="str">
-        <v>46-51</v>
+        <v>48-53</v>
       </c>
       <c r="F147" t="str">
         <v>25.00%</v>
@@ -3342,27 +3343,27 @@
     </row>
     <row r="148">
       <c r="A148">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B148" t="str">
-        <v>Malie City</v>
+        <v>Malie Garden</v>
       </c>
       <c r="C148" t="str">
-        <v>Outer Cape</v>
+        <v>Main Area</v>
       </c>
       <c r="D148" t="str">
-        <v>Minccino</v>
+        <v>Masquerain</v>
       </c>
       <c r="E148" t="str">
-        <v>46-51</v>
+        <v>50-55</v>
       </c>
       <c r="F148" t="str">
-        <v>25.00%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="149">
       <c r="A149">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B149" t="str">
         <v>Malie Garden</v>
@@ -3371,10 +3372,10 @@
         <v>Main Area</v>
       </c>
       <c r="D149" t="str">
-        <v>Masquerain</v>
+        <v>Kartana</v>
       </c>
       <c r="E149" t="str">
-        <v>47-52</v>
+        <v>50-55</v>
       </c>
       <c r="F149" t="str">
         <v>50.00%</v>
@@ -3382,27 +3383,27 @@
     </row>
     <row r="150">
       <c r="A150">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B150" t="str">
-        <v>Malie Garden</v>
+        <v>Route 10</v>
       </c>
       <c r="C150" t="str">
         <v>Main Area</v>
       </c>
       <c r="D150" t="str">
-        <v>Kartana</v>
+        <v>Ledian</v>
       </c>
       <c r="E150" t="str">
-        <v>47-52</v>
+        <v>51-56</v>
       </c>
       <c r="F150" t="str">
-        <v>50.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="151">
       <c r="A151">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B151" t="str">
         <v>Route 10</v>
@@ -3411,10 +3412,10 @@
         <v>Main Area</v>
       </c>
       <c r="D151" t="str">
-        <v>Ledian</v>
+        <v>Ariados</v>
       </c>
       <c r="E151" t="str">
-        <v>49-54</v>
+        <v>51-56</v>
       </c>
       <c r="F151" t="str">
         <v>16.67%</v>
@@ -3422,7 +3423,7 @@
     </row>
     <row r="152">
       <c r="A152">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B152" t="str">
         <v>Route 10</v>
@@ -3431,10 +3432,10 @@
         <v>Main Area</v>
       </c>
       <c r="D152" t="str">
-        <v>Ariados</v>
+        <v>Crabrawler</v>
       </c>
       <c r="E152" t="str">
-        <v>49-54</v>
+        <v>51-56</v>
       </c>
       <c r="F152" t="str">
         <v>16.67%</v>
@@ -3442,7 +3443,7 @@
     </row>
     <row r="153">
       <c r="A153">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B153" t="str">
         <v>Route 10</v>
@@ -3451,10 +3452,10 @@
         <v>Main Area</v>
       </c>
       <c r="D153" t="str">
-        <v>Crabrawler</v>
+        <v>Fearow</v>
       </c>
       <c r="E153" t="str">
-        <v>49-54</v>
+        <v>51-56</v>
       </c>
       <c r="F153" t="str">
         <v>16.67%</v>
@@ -3462,7 +3463,7 @@
     </row>
     <row r="154">
       <c r="A154">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B154" t="str">
         <v>Route 10</v>
@@ -3471,10 +3472,10 @@
         <v>Main Area</v>
       </c>
       <c r="D154" t="str">
-        <v>Fearow</v>
+        <v>Skarmory</v>
       </c>
       <c r="E154" t="str">
-        <v>49-54</v>
+        <v>51-56</v>
       </c>
       <c r="F154" t="str">
         <v>16.67%</v>
@@ -3482,7 +3483,7 @@
     </row>
     <row r="155">
       <c r="A155">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B155" t="str">
         <v>Route 10</v>
@@ -3491,10 +3492,10 @@
         <v>Main Area</v>
       </c>
       <c r="D155" t="str">
-        <v>Skarmory</v>
+        <v>Pancham</v>
       </c>
       <c r="E155" t="str">
-        <v>49-54</v>
+        <v>51-56</v>
       </c>
       <c r="F155" t="str">
         <v>16.67%</v>
@@ -3502,27 +3503,27 @@
     </row>
     <row r="156">
       <c r="A156">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B156" t="str">
-        <v>Route 10</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C156" t="str">
-        <v>Main Area</v>
+        <v>East</v>
       </c>
       <c r="D156" t="str">
-        <v>Pancham</v>
+        <v>Cleffa</v>
       </c>
       <c r="E156" t="str">
-        <v>49-54</v>
+        <v>52-57</v>
       </c>
       <c r="F156" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="157">
       <c r="A157">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B157" t="str">
         <v>Mount Hokulani</v>
@@ -3531,10 +3532,10 @@
         <v>East</v>
       </c>
       <c r="D157" t="str">
-        <v>Cleffa</v>
+        <v>Elgyem</v>
       </c>
       <c r="E157" t="str">
-        <v>50-55</v>
+        <v>52-57</v>
       </c>
       <c r="F157" t="str">
         <v>33.33%</v>
@@ -3542,7 +3543,7 @@
     </row>
     <row r="158">
       <c r="A158">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B158" t="str">
         <v>Mount Hokulani</v>
@@ -3551,10 +3552,10 @@
         <v>East</v>
       </c>
       <c r="D158" t="str">
-        <v>Elgyem</v>
+        <v>Beldum</v>
       </c>
       <c r="E158" t="str">
-        <v>50-55</v>
+        <v>52-57</v>
       </c>
       <c r="F158" t="str">
         <v>33.33%</v>
@@ -3562,47 +3563,47 @@
     </row>
     <row r="159">
       <c r="A159">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B159" t="str">
-        <v>Mount Hokulani</v>
+        <v>Captain Sophocles</v>
       </c>
       <c r="C159" t="str">
-        <v>East</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D159" t="str">
-        <v>Beldum</v>
+        <v>Boss</v>
       </c>
       <c r="E159" t="str">
-        <v>50-55</v>
+        <v>54-59</v>
       </c>
       <c r="F159" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="160">
       <c r="A160">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B160" t="str">
-        <v>Captain Sophocles</v>
+        <v>Route 11</v>
       </c>
       <c r="C160" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D160" t="str">
-        <v>Boss</v>
+        <v>Shiinotic</v>
       </c>
       <c r="E160" t="str">
-        <v>51-56</v>
+        <v>55-60</v>
       </c>
       <c r="F160" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="161">
       <c r="A161">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B161" t="str">
         <v>Route 11</v>
@@ -3611,10 +3612,10 @@
         <v>Main Area</v>
       </c>
       <c r="D161" t="str">
-        <v>Shiinotic</v>
+        <v>Parasect</v>
       </c>
       <c r="E161" t="str">
-        <v>53-58</v>
+        <v>55-60</v>
       </c>
       <c r="F161" t="str">
         <v>33.33%</v>
@@ -3622,7 +3623,7 @@
     </row>
     <row r="162">
       <c r="A162">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B162" t="str">
         <v>Route 11</v>
@@ -3631,10 +3632,10 @@
         <v>Main Area</v>
       </c>
       <c r="D162" t="str">
-        <v>Parasect</v>
+        <v>Komala</v>
       </c>
       <c r="E162" t="str">
-        <v>53-58</v>
+        <v>55-60</v>
       </c>
       <c r="F162" t="str">
         <v>33.33%</v>
@@ -3642,27 +3643,27 @@
     </row>
     <row r="163">
       <c r="A163">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B163" t="str">
-        <v>Route 11</v>
+        <v>Route 12</v>
       </c>
       <c r="C163" t="str">
         <v>Main Area</v>
       </c>
       <c r="D163" t="str">
-        <v>Komala</v>
+        <v>Houndoom</v>
       </c>
       <c r="E163" t="str">
-        <v>53-58</v>
+        <v>56-61</v>
       </c>
       <c r="F163" t="str">
-        <v>33.33%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="164">
       <c r="A164">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B164" t="str">
         <v>Route 12</v>
@@ -3671,10 +3672,10 @@
         <v>Main Area</v>
       </c>
       <c r="D164" t="str">
-        <v>Houndoom</v>
+        <v>Manectric</v>
       </c>
       <c r="E164" t="str">
-        <v>54-59</v>
+        <v>56-61</v>
       </c>
       <c r="F164" t="str">
         <v>50.00%</v>
@@ -3682,27 +3683,27 @@
     </row>
     <row r="165">
       <c r="A165">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B165" t="str">
-        <v>Route 12</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C165" t="str">
         <v>Main Area</v>
       </c>
       <c r="D165" t="str">
-        <v>Manectric</v>
+        <v>Mudbray</v>
       </c>
       <c r="E165" t="str">
-        <v>54-59</v>
+        <v>57-62</v>
       </c>
       <c r="F165" t="str">
-        <v>50.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="166">
       <c r="A166">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B166" t="str">
         <v>Blush Mountain</v>
@@ -3711,10 +3712,10 @@
         <v>Main Area</v>
       </c>
       <c r="D166" t="str">
-        <v>Mudbray</v>
+        <v>Torkoal</v>
       </c>
       <c r="E166" t="str">
-        <v>55-60</v>
+        <v>57-62</v>
       </c>
       <c r="F166" t="str">
         <v>11.11%</v>
@@ -3722,7 +3723,7 @@
     </row>
     <row r="167">
       <c r="A167">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B167" t="str">
         <v>Blush Mountain</v>
@@ -3731,10 +3732,10 @@
         <v>Main Area</v>
       </c>
       <c r="D167" t="str">
-        <v>Torkoal</v>
+        <v>Togedemaru</v>
       </c>
       <c r="E167" t="str">
-        <v>55-60</v>
+        <v>57-62</v>
       </c>
       <c r="F167" t="str">
         <v>11.11%</v>
@@ -3742,7 +3743,7 @@
     </row>
     <row r="168">
       <c r="A168">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B168" t="str">
         <v>Blush Mountain</v>
@@ -3751,10 +3752,10 @@
         <v>Main Area</v>
       </c>
       <c r="D168" t="str">
-        <v>Togedemaru</v>
+        <v>Elekid</v>
       </c>
       <c r="E168" t="str">
-        <v>55-60</v>
+        <v>57-62</v>
       </c>
       <c r="F168" t="str">
         <v>11.11%</v>
@@ -3762,7 +3763,7 @@
     </row>
     <row r="169">
       <c r="A169">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B169" t="str">
         <v>Blush Mountain</v>
@@ -3771,10 +3772,10 @@
         <v>Main Area</v>
       </c>
       <c r="D169" t="str">
-        <v>Elekid</v>
+        <v>Alolan Geodude</v>
       </c>
       <c r="E169" t="str">
-        <v>55-60</v>
+        <v>57-62</v>
       </c>
       <c r="F169" t="str">
         <v>11.11%</v>
@@ -3782,7 +3783,7 @@
     </row>
     <row r="170">
       <c r="A170">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B170" t="str">
         <v>Blush Mountain</v>
@@ -3791,10 +3792,10 @@
         <v>Main Area</v>
       </c>
       <c r="D170" t="str">
-        <v>Alolan Geodude</v>
+        <v>Alolan Graveler</v>
       </c>
       <c r="E170" t="str">
-        <v>55-60</v>
+        <v>57-62</v>
       </c>
       <c r="F170" t="str">
         <v>11.11%</v>
@@ -3802,7 +3803,7 @@
     </row>
     <row r="171">
       <c r="A171">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B171" t="str">
         <v>Blush Mountain</v>
@@ -3811,10 +3812,10 @@
         <v>Main Area</v>
       </c>
       <c r="D171" t="str">
-        <v>Alolan Graveler</v>
+        <v>Charjabug</v>
       </c>
       <c r="E171" t="str">
-        <v>55-60</v>
+        <v>57-62</v>
       </c>
       <c r="F171" t="str">
         <v>11.11%</v>
@@ -3822,7 +3823,7 @@
     </row>
     <row r="172">
       <c r="A172">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B172" t="str">
         <v>Blush Mountain</v>
@@ -3831,10 +3832,10 @@
         <v>Main Area</v>
       </c>
       <c r="D172" t="str">
-        <v>Charjabug</v>
+        <v>Turtonator</v>
       </c>
       <c r="E172" t="str">
-        <v>55-60</v>
+        <v>57-62</v>
       </c>
       <c r="F172" t="str">
         <v>11.11%</v>
@@ -3842,7 +3843,7 @@
     </row>
     <row r="173">
       <c r="A173">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B173" t="str">
         <v>Blush Mountain</v>
@@ -3851,10 +3852,10 @@
         <v>Main Area</v>
       </c>
       <c r="D173" t="str">
-        <v>Turtonator</v>
+        <v>Dedenne</v>
       </c>
       <c r="E173" t="str">
-        <v>55-60</v>
+        <v>57-62</v>
       </c>
       <c r="F173" t="str">
         <v>11.11%</v>
@@ -3862,47 +3863,47 @@
     </row>
     <row r="174">
       <c r="A174">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B174" t="str">
-        <v>Blush Mountain</v>
+        <v>Route 13</v>
       </c>
       <c r="C174" t="str">
         <v>Main Area</v>
       </c>
       <c r="D174" t="str">
-        <v>Dedenne</v>
+        <v>Minior</v>
       </c>
       <c r="E174" t="str">
-        <v>55-60</v>
+        <v>58-63</v>
       </c>
       <c r="F174" t="str">
-        <v>11.11%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="175">
       <c r="A175">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B175" t="str">
-        <v>Route 13</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C175" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D175" t="str">
-        <v>Minior</v>
+        <v>Celesteela</v>
       </c>
       <c r="E175" t="str">
-        <v>56-61</v>
+        <v>59-64</v>
       </c>
       <c r="F175" t="str">
-        <v>100.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="176">
       <c r="A176">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B176" t="str">
         <v>Haina Desert</v>
@@ -3911,10 +3912,10 @@
         <v>Main Area</v>
       </c>
       <c r="D176" t="str">
-        <v>Celesteela</v>
+        <v>Alolan Dugtrio</v>
       </c>
       <c r="E176" t="str">
-        <v>58-63</v>
+        <v>59-64</v>
       </c>
       <c r="F176" t="str">
         <v>25.00%</v>
@@ -3922,7 +3923,7 @@
     </row>
     <row r="177">
       <c r="A177">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B177" t="str">
         <v>Haina Desert</v>
@@ -3931,10 +3932,10 @@
         <v>Main Area</v>
       </c>
       <c r="D177" t="str">
-        <v>Alolan Dugtrio</v>
+        <v>Sandile</v>
       </c>
       <c r="E177" t="str">
-        <v>58-63</v>
+        <v>59-64</v>
       </c>
       <c r="F177" t="str">
         <v>25.00%</v>
@@ -3942,7 +3943,7 @@
     </row>
     <row r="178">
       <c r="A178">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B178" t="str">
         <v>Haina Desert</v>
@@ -3951,10 +3952,10 @@
         <v>Main Area</v>
       </c>
       <c r="D178" t="str">
-        <v>Sandile</v>
+        <v>Krokorok</v>
       </c>
       <c r="E178" t="str">
-        <v>58-63</v>
+        <v>59-64</v>
       </c>
       <c r="F178" t="str">
         <v>25.00%</v>
@@ -3962,47 +3963,47 @@
     </row>
     <row r="179">
       <c r="A179">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B179" t="str">
-        <v>Haina Desert</v>
+        <v>Ruins of Abundance</v>
       </c>
       <c r="C179" t="str">
-        <v>Main Area</v>
+        <v>Special Encounter</v>
       </c>
       <c r="D179" t="str">
-        <v>Krokorok</v>
+        <v>Tapu Bulu</v>
       </c>
       <c r="E179" t="str">
-        <v>58-63</v>
+        <v>60-65</v>
       </c>
       <c r="F179" t="str">
-        <v>25.00%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="180">
       <c r="A180">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B180" t="str">
-        <v>Ruins of Abundance</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C180" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D180" t="str">
-        <v>Tapu Bulu</v>
+        <v>Graveler</v>
       </c>
       <c r="E180" t="str">
-        <v>59-64</v>
+        <v>62-67</v>
       </c>
       <c r="F180" t="str">
-        <v>100.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="181">
       <c r="A181">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B181" t="str">
         <v>Tapu Village</v>
@@ -4011,10 +4012,10 @@
         <v>Main Area</v>
       </c>
       <c r="D181" t="str">
-        <v>Graveler</v>
+        <v>Bruxish</v>
       </c>
       <c r="E181" t="str">
-        <v>60-65</v>
+        <v>62-67</v>
       </c>
       <c r="F181" t="str">
         <v>16.67%</v>
@@ -4022,7 +4023,7 @@
     </row>
     <row r="182">
       <c r="A182">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B182" t="str">
         <v>Tapu Village</v>
@@ -4031,10 +4032,10 @@
         <v>Main Area</v>
       </c>
       <c r="D182" t="str">
-        <v>Bruxish</v>
+        <v>Absol</v>
       </c>
       <c r="E182" t="str">
-        <v>60-65</v>
+        <v>62-67</v>
       </c>
       <c r="F182" t="str">
         <v>16.67%</v>
@@ -4042,7 +4043,7 @@
     </row>
     <row r="183">
       <c r="A183">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B183" t="str">
         <v>Tapu Village</v>
@@ -4051,10 +4052,10 @@
         <v>Main Area</v>
       </c>
       <c r="D183" t="str">
-        <v>Absol</v>
+        <v>Snorunt</v>
       </c>
       <c r="E183" t="str">
-        <v>60-65</v>
+        <v>62-67</v>
       </c>
       <c r="F183" t="str">
         <v>16.67%</v>
@@ -4062,7 +4063,7 @@
     </row>
     <row r="184">
       <c r="A184">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B184" t="str">
         <v>Tapu Village</v>
@@ -4071,10 +4072,10 @@
         <v>Main Area</v>
       </c>
       <c r="D184" t="str">
-        <v>Snorunt</v>
+        <v>Alolan Sandshrew</v>
       </c>
       <c r="E184" t="str">
-        <v>60-65</v>
+        <v>62-67</v>
       </c>
       <c r="F184" t="str">
         <v>16.67%</v>
@@ -4082,7 +4083,7 @@
     </row>
     <row r="185">
       <c r="A185">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B185" t="str">
         <v>Tapu Village</v>
@@ -4091,10 +4092,10 @@
         <v>Main Area</v>
       </c>
       <c r="D185" t="str">
-        <v>Alolan Sandshrew</v>
+        <v>Alolan Vulpix</v>
       </c>
       <c r="E185" t="str">
-        <v>60-65</v>
+        <v>62-67</v>
       </c>
       <c r="F185" t="str">
         <v>16.67%</v>
@@ -4102,47 +4103,47 @@
     </row>
     <row r="186">
       <c r="A186">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B186" t="str">
-        <v>Tapu Village</v>
+        <v>Route 14</v>
       </c>
       <c r="C186" t="str">
         <v>Main Area</v>
       </c>
       <c r="D186" t="str">
-        <v>Alolan Vulpix</v>
+        <v>Bruxish</v>
       </c>
       <c r="E186" t="str">
-        <v>60-65</v>
+        <v>63-68</v>
       </c>
       <c r="F186" t="str">
-        <v>16.67%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="187">
       <c r="A187">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B187" t="str">
-        <v>Route 14</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C187" t="str">
-        <v>Special Encounter</v>
+        <v>Abandoned Site</v>
       </c>
       <c r="D187" t="str">
-        <v>Bruxish</v>
+        <v>Haunter</v>
       </c>
       <c r="E187" t="str">
-        <v>61-66</v>
+        <v>64-69</v>
       </c>
       <c r="F187" t="str">
-        <v>100.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="188">
       <c r="A188">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B188" t="str">
         <v>Thrifty Megamart</v>
@@ -4151,10 +4152,10 @@
         <v>Abandoned Site</v>
       </c>
       <c r="D188" t="str">
-        <v>Haunter</v>
+        <v>Klefki</v>
       </c>
       <c r="E188" t="str">
-        <v>63-68</v>
+        <v>64-69</v>
       </c>
       <c r="F188" t="str">
         <v>33.33%</v>
@@ -4162,7 +4163,7 @@
     </row>
     <row r="189">
       <c r="A189">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B189" t="str">
         <v>Thrifty Megamart</v>
@@ -4171,10 +4172,10 @@
         <v>Abandoned Site</v>
       </c>
       <c r="D189" t="str">
-        <v>Klefki</v>
+        <v>Shuppet</v>
       </c>
       <c r="E189" t="str">
-        <v>63-68</v>
+        <v>64-69</v>
       </c>
       <c r="F189" t="str">
         <v>33.33%</v>
@@ -4182,59 +4183,59 @@
     </row>
     <row r="190">
       <c r="A190">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B190" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Captain Acerola</v>
       </c>
       <c r="C190" t="str">
-        <v>Abandoned Site</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D190" t="str">
-        <v>Shuppet</v>
+        <v>Boss</v>
       </c>
       <c r="E190" t="str">
-        <v>63-68</v>
+        <v>65-70</v>
       </c>
       <c r="F190" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="191">
       <c r="A191">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B191" t="str">
-        <v>Captain Acerola</v>
+        <v>Route 15</v>
       </c>
       <c r="C191" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D191" t="str">
-        <v>Boss</v>
+        <v>Sandygast</v>
       </c>
       <c r="E191" t="str">
-        <v>64-69</v>
+        <v>66-71</v>
       </c>
       <c r="F191" t="str">
-        <v>-</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="192">
       <c r="A192">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B192" t="str">
-        <v>Route 15</v>
+        <v>Route 16</v>
       </c>
       <c r="C192" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D192" t="str">
-        <v>Sandygast</v>
+        <v>Klefki</v>
       </c>
       <c r="E192" t="str">
-        <v>65-70</v>
+        <v>67-72</v>
       </c>
       <c r="F192" t="str">
         <v>100.00%</v>
@@ -4242,27 +4243,27 @@
     </row>
     <row r="193">
       <c r="A193">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B193" t="str">
-        <v>Route 16</v>
+        <v>Route 17</v>
       </c>
       <c r="C193" t="str">
-        <v>Special Encounter</v>
+        <v>Northeast</v>
       </c>
       <c r="D193" t="str">
-        <v>Klefki</v>
+        <v>Scraggy</v>
       </c>
       <c r="E193" t="str">
-        <v>66-71</v>
+        <v>68-73</v>
       </c>
       <c r="F193" t="str">
-        <v>100.00%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="194">
       <c r="A194">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B194" t="str">
         <v>Route 17</v>
@@ -4271,7 +4272,7 @@
         <v>Northeast</v>
       </c>
       <c r="D194" t="str">
-        <v>Scraggy</v>
+        <v>Bisharp</v>
       </c>
       <c r="E194" t="str">
         <v>68-73</v>
@@ -4282,47 +4283,47 @@
     </row>
     <row r="195">
       <c r="A195">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B195" t="str">
-        <v>Route 17</v>
+        <v>Kahuna Nanu</v>
       </c>
       <c r="C195" t="str">
-        <v>Northeast</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D195" t="str">
-        <v>Bisharp</v>
+        <v>Boss</v>
       </c>
       <c r="E195" t="str">
-        <v>68-73</v>
+        <v>69-74</v>
       </c>
       <c r="F195" t="str">
-        <v>50.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="196">
       <c r="A196">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B196" t="str">
-        <v>Kahuna Nanu</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C196" t="str">
-        <v>Boss Battle</v>
+        <v>Main</v>
       </c>
       <c r="D196" t="str">
-        <v>Boss</v>
+        <v>Steenee</v>
       </c>
       <c r="E196" t="str">
-        <v>69-74</v>
+        <v>70-75</v>
       </c>
       <c r="F196" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="197">
       <c r="A197">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B197" t="str">
         <v>Seafolk Village</v>
@@ -4331,7 +4332,7 @@
         <v>Main</v>
       </c>
       <c r="D197" t="str">
-        <v>Steenee</v>
+        <v>Shellos</v>
       </c>
       <c r="E197" t="str">
         <v>70-75</v>
@@ -4342,7 +4343,7 @@
     </row>
     <row r="198">
       <c r="A198">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B198" t="str">
         <v>Seafolk Village</v>
@@ -4351,7 +4352,7 @@
         <v>Main</v>
       </c>
       <c r="D198" t="str">
-        <v>Shellos</v>
+        <v>Dhelmise</v>
       </c>
       <c r="E198" t="str">
         <v>70-75</v>
@@ -4362,19 +4363,19 @@
     </row>
     <row r="199">
       <c r="A199">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B199" t="str">
-        <v>Seafolk Village</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C199" t="str">
-        <v>Main</v>
+        <v>Main Area</v>
       </c>
       <c r="D199" t="str">
-        <v>Dhelmise</v>
+        <v>Tentacruel</v>
       </c>
       <c r="E199" t="str">
-        <v>70-75</v>
+        <v>71-76</v>
       </c>
       <c r="F199" t="str">
         <v>33.33%</v>
@@ -4382,7 +4383,7 @@
     </row>
     <row r="200">
       <c r="A200">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B200" t="str">
         <v>Poni Wilds</v>
@@ -4391,10 +4392,10 @@
         <v>Main Area</v>
       </c>
       <c r="D200" t="str">
-        <v>Tentacruel</v>
+        <v>Lumineon</v>
       </c>
       <c r="E200" t="str">
-        <v>72-77</v>
+        <v>71-76</v>
       </c>
       <c r="F200" t="str">
         <v>33.33%</v>
@@ -4402,7 +4403,7 @@
     </row>
     <row r="201">
       <c r="A201">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B201" t="str">
         <v>Poni Wilds</v>
@@ -4411,10 +4412,10 @@
         <v>Main Area</v>
       </c>
       <c r="D201" t="str">
-        <v>Lumineon</v>
+        <v>Lapras</v>
       </c>
       <c r="E201" t="str">
-        <v>72-77</v>
+        <v>71-76</v>
       </c>
       <c r="F201" t="str">
         <v>33.33%</v>
@@ -4422,27 +4423,27 @@
     </row>
     <row r="202">
       <c r="A202">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B202" t="str">
-        <v>Poni Wilds</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C202" t="str">
         <v>Main Area</v>
       </c>
       <c r="D202" t="str">
-        <v>Lapras</v>
+        <v>Wimpod</v>
       </c>
       <c r="E202" t="str">
         <v>72-77</v>
       </c>
       <c r="F202" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="203">
       <c r="A203">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B203" t="str">
         <v>Poni Breaker Coast</v>
@@ -4451,10 +4452,10 @@
         <v>Main Area</v>
       </c>
       <c r="D203" t="str">
-        <v>Wimpod</v>
+        <v>Relicanth</v>
       </c>
       <c r="E203" t="str">
-        <v>73-78</v>
+        <v>72-77</v>
       </c>
       <c r="F203" t="str">
         <v>20.00%</v>
@@ -4462,7 +4463,7 @@
     </row>
     <row r="204">
       <c r="A204">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B204" t="str">
         <v>Poni Breaker Coast</v>
@@ -4471,10 +4472,10 @@
         <v>Main Area</v>
       </c>
       <c r="D204" t="str">
-        <v>Relicanth</v>
+        <v>Wailmer</v>
       </c>
       <c r="E204" t="str">
-        <v>73-78</v>
+        <v>72-77</v>
       </c>
       <c r="F204" t="str">
         <v>20.00%</v>
@@ -4482,7 +4483,7 @@
     </row>
     <row r="205">
       <c r="A205">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B205" t="str">
         <v>Poni Breaker Coast</v>
@@ -4491,10 +4492,10 @@
         <v>Main Area</v>
       </c>
       <c r="D205" t="str">
-        <v>Wailmer</v>
+        <v>Carvanha</v>
       </c>
       <c r="E205" t="str">
-        <v>73-78</v>
+        <v>72-77</v>
       </c>
       <c r="F205" t="str">
         <v>20.00%</v>
@@ -4502,7 +4503,7 @@
     </row>
     <row r="206">
       <c r="A206">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B206" t="str">
         <v>Poni Breaker Coast</v>
@@ -4511,10 +4512,10 @@
         <v>Main Area</v>
       </c>
       <c r="D206" t="str">
-        <v>Carvanha</v>
+        <v>Sharpedo</v>
       </c>
       <c r="E206" t="str">
-        <v>73-78</v>
+        <v>72-77</v>
       </c>
       <c r="F206" t="str">
         <v>20.00%</v>
@@ -4522,47 +4523,47 @@
     </row>
     <row r="207">
       <c r="A207">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B207" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Ruins of Hope</v>
       </c>
       <c r="C207" t="str">
-        <v>Main Area</v>
+        <v>Special Encounter</v>
       </c>
       <c r="D207" t="str">
-        <v>Sharpedo</v>
+        <v>Tapu Fini</v>
       </c>
       <c r="E207" t="str">
-        <v>73-78</v>
+        <v>74-79</v>
       </c>
       <c r="F207" t="str">
-        <v>20.00%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="208">
       <c r="A208">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B208" t="str">
-        <v>Ruins of Hope</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C208" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D208" t="str">
-        <v>Tapu Fini</v>
+        <v>Pelipper</v>
       </c>
       <c r="E208" t="str">
-        <v>74-79</v>
+        <v>75-80</v>
       </c>
       <c r="F208" t="str">
-        <v>100.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="209">
       <c r="A209">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B209" t="str">
         <v>Exeggutor Island</v>
@@ -4571,7 +4572,7 @@
         <v>Main Area</v>
       </c>
       <c r="D209" t="str">
-        <v>Pelipper</v>
+        <v>Pinsir</v>
       </c>
       <c r="E209" t="str">
         <v>75-80</v>
@@ -4582,7 +4583,7 @@
     </row>
     <row r="210">
       <c r="A210">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B210" t="str">
         <v>Exeggutor Island</v>
@@ -4591,7 +4592,7 @@
         <v>Main Area</v>
       </c>
       <c r="D210" t="str">
-        <v>Pinsir</v>
+        <v>Gastrodon</v>
       </c>
       <c r="E210" t="str">
         <v>75-80</v>
@@ -4602,7 +4603,7 @@
     </row>
     <row r="211">
       <c r="A211">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B211" t="str">
         <v>Exeggutor Island</v>
@@ -4611,7 +4612,7 @@
         <v>Main Area</v>
       </c>
       <c r="D211" t="str">
-        <v>Gastrodon</v>
+        <v>Exeggcute</v>
       </c>
       <c r="E211" t="str">
         <v>75-80</v>
@@ -4622,7 +4623,7 @@
     </row>
     <row r="212">
       <c r="A212">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B212" t="str">
         <v>Exeggutor Island</v>
@@ -4631,7 +4632,7 @@
         <v>Main Area</v>
       </c>
       <c r="D212" t="str">
-        <v>Exeggcute</v>
+        <v>Tropius</v>
       </c>
       <c r="E212" t="str">
         <v>75-80</v>
@@ -4642,7 +4643,7 @@
     </row>
     <row r="213">
       <c r="A213">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B213" t="str">
         <v>Exeggutor Island</v>
@@ -4651,7 +4652,7 @@
         <v>Main Area</v>
       </c>
       <c r="D213" t="str">
-        <v>Tropius</v>
+        <v>Alolan Exeggutor</v>
       </c>
       <c r="E213" t="str">
         <v>75-80</v>
@@ -4662,59 +4663,59 @@
     </row>
     <row r="214">
       <c r="A214">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B214" t="str">
-        <v>Exeggutor Island</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C214" t="str">
-        <v>Main Area</v>
+        <v>Outside</v>
       </c>
       <c r="D214" t="str">
-        <v>Alolan Exeggutor</v>
+        <v>Machoke</v>
       </c>
       <c r="E214" t="str">
-        <v>75-80</v>
+        <v>76-81</v>
       </c>
       <c r="F214" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="215">
       <c r="A215">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B215" t="str">
         <v>Vast Poni Canyon</v>
       </c>
       <c r="C215" t="str">
-        <v>Inside</v>
+        <v>Outside</v>
       </c>
       <c r="D215" t="str">
-        <v>Boldore</v>
+        <v>Mienfoo</v>
       </c>
       <c r="E215" t="str">
-        <v>77-82</v>
+        <v>76-81</v>
       </c>
       <c r="F215" t="str">
-        <v>100.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="216">
       <c r="A216">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B216" t="str">
         <v>Vast Poni Canyon</v>
       </c>
       <c r="C216" t="str">
-        <v>Northwest (Hidden Area)</v>
+        <v>Outside</v>
       </c>
       <c r="D216" t="str">
-        <v>Corphish</v>
+        <v>Jangmo-o</v>
       </c>
       <c r="E216" t="str">
-        <v>77-82</v>
+        <v>76-81</v>
       </c>
       <c r="F216" t="str">
         <v>33.33%</v>
@@ -4722,27 +4723,27 @@
     </row>
     <row r="217">
       <c r="A217">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B217" t="str">
         <v>Vast Poni Canyon</v>
       </c>
       <c r="C217" t="str">
-        <v>Northwest (Hidden Area)</v>
+        <v>Inside</v>
       </c>
       <c r="D217" t="str">
-        <v>Dratini</v>
+        <v>Boldore</v>
       </c>
       <c r="E217" t="str">
         <v>77-82</v>
       </c>
       <c r="F217" t="str">
-        <v>33.33%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="218">
       <c r="A218">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B218" t="str">
         <v>Vast Poni Canyon</v>
@@ -4751,10 +4752,10 @@
         <v>Northwest (Hidden Area)</v>
       </c>
       <c r="D218" t="str">
-        <v>Golduck</v>
+        <v>Corphish</v>
       </c>
       <c r="E218" t="str">
-        <v>77-82</v>
+        <v>78-83</v>
       </c>
       <c r="F218" t="str">
         <v>33.33%</v>
@@ -4762,19 +4763,19 @@
     </row>
     <row r="219">
       <c r="A219">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B219" t="str">
         <v>Vast Poni Canyon</v>
       </c>
       <c r="C219" t="str">
-        <v>Outside</v>
+        <v>Northwest (Hidden Area)</v>
       </c>
       <c r="D219" t="str">
-        <v>Machoke</v>
+        <v>Dratini</v>
       </c>
       <c r="E219" t="str">
-        <v>77-82</v>
+        <v>78-83</v>
       </c>
       <c r="F219" t="str">
         <v>33.33%</v>
@@ -4782,19 +4783,19 @@
     </row>
     <row r="220">
       <c r="A220">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B220" t="str">
         <v>Vast Poni Canyon</v>
       </c>
       <c r="C220" t="str">
-        <v>Outside</v>
+        <v>Northwest (Hidden Area)</v>
       </c>
       <c r="D220" t="str">
-        <v>Mienfoo</v>
+        <v>Golduck</v>
       </c>
       <c r="E220" t="str">
-        <v>77-82</v>
+        <v>78-83</v>
       </c>
       <c r="F220" t="str">
         <v>33.33%</v>
@@ -4802,70 +4803,70 @@
     </row>
     <row r="221">
       <c r="A221">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B221" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Captain Kommo-o</v>
       </c>
       <c r="C221" t="str">
-        <v>Outside</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D221" t="str">
-        <v>Jangmo-o</v>
+        <v>Boss</v>
       </c>
       <c r="E221" t="str">
-        <v>77-82</v>
+        <v>79-84</v>
       </c>
       <c r="F221" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="222">
       <c r="A222">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B222" t="str">
-        <v>Captain Kommo-o</v>
+        <v>Altar of the Sunne/Moone</v>
       </c>
       <c r="C222" t="str">
-        <v>Boss Battle</v>
+        <v>Special Encounter</v>
       </c>
       <c r="D222" t="str">
-        <v>Boss</v>
+        <v>Cosmog</v>
       </c>
       <c r="E222" t="str">
-        <v>78-83</v>
+        <v>80-85</v>
       </c>
       <c r="F222" t="str">
-        <v>-</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="223">
       <c r="A223">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B223" t="str">
-        <v>Altar of the Sunne/Moone</v>
+        <v>Captain Mina</v>
       </c>
       <c r="C223" t="str">
-        <v>Special Encounter</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D223" t="str">
-        <v>Cosmog</v>
+        <v>Boss</v>
       </c>
       <c r="E223" t="str">
-        <v>79-84</v>
+        <v>81-86</v>
       </c>
       <c r="F223" t="str">
-        <v>100.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="224">
       <c r="A224">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B224" t="str">
-        <v>Captain Mina</v>
+        <v>Kahuna Hapu</v>
       </c>
       <c r="C224" t="str">
         <v>Boss Battle</v>
@@ -4874,7 +4875,7 @@
         <v>Boss</v>
       </c>
       <c r="E224" t="str">
-        <v>80-85</v>
+        <v>82-87</v>
       </c>
       <c r="F224" t="str">
         <v>-</v>
@@ -4882,27 +4883,27 @@
     </row>
     <row r="225">
       <c r="A225">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B225" t="str">
-        <v>Kahuna Hapu</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C225" t="str">
-        <v>Boss Battle</v>
+        <v>Cave</v>
       </c>
       <c r="D225" t="str">
-        <v>Boss</v>
+        <v>Drampa</v>
       </c>
       <c r="E225" t="str">
-        <v>82-87</v>
+        <v>83-88</v>
       </c>
       <c r="F225" t="str">
-        <v>-</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="226">
       <c r="A226">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B226" t="str">
         <v>Mount Lanakila</v>
@@ -4911,18 +4912,18 @@
         <v>Cave</v>
       </c>
       <c r="D226" t="str">
-        <v>Drampa</v>
+        <v>Glalie</v>
       </c>
       <c r="E226" t="str">
         <v>83-88</v>
       </c>
       <c r="F226" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="227">
       <c r="A227">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B227" t="str">
         <v>Mount Lanakila</v>
@@ -4931,18 +4932,18 @@
         <v>Cave</v>
       </c>
       <c r="D227" t="str">
-        <v>Glalie</v>
+        <v>Sneasel</v>
       </c>
       <c r="E227" t="str">
         <v>83-88</v>
       </c>
       <c r="F227" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="228">
       <c r="A228">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B228" t="str">
         <v>Mount Lanakila</v>
@@ -4951,41 +4952,41 @@
         <v>Cave</v>
       </c>
       <c r="D228" t="str">
-        <v>Sneasel</v>
+        <v>Crabominable</v>
       </c>
       <c r="E228" t="str">
         <v>83-88</v>
       </c>
       <c r="F228" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="229">
       <c r="A229">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B229" t="str">
-        <v>Mount Lanakila</v>
+        <v>Alola Pokemon League</v>
       </c>
       <c r="C229" t="str">
-        <v>Special Encounter</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D229" t="str">
-        <v>Crabominable</v>
+        <v>Boss</v>
       </c>
       <c r="E229" t="str">
-        <v>83-88</v>
+        <v>84-89</v>
       </c>
       <c r="F229" t="str">
-        <v>100.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="230">
       <c r="A230">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B230" t="str">
-        <v>Alola Pokemon League</v>
+        <v>Champion Hau</v>
       </c>
       <c r="C230" t="str">
         <v>Boss Battle</v>
@@ -4994,7 +4995,7 @@
         <v>Boss</v>
       </c>
       <c r="E230" t="str">
-        <v>84-89</v>
+        <v>85-90</v>
       </c>
       <c r="F230" t="str">
         <v>-</v>
@@ -5002,654 +5003,614 @@
     </row>
     <row r="231">
       <c r="A231">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B231" t="str">
-        <v>Champion Hau</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C231" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D231" t="str">
-        <v>Boss</v>
+        <v>Buneary</v>
       </c>
       <c r="E231" t="str">
-        <v>85-90</v>
+        <v>90-100</v>
       </c>
       <c r="F231" t="str">
-        <v>-</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="232">
       <c r="A232">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B232" t="str">
-        <v>Ultra Space Wilds</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C232" t="str">
-        <v>Wormholes</v>
+        <v>Main Area</v>
       </c>
       <c r="D232" t="str">
-        <v>Ultra Beasts</v>
+        <v>Granbull</v>
       </c>
       <c r="E232" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F232" t="str">
-        <v>10%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="233">
       <c r="A233">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B233" t="str">
-        <v>Ultra Space Wilds</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C233" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D233" t="str">
-        <v>Poipole</v>
+        <v>Zoroark</v>
       </c>
       <c r="E233" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F233" t="str">
-        <v>20.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="234">
       <c r="A234">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B234" t="str">
-        <v>Ultra Space Wilds</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C234" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D234" t="str">
-        <v>Xurkitree</v>
+        <v>Heracross</v>
       </c>
       <c r="E234" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F234" t="str">
-        <v>20.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="235">
       <c r="A235">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B235" t="str">
-        <v>Ultra Space Wilds</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C235" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D235" t="str">
-        <v>Celesteela</v>
+        <v>Riolu</v>
       </c>
       <c r="E235" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F235" t="str">
-        <v>20.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="236">
       <c r="A236">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B236" t="str">
-        <v>Ultra Space Wilds</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C236" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D236" t="str">
-        <v>Kartana</v>
+        <v>Stakataka</v>
       </c>
       <c r="E236" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F236" t="str">
-        <v>20.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="237">
       <c r="A237">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B237" t="str">
-        <v>Ultra Space Wilds</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C237" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D237" t="str">
-        <v>Guzzlord</v>
+        <v>Blacephalon</v>
       </c>
       <c r="E237" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F237" t="str">
-        <v>20.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="238">
       <c r="A238">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B238" t="str">
-        <v>Event: Magearna</v>
+        <v>Poni Plains</v>
       </c>
       <c r="C238" t="str">
-        <v>Special Encounter</v>
+        <v>Center</v>
       </c>
       <c r="D238" t="str">
-        <v>Magearna</v>
+        <v>Hariyama</v>
       </c>
       <c r="E238" t="str">
-        <v>95-100</v>
+        <v>90-100</v>
       </c>
       <c r="F238" t="str">
-        <v>100%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="239">
       <c r="A239">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B239" t="str">
-        <v>Event: Marshadow</v>
+        <v>Poni Plains</v>
       </c>
       <c r="C239" t="str">
-        <v>Special Encounter</v>
+        <v>Center</v>
       </c>
       <c r="D239" t="str">
-        <v>Marshadow</v>
+        <v>Mudsdale</v>
       </c>
       <c r="E239" t="str">
-        <v>95-100</v>
+        <v>90-100</v>
       </c>
       <c r="F239" t="str">
-        <v>100%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="240">
       <c r="A240">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B240" t="str">
-        <v>Event: Zeraora</v>
+        <v>Resolution Cave</v>
       </c>
       <c r="C240" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D240" t="str">
-        <v>Zeraora</v>
+        <v>Noivern</v>
       </c>
       <c r="E240" t="str">
-        <v>95-100</v>
+        <v>90-100</v>
       </c>
       <c r="F240" t="str">
-        <v>100%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="241">
       <c r="A241">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B241" t="str">
-        <v>Poni Grove</v>
+        <v>Resolution Cave</v>
       </c>
       <c r="C241" t="str">
         <v>Main Area</v>
       </c>
       <c r="D241" t="str">
-        <v>Buneary</v>
+        <v>Druddigon</v>
       </c>
       <c r="E241" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F241" t="str">
-        <v>14.29%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="242">
       <c r="A242">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B242" t="str">
-        <v>Poni Grove</v>
+        <v>Resolution Cave</v>
       </c>
       <c r="C242" t="str">
         <v>Main Area</v>
       </c>
       <c r="D242" t="str">
-        <v>Granbull</v>
+        <v>Guzzlord</v>
       </c>
       <c r="E242" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F242" t="str">
-        <v>14.29%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="243">
       <c r="A243">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B243" t="str">
-        <v>Poni Grove</v>
+        <v>Mahalo Trail</v>
       </c>
       <c r="C243" t="str">
         <v>Main Area</v>
       </c>
       <c r="D243" t="str">
-        <v>Zoroark</v>
+        <v>Solgaleo</v>
       </c>
       <c r="E243" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F243" t="str">
-        <v>14.29%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="244">
       <c r="A244">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B244" t="str">
-        <v>Poni Grove</v>
+        <v>Mahalo Trail</v>
       </c>
       <c r="C244" t="str">
         <v>Main Area</v>
       </c>
       <c r="D244" t="str">
-        <v>Heracross</v>
+        <v>Lunala</v>
       </c>
       <c r="E244" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F244" t="str">
-        <v>14.29%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="245">
       <c r="A245">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B245" t="str">
-        <v>Poni Grove</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C245" t="str">
         <v>Main Area</v>
       </c>
       <c r="D245" t="str">
-        <v>Riolu</v>
+        <v>Caterpie</v>
       </c>
       <c r="E245" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F245" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="246">
       <c r="A246">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B246" t="str">
-        <v>Poni Grove</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C246" t="str">
         <v>Main Area</v>
       </c>
       <c r="D246" t="str">
-        <v>Stakataka</v>
+        <v>Metapod</v>
       </c>
       <c r="E246" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F246" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="247">
       <c r="A247">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B247" t="str">
-        <v>Poni Grove</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C247" t="str">
         <v>Main Area</v>
       </c>
       <c r="D247" t="str">
-        <v>Blacephalon</v>
+        <v>Cutiefly</v>
       </c>
       <c r="E247" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F247" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="248">
       <c r="A248">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B248" t="str">
-        <v>Poni Plains</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C248" t="str">
-        <v>Center</v>
+        <v>Main Area</v>
       </c>
       <c r="D248" t="str">
-        <v>Hariyama</v>
+        <v>Butterfree</v>
       </c>
       <c r="E248" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F248" t="str">
-        <v>50.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="249">
       <c r="A249">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B249" t="str">
-        <v>Poni Plains</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C249" t="str">
-        <v>Center</v>
+        <v>Main Area</v>
       </c>
       <c r="D249" t="str">
-        <v>Mudsdale</v>
+        <v>Flabébé</v>
       </c>
       <c r="E249" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F249" t="str">
-        <v>50.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="250">
       <c r="A250">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B250" t="str">
-        <v>Resolution Cave</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C250" t="str">
         <v>Main Area</v>
       </c>
       <c r="D250" t="str">
-        <v>Noivern</v>
+        <v>Petilil</v>
       </c>
       <c r="E250" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F250" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="251">
       <c r="A251">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B251" t="str">
-        <v>Resolution Cave</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C251" t="str">
         <v>Main Area</v>
       </c>
       <c r="D251" t="str">
-        <v>Druddigon</v>
+        <v>Cottonee</v>
       </c>
       <c r="E251" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F251" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="252">
       <c r="A252">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B252" t="str">
-        <v>Resolution Cave</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C252" t="str">
         <v>Main Area</v>
       </c>
       <c r="D252" t="str">
-        <v>Guzzlord</v>
+        <v>Buzzwole</v>
       </c>
       <c r="E252" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F252" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="253">
       <c r="A253">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B253" t="str">
-        <v>Mahalo Trail</v>
+        <v>Ultra Space Wilds</v>
       </c>
       <c r="C253" t="str">
-        <v>Main Area</v>
+        <v>Wormholes</v>
       </c>
       <c r="D253" t="str">
-        <v>Solgaleo</v>
+        <v>Poipole</v>
       </c>
       <c r="E253" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F253" t="str">
-        <v>50.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="254">
       <c r="A254">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B254" t="str">
-        <v>Mahalo Trail</v>
+        <v>Ultra Space Wilds</v>
       </c>
       <c r="C254" t="str">
-        <v>Main Area</v>
+        <v>Wormholes</v>
       </c>
       <c r="D254" t="str">
-        <v>Lunala</v>
+        <v>Xurkitree</v>
       </c>
       <c r="E254" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F254" t="str">
-        <v>50.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="255">
       <c r="A255">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B255" t="str">
-        <v>Melemele Meadow</v>
+        <v>Ultra Space Wilds</v>
       </c>
       <c r="C255" t="str">
-        <v>Main Area</v>
+        <v>Wormholes</v>
       </c>
       <c r="D255" t="str">
-        <v>Caterpie</v>
+        <v>Celesteela</v>
       </c>
       <c r="E255" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F255" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="256">
       <c r="A256">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B256" t="str">
-        <v>Melemele Meadow</v>
+        <v>Ultra Space Wilds</v>
       </c>
       <c r="C256" t="str">
-        <v>Main Area</v>
+        <v>Wormholes</v>
       </c>
       <c r="D256" t="str">
-        <v>Metapod</v>
+        <v>Kartana</v>
       </c>
       <c r="E256" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F256" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="257">
       <c r="A257">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B257" t="str">
-        <v>Melemele Meadow</v>
+        <v>Ultra Space Wilds</v>
       </c>
       <c r="C257" t="str">
-        <v>Main Area</v>
+        <v>Wormholes</v>
       </c>
       <c r="D257" t="str">
-        <v>Cutiefly</v>
+        <v>Guzzlord</v>
       </c>
       <c r="E257" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F257" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="258">
       <c r="A258">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B258" t="str">
-        <v>Melemele Meadow</v>
+        <v>Event: Magearna</v>
       </c>
       <c r="C258" t="str">
-        <v>Main Area</v>
+        <v>Special Encounter</v>
       </c>
       <c r="D258" t="str">
-        <v>Butterfree</v>
+        <v>Magearna</v>
       </c>
       <c r="E258" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F258" t="str">
-        <v>12.50%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="259">
       <c r="A259">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B259" t="str">
-        <v>Melemele Meadow</v>
+        <v>Event: Marshadow</v>
       </c>
       <c r="C259" t="str">
-        <v>Main Area</v>
+        <v>Special Encounter</v>
       </c>
       <c r="D259" t="str">
-        <v>Flabébé</v>
+        <v>Marshadow</v>
       </c>
       <c r="E259" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F259" t="str">
-        <v>12.50%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="260">
       <c r="A260">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B260" t="str">
-        <v>Melemele Meadow</v>
+        <v>Event: Zeraora</v>
       </c>
       <c r="C260" t="str">
-        <v>Main Area</v>
+        <v>Special Encounter</v>
       </c>
       <c r="D260" t="str">
-        <v>Petilil</v>
+        <v>Zeraora</v>
       </c>
       <c r="E260" t="str">
-        <v>90-95</v>
+        <v>90-100</v>
       </c>
       <c r="F260" t="str">
-        <v>12.50%</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261">
-        <v>93</v>
-      </c>
-      <c r="B261" t="str">
-        <v>Melemele Meadow</v>
-      </c>
-      <c r="C261" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D261" t="str">
-        <v>Cottonee</v>
-      </c>
-      <c r="E261" t="str">
-        <v>90-95</v>
-      </c>
-      <c r="F261" t="str">
-        <v>12.50%</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262">
-        <v>93</v>
-      </c>
-      <c r="B262" t="str">
-        <v>Melemele Meadow</v>
-      </c>
-      <c r="C262" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D262" t="str">
-        <v>Buzzwole</v>
-      </c>
-      <c r="E262" t="str">
-        <v>90-95</v>
-      </c>
-      <c r="F262" t="str">
-        <v>12.50%</v>
+        <v>100.00%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F262"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F260"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C93"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5667,10 +5628,10 @@
         <v>Challenge 1</v>
       </c>
       <c r="B2" t="str">
-        <v>Meet Professor Kukui</v>
+        <v>Start the game</v>
       </c>
       <c r="C2" t="str">
-        <v>Starter</v>
+        <v>Starter Professor Kukui</v>
       </c>
     </row>
     <row r="3">
@@ -5678,10 +5639,10 @@
         <v>Challenge 2</v>
       </c>
       <c r="B3" t="str">
-        <v>Pick your Starter</v>
+        <v>Defeat 5 Pokemon in Starter Professor Kukui</v>
       </c>
       <c r="C3" t="str">
-        <v>Route 1</v>
+        <v>Route 1 East</v>
       </c>
     </row>
     <row r="4">
@@ -5689,10 +5650,10 @@
         <v>Challenge 3</v>
       </c>
       <c r="B4" t="str">
-        <v>Defeat 10 Pokemon in Route 1</v>
+        <v>Defeat 5 Pokemon in Route 1 East</v>
       </c>
       <c r="C4" t="str">
-        <v>Hau'oli City</v>
+        <v>Route 1 Hau'oli Outskirts</v>
       </c>
     </row>
     <row r="5">
@@ -5700,10 +5661,10 @@
         <v>Challenge 4</v>
       </c>
       <c r="B5" t="str">
-        <v>Defeat 5 Pokemon in Hau'oli City</v>
+        <v>Defeat 5 Pokemon in Route 1 Hau'oli Outskirts</v>
       </c>
       <c r="C5" t="str">
-        <v>Route 2</v>
+        <v>Route 1 South</v>
       </c>
     </row>
     <row r="6">
@@ -5711,10 +5672,10 @@
         <v>Challenge 5</v>
       </c>
       <c r="B6" t="str">
-        <v>Defeat 10 Pokemon in Route 2</v>
+        <v>Defeat 5 Pokemon in Route 1 South</v>
       </c>
       <c r="C6" t="str">
-        <v>Captain Ilima</v>
+        <v>Route 1 Trainers' School</v>
       </c>
     </row>
     <row r="7">
@@ -5722,10 +5683,10 @@
         <v>Challenge 6</v>
       </c>
       <c r="B7" t="str">
-        <v>Defeat Captain Ilima</v>
+        <v>Defeat 5 Pokemon in Route 1 Trainers' School</v>
       </c>
       <c r="C7" t="str">
-        <v>Hau'oli Cemetery</v>
+        <v>Hau'oli City Beachfront</v>
       </c>
     </row>
     <row r="8">
@@ -5733,10 +5694,10 @@
         <v>Challenge 7</v>
       </c>
       <c r="B8" t="str">
-        <v>Defeat 5 Pokemon in Hau'oli Cemetery</v>
+        <v>Defeat 5 Pokemon in Hau'oli City Beachfront</v>
       </c>
       <c r="C8" t="str">
-        <v>Verdant Cavern</v>
+        <v>Hau'oli City Shopping District</v>
       </c>
     </row>
     <row r="9">
@@ -5744,10 +5705,10 @@
         <v>Challenge 8</v>
       </c>
       <c r="B9" t="str">
-        <v>Defeat 10 Pokemon in Verdant Cavern</v>
+        <v>Defeat 5 Pokemon in Hau'oli City Shopping District</v>
       </c>
       <c r="C9" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Route 2 Main</v>
       </c>
     </row>
     <row r="10">
@@ -5755,10 +5716,10 @@
         <v>Challenge 9</v>
       </c>
       <c r="B10" t="str">
-        <v>Defeat 5 Pokemon in Ten Carat Hill</v>
+        <v>Defeat 5 Pokemon in Route 2 Main</v>
       </c>
       <c r="C10" t="str">
-        <v>Seaward Cave</v>
+        <v>Route 2 North</v>
       </c>
     </row>
     <row r="11">
@@ -5766,10 +5727,10 @@
         <v>Challenge 10</v>
       </c>
       <c r="B11" t="str">
-        <v>Defeat 5 Pokemon in Seaward Cave</v>
+        <v>Defeat 5 Pokemon in Route 2 North</v>
       </c>
       <c r="C11" t="str">
-        <v>Route 3</v>
+        <v>Captain Ilima</v>
       </c>
     </row>
     <row r="12">
@@ -5777,10 +5738,10 @@
         <v>Challenge 11</v>
       </c>
       <c r="B12" t="str">
-        <v>Defeat 10 Pokemon in Route 3</v>
+        <v>Defeat Captain Ilima</v>
       </c>
       <c r="C12" t="str">
-        <v>Ruins of Conflict</v>
+        <v>Hau'oli Cemetery Main Area</v>
       </c>
     </row>
     <row r="13">
@@ -5788,10 +5749,10 @@
         <v>Challenge 12</v>
       </c>
       <c r="B13" t="str">
-        <v>Catch Tapu Koko in Ruins of Conflict</v>
+        <v>Defeat 5 Pokemon in Hau'oli Cemetery Main Area</v>
       </c>
       <c r="C13" t="str">
-        <v>Kahuna Hala</v>
+        <v>Verdant Cavern Trial Site</v>
       </c>
     </row>
     <row r="14">
@@ -5799,10 +5760,10 @@
         <v>Challenge 13</v>
       </c>
       <c r="B14" t="str">
-        <v>Defeat Kahuna Hala</v>
+        <v>Defeat 5 Pokemon in Verdant Cavern Trial Site</v>
       </c>
       <c r="C14" t="str">
-        <v>Heahea Beach</v>
+        <v>Ten Carat Hill Inside</v>
       </c>
     </row>
     <row r="15">
@@ -5810,10 +5771,10 @@
         <v>Challenge 14</v>
       </c>
       <c r="B15" t="str">
-        <v>Defeat 5 Pokemon in Heahea Beach</v>
+        <v>Defeat 5 Pokemon in Ten Carat Hill Inside</v>
       </c>
       <c r="C15" t="str">
-        <v>Route 4</v>
+        <v>Ten Carat Hill Farthest Hollow</v>
       </c>
     </row>
     <row r="16">
@@ -5821,10 +5782,10 @@
         <v>Challenge 15</v>
       </c>
       <c r="B16" t="str">
-        <v>Defeat 10 Pokemon in Route 4</v>
+        <v>Defeat 5 Pokemon in Ten Carat Hill Farthest Hollow</v>
       </c>
       <c r="C16" t="str">
-        <v>Paniola Ranch</v>
+        <v>Seaward Cave Main Area</v>
       </c>
     </row>
     <row r="17">
@@ -5832,10 +5793,10 @@
         <v>Challenge 16</v>
       </c>
       <c r="B17" t="str">
-        <v>Defeat 5 Pokemon in Paniola Ranch</v>
+        <v>Defeat 5 Pokemon in Seaward Cave Main Area</v>
       </c>
       <c r="C17" t="str">
-        <v>Daycare</v>
+        <v>Route 3 North</v>
       </c>
     </row>
     <row r="18">
@@ -5843,10 +5804,10 @@
         <v>Challenge 17</v>
       </c>
       <c r="B18" t="str">
-        <v>Reach Daycare</v>
+        <v>Defeat 5 Pokemon in Route 3 North</v>
       </c>
       <c r="C18" t="str">
-        <v>Route 5</v>
+        <v>Ruins of Conflict Special Encounter</v>
       </c>
     </row>
     <row r="19">
@@ -5854,10 +5815,10 @@
         <v>Challenge 18</v>
       </c>
       <c r="B19" t="str">
-        <v>Defeat 5 Pokemon in Route 5</v>
+        <v>Defeat 5 Pokemon in Ruins of Conflict Special Encounter</v>
       </c>
       <c r="C19" t="str">
-        <v>Brooklet Hill</v>
+        <v>Kahuna Hala</v>
       </c>
     </row>
     <row r="20">
@@ -5865,10 +5826,10 @@
         <v>Challenge 19</v>
       </c>
       <c r="B20" t="str">
-        <v>Defeat 10 Pokemon in Brooklet Hill</v>
+        <v>Defeat Kahuna Hala</v>
       </c>
       <c r="C20" t="str">
-        <v>Captain Lana</v>
+        <v>Heahea Beach Main Area</v>
       </c>
     </row>
     <row r="21">
@@ -5876,10 +5837,10 @@
         <v>Challenge 20</v>
       </c>
       <c r="B21" t="str">
-        <v>Defeat Captain Lana</v>
+        <v>Defeat 5 Pokemon in Heahea Beach Main Area</v>
       </c>
       <c r="C21" t="str">
-        <v>Route 6</v>
+        <v>Route 4 Main Area</v>
       </c>
     </row>
     <row r="22">
@@ -5887,10 +5848,10 @@
         <v>Challenge 21</v>
       </c>
       <c r="B22" t="str">
-        <v>Defeat 5 Pokemon in Route 6</v>
+        <v>Defeat 5 Pokemon in Route 4 Main Area</v>
       </c>
       <c r="C22" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Paniola Ranch Main Area</v>
       </c>
     </row>
     <row r="23">
@@ -5898,10 +5859,10 @@
         <v>Challenge 22</v>
       </c>
       <c r="B23" t="str">
-        <v>Defeat 10 Pokemon in Wela Volcano Park</v>
+        <v>Defeat 5 Pokemon in Paniola Ranch Main Area</v>
       </c>
       <c r="C23" t="str">
-        <v>Captain Kiawe</v>
+        <v>Daycare NPC</v>
       </c>
     </row>
     <row r="24">
@@ -5909,10 +5870,10 @@
         <v>Challenge 23</v>
       </c>
       <c r="B24" t="str">
-        <v>Defeat Captain Kiawe</v>
+        <v>Interact with Daycare</v>
       </c>
       <c r="C24" t="str">
-        <v>Route 7</v>
+        <v>Route 5 Main Area</v>
       </c>
     </row>
     <row r="25">
@@ -5920,10 +5881,10 @@
         <v>Challenge 24</v>
       </c>
       <c r="B25" t="str">
-        <v>Defeat 5 Pokemon in Route 7</v>
+        <v>Defeat 5 Pokemon in Route 5 Main Area</v>
       </c>
       <c r="C25" t="str">
-        <v>Route 8</v>
+        <v>Brooklet Hill North</v>
       </c>
     </row>
     <row r="26">
@@ -5931,10 +5892,10 @@
         <v>Challenge 25</v>
       </c>
       <c r="B26" t="str">
-        <v>Defeat 5 Pokemon in Route 8</v>
+        <v>Defeat 5 Pokemon in Brooklet Hill North</v>
       </c>
       <c r="C26" t="str">
-        <v>Lush Jungle</v>
+        <v>Brooklet Hill South</v>
       </c>
     </row>
     <row r="27">
@@ -5942,10 +5903,10 @@
         <v>Challenge 26</v>
       </c>
       <c r="B27" t="str">
-        <v>Defeat 10 Pokemon in Lush Jungle</v>
+        <v>Defeat 5 Pokemon in Brooklet Hill South</v>
       </c>
       <c r="C27" t="str">
-        <v>Captain Mallow</v>
+        <v>Captain Lana</v>
       </c>
     </row>
     <row r="28">
@@ -5953,10 +5914,10 @@
         <v>Challenge 27</v>
       </c>
       <c r="B28" t="str">
-        <v>Defeat Captain Mallow</v>
+        <v>Defeat Captain Lana</v>
       </c>
       <c r="C28" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Wela Volcano Park Main Area</v>
       </c>
     </row>
     <row r="29">
@@ -5964,10 +5925,10 @@
         <v>Challenge 28</v>
       </c>
       <c r="B29" t="str">
-        <v>Defeat 5 Pokemon in Diglett's Tunnel</v>
+        <v>Defeat 5 Pokemon in Wela Volcano Park Main Area</v>
       </c>
       <c r="C29" t="str">
-        <v>Route 9</v>
+        <v>Captain Kiawe</v>
       </c>
     </row>
     <row r="30">
@@ -5975,10 +5936,10 @@
         <v>Challenge 29</v>
       </c>
       <c r="B30" t="str">
-        <v>Defeat 5 Pokemon in Route 9</v>
+        <v>Defeat Captain Kiawe</v>
       </c>
       <c r="C30" t="str">
-        <v>Konikoni City</v>
+        <v>Route 7 Main Area</v>
       </c>
     </row>
     <row r="31">
@@ -5986,10 +5947,10 @@
         <v>Challenge 30</v>
       </c>
       <c r="B31" t="str">
-        <v>Defeat 5 Pokemon in Konikoni City</v>
+        <v>Defeat 5 Pokemon in Route 7 Main Area</v>
       </c>
       <c r="C31" t="str">
-        <v>Memorial Hill</v>
+        <v>Route 8 Main</v>
       </c>
     </row>
     <row r="32">
@@ -5997,10 +5958,10 @@
         <v>Challenge 31</v>
       </c>
       <c r="B32" t="str">
-        <v>Defeat 5 Pokemon in Memorial Hill</v>
+        <v>Defeat 5 Pokemon in Route 8 Main</v>
       </c>
       <c r="C32" t="str">
-        <v>Akala Outskirts</v>
+        <v>Route 8 Fossil Restoration Center Part 1</v>
       </c>
     </row>
     <row r="33">
@@ -6008,10 +5969,10 @@
         <v>Challenge 32</v>
       </c>
       <c r="B33" t="str">
-        <v>Defeat 5 Pokemon in Akala Outskirts</v>
+        <v>Defeat 5 Pokemon in Route 8 Fossil Restoration Center Part 1</v>
       </c>
       <c r="C33" t="str">
-        <v>Ruins of Life</v>
+        <v>Route 8 Fossil Restoration Center Part 2</v>
       </c>
     </row>
     <row r="34">
@@ -6019,10 +5980,10 @@
         <v>Challenge 33</v>
       </c>
       <c r="B34" t="str">
-        <v>Catch Tapu Lele in Ruins of Life</v>
+        <v>Defeat 5 Pokemon in Route 8 Fossil Restoration Center Part 2</v>
       </c>
       <c r="C34" t="str">
-        <v>Kahuna Olivia</v>
+        <v>Lush Jungle North</v>
       </c>
     </row>
     <row r="35">
@@ -6030,10 +5991,10 @@
         <v>Challenge 34</v>
       </c>
       <c r="B35" t="str">
-        <v>Defeat Kahuna Olivia</v>
+        <v>Defeat 5 Pokemon in Lush Jungle North</v>
       </c>
       <c r="C35" t="str">
-        <v>Hano Beach</v>
+        <v>Lush Jungle East Cave</v>
       </c>
     </row>
     <row r="36">
@@ -6041,10 +6002,10 @@
         <v>Challenge 35</v>
       </c>
       <c r="B36" t="str">
-        <v>Defeat 5 Pokemon in Hano Beach</v>
+        <v>Defeat 5 Pokemon in Lush Jungle East Cave</v>
       </c>
       <c r="C36" t="str">
-        <v>Aether Paradise</v>
+        <v>Captain Mallow</v>
       </c>
     </row>
     <row r="37">
@@ -6052,10 +6013,10 @@
         <v>Challenge 36</v>
       </c>
       <c r="B37" t="str">
-        <v>Defeat 5 Pokemon in Aether Paradise</v>
+        <v>Defeat Captain Mallow</v>
       </c>
       <c r="C37" t="str">
-        <v>Malie City</v>
+        <v>Diglett's Tunnel Main Area</v>
       </c>
     </row>
     <row r="38">
@@ -6063,10 +6024,10 @@
         <v>Challenge 37</v>
       </c>
       <c r="B38" t="str">
-        <v>Defeat 5 Pokemon in Malie City</v>
+        <v>Defeat 5 Pokemon in Diglett's Tunnel Main Area</v>
       </c>
       <c r="C38" t="str">
-        <v>Malie Garden</v>
+        <v>Route 9 Main Area</v>
       </c>
     </row>
     <row r="39">
@@ -6074,10 +6035,10 @@
         <v>Challenge 38</v>
       </c>
       <c r="B39" t="str">
-        <v>Defeat 5 Pokemon in Malie Garden</v>
+        <v>Defeat 5 Pokemon in Route 9 Main Area</v>
       </c>
       <c r="C39" t="str">
-        <v>Route 10</v>
+        <v>Konikoni City Main Area</v>
       </c>
     </row>
     <row r="40">
@@ -6085,10 +6046,10 @@
         <v>Challenge 39</v>
       </c>
       <c r="B40" t="str">
-        <v>Defeat 5 Pokemon in Route 10</v>
+        <v>Defeat 5 Pokemon in Konikoni City Main Area</v>
       </c>
       <c r="C40" t="str">
-        <v>Mount Hokulani</v>
+        <v>Memorial Hill Main</v>
       </c>
     </row>
     <row r="41">
@@ -6096,10 +6057,10 @@
         <v>Challenge 40</v>
       </c>
       <c r="B41" t="str">
-        <v>Defeat 10 Pokemon in Mount Hokulani</v>
+        <v>Defeat 5 Pokemon in Memorial Hill Main</v>
       </c>
       <c r="C41" t="str">
-        <v>Captain Sophocles</v>
+        <v>Akala Outskirts Main Area</v>
       </c>
     </row>
     <row r="42">
@@ -6107,10 +6068,10 @@
         <v>Challenge 41</v>
       </c>
       <c r="B42" t="str">
-        <v>Defeat Captain Sophocles</v>
+        <v>Defeat 5 Pokemon in Akala Outskirts Main Area</v>
       </c>
       <c r="C42" t="str">
-        <v>Route 11</v>
+        <v>Ruins of Life Special Encounter</v>
       </c>
     </row>
     <row r="43">
@@ -6118,10 +6079,10 @@
         <v>Challenge 42</v>
       </c>
       <c r="B43" t="str">
-        <v>Defeat 5 Pokemon in Route 11</v>
+        <v>Defeat 5 Pokemon in Ruins of Life Special Encounter</v>
       </c>
       <c r="C43" t="str">
-        <v>Route 12</v>
+        <v>Kahuna Olivia</v>
       </c>
     </row>
     <row r="44">
@@ -6129,10 +6090,10 @@
         <v>Challenge 43</v>
       </c>
       <c r="B44" t="str">
-        <v>Defeat 5 Pokemon in Route 12</v>
+        <v>Defeat Kahuna Olivia</v>
       </c>
       <c r="C44" t="str">
-        <v>Blush Mountain</v>
+        <v>Hano Beach Main Area</v>
       </c>
     </row>
     <row r="45">
@@ -6140,10 +6101,10 @@
         <v>Challenge 44</v>
       </c>
       <c r="B45" t="str">
-        <v>Defeat 5 Pokemon in Blush Mountain</v>
+        <v>Defeat 5 Pokemon in Hano Beach Main Area</v>
       </c>
       <c r="C45" t="str">
-        <v>Route 13</v>
+        <v>Aether Paradise Special Encounter</v>
       </c>
     </row>
     <row r="46">
@@ -6151,10 +6112,10 @@
         <v>Challenge 45</v>
       </c>
       <c r="B46" t="str">
-        <v>Defeat 5 Pokemon in Route 13</v>
+        <v>Defeat 5 Pokemon in Aether Paradise Special Encounter</v>
       </c>
       <c r="C46" t="str">
-        <v>Haina Desert</v>
+        <v>Malie City Outer Cape</v>
       </c>
     </row>
     <row r="47">
@@ -6162,10 +6123,10 @@
         <v>Challenge 46</v>
       </c>
       <c r="B47" t="str">
-        <v>Defeat 5 Pokemon in Haina Desert</v>
+        <v>Defeat 5 Pokemon in Malie City Outer Cape</v>
       </c>
       <c r="C47" t="str">
-        <v>Ruins of Abundance</v>
+        <v>Malie Garden Main Area</v>
       </c>
     </row>
     <row r="48">
@@ -6173,10 +6134,10 @@
         <v>Challenge 47</v>
       </c>
       <c r="B48" t="str">
-        <v>Catch Tapu Bulu in Ruins of Abundance</v>
+        <v>Defeat 5 Pokemon in Malie Garden Main Area</v>
       </c>
       <c r="C48" t="str">
-        <v>Tapu Village</v>
+        <v>Route 10 Main Area</v>
       </c>
     </row>
     <row r="49">
@@ -6184,10 +6145,10 @@
         <v>Challenge 48</v>
       </c>
       <c r="B49" t="str">
-        <v>Defeat 5 Pokemon in Tapu Village</v>
+        <v>Defeat 5 Pokemon in Route 10 Main Area</v>
       </c>
       <c r="C49" t="str">
-        <v>Route 14</v>
+        <v>Mount Hokulani East</v>
       </c>
     </row>
     <row r="50">
@@ -6195,10 +6156,10 @@
         <v>Challenge 49</v>
       </c>
       <c r="B50" t="str">
-        <v>Defeat 5 Pokemon in Route 14</v>
+        <v>Defeat 5 Pokemon in Mount Hokulani East</v>
       </c>
       <c r="C50" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Captain Sophocles</v>
       </c>
     </row>
     <row r="51">
@@ -6206,10 +6167,10 @@
         <v>Challenge 50</v>
       </c>
       <c r="B51" t="str">
-        <v>Defeat 10 Pokemon in Thrifty Megamart</v>
+        <v>Defeat Captain Sophocles</v>
       </c>
       <c r="C51" t="str">
-        <v>Captain Acerola</v>
+        <v>Route 11 Main Area</v>
       </c>
     </row>
     <row r="52">
@@ -6217,10 +6178,10 @@
         <v>Challenge 51</v>
       </c>
       <c r="B52" t="str">
-        <v>Defeat Captain Acerola</v>
+        <v>Defeat 5 Pokemon in Route 11 Main Area</v>
       </c>
       <c r="C52" t="str">
-        <v>Route 15</v>
+        <v>Route 12 Main Area</v>
       </c>
     </row>
     <row r="53">
@@ -6228,10 +6189,10 @@
         <v>Challenge 52</v>
       </c>
       <c r="B53" t="str">
-        <v>Defeat 5 Pokemon in Route 15</v>
+        <v>Defeat 5 Pokemon in Route 12 Main Area</v>
       </c>
       <c r="C53" t="str">
-        <v>Route 16</v>
+        <v>Blush Mountain Main Area</v>
       </c>
     </row>
     <row r="54">
@@ -6239,10 +6200,10 @@
         <v>Challenge 53</v>
       </c>
       <c r="B54" t="str">
-        <v>Defeat 5 Pokemon in Route 16</v>
+        <v>Defeat 5 Pokemon in Blush Mountain Main Area</v>
       </c>
       <c r="C54" t="str">
-        <v>Route 17</v>
+        <v>Route 13 Main Area</v>
       </c>
     </row>
     <row r="55">
@@ -6250,10 +6211,10 @@
         <v>Challenge 54</v>
       </c>
       <c r="B55" t="str">
-        <v>Defeat 10 Pokemon in Route 17</v>
+        <v>Defeat 5 Pokemon in Route 13 Main Area</v>
       </c>
       <c r="C55" t="str">
-        <v>Kahuna Nanu</v>
+        <v>Haina Desert Main Area</v>
       </c>
     </row>
     <row r="56">
@@ -6261,10 +6222,10 @@
         <v>Challenge 55</v>
       </c>
       <c r="B56" t="str">
-        <v>Defeat Kahuna Nanu</v>
+        <v>Defeat 5 Pokemon in Haina Desert Main Area</v>
       </c>
       <c r="C56" t="str">
-        <v>Seafolk Village</v>
+        <v>Ruins of Abundance Special Encounter</v>
       </c>
     </row>
     <row r="57">
@@ -6272,10 +6233,10 @@
         <v>Challenge 56</v>
       </c>
       <c r="B57" t="str">
-        <v>Defeat 5 Pokemon in Seafolk Village</v>
+        <v>Defeat 5 Pokemon in Ruins of Abundance Special Encounter</v>
       </c>
       <c r="C57" t="str">
-        <v>Poni Wilds</v>
+        <v>Tapu Village Main Area</v>
       </c>
     </row>
     <row r="58">
@@ -6283,10 +6244,10 @@
         <v>Challenge 57</v>
       </c>
       <c r="B58" t="str">
-        <v>Defeat 5 Pokemon in Poni Wilds</v>
+        <v>Defeat 5 Pokemon in Tapu Village Main Area</v>
       </c>
       <c r="C58" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Route 14 Main Area</v>
       </c>
     </row>
     <row r="59">
@@ -6294,10 +6255,10 @@
         <v>Challenge 58</v>
       </c>
       <c r="B59" t="str">
-        <v>Defeat 5 Pokemon in Poni Breaker Coast</v>
+        <v>Defeat 5 Pokemon in Route 14 Main Area</v>
       </c>
       <c r="C59" t="str">
-        <v>Ruins of Hope</v>
+        <v>Thrifty Megamart Abandoned Site</v>
       </c>
     </row>
     <row r="60">
@@ -6305,10 +6266,10 @@
         <v>Challenge 59</v>
       </c>
       <c r="B60" t="str">
-        <v>Catch Tapu Fini in Ruins of Hope</v>
+        <v>Defeat 5 Pokemon in Thrifty Megamart Abandoned Site</v>
       </c>
       <c r="C60" t="str">
-        <v>Exeggutor Island</v>
+        <v>Captain Acerola</v>
       </c>
     </row>
     <row r="61">
@@ -6316,10 +6277,10 @@
         <v>Challenge 60</v>
       </c>
       <c r="B61" t="str">
-        <v>Defeat 5 Pokemon in Exeggutor Island</v>
+        <v>Defeat Captain Acerola</v>
       </c>
       <c r="C61" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Route 15 Main Area</v>
       </c>
     </row>
     <row r="62">
@@ -6327,10 +6288,10 @@
         <v>Challenge 61</v>
       </c>
       <c r="B62" t="str">
-        <v>Defeat 10 Pokemon in Vast Poni Canyon</v>
+        <v>Defeat 5 Pokemon in Route 15 Main Area</v>
       </c>
       <c r="C62" t="str">
-        <v>Captain Kommo-o</v>
+        <v>Route 16 Main Area</v>
       </c>
     </row>
     <row r="63">
@@ -6338,10 +6299,10 @@
         <v>Challenge 62</v>
       </c>
       <c r="B63" t="str">
-        <v>Defeat Captain Kommo-o</v>
+        <v>Defeat 5 Pokemon in Route 16 Main Area</v>
       </c>
       <c r="C63" t="str">
-        <v>Altar of the Sunne/Moone</v>
+        <v>Route 17 Northeast</v>
       </c>
     </row>
     <row r="64">
@@ -6349,10 +6310,10 @@
         <v>Challenge 63</v>
       </c>
       <c r="B64" t="str">
-        <v>Catch Cosmog in Altar of the Sunne/Moone</v>
+        <v>Defeat 5 Pokemon in Route 17 Northeast</v>
       </c>
       <c r="C64" t="str">
-        <v>Captain Mina</v>
+        <v>Kahuna Nanu</v>
       </c>
     </row>
     <row r="65">
@@ -6360,10 +6321,10 @@
         <v>Challenge 64</v>
       </c>
       <c r="B65" t="str">
-        <v>Defeat Captain Mina</v>
+        <v>Defeat Kahuna Nanu</v>
       </c>
       <c r="C65" t="str">
-        <v>Kahuna Hapu</v>
+        <v>Seafolk Village Main</v>
       </c>
     </row>
     <row r="66">
@@ -6371,10 +6332,10 @@
         <v>Challenge 65</v>
       </c>
       <c r="B66" t="str">
-        <v>Defeat Kahuna Hapu</v>
+        <v>Defeat 5 Pokemon in Seafolk Village Main</v>
       </c>
       <c r="C66" t="str">
-        <v>Mount Lanakila</v>
+        <v>Poni Wilds Main Area</v>
       </c>
     </row>
     <row r="67">
@@ -6382,10 +6343,10 @@
         <v>Challenge 66</v>
       </c>
       <c r="B67" t="str">
-        <v>Defeat 15 Pokemon in Mount Lanakila</v>
+        <v>Defeat 5 Pokemon in Poni Wilds Main Area</v>
       </c>
       <c r="C67" t="str">
-        <v>Alola Pokemon League</v>
+        <v>Poni Breaker Coast Main Area</v>
       </c>
     </row>
     <row r="68">
@@ -6393,114 +6354,763 @@
         <v>Challenge 67</v>
       </c>
       <c r="B68" t="str">
-        <v>Defeat Alola Pokemon League</v>
+        <v>Defeat 5 Pokemon in Poni Breaker Coast Main Area</v>
       </c>
       <c r="C68" t="str">
-        <v>Champion Hau</v>
+        <v>Ruins of Hope Special Encounter</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Extra Challenge $1-1</v>
+        <v>Challenge 68</v>
       </c>
       <c r="B69" t="str">
-        <v>Defeat Champion Hau</v>
+        <v>Defeat 5 Pokemon in Ruins of Hope Special Encounter</v>
       </c>
       <c r="C69" t="str">
-        <v>Ultra Space Wilds Access</v>
+        <v>Exeggutor Island Main Area</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Extra Challenge $1-2</v>
+        <v>Challenge 69</v>
       </c>
       <c r="B70" t="str">
-        <v>Catch 5 Ultra Beasts</v>
+        <v>Defeat 5 Pokemon in Exeggutor Island Main Area</v>
       </c>
       <c r="C70" t="str">
-        <v>Ultra Space Core</v>
+        <v>Vast Poni Canyon Outside</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Extra Challenge $1-3</v>
+        <v>Challenge 70</v>
       </c>
       <c r="B71" t="str">
-        <v>Defeat Necrozma</v>
+        <v>Defeat 5 Pokemon in Vast Poni Canyon Outside</v>
       </c>
       <c r="C71" t="str">
-        <v>Ultra Space Master Ribbon</v>
+        <v>Vast Poni Canyon Inside</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Extra Challenge $2-1</v>
+        <v>Challenge 71</v>
       </c>
       <c r="B72" t="str">
-        <v>Complete Pokedex 50%</v>
+        <v>Defeat 5 Pokemon in Vast Poni Canyon Inside</v>
       </c>
       <c r="C72" t="str">
-        <v>Event: Magearna</v>
+        <v>Vast Poni Canyon Northwest (Hidden Area)</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Extra Challenge $2-2</v>
+        <v>Challenge 72</v>
       </c>
       <c r="B73" t="str">
-        <v>Complete Pokedex 75%</v>
+        <v>Defeat 5 Pokemon in Vast Poni Canyon Northwest (Hidden Area)</v>
       </c>
       <c r="C73" t="str">
-        <v>Event: Marshadow</v>
+        <v>Captain Kommo-o</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Extra Challenge $2-3</v>
+        <v>Challenge 73</v>
       </c>
       <c r="B74" t="str">
-        <v>Complete Pokedex 100%</v>
+        <v>Defeat Captain Kommo-o</v>
       </c>
       <c r="C74" t="str">
-        <v>Event: Zeraora</v>
+        <v>Altar of the Sunne/Moone Special Encounter</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Extra Challenge $3-1</v>
+        <v>Challenge 74</v>
       </c>
       <c r="B75" t="str">
-        <v>Catch 100 Pokemon</v>
+        <v>Defeat 5 Pokemon in Altar of the Sunne/Moone Special Encounter</v>
       </c>
       <c r="C75" t="str">
-        <v>Poni Grove</v>
+        <v>Captain Mina</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Extra Challenge $3-2</v>
+        <v>Challenge 75</v>
       </c>
       <c r="B76" t="str">
-        <v>Defeat 15 Pokemon in Poni Grove</v>
+        <v>Defeat Captain Mina</v>
       </c>
       <c r="C76" t="str">
-        <v>Poni Plains</v>
+        <v>Kahuna Hapu</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
+        <v>Challenge 76</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Defeat Kahuna Hapu</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Mount Lanakila Cave</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Challenge 77</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Defeat 5 Pokemon in Mount Lanakila Cave</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Alola Pokemon League</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Challenge 78</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Defeat Alola Pokemon League</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Champion Hau</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>Extra Challenge $1-1</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Collect 10 Zygarde Cells</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Zygarde 10% Forme</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Extra Challenge $1-2</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Collect 50 Zygarde Cells</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Zygarde 50% Forme</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>Extra Challenge $1-3</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Collect 100 Zygarde Cells</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Zygarde Complete Forme</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Extra Challenge $2-1</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Collect 20 Totem Stickers</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Totem Gumshoos/Raticate</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Extra Challenge $2-2</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Collect 50 Totem Stickers</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Totem Lurantis/Salazzle</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Extra Challenge $2-3</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Collect 100 Totem Stickers</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Totem Kommo-o/Ribombee</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>Extra Challenge $3-1</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Catch Tapu Koko</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Electric Seed</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>Extra Challenge $3-2</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Catch Tapu Lele</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Psychic Seed</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
         <v>Extra Challenge $3-3</v>
       </c>
-      <c r="B77" t="str">
-        <v>Defeat 15 Pokemon in Poni Plains</v>
-      </c>
-      <c r="C77" t="str">
-        <v>Resolution Cave</v>
+      <c r="B88" t="str">
+        <v>Catch Tapu Bulu</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Grassy Seed</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Extra Challenge $3-4</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Catch Tapu Fini</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Misty Seed</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Extra Challenge $4-1</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Defeat Champion Hau</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Poni Grove Main Area</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>Extra Challenge $4-2</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Defeat 15 Pokemon in Poni Grove Main Area</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Poni Plains Center</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Extra Challenge $4-3</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Defeat 15 Pokemon in Poni Plains Center</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Resolution Cave Main Area</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Extra Challenge $4-4</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Defeat 15 Pokemon in Resolution Cave Main Area</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Ultra Space Wilds</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C77"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C93"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D33"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Pokemon Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Pokemon Type</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Path to be include</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Obtained?</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Pikachu</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Electric</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Route 1</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Alolan Raichu</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Electric/Psychic</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Route 1</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Yes (Evolution)</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Oricorio</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Fire/Electric/Psychic/Ghost</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Route 3</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Lycanroc</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Rock</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Ten Carat Hill</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Staryu</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Water</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Route 7</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Pyukumuku</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Water</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Route 7</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Bounsweet</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Lush Jungle</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Oranguru</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Normal/Psychic</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Lush Jungle</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Passimian</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Fighting</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Lush Jungle</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Corsola</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Water/Rock</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Route 9</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Mareanie</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Poison/Water</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Route 9</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Minior</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Rock/Flying</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Route 13</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Bruxish</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Water/Psychic</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Route 14</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Sandygast</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Ghost/Ground</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Route 15</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Klefki</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Steel/Fairy</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Route 16</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Crabominable</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Fighting/Ice</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Mount Lanakila</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Type: Null</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Aether Paradise</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Silvally</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Aether Paradise</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Yes (Evolution)</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Ditto</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Aether Paradise</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Porygon</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Aether Paradise</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Tapu Koko</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Electric/Fairy</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Ruins of Conflict</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Tapu Lele</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Psychic/Fairy</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Ruins of Life</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Tapu Bulu</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Grass/Fairy</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Ruins of Abundance</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Tapu Fini</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Water/Fairy</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Ruins of Hope</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Cosmog</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Psychic</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Altar of the Sunne/Moone</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Cosmoem</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Psychic</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Altar of the Sunne/Moone</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Yes (Evolution)</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Poipole</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Poison</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Ultra Space Wilds</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Naganadel</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Poison/Dragon</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Ultra Space Wilds</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Yes (Evolution)</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Xurkitree</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Electric</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Ultra Space Wilds</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Magearna</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Steel/Fairy</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Event: Magearna</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Marshadow</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Ghost/Fighting</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Event: Marshadow</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Zeraora</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Electric</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Event: Zeraora</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Yes (Added)</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D33"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Alola_Paths_and_Challenges.xlsx
+++ b/Alola_Paths_and_Challenges.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F260"/>
+  <dimension ref="A1:F247"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -655,7 +655,7 @@
         <v>Inkay</v>
       </c>
       <c r="E13" t="str">
-        <v>4-9</v>
+        <v>5-10</v>
       </c>
       <c r="F13" t="str">
         <v>20.00%</v>
@@ -675,7 +675,7 @@
         <v>Slowpoke</v>
       </c>
       <c r="E14" t="str">
-        <v>4-9</v>
+        <v>5-10</v>
       </c>
       <c r="F14" t="str">
         <v>20.00%</v>
@@ -695,7 +695,7 @@
         <v>Alolan Meowth</v>
       </c>
       <c r="E15" t="str">
-        <v>4-9</v>
+        <v>5-10</v>
       </c>
       <c r="F15" t="str">
         <v>20.00%</v>
@@ -715,7 +715,7 @@
         <v>Tentacool</v>
       </c>
       <c r="E16" t="str">
-        <v>4-9</v>
+        <v>5-10</v>
       </c>
       <c r="F16" t="str">
         <v>20.00%</v>
@@ -735,7 +735,7 @@
         <v>Finneon</v>
       </c>
       <c r="E17" t="str">
-        <v>4-9</v>
+        <v>5-10</v>
       </c>
       <c r="F17" t="str">
         <v>20.00%</v>
@@ -746,19 +746,19 @@
         <v>4</v>
       </c>
       <c r="B18" t="str">
-        <v>Route 1</v>
+        <v>Hau'oli City</v>
       </c>
       <c r="C18" t="str">
-        <v>South</v>
+        <v>Shopping District</v>
       </c>
       <c r="D18" t="str">
-        <v>Bonsly</v>
+        <v>Furfrou</v>
       </c>
       <c r="E18" t="str">
-        <v>5-10</v>
+        <v>6-11</v>
       </c>
       <c r="F18" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="19">
@@ -766,19 +766,19 @@
         <v>4</v>
       </c>
       <c r="B19" t="str">
-        <v>Route 1</v>
+        <v>Hau'oli City</v>
       </c>
       <c r="C19" t="str">
-        <v>South</v>
+        <v>Shopping District</v>
       </c>
       <c r="D19" t="str">
-        <v>Munchlax</v>
+        <v>Hypno</v>
       </c>
       <c r="E19" t="str">
-        <v>5-10</v>
+        <v>6-11</v>
       </c>
       <c r="F19" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="20">
@@ -786,199 +786,199 @@
         <v>4</v>
       </c>
       <c r="B20" t="str">
-        <v>Route 1</v>
+        <v>Hau'oli City</v>
       </c>
       <c r="C20" t="str">
-        <v>South</v>
+        <v>Shopping District</v>
       </c>
       <c r="D20" t="str">
-        <v>Rockruff</v>
+        <v>Abra</v>
       </c>
       <c r="E20" t="str">
-        <v>5-10</v>
+        <v>6-11</v>
       </c>
       <c r="F20" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B21" t="str">
-        <v>Route 1</v>
+        <v>Hau'oli City</v>
       </c>
       <c r="C21" t="str">
-        <v>Trainers' School</v>
+        <v>Shopping District</v>
       </c>
       <c r="D21" t="str">
-        <v>Zorua</v>
+        <v>Mime Jr.</v>
       </c>
       <c r="E21" t="str">
         <v>6-11</v>
       </c>
       <c r="F21" t="str">
-        <v>100.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B22" t="str">
         <v>Hau'oli City</v>
       </c>
       <c r="C22" t="str">
-        <v>Beachfront</v>
+        <v>Shopping District</v>
       </c>
       <c r="D22" t="str">
-        <v>Luvdisc</v>
+        <v>Bewear</v>
       </c>
       <c r="E22" t="str">
-        <v>7-12</v>
+        <v>6-11</v>
       </c>
       <c r="F22" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23" t="str">
-        <v>Hau'oli City</v>
+        <v>Route 2</v>
       </c>
       <c r="C23" t="str">
-        <v>Beachfront</v>
+        <v>North</v>
       </c>
       <c r="D23" t="str">
-        <v>Corsola</v>
+        <v>Drowzee</v>
       </c>
       <c r="E23" t="str">
         <v>7-12</v>
       </c>
       <c r="F23" t="str">
-        <v>25.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B24" t="str">
-        <v>Hau'oli City</v>
+        <v>Route 2</v>
       </c>
       <c r="C24" t="str">
-        <v>Beachfront</v>
+        <v>North</v>
       </c>
       <c r="D24" t="str">
-        <v>Remoraid</v>
+        <v>Makuhita</v>
       </c>
       <c r="E24" t="str">
         <v>7-12</v>
       </c>
       <c r="F24" t="str">
-        <v>25.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B25" t="str">
-        <v>Hau'oli City</v>
+        <v>Route 2</v>
       </c>
       <c r="C25" t="str">
-        <v>Beachfront</v>
+        <v>North</v>
       </c>
       <c r="D25" t="str">
-        <v>Clamperl</v>
+        <v>Spearow</v>
       </c>
       <c r="E25" t="str">
         <v>7-12</v>
       </c>
       <c r="F25" t="str">
-        <v>25.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B26" t="str">
-        <v>Hau'oli City</v>
+        <v>Route 2</v>
       </c>
       <c r="C26" t="str">
-        <v>Shopping District</v>
+        <v>North</v>
       </c>
       <c r="D26" t="str">
-        <v>Furfrou</v>
+        <v>Ekans</v>
       </c>
       <c r="E26" t="str">
-        <v>8-13</v>
+        <v>7-12</v>
       </c>
       <c r="F26" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B27" t="str">
-        <v>Hau'oli City</v>
+        <v>Route 2</v>
       </c>
       <c r="C27" t="str">
-        <v>Shopping District</v>
+        <v>North</v>
       </c>
       <c r="D27" t="str">
-        <v>Hypno</v>
+        <v>Growlithe</v>
       </c>
       <c r="E27" t="str">
-        <v>8-13</v>
+        <v>7-12</v>
       </c>
       <c r="F27" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B28" t="str">
-        <v>Hau'oli City</v>
+        <v>Route 2</v>
       </c>
       <c r="C28" t="str">
-        <v>Shopping District</v>
+        <v>North</v>
       </c>
       <c r="D28" t="str">
-        <v>Abra</v>
+        <v>Smeargle</v>
       </c>
       <c r="E28" t="str">
-        <v>8-13</v>
+        <v>7-12</v>
       </c>
       <c r="F28" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B29" t="str">
-        <v>Hau'oli City</v>
+        <v>Captain Ilima</v>
       </c>
       <c r="C29" t="str">
-        <v>Shopping District</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D29" t="str">
-        <v>Mime Jr.</v>
+        <v>Boss</v>
       </c>
       <c r="E29" t="str">
-        <v>8-13</v>
+        <v>9-14</v>
       </c>
       <c r="F29" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="30">
@@ -986,876 +986,876 @@
         <v>7</v>
       </c>
       <c r="B30" t="str">
-        <v>Hau'oli City</v>
+        <v>Hau'oli Cemetery</v>
       </c>
       <c r="C30" t="str">
-        <v>Shopping District</v>
+        <v>Main Area</v>
       </c>
       <c r="D30" t="str">
-        <v>Bewear</v>
+        <v>Gastly</v>
       </c>
       <c r="E30" t="str">
-        <v>8-13</v>
+        <v>10-15</v>
       </c>
       <c r="F30" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B31" t="str">
-        <v>Route 2</v>
+        <v>Hau'oli Cemetery</v>
       </c>
       <c r="C31" t="str">
-        <v>Main</v>
+        <v>Main Area</v>
       </c>
       <c r="D31" t="str">
-        <v>Machop</v>
+        <v>Drifloon</v>
       </c>
       <c r="E31" t="str">
-        <v>9-14</v>
+        <v>10-15</v>
       </c>
       <c r="F31" t="str">
-        <v>50.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B32" t="str">
-        <v>Route 2</v>
+        <v>Hau'oli Cemetery</v>
       </c>
       <c r="C32" t="str">
-        <v>Main</v>
+        <v>Main Area</v>
       </c>
       <c r="D32" t="str">
-        <v>Hawlucha</v>
+        <v>Murkrow</v>
       </c>
       <c r="E32" t="str">
-        <v>9-14</v>
+        <v>10-15</v>
       </c>
       <c r="F32" t="str">
-        <v>50.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B33" t="str">
-        <v>Route 2</v>
+        <v>Hau'oli Cemetery</v>
       </c>
       <c r="C33" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D33" t="str">
-        <v>Drowzee</v>
+        <v>Misdreavus</v>
       </c>
       <c r="E33" t="str">
         <v>10-15</v>
       </c>
       <c r="F33" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B34" t="str">
-        <v>Route 2</v>
+        <v>Ten Carat Hill</v>
       </c>
       <c r="C34" t="str">
-        <v>North</v>
+        <v>Farthest Hollow</v>
       </c>
       <c r="D34" t="str">
-        <v>Makuhita</v>
+        <v>Roggenrola</v>
       </c>
       <c r="E34" t="str">
-        <v>10-15</v>
+        <v>14-19</v>
       </c>
       <c r="F34" t="str">
-        <v>16.67%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B35" t="str">
-        <v>Route 2</v>
+        <v>Ten Carat Hill</v>
       </c>
       <c r="C35" t="str">
-        <v>North</v>
+        <v>Farthest Hollow</v>
       </c>
       <c r="D35" t="str">
-        <v>Spearow</v>
+        <v>Carbink</v>
       </c>
       <c r="E35" t="str">
-        <v>10-15</v>
+        <v>14-19</v>
       </c>
       <c r="F35" t="str">
-        <v>16.67%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B36" t="str">
-        <v>Route 2</v>
+        <v>Ten Carat Hill</v>
       </c>
       <c r="C36" t="str">
-        <v>North</v>
+        <v>Farthest Hollow</v>
       </c>
       <c r="D36" t="str">
-        <v>Ekans</v>
+        <v>Spinda</v>
       </c>
       <c r="E36" t="str">
-        <v>10-15</v>
+        <v>14-19</v>
       </c>
       <c r="F36" t="str">
-        <v>16.67%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B37" t="str">
-        <v>Route 2</v>
+        <v>Ten Carat Hill</v>
       </c>
       <c r="C37" t="str">
-        <v>North</v>
+        <v>Farthest Hollow</v>
       </c>
       <c r="D37" t="str">
-        <v>Growlithe</v>
+        <v>Necrozma</v>
       </c>
       <c r="E37" t="str">
-        <v>10-15</v>
+        <v>14-19</v>
       </c>
       <c r="F37" t="str">
-        <v>16.67%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B38" t="str">
-        <v>Route 2</v>
+        <v>Ten Carat Hill</v>
       </c>
       <c r="C38" t="str">
-        <v>North</v>
+        <v>Farthest Hollow</v>
       </c>
       <c r="D38" t="str">
-        <v>Smeargle</v>
+        <v>Mawile</v>
       </c>
       <c r="E38" t="str">
-        <v>10-15</v>
+        <v>14-19</v>
       </c>
       <c r="F38" t="str">
-        <v>16.67%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B39" t="str">
-        <v>Captain Ilima</v>
+        <v>Ten Carat Hill</v>
       </c>
       <c r="C39" t="str">
-        <v>Boss Battle</v>
+        <v>Farthest Hollow</v>
       </c>
       <c r="D39" t="str">
-        <v>Boss</v>
+        <v>Lycanroc</v>
       </c>
       <c r="E39" t="str">
-        <v>11-16</v>
+        <v>14-19</v>
       </c>
       <c r="F39" t="str">
-        <v>-</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B40" t="str">
-        <v>Hau'oli Cemetery</v>
+        <v>Ten Carat Hill</v>
       </c>
       <c r="C40" t="str">
-        <v>Main Area</v>
+        <v>Farthest Hollow</v>
       </c>
       <c r="D40" t="str">
-        <v>Gastly</v>
+        <v>Marshadow</v>
       </c>
       <c r="E40" t="str">
-        <v>12-17</v>
+        <v>14-19</v>
       </c>
       <c r="F40" t="str">
-        <v>25.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B41" t="str">
-        <v>Hau'oli Cemetery</v>
+        <v>Seaward Cave</v>
       </c>
       <c r="C41" t="str">
         <v>Main Area</v>
       </c>
       <c r="D41" t="str">
-        <v>Drifloon</v>
+        <v>Barboach</v>
       </c>
       <c r="E41" t="str">
-        <v>12-17</v>
+        <v>15-20</v>
       </c>
       <c r="F41" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B42" t="str">
-        <v>Hau'oli Cemetery</v>
+        <v>Seaward Cave</v>
       </c>
       <c r="C42" t="str">
         <v>Main Area</v>
       </c>
       <c r="D42" t="str">
-        <v>Murkrow</v>
+        <v>Smoochum</v>
       </c>
       <c r="E42" t="str">
-        <v>12-17</v>
+        <v>15-20</v>
       </c>
       <c r="F42" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B43" t="str">
-        <v>Hau'oli Cemetery</v>
+        <v>Seaward Cave</v>
       </c>
       <c r="C43" t="str">
         <v>Main Area</v>
       </c>
       <c r="D43" t="str">
-        <v>Misdreavus</v>
+        <v>Seel</v>
       </c>
       <c r="E43" t="str">
-        <v>12-17</v>
+        <v>15-20</v>
       </c>
       <c r="F43" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B44" t="str">
-        <v>Verdant Cavern</v>
+        <v>Route 3</v>
       </c>
       <c r="C44" t="str">
-        <v>Trial Site</v>
+        <v>North</v>
       </c>
       <c r="D44" t="str">
-        <v>Pheromosa</v>
+        <v>Mankey</v>
       </c>
       <c r="E44" t="str">
-        <v>14-19</v>
+        <v>17-22</v>
       </c>
       <c r="F44" t="str">
-        <v>100.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B45" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Route 3</v>
       </c>
       <c r="C45" t="str">
-        <v>Inside</v>
+        <v>North</v>
       </c>
       <c r="D45" t="str">
-        <v>Mawile</v>
+        <v>Delibird</v>
       </c>
       <c r="E45" t="str">
-        <v>15-20</v>
+        <v>17-22</v>
       </c>
       <c r="F45" t="str">
-        <v>50.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B46" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Route 3</v>
       </c>
       <c r="C46" t="str">
-        <v>Inside</v>
+        <v>North</v>
       </c>
       <c r="D46" t="str">
-        <v>Lycanroc</v>
+        <v>Bagon</v>
       </c>
       <c r="E46" t="str">
-        <v>15-20</v>
+        <v>17-22</v>
       </c>
       <c r="F46" t="str">
-        <v>50.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B47" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Route 3</v>
       </c>
       <c r="C47" t="str">
-        <v>Farthest Hollow</v>
+        <v>North</v>
       </c>
       <c r="D47" t="str">
-        <v>Roggenrola</v>
+        <v>Oricorio</v>
       </c>
       <c r="E47" t="str">
-        <v>16-21</v>
+        <v>17-22</v>
       </c>
       <c r="F47" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B48" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Route 3</v>
       </c>
       <c r="C48" t="str">
-        <v>Farthest Hollow</v>
+        <v>North</v>
       </c>
       <c r="D48" t="str">
-        <v>Carbink</v>
+        <v>Igglybuff</v>
       </c>
       <c r="E48" t="str">
-        <v>16-21</v>
+        <v>17-22</v>
       </c>
       <c r="F48" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B49" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Kahuna Hala</v>
       </c>
       <c r="C49" t="str">
-        <v>Farthest Hollow</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D49" t="str">
-        <v>Spinda</v>
+        <v>Boss</v>
       </c>
       <c r="E49" t="str">
-        <v>16-21</v>
+        <v>18-23</v>
       </c>
       <c r="F49" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B50" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C50" t="str">
-        <v>Farthest Hollow</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D50" t="str">
-        <v>Necrozma</v>
+        <v>Vikavolt</v>
       </c>
       <c r="E50" t="str">
-        <v>16-21</v>
+        <v>19-24</v>
       </c>
       <c r="F50" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B51" t="str">
-        <v>Seaward Cave</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C51" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D51" t="str">
-        <v>Barboach</v>
+        <v>Ribombee</v>
       </c>
       <c r="E51" t="str">
-        <v>17-22</v>
+        <v>19-24</v>
       </c>
       <c r="F51" t="str">
-        <v>33.33%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B52" t="str">
-        <v>Seaward Cave</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C52" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D52" t="str">
-        <v>Smoochum</v>
+        <v>Araquanid</v>
       </c>
       <c r="E52" t="str">
-        <v>17-22</v>
+        <v>19-24</v>
       </c>
       <c r="F52" t="str">
-        <v>33.33%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B53" t="str">
-        <v>Seaward Cave</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C53" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D53" t="str">
-        <v>Seel</v>
+        <v>Lurantis</v>
       </c>
       <c r="E53" t="str">
-        <v>17-22</v>
+        <v>19-24</v>
       </c>
       <c r="F53" t="str">
-        <v>33.33%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B54" t="str">
-        <v>Route 3</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C54" t="str">
-        <v>North</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D54" t="str">
-        <v>Mankey</v>
+        <v>Salazzle</v>
       </c>
       <c r="E54" t="str">
-        <v>18-23</v>
+        <v>19-24</v>
       </c>
       <c r="F54" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B55" t="str">
-        <v>Route 3</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C55" t="str">
-        <v>North</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D55" t="str">
-        <v>Delibird</v>
+        <v>Alolan Marowak</v>
       </c>
       <c r="E55" t="str">
-        <v>18-23</v>
+        <v>19-24</v>
       </c>
       <c r="F55" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B56" t="str">
-        <v>Route 3</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C56" t="str">
-        <v>North</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D56" t="str">
-        <v>Bagon</v>
+        <v>Kommo-o</v>
       </c>
       <c r="E56" t="str">
-        <v>18-23</v>
+        <v>19-24</v>
       </c>
       <c r="F56" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B57" t="str">
-        <v>Route 3</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C57" t="str">
-        <v>North</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D57" t="str">
-        <v>Oricorio</v>
+        <v>Mimikyu</v>
       </c>
       <c r="E57" t="str">
-        <v>18-23</v>
+        <v>19-24</v>
       </c>
       <c r="F57" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B58" t="str">
-        <v>Ruins of Conflict</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C58" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D58" t="str">
-        <v>Tapu Koko</v>
+        <v>Poliwhirl</v>
       </c>
       <c r="E58" t="str">
         <v>19-24</v>
       </c>
       <c r="F58" t="str">
-        <v>100.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B59" t="str">
-        <v>Kahuna Hala</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C59" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area Part 2</v>
       </c>
       <c r="D59" t="str">
-        <v>Boss</v>
+        <v>Ditto</v>
       </c>
       <c r="E59" t="str">
-        <v>20-25</v>
+        <v>19-24</v>
       </c>
       <c r="F59" t="str">
-        <v>-</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B60" t="str">
-        <v>Heahea Beach</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C60" t="str">
         <v>Main Area</v>
       </c>
       <c r="D60" t="str">
-        <v>Vikavolt</v>
+        <v>Eevee</v>
       </c>
       <c r="E60" t="str">
         <v>21-26</v>
       </c>
       <c r="F60" t="str">
-        <v>12.50%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B61" t="str">
-        <v>Heahea Beach</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C61" t="str">
         <v>Main Area</v>
       </c>
       <c r="D61" t="str">
-        <v>Ribombee</v>
+        <v>Mareep</v>
       </c>
       <c r="E61" t="str">
         <v>21-26</v>
       </c>
       <c r="F61" t="str">
-        <v>12.50%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B62" t="str">
-        <v>Heahea Beach</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C62" t="str">
         <v>Main Area</v>
       </c>
       <c r="D62" t="str">
-        <v>Araquanid</v>
+        <v>Tauros</v>
       </c>
       <c r="E62" t="str">
         <v>21-26</v>
       </c>
       <c r="F62" t="str">
-        <v>12.50%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B63" t="str">
-        <v>Heahea Beach</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C63" t="str">
         <v>Main Area</v>
       </c>
       <c r="D63" t="str">
-        <v>Lurantis</v>
+        <v>Miltank</v>
       </c>
       <c r="E63" t="str">
         <v>21-26</v>
       </c>
       <c r="F63" t="str">
-        <v>12.50%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B64" t="str">
-        <v>Heahea Beach</v>
+        <v>Daycare</v>
       </c>
       <c r="C64" t="str">
-        <v>Main Area</v>
+        <v>NPC</v>
       </c>
       <c r="D64" t="str">
-        <v>Salazzle</v>
+        <v>NPC</v>
       </c>
       <c r="E64" t="str">
-        <v>21-26</v>
+        <v>-</v>
       </c>
       <c r="F64" t="str">
-        <v>12.50%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B65" t="str">
-        <v>Heahea Beach</v>
+        <v>Route 5</v>
       </c>
       <c r="C65" t="str">
         <v>Main Area</v>
       </c>
       <c r="D65" t="str">
-        <v>Alolan Marowak</v>
+        <v>Noibat</v>
       </c>
       <c r="E65" t="str">
-        <v>21-26</v>
+        <v>23-28</v>
       </c>
       <c r="F65" t="str">
-        <v>12.50%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B66" t="str">
-        <v>Heahea Beach</v>
+        <v>Route 5</v>
       </c>
       <c r="C66" t="str">
         <v>Main Area</v>
       </c>
       <c r="D66" t="str">
-        <v>Kommo-o</v>
+        <v>Fomantis</v>
       </c>
       <c r="E66" t="str">
-        <v>21-26</v>
+        <v>23-28</v>
       </c>
       <c r="F66" t="str">
-        <v>12.50%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B67" t="str">
-        <v>Heahea Beach</v>
+        <v>Route 5</v>
       </c>
       <c r="C67" t="str">
         <v>Main Area</v>
       </c>
       <c r="D67" t="str">
-        <v>Mimikyu</v>
+        <v>Bounsweet</v>
       </c>
       <c r="E67" t="str">
-        <v>21-26</v>
+        <v>23-28</v>
       </c>
       <c r="F67" t="str">
-        <v>12.50%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B68" t="str">
-        <v>Route 4</v>
+        <v>Brooklet Hill</v>
       </c>
       <c r="C68" t="str">
-        <v>Main Area</v>
+        <v>South</v>
       </c>
       <c r="D68" t="str">
-        <v>Igglybuff</v>
+        <v>Wingull</v>
       </c>
       <c r="E68" t="str">
-        <v>22-27</v>
+        <v>25-30</v>
       </c>
       <c r="F68" t="str">
-        <v>100.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B69" t="str">
-        <v>Paniola Ranch</v>
+        <v>Brooklet Hill</v>
       </c>
       <c r="C69" t="str">
-        <v>Main Area</v>
+        <v>South</v>
       </c>
       <c r="D69" t="str">
-        <v>Eevee</v>
+        <v>Lillipup</v>
       </c>
       <c r="E69" t="str">
-        <v>23-28</v>
+        <v>25-30</v>
       </c>
       <c r="F69" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B70" t="str">
-        <v>Paniola Ranch</v>
+        <v>Brooklet Hill</v>
       </c>
       <c r="C70" t="str">
-        <v>Main Area</v>
+        <v>South</v>
       </c>
       <c r="D70" t="str">
-        <v>Mareep</v>
+        <v>Paras</v>
       </c>
       <c r="E70" t="str">
-        <v>23-28</v>
+        <v>25-30</v>
       </c>
       <c r="F70" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B71" t="str">
-        <v>Paniola Ranch</v>
+        <v>Brooklet Hill</v>
       </c>
       <c r="C71" t="str">
-        <v>Main Area</v>
+        <v>South</v>
       </c>
       <c r="D71" t="str">
-        <v>Tauros</v>
+        <v>Goldeen</v>
       </c>
       <c r="E71" t="str">
-        <v>23-28</v>
+        <v>25-30</v>
       </c>
       <c r="F71" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B72" t="str">
-        <v>Paniola Ranch</v>
+        <v>Brooklet Hill</v>
       </c>
       <c r="C72" t="str">
-        <v>Main Area</v>
+        <v>South</v>
       </c>
       <c r="D72" t="str">
-        <v>Miltank</v>
+        <v>Feebas</v>
       </c>
       <c r="E72" t="str">
-        <v>23-28</v>
+        <v>25-30</v>
       </c>
       <c r="F72" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B73" t="str">
-        <v>Daycare</v>
+        <v>Captain Lana</v>
       </c>
       <c r="C73" t="str">
-        <v>NPC</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D73" t="str">
-        <v>NPC</v>
+        <v>Boss</v>
       </c>
       <c r="E73" t="str">
-        <v>-</v>
+        <v>26-31</v>
       </c>
       <c r="F73" t="str">
         <v>-</v>
@@ -1863,119 +1863,119 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B74" t="str">
-        <v>Route 5</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C74" t="str">
         <v>Main Area</v>
       </c>
       <c r="D74" t="str">
-        <v>Noibat</v>
+        <v>Cubone</v>
       </c>
       <c r="E74" t="str">
-        <v>26-31</v>
+        <v>27-32</v>
       </c>
       <c r="F74" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B75" t="str">
-        <v>Route 5</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C75" t="str">
         <v>Main Area</v>
       </c>
       <c r="D75" t="str">
-        <v>Fomantis</v>
+        <v>Kangaskhan</v>
       </c>
       <c r="E75" t="str">
-        <v>26-31</v>
+        <v>27-32</v>
       </c>
       <c r="F75" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B76" t="str">
-        <v>Route 5</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C76" t="str">
         <v>Main Area</v>
       </c>
       <c r="D76" t="str">
-        <v>Bounsweet</v>
+        <v>Magby</v>
       </c>
       <c r="E76" t="str">
-        <v>26-31</v>
+        <v>27-32</v>
       </c>
       <c r="F76" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B77" t="str">
-        <v>Brooklet Hill</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C77" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D77" t="str">
-        <v>Magikarp</v>
+        <v>Nihilego</v>
       </c>
       <c r="E77" t="str">
         <v>27-32</v>
       </c>
       <c r="F77" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B78" t="str">
-        <v>Brooklet Hill</v>
+        <v>Captain Kiawe</v>
       </c>
       <c r="C78" t="str">
-        <v>North</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D78" t="str">
-        <v>Psyduck</v>
+        <v>Boss</v>
       </c>
       <c r="E78" t="str">
-        <v>27-32</v>
+        <v>29-34</v>
       </c>
       <c r="F78" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B79" t="str">
-        <v>Brooklet Hill</v>
+        <v>Route 7</v>
       </c>
       <c r="C79" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D79" t="str">
-        <v>Surskit</v>
+        <v>Staryu</v>
       </c>
       <c r="E79" t="str">
-        <v>27-32</v>
+        <v>30-35</v>
       </c>
       <c r="F79" t="str">
         <v>20.00%</v>
@@ -1983,19 +1983,19 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B80" t="str">
-        <v>Brooklet Hill</v>
+        <v>Route 7</v>
       </c>
       <c r="C80" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D80" t="str">
-        <v>Dewpider</v>
+        <v>Pyukumuku</v>
       </c>
       <c r="E80" t="str">
-        <v>27-32</v>
+        <v>30-35</v>
       </c>
       <c r="F80" t="str">
         <v>20.00%</v>
@@ -2003,19 +2003,19 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B81" t="str">
-        <v>Brooklet Hill</v>
+        <v>Route 7</v>
       </c>
       <c r="C81" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D81" t="str">
-        <v>Poliwag</v>
+        <v>Corsola</v>
       </c>
       <c r="E81" t="str">
-        <v>27-32</v>
+        <v>30-35</v>
       </c>
       <c r="F81" t="str">
         <v>20.00%</v>
@@ -2023,19 +2023,19 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B82" t="str">
-        <v>Brooklet Hill</v>
+        <v>Route 7</v>
       </c>
       <c r="C82" t="str">
-        <v>South</v>
+        <v>Main Area</v>
       </c>
       <c r="D82" t="str">
-        <v>Wingull</v>
+        <v>Mareanie</v>
       </c>
       <c r="E82" t="str">
-        <v>28-33</v>
+        <v>30-35</v>
       </c>
       <c r="F82" t="str">
         <v>20.00%</v>
@@ -2043,19 +2043,19 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B83" t="str">
-        <v>Brooklet Hill</v>
+        <v>Route 7</v>
       </c>
       <c r="C83" t="str">
-        <v>South</v>
+        <v>Main Area</v>
       </c>
       <c r="D83" t="str">
-        <v>Lillipup</v>
+        <v>Bruxish</v>
       </c>
       <c r="E83" t="str">
-        <v>28-33</v>
+        <v>30-35</v>
       </c>
       <c r="F83" t="str">
         <v>20.00%</v>
@@ -2063,2039 +2063,2039 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B84" t="str">
-        <v>Brooklet Hill</v>
+        <v>Route 8</v>
       </c>
       <c r="C84" t="str">
-        <v>South</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D84" t="str">
-        <v>Paras</v>
+        <v>Omanyte</v>
       </c>
       <c r="E84" t="str">
-        <v>28-33</v>
+        <v>32-37</v>
       </c>
       <c r="F84" t="str">
-        <v>20.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B85" t="str">
-        <v>Brooklet Hill</v>
+        <v>Route 8</v>
       </c>
       <c r="C85" t="str">
-        <v>South</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D85" t="str">
-        <v>Goldeen</v>
+        <v>Kabuto</v>
       </c>
       <c r="E85" t="str">
-        <v>28-33</v>
+        <v>32-37</v>
       </c>
       <c r="F85" t="str">
-        <v>20.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B86" t="str">
-        <v>Brooklet Hill</v>
+        <v>Route 8</v>
       </c>
       <c r="C86" t="str">
-        <v>South</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D86" t="str">
-        <v>Feebas</v>
+        <v>Lileep</v>
       </c>
       <c r="E86" t="str">
-        <v>28-33</v>
+        <v>32-37</v>
       </c>
       <c r="F86" t="str">
-        <v>20.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B87" t="str">
-        <v>Captain Lana</v>
+        <v>Route 8</v>
       </c>
       <c r="C87" t="str">
-        <v>Boss Battle</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D87" t="str">
-        <v>Boss</v>
+        <v>Anorith</v>
       </c>
       <c r="E87" t="str">
-        <v>29-34</v>
+        <v>32-37</v>
       </c>
       <c r="F87" t="str">
-        <v>-</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="88">
       <c r="A88">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B88" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Route 8</v>
       </c>
       <c r="C88" t="str">
-        <v>Main Area</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D88" t="str">
-        <v>Cubone</v>
+        <v>Cranidos</v>
       </c>
       <c r="E88" t="str">
-        <v>30-35</v>
+        <v>32-37</v>
       </c>
       <c r="F88" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B89" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Route 8</v>
       </c>
       <c r="C89" t="str">
-        <v>Main Area</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D89" t="str">
-        <v>Kangaskhan</v>
+        <v>Shieldon</v>
       </c>
       <c r="E89" t="str">
-        <v>30-35</v>
+        <v>32-37</v>
       </c>
       <c r="F89" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="90">
       <c r="A90">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B90" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Route 8</v>
       </c>
       <c r="C90" t="str">
-        <v>Main Area</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D90" t="str">
-        <v>Magby</v>
+        <v>Archen</v>
       </c>
       <c r="E90" t="str">
-        <v>30-35</v>
+        <v>32-37</v>
       </c>
       <c r="F90" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B91" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Route 8</v>
       </c>
       <c r="C91" t="str">
-        <v>Main Area</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D91" t="str">
-        <v>Nihilego</v>
+        <v>Tirtouga</v>
       </c>
       <c r="E91" t="str">
-        <v>30-35</v>
+        <v>32-37</v>
       </c>
       <c r="F91" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B92" t="str">
-        <v>Captain Kiawe</v>
+        <v>Route 8</v>
       </c>
       <c r="C92" t="str">
-        <v>Boss Battle</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D92" t="str">
-        <v>Boss</v>
+        <v>Tyrunt</v>
       </c>
       <c r="E92" t="str">
-        <v>31-36</v>
+        <v>32-37</v>
       </c>
       <c r="F92" t="str">
-        <v>-</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B93" t="str">
-        <v>Route 7</v>
+        <v>Route 8</v>
       </c>
       <c r="C93" t="str">
-        <v>Main Area</v>
+        <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D93" t="str">
-        <v>Staryu</v>
+        <v>Amaura</v>
       </c>
       <c r="E93" t="str">
         <v>32-37</v>
       </c>
       <c r="F93" t="str">
-        <v>50.00%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B94" t="str">
-        <v>Route 7</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C94" t="str">
-        <v>Main Area</v>
+        <v>North</v>
       </c>
       <c r="D94" t="str">
-        <v>Pyukumuku</v>
+        <v>Trumbeak</v>
       </c>
       <c r="E94" t="str">
-        <v>32-37</v>
+        <v>33-38</v>
       </c>
       <c r="F94" t="str">
-        <v>50.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="95">
       <c r="A95">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B95" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C95" t="str">
-        <v>Main</v>
+        <v>North</v>
       </c>
       <c r="D95" t="str">
-        <v>Arbok</v>
+        <v>Steenee</v>
       </c>
       <c r="E95" t="str">
         <v>33-38</v>
       </c>
       <c r="F95" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B96" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C96" t="str">
-        <v>Main</v>
+        <v>North</v>
       </c>
       <c r="D96" t="str">
-        <v>Wimpod</v>
+        <v>Comfey</v>
       </c>
       <c r="E96" t="str">
         <v>33-38</v>
       </c>
       <c r="F96" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="97">
       <c r="A97">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B97" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C97" t="str">
-        <v>Main</v>
+        <v>North</v>
       </c>
       <c r="D97" t="str">
-        <v>Fletchinder</v>
+        <v>Hoothoot</v>
       </c>
       <c r="E97" t="str">
         <v>33-38</v>
       </c>
       <c r="F97" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B98" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C98" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>North</v>
       </c>
       <c r="D98" t="str">
-        <v>Omanyte</v>
+        <v>Oranguru</v>
       </c>
       <c r="E98" t="str">
-        <v>34-39</v>
+        <v>33-38</v>
       </c>
       <c r="F98" t="str">
-        <v>11.11%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B99" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C99" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>North</v>
       </c>
       <c r="D99" t="str">
-        <v>Kabuto</v>
+        <v>Bounsweet</v>
       </c>
       <c r="E99" t="str">
-        <v>34-39</v>
+        <v>33-38</v>
       </c>
       <c r="F99" t="str">
-        <v>11.11%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="100">
       <c r="A100">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B100" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C100" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>North</v>
       </c>
       <c r="D100" t="str">
-        <v>Lileep</v>
+        <v>Solgaleo</v>
       </c>
       <c r="E100" t="str">
-        <v>34-39</v>
+        <v>33-38</v>
       </c>
       <c r="F100" t="str">
-        <v>11.11%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="101">
       <c r="A101">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B101" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C101" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>North</v>
       </c>
       <c r="D101" t="str">
-        <v>Anorith</v>
+        <v>Lunala</v>
       </c>
       <c r="E101" t="str">
-        <v>34-39</v>
+        <v>33-38</v>
       </c>
       <c r="F101" t="str">
-        <v>11.11%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="102">
       <c r="A102">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B102" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C102" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>East Cave</v>
       </c>
       <c r="D102" t="str">
-        <v>Cranidos</v>
+        <v>Golbat</v>
       </c>
       <c r="E102" t="str">
         <v>34-39</v>
       </c>
       <c r="F102" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="103">
       <c r="A103">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B103" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C103" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>East Cave</v>
       </c>
       <c r="D103" t="str">
-        <v>Shieldon</v>
+        <v>Salandit</v>
       </c>
       <c r="E103" t="str">
         <v>34-39</v>
       </c>
       <c r="F103" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="104">
       <c r="A104">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B104" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C104" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>East Cave</v>
       </c>
       <c r="D104" t="str">
-        <v>Archen</v>
+        <v>Larvesta</v>
       </c>
       <c r="E104" t="str">
         <v>34-39</v>
       </c>
       <c r="F104" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="105">
       <c r="A105">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B105" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C105" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>East Cave</v>
       </c>
       <c r="D105" t="str">
-        <v>Tirtouga</v>
+        <v>Oranguru</v>
       </c>
       <c r="E105" t="str">
         <v>34-39</v>
       </c>
       <c r="F105" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="106">
       <c r="A106">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B106" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C106" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>East Cave</v>
       </c>
       <c r="D106" t="str">
-        <v>Tyrunt</v>
+        <v>Passimian</v>
       </c>
       <c r="E106" t="str">
         <v>34-39</v>
       </c>
       <c r="F106" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="107">
       <c r="A107">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B107" t="str">
-        <v>Route 8</v>
+        <v>Captain Mallow</v>
       </c>
       <c r="C107" t="str">
-        <v>Fossil Restoration Center Part 2</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D107" t="str">
-        <v>Amaura</v>
+        <v>Boss</v>
       </c>
       <c r="E107" t="str">
-        <v>34-39</v>
+        <v>36-41</v>
       </c>
       <c r="F107" t="str">
-        <v>100.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="108">
       <c r="A108">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B108" t="str">
-        <v>Lush Jungle</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C108" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D108" t="str">
-        <v>Trumbeak</v>
+        <v>Zubat</v>
       </c>
       <c r="E108" t="str">
-        <v>35-40</v>
+        <v>37-42</v>
       </c>
       <c r="F108" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="109">
       <c r="A109">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B109" t="str">
-        <v>Lush Jungle</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C109" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D109" t="str">
-        <v>Steenee</v>
+        <v>Alolan Diglett</v>
       </c>
       <c r="E109" t="str">
-        <v>35-40</v>
+        <v>37-42</v>
       </c>
       <c r="F109" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="110">
       <c r="A110">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B110" t="str">
-        <v>Lush Jungle</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C110" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D110" t="str">
-        <v>Comfey</v>
+        <v>Kecleon</v>
       </c>
       <c r="E110" t="str">
-        <v>35-40</v>
+        <v>37-42</v>
       </c>
       <c r="F110" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="111">
       <c r="A111">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B111" t="str">
-        <v>Lush Jungle</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C111" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D111" t="str">
-        <v>Hoothoot</v>
+        <v>Larvitar</v>
       </c>
       <c r="E111" t="str">
-        <v>35-40</v>
+        <v>37-42</v>
       </c>
       <c r="F111" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="112">
       <c r="A112">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B112" t="str">
-        <v>Lush Jungle</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C112" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D112" t="str">
-        <v>Oranguru</v>
+        <v>Gumshoos</v>
       </c>
       <c r="E112" t="str">
-        <v>35-40</v>
+        <v>42-47</v>
       </c>
       <c r="F112" t="str">
-        <v>16.67%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="113">
       <c r="A113">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B113" t="str">
-        <v>Lush Jungle</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C113" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D113" t="str">
-        <v>Bounsweet</v>
+        <v>Wingull</v>
       </c>
       <c r="E113" t="str">
-        <v>35-40</v>
+        <v>42-47</v>
       </c>
       <c r="F113" t="str">
-        <v>16.67%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="114">
       <c r="A114">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B114" t="str">
-        <v>Lush Jungle</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C114" t="str">
-        <v>East Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D114" t="str">
-        <v>Golbat</v>
+        <v>Magikarp</v>
       </c>
       <c r="E114" t="str">
-        <v>36-41</v>
+        <v>42-47</v>
       </c>
       <c r="F114" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="115">
       <c r="A115">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B115" t="str">
-        <v>Lush Jungle</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C115" t="str">
-        <v>East Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D115" t="str">
-        <v>Salandit</v>
+        <v>Stufful</v>
       </c>
       <c r="E115" t="str">
-        <v>36-41</v>
+        <v>42-47</v>
       </c>
       <c r="F115" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="116">
       <c r="A116">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B116" t="str">
-        <v>Lush Jungle</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C116" t="str">
-        <v>East Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D116" t="str">
-        <v>Larvesta</v>
+        <v>Chinchou</v>
       </c>
       <c r="E116" t="str">
-        <v>36-41</v>
+        <v>42-47</v>
       </c>
       <c r="F116" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="117">
       <c r="A117">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B117" t="str">
-        <v>Lush Jungle</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C117" t="str">
-        <v>East Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D117" t="str">
-        <v>Oranguru</v>
+        <v>Alolan Raticate</v>
       </c>
       <c r="E117" t="str">
-        <v>36-41</v>
+        <v>42-47</v>
       </c>
       <c r="F117" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="118">
       <c r="A118">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B118" t="str">
-        <v>Lush Jungle</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C118" t="str">
-        <v>East Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D118" t="str">
-        <v>Passimian</v>
+        <v>Natu</v>
       </c>
       <c r="E118" t="str">
-        <v>36-41</v>
+        <v>42-47</v>
       </c>
       <c r="F118" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="119">
       <c r="A119">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B119" t="str">
-        <v>Captain Mallow</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C119" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D119" t="str">
-        <v>Boss</v>
+        <v>Nosepass</v>
       </c>
       <c r="E119" t="str">
-        <v>38-43</v>
+        <v>42-47</v>
       </c>
       <c r="F119" t="str">
-        <v>-</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="120">
       <c r="A120">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B120" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Kahuna Olivia</v>
       </c>
       <c r="C120" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D120" t="str">
-        <v>Zubat</v>
+        <v>Boss</v>
       </c>
       <c r="E120" t="str">
-        <v>39-44</v>
+        <v>44-49</v>
       </c>
       <c r="F120" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="121">
       <c r="A121">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B121" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Malie City</v>
       </c>
       <c r="C121" t="str">
-        <v>Main Area</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D121" t="str">
-        <v>Alolan Diglett</v>
+        <v>Magnemite</v>
       </c>
       <c r="E121" t="str">
-        <v>39-44</v>
+        <v>46-51</v>
       </c>
       <c r="F121" t="str">
-        <v>25.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="122">
       <c r="A122">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B122" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Malie City</v>
       </c>
       <c r="C122" t="str">
-        <v>Main Area</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D122" t="str">
-        <v>Kecleon</v>
+        <v>Alolan Grimer</v>
       </c>
       <c r="E122" t="str">
-        <v>39-44</v>
+        <v>46-51</v>
       </c>
       <c r="F122" t="str">
-        <v>25.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="123">
       <c r="A123">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B123" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Malie City</v>
       </c>
       <c r="C123" t="str">
-        <v>Main Area</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D123" t="str">
-        <v>Larvitar</v>
+        <v>Trubbish</v>
       </c>
       <c r="E123" t="str">
-        <v>39-44</v>
+        <v>46-51</v>
       </c>
       <c r="F123" t="str">
-        <v>25.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="124">
       <c r="A124">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B124" t="str">
-        <v>Route 9</v>
+        <v>Malie City</v>
       </c>
       <c r="C124" t="str">
-        <v>Main Area</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D124" t="str">
-        <v>Corsola</v>
+        <v>Minccino</v>
       </c>
       <c r="E124" t="str">
-        <v>40-45</v>
+        <v>46-51</v>
       </c>
       <c r="F124" t="str">
-        <v>50.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="125">
       <c r="A125">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B125" t="str">
-        <v>Route 9</v>
+        <v>Malie City</v>
       </c>
       <c r="C125" t="str">
-        <v>Main Area</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D125" t="str">
-        <v>Mareanie</v>
+        <v>Masquerain</v>
       </c>
       <c r="E125" t="str">
-        <v>40-45</v>
+        <v>46-51</v>
       </c>
       <c r="F125" t="str">
-        <v>50.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="126">
       <c r="A126">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B126" t="str">
-        <v>Konikoni City</v>
+        <v>Malie City</v>
       </c>
       <c r="C126" t="str">
-        <v>Main Area</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D126" t="str">
-        <v>Poliwhirl</v>
+        <v>Kartana</v>
       </c>
       <c r="E126" t="str">
-        <v>41-46</v>
+        <v>46-51</v>
       </c>
       <c r="F126" t="str">
-        <v>50.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="127">
       <c r="A127">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B127" t="str">
-        <v>Konikoni City</v>
+        <v>Route 10</v>
       </c>
       <c r="C127" t="str">
         <v>Main Area</v>
       </c>
       <c r="D127" t="str">
-        <v>Ditto</v>
+        <v>Ledian</v>
       </c>
       <c r="E127" t="str">
-        <v>41-46</v>
+        <v>49-54</v>
       </c>
       <c r="F127" t="str">
-        <v>50.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="128">
       <c r="A128">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B128" t="str">
-        <v>Memorial Hill</v>
+        <v>Route 10</v>
       </c>
       <c r="C128" t="str">
-        <v>Main</v>
+        <v>Main Area</v>
       </c>
       <c r="D128" t="str">
-        <v>Phantump</v>
+        <v>Ariados</v>
       </c>
       <c r="E128" t="str">
-        <v>42-47</v>
+        <v>49-54</v>
       </c>
       <c r="F128" t="str">
-        <v>100.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="129">
       <c r="A129">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B129" t="str">
-        <v>Akala Outskirts</v>
+        <v>Route 10</v>
       </c>
       <c r="C129" t="str">
         <v>Main Area</v>
       </c>
       <c r="D129" t="str">
-        <v>Gumshoos</v>
+        <v>Crabrawler</v>
       </c>
       <c r="E129" t="str">
-        <v>43-48</v>
+        <v>49-54</v>
       </c>
       <c r="F129" t="str">
-        <v>12.50%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="130">
       <c r="A130">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B130" t="str">
-        <v>Akala Outskirts</v>
+        <v>Route 10</v>
       </c>
       <c r="C130" t="str">
         <v>Main Area</v>
       </c>
       <c r="D130" t="str">
-        <v>Wingull</v>
+        <v>Fearow</v>
       </c>
       <c r="E130" t="str">
-        <v>43-48</v>
+        <v>49-54</v>
       </c>
       <c r="F130" t="str">
-        <v>12.50%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="131">
       <c r="A131">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B131" t="str">
-        <v>Akala Outskirts</v>
+        <v>Route 10</v>
       </c>
       <c r="C131" t="str">
         <v>Main Area</v>
       </c>
       <c r="D131" t="str">
-        <v>Magikarp</v>
+        <v>Skarmory</v>
       </c>
       <c r="E131" t="str">
-        <v>43-48</v>
+        <v>49-54</v>
       </c>
       <c r="F131" t="str">
-        <v>12.50%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="132">
       <c r="A132">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B132" t="str">
-        <v>Akala Outskirts</v>
+        <v>Route 10</v>
       </c>
       <c r="C132" t="str">
         <v>Main Area</v>
       </c>
       <c r="D132" t="str">
-        <v>Stufful</v>
+        <v>Pancham</v>
       </c>
       <c r="E132" t="str">
-        <v>43-48</v>
+        <v>49-54</v>
       </c>
       <c r="F132" t="str">
-        <v>12.50%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="133">
       <c r="A133">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B133" t="str">
-        <v>Akala Outskirts</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C133" t="str">
-        <v>Main Area</v>
+        <v>East</v>
       </c>
       <c r="D133" t="str">
-        <v>Chinchou</v>
+        <v>Cleffa</v>
       </c>
       <c r="E133" t="str">
-        <v>43-48</v>
+        <v>50-55</v>
       </c>
       <c r="F133" t="str">
-        <v>12.50%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="134">
       <c r="A134">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B134" t="str">
-        <v>Akala Outskirts</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C134" t="str">
-        <v>Main Area</v>
+        <v>East</v>
       </c>
       <c r="D134" t="str">
-        <v>Alolan Raticate</v>
+        <v>Elgyem</v>
       </c>
       <c r="E134" t="str">
-        <v>43-48</v>
+        <v>50-55</v>
       </c>
       <c r="F134" t="str">
-        <v>12.50%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="135">
       <c r="A135">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B135" t="str">
-        <v>Akala Outskirts</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C135" t="str">
-        <v>Main Area</v>
+        <v>East</v>
       </c>
       <c r="D135" t="str">
-        <v>Natu</v>
+        <v>Beldum</v>
       </c>
       <c r="E135" t="str">
-        <v>43-48</v>
+        <v>50-55</v>
       </c>
       <c r="F135" t="str">
-        <v>12.50%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="136">
       <c r="A136">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B136" t="str">
-        <v>Akala Outskirts</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C136" t="str">
-        <v>Main Area</v>
+        <v>East</v>
       </c>
       <c r="D136" t="str">
-        <v>Nosepass</v>
+        <v>Minior</v>
       </c>
       <c r="E136" t="str">
-        <v>43-48</v>
+        <v>50-55</v>
       </c>
       <c r="F136" t="str">
-        <v>12.50%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="137">
       <c r="A137">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B137" t="str">
-        <v>Ruins of Life</v>
+        <v>Captain Sophocles</v>
       </c>
       <c r="C137" t="str">
-        <v>Special Encounter</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D137" t="str">
-        <v>Tapu Lele</v>
+        <v>Boss</v>
       </c>
       <c r="E137" t="str">
-        <v>44-49</v>
+        <v>52-57</v>
       </c>
       <c r="F137" t="str">
-        <v>100.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="138">
       <c r="A138">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B138" t="str">
-        <v>Kahuna Olivia</v>
+        <v>Route 11</v>
       </c>
       <c r="C138" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D138" t="str">
-        <v>Boss</v>
+        <v>Shiinotic</v>
       </c>
       <c r="E138" t="str">
-        <v>45-50</v>
+        <v>53-58</v>
       </c>
       <c r="F138" t="str">
-        <v>-</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="139">
       <c r="A139">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B139" t="str">
-        <v>Hano Beach</v>
+        <v>Route 11</v>
       </c>
       <c r="C139" t="str">
         <v>Main Area</v>
       </c>
       <c r="D139" t="str">
-        <v>Staryu</v>
+        <v>Parasect</v>
       </c>
       <c r="E139" t="str">
-        <v>46-51</v>
+        <v>53-58</v>
       </c>
       <c r="F139" t="str">
-        <v>50.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="140">
       <c r="A140">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B140" t="str">
-        <v>Hano Beach</v>
+        <v>Route 11</v>
       </c>
       <c r="C140" t="str">
         <v>Main Area</v>
       </c>
       <c r="D140" t="str">
-        <v>Sandygast</v>
+        <v>Komala</v>
       </c>
       <c r="E140" t="str">
-        <v>46-51</v>
+        <v>53-58</v>
       </c>
       <c r="F140" t="str">
-        <v>50.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="141">
       <c r="A141">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B141" t="str">
-        <v>Aether Paradise</v>
+        <v>Route 11</v>
       </c>
       <c r="C141" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D141" t="str">
-        <v>Type: Null</v>
+        <v>Houndoom</v>
       </c>
       <c r="E141" t="str">
-        <v>47-52</v>
+        <v>53-58</v>
       </c>
       <c r="F141" t="str">
-        <v>33.33%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="142">
       <c r="A142">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B142" t="str">
-        <v>Aether Paradise</v>
+        <v>Route 11</v>
       </c>
       <c r="C142" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D142" t="str">
-        <v>Ditto</v>
+        <v>Manectric</v>
       </c>
       <c r="E142" t="str">
-        <v>47-52</v>
+        <v>53-58</v>
       </c>
       <c r="F142" t="str">
-        <v>33.33%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="143">
       <c r="A143">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B143" t="str">
-        <v>Aether Paradise</v>
+        <v>Route 11</v>
       </c>
       <c r="C143" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D143" t="str">
-        <v>Porygon</v>
+        <v>Scraggy</v>
       </c>
       <c r="E143" t="str">
-        <v>47-52</v>
+        <v>53-58</v>
       </c>
       <c r="F143" t="str">
-        <v>33.33%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="144">
       <c r="A144">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B144" t="str">
-        <v>Malie City</v>
+        <v>Route 11</v>
       </c>
       <c r="C144" t="str">
-        <v>Outer Cape</v>
+        <v>Main Area</v>
       </c>
       <c r="D144" t="str">
-        <v>Magnemite</v>
+        <v>Bisharp</v>
       </c>
       <c r="E144" t="str">
-        <v>48-53</v>
+        <v>53-58</v>
       </c>
       <c r="F144" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="145">
       <c r="A145">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B145" t="str">
-        <v>Malie City</v>
+        <v>Route 11</v>
       </c>
       <c r="C145" t="str">
-        <v>Outer Cape</v>
+        <v>Main Area</v>
       </c>
       <c r="D145" t="str">
-        <v>Alolan Grimer</v>
+        <v>Machop</v>
       </c>
       <c r="E145" t="str">
-        <v>48-53</v>
+        <v>53-58</v>
       </c>
       <c r="F145" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="146">
       <c r="A146">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B146" t="str">
-        <v>Malie City</v>
+        <v>Route 11</v>
       </c>
       <c r="C146" t="str">
-        <v>Outer Cape</v>
+        <v>Main Area</v>
       </c>
       <c r="D146" t="str">
-        <v>Trubbish</v>
+        <v>Hawlucha</v>
       </c>
       <c r="E146" t="str">
-        <v>48-53</v>
+        <v>53-58</v>
       </c>
       <c r="F146" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="147">
       <c r="A147">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B147" t="str">
-        <v>Malie City</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C147" t="str">
-        <v>Outer Cape</v>
+        <v>Main Area</v>
       </c>
       <c r="D147" t="str">
-        <v>Minccino</v>
+        <v>Mudbray</v>
       </c>
       <c r="E147" t="str">
-        <v>48-53</v>
+        <v>56-61</v>
       </c>
       <c r="F147" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="148">
       <c r="A148">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B148" t="str">
-        <v>Malie Garden</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C148" t="str">
         <v>Main Area</v>
       </c>
       <c r="D148" t="str">
-        <v>Masquerain</v>
+        <v>Torkoal</v>
       </c>
       <c r="E148" t="str">
-        <v>50-55</v>
+        <v>56-61</v>
       </c>
       <c r="F148" t="str">
-        <v>50.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="149">
       <c r="A149">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B149" t="str">
-        <v>Malie Garden</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C149" t="str">
         <v>Main Area</v>
       </c>
       <c r="D149" t="str">
-        <v>Kartana</v>
+        <v>Togedemaru</v>
       </c>
       <c r="E149" t="str">
-        <v>50-55</v>
+        <v>56-61</v>
       </c>
       <c r="F149" t="str">
-        <v>50.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="150">
       <c r="A150">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B150" t="str">
-        <v>Route 10</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C150" t="str">
         <v>Main Area</v>
       </c>
       <c r="D150" t="str">
-        <v>Ledian</v>
+        <v>Elekid</v>
       </c>
       <c r="E150" t="str">
-        <v>51-56</v>
+        <v>56-61</v>
       </c>
       <c r="F150" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="151">
       <c r="A151">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B151" t="str">
-        <v>Route 10</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C151" t="str">
         <v>Main Area</v>
       </c>
       <c r="D151" t="str">
-        <v>Ariados</v>
+        <v>Alolan Geodude</v>
       </c>
       <c r="E151" t="str">
-        <v>51-56</v>
+        <v>56-61</v>
       </c>
       <c r="F151" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="152">
       <c r="A152">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B152" t="str">
-        <v>Route 10</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C152" t="str">
         <v>Main Area</v>
       </c>
       <c r="D152" t="str">
-        <v>Crabrawler</v>
+        <v>Alolan Graveler</v>
       </c>
       <c r="E152" t="str">
-        <v>51-56</v>
+        <v>56-61</v>
       </c>
       <c r="F152" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="153">
       <c r="A153">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B153" t="str">
-        <v>Route 10</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C153" t="str">
         <v>Main Area</v>
       </c>
       <c r="D153" t="str">
-        <v>Fearow</v>
+        <v>Charjabug</v>
       </c>
       <c r="E153" t="str">
-        <v>51-56</v>
+        <v>56-61</v>
       </c>
       <c r="F153" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="154">
       <c r="A154">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B154" t="str">
-        <v>Route 10</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C154" t="str">
         <v>Main Area</v>
       </c>
       <c r="D154" t="str">
-        <v>Skarmory</v>
+        <v>Turtonator</v>
       </c>
       <c r="E154" t="str">
-        <v>51-56</v>
+        <v>56-61</v>
       </c>
       <c r="F154" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="155">
       <c r="A155">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B155" t="str">
-        <v>Route 10</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C155" t="str">
         <v>Main Area</v>
       </c>
       <c r="D155" t="str">
-        <v>Pancham</v>
+        <v>Dedenne</v>
       </c>
       <c r="E155" t="str">
-        <v>51-56</v>
+        <v>56-61</v>
       </c>
       <c r="F155" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="156">
       <c r="A156">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B156" t="str">
-        <v>Mount Hokulani</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C156" t="str">
-        <v>East</v>
+        <v>Main Area</v>
       </c>
       <c r="D156" t="str">
-        <v>Cleffa</v>
+        <v>Celesteela</v>
       </c>
       <c r="E156" t="str">
-        <v>52-57</v>
+        <v>57-62</v>
       </c>
       <c r="F156" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="157">
       <c r="A157">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B157" t="str">
-        <v>Mount Hokulani</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C157" t="str">
-        <v>East</v>
+        <v>Main Area</v>
       </c>
       <c r="D157" t="str">
-        <v>Elgyem</v>
+        <v>Alolan Dugtrio</v>
       </c>
       <c r="E157" t="str">
-        <v>52-57</v>
+        <v>57-62</v>
       </c>
       <c r="F157" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="158">
       <c r="A158">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B158" t="str">
-        <v>Mount Hokulani</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C158" t="str">
-        <v>East</v>
+        <v>Main Area</v>
       </c>
       <c r="D158" t="str">
-        <v>Beldum</v>
+        <v>Sandile</v>
       </c>
       <c r="E158" t="str">
-        <v>52-57</v>
+        <v>57-62</v>
       </c>
       <c r="F158" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="159">
       <c r="A159">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B159" t="str">
-        <v>Captain Sophocles</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C159" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D159" t="str">
-        <v>Boss</v>
+        <v>Krokorok</v>
       </c>
       <c r="E159" t="str">
-        <v>54-59</v>
+        <v>57-62</v>
       </c>
       <c r="F159" t="str">
-        <v>-</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="160">
       <c r="A160">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="B160" t="str">
-        <v>Route 11</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C160" t="str">
         <v>Main Area</v>
       </c>
       <c r="D160" t="str">
-        <v>Shiinotic</v>
+        <v>Staryu</v>
       </c>
       <c r="E160" t="str">
-        <v>55-60</v>
+        <v>57-62</v>
       </c>
       <c r="F160" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="161">
       <c r="A161">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="B161" t="str">
-        <v>Route 11</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C161" t="str">
         <v>Main Area</v>
       </c>
       <c r="D161" t="str">
-        <v>Parasect</v>
+        <v>Sandygast</v>
       </c>
       <c r="E161" t="str">
-        <v>55-60</v>
+        <v>57-62</v>
       </c>
       <c r="F161" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="162">
       <c r="A162">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B162" t="str">
-        <v>Route 11</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C162" t="str">
         <v>Main Area</v>
       </c>
       <c r="D162" t="str">
-        <v>Komala</v>
+        <v>Graveler</v>
       </c>
       <c r="E162" t="str">
-        <v>55-60</v>
+        <v>59-64</v>
       </c>
       <c r="F162" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="163">
       <c r="A163">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B163" t="str">
-        <v>Route 12</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C163" t="str">
         <v>Main Area</v>
       </c>
       <c r="D163" t="str">
-        <v>Houndoom</v>
+        <v>Bruxish</v>
       </c>
       <c r="E163" t="str">
-        <v>56-61</v>
+        <v>59-64</v>
       </c>
       <c r="F163" t="str">
-        <v>50.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="164">
       <c r="A164">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B164" t="str">
-        <v>Route 12</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C164" t="str">
         <v>Main Area</v>
       </c>
       <c r="D164" t="str">
-        <v>Manectric</v>
+        <v>Absol</v>
       </c>
       <c r="E164" t="str">
-        <v>56-61</v>
+        <v>59-64</v>
       </c>
       <c r="F164" t="str">
-        <v>50.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="165">
       <c r="A165">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B165" t="str">
-        <v>Blush Mountain</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C165" t="str">
         <v>Main Area</v>
       </c>
       <c r="D165" t="str">
-        <v>Mudbray</v>
+        <v>Snorunt</v>
       </c>
       <c r="E165" t="str">
-        <v>57-62</v>
+        <v>59-64</v>
       </c>
       <c r="F165" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="166">
       <c r="A166">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B166" t="str">
-        <v>Blush Mountain</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C166" t="str">
         <v>Main Area</v>
       </c>
       <c r="D166" t="str">
-        <v>Torkoal</v>
+        <v>Alolan Sandshrew</v>
       </c>
       <c r="E166" t="str">
-        <v>57-62</v>
+        <v>59-64</v>
       </c>
       <c r="F166" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="167">
       <c r="A167">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B167" t="str">
-        <v>Blush Mountain</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C167" t="str">
         <v>Main Area</v>
       </c>
       <c r="D167" t="str">
-        <v>Togedemaru</v>
+        <v>Alolan Vulpix</v>
       </c>
       <c r="E167" t="str">
-        <v>57-62</v>
+        <v>59-64</v>
       </c>
       <c r="F167" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="168">
       <c r="A168">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B168" t="str">
-        <v>Blush Mountain</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C168" t="str">
-        <v>Main Area</v>
+        <v>Abandoned Site</v>
       </c>
       <c r="D168" t="str">
-        <v>Elekid</v>
+        <v>Haunter</v>
       </c>
       <c r="E168" t="str">
-        <v>57-62</v>
+        <v>61-66</v>
       </c>
       <c r="F168" t="str">
-        <v>11.11%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="169">
       <c r="A169">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B169" t="str">
-        <v>Blush Mountain</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C169" t="str">
-        <v>Main Area</v>
+        <v>Abandoned Site</v>
       </c>
       <c r="D169" t="str">
-        <v>Alolan Geodude</v>
+        <v>Klefki</v>
       </c>
       <c r="E169" t="str">
-        <v>57-62</v>
+        <v>61-66</v>
       </c>
       <c r="F169" t="str">
-        <v>11.11%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="170">
       <c r="A170">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B170" t="str">
-        <v>Blush Mountain</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C170" t="str">
-        <v>Main Area</v>
+        <v>Abandoned Site</v>
       </c>
       <c r="D170" t="str">
-        <v>Alolan Graveler</v>
+        <v>Shuppet</v>
       </c>
       <c r="E170" t="str">
-        <v>57-62</v>
+        <v>61-66</v>
       </c>
       <c r="F170" t="str">
-        <v>11.11%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="171">
       <c r="A171">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B171" t="str">
-        <v>Blush Mountain</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C171" t="str">
-        <v>Main Area</v>
+        <v>Abandoned Site</v>
       </c>
       <c r="D171" t="str">
-        <v>Charjabug</v>
+        <v>Boldore</v>
       </c>
       <c r="E171" t="str">
-        <v>57-62</v>
+        <v>61-66</v>
       </c>
       <c r="F171" t="str">
-        <v>11.11%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="172">
       <c r="A172">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B172" t="str">
-        <v>Blush Mountain</v>
+        <v>Captain Acerola</v>
       </c>
       <c r="C172" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D172" t="str">
-        <v>Turtonator</v>
+        <v>Boss</v>
       </c>
       <c r="E172" t="str">
-        <v>57-62</v>
+        <v>63-68</v>
       </c>
       <c r="F172" t="str">
-        <v>11.11%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="173">
       <c r="A173">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B173" t="str">
-        <v>Blush Mountain</v>
+        <v>Kahuna Nanu</v>
       </c>
       <c r="C173" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D173" t="str">
-        <v>Dedenne</v>
+        <v>Boss</v>
       </c>
       <c r="E173" t="str">
-        <v>57-62</v>
+        <v>68-73</v>
       </c>
       <c r="F173" t="str">
-        <v>11.11%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="174">
       <c r="A174">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B174" t="str">
-        <v>Route 13</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C174" t="str">
-        <v>Main Area</v>
+        <v>Main</v>
       </c>
       <c r="D174" t="str">
-        <v>Minior</v>
+        <v>Steenee</v>
       </c>
       <c r="E174" t="str">
-        <v>58-63</v>
+        <v>69-74</v>
       </c>
       <c r="F174" t="str">
-        <v>100.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="175">
       <c r="A175">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B175" t="str">
-        <v>Haina Desert</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C175" t="str">
-        <v>Main Area</v>
+        <v>Main</v>
       </c>
       <c r="D175" t="str">
-        <v>Celesteela</v>
+        <v>Shellos</v>
       </c>
       <c r="E175" t="str">
-        <v>59-64</v>
+        <v>69-74</v>
       </c>
       <c r="F175" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="176">
       <c r="A176">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B176" t="str">
-        <v>Haina Desert</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C176" t="str">
-        <v>Main Area</v>
+        <v>Main</v>
       </c>
       <c r="D176" t="str">
-        <v>Alolan Dugtrio</v>
+        <v>Dhelmise</v>
       </c>
       <c r="E176" t="str">
-        <v>59-64</v>
+        <v>69-74</v>
       </c>
       <c r="F176" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="177">
       <c r="A177">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B177" t="str">
-        <v>Haina Desert</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C177" t="str">
         <v>Main Area</v>
       </c>
       <c r="D177" t="str">
-        <v>Sandile</v>
+        <v>Tentacruel</v>
       </c>
       <c r="E177" t="str">
-        <v>59-64</v>
+        <v>71-76</v>
       </c>
       <c r="F177" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="178">
       <c r="A178">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B178" t="str">
-        <v>Haina Desert</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C178" t="str">
         <v>Main Area</v>
       </c>
       <c r="D178" t="str">
-        <v>Krokorok</v>
+        <v>Lumineon</v>
       </c>
       <c r="E178" t="str">
-        <v>59-64</v>
+        <v>71-76</v>
       </c>
       <c r="F178" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="179">
       <c r="A179">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B179" t="str">
-        <v>Ruins of Abundance</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C179" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D179" t="str">
-        <v>Tapu Bulu</v>
+        <v>Lapras</v>
       </c>
       <c r="E179" t="str">
-        <v>60-65</v>
+        <v>71-76</v>
       </c>
       <c r="F179" t="str">
-        <v>100.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="180">
       <c r="A180">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B180" t="str">
-        <v>Tapu Village</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C180" t="str">
         <v>Main Area</v>
       </c>
       <c r="D180" t="str">
-        <v>Graveler</v>
+        <v>Wimpod</v>
       </c>
       <c r="E180" t="str">
-        <v>62-67</v>
+        <v>72-77</v>
       </c>
       <c r="F180" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="181">
       <c r="A181">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B181" t="str">
-        <v>Tapu Village</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C181" t="str">
         <v>Main Area</v>
       </c>
       <c r="D181" t="str">
-        <v>Bruxish</v>
+        <v>Relicanth</v>
       </c>
       <c r="E181" t="str">
-        <v>62-67</v>
+        <v>72-77</v>
       </c>
       <c r="F181" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="182">
       <c r="A182">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B182" t="str">
-        <v>Tapu Village</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C182" t="str">
         <v>Main Area</v>
       </c>
       <c r="D182" t="str">
-        <v>Absol</v>
+        <v>Wailmer</v>
       </c>
       <c r="E182" t="str">
-        <v>62-67</v>
+        <v>72-77</v>
       </c>
       <c r="F182" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="183">
       <c r="A183">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B183" t="str">
-        <v>Tapu Village</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C183" t="str">
         <v>Main Area</v>
       </c>
       <c r="D183" t="str">
-        <v>Snorunt</v>
+        <v>Carvanha</v>
       </c>
       <c r="E183" t="str">
-        <v>62-67</v>
+        <v>72-77</v>
       </c>
       <c r="F183" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="184">
       <c r="A184">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B184" t="str">
-        <v>Tapu Village</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C184" t="str">
         <v>Main Area</v>
       </c>
       <c r="D184" t="str">
-        <v>Alolan Sandshrew</v>
+        <v>Sharpedo</v>
       </c>
       <c r="E184" t="str">
-        <v>62-67</v>
+        <v>72-77</v>
       </c>
       <c r="F184" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="185">
       <c r="A185">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B185" t="str">
-        <v>Tapu Village</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C185" t="str">
         <v>Main Area</v>
       </c>
       <c r="D185" t="str">
-        <v>Alolan Vulpix</v>
+        <v>Pelipper</v>
       </c>
       <c r="E185" t="str">
-        <v>62-67</v>
+        <v>73-78</v>
       </c>
       <c r="F185" t="str">
         <v>16.67%</v>
@@ -4103,219 +4103,219 @@
     </row>
     <row r="186">
       <c r="A186">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B186" t="str">
-        <v>Route 14</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C186" t="str">
         <v>Main Area</v>
       </c>
       <c r="D186" t="str">
-        <v>Bruxish</v>
+        <v>Pinsir</v>
       </c>
       <c r="E186" t="str">
-        <v>63-68</v>
+        <v>73-78</v>
       </c>
       <c r="F186" t="str">
-        <v>100.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="187">
       <c r="A187">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B187" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C187" t="str">
-        <v>Abandoned Site</v>
+        <v>Main Area</v>
       </c>
       <c r="D187" t="str">
-        <v>Haunter</v>
+        <v>Gastrodon</v>
       </c>
       <c r="E187" t="str">
-        <v>64-69</v>
+        <v>73-78</v>
       </c>
       <c r="F187" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="188">
       <c r="A188">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B188" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C188" t="str">
-        <v>Abandoned Site</v>
+        <v>Main Area</v>
       </c>
       <c r="D188" t="str">
-        <v>Klefki</v>
+        <v>Exeggcute</v>
       </c>
       <c r="E188" t="str">
-        <v>64-69</v>
+        <v>73-78</v>
       </c>
       <c r="F188" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="189">
       <c r="A189">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B189" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C189" t="str">
-        <v>Abandoned Site</v>
+        <v>Main Area</v>
       </c>
       <c r="D189" t="str">
-        <v>Shuppet</v>
+        <v>Tropius</v>
       </c>
       <c r="E189" t="str">
-        <v>64-69</v>
+        <v>73-78</v>
       </c>
       <c r="F189" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="190">
       <c r="A190">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B190" t="str">
-        <v>Captain Acerola</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C190" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D190" t="str">
-        <v>Boss</v>
+        <v>Alolan Exeggutor</v>
       </c>
       <c r="E190" t="str">
-        <v>65-70</v>
+        <v>73-78</v>
       </c>
       <c r="F190" t="str">
-        <v>-</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="191">
       <c r="A191">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B191" t="str">
-        <v>Route 15</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C191" t="str">
-        <v>Main Area</v>
+        <v>Outside</v>
       </c>
       <c r="D191" t="str">
-        <v>Sandygast</v>
+        <v>Machoke</v>
       </c>
       <c r="E191" t="str">
-        <v>66-71</v>
+        <v>75-80</v>
       </c>
       <c r="F191" t="str">
-        <v>100.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="192">
       <c r="A192">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B192" t="str">
-        <v>Route 16</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C192" t="str">
-        <v>Main Area</v>
+        <v>Outside</v>
       </c>
       <c r="D192" t="str">
-        <v>Klefki</v>
+        <v>Mienfoo</v>
       </c>
       <c r="E192" t="str">
-        <v>67-72</v>
+        <v>75-80</v>
       </c>
       <c r="F192" t="str">
-        <v>100.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="193">
       <c r="A193">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B193" t="str">
-        <v>Route 17</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C193" t="str">
-        <v>Northeast</v>
+        <v>Outside</v>
       </c>
       <c r="D193" t="str">
-        <v>Scraggy</v>
+        <v>Jangmo-o</v>
       </c>
       <c r="E193" t="str">
-        <v>68-73</v>
+        <v>75-80</v>
       </c>
       <c r="F193" t="str">
-        <v>50.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="194">
       <c r="A194">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B194" t="str">
-        <v>Route 17</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C194" t="str">
-        <v>Northeast</v>
+        <v>Outside</v>
       </c>
       <c r="D194" t="str">
-        <v>Bisharp</v>
+        <v>Pheromosa</v>
       </c>
       <c r="E194" t="str">
-        <v>68-73</v>
+        <v>75-80</v>
       </c>
       <c r="F194" t="str">
-        <v>50.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="195">
       <c r="A195">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="B195" t="str">
-        <v>Kahuna Nanu</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C195" t="str">
-        <v>Boss Battle</v>
+        <v>Northwest (Hidden Area)</v>
       </c>
       <c r="D195" t="str">
-        <v>Boss</v>
+        <v>Corphish</v>
       </c>
       <c r="E195" t="str">
-        <v>69-74</v>
+        <v>77-82</v>
       </c>
       <c r="F195" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="196">
       <c r="A196">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="B196" t="str">
-        <v>Seafolk Village</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C196" t="str">
-        <v>Main</v>
+        <v>Northwest (Hidden Area)</v>
       </c>
       <c r="D196" t="str">
-        <v>Steenee</v>
+        <v>Dratini</v>
       </c>
       <c r="E196" t="str">
-        <v>70-75</v>
+        <v>77-82</v>
       </c>
       <c r="F196" t="str">
         <v>33.33%</v>
@@ -4323,19 +4323,19 @@
     </row>
     <row r="197">
       <c r="A197">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="B197" t="str">
-        <v>Seafolk Village</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C197" t="str">
-        <v>Main</v>
+        <v>Northwest (Hidden Area)</v>
       </c>
       <c r="D197" t="str">
-        <v>Shellos</v>
+        <v>Golduck</v>
       </c>
       <c r="E197" t="str">
-        <v>70-75</v>
+        <v>77-82</v>
       </c>
       <c r="F197" t="str">
         <v>33.33%</v>
@@ -4343,339 +4343,339 @@
     </row>
     <row r="198">
       <c r="A198">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="B198" t="str">
-        <v>Seafolk Village</v>
+        <v>Captain Kommo-o</v>
       </c>
       <c r="C198" t="str">
-        <v>Main</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D198" t="str">
-        <v>Dhelmise</v>
+        <v>Boss</v>
       </c>
       <c r="E198" t="str">
-        <v>70-75</v>
+        <v>79-84</v>
       </c>
       <c r="F198" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="199">
       <c r="A199">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="B199" t="str">
-        <v>Poni Wilds</v>
+        <v>Captain Mina</v>
       </c>
       <c r="C199" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D199" t="str">
-        <v>Tentacruel</v>
+        <v>Boss</v>
       </c>
       <c r="E199" t="str">
-        <v>71-76</v>
+        <v>80-85</v>
       </c>
       <c r="F199" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="200">
       <c r="A200">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="B200" t="str">
-        <v>Poni Wilds</v>
+        <v>Kahuna Hapu</v>
       </c>
       <c r="C200" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D200" t="str">
-        <v>Lumineon</v>
+        <v>Boss</v>
       </c>
       <c r="E200" t="str">
-        <v>71-76</v>
+        <v>81-86</v>
       </c>
       <c r="F200" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="201">
       <c r="A201">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B201" t="str">
-        <v>Poni Wilds</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C201" t="str">
-        <v>Main Area</v>
+        <v>Cave</v>
       </c>
       <c r="D201" t="str">
-        <v>Lapras</v>
+        <v>Drampa</v>
       </c>
       <c r="E201" t="str">
-        <v>71-76</v>
+        <v>83-88</v>
       </c>
       <c r="F201" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="202">
       <c r="A202">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="B202" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C202" t="str">
-        <v>Main Area</v>
+        <v>Cave</v>
       </c>
       <c r="D202" t="str">
-        <v>Wimpod</v>
+        <v>Glalie</v>
       </c>
       <c r="E202" t="str">
-        <v>72-77</v>
+        <v>83-88</v>
       </c>
       <c r="F202" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="203">
       <c r="A203">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="B203" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C203" t="str">
-        <v>Main Area</v>
+        <v>Cave</v>
       </c>
       <c r="D203" t="str">
-        <v>Relicanth</v>
+        <v>Sneasel</v>
       </c>
       <c r="E203" t="str">
-        <v>72-77</v>
+        <v>83-88</v>
       </c>
       <c r="F203" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="204">
       <c r="A204">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="B204" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C204" t="str">
-        <v>Main Area</v>
+        <v>Cave</v>
       </c>
       <c r="D204" t="str">
-        <v>Wailmer</v>
+        <v>Crabominable</v>
       </c>
       <c r="E204" t="str">
-        <v>72-77</v>
+        <v>83-88</v>
       </c>
       <c r="F204" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="205">
       <c r="A205">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B205" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Alola Pokemon League</v>
       </c>
       <c r="C205" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D205" t="str">
-        <v>Carvanha</v>
+        <v>Boss</v>
       </c>
       <c r="E205" t="str">
-        <v>72-77</v>
+        <v>84-89</v>
       </c>
       <c r="F205" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="206">
       <c r="A206">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="B206" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Champion Hau</v>
       </c>
       <c r="C206" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D206" t="str">
-        <v>Sharpedo</v>
+        <v>Boss</v>
       </c>
       <c r="E206" t="str">
-        <v>72-77</v>
+        <v>85-90</v>
       </c>
       <c r="F206" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="207">
       <c r="A207">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="B207" t="str">
-        <v>Ruins of Hope</v>
+        <v>Route 7</v>
       </c>
       <c r="C207" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D207" t="str">
-        <v>Tapu Fini</v>
+        <v>Staryu</v>
       </c>
       <c r="E207" t="str">
-        <v>74-79</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F207" t="str">
-        <v>100.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="208">
       <c r="A208">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B208" t="str">
-        <v>Exeggutor Island</v>
+        <v>Route 7</v>
       </c>
       <c r="C208" t="str">
         <v>Main Area</v>
       </c>
       <c r="D208" t="str">
-        <v>Pelipper</v>
+        <v>Pyukumuku</v>
       </c>
       <c r="E208" t="str">
-        <v>75-80</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F208" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="209">
       <c r="A209">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B209" t="str">
-        <v>Exeggutor Island</v>
+        <v>Route 7</v>
       </c>
       <c r="C209" t="str">
         <v>Main Area</v>
       </c>
       <c r="D209" t="str">
-        <v>Pinsir</v>
+        <v>Corsola</v>
       </c>
       <c r="E209" t="str">
-        <v>75-80</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F209" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="210">
       <c r="A210">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B210" t="str">
-        <v>Exeggutor Island</v>
+        <v>Route 7</v>
       </c>
       <c r="C210" t="str">
         <v>Main Area</v>
       </c>
       <c r="D210" t="str">
-        <v>Gastrodon</v>
+        <v>Mareanie</v>
       </c>
       <c r="E210" t="str">
-        <v>75-80</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F210" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="211">
       <c r="A211">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B211" t="str">
-        <v>Exeggutor Island</v>
+        <v>Route 7</v>
       </c>
       <c r="C211" t="str">
         <v>Main Area</v>
       </c>
       <c r="D211" t="str">
-        <v>Exeggcute</v>
+        <v>Bruxish</v>
       </c>
       <c r="E211" t="str">
-        <v>75-80</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F211" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="212">
       <c r="A212">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="B212" t="str">
-        <v>Exeggutor Island</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C212" t="str">
-        <v>Main Area</v>
+        <v>Labs</v>
       </c>
       <c r="D212" t="str">
-        <v>Tropius</v>
+        <v>Type: Null</v>
       </c>
       <c r="E212" t="str">
-        <v>75-80</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F212" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="213">
       <c r="A213">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="B213" t="str">
-        <v>Exeggutor Island</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C213" t="str">
-        <v>Main Area</v>
+        <v>Labs</v>
       </c>
       <c r="D213" t="str">
-        <v>Alolan Exeggutor</v>
+        <v>Ditto</v>
       </c>
       <c r="E213" t="str">
-        <v>75-80</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F213" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="214">
       <c r="A214">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="B214" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C214" t="str">
-        <v>Outside</v>
+        <v>Labs</v>
       </c>
       <c r="D214" t="str">
-        <v>Machoke</v>
+        <v>Porygon</v>
       </c>
       <c r="E214" t="str">
-        <v>76-81</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F214" t="str">
         <v>33.33%</v>
@@ -4683,59 +4683,59 @@
     </row>
     <row r="215">
       <c r="A215">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="B215" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Ruins of Conflict</v>
       </c>
       <c r="C215" t="str">
-        <v>Outside</v>
+        <v>Tapu Koko</v>
       </c>
       <c r="D215" t="str">
-        <v>Mienfoo</v>
+        <v>Tapu Koko</v>
       </c>
       <c r="E215" t="str">
-        <v>76-81</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F215" t="str">
-        <v>33.33%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="216">
       <c r="A216">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="B216" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Ruins of Life</v>
       </c>
       <c r="C216" t="str">
-        <v>Outside</v>
+        <v>Tapu Lele</v>
       </c>
       <c r="D216" t="str">
-        <v>Jangmo-o</v>
+        <v>Tapu Lele</v>
       </c>
       <c r="E216" t="str">
-        <v>76-81</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F216" t="str">
-        <v>33.33%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="217">
       <c r="A217">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="B217" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Ruins of Abundance</v>
       </c>
       <c r="C217" t="str">
-        <v>Inside</v>
+        <v>Tapu Bulu</v>
       </c>
       <c r="D217" t="str">
-        <v>Boldore</v>
+        <v>Tapu Bulu</v>
       </c>
       <c r="E217" t="str">
-        <v>77-82</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F217" t="str">
         <v>100.00%</v>
@@ -4743,99 +4743,99 @@
     </row>
     <row r="218">
       <c r="A218">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="B218" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Ruins of Hope</v>
       </c>
       <c r="C218" t="str">
-        <v>Northwest (Hidden Area)</v>
+        <v>Tapu Fini</v>
       </c>
       <c r="D218" t="str">
-        <v>Corphish</v>
+        <v>Tapu Fini</v>
       </c>
       <c r="E218" t="str">
-        <v>78-83</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F218" t="str">
-        <v>33.33%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="219">
       <c r="A219">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="B219" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Lake of the Sunne</v>
       </c>
       <c r="C219" t="str">
-        <v>Northwest (Hidden Area)</v>
+        <v>Special Encounter</v>
       </c>
       <c r="D219" t="str">
-        <v>Dratini</v>
+        <v>Cosmog</v>
       </c>
       <c r="E219" t="str">
-        <v>78-83</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F219" t="str">
-        <v>33.33%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="220">
       <c r="A220">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="B220" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Altar of the Sunne</v>
       </c>
       <c r="C220" t="str">
-        <v>Northwest (Hidden Area)</v>
+        <v>Special Encounter</v>
       </c>
       <c r="D220" t="str">
-        <v>Golduck</v>
+        <v>Solgaleo</v>
       </c>
       <c r="E220" t="str">
-        <v>78-83</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F220" t="str">
-        <v>33.33%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="221">
       <c r="A221">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B221" t="str">
-        <v>Captain Kommo-o</v>
+        <v>Altar of the Moone</v>
       </c>
       <c r="C221" t="str">
-        <v>Boss Battle</v>
+        <v>Special Encounter</v>
       </c>
       <c r="D221" t="str">
-        <v>Boss</v>
+        <v>Lunala</v>
       </c>
       <c r="E221" t="str">
-        <v>79-84</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F221" t="str">
-        <v>-</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="222">
       <c r="A222">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B222" t="str">
-        <v>Altar of the Sunne/Moone</v>
+        <v>Ultra Deep Sea</v>
       </c>
       <c r="C222" t="str">
-        <v>Special Encounter</v>
+        <v>Nihilego</v>
       </c>
       <c r="D222" t="str">
-        <v>Cosmog</v>
+        <v>Nihilego</v>
       </c>
       <c r="E222" t="str">
-        <v>80-85</v>
+        <v>90-100</v>
       </c>
       <c r="F222" t="str">
         <v>100.00%</v>
@@ -4843,187 +4843,187 @@
     </row>
     <row r="223">
       <c r="A223">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B223" t="str">
-        <v>Captain Mina</v>
+        <v>Ultra Jungle</v>
       </c>
       <c r="C223" t="str">
-        <v>Boss Battle</v>
+        <v>Buzzwole</v>
       </c>
       <c r="D223" t="str">
-        <v>Boss</v>
+        <v>Buzzwole</v>
       </c>
       <c r="E223" t="str">
-        <v>81-86</v>
+        <v>90-100</v>
       </c>
       <c r="F223" t="str">
-        <v>-</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="224">
       <c r="A224">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B224" t="str">
-        <v>Kahuna Hapu</v>
+        <v>Ultra Desert</v>
       </c>
       <c r="C224" t="str">
-        <v>Boss Battle</v>
+        <v>Pheromosa</v>
       </c>
       <c r="D224" t="str">
-        <v>Boss</v>
+        <v>Pheromosa</v>
       </c>
       <c r="E224" t="str">
-        <v>82-87</v>
+        <v>90-100</v>
       </c>
       <c r="F224" t="str">
-        <v>-</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="225">
       <c r="A225">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B225" t="str">
-        <v>Mount Lanakila</v>
+        <v>Ultra Plant</v>
       </c>
       <c r="C225" t="str">
-        <v>Cave</v>
+        <v>Xurkitree</v>
       </c>
       <c r="D225" t="str">
-        <v>Drampa</v>
+        <v>Xurkitree</v>
       </c>
       <c r="E225" t="str">
-        <v>83-88</v>
+        <v>90-100</v>
       </c>
       <c r="F225" t="str">
-        <v>25.00%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="226">
       <c r="A226">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B226" t="str">
-        <v>Mount Lanakila</v>
+        <v>Ultra Crater</v>
       </c>
       <c r="C226" t="str">
-        <v>Cave</v>
+        <v>Celesteela</v>
       </c>
       <c r="D226" t="str">
-        <v>Glalie</v>
+        <v>Celesteela</v>
       </c>
       <c r="E226" t="str">
-        <v>83-88</v>
+        <v>90-100</v>
       </c>
       <c r="F226" t="str">
-        <v>25.00%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="227">
       <c r="A227">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B227" t="str">
-        <v>Mount Lanakila</v>
+        <v>Ultra Forest</v>
       </c>
       <c r="C227" t="str">
-        <v>Cave</v>
+        <v>Kartana</v>
       </c>
       <c r="D227" t="str">
-        <v>Sneasel</v>
+        <v>Kartana</v>
       </c>
       <c r="E227" t="str">
-        <v>83-88</v>
+        <v>90-100</v>
       </c>
       <c r="F227" t="str">
-        <v>25.00%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="228">
       <c r="A228">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B228" t="str">
-        <v>Mount Lanakila</v>
+        <v>Ultra Ruin</v>
       </c>
       <c r="C228" t="str">
-        <v>Cave</v>
+        <v>Guzzlord</v>
       </c>
       <c r="D228" t="str">
-        <v>Crabominable</v>
+        <v>Guzzlord</v>
       </c>
       <c r="E228" t="str">
-        <v>83-88</v>
+        <v>90-100</v>
       </c>
       <c r="F228" t="str">
-        <v>25.00%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="229">
       <c r="A229">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B229" t="str">
-        <v>Alola Pokemon League</v>
+        <v>Ultra Megalopolis</v>
       </c>
       <c r="C229" t="str">
-        <v>Boss Battle</v>
+        <v>Poipole</v>
       </c>
       <c r="D229" t="str">
-        <v>Boss</v>
+        <v>Poipole</v>
       </c>
       <c r="E229" t="str">
-        <v>84-89</v>
+        <v>90-100</v>
       </c>
       <c r="F229" t="str">
-        <v>-</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="230">
       <c r="A230">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B230" t="str">
-        <v>Champion Hau</v>
+        <v>Ultra Megalopolis</v>
       </c>
       <c r="C230" t="str">
-        <v>Boss Battle</v>
+        <v>Stakataka</v>
       </c>
       <c r="D230" t="str">
-        <v>Boss</v>
+        <v>Stakataka</v>
       </c>
       <c r="E230" t="str">
-        <v>85-90</v>
+        <v>90-100</v>
       </c>
       <c r="F230" t="str">
-        <v>-</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="231">
       <c r="A231">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B231" t="str">
-        <v>Poni Grove</v>
+        <v>Ultra Megalopolis</v>
       </c>
       <c r="C231" t="str">
-        <v>Main Area</v>
+        <v>Blacephalon</v>
       </c>
       <c r="D231" t="str">
-        <v>Buneary</v>
+        <v>Blacephalon</v>
       </c>
       <c r="E231" t="str">
         <v>90-100</v>
       </c>
       <c r="F231" t="str">
-        <v>14.29%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="232">
       <c r="A232">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B232" t="str">
         <v>Poni Grove</v>
@@ -5032,18 +5032,18 @@
         <v>Main Area</v>
       </c>
       <c r="D232" t="str">
-        <v>Granbull</v>
+        <v>Buneary</v>
       </c>
       <c r="E232" t="str">
         <v>90-100</v>
       </c>
       <c r="F232" t="str">
-        <v>14.29%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="233">
       <c r="A233">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B233" t="str">
         <v>Poni Grove</v>
@@ -5052,18 +5052,18 @@
         <v>Main Area</v>
       </c>
       <c r="D233" t="str">
-        <v>Zoroark</v>
+        <v>Granbull</v>
       </c>
       <c r="E233" t="str">
         <v>90-100</v>
       </c>
       <c r="F233" t="str">
-        <v>14.29%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="234">
       <c r="A234">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B234" t="str">
         <v>Poni Grove</v>
@@ -5072,18 +5072,18 @@
         <v>Main Area</v>
       </c>
       <c r="D234" t="str">
-        <v>Heracross</v>
+        <v>Zoroark</v>
       </c>
       <c r="E234" t="str">
         <v>90-100</v>
       </c>
       <c r="F234" t="str">
-        <v>14.29%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="235">
       <c r="A235">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B235" t="str">
         <v>Poni Grove</v>
@@ -5092,18 +5092,18 @@
         <v>Main Area</v>
       </c>
       <c r="D235" t="str">
-        <v>Riolu</v>
+        <v>Heracross</v>
       </c>
       <c r="E235" t="str">
         <v>90-100</v>
       </c>
       <c r="F235" t="str">
-        <v>14.29%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="236">
       <c r="A236">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B236" t="str">
         <v>Poni Grove</v>
@@ -5112,18 +5112,18 @@
         <v>Main Area</v>
       </c>
       <c r="D236" t="str">
-        <v>Stakataka</v>
+        <v>Riolu</v>
       </c>
       <c r="E236" t="str">
         <v>90-100</v>
       </c>
       <c r="F236" t="str">
-        <v>14.29%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="237">
       <c r="A237">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B237" t="str">
         <v>Poni Grove</v>
@@ -5132,98 +5132,98 @@
         <v>Main Area</v>
       </c>
       <c r="D237" t="str">
-        <v>Blacephalon</v>
+        <v>Stakataka</v>
       </c>
       <c r="E237" t="str">
         <v>90-100</v>
       </c>
       <c r="F237" t="str">
-        <v>14.29%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="238">
       <c r="A238">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B238" t="str">
-        <v>Poni Plains</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C238" t="str">
-        <v>Center</v>
+        <v>Main Area</v>
       </c>
       <c r="D238" t="str">
-        <v>Hariyama</v>
+        <v>Blacephalon</v>
       </c>
       <c r="E238" t="str">
         <v>90-100</v>
       </c>
       <c r="F238" t="str">
-        <v>50.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="239">
       <c r="A239">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B239" t="str">
-        <v>Poni Plains</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C239" t="str">
-        <v>Center</v>
+        <v>Main Area</v>
       </c>
       <c r="D239" t="str">
-        <v>Mudsdale</v>
+        <v>Hariyama</v>
       </c>
       <c r="E239" t="str">
         <v>90-100</v>
       </c>
       <c r="F239" t="str">
-        <v>50.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="240">
       <c r="A240">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B240" t="str">
-        <v>Resolution Cave</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C240" t="str">
         <v>Main Area</v>
       </c>
       <c r="D240" t="str">
-        <v>Noivern</v>
+        <v>Mudsdale</v>
       </c>
       <c r="E240" t="str">
         <v>90-100</v>
       </c>
       <c r="F240" t="str">
-        <v>33.33%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="241">
       <c r="A241">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B241" t="str">
-        <v>Resolution Cave</v>
+        <v>Poni Plains</v>
       </c>
       <c r="C241" t="str">
-        <v>Main Area</v>
+        <v>Center</v>
       </c>
       <c r="D241" t="str">
-        <v>Druddigon</v>
+        <v>Special Encounter</v>
       </c>
       <c r="E241" t="str">
         <v>90-100</v>
       </c>
       <c r="F241" t="str">
-        <v>33.33%</v>
+        <v>100%</v>
       </c>
     </row>
     <row r="242">
       <c r="A242">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B242" t="str">
         <v>Resolution Cave</v>
@@ -5232,7 +5232,7 @@
         <v>Main Area</v>
       </c>
       <c r="D242" t="str">
-        <v>Guzzlord</v>
+        <v>Noivern</v>
       </c>
       <c r="E242" t="str">
         <v>90-100</v>
@@ -5243,374 +5243,114 @@
     </row>
     <row r="243">
       <c r="A243">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B243" t="str">
-        <v>Mahalo Trail</v>
+        <v>Resolution Cave</v>
       </c>
       <c r="C243" t="str">
         <v>Main Area</v>
       </c>
       <c r="D243" t="str">
-        <v>Solgaleo</v>
+        <v>Druddigon</v>
       </c>
       <c r="E243" t="str">
         <v>90-100</v>
       </c>
       <c r="F243" t="str">
-        <v>50.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="244">
       <c r="A244">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B244" t="str">
-        <v>Mahalo Trail</v>
+        <v>Resolution Cave</v>
       </c>
       <c r="C244" t="str">
         <v>Main Area</v>
       </c>
       <c r="D244" t="str">
-        <v>Lunala</v>
+        <v>Guzzlord</v>
       </c>
       <c r="E244" t="str">
         <v>90-100</v>
       </c>
       <c r="F244" t="str">
-        <v>50.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="245">
       <c r="A245">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B245" t="str">
-        <v>Melemele Meadow</v>
+        <v>Shopping Mall Antiquities</v>
       </c>
       <c r="C245" t="str">
-        <v>Main Area</v>
+        <v>Event</v>
       </c>
       <c r="D245" t="str">
-        <v>Caterpie</v>
+        <v>Magearna</v>
       </c>
       <c r="E245" t="str">
         <v>90-100</v>
       </c>
       <c r="F245" t="str">
-        <v>12.50%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="246">
       <c r="A246">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B246" t="str">
-        <v>Melemele Meadow</v>
+        <v>Ten Carat Hill</v>
       </c>
       <c r="C246" t="str">
-        <v>Main Area</v>
+        <v>Deepest Cave</v>
       </c>
       <c r="D246" t="str">
-        <v>Metapod</v>
+        <v>Special Encounter</v>
       </c>
       <c r="E246" t="str">
         <v>90-100</v>
       </c>
       <c r="F246" t="str">
-        <v>12.50%</v>
+        <v>100%</v>
       </c>
     </row>
     <row r="247">
       <c r="A247">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B247" t="str">
-        <v>Melemele Meadow</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C247" t="str">
-        <v>Main Area</v>
+        <v>Secret Lab</v>
       </c>
       <c r="D247" t="str">
-        <v>Cutiefly</v>
+        <v>Zeraora</v>
       </c>
       <c r="E247" t="str">
         <v>90-100</v>
       </c>
       <c r="F247" t="str">
-        <v>12.50%</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248">
-        <v>83</v>
-      </c>
-      <c r="B248" t="str">
-        <v>Melemele Meadow</v>
-      </c>
-      <c r="C248" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D248" t="str">
-        <v>Butterfree</v>
-      </c>
-      <c r="E248" t="str">
-        <v>90-100</v>
-      </c>
-      <c r="F248" t="str">
-        <v>12.50%</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249">
-        <v>83</v>
-      </c>
-      <c r="B249" t="str">
-        <v>Melemele Meadow</v>
-      </c>
-      <c r="C249" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D249" t="str">
-        <v>Flabébé</v>
-      </c>
-      <c r="E249" t="str">
-        <v>90-100</v>
-      </c>
-      <c r="F249" t="str">
-        <v>12.50%</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250">
-        <v>83</v>
-      </c>
-      <c r="B250" t="str">
-        <v>Melemele Meadow</v>
-      </c>
-      <c r="C250" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D250" t="str">
-        <v>Petilil</v>
-      </c>
-      <c r="E250" t="str">
-        <v>90-100</v>
-      </c>
-      <c r="F250" t="str">
-        <v>12.50%</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251">
-        <v>83</v>
-      </c>
-      <c r="B251" t="str">
-        <v>Melemele Meadow</v>
-      </c>
-      <c r="C251" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D251" t="str">
-        <v>Cottonee</v>
-      </c>
-      <c r="E251" t="str">
-        <v>90-100</v>
-      </c>
-      <c r="F251" t="str">
-        <v>12.50%</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252">
-        <v>83</v>
-      </c>
-      <c r="B252" t="str">
-        <v>Melemele Meadow</v>
-      </c>
-      <c r="C252" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D252" t="str">
-        <v>Buzzwole</v>
-      </c>
-      <c r="E252" t="str">
-        <v>90-100</v>
-      </c>
-      <c r="F252" t="str">
-        <v>12.50%</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253">
-        <v>84</v>
-      </c>
-      <c r="B253" t="str">
-        <v>Ultra Space Wilds</v>
-      </c>
-      <c r="C253" t="str">
-        <v>Wormholes</v>
-      </c>
-      <c r="D253" t="str">
-        <v>Poipole</v>
-      </c>
-      <c r="E253" t="str">
-        <v>90-100</v>
-      </c>
-      <c r="F253" t="str">
-        <v>20.00%</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254">
-        <v>84</v>
-      </c>
-      <c r="B254" t="str">
-        <v>Ultra Space Wilds</v>
-      </c>
-      <c r="C254" t="str">
-        <v>Wormholes</v>
-      </c>
-      <c r="D254" t="str">
-        <v>Xurkitree</v>
-      </c>
-      <c r="E254" t="str">
-        <v>90-100</v>
-      </c>
-      <c r="F254" t="str">
-        <v>20.00%</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255">
-        <v>84</v>
-      </c>
-      <c r="B255" t="str">
-        <v>Ultra Space Wilds</v>
-      </c>
-      <c r="C255" t="str">
-        <v>Wormholes</v>
-      </c>
-      <c r="D255" t="str">
-        <v>Celesteela</v>
-      </c>
-      <c r="E255" t="str">
-        <v>90-100</v>
-      </c>
-      <c r="F255" t="str">
-        <v>20.00%</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256">
-        <v>84</v>
-      </c>
-      <c r="B256" t="str">
-        <v>Ultra Space Wilds</v>
-      </c>
-      <c r="C256" t="str">
-        <v>Wormholes</v>
-      </c>
-      <c r="D256" t="str">
-        <v>Kartana</v>
-      </c>
-      <c r="E256" t="str">
-        <v>90-100</v>
-      </c>
-      <c r="F256" t="str">
-        <v>20.00%</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257">
-        <v>84</v>
-      </c>
-      <c r="B257" t="str">
-        <v>Ultra Space Wilds</v>
-      </c>
-      <c r="C257" t="str">
-        <v>Wormholes</v>
-      </c>
-      <c r="D257" t="str">
-        <v>Guzzlord</v>
-      </c>
-      <c r="E257" t="str">
-        <v>90-100</v>
-      </c>
-      <c r="F257" t="str">
-        <v>20.00%</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258">
-        <v>85</v>
-      </c>
-      <c r="B258" t="str">
-        <v>Event: Magearna</v>
-      </c>
-      <c r="C258" t="str">
-        <v>Special Encounter</v>
-      </c>
-      <c r="D258" t="str">
-        <v>Magearna</v>
-      </c>
-      <c r="E258" t="str">
-        <v>90-100</v>
-      </c>
-      <c r="F258" t="str">
-        <v>100.00%</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259">
-        <v>86</v>
-      </c>
-      <c r="B259" t="str">
-        <v>Event: Marshadow</v>
-      </c>
-      <c r="C259" t="str">
-        <v>Special Encounter</v>
-      </c>
-      <c r="D259" t="str">
-        <v>Marshadow</v>
-      </c>
-      <c r="E259" t="str">
-        <v>90-100</v>
-      </c>
-      <c r="F259" t="str">
-        <v>100.00%</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260">
-        <v>87</v>
-      </c>
-      <c r="B260" t="str">
-        <v>Event: Zeraora</v>
-      </c>
-      <c r="C260" t="str">
-        <v>Special Encounter</v>
-      </c>
-      <c r="D260" t="str">
-        <v>Zeraora</v>
-      </c>
-      <c r="E260" t="str">
-        <v>90-100</v>
-      </c>
-      <c r="F260" t="str">
         <v>100.00%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F260"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F247"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C93"/>
+  <dimension ref="A1:C78"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5639,7 +5379,7 @@
         <v>Challenge 2</v>
       </c>
       <c r="B3" t="str">
-        <v>Defeat 5 Pokemon in Starter Professor Kukui</v>
+        <v>Defeat 10 Pokemon in Starter Professor Kukui</v>
       </c>
       <c r="C3" t="str">
         <v>Route 1 East</v>
@@ -5650,7 +5390,7 @@
         <v>Challenge 3</v>
       </c>
       <c r="B4" t="str">
-        <v>Defeat 5 Pokemon in Route 1 East</v>
+        <v>Defeat 10 Pokemon in Route 1 East</v>
       </c>
       <c r="C4" t="str">
         <v>Route 1 Hau'oli Outskirts</v>
@@ -5661,10 +5401,10 @@
         <v>Challenge 4</v>
       </c>
       <c r="B5" t="str">
-        <v>Defeat 5 Pokemon in Route 1 Hau'oli Outskirts</v>
+        <v>Defeat 10 Pokemon in Route 1 Hau'oli Outskirts</v>
       </c>
       <c r="C5" t="str">
-        <v>Route 1 South</v>
+        <v>Hau'oli City Shopping District</v>
       </c>
     </row>
     <row r="6">
@@ -5672,10 +5412,10 @@
         <v>Challenge 5</v>
       </c>
       <c r="B6" t="str">
-        <v>Defeat 5 Pokemon in Route 1 South</v>
+        <v>Defeat 10 Pokemon in Hau'oli City Shopping District</v>
       </c>
       <c r="C6" t="str">
-        <v>Route 1 Trainers' School</v>
+        <v>Route 2 North</v>
       </c>
     </row>
     <row r="7">
@@ -5683,10 +5423,10 @@
         <v>Challenge 6</v>
       </c>
       <c r="B7" t="str">
-        <v>Defeat 5 Pokemon in Route 1 Trainers' School</v>
+        <v>Defeat 10 Pokemon in Route 2 North</v>
       </c>
       <c r="C7" t="str">
-        <v>Hau'oli City Beachfront</v>
+        <v>Captain Ilima</v>
       </c>
     </row>
     <row r="8">
@@ -5694,10 +5434,10 @@
         <v>Challenge 7</v>
       </c>
       <c r="B8" t="str">
-        <v>Defeat 5 Pokemon in Hau'oli City Beachfront</v>
+        <v>Defeat Captain Ilima</v>
       </c>
       <c r="C8" t="str">
-        <v>Hau'oli City Shopping District</v>
+        <v>Hau'oli Cemetery Main Area</v>
       </c>
     </row>
     <row r="9">
@@ -5705,10 +5445,10 @@
         <v>Challenge 8</v>
       </c>
       <c r="B9" t="str">
-        <v>Defeat 5 Pokemon in Hau'oli City Shopping District</v>
+        <v>Defeat 10 Pokemon in Hau'oli Cemetery Main Area</v>
       </c>
       <c r="C9" t="str">
-        <v>Route 2 Main</v>
+        <v>Ten Carat Hill Farthest Hollow</v>
       </c>
     </row>
     <row r="10">
@@ -5716,10 +5456,10 @@
         <v>Challenge 9</v>
       </c>
       <c r="B10" t="str">
-        <v>Defeat 5 Pokemon in Route 2 Main</v>
+        <v>Defeat 10 Pokemon in Ten Carat Hill Farthest Hollow</v>
       </c>
       <c r="C10" t="str">
-        <v>Route 2 North</v>
+        <v>Seaward Cave Main Area</v>
       </c>
     </row>
     <row r="11">
@@ -5727,10 +5467,10 @@
         <v>Challenge 10</v>
       </c>
       <c r="B11" t="str">
-        <v>Defeat 5 Pokemon in Route 2 North</v>
+        <v>Defeat 10 Pokemon in Seaward Cave Main Area</v>
       </c>
       <c r="C11" t="str">
-        <v>Captain Ilima</v>
+        <v>Route 3 North</v>
       </c>
     </row>
     <row r="12">
@@ -5738,10 +5478,10 @@
         <v>Challenge 11</v>
       </c>
       <c r="B12" t="str">
-        <v>Defeat Captain Ilima</v>
+        <v>Defeat 10 Pokemon in Route 3 North</v>
       </c>
       <c r="C12" t="str">
-        <v>Hau'oli Cemetery Main Area</v>
+        <v>Kahuna Hala</v>
       </c>
     </row>
     <row r="13">
@@ -5749,10 +5489,10 @@
         <v>Challenge 12</v>
       </c>
       <c r="B13" t="str">
-        <v>Defeat 5 Pokemon in Hau'oli Cemetery Main Area</v>
+        <v>Defeat Kahuna Hala</v>
       </c>
       <c r="C13" t="str">
-        <v>Verdant Cavern Trial Site</v>
+        <v>Heahea Beach Main Area Part 1</v>
       </c>
     </row>
     <row r="14">
@@ -5760,10 +5500,10 @@
         <v>Challenge 13</v>
       </c>
       <c r="B14" t="str">
-        <v>Defeat 5 Pokemon in Verdant Cavern Trial Site</v>
+        <v>Defeat Kahuna Hala</v>
       </c>
       <c r="C14" t="str">
-        <v>Ten Carat Hill Inside</v>
+        <v>Heahea Beach Main Area Part 2</v>
       </c>
     </row>
     <row r="15">
@@ -5771,10 +5511,10 @@
         <v>Challenge 14</v>
       </c>
       <c r="B15" t="str">
-        <v>Defeat 5 Pokemon in Ten Carat Hill Inside</v>
+        <v>Defeat 10 Pokemon in Heahea Beach Main Area Part 2</v>
       </c>
       <c r="C15" t="str">
-        <v>Ten Carat Hill Farthest Hollow</v>
+        <v>Paniola Ranch Main Area</v>
       </c>
     </row>
     <row r="16">
@@ -5782,10 +5522,10 @@
         <v>Challenge 15</v>
       </c>
       <c r="B16" t="str">
-        <v>Defeat 5 Pokemon in Ten Carat Hill Farthest Hollow</v>
+        <v>Defeat 10 Pokemon in Paniola Ranch Main Area</v>
       </c>
       <c r="C16" t="str">
-        <v>Seaward Cave Main Area</v>
+        <v>Daycare NPC</v>
       </c>
     </row>
     <row r="17">
@@ -5793,10 +5533,10 @@
         <v>Challenge 16</v>
       </c>
       <c r="B17" t="str">
-        <v>Defeat 5 Pokemon in Seaward Cave Main Area</v>
+        <v>Interact with Daycare</v>
       </c>
       <c r="C17" t="str">
-        <v>Route 3 North</v>
+        <v>Route 5 Main Area</v>
       </c>
     </row>
     <row r="18">
@@ -5804,10 +5544,10 @@
         <v>Challenge 17</v>
       </c>
       <c r="B18" t="str">
-        <v>Defeat 5 Pokemon in Route 3 North</v>
+        <v>Defeat 10 Pokemon in Route 5 Main Area</v>
       </c>
       <c r="C18" t="str">
-        <v>Ruins of Conflict Special Encounter</v>
+        <v>Brooklet Hill South</v>
       </c>
     </row>
     <row r="19">
@@ -5815,10 +5555,10 @@
         <v>Challenge 18</v>
       </c>
       <c r="B19" t="str">
-        <v>Defeat 5 Pokemon in Ruins of Conflict Special Encounter</v>
+        <v>Defeat 10 Pokemon in Brooklet Hill South</v>
       </c>
       <c r="C19" t="str">
-        <v>Kahuna Hala</v>
+        <v>Captain Lana</v>
       </c>
     </row>
     <row r="20">
@@ -5826,10 +5566,10 @@
         <v>Challenge 19</v>
       </c>
       <c r="B20" t="str">
-        <v>Defeat Kahuna Hala</v>
+        <v>Defeat Captain Lana</v>
       </c>
       <c r="C20" t="str">
-        <v>Heahea Beach Main Area</v>
+        <v>Wela Volcano Park Main Area</v>
       </c>
     </row>
     <row r="21">
@@ -5837,10 +5577,10 @@
         <v>Challenge 20</v>
       </c>
       <c r="B21" t="str">
-        <v>Defeat 5 Pokemon in Heahea Beach Main Area</v>
+        <v>Defeat 10 Pokemon in Wela Volcano Park Main Area</v>
       </c>
       <c r="C21" t="str">
-        <v>Route 4 Main Area</v>
+        <v>Captain Kiawe</v>
       </c>
     </row>
     <row r="22">
@@ -5848,10 +5588,10 @@
         <v>Challenge 21</v>
       </c>
       <c r="B22" t="str">
-        <v>Defeat 5 Pokemon in Route 4 Main Area</v>
+        <v>Defeat Captain Kiawe</v>
       </c>
       <c r="C22" t="str">
-        <v>Paniola Ranch Main Area</v>
+        <v>Route 7 Main Area</v>
       </c>
     </row>
     <row r="23">
@@ -5859,10 +5599,10 @@
         <v>Challenge 22</v>
       </c>
       <c r="B23" t="str">
-        <v>Defeat 5 Pokemon in Paniola Ranch Main Area</v>
+        <v>Defeat 10 Pokemon in Route 7 Main Area</v>
       </c>
       <c r="C23" t="str">
-        <v>Daycare NPC</v>
+        <v>Route 8 Fossil Restoration Center Part 1</v>
       </c>
     </row>
     <row r="24">
@@ -5870,10 +5610,10 @@
         <v>Challenge 23</v>
       </c>
       <c r="B24" t="str">
-        <v>Interact with Daycare</v>
+        <v>Defeat 10 Pokemon in Route 8 Fossil Restoration Center Part 1</v>
       </c>
       <c r="C24" t="str">
-        <v>Route 5 Main Area</v>
+        <v>Route 8 Fossil Restoration Center Part 2</v>
       </c>
     </row>
     <row r="25">
@@ -5881,10 +5621,10 @@
         <v>Challenge 24</v>
       </c>
       <c r="B25" t="str">
-        <v>Defeat 5 Pokemon in Route 5 Main Area</v>
+        <v>Defeat 10 Pokemon in Route 8 Fossil Restoration Center Part 2</v>
       </c>
       <c r="C25" t="str">
-        <v>Brooklet Hill North</v>
+        <v>Lush Jungle North</v>
       </c>
     </row>
     <row r="26">
@@ -5892,10 +5632,10 @@
         <v>Challenge 25</v>
       </c>
       <c r="B26" t="str">
-        <v>Defeat 5 Pokemon in Brooklet Hill North</v>
+        <v>Defeat 10 Pokemon in Lush Jungle North</v>
       </c>
       <c r="C26" t="str">
-        <v>Brooklet Hill South</v>
+        <v>Lush Jungle East Cave</v>
       </c>
     </row>
     <row r="27">
@@ -5903,10 +5643,10 @@
         <v>Challenge 26</v>
       </c>
       <c r="B27" t="str">
-        <v>Defeat 5 Pokemon in Brooklet Hill South</v>
+        <v>Defeat 10 Pokemon in Lush Jungle East Cave</v>
       </c>
       <c r="C27" t="str">
-        <v>Captain Lana</v>
+        <v>Captain Mallow</v>
       </c>
     </row>
     <row r="28">
@@ -5914,10 +5654,10 @@
         <v>Challenge 27</v>
       </c>
       <c r="B28" t="str">
-        <v>Defeat Captain Lana</v>
+        <v>Defeat Captain Mallow</v>
       </c>
       <c r="C28" t="str">
-        <v>Wela Volcano Park Main Area</v>
+        <v>Diglett's Tunnel Main Area</v>
       </c>
     </row>
     <row r="29">
@@ -5925,10 +5665,10 @@
         <v>Challenge 28</v>
       </c>
       <c r="B29" t="str">
-        <v>Defeat 5 Pokemon in Wela Volcano Park Main Area</v>
+        <v>Defeat 10 Pokemon in Diglett's Tunnel Main Area</v>
       </c>
       <c r="C29" t="str">
-        <v>Captain Kiawe</v>
+        <v>Akala Outskirts Main Area</v>
       </c>
     </row>
     <row r="30">
@@ -5936,10 +5676,10 @@
         <v>Challenge 29</v>
       </c>
       <c r="B30" t="str">
-        <v>Defeat Captain Kiawe</v>
+        <v>Defeat 10 Pokemon in Akala Outskirts Main Area</v>
       </c>
       <c r="C30" t="str">
-        <v>Route 7 Main Area</v>
+        <v>Kahuna Olivia</v>
       </c>
     </row>
     <row r="31">
@@ -5947,10 +5687,10 @@
         <v>Challenge 30</v>
       </c>
       <c r="B31" t="str">
-        <v>Defeat 5 Pokemon in Route 7 Main Area</v>
+        <v>Defeat 10 Pokemon in Kahuna Olivia</v>
       </c>
       <c r="C31" t="str">
-        <v>Route 8 Main</v>
+        <v>Malie City Outer Cape</v>
       </c>
     </row>
     <row r="32">
@@ -5958,10 +5698,10 @@
         <v>Challenge 31</v>
       </c>
       <c r="B32" t="str">
-        <v>Defeat 5 Pokemon in Route 8 Main</v>
+        <v>Defeat 10 Pokemon in Malie City Outer Cape</v>
       </c>
       <c r="C32" t="str">
-        <v>Route 8 Fossil Restoration Center Part 1</v>
+        <v>Route 10 Main Area</v>
       </c>
     </row>
     <row r="33">
@@ -5969,10 +5709,10 @@
         <v>Challenge 32</v>
       </c>
       <c r="B33" t="str">
-        <v>Defeat 5 Pokemon in Route 8 Fossil Restoration Center Part 1</v>
+        <v>Defeat 10 Pokemon in Route 10 Main Area</v>
       </c>
       <c r="C33" t="str">
-        <v>Route 8 Fossil Restoration Center Part 2</v>
+        <v>Mount Hokulani East</v>
       </c>
     </row>
     <row r="34">
@@ -5980,10 +5720,10 @@
         <v>Challenge 33</v>
       </c>
       <c r="B34" t="str">
-        <v>Defeat 5 Pokemon in Route 8 Fossil Restoration Center Part 2</v>
+        <v>Defeat 10 Pokemon in Mount Hokulani East</v>
       </c>
       <c r="C34" t="str">
-        <v>Lush Jungle North</v>
+        <v>Captain Sophocles</v>
       </c>
     </row>
     <row r="35">
@@ -5991,10 +5731,10 @@
         <v>Challenge 34</v>
       </c>
       <c r="B35" t="str">
-        <v>Defeat 5 Pokemon in Lush Jungle North</v>
+        <v>Defeat Captain Sophocles</v>
       </c>
       <c r="C35" t="str">
-        <v>Lush Jungle East Cave</v>
+        <v>Route 11 Main Area</v>
       </c>
     </row>
     <row r="36">
@@ -6002,10 +5742,10 @@
         <v>Challenge 35</v>
       </c>
       <c r="B36" t="str">
-        <v>Defeat 5 Pokemon in Lush Jungle East Cave</v>
+        <v>Defeat 10 Pokemon in Route 11 Main Area</v>
       </c>
       <c r="C36" t="str">
-        <v>Captain Mallow</v>
+        <v>Blush Mountain Main Area</v>
       </c>
     </row>
     <row r="37">
@@ -6013,10 +5753,10 @@
         <v>Challenge 36</v>
       </c>
       <c r="B37" t="str">
-        <v>Defeat Captain Mallow</v>
+        <v>Defeat 10 Pokemon in Blush Mountain Main Area</v>
       </c>
       <c r="C37" t="str">
-        <v>Diglett's Tunnel Main Area</v>
+        <v>Haina Desert Main Area</v>
       </c>
     </row>
     <row r="38">
@@ -6024,10 +5764,10 @@
         <v>Challenge 37</v>
       </c>
       <c r="B38" t="str">
-        <v>Defeat 5 Pokemon in Diglett's Tunnel Main Area</v>
+        <v>Defeat 10 Pokemon in Haina Desert Main Area</v>
       </c>
       <c r="C38" t="str">
-        <v>Route 9 Main Area</v>
+        <v>Tapu Village Main Area</v>
       </c>
     </row>
     <row r="39">
@@ -6035,10 +5775,10 @@
         <v>Challenge 38</v>
       </c>
       <c r="B39" t="str">
-        <v>Defeat 5 Pokemon in Route 9 Main Area</v>
+        <v>Defeat 10 Pokemon in Tapu Village Main Area</v>
       </c>
       <c r="C39" t="str">
-        <v>Konikoni City Main Area</v>
+        <v>Thrifty Megamart Abandoned Site</v>
       </c>
     </row>
     <row r="40">
@@ -6046,10 +5786,10 @@
         <v>Challenge 39</v>
       </c>
       <c r="B40" t="str">
-        <v>Defeat 5 Pokemon in Konikoni City Main Area</v>
+        <v>Defeat 10 Pokemon in Thrifty Megamart Abandoned Site</v>
       </c>
       <c r="C40" t="str">
-        <v>Memorial Hill Main</v>
+        <v>Captain Acerola</v>
       </c>
     </row>
     <row r="41">
@@ -6057,10 +5797,10 @@
         <v>Challenge 40</v>
       </c>
       <c r="B41" t="str">
-        <v>Defeat 5 Pokemon in Memorial Hill Main</v>
+        <v>Defeat 10 Pokemon in Captain Acerola</v>
       </c>
       <c r="C41" t="str">
-        <v>Akala Outskirts Main Area</v>
+        <v>Kahuna Nanu</v>
       </c>
     </row>
     <row r="42">
@@ -6068,10 +5808,10 @@
         <v>Challenge 41</v>
       </c>
       <c r="B42" t="str">
-        <v>Defeat 5 Pokemon in Akala Outskirts Main Area</v>
+        <v>Defeat Kahuna Nanu</v>
       </c>
       <c r="C42" t="str">
-        <v>Ruins of Life Special Encounter</v>
+        <v>Seafolk Village Main</v>
       </c>
     </row>
     <row r="43">
@@ -6079,10 +5819,10 @@
         <v>Challenge 42</v>
       </c>
       <c r="B43" t="str">
-        <v>Defeat 5 Pokemon in Ruins of Life Special Encounter</v>
+        <v>Defeat 10 Pokemon in Seafolk Village Main</v>
       </c>
       <c r="C43" t="str">
-        <v>Kahuna Olivia</v>
+        <v>Poni Wilds Main Area</v>
       </c>
     </row>
     <row r="44">
@@ -6090,10 +5830,10 @@
         <v>Challenge 43</v>
       </c>
       <c r="B44" t="str">
-        <v>Defeat Kahuna Olivia</v>
+        <v>Defeat 10 Pokemon in Poni Wilds Main Area</v>
       </c>
       <c r="C44" t="str">
-        <v>Hano Beach Main Area</v>
+        <v>Poni Breaker Coast Main Area</v>
       </c>
     </row>
     <row r="45">
@@ -6101,10 +5841,10 @@
         <v>Challenge 44</v>
       </c>
       <c r="B45" t="str">
-        <v>Defeat 5 Pokemon in Hano Beach Main Area</v>
+        <v>Defeat 10 Pokemon in Poni Breaker Coast Main Area</v>
       </c>
       <c r="C45" t="str">
-        <v>Aether Paradise Special Encounter</v>
+        <v>Exeggutor Island Main Area</v>
       </c>
     </row>
     <row r="46">
@@ -6112,10 +5852,10 @@
         <v>Challenge 45</v>
       </c>
       <c r="B46" t="str">
-        <v>Defeat 5 Pokemon in Aether Paradise Special Encounter</v>
+        <v>Defeat 10 Pokemon in Exeggutor Island Main Area</v>
       </c>
       <c r="C46" t="str">
-        <v>Malie City Outer Cape</v>
+        <v>Vast Poni Canyon Outside</v>
       </c>
     </row>
     <row r="47">
@@ -6123,10 +5863,10 @@
         <v>Challenge 46</v>
       </c>
       <c r="B47" t="str">
-        <v>Defeat 5 Pokemon in Malie City Outer Cape</v>
+        <v>Defeat 10 Pokemon in Vast Poni Canyon Outside</v>
       </c>
       <c r="C47" t="str">
-        <v>Malie Garden Main Area</v>
+        <v>Vast Poni Canyon Northwest (Hidden Area)</v>
       </c>
     </row>
     <row r="48">
@@ -6134,10 +5874,10 @@
         <v>Challenge 47</v>
       </c>
       <c r="B48" t="str">
-        <v>Defeat 5 Pokemon in Malie Garden Main Area</v>
+        <v>Defeat 10 Pokemon in Vast Poni Canyon Northwest (Hidden Area)</v>
       </c>
       <c r="C48" t="str">
-        <v>Route 10 Main Area</v>
+        <v>Captain Kommo-o</v>
       </c>
     </row>
     <row r="49">
@@ -6145,10 +5885,10 @@
         <v>Challenge 48</v>
       </c>
       <c r="B49" t="str">
-        <v>Defeat 5 Pokemon in Route 10 Main Area</v>
+        <v>Defeat Captain Kommo-o</v>
       </c>
       <c r="C49" t="str">
-        <v>Mount Hokulani East</v>
+        <v>Captain Mina</v>
       </c>
     </row>
     <row r="50">
@@ -6156,10 +5896,10 @@
         <v>Challenge 49</v>
       </c>
       <c r="B50" t="str">
-        <v>Defeat 5 Pokemon in Mount Hokulani East</v>
+        <v>Defeat Captain Mina</v>
       </c>
       <c r="C50" t="str">
-        <v>Captain Sophocles</v>
+        <v>Kahuna Hapu</v>
       </c>
     </row>
     <row r="51">
@@ -6167,10 +5907,10 @@
         <v>Challenge 50</v>
       </c>
       <c r="B51" t="str">
-        <v>Defeat Captain Sophocles</v>
+        <v>Defeat Kahuna Hapu</v>
       </c>
       <c r="C51" t="str">
-        <v>Route 11 Main Area</v>
+        <v>Mount Lanakila Cave</v>
       </c>
     </row>
     <row r="52">
@@ -6178,10 +5918,10 @@
         <v>Challenge 51</v>
       </c>
       <c r="B52" t="str">
-        <v>Defeat 5 Pokemon in Route 11 Main Area</v>
+        <v>Defeat 10 Pokemon in Mount Lanakila Cave</v>
       </c>
       <c r="C52" t="str">
-        <v>Route 12 Main Area</v>
+        <v>Alola Pokemon League</v>
       </c>
     </row>
     <row r="53">
@@ -6189,462 +5929,297 @@
         <v>Challenge 52</v>
       </c>
       <c r="B53" t="str">
-        <v>Defeat 5 Pokemon in Route 12 Main Area</v>
+        <v>Defeat Alola Pokemon League</v>
       </c>
       <c r="C53" t="str">
-        <v>Blush Mountain Main Area</v>
+        <v>Champion Hau</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Challenge 53</v>
+        <v>Extra Challenge $1-1</v>
       </c>
       <c r="B54" t="str">
-        <v>Defeat 5 Pokemon in Blush Mountain Main Area</v>
+        <v>Defeat Kahuna Olivia</v>
       </c>
       <c r="C54" t="str">
-        <v>Route 13 Main Area</v>
+        <v>Route 7 Main Area</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Challenge 54</v>
+        <v>Extra Challenge $1-2</v>
       </c>
       <c r="B55" t="str">
-        <v>Defeat 5 Pokemon in Route 13 Main Area</v>
+        <v>Defeat 15 Pokemon in Route 7</v>
       </c>
       <c r="C55" t="str">
-        <v>Haina Desert Main Area</v>
+        <v>Aether Paradise Labs</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Challenge 55</v>
+        <v>Extra Challenge $2-1</v>
       </c>
       <c r="B56" t="str">
-        <v>Defeat 5 Pokemon in Haina Desert Main Area</v>
+        <v>Defeat 15 Pokemon in Route 3 North</v>
       </c>
       <c r="C56" t="str">
-        <v>Ruins of Abundance Special Encounter</v>
+        <v>Ruins of Conflict Tapu Koko</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Challenge 56</v>
+        <v>Extra Challenge $2-2</v>
       </c>
       <c r="B57" t="str">
-        <v>Defeat 5 Pokemon in Ruins of Abundance Special Encounter</v>
+        <v>Defeat 15 Pokemon in Akala Outskirts</v>
       </c>
       <c r="C57" t="str">
-        <v>Tapu Village Main Area</v>
+        <v>Ruins of Life Tapu Lele</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Challenge 57</v>
+        <v>Extra Challenge $3-1</v>
       </c>
       <c r="B58" t="str">
-        <v>Defeat 5 Pokemon in Tapu Village Main Area</v>
+        <v>Defeat Kahuna Nanu</v>
       </c>
       <c r="C58" t="str">
-        <v>Route 14 Main Area</v>
+        <v>Ruins of Abundance Tapu Bulu</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Challenge 58</v>
+        <v>Extra Challenge $3-2</v>
       </c>
       <c r="B59" t="str">
-        <v>Defeat 5 Pokemon in Route 14 Main Area</v>
+        <v>Defeat 15 Pokemon in Poni Breaker Coast</v>
       </c>
       <c r="C59" t="str">
-        <v>Thrifty Megamart Abandoned Site</v>
+        <v>Ruins of Hope Tapu Fini</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Challenge 59</v>
+        <v>Extra Challenge $4-1</v>
       </c>
       <c r="B60" t="str">
-        <v>Defeat 5 Pokemon in Thrifty Megamart Abandoned Site</v>
+        <v>Defeat Captain Kommo-o</v>
       </c>
       <c r="C60" t="str">
-        <v>Captain Acerola</v>
+        <v>Lake of the Sunne Special Encounter</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Challenge 60</v>
+        <v>Extra Challenge $4-2</v>
       </c>
       <c r="B61" t="str">
-        <v>Defeat Captain Acerola</v>
+        <v>Defeat 10 Pokemon in Lake of the Sunne</v>
       </c>
       <c r="C61" t="str">
-        <v>Route 15 Main Area</v>
+        <v>Altar of the Sunne Special Encounter</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Challenge 61</v>
+        <v>Extra Challenge $4-3</v>
       </c>
       <c r="B62" t="str">
-        <v>Defeat 5 Pokemon in Route 15 Main Area</v>
+        <v>Defeat 10 Pokemon in Altar of the Sunne</v>
       </c>
       <c r="C62" t="str">
-        <v>Route 16 Main Area</v>
+        <v>Altar of the Moone Special Encounter</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Challenge 62</v>
+        <v>Extra Challenge $5-1</v>
       </c>
       <c r="B63" t="str">
-        <v>Defeat 5 Pokemon in Route 16 Main Area</v>
+        <v>Defeat Champion Hau</v>
       </c>
       <c r="C63" t="str">
-        <v>Route 17 Northeast</v>
+        <v>Ultra Deep Sea Nihilego</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Challenge 63</v>
+        <v>Extra Challenge $5-2</v>
       </c>
       <c r="B64" t="str">
-        <v>Defeat 5 Pokemon in Route 17 Northeast</v>
+        <v>Defeat 10 Pokemon in Ultra Deep Sea</v>
       </c>
       <c r="C64" t="str">
-        <v>Kahuna Nanu</v>
+        <v>Ultra Jungle Buzzwole</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Challenge 64</v>
+        <v>Extra Challenge $5-3</v>
       </c>
       <c r="B65" t="str">
-        <v>Defeat Kahuna Nanu</v>
+        <v>Defeat 10 Pokemon in Ultra Jungle</v>
       </c>
       <c r="C65" t="str">
-        <v>Seafolk Village Main</v>
+        <v>Ultra Desert Pheromosa</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Challenge 65</v>
+        <v>Extra Challenge $5-4</v>
       </c>
       <c r="B66" t="str">
-        <v>Defeat 5 Pokemon in Seafolk Village Main</v>
+        <v>Defeat 10 Pokemon in Ultra Desert</v>
       </c>
       <c r="C66" t="str">
-        <v>Poni Wilds Main Area</v>
+        <v>Ultra Plant Xurkitree</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Challenge 66</v>
+        <v>Extra Challenge $5-5</v>
       </c>
       <c r="B67" t="str">
-        <v>Defeat 5 Pokemon in Poni Wilds Main Area</v>
+        <v>Defeat 10 Pokemon in Ultra Plant</v>
       </c>
       <c r="C67" t="str">
-        <v>Poni Breaker Coast Main Area</v>
+        <v>Ultra Crater Celesteela</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Challenge 67</v>
+        <v>Extra Challenge $5-6</v>
       </c>
       <c r="B68" t="str">
-        <v>Defeat 5 Pokemon in Poni Breaker Coast Main Area</v>
+        <v>Defeat 10 Pokemon in Ultra Crater</v>
       </c>
       <c r="C68" t="str">
-        <v>Ruins of Hope Special Encounter</v>
+        <v>Ultra Forest Kartana</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Challenge 68</v>
+        <v>Extra Challenge $5-7</v>
       </c>
       <c r="B69" t="str">
-        <v>Defeat 5 Pokemon in Ruins of Hope Special Encounter</v>
+        <v>Defeat 10 Pokemon in Ultra Forest</v>
       </c>
       <c r="C69" t="str">
-        <v>Exeggutor Island Main Area</v>
+        <v>Ultra Ruin Guzzlord</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Challenge 69</v>
+        <v>Extra Challenge $5-8</v>
       </c>
       <c r="B70" t="str">
-        <v>Defeat 5 Pokemon in Exeggutor Island Main Area</v>
+        <v>Defeat 10 Pokemon in Ultra Ruin</v>
       </c>
       <c r="C70" t="str">
-        <v>Vast Poni Canyon Outside</v>
+        <v>Ultra Megalopolis Poipole</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Challenge 70</v>
+        <v>Extra Challenge $5-9</v>
       </c>
       <c r="B71" t="str">
-        <v>Defeat 5 Pokemon in Vast Poni Canyon Outside</v>
+        <v>Defeat 10 Pokemon in Ultra Megalopolis Poipole</v>
       </c>
       <c r="C71" t="str">
-        <v>Vast Poni Canyon Inside</v>
+        <v>Ultra Megalopolis Stakataka</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Challenge 71</v>
+        <v>Extra Challenge $5-10</v>
       </c>
       <c r="B72" t="str">
-        <v>Defeat 5 Pokemon in Vast Poni Canyon Inside</v>
+        <v>Defeat 10 Pokemon in Ultra Megalopolis Stakataka</v>
       </c>
       <c r="C72" t="str">
-        <v>Vast Poni Canyon Northwest (Hidden Area)</v>
+        <v>Ultra Megalopolis Blacephalon</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Challenge 72</v>
+        <v>Extra Challenge $6-1</v>
       </c>
       <c r="B73" t="str">
-        <v>Defeat 5 Pokemon in Vast Poni Canyon Northwest (Hidden Area)</v>
+        <v>Defeat Champion Hau</v>
       </c>
       <c r="C73" t="str">
-        <v>Captain Kommo-o</v>
+        <v>Poni Grove Main Area</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Challenge 73</v>
+        <v>Extra Challenge $6-2</v>
       </c>
       <c r="B74" t="str">
-        <v>Defeat Captain Kommo-o</v>
+        <v>Defeat 15 Pokemon in Poni Grove Main Area</v>
       </c>
       <c r="C74" t="str">
-        <v>Altar of the Sunne/Moone Special Encounter</v>
+        <v>Poni Plains Center</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Challenge 74</v>
+        <v>Extra Challenge $6-3</v>
       </c>
       <c r="B75" t="str">
-        <v>Defeat 5 Pokemon in Altar of the Sunne/Moone Special Encounter</v>
+        <v>Defeat 15 Pokemon in Poni Plains Center</v>
       </c>
       <c r="C75" t="str">
-        <v>Captain Mina</v>
+        <v>Resolution Cave Main Area</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Challenge 75</v>
+        <v>Extra Challenge $6-4</v>
       </c>
       <c r="B76" t="str">
-        <v>Defeat Captain Mina</v>
+        <v>Defeat 15 Pokemon in Resolution Cave Main Area</v>
       </c>
       <c r="C76" t="str">
-        <v>Kahuna Hapu</v>
+        <v>Shopping Mall Antiquities Event</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Challenge 76</v>
+        <v>Extra Challenge $6-5</v>
       </c>
       <c r="B77" t="str">
-        <v>Defeat Kahuna Hapu</v>
+        <v>Defeat 15 Pokemon in Shopping Mall Antiquities Event</v>
       </c>
       <c r="C77" t="str">
-        <v>Mount Lanakila Cave</v>
+        <v>Ten Carat Hill Deepest Cave</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Challenge 77</v>
+        <v>Extra Challenge $6-6</v>
       </c>
       <c r="B78" t="str">
-        <v>Defeat 5 Pokemon in Mount Lanakila Cave</v>
+        <v>Defeat 15 Pokemon in Ten Carat Hill Deepest Cave</v>
       </c>
       <c r="C78" t="str">
-        <v>Alola Pokemon League</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v>Challenge 78</v>
-      </c>
-      <c r="B79" t="str">
-        <v>Defeat Alola Pokemon League</v>
-      </c>
-      <c r="C79" t="str">
-        <v>Champion Hau</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v>Extra Challenge $1-1</v>
-      </c>
-      <c r="B80" t="str">
-        <v>Collect 10 Zygarde Cells</v>
-      </c>
-      <c r="C80" t="str">
-        <v>Zygarde 10% Forme</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v>Extra Challenge $1-2</v>
-      </c>
-      <c r="B81" t="str">
-        <v>Collect 50 Zygarde Cells</v>
-      </c>
-      <c r="C81" t="str">
-        <v>Zygarde 50% Forme</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v>Extra Challenge $1-3</v>
-      </c>
-      <c r="B82" t="str">
-        <v>Collect 100 Zygarde Cells</v>
-      </c>
-      <c r="C82" t="str">
-        <v>Zygarde Complete Forme</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v>Extra Challenge $2-1</v>
-      </c>
-      <c r="B83" t="str">
-        <v>Collect 20 Totem Stickers</v>
-      </c>
-      <c r="C83" t="str">
-        <v>Totem Gumshoos/Raticate</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>Extra Challenge $2-2</v>
-      </c>
-      <c r="B84" t="str">
-        <v>Collect 50 Totem Stickers</v>
-      </c>
-      <c r="C84" t="str">
-        <v>Totem Lurantis/Salazzle</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>Extra Challenge $2-3</v>
-      </c>
-      <c r="B85" t="str">
-        <v>Collect 100 Totem Stickers</v>
-      </c>
-      <c r="C85" t="str">
-        <v>Totem Kommo-o/Ribombee</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>Extra Challenge $3-1</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Catch Tapu Koko</v>
-      </c>
-      <c r="C86" t="str">
-        <v>Electric Seed</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>Extra Challenge $3-2</v>
-      </c>
-      <c r="B87" t="str">
-        <v>Catch Tapu Lele</v>
-      </c>
-      <c r="C87" t="str">
-        <v>Psychic Seed</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v>Extra Challenge $3-3</v>
-      </c>
-      <c r="B88" t="str">
-        <v>Catch Tapu Bulu</v>
-      </c>
-      <c r="C88" t="str">
-        <v>Grassy Seed</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v>Extra Challenge $3-4</v>
-      </c>
-      <c r="B89" t="str">
-        <v>Catch Tapu Fini</v>
-      </c>
-      <c r="C89" t="str">
-        <v>Misty Seed</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v>Extra Challenge $4-1</v>
-      </c>
-      <c r="B90" t="str">
-        <v>Defeat Champion Hau</v>
-      </c>
-      <c r="C90" t="str">
-        <v>Poni Grove Main Area</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v>Extra Challenge $4-2</v>
-      </c>
-      <c r="B91" t="str">
-        <v>Defeat 15 Pokemon in Poni Grove Main Area</v>
-      </c>
-      <c r="C91" t="str">
-        <v>Poni Plains Center</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v>Extra Challenge $4-3</v>
-      </c>
-      <c r="B92" t="str">
-        <v>Defeat 15 Pokemon in Poni Plains Center</v>
-      </c>
-      <c r="C92" t="str">
-        <v>Resolution Cave Main Area</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>Extra Challenge $4-4</v>
-      </c>
-      <c r="B93" t="str">
-        <v>Defeat 15 Pokemon in Resolution Cave Main Area</v>
-      </c>
-      <c r="C93" t="str">
-        <v>Ultra Space Wilds</v>
+        <v>Aether Paradise Secret Lab</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C93"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C78"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6668,7 +6243,7 @@
         <v>Electric</v>
       </c>
       <c r="C2" t="str">
-        <v>Route 1</v>
+        <v>Route 1 East</v>
       </c>
       <c r="D2" t="str">
         <v>Yes (Added)</v>
@@ -6682,7 +6257,7 @@
         <v>Electric/Psychic</v>
       </c>
       <c r="C3" t="str">
-        <v>Route 1</v>
+        <v>Route 1 East</v>
       </c>
       <c r="D3" t="str">
         <v>Yes (Evolution)</v>
@@ -6696,7 +6271,7 @@
         <v>Fire/Electric/Psychic/Ghost</v>
       </c>
       <c r="C4" t="str">
-        <v>Route 3</v>
+        <v>Route 3 North</v>
       </c>
       <c r="D4" t="str">
         <v>Yes (Added)</v>
@@ -6710,7 +6285,7 @@
         <v>Rock</v>
       </c>
       <c r="C5" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Ten Carat Hill Inside</v>
       </c>
       <c r="D5" t="str">
         <v>Yes (Added)</v>
@@ -6724,7 +6299,7 @@
         <v>Water</v>
       </c>
       <c r="C6" t="str">
-        <v>Route 7</v>
+        <v>Route 7 Main Area</v>
       </c>
       <c r="D6" t="str">
         <v>Yes (Added)</v>
@@ -6738,7 +6313,7 @@
         <v>Water</v>
       </c>
       <c r="C7" t="str">
-        <v>Route 7</v>
+        <v>Route 7 Main Area</v>
       </c>
       <c r="D7" t="str">
         <v>Yes (Added)</v>
@@ -6752,7 +6327,7 @@
         <v>Grass</v>
       </c>
       <c r="C8" t="str">
-        <v>Lush Jungle</v>
+        <v>Lush Jungle North</v>
       </c>
       <c r="D8" t="str">
         <v>Yes (Added)</v>
@@ -6766,7 +6341,7 @@
         <v>Normal/Psychic</v>
       </c>
       <c r="C9" t="str">
-        <v>Lush Jungle</v>
+        <v>Lush Jungle East Cave</v>
       </c>
       <c r="D9" t="str">
         <v>Yes (Added)</v>
@@ -6780,7 +6355,7 @@
         <v>Fighting</v>
       </c>
       <c r="C10" t="str">
-        <v>Lush Jungle</v>
+        <v>Lush Jungle East Cave</v>
       </c>
       <c r="D10" t="str">
         <v>Yes (Added)</v>
@@ -6794,10 +6369,10 @@
         <v>Water/Rock</v>
       </c>
       <c r="C11" t="str">
-        <v>Route 9</v>
+        <v>Route 7 Main Area</v>
       </c>
       <c r="D11" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes (Relocated)</v>
       </c>
     </row>
     <row r="12">
@@ -6808,10 +6383,10 @@
         <v>Poison/Water</v>
       </c>
       <c r="C12" t="str">
-        <v>Route 9</v>
+        <v>Route 7 Main Area</v>
       </c>
       <c r="D12" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes (Relocated)</v>
       </c>
     </row>
     <row r="13">
@@ -6822,7 +6397,7 @@
         <v>Rock/Flying</v>
       </c>
       <c r="C13" t="str">
-        <v>Route 13</v>
+        <v>Mount Hokulani East</v>
       </c>
       <c r="D13" t="str">
         <v>Yes (Added)</v>
@@ -6836,7 +6411,7 @@
         <v>Water/Psychic</v>
       </c>
       <c r="C14" t="str">
-        <v>Route 14</v>
+        <v>Route 14 Main Area</v>
       </c>
       <c r="D14" t="str">
         <v>Yes (Added)</v>
@@ -6850,7 +6425,7 @@
         <v>Ghost/Ground</v>
       </c>
       <c r="C15" t="str">
-        <v>Route 15</v>
+        <v>Route 15 Main Area</v>
       </c>
       <c r="D15" t="str">
         <v>Yes (Added)</v>
@@ -6864,7 +6439,7 @@
         <v>Steel/Fairy</v>
       </c>
       <c r="C16" t="str">
-        <v>Route 16</v>
+        <v>Route 16 Main Area</v>
       </c>
       <c r="D16" t="str">
         <v>Yes (Added)</v>
@@ -6878,7 +6453,7 @@
         <v>Fighting/Ice</v>
       </c>
       <c r="C17" t="str">
-        <v>Mount Lanakila</v>
+        <v>Mount Lanakila Cave</v>
       </c>
       <c r="D17" t="str">
         <v>Yes (Added)</v>
@@ -6892,10 +6467,10 @@
         <v>Normal</v>
       </c>
       <c r="C18" t="str">
-        <v>Aether Paradise</v>
+        <v>Aether Paradise Labs</v>
       </c>
       <c r="D18" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes (Added to Extra)</v>
       </c>
     </row>
     <row r="19">
@@ -6906,7 +6481,7 @@
         <v>Normal</v>
       </c>
       <c r="C19" t="str">
-        <v>Aether Paradise</v>
+        <v>Aether Paradise Labs</v>
       </c>
       <c r="D19" t="str">
         <v>Yes (Evolution)</v>
@@ -6920,10 +6495,10 @@
         <v>Normal</v>
       </c>
       <c r="C20" t="str">
-        <v>Aether Paradise</v>
+        <v>Aether Paradise Labs</v>
       </c>
       <c r="D20" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes (Added to Extra)</v>
       </c>
     </row>
     <row r="21">
@@ -6934,10 +6509,10 @@
         <v>Normal</v>
       </c>
       <c r="C21" t="str">
-        <v>Aether Paradise</v>
+        <v>Aether Paradise Labs</v>
       </c>
       <c r="D21" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes (Added to Extra)</v>
       </c>
     </row>
     <row r="22">
@@ -6951,7 +6526,7 @@
         <v>Ruins of Conflict</v>
       </c>
       <c r="D22" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes (Added to Extra)</v>
       </c>
     </row>
     <row r="23">
@@ -6965,7 +6540,7 @@
         <v>Ruins of Life</v>
       </c>
       <c r="D23" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes (Added to Extra)</v>
       </c>
     </row>
     <row r="24">
@@ -6979,7 +6554,7 @@
         <v>Ruins of Abundance</v>
       </c>
       <c r="D24" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes (Added to Extra)</v>
       </c>
     </row>
     <row r="25">
@@ -6993,7 +6568,7 @@
         <v>Ruins of Hope</v>
       </c>
       <c r="D25" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes (Added to Extra)</v>
       </c>
     </row>
     <row r="26">
@@ -7004,10 +6579,10 @@
         <v>Psychic</v>
       </c>
       <c r="C26" t="str">
-        <v>Altar of the Sunne/Moone</v>
+        <v>Lake of the Sunne</v>
       </c>
       <c r="D26" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes (Added to Extra)</v>
       </c>
     </row>
     <row r="27">
@@ -7018,7 +6593,7 @@
         <v>Psychic</v>
       </c>
       <c r="C27" t="str">
-        <v>Altar of the Sunne/Moone</v>
+        <v>Lake of the Sunne</v>
       </c>
       <c r="D27" t="str">
         <v>Yes (Evolution)</v>
@@ -7032,10 +6607,10 @@
         <v>Poison</v>
       </c>
       <c r="C28" t="str">
-        <v>Ultra Space Wilds</v>
+        <v>Ultra Megalopolis</v>
       </c>
       <c r="D28" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes (Added to Extra)</v>
       </c>
     </row>
     <row r="29">
@@ -7046,7 +6621,7 @@
         <v>Poison/Dragon</v>
       </c>
       <c r="C29" t="str">
-        <v>Ultra Space Wilds</v>
+        <v>Ultra Megalopolis</v>
       </c>
       <c r="D29" t="str">
         <v>Yes (Evolution)</v>
@@ -7054,63 +6629,49 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Xurkitree</v>
+        <v>Magearna</v>
       </c>
       <c r="B30" t="str">
-        <v>Electric</v>
+        <v>Steel/Fairy</v>
       </c>
       <c r="C30" t="str">
-        <v>Ultra Space Wilds</v>
+        <v>Shopping Mall Antiquities Event</v>
       </c>
       <c r="D30" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes (Added to Extra)</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Magearna</v>
+        <v>Marshadow</v>
       </c>
       <c r="B31" t="str">
-        <v>Steel/Fairy</v>
+        <v>Ghost/Fighting</v>
       </c>
       <c r="C31" t="str">
-        <v>Event: Magearna</v>
+        <v>Ten Carat Hill Deepest Cave</v>
       </c>
       <c r="D31" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes (Added to Extra)</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Marshadow</v>
+        <v>Zeraora</v>
       </c>
       <c r="B32" t="str">
-        <v>Ghost/Fighting</v>
+        <v>Electric</v>
       </c>
       <c r="C32" t="str">
-        <v>Event: Marshadow</v>
+        <v>Aether Paradise Secret Lab</v>
       </c>
       <c r="D32" t="str">
-        <v>Yes (Added)</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>Zeraora</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Electric</v>
-      </c>
-      <c r="C33" t="str">
-        <v>Event: Zeraora</v>
-      </c>
-      <c r="D33" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes (Added to Extra)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D32"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Alola_Paths_and_Challenges.xlsx
+++ b/Alola_Paths_and_Challenges.xlsx
@@ -1078,7 +1078,7 @@
         <v>14-19</v>
       </c>
       <c r="F34" t="str">
-        <v>14.29%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="35">
@@ -1098,7 +1098,7 @@
         <v>14-19</v>
       </c>
       <c r="F35" t="str">
-        <v>14.29%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="36">
@@ -1118,7 +1118,7 @@
         <v>14-19</v>
       </c>
       <c r="F36" t="str">
-        <v>14.29%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="37">
@@ -1132,13 +1132,13 @@
         <v>Farthest Hollow</v>
       </c>
       <c r="D37" t="str">
-        <v>Necrozma</v>
+        <v>Mawile</v>
       </c>
       <c r="E37" t="str">
         <v>14-19</v>
       </c>
       <c r="F37" t="str">
-        <v>14.29%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="38">
@@ -1152,13 +1152,13 @@
         <v>Farthest Hollow</v>
       </c>
       <c r="D38" t="str">
-        <v>Mawile</v>
+        <v>Lycanroc</v>
       </c>
       <c r="E38" t="str">
         <v>14-19</v>
       </c>
       <c r="F38" t="str">
-        <v>14.29%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="39">
@@ -1172,33 +1172,33 @@
         <v>Farthest Hollow</v>
       </c>
       <c r="D39" t="str">
-        <v>Lycanroc</v>
+        <v>Marshadow</v>
       </c>
       <c r="E39" t="str">
         <v>14-19</v>
       </c>
       <c r="F39" t="str">
-        <v>14.29%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B40" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Seaward Cave</v>
       </c>
       <c r="C40" t="str">
-        <v>Farthest Hollow</v>
+        <v>Main Area</v>
       </c>
       <c r="D40" t="str">
-        <v>Marshadow</v>
+        <v>Barboach</v>
       </c>
       <c r="E40" t="str">
-        <v>14-19</v>
+        <v>15-20</v>
       </c>
       <c r="F40" t="str">
-        <v>14.29%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="41">
@@ -1212,7 +1212,7 @@
         <v>Main Area</v>
       </c>
       <c r="D41" t="str">
-        <v>Barboach</v>
+        <v>Smoochum</v>
       </c>
       <c r="E41" t="str">
         <v>15-20</v>
@@ -1232,7 +1232,7 @@
         <v>Main Area</v>
       </c>
       <c r="D42" t="str">
-        <v>Smoochum</v>
+        <v>Seel</v>
       </c>
       <c r="E42" t="str">
         <v>15-20</v>
@@ -1243,22 +1243,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B43" t="str">
-        <v>Seaward Cave</v>
+        <v>Route 3</v>
       </c>
       <c r="C43" t="str">
-        <v>Main Area</v>
+        <v>North</v>
       </c>
       <c r="D43" t="str">
-        <v>Seel</v>
+        <v>Mankey</v>
       </c>
       <c r="E43" t="str">
-        <v>15-20</v>
+        <v>17-22</v>
       </c>
       <c r="F43" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="44">
@@ -1272,7 +1272,7 @@
         <v>North</v>
       </c>
       <c r="D44" t="str">
-        <v>Mankey</v>
+        <v>Delibird</v>
       </c>
       <c r="E44" t="str">
         <v>17-22</v>
@@ -1292,7 +1292,7 @@
         <v>North</v>
       </c>
       <c r="D45" t="str">
-        <v>Delibird</v>
+        <v>Bagon</v>
       </c>
       <c r="E45" t="str">
         <v>17-22</v>
@@ -1312,7 +1312,7 @@
         <v>North</v>
       </c>
       <c r="D46" t="str">
-        <v>Bagon</v>
+        <v>Oricorio</v>
       </c>
       <c r="E46" t="str">
         <v>17-22</v>
@@ -1332,7 +1332,7 @@
         <v>North</v>
       </c>
       <c r="D47" t="str">
-        <v>Oricorio</v>
+        <v>Igglybuff</v>
       </c>
       <c r="E47" t="str">
         <v>17-22</v>
@@ -1343,42 +1343,42 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B48" t="str">
-        <v>Route 3</v>
+        <v>Kahuna Hala</v>
       </c>
       <c r="C48" t="str">
-        <v>North</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D48" t="str">
-        <v>Igglybuff</v>
+        <v>Boss</v>
       </c>
       <c r="E48" t="str">
-        <v>17-22</v>
+        <v>18-23</v>
       </c>
       <c r="F48" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B49" t="str">
-        <v>Kahuna Hala</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C49" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D49" t="str">
-        <v>Boss</v>
+        <v>Vikavolt</v>
       </c>
       <c r="E49" t="str">
-        <v>18-23</v>
+        <v>19-24</v>
       </c>
       <c r="F49" t="str">
-        <v>-</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="50">
@@ -1392,7 +1392,7 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D50" t="str">
-        <v>Vikavolt</v>
+        <v>Ribombee</v>
       </c>
       <c r="E50" t="str">
         <v>19-24</v>
@@ -1412,7 +1412,7 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D51" t="str">
-        <v>Ribombee</v>
+        <v>Araquanid</v>
       </c>
       <c r="E51" t="str">
         <v>19-24</v>
@@ -1432,7 +1432,7 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D52" t="str">
-        <v>Araquanid</v>
+        <v>Lurantis</v>
       </c>
       <c r="E52" t="str">
         <v>19-24</v>
@@ -1452,7 +1452,7 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D53" t="str">
-        <v>Lurantis</v>
+        <v>Salazzle</v>
       </c>
       <c r="E53" t="str">
         <v>19-24</v>
@@ -1472,7 +1472,7 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D54" t="str">
-        <v>Salazzle</v>
+        <v>Alolan Marowak</v>
       </c>
       <c r="E54" t="str">
         <v>19-24</v>
@@ -1492,7 +1492,7 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D55" t="str">
-        <v>Alolan Marowak</v>
+        <v>Kommo-o</v>
       </c>
       <c r="E55" t="str">
         <v>19-24</v>
@@ -1512,7 +1512,7 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D56" t="str">
-        <v>Kommo-o</v>
+        <v>Mimikyu</v>
       </c>
       <c r="E56" t="str">
         <v>19-24</v>
@@ -1532,7 +1532,7 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D57" t="str">
-        <v>Mimikyu</v>
+        <v>Poliwhirl</v>
       </c>
       <c r="E57" t="str">
         <v>19-24</v>
@@ -1543,42 +1543,42 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B58" t="str">
         <v>Heahea Beach</v>
       </c>
       <c r="C58" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area Part 2</v>
       </c>
       <c r="D58" t="str">
-        <v>Poliwhirl</v>
+        <v>Ditto</v>
       </c>
       <c r="E58" t="str">
         <v>19-24</v>
       </c>
       <c r="F58" t="str">
-        <v>11.11%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B59" t="str">
-        <v>Heahea Beach</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C59" t="str">
-        <v>Main Area Part 2</v>
+        <v>Main Area</v>
       </c>
       <c r="D59" t="str">
-        <v>Ditto</v>
+        <v>Eevee</v>
       </c>
       <c r="E59" t="str">
-        <v>19-24</v>
+        <v>21-26</v>
       </c>
       <c r="F59" t="str">
-        <v>100.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="60">
@@ -1592,7 +1592,7 @@
         <v>Main Area</v>
       </c>
       <c r="D60" t="str">
-        <v>Eevee</v>
+        <v>Mareep</v>
       </c>
       <c r="E60" t="str">
         <v>21-26</v>
@@ -1612,7 +1612,7 @@
         <v>Main Area</v>
       </c>
       <c r="D61" t="str">
-        <v>Mareep</v>
+        <v>Tauros</v>
       </c>
       <c r="E61" t="str">
         <v>21-26</v>
@@ -1632,7 +1632,7 @@
         <v>Main Area</v>
       </c>
       <c r="D62" t="str">
-        <v>Tauros</v>
+        <v>Miltank</v>
       </c>
       <c r="E62" t="str">
         <v>21-26</v>
@@ -1643,42 +1643,42 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B63" t="str">
-        <v>Paniola Ranch</v>
+        <v>Daycare</v>
       </c>
       <c r="C63" t="str">
-        <v>Main Area</v>
+        <v>NPC</v>
       </c>
       <c r="D63" t="str">
-        <v>Miltank</v>
+        <v>NPC</v>
       </c>
       <c r="E63" t="str">
-        <v>21-26</v>
+        <v>-</v>
       </c>
       <c r="F63" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B64" t="str">
-        <v>Daycare</v>
+        <v>Route 5</v>
       </c>
       <c r="C64" t="str">
-        <v>NPC</v>
+        <v>Main Area</v>
       </c>
       <c r="D64" t="str">
-        <v>NPC</v>
+        <v>Noibat</v>
       </c>
       <c r="E64" t="str">
-        <v>-</v>
+        <v>23-28</v>
       </c>
       <c r="F64" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="65">
@@ -1692,7 +1692,7 @@
         <v>Main Area</v>
       </c>
       <c r="D65" t="str">
-        <v>Noibat</v>
+        <v>Fomantis</v>
       </c>
       <c r="E65" t="str">
         <v>23-28</v>
@@ -1712,7 +1712,7 @@
         <v>Main Area</v>
       </c>
       <c r="D66" t="str">
-        <v>Fomantis</v>
+        <v>Bounsweet</v>
       </c>
       <c r="E66" t="str">
         <v>23-28</v>
@@ -1723,22 +1723,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B67" t="str">
-        <v>Route 5</v>
+        <v>Brooklet Hill</v>
       </c>
       <c r="C67" t="str">
-        <v>Main Area</v>
+        <v>South</v>
       </c>
       <c r="D67" t="str">
-        <v>Bounsweet</v>
+        <v>Wingull</v>
       </c>
       <c r="E67" t="str">
-        <v>23-28</v>
+        <v>25-30</v>
       </c>
       <c r="F67" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="68">
@@ -1752,7 +1752,7 @@
         <v>South</v>
       </c>
       <c r="D68" t="str">
-        <v>Wingull</v>
+        <v>Lillipup</v>
       </c>
       <c r="E68" t="str">
         <v>25-30</v>
@@ -1772,7 +1772,7 @@
         <v>South</v>
       </c>
       <c r="D69" t="str">
-        <v>Lillipup</v>
+        <v>Paras</v>
       </c>
       <c r="E69" t="str">
         <v>25-30</v>
@@ -1792,7 +1792,7 @@
         <v>South</v>
       </c>
       <c r="D70" t="str">
-        <v>Paras</v>
+        <v>Goldeen</v>
       </c>
       <c r="E70" t="str">
         <v>25-30</v>
@@ -1812,7 +1812,7 @@
         <v>South</v>
       </c>
       <c r="D71" t="str">
-        <v>Goldeen</v>
+        <v>Feebas</v>
       </c>
       <c r="E71" t="str">
         <v>25-30</v>
@@ -1823,42 +1823,42 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B72" t="str">
-        <v>Brooklet Hill</v>
+        <v>Captain Lana</v>
       </c>
       <c r="C72" t="str">
-        <v>South</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D72" t="str">
-        <v>Feebas</v>
+        <v>Boss</v>
       </c>
       <c r="E72" t="str">
-        <v>25-30</v>
+        <v>26-31</v>
       </c>
       <c r="F72" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B73" t="str">
-        <v>Captain Lana</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C73" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D73" t="str">
-        <v>Boss</v>
+        <v>Cubone</v>
       </c>
       <c r="E73" t="str">
-        <v>26-31</v>
+        <v>27-32</v>
       </c>
       <c r="F73" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="74">
@@ -1872,13 +1872,13 @@
         <v>Main Area</v>
       </c>
       <c r="D74" t="str">
-        <v>Cubone</v>
+        <v>Kangaskhan</v>
       </c>
       <c r="E74" t="str">
         <v>27-32</v>
       </c>
       <c r="F74" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="75">
@@ -1892,73 +1892,73 @@
         <v>Main Area</v>
       </c>
       <c r="D75" t="str">
-        <v>Kangaskhan</v>
+        <v>Magby</v>
       </c>
       <c r="E75" t="str">
         <v>27-32</v>
       </c>
       <c r="F75" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B76" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Captain Kiawe</v>
       </c>
       <c r="C76" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D76" t="str">
-        <v>Magby</v>
+        <v>Boss</v>
       </c>
       <c r="E76" t="str">
-        <v>27-32</v>
+        <v>29-34</v>
       </c>
       <c r="F76" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B77" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Route 7</v>
       </c>
       <c r="C77" t="str">
         <v>Main Area</v>
       </c>
       <c r="D77" t="str">
-        <v>Nihilego</v>
+        <v>Staryu</v>
       </c>
       <c r="E77" t="str">
-        <v>27-32</v>
+        <v>30-35</v>
       </c>
       <c r="F77" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B78" t="str">
-        <v>Captain Kiawe</v>
+        <v>Route 7</v>
       </c>
       <c r="C78" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D78" t="str">
-        <v>Boss</v>
+        <v>Pyukumuku</v>
       </c>
       <c r="E78" t="str">
-        <v>29-34</v>
+        <v>30-35</v>
       </c>
       <c r="F78" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="79">
@@ -1972,7 +1972,7 @@
         <v>Main Area</v>
       </c>
       <c r="D79" t="str">
-        <v>Staryu</v>
+        <v>Corsola</v>
       </c>
       <c r="E79" t="str">
         <v>30-35</v>
@@ -1992,7 +1992,7 @@
         <v>Main Area</v>
       </c>
       <c r="D80" t="str">
-        <v>Pyukumuku</v>
+        <v>Mareanie</v>
       </c>
       <c r="E80" t="str">
         <v>30-35</v>
@@ -2012,7 +2012,7 @@
         <v>Main Area</v>
       </c>
       <c r="D81" t="str">
-        <v>Corsola</v>
+        <v>Bruxish</v>
       </c>
       <c r="E81" t="str">
         <v>30-35</v>
@@ -2023,42 +2023,42 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B82" t="str">
-        <v>Route 7</v>
+        <v>Route 8</v>
       </c>
       <c r="C82" t="str">
-        <v>Main Area</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D82" t="str">
-        <v>Mareanie</v>
+        <v>Omanyte</v>
       </c>
       <c r="E82" t="str">
-        <v>30-35</v>
+        <v>32-37</v>
       </c>
       <c r="F82" t="str">
-        <v>20.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B83" t="str">
-        <v>Route 7</v>
+        <v>Route 8</v>
       </c>
       <c r="C83" t="str">
-        <v>Main Area</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D83" t="str">
-        <v>Bruxish</v>
+        <v>Kabuto</v>
       </c>
       <c r="E83" t="str">
-        <v>30-35</v>
+        <v>32-37</v>
       </c>
       <c r="F83" t="str">
-        <v>20.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="84">
@@ -2072,7 +2072,7 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D84" t="str">
-        <v>Omanyte</v>
+        <v>Lileep</v>
       </c>
       <c r="E84" t="str">
         <v>32-37</v>
@@ -2092,7 +2092,7 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D85" t="str">
-        <v>Kabuto</v>
+        <v>Anorith</v>
       </c>
       <c r="E85" t="str">
         <v>32-37</v>
@@ -2112,7 +2112,7 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D86" t="str">
-        <v>Lileep</v>
+        <v>Cranidos</v>
       </c>
       <c r="E86" t="str">
         <v>32-37</v>
@@ -2132,7 +2132,7 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D87" t="str">
-        <v>Anorith</v>
+        <v>Shieldon</v>
       </c>
       <c r="E87" t="str">
         <v>32-37</v>
@@ -2152,7 +2152,7 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D88" t="str">
-        <v>Cranidos</v>
+        <v>Archen</v>
       </c>
       <c r="E88" t="str">
         <v>32-37</v>
@@ -2172,7 +2172,7 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D89" t="str">
-        <v>Shieldon</v>
+        <v>Tirtouga</v>
       </c>
       <c r="E89" t="str">
         <v>32-37</v>
@@ -2192,7 +2192,7 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D90" t="str">
-        <v>Archen</v>
+        <v>Tyrunt</v>
       </c>
       <c r="E90" t="str">
         <v>32-37</v>
@@ -2203,62 +2203,62 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B91" t="str">
         <v>Route 8</v>
       </c>
       <c r="C91" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D91" t="str">
-        <v>Tirtouga</v>
+        <v>Amaura</v>
       </c>
       <c r="E91" t="str">
         <v>32-37</v>
       </c>
       <c r="F91" t="str">
-        <v>11.11%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B92" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C92" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>North</v>
       </c>
       <c r="D92" t="str">
-        <v>Tyrunt</v>
+        <v>Trumbeak</v>
       </c>
       <c r="E92" t="str">
-        <v>32-37</v>
+        <v>33-38</v>
       </c>
       <c r="F92" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B93" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C93" t="str">
-        <v>Fossil Restoration Center Part 2</v>
+        <v>North</v>
       </c>
       <c r="D93" t="str">
-        <v>Amaura</v>
+        <v>Steenee</v>
       </c>
       <c r="E93" t="str">
-        <v>32-37</v>
+        <v>33-38</v>
       </c>
       <c r="F93" t="str">
-        <v>100.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="94">
@@ -2272,13 +2272,13 @@
         <v>North</v>
       </c>
       <c r="D94" t="str">
-        <v>Trumbeak</v>
+        <v>Comfey</v>
       </c>
       <c r="E94" t="str">
         <v>33-38</v>
       </c>
       <c r="F94" t="str">
-        <v>12.50%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="95">
@@ -2292,13 +2292,13 @@
         <v>North</v>
       </c>
       <c r="D95" t="str">
-        <v>Steenee</v>
+        <v>Hoothoot</v>
       </c>
       <c r="E95" t="str">
         <v>33-38</v>
       </c>
       <c r="F95" t="str">
-        <v>12.50%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="96">
@@ -2312,13 +2312,13 @@
         <v>North</v>
       </c>
       <c r="D96" t="str">
-        <v>Comfey</v>
+        <v>Oranguru</v>
       </c>
       <c r="E96" t="str">
         <v>33-38</v>
       </c>
       <c r="F96" t="str">
-        <v>12.50%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="97">
@@ -2332,93 +2332,93 @@
         <v>North</v>
       </c>
       <c r="D97" t="str">
-        <v>Hoothoot</v>
+        <v>Bounsweet</v>
       </c>
       <c r="E97" t="str">
         <v>33-38</v>
       </c>
       <c r="F97" t="str">
-        <v>12.50%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B98" t="str">
         <v>Lush Jungle</v>
       </c>
       <c r="C98" t="str">
-        <v>North</v>
+        <v>East Cave</v>
       </c>
       <c r="D98" t="str">
-        <v>Oranguru</v>
+        <v>Golbat</v>
       </c>
       <c r="E98" t="str">
-        <v>33-38</v>
+        <v>34-39</v>
       </c>
       <c r="F98" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B99" t="str">
         <v>Lush Jungle</v>
       </c>
       <c r="C99" t="str">
-        <v>North</v>
+        <v>East Cave</v>
       </c>
       <c r="D99" t="str">
-        <v>Bounsweet</v>
+        <v>Salandit</v>
       </c>
       <c r="E99" t="str">
-        <v>33-38</v>
+        <v>34-39</v>
       </c>
       <c r="F99" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="100">
       <c r="A100">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B100" t="str">
         <v>Lush Jungle</v>
       </c>
       <c r="C100" t="str">
-        <v>North</v>
+        <v>East Cave</v>
       </c>
       <c r="D100" t="str">
-        <v>Solgaleo</v>
+        <v>Larvesta</v>
       </c>
       <c r="E100" t="str">
-        <v>33-38</v>
+        <v>34-39</v>
       </c>
       <c r="F100" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="101">
       <c r="A101">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B101" t="str">
         <v>Lush Jungle</v>
       </c>
       <c r="C101" t="str">
-        <v>North</v>
+        <v>East Cave</v>
       </c>
       <c r="D101" t="str">
-        <v>Lunala</v>
+        <v>Oranguru</v>
       </c>
       <c r="E101" t="str">
-        <v>33-38</v>
+        <v>34-39</v>
       </c>
       <c r="F101" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="102">
@@ -2432,7 +2432,7 @@
         <v>East Cave</v>
       </c>
       <c r="D102" t="str">
-        <v>Golbat</v>
+        <v>Passimian</v>
       </c>
       <c r="E102" t="str">
         <v>34-39</v>
@@ -2443,182 +2443,182 @@
     </row>
     <row r="103">
       <c r="A103">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B103" t="str">
-        <v>Lush Jungle</v>
+        <v>Captain Mallow</v>
       </c>
       <c r="C103" t="str">
-        <v>East Cave</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D103" t="str">
-        <v>Salandit</v>
+        <v>Boss</v>
       </c>
       <c r="E103" t="str">
-        <v>34-39</v>
+        <v>36-41</v>
       </c>
       <c r="F103" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="104">
       <c r="A104">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B104" t="str">
-        <v>Lush Jungle</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C104" t="str">
-        <v>East Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D104" t="str">
-        <v>Larvesta</v>
+        <v>Zubat</v>
       </c>
       <c r="E104" t="str">
-        <v>34-39</v>
+        <v>37-42</v>
       </c>
       <c r="F104" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="105">
       <c r="A105">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B105" t="str">
-        <v>Lush Jungle</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C105" t="str">
-        <v>East Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D105" t="str">
-        <v>Oranguru</v>
+        <v>Alolan Diglett</v>
       </c>
       <c r="E105" t="str">
-        <v>34-39</v>
+        <v>37-42</v>
       </c>
       <c r="F105" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="106">
       <c r="A106">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B106" t="str">
-        <v>Lush Jungle</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C106" t="str">
-        <v>East Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D106" t="str">
-        <v>Passimian</v>
+        <v>Kecleon</v>
       </c>
       <c r="E106" t="str">
-        <v>34-39</v>
+        <v>37-42</v>
       </c>
       <c r="F106" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="107">
       <c r="A107">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B107" t="str">
-        <v>Captain Mallow</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C107" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D107" t="str">
-        <v>Boss</v>
+        <v>Larvitar</v>
       </c>
       <c r="E107" t="str">
-        <v>36-41</v>
+        <v>37-42</v>
       </c>
       <c r="F107" t="str">
-        <v>-</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="108">
       <c r="A108">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B108" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C108" t="str">
         <v>Main Area</v>
       </c>
       <c r="D108" t="str">
-        <v>Zubat</v>
+        <v>Gumshoos</v>
       </c>
       <c r="E108" t="str">
-        <v>37-42</v>
+        <v>42-47</v>
       </c>
       <c r="F108" t="str">
-        <v>25.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="109">
       <c r="A109">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B109" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C109" t="str">
         <v>Main Area</v>
       </c>
       <c r="D109" t="str">
-        <v>Alolan Diglett</v>
+        <v>Wingull</v>
       </c>
       <c r="E109" t="str">
-        <v>37-42</v>
+        <v>42-47</v>
       </c>
       <c r="F109" t="str">
-        <v>25.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="110">
       <c r="A110">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B110" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C110" t="str">
         <v>Main Area</v>
       </c>
       <c r="D110" t="str">
-        <v>Kecleon</v>
+        <v>Magikarp</v>
       </c>
       <c r="E110" t="str">
-        <v>37-42</v>
+        <v>42-47</v>
       </c>
       <c r="F110" t="str">
-        <v>25.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="111">
       <c r="A111">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B111" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C111" t="str">
         <v>Main Area</v>
       </c>
       <c r="D111" t="str">
-        <v>Larvitar</v>
+        <v>Stufful</v>
       </c>
       <c r="E111" t="str">
-        <v>37-42</v>
+        <v>42-47</v>
       </c>
       <c r="F111" t="str">
-        <v>25.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="112">
@@ -2632,7 +2632,7 @@
         <v>Main Area</v>
       </c>
       <c r="D112" t="str">
-        <v>Gumshoos</v>
+        <v>Chinchou</v>
       </c>
       <c r="E112" t="str">
         <v>42-47</v>
@@ -2652,7 +2652,7 @@
         <v>Main Area</v>
       </c>
       <c r="D113" t="str">
-        <v>Wingull</v>
+        <v>Alolan Raticate</v>
       </c>
       <c r="E113" t="str">
         <v>42-47</v>
@@ -2672,7 +2672,7 @@
         <v>Main Area</v>
       </c>
       <c r="D114" t="str">
-        <v>Magikarp</v>
+        <v>Natu</v>
       </c>
       <c r="E114" t="str">
         <v>42-47</v>
@@ -2692,7 +2692,7 @@
         <v>Main Area</v>
       </c>
       <c r="D115" t="str">
-        <v>Stufful</v>
+        <v>Nosepass</v>
       </c>
       <c r="E115" t="str">
         <v>42-47</v>
@@ -2703,102 +2703,102 @@
     </row>
     <row r="116">
       <c r="A116">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B116" t="str">
-        <v>Akala Outskirts</v>
+        <v>Kahuna Olivia</v>
       </c>
       <c r="C116" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D116" t="str">
-        <v>Chinchou</v>
+        <v>Boss</v>
       </c>
       <c r="E116" t="str">
-        <v>42-47</v>
+        <v>44-49</v>
       </c>
       <c r="F116" t="str">
-        <v>12.50%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="117">
       <c r="A117">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B117" t="str">
-        <v>Akala Outskirts</v>
+        <v>Malie City</v>
       </c>
       <c r="C117" t="str">
-        <v>Main Area</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D117" t="str">
-        <v>Alolan Raticate</v>
+        <v>Magnemite</v>
       </c>
       <c r="E117" t="str">
-        <v>42-47</v>
+        <v>46-51</v>
       </c>
       <c r="F117" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="118">
       <c r="A118">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B118" t="str">
-        <v>Akala Outskirts</v>
+        <v>Malie City</v>
       </c>
       <c r="C118" t="str">
-        <v>Main Area</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D118" t="str">
-        <v>Natu</v>
+        <v>Alolan Grimer</v>
       </c>
       <c r="E118" t="str">
-        <v>42-47</v>
+        <v>46-51</v>
       </c>
       <c r="F118" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="119">
       <c r="A119">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B119" t="str">
-        <v>Akala Outskirts</v>
+        <v>Malie City</v>
       </c>
       <c r="C119" t="str">
-        <v>Main Area</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D119" t="str">
-        <v>Nosepass</v>
+        <v>Trubbish</v>
       </c>
       <c r="E119" t="str">
-        <v>42-47</v>
+        <v>46-51</v>
       </c>
       <c r="F119" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="120">
       <c r="A120">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B120" t="str">
-        <v>Kahuna Olivia</v>
+        <v>Malie City</v>
       </c>
       <c r="C120" t="str">
-        <v>Boss Battle</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D120" t="str">
-        <v>Boss</v>
+        <v>Minccino</v>
       </c>
       <c r="E120" t="str">
-        <v>44-49</v>
+        <v>46-51</v>
       </c>
       <c r="F120" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="121">
@@ -2812,30 +2812,30 @@
         <v>Outer Cape</v>
       </c>
       <c r="D121" t="str">
-        <v>Magnemite</v>
+        <v>Masquerain</v>
       </c>
       <c r="E121" t="str">
         <v>46-51</v>
       </c>
       <c r="F121" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="122">
       <c r="A122">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B122" t="str">
-        <v>Malie City</v>
+        <v>Route 10</v>
       </c>
       <c r="C122" t="str">
-        <v>Outer Cape</v>
+        <v>Main Area</v>
       </c>
       <c r="D122" t="str">
-        <v>Alolan Grimer</v>
+        <v>Ledian</v>
       </c>
       <c r="E122" t="str">
-        <v>46-51</v>
+        <v>49-54</v>
       </c>
       <c r="F122" t="str">
         <v>16.67%</v>
@@ -2843,19 +2843,19 @@
     </row>
     <row r="123">
       <c r="A123">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B123" t="str">
-        <v>Malie City</v>
+        <v>Route 10</v>
       </c>
       <c r="C123" t="str">
-        <v>Outer Cape</v>
+        <v>Main Area</v>
       </c>
       <c r="D123" t="str">
-        <v>Trubbish</v>
+        <v>Ariados</v>
       </c>
       <c r="E123" t="str">
-        <v>46-51</v>
+        <v>49-54</v>
       </c>
       <c r="F123" t="str">
         <v>16.67%</v>
@@ -2863,19 +2863,19 @@
     </row>
     <row r="124">
       <c r="A124">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B124" t="str">
-        <v>Malie City</v>
+        <v>Route 10</v>
       </c>
       <c r="C124" t="str">
-        <v>Outer Cape</v>
+        <v>Main Area</v>
       </c>
       <c r="D124" t="str">
-        <v>Minccino</v>
+        <v>Crabrawler</v>
       </c>
       <c r="E124" t="str">
-        <v>46-51</v>
+        <v>49-54</v>
       </c>
       <c r="F124" t="str">
         <v>16.67%</v>
@@ -2883,19 +2883,19 @@
     </row>
     <row r="125">
       <c r="A125">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B125" t="str">
-        <v>Malie City</v>
+        <v>Route 10</v>
       </c>
       <c r="C125" t="str">
-        <v>Outer Cape</v>
+        <v>Main Area</v>
       </c>
       <c r="D125" t="str">
-        <v>Masquerain</v>
+        <v>Fearow</v>
       </c>
       <c r="E125" t="str">
-        <v>46-51</v>
+        <v>49-54</v>
       </c>
       <c r="F125" t="str">
         <v>16.67%</v>
@@ -2903,19 +2903,19 @@
     </row>
     <row r="126">
       <c r="A126">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B126" t="str">
-        <v>Malie City</v>
+        <v>Route 10</v>
       </c>
       <c r="C126" t="str">
-        <v>Outer Cape</v>
+        <v>Main Area</v>
       </c>
       <c r="D126" t="str">
-        <v>Kartana</v>
+        <v>Skarmory</v>
       </c>
       <c r="E126" t="str">
-        <v>46-51</v>
+        <v>49-54</v>
       </c>
       <c r="F126" t="str">
         <v>16.67%</v>
@@ -2932,7 +2932,7 @@
         <v>Main Area</v>
       </c>
       <c r="D127" t="str">
-        <v>Ledian</v>
+        <v>Pancham</v>
       </c>
       <c r="E127" t="str">
         <v>49-54</v>
@@ -2943,202 +2943,202 @@
     </row>
     <row r="128">
       <c r="A128">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B128" t="str">
-        <v>Route 10</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C128" t="str">
-        <v>Main Area</v>
+        <v>East</v>
       </c>
       <c r="D128" t="str">
-        <v>Ariados</v>
+        <v>Cleffa</v>
       </c>
       <c r="E128" t="str">
-        <v>49-54</v>
+        <v>50-55</v>
       </c>
       <c r="F128" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="129">
       <c r="A129">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B129" t="str">
-        <v>Route 10</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C129" t="str">
-        <v>Main Area</v>
+        <v>East</v>
       </c>
       <c r="D129" t="str">
-        <v>Crabrawler</v>
+        <v>Elgyem</v>
       </c>
       <c r="E129" t="str">
-        <v>49-54</v>
+        <v>50-55</v>
       </c>
       <c r="F129" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="130">
       <c r="A130">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B130" t="str">
-        <v>Route 10</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C130" t="str">
-        <v>Main Area</v>
+        <v>East</v>
       </c>
       <c r="D130" t="str">
-        <v>Fearow</v>
+        <v>Beldum</v>
       </c>
       <c r="E130" t="str">
-        <v>49-54</v>
+        <v>50-55</v>
       </c>
       <c r="F130" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="131">
       <c r="A131">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B131" t="str">
-        <v>Route 10</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C131" t="str">
-        <v>Main Area</v>
+        <v>East</v>
       </c>
       <c r="D131" t="str">
-        <v>Skarmory</v>
+        <v>Minior</v>
       </c>
       <c r="E131" t="str">
-        <v>49-54</v>
+        <v>50-55</v>
       </c>
       <c r="F131" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="132">
       <c r="A132">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B132" t="str">
-        <v>Route 10</v>
+        <v>Captain Sophocles</v>
       </c>
       <c r="C132" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D132" t="str">
-        <v>Pancham</v>
+        <v>Boss</v>
       </c>
       <c r="E132" t="str">
-        <v>49-54</v>
+        <v>52-57</v>
       </c>
       <c r="F132" t="str">
-        <v>16.67%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="133">
       <c r="A133">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B133" t="str">
-        <v>Mount Hokulani</v>
+        <v>Route 11</v>
       </c>
       <c r="C133" t="str">
-        <v>East</v>
+        <v>Main Area</v>
       </c>
       <c r="D133" t="str">
-        <v>Cleffa</v>
+        <v>Shiinotic</v>
       </c>
       <c r="E133" t="str">
-        <v>50-55</v>
+        <v>53-58</v>
       </c>
       <c r="F133" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="134">
       <c r="A134">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B134" t="str">
-        <v>Mount Hokulani</v>
+        <v>Route 11</v>
       </c>
       <c r="C134" t="str">
-        <v>East</v>
+        <v>Main Area</v>
       </c>
       <c r="D134" t="str">
-        <v>Elgyem</v>
+        <v>Parasect</v>
       </c>
       <c r="E134" t="str">
-        <v>50-55</v>
+        <v>53-58</v>
       </c>
       <c r="F134" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="135">
       <c r="A135">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B135" t="str">
-        <v>Mount Hokulani</v>
+        <v>Route 11</v>
       </c>
       <c r="C135" t="str">
-        <v>East</v>
+        <v>Main Area</v>
       </c>
       <c r="D135" t="str">
-        <v>Beldum</v>
+        <v>Komala</v>
       </c>
       <c r="E135" t="str">
-        <v>50-55</v>
+        <v>53-58</v>
       </c>
       <c r="F135" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="136">
       <c r="A136">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B136" t="str">
-        <v>Mount Hokulani</v>
+        <v>Route 11</v>
       </c>
       <c r="C136" t="str">
-        <v>East</v>
+        <v>Main Area</v>
       </c>
       <c r="D136" t="str">
-        <v>Minior</v>
+        <v>Houndoom</v>
       </c>
       <c r="E136" t="str">
-        <v>50-55</v>
+        <v>53-58</v>
       </c>
       <c r="F136" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="137">
       <c r="A137">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B137" t="str">
-        <v>Captain Sophocles</v>
+        <v>Route 11</v>
       </c>
       <c r="C137" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D137" t="str">
-        <v>Boss</v>
+        <v>Manectric</v>
       </c>
       <c r="E137" t="str">
-        <v>52-57</v>
+        <v>53-58</v>
       </c>
       <c r="F137" t="str">
-        <v>-</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="138">
@@ -3152,7 +3152,7 @@
         <v>Main Area</v>
       </c>
       <c r="D138" t="str">
-        <v>Shiinotic</v>
+        <v>Scraggy</v>
       </c>
       <c r="E138" t="str">
         <v>53-58</v>
@@ -3172,7 +3172,7 @@
         <v>Main Area</v>
       </c>
       <c r="D139" t="str">
-        <v>Parasect</v>
+        <v>Bisharp</v>
       </c>
       <c r="E139" t="str">
         <v>53-58</v>
@@ -3192,7 +3192,7 @@
         <v>Main Area</v>
       </c>
       <c r="D140" t="str">
-        <v>Komala</v>
+        <v>Machop</v>
       </c>
       <c r="E140" t="str">
         <v>53-58</v>
@@ -3212,7 +3212,7 @@
         <v>Main Area</v>
       </c>
       <c r="D141" t="str">
-        <v>Houndoom</v>
+        <v>Hawlucha</v>
       </c>
       <c r="E141" t="str">
         <v>53-58</v>
@@ -3223,19 +3223,19 @@
     </row>
     <row r="142">
       <c r="A142">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B142" t="str">
-        <v>Route 11</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C142" t="str">
         <v>Main Area</v>
       </c>
       <c r="D142" t="str">
-        <v>Manectric</v>
+        <v>Mudbray</v>
       </c>
       <c r="E142" t="str">
-        <v>53-58</v>
+        <v>56-61</v>
       </c>
       <c r="F142" t="str">
         <v>11.11%</v>
@@ -3243,19 +3243,19 @@
     </row>
     <row r="143">
       <c r="A143">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B143" t="str">
-        <v>Route 11</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C143" t="str">
         <v>Main Area</v>
       </c>
       <c r="D143" t="str">
-        <v>Scraggy</v>
+        <v>Torkoal</v>
       </c>
       <c r="E143" t="str">
-        <v>53-58</v>
+        <v>56-61</v>
       </c>
       <c r="F143" t="str">
         <v>11.11%</v>
@@ -3263,19 +3263,19 @@
     </row>
     <row r="144">
       <c r="A144">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B144" t="str">
-        <v>Route 11</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C144" t="str">
         <v>Main Area</v>
       </c>
       <c r="D144" t="str">
-        <v>Bisharp</v>
+        <v>Togedemaru</v>
       </c>
       <c r="E144" t="str">
-        <v>53-58</v>
+        <v>56-61</v>
       </c>
       <c r="F144" t="str">
         <v>11.11%</v>
@@ -3283,19 +3283,19 @@
     </row>
     <row r="145">
       <c r="A145">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B145" t="str">
-        <v>Route 11</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C145" t="str">
         <v>Main Area</v>
       </c>
       <c r="D145" t="str">
-        <v>Machop</v>
+        <v>Elekid</v>
       </c>
       <c r="E145" t="str">
-        <v>53-58</v>
+        <v>56-61</v>
       </c>
       <c r="F145" t="str">
         <v>11.11%</v>
@@ -3303,19 +3303,19 @@
     </row>
     <row r="146">
       <c r="A146">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B146" t="str">
-        <v>Route 11</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C146" t="str">
         <v>Main Area</v>
       </c>
       <c r="D146" t="str">
-        <v>Hawlucha</v>
+        <v>Alolan Geodude</v>
       </c>
       <c r="E146" t="str">
-        <v>53-58</v>
+        <v>56-61</v>
       </c>
       <c r="F146" t="str">
         <v>11.11%</v>
@@ -3332,7 +3332,7 @@
         <v>Main Area</v>
       </c>
       <c r="D147" t="str">
-        <v>Mudbray</v>
+        <v>Alolan Graveler</v>
       </c>
       <c r="E147" t="str">
         <v>56-61</v>
@@ -3352,7 +3352,7 @@
         <v>Main Area</v>
       </c>
       <c r="D148" t="str">
-        <v>Torkoal</v>
+        <v>Charjabug</v>
       </c>
       <c r="E148" t="str">
         <v>56-61</v>
@@ -3372,7 +3372,7 @@
         <v>Main Area</v>
       </c>
       <c r="D149" t="str">
-        <v>Togedemaru</v>
+        <v>Turtonator</v>
       </c>
       <c r="E149" t="str">
         <v>56-61</v>
@@ -3392,7 +3392,7 @@
         <v>Main Area</v>
       </c>
       <c r="D150" t="str">
-        <v>Elekid</v>
+        <v>Dedenne</v>
       </c>
       <c r="E150" t="str">
         <v>56-61</v>
@@ -3403,119 +3403,119 @@
     </row>
     <row r="151">
       <c r="A151">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B151" t="str">
-        <v>Blush Mountain</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C151" t="str">
         <v>Main Area</v>
       </c>
       <c r="D151" t="str">
-        <v>Alolan Geodude</v>
+        <v>Alolan Dugtrio</v>
       </c>
       <c r="E151" t="str">
-        <v>56-61</v>
+        <v>57-62</v>
       </c>
       <c r="F151" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="152">
       <c r="A152">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B152" t="str">
-        <v>Blush Mountain</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C152" t="str">
         <v>Main Area</v>
       </c>
       <c r="D152" t="str">
-        <v>Alolan Graveler</v>
+        <v>Sandile</v>
       </c>
       <c r="E152" t="str">
-        <v>56-61</v>
+        <v>57-62</v>
       </c>
       <c r="F152" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="153">
       <c r="A153">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B153" t="str">
-        <v>Blush Mountain</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C153" t="str">
         <v>Main Area</v>
       </c>
       <c r="D153" t="str">
-        <v>Charjabug</v>
+        <v>Krokorok</v>
       </c>
       <c r="E153" t="str">
-        <v>56-61</v>
+        <v>57-62</v>
       </c>
       <c r="F153" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="154">
       <c r="A154">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B154" t="str">
-        <v>Blush Mountain</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C154" t="str">
         <v>Main Area</v>
       </c>
       <c r="D154" t="str">
-        <v>Turtonator</v>
+        <v>Staryu</v>
       </c>
       <c r="E154" t="str">
-        <v>56-61</v>
+        <v>57-62</v>
       </c>
       <c r="F154" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="155">
       <c r="A155">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B155" t="str">
-        <v>Blush Mountain</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C155" t="str">
         <v>Main Area</v>
       </c>
       <c r="D155" t="str">
-        <v>Dedenne</v>
+        <v>Sandygast</v>
       </c>
       <c r="E155" t="str">
-        <v>56-61</v>
+        <v>57-62</v>
       </c>
       <c r="F155" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="156">
       <c r="A156">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B156" t="str">
-        <v>Haina Desert</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C156" t="str">
         <v>Main Area</v>
       </c>
       <c r="D156" t="str">
-        <v>Celesteela</v>
+        <v>Graveler</v>
       </c>
       <c r="E156" t="str">
-        <v>57-62</v>
+        <v>59-64</v>
       </c>
       <c r="F156" t="str">
         <v>16.67%</v>
@@ -3523,19 +3523,19 @@
     </row>
     <row r="157">
       <c r="A157">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B157" t="str">
-        <v>Haina Desert</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C157" t="str">
         <v>Main Area</v>
       </c>
       <c r="D157" t="str">
-        <v>Alolan Dugtrio</v>
+        <v>Bruxish</v>
       </c>
       <c r="E157" t="str">
-        <v>57-62</v>
+        <v>59-64</v>
       </c>
       <c r="F157" t="str">
         <v>16.67%</v>
@@ -3543,19 +3543,19 @@
     </row>
     <row r="158">
       <c r="A158">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B158" t="str">
-        <v>Haina Desert</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C158" t="str">
         <v>Main Area</v>
       </c>
       <c r="D158" t="str">
-        <v>Sandile</v>
+        <v>Absol</v>
       </c>
       <c r="E158" t="str">
-        <v>57-62</v>
+        <v>59-64</v>
       </c>
       <c r="F158" t="str">
         <v>16.67%</v>
@@ -3563,19 +3563,19 @@
     </row>
     <row r="159">
       <c r="A159">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B159" t="str">
-        <v>Haina Desert</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C159" t="str">
         <v>Main Area</v>
       </c>
       <c r="D159" t="str">
-        <v>Krokorok</v>
+        <v>Snorunt</v>
       </c>
       <c r="E159" t="str">
-        <v>57-62</v>
+        <v>59-64</v>
       </c>
       <c r="F159" t="str">
         <v>16.67%</v>
@@ -3583,19 +3583,19 @@
     </row>
     <row r="160">
       <c r="A160">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B160" t="str">
-        <v>Haina Desert</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C160" t="str">
         <v>Main Area</v>
       </c>
       <c r="D160" t="str">
-        <v>Staryu</v>
+        <v>Alolan Sandshrew</v>
       </c>
       <c r="E160" t="str">
-        <v>57-62</v>
+        <v>59-64</v>
       </c>
       <c r="F160" t="str">
         <v>16.67%</v>
@@ -3603,19 +3603,19 @@
     </row>
     <row r="161">
       <c r="A161">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B161" t="str">
-        <v>Haina Desert</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C161" t="str">
         <v>Main Area</v>
       </c>
       <c r="D161" t="str">
-        <v>Sandygast</v>
+        <v>Alolan Vulpix</v>
       </c>
       <c r="E161" t="str">
-        <v>57-62</v>
+        <v>59-64</v>
       </c>
       <c r="F161" t="str">
         <v>16.67%</v>
@@ -3623,362 +3623,362 @@
     </row>
     <row r="162">
       <c r="A162">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B162" t="str">
-        <v>Tapu Village</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C162" t="str">
-        <v>Main Area</v>
+        <v>Abandoned Site</v>
       </c>
       <c r="D162" t="str">
-        <v>Graveler</v>
+        <v>Haunter</v>
       </c>
       <c r="E162" t="str">
-        <v>59-64</v>
+        <v>61-66</v>
       </c>
       <c r="F162" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="163">
       <c r="A163">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B163" t="str">
-        <v>Tapu Village</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C163" t="str">
-        <v>Main Area</v>
+        <v>Abandoned Site</v>
       </c>
       <c r="D163" t="str">
-        <v>Bruxish</v>
+        <v>Klefki</v>
       </c>
       <c r="E163" t="str">
-        <v>59-64</v>
+        <v>61-66</v>
       </c>
       <c r="F163" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="164">
       <c r="A164">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B164" t="str">
-        <v>Tapu Village</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C164" t="str">
-        <v>Main Area</v>
+        <v>Abandoned Site</v>
       </c>
       <c r="D164" t="str">
-        <v>Absol</v>
+        <v>Shuppet</v>
       </c>
       <c r="E164" t="str">
-        <v>59-64</v>
+        <v>61-66</v>
       </c>
       <c r="F164" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="165">
       <c r="A165">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B165" t="str">
-        <v>Tapu Village</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C165" t="str">
-        <v>Main Area</v>
+        <v>Abandoned Site</v>
       </c>
       <c r="D165" t="str">
-        <v>Snorunt</v>
+        <v>Boldore</v>
       </c>
       <c r="E165" t="str">
-        <v>59-64</v>
+        <v>61-66</v>
       </c>
       <c r="F165" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="166">
       <c r="A166">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B166" t="str">
-        <v>Tapu Village</v>
+        <v>Captain Acerola</v>
       </c>
       <c r="C166" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D166" t="str">
-        <v>Alolan Sandshrew</v>
+        <v>Boss</v>
       </c>
       <c r="E166" t="str">
-        <v>59-64</v>
+        <v>63-68</v>
       </c>
       <c r="F166" t="str">
-        <v>16.67%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="167">
       <c r="A167">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B167" t="str">
-        <v>Tapu Village</v>
+        <v>Kahuna Nanu</v>
       </c>
       <c r="C167" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D167" t="str">
-        <v>Alolan Vulpix</v>
+        <v>Boss</v>
       </c>
       <c r="E167" t="str">
-        <v>59-64</v>
+        <v>68-73</v>
       </c>
       <c r="F167" t="str">
-        <v>16.67%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="168">
       <c r="A168">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B168" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C168" t="str">
-        <v>Abandoned Site</v>
+        <v>Main</v>
       </c>
       <c r="D168" t="str">
-        <v>Haunter</v>
+        <v>Steenee</v>
       </c>
       <c r="E168" t="str">
-        <v>61-66</v>
+        <v>69-74</v>
       </c>
       <c r="F168" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="169">
       <c r="A169">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B169" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C169" t="str">
-        <v>Abandoned Site</v>
+        <v>Main</v>
       </c>
       <c r="D169" t="str">
-        <v>Klefki</v>
+        <v>Shellos</v>
       </c>
       <c r="E169" t="str">
-        <v>61-66</v>
+        <v>69-74</v>
       </c>
       <c r="F169" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="170">
       <c r="A170">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B170" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C170" t="str">
-        <v>Abandoned Site</v>
+        <v>Main</v>
       </c>
       <c r="D170" t="str">
-        <v>Shuppet</v>
+        <v>Dhelmise</v>
       </c>
       <c r="E170" t="str">
-        <v>61-66</v>
+        <v>69-74</v>
       </c>
       <c r="F170" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="171">
       <c r="A171">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B171" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C171" t="str">
-        <v>Abandoned Site</v>
+        <v>Main Area</v>
       </c>
       <c r="D171" t="str">
-        <v>Boldore</v>
+        <v>Tentacruel</v>
       </c>
       <c r="E171" t="str">
-        <v>61-66</v>
+        <v>71-76</v>
       </c>
       <c r="F171" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="172">
       <c r="A172">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B172" t="str">
-        <v>Captain Acerola</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C172" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D172" t="str">
-        <v>Boss</v>
+        <v>Lumineon</v>
       </c>
       <c r="E172" t="str">
-        <v>63-68</v>
+        <v>71-76</v>
       </c>
       <c r="F172" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="173">
       <c r="A173">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B173" t="str">
-        <v>Kahuna Nanu</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C173" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D173" t="str">
-        <v>Boss</v>
+        <v>Lapras</v>
       </c>
       <c r="E173" t="str">
-        <v>68-73</v>
+        <v>71-76</v>
       </c>
       <c r="F173" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="174">
       <c r="A174">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B174" t="str">
-        <v>Seafolk Village</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C174" t="str">
-        <v>Main</v>
+        <v>Main Area</v>
       </c>
       <c r="D174" t="str">
-        <v>Steenee</v>
+        <v>Noivern</v>
       </c>
       <c r="E174" t="str">
-        <v>69-74</v>
+        <v>71-76</v>
       </c>
       <c r="F174" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="175">
       <c r="A175">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B175" t="str">
-        <v>Seafolk Village</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C175" t="str">
-        <v>Main</v>
+        <v>Main Area</v>
       </c>
       <c r="D175" t="str">
-        <v>Shellos</v>
+        <v>Druddigon</v>
       </c>
       <c r="E175" t="str">
-        <v>69-74</v>
+        <v>71-76</v>
       </c>
       <c r="F175" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="176">
       <c r="A176">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B176" t="str">
-        <v>Seafolk Village</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C176" t="str">
-        <v>Main</v>
+        <v>Main Area</v>
       </c>
       <c r="D176" t="str">
-        <v>Dhelmise</v>
+        <v>Wimpod</v>
       </c>
       <c r="E176" t="str">
-        <v>69-74</v>
+        <v>72-77</v>
       </c>
       <c r="F176" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="177">
       <c r="A177">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B177" t="str">
-        <v>Poni Wilds</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C177" t="str">
         <v>Main Area</v>
       </c>
       <c r="D177" t="str">
-        <v>Tentacruel</v>
+        <v>Relicanth</v>
       </c>
       <c r="E177" t="str">
-        <v>71-76</v>
+        <v>72-77</v>
       </c>
       <c r="F177" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="178">
       <c r="A178">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B178" t="str">
-        <v>Poni Wilds</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C178" t="str">
         <v>Main Area</v>
       </c>
       <c r="D178" t="str">
-        <v>Lumineon</v>
+        <v>Wailmer</v>
       </c>
       <c r="E178" t="str">
-        <v>71-76</v>
+        <v>72-77</v>
       </c>
       <c r="F178" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="179">
       <c r="A179">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B179" t="str">
-        <v>Poni Wilds</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C179" t="str">
         <v>Main Area</v>
       </c>
       <c r="D179" t="str">
-        <v>Lapras</v>
+        <v>Carvanha</v>
       </c>
       <c r="E179" t="str">
-        <v>71-76</v>
+        <v>72-77</v>
       </c>
       <c r="F179" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="180">
@@ -3992,7 +3992,7 @@
         <v>Main Area</v>
       </c>
       <c r="D180" t="str">
-        <v>Wimpod</v>
+        <v>Sharpedo</v>
       </c>
       <c r="E180" t="str">
         <v>72-77</v>
@@ -4003,82 +4003,82 @@
     </row>
     <row r="181">
       <c r="A181">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B181" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C181" t="str">
         <v>Main Area</v>
       </c>
       <c r="D181" t="str">
-        <v>Relicanth</v>
+        <v>Pelipper</v>
       </c>
       <c r="E181" t="str">
-        <v>72-77</v>
+        <v>73-78</v>
       </c>
       <c r="F181" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="182">
       <c r="A182">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B182" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C182" t="str">
         <v>Main Area</v>
       </c>
       <c r="D182" t="str">
-        <v>Wailmer</v>
+        <v>Pinsir</v>
       </c>
       <c r="E182" t="str">
-        <v>72-77</v>
+        <v>73-78</v>
       </c>
       <c r="F182" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="183">
       <c r="A183">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B183" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C183" t="str">
         <v>Main Area</v>
       </c>
       <c r="D183" t="str">
-        <v>Carvanha</v>
+        <v>Gastrodon</v>
       </c>
       <c r="E183" t="str">
-        <v>72-77</v>
+        <v>73-78</v>
       </c>
       <c r="F183" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="184">
       <c r="A184">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B184" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C184" t="str">
         <v>Main Area</v>
       </c>
       <c r="D184" t="str">
-        <v>Sharpedo</v>
+        <v>Exeggcute</v>
       </c>
       <c r="E184" t="str">
-        <v>72-77</v>
+        <v>73-78</v>
       </c>
       <c r="F184" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="185">
@@ -4092,7 +4092,7 @@
         <v>Main Area</v>
       </c>
       <c r="D185" t="str">
-        <v>Pelipper</v>
+        <v>Tropius</v>
       </c>
       <c r="E185" t="str">
         <v>73-78</v>
@@ -4112,7 +4112,7 @@
         <v>Main Area</v>
       </c>
       <c r="D186" t="str">
-        <v>Pinsir</v>
+        <v>Alolan Exeggutor</v>
       </c>
       <c r="E186" t="str">
         <v>73-78</v>
@@ -4123,270 +4123,270 @@
     </row>
     <row r="187">
       <c r="A187">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B187" t="str">
-        <v>Exeggutor Island</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C187" t="str">
-        <v>Main Area</v>
+        <v>Outside</v>
       </c>
       <c r="D187" t="str">
-        <v>Gastrodon</v>
+        <v>Machoke</v>
       </c>
       <c r="E187" t="str">
-        <v>73-78</v>
+        <v>75-80</v>
       </c>
       <c r="F187" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="188">
       <c r="A188">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B188" t="str">
-        <v>Exeggutor Island</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C188" t="str">
-        <v>Main Area</v>
+        <v>Outside</v>
       </c>
       <c r="D188" t="str">
-        <v>Exeggcute</v>
+        <v>Mienfoo</v>
       </c>
       <c r="E188" t="str">
-        <v>73-78</v>
+        <v>75-80</v>
       </c>
       <c r="F188" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="189">
       <c r="A189">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B189" t="str">
-        <v>Exeggutor Island</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C189" t="str">
-        <v>Main Area</v>
+        <v>Outside</v>
       </c>
       <c r="D189" t="str">
-        <v>Tropius</v>
+        <v>Jangmo-o</v>
       </c>
       <c r="E189" t="str">
-        <v>73-78</v>
+        <v>75-80</v>
       </c>
       <c r="F189" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="190">
       <c r="A190">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B190" t="str">
-        <v>Exeggutor Island</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C190" t="str">
-        <v>Main Area</v>
+        <v>Northwest (Hidden Area)</v>
       </c>
       <c r="D190" t="str">
-        <v>Alolan Exeggutor</v>
+        <v>Corphish</v>
       </c>
       <c r="E190" t="str">
-        <v>73-78</v>
+        <v>77-82</v>
       </c>
       <c r="F190" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="191">
       <c r="A191">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B191" t="str">
         <v>Vast Poni Canyon</v>
       </c>
       <c r="C191" t="str">
-        <v>Outside</v>
+        <v>Northwest (Hidden Area)</v>
       </c>
       <c r="D191" t="str">
-        <v>Machoke</v>
+        <v>Dratini</v>
       </c>
       <c r="E191" t="str">
-        <v>75-80</v>
+        <v>77-82</v>
       </c>
       <c r="F191" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="192">
       <c r="A192">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B192" t="str">
         <v>Vast Poni Canyon</v>
       </c>
       <c r="C192" t="str">
-        <v>Outside</v>
+        <v>Northwest (Hidden Area)</v>
       </c>
       <c r="D192" t="str">
-        <v>Mienfoo</v>
+        <v>Golduck</v>
       </c>
       <c r="E192" t="str">
-        <v>75-80</v>
+        <v>77-82</v>
       </c>
       <c r="F192" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="193">
       <c r="A193">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B193" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Captain Kommo-o</v>
       </c>
       <c r="C193" t="str">
-        <v>Outside</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D193" t="str">
-        <v>Jangmo-o</v>
+        <v>Boss</v>
       </c>
       <c r="E193" t="str">
-        <v>75-80</v>
+        <v>79-84</v>
       </c>
       <c r="F193" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="194">
       <c r="A194">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B194" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Captain Mina</v>
       </c>
       <c r="C194" t="str">
-        <v>Outside</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D194" t="str">
-        <v>Pheromosa</v>
+        <v>Boss</v>
       </c>
       <c r="E194" t="str">
-        <v>75-80</v>
+        <v>80-85</v>
       </c>
       <c r="F194" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="195">
       <c r="A195">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B195" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Kahuna Hapu</v>
       </c>
       <c r="C195" t="str">
-        <v>Northwest (Hidden Area)</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D195" t="str">
-        <v>Corphish</v>
+        <v>Boss</v>
       </c>
       <c r="E195" t="str">
-        <v>77-82</v>
+        <v>81-86</v>
       </c>
       <c r="F195" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="196">
       <c r="A196">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B196" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C196" t="str">
-        <v>Northwest (Hidden Area)</v>
+        <v>Cave</v>
       </c>
       <c r="D196" t="str">
-        <v>Dratini</v>
+        <v>Drampa</v>
       </c>
       <c r="E196" t="str">
-        <v>77-82</v>
+        <v>83-88</v>
       </c>
       <c r="F196" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="197">
       <c r="A197">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B197" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C197" t="str">
-        <v>Northwest (Hidden Area)</v>
+        <v>Cave</v>
       </c>
       <c r="D197" t="str">
-        <v>Golduck</v>
+        <v>Glalie</v>
       </c>
       <c r="E197" t="str">
-        <v>77-82</v>
+        <v>83-88</v>
       </c>
       <c r="F197" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="198">
       <c r="A198">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B198" t="str">
-        <v>Captain Kommo-o</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C198" t="str">
-        <v>Boss Battle</v>
+        <v>Cave</v>
       </c>
       <c r="D198" t="str">
-        <v>Boss</v>
+        <v>Sneasel</v>
       </c>
       <c r="E198" t="str">
-        <v>79-84</v>
+        <v>83-88</v>
       </c>
       <c r="F198" t="str">
-        <v>-</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="199">
       <c r="A199">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B199" t="str">
-        <v>Captain Mina</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C199" t="str">
-        <v>Boss Battle</v>
+        <v>Cave</v>
       </c>
       <c r="D199" t="str">
-        <v>Boss</v>
+        <v>Crabominable</v>
       </c>
       <c r="E199" t="str">
-        <v>80-85</v>
+        <v>83-88</v>
       </c>
       <c r="F199" t="str">
-        <v>-</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="200">
       <c r="A200">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B200" t="str">
-        <v>Kahuna Hapu</v>
+        <v>Alola Pokemon League</v>
       </c>
       <c r="C200" t="str">
         <v>Boss Battle</v>
@@ -4395,7 +4395,7 @@
         <v>Boss</v>
       </c>
       <c r="E200" t="str">
-        <v>81-86</v>
+        <v>84-89</v>
       </c>
       <c r="F200" t="str">
         <v>-</v>
@@ -4403,342 +4403,342 @@
     </row>
     <row r="201">
       <c r="A201">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B201" t="str">
-        <v>Mount Lanakila</v>
+        <v>Champion Hau</v>
       </c>
       <c r="C201" t="str">
-        <v>Cave</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D201" t="str">
-        <v>Drampa</v>
+        <v>Boss</v>
       </c>
       <c r="E201" t="str">
-        <v>83-88</v>
+        <v>85-90</v>
       </c>
       <c r="F201" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="202">
       <c r="A202">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B202" t="str">
-        <v>Mount Lanakila</v>
+        <v>Route 7</v>
       </c>
       <c r="C202" t="str">
-        <v>Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D202" t="str">
-        <v>Glalie</v>
+        <v>Staryu</v>
       </c>
       <c r="E202" t="str">
-        <v>83-88</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F202" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="203">
       <c r="A203">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B203" t="str">
-        <v>Mount Lanakila</v>
+        <v>Route 7</v>
       </c>
       <c r="C203" t="str">
-        <v>Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D203" t="str">
-        <v>Sneasel</v>
+        <v>Pyukumuku</v>
       </c>
       <c r="E203" t="str">
-        <v>83-88</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F203" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="204">
       <c r="A204">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B204" t="str">
-        <v>Mount Lanakila</v>
+        <v>Route 7</v>
       </c>
       <c r="C204" t="str">
-        <v>Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D204" t="str">
-        <v>Crabominable</v>
+        <v>Corsola</v>
       </c>
       <c r="E204" t="str">
-        <v>83-88</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F204" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="205">
       <c r="A205">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B205" t="str">
-        <v>Alola Pokemon League</v>
+        <v>Route 7</v>
       </c>
       <c r="C205" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D205" t="str">
-        <v>Boss</v>
+        <v>Mareanie</v>
       </c>
       <c r="E205" t="str">
-        <v>84-89</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F205" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="206">
       <c r="A206">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B206" t="str">
-        <v>Champion Hau</v>
+        <v>Route 7</v>
       </c>
       <c r="C206" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D206" t="str">
-        <v>Boss</v>
+        <v>Bruxish</v>
       </c>
       <c r="E206" t="str">
-        <v>85-90</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F206" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="207">
       <c r="A207">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B207" t="str">
-        <v>Route 7</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C207" t="str">
-        <v>Main Area</v>
+        <v>Labs</v>
       </c>
       <c r="D207" t="str">
-        <v>Staryu</v>
+        <v>Type: Null</v>
       </c>
       <c r="E207" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F207" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="208">
       <c r="A208">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B208" t="str">
-        <v>Route 7</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C208" t="str">
-        <v>Main Area</v>
+        <v>Labs</v>
       </c>
       <c r="D208" t="str">
-        <v>Pyukumuku</v>
+        <v>Ditto</v>
       </c>
       <c r="E208" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F208" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="209">
       <c r="A209">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B209" t="str">
-        <v>Route 7</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C209" t="str">
-        <v>Main Area</v>
+        <v>Labs</v>
       </c>
       <c r="D209" t="str">
-        <v>Corsola</v>
+        <v>Porygon</v>
       </c>
       <c r="E209" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F209" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="210">
       <c r="A210">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B210" t="str">
-        <v>Route 7</v>
+        <v>Ruins of Conflict</v>
       </c>
       <c r="C210" t="str">
-        <v>Main Area</v>
+        <v>Special Encounter</v>
       </c>
       <c r="D210" t="str">
-        <v>Mareanie</v>
+        <v>Special Encounter</v>
       </c>
       <c r="E210" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F210" t="str">
-        <v>20.00%</v>
+        <v>100%</v>
       </c>
     </row>
     <row r="211">
       <c r="A211">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B211" t="str">
-        <v>Route 7</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C211" t="str">
         <v>Main Area</v>
       </c>
       <c r="D211" t="str">
-        <v>Bruxish</v>
+        <v>Tapu Koko</v>
       </c>
       <c r="E211" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F211" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="212">
       <c r="A212">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B212" t="str">
-        <v>Aether Paradise</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C212" t="str">
-        <v>Labs</v>
+        <v>Main Area</v>
       </c>
       <c r="D212" t="str">
-        <v>Type: Null</v>
+        <v>Tapu Lele</v>
       </c>
       <c r="E212" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F212" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="213">
       <c r="A213">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B213" t="str">
-        <v>Aether Paradise</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C213" t="str">
-        <v>Labs</v>
+        <v>Main Area</v>
       </c>
       <c r="D213" t="str">
-        <v>Ditto</v>
+        <v>Tapu Bulu</v>
       </c>
       <c r="E213" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F213" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="214">
       <c r="A214">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B214" t="str">
-        <v>Aether Paradise</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C214" t="str">
-        <v>Labs</v>
+        <v>Main Area</v>
       </c>
       <c r="D214" t="str">
-        <v>Porygon</v>
+        <v>Tapu Fini</v>
       </c>
       <c r="E214" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F214" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="215">
       <c r="A215">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B215" t="str">
-        <v>Ruins of Conflict</v>
+        <v>Route 15</v>
       </c>
       <c r="C215" t="str">
-        <v>Tapu Koko</v>
+        <v>Main Area</v>
       </c>
       <c r="D215" t="str">
-        <v>Tapu Koko</v>
+        <v>Special Encounter</v>
       </c>
       <c r="E215" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F215" t="str">
-        <v>100.00%</v>
+        <v>100%</v>
       </c>
     </row>
     <row r="216">
       <c r="A216">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B216" t="str">
-        <v>Ruins of Life</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C216" t="str">
-        <v>Tapu Lele</v>
+        <v>Main Area</v>
       </c>
       <c r="D216" t="str">
-        <v>Tapu Lele</v>
+        <v>Cosmog</v>
       </c>
       <c r="E216" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F216" t="str">
-        <v>100.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="217">
       <c r="A217">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B217" t="str">
-        <v>Ruins of Abundance</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C217" t="str">
-        <v>Tapu Bulu</v>
+        <v>Main Area</v>
       </c>
       <c r="D217" t="str">
-        <v>Tapu Bulu</v>
+        <v>Cosmoem</v>
       </c>
       <c r="E217" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F217" t="str">
-        <v>100.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="218">
@@ -4746,284 +4746,284 @@
         <v>58</v>
       </c>
       <c r="B218" t="str">
-        <v>Ruins of Hope</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C218" t="str">
-        <v>Tapu Fini</v>
+        <v>Main Area</v>
       </c>
       <c r="D218" t="str">
-        <v>Tapu Fini</v>
+        <v>Solgaleo</v>
       </c>
       <c r="E218" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F218" t="str">
-        <v>100.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="219">
       <c r="A219">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B219" t="str">
-        <v>Lake of the Sunne</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C219" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D219" t="str">
-        <v>Cosmog</v>
+        <v>Lunala</v>
       </c>
       <c r="E219" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F219" t="str">
-        <v>100.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="220">
       <c r="A220">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B220" t="str">
-        <v>Altar of the Sunne</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C220" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D220" t="str">
-        <v>Solgaleo</v>
+        <v>Necrozma</v>
       </c>
       <c r="E220" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F220" t="str">
-        <v>100.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="221">
       <c r="A221">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B221" t="str">
-        <v>Altar of the Moone</v>
+        <v>Route 3</v>
       </c>
       <c r="C221" t="str">
-        <v>Special Encounter</v>
+        <v>North</v>
       </c>
       <c r="D221" t="str">
-        <v>Lunala</v>
+        <v>Mankey</v>
       </c>
       <c r="E221" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F221" t="str">
-        <v>100.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="222">
       <c r="A222">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B222" t="str">
-        <v>Ultra Deep Sea</v>
+        <v>Route 3</v>
       </c>
       <c r="C222" t="str">
-        <v>Nihilego</v>
+        <v>North</v>
       </c>
       <c r="D222" t="str">
-        <v>Nihilego</v>
+        <v>Delibird</v>
       </c>
       <c r="E222" t="str">
-        <v>90-100</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F222" t="str">
-        <v>100.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="223">
       <c r="A223">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B223" t="str">
-        <v>Ultra Jungle</v>
+        <v>Route 3</v>
       </c>
       <c r="C223" t="str">
-        <v>Buzzwole</v>
+        <v>North</v>
       </c>
       <c r="D223" t="str">
-        <v>Buzzwole</v>
+        <v>Bagon</v>
       </c>
       <c r="E223" t="str">
-        <v>90-100</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F223" t="str">
-        <v>100.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="224">
       <c r="A224">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B224" t="str">
-        <v>Ultra Desert</v>
+        <v>Route 3</v>
       </c>
       <c r="C224" t="str">
-        <v>Pheromosa</v>
+        <v>North</v>
       </c>
       <c r="D224" t="str">
-        <v>Pheromosa</v>
+        <v>Oricorio</v>
       </c>
       <c r="E224" t="str">
-        <v>90-100</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F224" t="str">
-        <v>100.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="225">
       <c r="A225">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B225" t="str">
-        <v>Ultra Plant</v>
+        <v>Route 3</v>
       </c>
       <c r="C225" t="str">
-        <v>Xurkitree</v>
+        <v>North</v>
       </c>
       <c r="D225" t="str">
-        <v>Xurkitree</v>
+        <v>Igglybuff</v>
       </c>
       <c r="E225" t="str">
-        <v>90-100</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F225" t="str">
-        <v>100.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="226">
       <c r="A226">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B226" t="str">
-        <v>Ultra Crater</v>
+        <v>Ten Carat Hill</v>
       </c>
       <c r="C226" t="str">
-        <v>Celesteela</v>
+        <v>Deepest Cave</v>
       </c>
       <c r="D226" t="str">
-        <v>Celesteela</v>
+        <v>Special Encounter</v>
       </c>
       <c r="E226" t="str">
-        <v>90-100</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F226" t="str">
-        <v>100.00%</v>
+        <v>100%</v>
       </c>
     </row>
     <row r="227">
       <c r="A227">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B227" t="str">
-        <v>Ultra Forest</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C227" t="str">
-        <v>Kartana</v>
+        <v>Main Area</v>
       </c>
       <c r="D227" t="str">
-        <v>Kartana</v>
+        <v>Buneary</v>
       </c>
       <c r="E227" t="str">
         <v>90-100</v>
       </c>
       <c r="F227" t="str">
-        <v>100.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="228">
       <c r="A228">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B228" t="str">
-        <v>Ultra Ruin</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C228" t="str">
-        <v>Guzzlord</v>
+        <v>Main Area</v>
       </c>
       <c r="D228" t="str">
-        <v>Guzzlord</v>
+        <v>Granbull</v>
       </c>
       <c r="E228" t="str">
         <v>90-100</v>
       </c>
       <c r="F228" t="str">
-        <v>100.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="229">
       <c r="A229">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B229" t="str">
-        <v>Ultra Megalopolis</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C229" t="str">
-        <v>Poipole</v>
+        <v>Main Area</v>
       </c>
       <c r="D229" t="str">
-        <v>Poipole</v>
+        <v>Zoroark</v>
       </c>
       <c r="E229" t="str">
         <v>90-100</v>
       </c>
       <c r="F229" t="str">
-        <v>100.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="230">
       <c r="A230">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B230" t="str">
-        <v>Ultra Megalopolis</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C230" t="str">
-        <v>Stakataka</v>
+        <v>Main Area</v>
       </c>
       <c r="D230" t="str">
-        <v>Stakataka</v>
+        <v>Heracross</v>
       </c>
       <c r="E230" t="str">
         <v>90-100</v>
       </c>
       <c r="F230" t="str">
-        <v>100.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="231">
       <c r="A231">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B231" t="str">
-        <v>Ultra Megalopolis</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C231" t="str">
-        <v>Blacephalon</v>
+        <v>Main Area</v>
       </c>
       <c r="D231" t="str">
-        <v>Blacephalon</v>
+        <v>Riolu</v>
       </c>
       <c r="E231" t="str">
         <v>90-100</v>
       </c>
       <c r="F231" t="str">
-        <v>100.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="232">
       <c r="A232">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B232" t="str">
         <v>Poni Grove</v>
@@ -5032,18 +5032,18 @@
         <v>Main Area</v>
       </c>
       <c r="D232" t="str">
-        <v>Buneary</v>
+        <v>Hariyama</v>
       </c>
       <c r="E232" t="str">
         <v>90-100</v>
       </c>
       <c r="F232" t="str">
-        <v>11.11%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="233">
       <c r="A233">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B233" t="str">
         <v>Poni Grove</v>
@@ -5052,27 +5052,27 @@
         <v>Main Area</v>
       </c>
       <c r="D233" t="str">
-        <v>Granbull</v>
+        <v>Mudsdale</v>
       </c>
       <c r="E233" t="str">
         <v>90-100</v>
       </c>
       <c r="F233" t="str">
-        <v>11.11%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="234">
       <c r="A234">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B234" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C234" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D234" t="str">
-        <v>Zoroark</v>
+        <v>Nihilego</v>
       </c>
       <c r="E234" t="str">
         <v>90-100</v>
@@ -5083,16 +5083,16 @@
     </row>
     <row r="235">
       <c r="A235">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B235" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C235" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D235" t="str">
-        <v>Heracross</v>
+        <v>Buzzwole</v>
       </c>
       <c r="E235" t="str">
         <v>90-100</v>
@@ -5103,16 +5103,16 @@
     </row>
     <row r="236">
       <c r="A236">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B236" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C236" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D236" t="str">
-        <v>Riolu</v>
+        <v>Pheromosa</v>
       </c>
       <c r="E236" t="str">
         <v>90-100</v>
@@ -5123,16 +5123,16 @@
     </row>
     <row r="237">
       <c r="A237">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B237" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C237" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D237" t="str">
-        <v>Stakataka</v>
+        <v>Xurkitree</v>
       </c>
       <c r="E237" t="str">
         <v>90-100</v>
@@ -5143,16 +5143,16 @@
     </row>
     <row r="238">
       <c r="A238">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B238" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C238" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D238" t="str">
-        <v>Blacephalon</v>
+        <v>Celesteela</v>
       </c>
       <c r="E238" t="str">
         <v>90-100</v>
@@ -5163,16 +5163,16 @@
     </row>
     <row r="239">
       <c r="A239">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B239" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C239" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D239" t="str">
-        <v>Hariyama</v>
+        <v>Kartana</v>
       </c>
       <c r="E239" t="str">
         <v>90-100</v>
@@ -5183,16 +5183,16 @@
     </row>
     <row r="240">
       <c r="A240">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B240" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C240" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D240" t="str">
-        <v>Mudsdale</v>
+        <v>Guzzlord</v>
       </c>
       <c r="E240" t="str">
         <v>90-100</v>
@@ -5203,127 +5203,127 @@
     </row>
     <row r="241">
       <c r="A241">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B241" t="str">
-        <v>Poni Plains</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C241" t="str">
-        <v>Center</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D241" t="str">
-        <v>Special Encounter</v>
+        <v>Poipole</v>
       </c>
       <c r="E241" t="str">
         <v>90-100</v>
       </c>
       <c r="F241" t="str">
-        <v>100%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="242">
       <c r="A242">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B242" t="str">
-        <v>Resolution Cave</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C242" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D242" t="str">
-        <v>Noivern</v>
+        <v>Stakataka</v>
       </c>
       <c r="E242" t="str">
         <v>90-100</v>
       </c>
       <c r="F242" t="str">
-        <v>33.33%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="243">
       <c r="A243">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B243" t="str">
-        <v>Resolution Cave</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C243" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 2</v>
       </c>
       <c r="D243" t="str">
-        <v>Druddigon</v>
+        <v>Blacephalon</v>
       </c>
       <c r="E243" t="str">
         <v>90-100</v>
       </c>
       <c r="F243" t="str">
-        <v>33.33%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="244">
       <c r="A244">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B244" t="str">
-        <v>Resolution Cave</v>
+        <v>Poni Plains</v>
       </c>
       <c r="C244" t="str">
-        <v>Main Area</v>
+        <v>Center</v>
       </c>
       <c r="D244" t="str">
-        <v>Guzzlord</v>
+        <v>Special Encounter</v>
       </c>
       <c r="E244" t="str">
         <v>90-100</v>
       </c>
       <c r="F244" t="str">
-        <v>33.33%</v>
+        <v>100%</v>
       </c>
     </row>
     <row r="245">
       <c r="A245">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B245" t="str">
-        <v>Shopping Mall Antiquities</v>
+        <v>Resolution Cave</v>
       </c>
       <c r="C245" t="str">
-        <v>Event</v>
+        <v>Main Area</v>
       </c>
       <c r="D245" t="str">
-        <v>Magearna</v>
+        <v>Special Encounter</v>
       </c>
       <c r="E245" t="str">
         <v>90-100</v>
       </c>
       <c r="F245" t="str">
-        <v>100.00%</v>
+        <v>100%</v>
       </c>
     </row>
     <row r="246">
       <c r="A246">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B246" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Shopping Mall Antiquities</v>
       </c>
       <c r="C246" t="str">
-        <v>Deepest Cave</v>
+        <v>Event</v>
       </c>
       <c r="D246" t="str">
-        <v>Special Encounter</v>
+        <v>Magearna</v>
       </c>
       <c r="E246" t="str">
         <v>90-100</v>
       </c>
       <c r="F246" t="str">
-        <v>100%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="247">
       <c r="A247">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B247" t="str">
         <v>Aether Paradise</v>
@@ -5350,7 +5350,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C68"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5951,7 +5951,7 @@
         <v>Extra Challenge $1-2</v>
       </c>
       <c r="B55" t="str">
-        <v>Defeat 15 Pokemon in Route 7</v>
+        <v>Defeat 15 Pokemon in Route 7 Main Area</v>
       </c>
       <c r="C55" t="str">
         <v>Aether Paradise Labs</v>
@@ -5962,10 +5962,10 @@
         <v>Extra Challenge $2-1</v>
       </c>
       <c r="B56" t="str">
-        <v>Defeat 15 Pokemon in Route 3 North</v>
+        <v>Defeat Kahuna Hala</v>
       </c>
       <c r="C56" t="str">
-        <v>Ruins of Conflict Tapu Koko</v>
+        <v>Ruins of Conflict Special Encounter</v>
       </c>
     </row>
     <row r="57">
@@ -5973,10 +5973,10 @@
         <v>Extra Challenge $2-2</v>
       </c>
       <c r="B57" t="str">
-        <v>Defeat 15 Pokemon in Akala Outskirts</v>
+        <v>Defeat 15 Pokemon in Ruins of Conflict Special Encounter</v>
       </c>
       <c r="C57" t="str">
-        <v>Ruins of Life Tapu Lele</v>
+        <v>Sacred Shrine Main Area</v>
       </c>
     </row>
     <row r="58">
@@ -5987,7 +5987,7 @@
         <v>Defeat Kahuna Nanu</v>
       </c>
       <c r="C58" t="str">
-        <v>Ruins of Abundance Tapu Bulu</v>
+        <v>Route 15 Main Area</v>
       </c>
     </row>
     <row r="59">
@@ -5995,10 +5995,10 @@
         <v>Extra Challenge $3-2</v>
       </c>
       <c r="B59" t="str">
-        <v>Defeat 15 Pokemon in Poni Breaker Coast</v>
+        <v>Defeat 15 Pokemon in Route 15 Main Area</v>
       </c>
       <c r="C59" t="str">
-        <v>Ruins of Hope Tapu Fini</v>
+        <v>Obsidian Sphere Main Area</v>
       </c>
     </row>
     <row r="60">
@@ -6006,10 +6006,10 @@
         <v>Extra Challenge $4-1</v>
       </c>
       <c r="B60" t="str">
-        <v>Defeat Captain Kommo-o</v>
+        <v>Defeat Captain Ilima</v>
       </c>
       <c r="C60" t="str">
-        <v>Lake of the Sunne Special Encounter</v>
+        <v>Route 3 North</v>
       </c>
     </row>
     <row r="61">
@@ -6017,209 +6017,99 @@
         <v>Extra Challenge $4-2</v>
       </c>
       <c r="B61" t="str">
-        <v>Defeat 10 Pokemon in Lake of the Sunne</v>
+        <v>Defeat 15 Pokemon in Route 3 North</v>
       </c>
       <c r="C61" t="str">
-        <v>Altar of the Sunne Special Encounter</v>
+        <v>Ten Carat Hill Deepest Cave</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Extra Challenge $4-3</v>
+        <v>Extra Challenge $5-1</v>
       </c>
       <c r="B62" t="str">
-        <v>Defeat 10 Pokemon in Altar of the Sunne</v>
+        <v>Defeat Champion Hau</v>
       </c>
       <c r="C62" t="str">
-        <v>Altar of the Moone Special Encounter</v>
+        <v>Poni Grove Main Area</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Extra Challenge $5-1</v>
+        <v>Extra Challenge $5-2</v>
       </c>
       <c r="B63" t="str">
-        <v>Defeat Champion Hau</v>
+        <v>Defeat 15 Pokemon in Poni Grove Main Area</v>
       </c>
       <c r="C63" t="str">
-        <v>Ultra Deep Sea Nihilego</v>
+        <v>The Interdimensional Rift Main Area Part 1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Extra Challenge $5-2</v>
+        <v>Extra Challenge $5-3</v>
       </c>
       <c r="B64" t="str">
-        <v>Defeat 10 Pokemon in Ultra Deep Sea</v>
+        <v>Defeat 15 Pokemon in The Interdimensional Rift Main Area Part 1</v>
       </c>
       <c r="C64" t="str">
-        <v>Ultra Jungle Buzzwole</v>
+        <v>The Interdimensional Rift Main Area Part 2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Extra Challenge $5-3</v>
+        <v>Extra Challenge $6-1</v>
       </c>
       <c r="B65" t="str">
-        <v>Defeat 10 Pokemon in Ultra Jungle</v>
+        <v>Defeat Champion Hau</v>
       </c>
       <c r="C65" t="str">
-        <v>Ultra Desert Pheromosa</v>
+        <v>Poni Plains Center</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Extra Challenge $5-4</v>
+        <v>Extra Challenge $6-2</v>
       </c>
       <c r="B66" t="str">
-        <v>Defeat 10 Pokemon in Ultra Desert</v>
+        <v>Defeat 15 Pokemon in Poni Plains Center</v>
       </c>
       <c r="C66" t="str">
-        <v>Ultra Plant Xurkitree</v>
+        <v>Resolution Cave Main Area</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Extra Challenge $5-5</v>
+        <v>Extra Challenge $6-3</v>
       </c>
       <c r="B67" t="str">
-        <v>Defeat 10 Pokemon in Ultra Plant</v>
+        <v>Defeat 15 Pokemon in Resolution Cave Main Area</v>
       </c>
       <c r="C67" t="str">
-        <v>Ultra Crater Celesteela</v>
+        <v>Shopping Mall Antiquities Event</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Extra Challenge $5-6</v>
+        <v>Extra Challenge $6-4</v>
       </c>
       <c r="B68" t="str">
-        <v>Defeat 10 Pokemon in Ultra Crater</v>
+        <v>Defeat 15 Pokemon in Shopping Mall Antiquities Event</v>
       </c>
       <c r="C68" t="str">
-        <v>Ultra Forest Kartana</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>Extra Challenge $5-7</v>
-      </c>
-      <c r="B69" t="str">
-        <v>Defeat 10 Pokemon in Ultra Forest</v>
-      </c>
-      <c r="C69" t="str">
-        <v>Ultra Ruin Guzzlord</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>Extra Challenge $5-8</v>
-      </c>
-      <c r="B70" t="str">
-        <v>Defeat 10 Pokemon in Ultra Ruin</v>
-      </c>
-      <c r="C70" t="str">
-        <v>Ultra Megalopolis Poipole</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>Extra Challenge $5-9</v>
-      </c>
-      <c r="B71" t="str">
-        <v>Defeat 10 Pokemon in Ultra Megalopolis Poipole</v>
-      </c>
-      <c r="C71" t="str">
-        <v>Ultra Megalopolis Stakataka</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>Extra Challenge $5-10</v>
-      </c>
-      <c r="B72" t="str">
-        <v>Defeat 10 Pokemon in Ultra Megalopolis Stakataka</v>
-      </c>
-      <c r="C72" t="str">
-        <v>Ultra Megalopolis Blacephalon</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>Extra Challenge $6-1</v>
-      </c>
-      <c r="B73" t="str">
-        <v>Defeat Champion Hau</v>
-      </c>
-      <c r="C73" t="str">
-        <v>Poni Grove Main Area</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>Extra Challenge $6-2</v>
-      </c>
-      <c r="B74" t="str">
-        <v>Defeat 15 Pokemon in Poni Grove Main Area</v>
-      </c>
-      <c r="C74" t="str">
-        <v>Poni Plains Center</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>Extra Challenge $6-3</v>
-      </c>
-      <c r="B75" t="str">
-        <v>Defeat 15 Pokemon in Poni Plains Center</v>
-      </c>
-      <c r="C75" t="str">
-        <v>Resolution Cave Main Area</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>Extra Challenge $6-4</v>
-      </c>
-      <c r="B76" t="str">
-        <v>Defeat 15 Pokemon in Resolution Cave Main Area</v>
-      </c>
-      <c r="C76" t="str">
-        <v>Shopping Mall Antiquities Event</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v>Extra Challenge $6-5</v>
-      </c>
-      <c r="B77" t="str">
-        <v>Defeat 15 Pokemon in Shopping Mall Antiquities Event</v>
-      </c>
-      <c r="C77" t="str">
-        <v>Ten Carat Hill Deepest Cave</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>Extra Challenge $6-6</v>
-      </c>
-      <c r="B78" t="str">
-        <v>Defeat 15 Pokemon in Ten Carat Hill Deepest Cave</v>
-      </c>
-      <c r="C78" t="str">
         <v>Aether Paradise Secret Lab</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C78"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C68"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D44"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6523,7 +6413,7 @@
         <v>Electric/Fairy</v>
       </c>
       <c r="C22" t="str">
-        <v>Ruins of Conflict</v>
+        <v>Sacred Shrine Main Area</v>
       </c>
       <c r="D22" t="str">
         <v>Yes (Added to Extra)</v>
@@ -6537,7 +6427,7 @@
         <v>Psychic/Fairy</v>
       </c>
       <c r="C23" t="str">
-        <v>Ruins of Life</v>
+        <v>Sacred Shrine Main Area</v>
       </c>
       <c r="D23" t="str">
         <v>Yes (Added to Extra)</v>
@@ -6551,7 +6441,7 @@
         <v>Grass/Fairy</v>
       </c>
       <c r="C24" t="str">
-        <v>Ruins of Abundance</v>
+        <v>Sacred Shrine Main Area</v>
       </c>
       <c r="D24" t="str">
         <v>Yes (Added to Extra)</v>
@@ -6565,7 +6455,7 @@
         <v>Water/Fairy</v>
       </c>
       <c r="C25" t="str">
-        <v>Ruins of Hope</v>
+        <v>Sacred Shrine Main Area</v>
       </c>
       <c r="D25" t="str">
         <v>Yes (Added to Extra)</v>
@@ -6579,7 +6469,7 @@
         <v>Psychic</v>
       </c>
       <c r="C26" t="str">
-        <v>Lake of the Sunne</v>
+        <v>Obsidian Sphere Main Area</v>
       </c>
       <c r="D26" t="str">
         <v>Yes (Added to Extra)</v>
@@ -6593,7 +6483,7 @@
         <v>Psychic</v>
       </c>
       <c r="C27" t="str">
-        <v>Lake of the Sunne</v>
+        <v>Obsidian Sphere Main Area</v>
       </c>
       <c r="D27" t="str">
         <v>Yes (Evolution)</v>
@@ -6601,13 +6491,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Poipole</v>
+        <v>Solgaleo</v>
       </c>
       <c r="B28" t="str">
-        <v>Poison</v>
+        <v>Psychic/Steel</v>
       </c>
       <c r="C28" t="str">
-        <v>Ultra Megalopolis</v>
+        <v>Obsidian Sphere Main Area</v>
       </c>
       <c r="D28" t="str">
         <v>Yes (Added to Extra)</v>
@@ -6615,27 +6505,27 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Naganadel</v>
+        <v>Lunala</v>
       </c>
       <c r="B29" t="str">
-        <v>Poison/Dragon</v>
+        <v>Psychic/Ghost</v>
       </c>
       <c r="C29" t="str">
-        <v>Ultra Megalopolis</v>
+        <v>Obsidian Sphere Main Area</v>
       </c>
       <c r="D29" t="str">
-        <v>Yes (Evolution)</v>
+        <v>Yes (Added to Extra)</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Magearna</v>
+        <v>Necrozma</v>
       </c>
       <c r="B30" t="str">
-        <v>Steel/Fairy</v>
+        <v>Psychic</v>
       </c>
       <c r="C30" t="str">
-        <v>Shopping Mall Antiquities Event</v>
+        <v>Obsidian Sphere Main Area</v>
       </c>
       <c r="D30" t="str">
         <v>Yes (Added to Extra)</v>
@@ -6643,13 +6533,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Marshadow</v>
+        <v>Poipole</v>
       </c>
       <c r="B31" t="str">
-        <v>Ghost/Fighting</v>
+        <v>Poison</v>
       </c>
       <c r="C31" t="str">
-        <v>Ten Carat Hill Deepest Cave</v>
+        <v>The Interdimensional Rift Main Area</v>
       </c>
       <c r="D31" t="str">
         <v>Yes (Added to Extra)</v>
@@ -6657,21 +6547,189 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
+        <v>Naganadel</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Poison/Dragon</v>
+      </c>
+      <c r="C32" t="str">
+        <v>The Interdimensional Rift Main Area</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Yes (Evolution)</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Nihilego</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Rock/Poison</v>
+      </c>
+      <c r="C33" t="str">
+        <v>The Interdimensional Rift Main Area</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Yes (Added to Extra)</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Buzzwole</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Bug/Fighting</v>
+      </c>
+      <c r="C34" t="str">
+        <v>The Interdimensional Rift Main Area</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Yes (Added to Extra)</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Pheromosa</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Bug/Fighting</v>
+      </c>
+      <c r="C35" t="str">
+        <v>The Interdimensional Rift Main Area</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Yes (Added to Extra)</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Xurkitree</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Electric</v>
+      </c>
+      <c r="C36" t="str">
+        <v>The Interdimensional Rift Main Area</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Yes (Added to Extra)</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Celesteela</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Steel/Flying</v>
+      </c>
+      <c r="C37" t="str">
+        <v>The Interdimensional Rift Main Area</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Yes (Added to Extra)</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Kartana</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Grass/Steel</v>
+      </c>
+      <c r="C38" t="str">
+        <v>The Interdimensional Rift Main Area</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Yes (Added to Extra)</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Guzzlord</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Dark/Dragon</v>
+      </c>
+      <c r="C39" t="str">
+        <v>The Interdimensional Rift Main Area</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Yes (Added to Extra)</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Stakataka</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Rock/Steel</v>
+      </c>
+      <c r="C40" t="str">
+        <v>The Interdimensional Rift Main Area</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Yes (Added to Extra)</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Blacephalon</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Fire/Ghost</v>
+      </c>
+      <c r="C41" t="str">
+        <v>The Interdimensional Rift Main Area</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Yes (Added to Extra)</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Magearna</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Steel/Fairy</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Shopping Mall Antiquities Event</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Yes (Added to Extra)</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Marshadow</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Ghost/Fighting</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Ten Carat Hill Deepest Cave</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Yes (Added to Extra)</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
         <v>Zeraora</v>
       </c>
-      <c r="B32" t="str">
+      <c r="B44" t="str">
         <v>Electric</v>
       </c>
-      <c r="C32" t="str">
+      <c r="C44" t="str">
         <v>Aether Paradise Secret Lab</v>
       </c>
-      <c r="D32" t="str">
+      <c r="D44" t="str">
         <v>Yes (Added to Extra)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D44"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Alola_Paths_and_Challenges.xlsx
+++ b/Alola_Paths_and_Challenges.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F247"/>
+  <dimension ref="A1:F248"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1078,7 +1078,7 @@
         <v>14-19</v>
       </c>
       <c r="F34" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="35">
@@ -1098,7 +1098,7 @@
         <v>14-19</v>
       </c>
       <c r="F35" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="36">
@@ -1118,7 +1118,7 @@
         <v>14-19</v>
       </c>
       <c r="F36" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="37">
@@ -1138,7 +1138,7 @@
         <v>14-19</v>
       </c>
       <c r="F37" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="38">
@@ -1158,27 +1158,27 @@
         <v>14-19</v>
       </c>
       <c r="F38" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B39" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Seaward Cave</v>
       </c>
       <c r="C39" t="str">
-        <v>Farthest Hollow</v>
+        <v>Main Area</v>
       </c>
       <c r="D39" t="str">
-        <v>Marshadow</v>
+        <v>Barboach</v>
       </c>
       <c r="E39" t="str">
-        <v>14-19</v>
+        <v>16-21</v>
       </c>
       <c r="F39" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="40">
@@ -1192,10 +1192,10 @@
         <v>Main Area</v>
       </c>
       <c r="D40" t="str">
-        <v>Barboach</v>
+        <v>Smoochum</v>
       </c>
       <c r="E40" t="str">
-        <v>15-20</v>
+        <v>16-21</v>
       </c>
       <c r="F40" t="str">
         <v>33.33%</v>
@@ -1212,10 +1212,10 @@
         <v>Main Area</v>
       </c>
       <c r="D41" t="str">
-        <v>Smoochum</v>
+        <v>Seel</v>
       </c>
       <c r="E41" t="str">
-        <v>15-20</v>
+        <v>16-21</v>
       </c>
       <c r="F41" t="str">
         <v>33.33%</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B42" t="str">
-        <v>Seaward Cave</v>
+        <v>Route 3</v>
       </c>
       <c r="C42" t="str">
-        <v>Main Area</v>
+        <v>North</v>
       </c>
       <c r="D42" t="str">
-        <v>Seel</v>
+        <v>Mankey</v>
       </c>
       <c r="E42" t="str">
-        <v>15-20</v>
+        <v>17-22</v>
       </c>
       <c r="F42" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="43">
@@ -1252,7 +1252,7 @@
         <v>North</v>
       </c>
       <c r="D43" t="str">
-        <v>Mankey</v>
+        <v>Delibird</v>
       </c>
       <c r="E43" t="str">
         <v>17-22</v>
@@ -1272,7 +1272,7 @@
         <v>North</v>
       </c>
       <c r="D44" t="str">
-        <v>Delibird</v>
+        <v>Bagon</v>
       </c>
       <c r="E44" t="str">
         <v>17-22</v>
@@ -1292,7 +1292,7 @@
         <v>North</v>
       </c>
       <c r="D45" t="str">
-        <v>Bagon</v>
+        <v>Oricorio</v>
       </c>
       <c r="E45" t="str">
         <v>17-22</v>
@@ -1312,7 +1312,7 @@
         <v>North</v>
       </c>
       <c r="D46" t="str">
-        <v>Oricorio</v>
+        <v>Igglybuff</v>
       </c>
       <c r="E46" t="str">
         <v>17-22</v>
@@ -1323,42 +1323,42 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B47" t="str">
-        <v>Route 3</v>
+        <v>Kahuna Hala</v>
       </c>
       <c r="C47" t="str">
-        <v>North</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D47" t="str">
-        <v>Igglybuff</v>
+        <v>Boss</v>
       </c>
       <c r="E47" t="str">
-        <v>17-22</v>
+        <v>18-23</v>
       </c>
       <c r="F47" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B48" t="str">
-        <v>Kahuna Hala</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C48" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D48" t="str">
-        <v>Boss</v>
+        <v>Vikavolt</v>
       </c>
       <c r="E48" t="str">
-        <v>18-23</v>
+        <v>20-25</v>
       </c>
       <c r="F48" t="str">
-        <v>-</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="49">
@@ -1372,10 +1372,10 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D49" t="str">
-        <v>Vikavolt</v>
+        <v>Ribombee</v>
       </c>
       <c r="E49" t="str">
-        <v>19-24</v>
+        <v>20-25</v>
       </c>
       <c r="F49" t="str">
         <v>11.11%</v>
@@ -1392,10 +1392,10 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D50" t="str">
-        <v>Ribombee</v>
+        <v>Araquanid</v>
       </c>
       <c r="E50" t="str">
-        <v>19-24</v>
+        <v>20-25</v>
       </c>
       <c r="F50" t="str">
         <v>11.11%</v>
@@ -1412,10 +1412,10 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D51" t="str">
-        <v>Araquanid</v>
+        <v>Lurantis</v>
       </c>
       <c r="E51" t="str">
-        <v>19-24</v>
+        <v>20-25</v>
       </c>
       <c r="F51" t="str">
         <v>11.11%</v>
@@ -1432,10 +1432,10 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D52" t="str">
-        <v>Lurantis</v>
+        <v>Salazzle</v>
       </c>
       <c r="E52" t="str">
-        <v>19-24</v>
+        <v>20-25</v>
       </c>
       <c r="F52" t="str">
         <v>11.11%</v>
@@ -1452,10 +1452,10 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D53" t="str">
-        <v>Salazzle</v>
+        <v>Alolan Marowak</v>
       </c>
       <c r="E53" t="str">
-        <v>19-24</v>
+        <v>20-25</v>
       </c>
       <c r="F53" t="str">
         <v>11.11%</v>
@@ -1472,10 +1472,10 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D54" t="str">
-        <v>Alolan Marowak</v>
+        <v>Kommo-o</v>
       </c>
       <c r="E54" t="str">
-        <v>19-24</v>
+        <v>20-25</v>
       </c>
       <c r="F54" t="str">
         <v>11.11%</v>
@@ -1492,10 +1492,10 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D55" t="str">
-        <v>Kommo-o</v>
+        <v>Mimikyu</v>
       </c>
       <c r="E55" t="str">
-        <v>19-24</v>
+        <v>20-25</v>
       </c>
       <c r="F55" t="str">
         <v>11.11%</v>
@@ -1512,10 +1512,10 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D56" t="str">
-        <v>Mimikyu</v>
+        <v>Poliwhirl</v>
       </c>
       <c r="E56" t="str">
-        <v>19-24</v>
+        <v>20-25</v>
       </c>
       <c r="F56" t="str">
         <v>11.11%</v>
@@ -1523,42 +1523,42 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B57" t="str">
         <v>Heahea Beach</v>
       </c>
       <c r="C57" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area Part 2</v>
       </c>
       <c r="D57" t="str">
-        <v>Poliwhirl</v>
+        <v>Ditto</v>
       </c>
       <c r="E57" t="str">
-        <v>19-24</v>
+        <v>20-25</v>
       </c>
       <c r="F57" t="str">
-        <v>11.11%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B58" t="str">
-        <v>Heahea Beach</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C58" t="str">
-        <v>Main Area Part 2</v>
+        <v>Main Area</v>
       </c>
       <c r="D58" t="str">
-        <v>Ditto</v>
+        <v>Eevee</v>
       </c>
       <c r="E58" t="str">
-        <v>19-24</v>
+        <v>21-26</v>
       </c>
       <c r="F58" t="str">
-        <v>100.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="59">
@@ -1572,7 +1572,7 @@
         <v>Main Area</v>
       </c>
       <c r="D59" t="str">
-        <v>Eevee</v>
+        <v>Mareep</v>
       </c>
       <c r="E59" t="str">
         <v>21-26</v>
@@ -1592,7 +1592,7 @@
         <v>Main Area</v>
       </c>
       <c r="D60" t="str">
-        <v>Mareep</v>
+        <v>Tauros</v>
       </c>
       <c r="E60" t="str">
         <v>21-26</v>
@@ -1612,7 +1612,7 @@
         <v>Main Area</v>
       </c>
       <c r="D61" t="str">
-        <v>Tauros</v>
+        <v>Miltank</v>
       </c>
       <c r="E61" t="str">
         <v>21-26</v>
@@ -1623,42 +1623,42 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B62" t="str">
-        <v>Paniola Ranch</v>
+        <v>Daycare</v>
       </c>
       <c r="C62" t="str">
-        <v>Main Area</v>
+        <v>NPC</v>
       </c>
       <c r="D62" t="str">
-        <v>Miltank</v>
+        <v>NPC</v>
       </c>
       <c r="E62" t="str">
-        <v>21-26</v>
+        <v>-</v>
       </c>
       <c r="F62" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B63" t="str">
-        <v>Daycare</v>
+        <v>Route 5</v>
       </c>
       <c r="C63" t="str">
-        <v>NPC</v>
+        <v>Main Area</v>
       </c>
       <c r="D63" t="str">
-        <v>NPC</v>
+        <v>Noibat</v>
       </c>
       <c r="E63" t="str">
-        <v>-</v>
+        <v>24-29</v>
       </c>
       <c r="F63" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="64">
@@ -1672,10 +1672,10 @@
         <v>Main Area</v>
       </c>
       <c r="D64" t="str">
-        <v>Noibat</v>
+        <v>Fomantis</v>
       </c>
       <c r="E64" t="str">
-        <v>23-28</v>
+        <v>24-29</v>
       </c>
       <c r="F64" t="str">
         <v>33.33%</v>
@@ -1692,10 +1692,10 @@
         <v>Main Area</v>
       </c>
       <c r="D65" t="str">
-        <v>Fomantis</v>
+        <v>Bounsweet</v>
       </c>
       <c r="E65" t="str">
-        <v>23-28</v>
+        <v>24-29</v>
       </c>
       <c r="F65" t="str">
         <v>33.33%</v>
@@ -1703,22 +1703,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B66" t="str">
-        <v>Route 5</v>
+        <v>Brooklet Hill</v>
       </c>
       <c r="C66" t="str">
-        <v>Main Area</v>
+        <v>South</v>
       </c>
       <c r="D66" t="str">
-        <v>Bounsweet</v>
+        <v>Wingull</v>
       </c>
       <c r="E66" t="str">
-        <v>23-28</v>
+        <v>25-30</v>
       </c>
       <c r="F66" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="67">
@@ -1732,7 +1732,7 @@
         <v>South</v>
       </c>
       <c r="D67" t="str">
-        <v>Wingull</v>
+        <v>Lillipup</v>
       </c>
       <c r="E67" t="str">
         <v>25-30</v>
@@ -1752,7 +1752,7 @@
         <v>South</v>
       </c>
       <c r="D68" t="str">
-        <v>Lillipup</v>
+        <v>Paras</v>
       </c>
       <c r="E68" t="str">
         <v>25-30</v>
@@ -1772,7 +1772,7 @@
         <v>South</v>
       </c>
       <c r="D69" t="str">
-        <v>Paras</v>
+        <v>Goldeen</v>
       </c>
       <c r="E69" t="str">
         <v>25-30</v>
@@ -1792,7 +1792,7 @@
         <v>South</v>
       </c>
       <c r="D70" t="str">
-        <v>Goldeen</v>
+        <v>Feebas</v>
       </c>
       <c r="E70" t="str">
         <v>25-30</v>
@@ -1803,42 +1803,42 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B71" t="str">
-        <v>Brooklet Hill</v>
+        <v>Captain Lana</v>
       </c>
       <c r="C71" t="str">
-        <v>South</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D71" t="str">
-        <v>Feebas</v>
+        <v>Boss</v>
       </c>
       <c r="E71" t="str">
-        <v>25-30</v>
+        <v>27-32</v>
       </c>
       <c r="F71" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B72" t="str">
-        <v>Captain Lana</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C72" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D72" t="str">
-        <v>Boss</v>
+        <v>Cubone</v>
       </c>
       <c r="E72" t="str">
-        <v>26-31</v>
+        <v>28-33</v>
       </c>
       <c r="F72" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="73">
@@ -1852,10 +1852,10 @@
         <v>Main Area</v>
       </c>
       <c r="D73" t="str">
-        <v>Cubone</v>
+        <v>Kangaskhan</v>
       </c>
       <c r="E73" t="str">
-        <v>27-32</v>
+        <v>28-33</v>
       </c>
       <c r="F73" t="str">
         <v>33.33%</v>
@@ -1872,10 +1872,10 @@
         <v>Main Area</v>
       </c>
       <c r="D74" t="str">
-        <v>Kangaskhan</v>
+        <v>Magby</v>
       </c>
       <c r="E74" t="str">
-        <v>27-32</v>
+        <v>28-33</v>
       </c>
       <c r="F74" t="str">
         <v>33.33%</v>
@@ -1883,42 +1883,42 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B75" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Captain Kiawe</v>
       </c>
       <c r="C75" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D75" t="str">
-        <v>Magby</v>
+        <v>Boss</v>
       </c>
       <c r="E75" t="str">
-        <v>27-32</v>
+        <v>29-34</v>
       </c>
       <c r="F75" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B76" t="str">
-        <v>Captain Kiawe</v>
+        <v>Route 7</v>
       </c>
       <c r="C76" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D76" t="str">
-        <v>Boss</v>
+        <v>Staryu</v>
       </c>
       <c r="E76" t="str">
-        <v>29-34</v>
+        <v>31-36</v>
       </c>
       <c r="F76" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="77">
@@ -1932,10 +1932,10 @@
         <v>Main Area</v>
       </c>
       <c r="D77" t="str">
-        <v>Staryu</v>
+        <v>Pyukumuku</v>
       </c>
       <c r="E77" t="str">
-        <v>30-35</v>
+        <v>31-36</v>
       </c>
       <c r="F77" t="str">
         <v>20.00%</v>
@@ -1952,10 +1952,10 @@
         <v>Main Area</v>
       </c>
       <c r="D78" t="str">
-        <v>Pyukumuku</v>
+        <v>Corsola</v>
       </c>
       <c r="E78" t="str">
-        <v>30-35</v>
+        <v>31-36</v>
       </c>
       <c r="F78" t="str">
         <v>20.00%</v>
@@ -1972,10 +1972,10 @@
         <v>Main Area</v>
       </c>
       <c r="D79" t="str">
-        <v>Corsola</v>
+        <v>Mareanie</v>
       </c>
       <c r="E79" t="str">
-        <v>30-35</v>
+        <v>31-36</v>
       </c>
       <c r="F79" t="str">
         <v>20.00%</v>
@@ -1992,10 +1992,10 @@
         <v>Main Area</v>
       </c>
       <c r="D80" t="str">
-        <v>Mareanie</v>
+        <v>Bruxish</v>
       </c>
       <c r="E80" t="str">
-        <v>30-35</v>
+        <v>31-36</v>
       </c>
       <c r="F80" t="str">
         <v>20.00%</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B81" t="str">
-        <v>Route 7</v>
+        <v>Route 8</v>
       </c>
       <c r="C81" t="str">
-        <v>Main Area</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D81" t="str">
-        <v>Bruxish</v>
+        <v>Omanyte</v>
       </c>
       <c r="E81" t="str">
-        <v>30-35</v>
+        <v>32-37</v>
       </c>
       <c r="F81" t="str">
-        <v>20.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="82">
@@ -2032,7 +2032,7 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D82" t="str">
-        <v>Omanyte</v>
+        <v>Kabuto</v>
       </c>
       <c r="E82" t="str">
         <v>32-37</v>
@@ -2052,7 +2052,7 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D83" t="str">
-        <v>Kabuto</v>
+        <v>Lileep</v>
       </c>
       <c r="E83" t="str">
         <v>32-37</v>
@@ -2072,7 +2072,7 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D84" t="str">
-        <v>Lileep</v>
+        <v>Anorith</v>
       </c>
       <c r="E84" t="str">
         <v>32-37</v>
@@ -2092,7 +2092,7 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D85" t="str">
-        <v>Anorith</v>
+        <v>Cranidos</v>
       </c>
       <c r="E85" t="str">
         <v>32-37</v>
@@ -2112,7 +2112,7 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D86" t="str">
-        <v>Cranidos</v>
+        <v>Shieldon</v>
       </c>
       <c r="E86" t="str">
         <v>32-37</v>
@@ -2132,7 +2132,7 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D87" t="str">
-        <v>Shieldon</v>
+        <v>Archen</v>
       </c>
       <c r="E87" t="str">
         <v>32-37</v>
@@ -2152,7 +2152,7 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D88" t="str">
-        <v>Archen</v>
+        <v>Tirtouga</v>
       </c>
       <c r="E88" t="str">
         <v>32-37</v>
@@ -2172,7 +2172,7 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D89" t="str">
-        <v>Tirtouga</v>
+        <v>Tyrunt</v>
       </c>
       <c r="E89" t="str">
         <v>32-37</v>
@@ -2183,42 +2183,42 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B90" t="str">
         <v>Route 8</v>
       </c>
       <c r="C90" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D90" t="str">
-        <v>Tyrunt</v>
+        <v>Amaura</v>
       </c>
       <c r="E90" t="str">
         <v>32-37</v>
       </c>
       <c r="F90" t="str">
-        <v>11.11%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B91" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C91" t="str">
-        <v>Fossil Restoration Center Part 2</v>
+        <v>North</v>
       </c>
       <c r="D91" t="str">
-        <v>Amaura</v>
+        <v>Trumbeak</v>
       </c>
       <c r="E91" t="str">
-        <v>32-37</v>
+        <v>33-38</v>
       </c>
       <c r="F91" t="str">
-        <v>100.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="92">
@@ -2232,7 +2232,7 @@
         <v>North</v>
       </c>
       <c r="D92" t="str">
-        <v>Trumbeak</v>
+        <v>Steenee</v>
       </c>
       <c r="E92" t="str">
         <v>33-38</v>
@@ -2252,7 +2252,7 @@
         <v>North</v>
       </c>
       <c r="D93" t="str">
-        <v>Steenee</v>
+        <v>Comfey</v>
       </c>
       <c r="E93" t="str">
         <v>33-38</v>
@@ -2272,7 +2272,7 @@
         <v>North</v>
       </c>
       <c r="D94" t="str">
-        <v>Comfey</v>
+        <v>Hoothoot</v>
       </c>
       <c r="E94" t="str">
         <v>33-38</v>
@@ -2292,7 +2292,7 @@
         <v>North</v>
       </c>
       <c r="D95" t="str">
-        <v>Hoothoot</v>
+        <v>Oranguru</v>
       </c>
       <c r="E95" t="str">
         <v>33-38</v>
@@ -2312,7 +2312,7 @@
         <v>North</v>
       </c>
       <c r="D96" t="str">
-        <v>Oranguru</v>
+        <v>Bounsweet</v>
       </c>
       <c r="E96" t="str">
         <v>33-38</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B97" t="str">
         <v>Lush Jungle</v>
       </c>
       <c r="C97" t="str">
-        <v>North</v>
+        <v>East Cave</v>
       </c>
       <c r="D97" t="str">
-        <v>Bounsweet</v>
+        <v>Golbat</v>
       </c>
       <c r="E97" t="str">
-        <v>33-38</v>
+        <v>35-40</v>
       </c>
       <c r="F97" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="98">
@@ -2352,10 +2352,10 @@
         <v>East Cave</v>
       </c>
       <c r="D98" t="str">
-        <v>Golbat</v>
+        <v>Salandit</v>
       </c>
       <c r="E98" t="str">
-        <v>34-39</v>
+        <v>35-40</v>
       </c>
       <c r="F98" t="str">
         <v>20.00%</v>
@@ -2372,10 +2372,10 @@
         <v>East Cave</v>
       </c>
       <c r="D99" t="str">
-        <v>Salandit</v>
+        <v>Larvesta</v>
       </c>
       <c r="E99" t="str">
-        <v>34-39</v>
+        <v>35-40</v>
       </c>
       <c r="F99" t="str">
         <v>20.00%</v>
@@ -2392,10 +2392,10 @@
         <v>East Cave</v>
       </c>
       <c r="D100" t="str">
-        <v>Larvesta</v>
+        <v>Oranguru</v>
       </c>
       <c r="E100" t="str">
-        <v>34-39</v>
+        <v>35-40</v>
       </c>
       <c r="F100" t="str">
         <v>20.00%</v>
@@ -2412,10 +2412,10 @@
         <v>East Cave</v>
       </c>
       <c r="D101" t="str">
-        <v>Oranguru</v>
+        <v>Passimian</v>
       </c>
       <c r="E101" t="str">
-        <v>34-39</v>
+        <v>35-40</v>
       </c>
       <c r="F101" t="str">
         <v>20.00%</v>
@@ -2423,42 +2423,42 @@
     </row>
     <row r="102">
       <c r="A102">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B102" t="str">
-        <v>Lush Jungle</v>
+        <v>Captain Mallow</v>
       </c>
       <c r="C102" t="str">
-        <v>East Cave</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D102" t="str">
-        <v>Passimian</v>
+        <v>Boss</v>
       </c>
       <c r="E102" t="str">
-        <v>34-39</v>
+        <v>36-41</v>
       </c>
       <c r="F102" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="103">
       <c r="A103">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B103" t="str">
-        <v>Captain Mallow</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C103" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D103" t="str">
-        <v>Boss</v>
+        <v>Zubat</v>
       </c>
       <c r="E103" t="str">
-        <v>36-41</v>
+        <v>38-43</v>
       </c>
       <c r="F103" t="str">
-        <v>-</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="104">
@@ -2472,10 +2472,10 @@
         <v>Main Area</v>
       </c>
       <c r="D104" t="str">
-        <v>Zubat</v>
+        <v>Alolan Diglett</v>
       </c>
       <c r="E104" t="str">
-        <v>37-42</v>
+        <v>38-43</v>
       </c>
       <c r="F104" t="str">
         <v>25.00%</v>
@@ -2492,10 +2492,10 @@
         <v>Main Area</v>
       </c>
       <c r="D105" t="str">
-        <v>Alolan Diglett</v>
+        <v>Kecleon</v>
       </c>
       <c r="E105" t="str">
-        <v>37-42</v>
+        <v>38-43</v>
       </c>
       <c r="F105" t="str">
         <v>25.00%</v>
@@ -2512,10 +2512,10 @@
         <v>Main Area</v>
       </c>
       <c r="D106" t="str">
-        <v>Kecleon</v>
+        <v>Larvitar</v>
       </c>
       <c r="E106" t="str">
-        <v>37-42</v>
+        <v>38-43</v>
       </c>
       <c r="F106" t="str">
         <v>25.00%</v>
@@ -2523,27 +2523,27 @@
     </row>
     <row r="107">
       <c r="A107">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B107" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Memorial Hill</v>
       </c>
       <c r="C107" t="str">
-        <v>Main Area</v>
+        <v>Main</v>
       </c>
       <c r="D107" t="str">
-        <v>Larvitar</v>
+        <v>Phantump</v>
       </c>
       <c r="E107" t="str">
-        <v>37-42</v>
+        <v>42-47</v>
       </c>
       <c r="F107" t="str">
-        <v>25.00%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="108">
       <c r="A108">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B108" t="str">
         <v>Akala Outskirts</v>
@@ -2555,7 +2555,7 @@
         <v>Gumshoos</v>
       </c>
       <c r="E108" t="str">
-        <v>42-47</v>
+        <v>43-48</v>
       </c>
       <c r="F108" t="str">
         <v>12.50%</v>
@@ -2563,7 +2563,7 @@
     </row>
     <row r="109">
       <c r="A109">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B109" t="str">
         <v>Akala Outskirts</v>
@@ -2575,7 +2575,7 @@
         <v>Wingull</v>
       </c>
       <c r="E109" t="str">
-        <v>42-47</v>
+        <v>43-48</v>
       </c>
       <c r="F109" t="str">
         <v>12.50%</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="110">
       <c r="A110">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B110" t="str">
         <v>Akala Outskirts</v>
@@ -2595,7 +2595,7 @@
         <v>Magikarp</v>
       </c>
       <c r="E110" t="str">
-        <v>42-47</v>
+        <v>43-48</v>
       </c>
       <c r="F110" t="str">
         <v>12.50%</v>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="111">
       <c r="A111">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B111" t="str">
         <v>Akala Outskirts</v>
@@ -2615,7 +2615,7 @@
         <v>Stufful</v>
       </c>
       <c r="E111" t="str">
-        <v>42-47</v>
+        <v>43-48</v>
       </c>
       <c r="F111" t="str">
         <v>12.50%</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="112">
       <c r="A112">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B112" t="str">
         <v>Akala Outskirts</v>
@@ -2635,7 +2635,7 @@
         <v>Chinchou</v>
       </c>
       <c r="E112" t="str">
-        <v>42-47</v>
+        <v>43-48</v>
       </c>
       <c r="F112" t="str">
         <v>12.50%</v>
@@ -2643,7 +2643,7 @@
     </row>
     <row r="113">
       <c r="A113">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B113" t="str">
         <v>Akala Outskirts</v>
@@ -2655,7 +2655,7 @@
         <v>Alolan Raticate</v>
       </c>
       <c r="E113" t="str">
-        <v>42-47</v>
+        <v>43-48</v>
       </c>
       <c r="F113" t="str">
         <v>12.50%</v>
@@ -2663,7 +2663,7 @@
     </row>
     <row r="114">
       <c r="A114">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B114" t="str">
         <v>Akala Outskirts</v>
@@ -2675,7 +2675,7 @@
         <v>Natu</v>
       </c>
       <c r="E114" t="str">
-        <v>42-47</v>
+        <v>43-48</v>
       </c>
       <c r="F114" t="str">
         <v>12.50%</v>
@@ -2683,7 +2683,7 @@
     </row>
     <row r="115">
       <c r="A115">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B115" t="str">
         <v>Akala Outskirts</v>
@@ -2695,7 +2695,7 @@
         <v>Nosepass</v>
       </c>
       <c r="E115" t="str">
-        <v>42-47</v>
+        <v>43-48</v>
       </c>
       <c r="F115" t="str">
         <v>12.50%</v>
@@ -2703,7 +2703,7 @@
     </row>
     <row r="116">
       <c r="A116">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B116" t="str">
         <v>Kahuna Olivia</v>
@@ -2723,7 +2723,7 @@
     </row>
     <row r="117">
       <c r="A117">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B117" t="str">
         <v>Malie City</v>
@@ -2735,7 +2735,7 @@
         <v>Magnemite</v>
       </c>
       <c r="E117" t="str">
-        <v>46-51</v>
+        <v>47-52</v>
       </c>
       <c r="F117" t="str">
         <v>20.00%</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="118">
       <c r="A118">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B118" t="str">
         <v>Malie City</v>
@@ -2755,7 +2755,7 @@
         <v>Alolan Grimer</v>
       </c>
       <c r="E118" t="str">
-        <v>46-51</v>
+        <v>47-52</v>
       </c>
       <c r="F118" t="str">
         <v>20.00%</v>
@@ -2763,7 +2763,7 @@
     </row>
     <row r="119">
       <c r="A119">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B119" t="str">
         <v>Malie City</v>
@@ -2775,7 +2775,7 @@
         <v>Trubbish</v>
       </c>
       <c r="E119" t="str">
-        <v>46-51</v>
+        <v>47-52</v>
       </c>
       <c r="F119" t="str">
         <v>20.00%</v>
@@ -2783,7 +2783,7 @@
     </row>
     <row r="120">
       <c r="A120">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B120" t="str">
         <v>Malie City</v>
@@ -2795,7 +2795,7 @@
         <v>Minccino</v>
       </c>
       <c r="E120" t="str">
-        <v>46-51</v>
+        <v>47-52</v>
       </c>
       <c r="F120" t="str">
         <v>20.00%</v>
@@ -2803,7 +2803,7 @@
     </row>
     <row r="121">
       <c r="A121">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B121" t="str">
         <v>Malie City</v>
@@ -2815,7 +2815,7 @@
         <v>Masquerain</v>
       </c>
       <c r="E121" t="str">
-        <v>46-51</v>
+        <v>47-52</v>
       </c>
       <c r="F121" t="str">
         <v>20.00%</v>
@@ -2823,7 +2823,7 @@
     </row>
     <row r="122">
       <c r="A122">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B122" t="str">
         <v>Route 10</v>
@@ -2835,7 +2835,7 @@
         <v>Ledian</v>
       </c>
       <c r="E122" t="str">
-        <v>49-54</v>
+        <v>50-55</v>
       </c>
       <c r="F122" t="str">
         <v>16.67%</v>
@@ -2843,7 +2843,7 @@
     </row>
     <row r="123">
       <c r="A123">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B123" t="str">
         <v>Route 10</v>
@@ -2855,7 +2855,7 @@
         <v>Ariados</v>
       </c>
       <c r="E123" t="str">
-        <v>49-54</v>
+        <v>50-55</v>
       </c>
       <c r="F123" t="str">
         <v>16.67%</v>
@@ -2863,7 +2863,7 @@
     </row>
     <row r="124">
       <c r="A124">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B124" t="str">
         <v>Route 10</v>
@@ -2875,7 +2875,7 @@
         <v>Crabrawler</v>
       </c>
       <c r="E124" t="str">
-        <v>49-54</v>
+        <v>50-55</v>
       </c>
       <c r="F124" t="str">
         <v>16.67%</v>
@@ -2883,7 +2883,7 @@
     </row>
     <row r="125">
       <c r="A125">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B125" t="str">
         <v>Route 10</v>
@@ -2895,7 +2895,7 @@
         <v>Fearow</v>
       </c>
       <c r="E125" t="str">
-        <v>49-54</v>
+        <v>50-55</v>
       </c>
       <c r="F125" t="str">
         <v>16.67%</v>
@@ -2903,7 +2903,7 @@
     </row>
     <row r="126">
       <c r="A126">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B126" t="str">
         <v>Route 10</v>
@@ -2915,7 +2915,7 @@
         <v>Skarmory</v>
       </c>
       <c r="E126" t="str">
-        <v>49-54</v>
+        <v>50-55</v>
       </c>
       <c r="F126" t="str">
         <v>16.67%</v>
@@ -2923,7 +2923,7 @@
     </row>
     <row r="127">
       <c r="A127">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B127" t="str">
         <v>Route 10</v>
@@ -2935,7 +2935,7 @@
         <v>Pancham</v>
       </c>
       <c r="E127" t="str">
-        <v>49-54</v>
+        <v>50-55</v>
       </c>
       <c r="F127" t="str">
         <v>16.67%</v>
@@ -2943,7 +2943,7 @@
     </row>
     <row r="128">
       <c r="A128">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B128" t="str">
         <v>Mount Hokulani</v>
@@ -2955,7 +2955,7 @@
         <v>Cleffa</v>
       </c>
       <c r="E128" t="str">
-        <v>50-55</v>
+        <v>51-56</v>
       </c>
       <c r="F128" t="str">
         <v>25.00%</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="129">
       <c r="A129">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B129" t="str">
         <v>Mount Hokulani</v>
@@ -2975,7 +2975,7 @@
         <v>Elgyem</v>
       </c>
       <c r="E129" t="str">
-        <v>50-55</v>
+        <v>51-56</v>
       </c>
       <c r="F129" t="str">
         <v>25.00%</v>
@@ -2983,7 +2983,7 @@
     </row>
     <row r="130">
       <c r="A130">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B130" t="str">
         <v>Mount Hokulani</v>
@@ -2995,7 +2995,7 @@
         <v>Beldum</v>
       </c>
       <c r="E130" t="str">
-        <v>50-55</v>
+        <v>51-56</v>
       </c>
       <c r="F130" t="str">
         <v>25.00%</v>
@@ -3003,7 +3003,7 @@
     </row>
     <row r="131">
       <c r="A131">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B131" t="str">
         <v>Mount Hokulani</v>
@@ -3015,7 +3015,7 @@
         <v>Minior</v>
       </c>
       <c r="E131" t="str">
-        <v>50-55</v>
+        <v>51-56</v>
       </c>
       <c r="F131" t="str">
         <v>25.00%</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="132">
       <c r="A132">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B132" t="str">
         <v>Captain Sophocles</v>
@@ -3035,7 +3035,7 @@
         <v>Boss</v>
       </c>
       <c r="E132" t="str">
-        <v>52-57</v>
+        <v>53-58</v>
       </c>
       <c r="F132" t="str">
         <v>-</v>
@@ -3043,7 +3043,7 @@
     </row>
     <row r="133">
       <c r="A133">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B133" t="str">
         <v>Route 11</v>
@@ -3055,7 +3055,7 @@
         <v>Shiinotic</v>
       </c>
       <c r="E133" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="F133" t="str">
         <v>11.11%</v>
@@ -3063,7 +3063,7 @@
     </row>
     <row r="134">
       <c r="A134">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B134" t="str">
         <v>Route 11</v>
@@ -3075,7 +3075,7 @@
         <v>Parasect</v>
       </c>
       <c r="E134" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="F134" t="str">
         <v>11.11%</v>
@@ -3083,7 +3083,7 @@
     </row>
     <row r="135">
       <c r="A135">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B135" t="str">
         <v>Route 11</v>
@@ -3095,7 +3095,7 @@
         <v>Komala</v>
       </c>
       <c r="E135" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="F135" t="str">
         <v>11.11%</v>
@@ -3103,7 +3103,7 @@
     </row>
     <row r="136">
       <c r="A136">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B136" t="str">
         <v>Route 11</v>
@@ -3115,7 +3115,7 @@
         <v>Houndoom</v>
       </c>
       <c r="E136" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="F136" t="str">
         <v>11.11%</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="137">
       <c r="A137">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B137" t="str">
         <v>Route 11</v>
@@ -3135,7 +3135,7 @@
         <v>Manectric</v>
       </c>
       <c r="E137" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="F137" t="str">
         <v>11.11%</v>
@@ -3143,7 +3143,7 @@
     </row>
     <row r="138">
       <c r="A138">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B138" t="str">
         <v>Route 11</v>
@@ -3155,7 +3155,7 @@
         <v>Scraggy</v>
       </c>
       <c r="E138" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="F138" t="str">
         <v>11.11%</v>
@@ -3163,7 +3163,7 @@
     </row>
     <row r="139">
       <c r="A139">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B139" t="str">
         <v>Route 11</v>
@@ -3175,7 +3175,7 @@
         <v>Bisharp</v>
       </c>
       <c r="E139" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="F139" t="str">
         <v>11.11%</v>
@@ -3183,7 +3183,7 @@
     </row>
     <row r="140">
       <c r="A140">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B140" t="str">
         <v>Route 11</v>
@@ -3195,7 +3195,7 @@
         <v>Machop</v>
       </c>
       <c r="E140" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="F140" t="str">
         <v>11.11%</v>
@@ -3203,7 +3203,7 @@
     </row>
     <row r="141">
       <c r="A141">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B141" t="str">
         <v>Route 11</v>
@@ -3215,7 +3215,7 @@
         <v>Hawlucha</v>
       </c>
       <c r="E141" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="F141" t="str">
         <v>11.11%</v>
@@ -3223,7 +3223,7 @@
     </row>
     <row r="142">
       <c r="A142">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B142" t="str">
         <v>Blush Mountain</v>
@@ -3235,7 +3235,7 @@
         <v>Mudbray</v>
       </c>
       <c r="E142" t="str">
-        <v>56-61</v>
+        <v>57-62</v>
       </c>
       <c r="F142" t="str">
         <v>11.11%</v>
@@ -3243,7 +3243,7 @@
     </row>
     <row r="143">
       <c r="A143">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B143" t="str">
         <v>Blush Mountain</v>
@@ -3255,7 +3255,7 @@
         <v>Torkoal</v>
       </c>
       <c r="E143" t="str">
-        <v>56-61</v>
+        <v>57-62</v>
       </c>
       <c r="F143" t="str">
         <v>11.11%</v>
@@ -3263,7 +3263,7 @@
     </row>
     <row r="144">
       <c r="A144">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B144" t="str">
         <v>Blush Mountain</v>
@@ -3275,7 +3275,7 @@
         <v>Togedemaru</v>
       </c>
       <c r="E144" t="str">
-        <v>56-61</v>
+        <v>57-62</v>
       </c>
       <c r="F144" t="str">
         <v>11.11%</v>
@@ -3283,7 +3283,7 @@
     </row>
     <row r="145">
       <c r="A145">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B145" t="str">
         <v>Blush Mountain</v>
@@ -3295,7 +3295,7 @@
         <v>Elekid</v>
       </c>
       <c r="E145" t="str">
-        <v>56-61</v>
+        <v>57-62</v>
       </c>
       <c r="F145" t="str">
         <v>11.11%</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="146">
       <c r="A146">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B146" t="str">
         <v>Blush Mountain</v>
@@ -3315,7 +3315,7 @@
         <v>Alolan Geodude</v>
       </c>
       <c r="E146" t="str">
-        <v>56-61</v>
+        <v>57-62</v>
       </c>
       <c r="F146" t="str">
         <v>11.11%</v>
@@ -3323,7 +3323,7 @@
     </row>
     <row r="147">
       <c r="A147">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B147" t="str">
         <v>Blush Mountain</v>
@@ -3335,7 +3335,7 @@
         <v>Alolan Graveler</v>
       </c>
       <c r="E147" t="str">
-        <v>56-61</v>
+        <v>57-62</v>
       </c>
       <c r="F147" t="str">
         <v>11.11%</v>
@@ -3343,7 +3343,7 @@
     </row>
     <row r="148">
       <c r="A148">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B148" t="str">
         <v>Blush Mountain</v>
@@ -3355,7 +3355,7 @@
         <v>Charjabug</v>
       </c>
       <c r="E148" t="str">
-        <v>56-61</v>
+        <v>57-62</v>
       </c>
       <c r="F148" t="str">
         <v>11.11%</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="149">
       <c r="A149">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B149" t="str">
         <v>Blush Mountain</v>
@@ -3375,7 +3375,7 @@
         <v>Turtonator</v>
       </c>
       <c r="E149" t="str">
-        <v>56-61</v>
+        <v>57-62</v>
       </c>
       <c r="F149" t="str">
         <v>11.11%</v>
@@ -3383,7 +3383,7 @@
     </row>
     <row r="150">
       <c r="A150">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B150" t="str">
         <v>Blush Mountain</v>
@@ -3395,7 +3395,7 @@
         <v>Dedenne</v>
       </c>
       <c r="E150" t="str">
-        <v>56-61</v>
+        <v>57-62</v>
       </c>
       <c r="F150" t="str">
         <v>11.11%</v>
@@ -3403,7 +3403,7 @@
     </row>
     <row r="151">
       <c r="A151">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B151" t="str">
         <v>Haina Desert</v>
@@ -3415,7 +3415,7 @@
         <v>Alolan Dugtrio</v>
       </c>
       <c r="E151" t="str">
-        <v>57-62</v>
+        <v>58-63</v>
       </c>
       <c r="F151" t="str">
         <v>20.00%</v>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="152">
       <c r="A152">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B152" t="str">
         <v>Haina Desert</v>
@@ -3435,7 +3435,7 @@
         <v>Sandile</v>
       </c>
       <c r="E152" t="str">
-        <v>57-62</v>
+        <v>58-63</v>
       </c>
       <c r="F152" t="str">
         <v>20.00%</v>
@@ -3443,7 +3443,7 @@
     </row>
     <row r="153">
       <c r="A153">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B153" t="str">
         <v>Haina Desert</v>
@@ -3455,7 +3455,7 @@
         <v>Krokorok</v>
       </c>
       <c r="E153" t="str">
-        <v>57-62</v>
+        <v>58-63</v>
       </c>
       <c r="F153" t="str">
         <v>20.00%</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="154">
       <c r="A154">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B154" t="str">
         <v>Haina Desert</v>
@@ -3475,7 +3475,7 @@
         <v>Staryu</v>
       </c>
       <c r="E154" t="str">
-        <v>57-62</v>
+        <v>58-63</v>
       </c>
       <c r="F154" t="str">
         <v>20.00%</v>
@@ -3483,7 +3483,7 @@
     </row>
     <row r="155">
       <c r="A155">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B155" t="str">
         <v>Haina Desert</v>
@@ -3495,7 +3495,7 @@
         <v>Sandygast</v>
       </c>
       <c r="E155" t="str">
-        <v>57-62</v>
+        <v>58-63</v>
       </c>
       <c r="F155" t="str">
         <v>20.00%</v>
@@ -3503,7 +3503,7 @@
     </row>
     <row r="156">
       <c r="A156">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B156" t="str">
         <v>Tapu Village</v>
@@ -3523,7 +3523,7 @@
     </row>
     <row r="157">
       <c r="A157">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B157" t="str">
         <v>Tapu Village</v>
@@ -3543,7 +3543,7 @@
     </row>
     <row r="158">
       <c r="A158">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B158" t="str">
         <v>Tapu Village</v>
@@ -3563,7 +3563,7 @@
     </row>
     <row r="159">
       <c r="A159">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B159" t="str">
         <v>Tapu Village</v>
@@ -3583,7 +3583,7 @@
     </row>
     <row r="160">
       <c r="A160">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B160" t="str">
         <v>Tapu Village</v>
@@ -3603,7 +3603,7 @@
     </row>
     <row r="161">
       <c r="A161">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B161" t="str">
         <v>Tapu Village</v>
@@ -3623,7 +3623,7 @@
     </row>
     <row r="162">
       <c r="A162">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B162" t="str">
         <v>Thrifty Megamart</v>
@@ -3635,7 +3635,7 @@
         <v>Haunter</v>
       </c>
       <c r="E162" t="str">
-        <v>61-66</v>
+        <v>62-67</v>
       </c>
       <c r="F162" t="str">
         <v>25.00%</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="163">
       <c r="A163">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B163" t="str">
         <v>Thrifty Megamart</v>
@@ -3655,7 +3655,7 @@
         <v>Klefki</v>
       </c>
       <c r="E163" t="str">
-        <v>61-66</v>
+        <v>62-67</v>
       </c>
       <c r="F163" t="str">
         <v>25.00%</v>
@@ -3663,7 +3663,7 @@
     </row>
     <row r="164">
       <c r="A164">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B164" t="str">
         <v>Thrifty Megamart</v>
@@ -3675,7 +3675,7 @@
         <v>Shuppet</v>
       </c>
       <c r="E164" t="str">
-        <v>61-66</v>
+        <v>62-67</v>
       </c>
       <c r="F164" t="str">
         <v>25.00%</v>
@@ -3683,7 +3683,7 @@
     </row>
     <row r="165">
       <c r="A165">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B165" t="str">
         <v>Thrifty Megamart</v>
@@ -3695,7 +3695,7 @@
         <v>Boldore</v>
       </c>
       <c r="E165" t="str">
-        <v>61-66</v>
+        <v>62-67</v>
       </c>
       <c r="F165" t="str">
         <v>25.00%</v>
@@ -3703,7 +3703,7 @@
     </row>
     <row r="166">
       <c r="A166">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B166" t="str">
         <v>Captain Acerola</v>
@@ -3715,7 +3715,7 @@
         <v>Boss</v>
       </c>
       <c r="E166" t="str">
-        <v>63-68</v>
+        <v>64-69</v>
       </c>
       <c r="F166" t="str">
         <v>-</v>
@@ -3723,7 +3723,7 @@
     </row>
     <row r="167">
       <c r="A167">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B167" t="str">
         <v>Kahuna Nanu</v>
@@ -3735,7 +3735,7 @@
         <v>Boss</v>
       </c>
       <c r="E167" t="str">
-        <v>68-73</v>
+        <v>69-74</v>
       </c>
       <c r="F167" t="str">
         <v>-</v>
@@ -3743,7 +3743,7 @@
     </row>
     <row r="168">
       <c r="A168">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B168" t="str">
         <v>Seafolk Village</v>
@@ -3755,7 +3755,7 @@
         <v>Steenee</v>
       </c>
       <c r="E168" t="str">
-        <v>69-74</v>
+        <v>70-75</v>
       </c>
       <c r="F168" t="str">
         <v>33.33%</v>
@@ -3763,7 +3763,7 @@
     </row>
     <row r="169">
       <c r="A169">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B169" t="str">
         <v>Seafolk Village</v>
@@ -3775,7 +3775,7 @@
         <v>Shellos</v>
       </c>
       <c r="E169" t="str">
-        <v>69-74</v>
+        <v>70-75</v>
       </c>
       <c r="F169" t="str">
         <v>33.33%</v>
@@ -3783,7 +3783,7 @@
     </row>
     <row r="170">
       <c r="A170">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B170" t="str">
         <v>Seafolk Village</v>
@@ -3795,7 +3795,7 @@
         <v>Dhelmise</v>
       </c>
       <c r="E170" t="str">
-        <v>69-74</v>
+        <v>70-75</v>
       </c>
       <c r="F170" t="str">
         <v>33.33%</v>
@@ -3803,7 +3803,7 @@
     </row>
     <row r="171">
       <c r="A171">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B171" t="str">
         <v>Poni Wilds</v>
@@ -3815,7 +3815,7 @@
         <v>Tentacruel</v>
       </c>
       <c r="E171" t="str">
-        <v>71-76</v>
+        <v>72-77</v>
       </c>
       <c r="F171" t="str">
         <v>20.00%</v>
@@ -3823,7 +3823,7 @@
     </row>
     <row r="172">
       <c r="A172">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B172" t="str">
         <v>Poni Wilds</v>
@@ -3835,7 +3835,7 @@
         <v>Lumineon</v>
       </c>
       <c r="E172" t="str">
-        <v>71-76</v>
+        <v>72-77</v>
       </c>
       <c r="F172" t="str">
         <v>20.00%</v>
@@ -3843,7 +3843,7 @@
     </row>
     <row r="173">
       <c r="A173">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B173" t="str">
         <v>Poni Wilds</v>
@@ -3855,7 +3855,7 @@
         <v>Lapras</v>
       </c>
       <c r="E173" t="str">
-        <v>71-76</v>
+        <v>72-77</v>
       </c>
       <c r="F173" t="str">
         <v>20.00%</v>
@@ -3863,7 +3863,7 @@
     </row>
     <row r="174">
       <c r="A174">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B174" t="str">
         <v>Poni Wilds</v>
@@ -3875,7 +3875,7 @@
         <v>Noivern</v>
       </c>
       <c r="E174" t="str">
-        <v>71-76</v>
+        <v>72-77</v>
       </c>
       <c r="F174" t="str">
         <v>20.00%</v>
@@ -3883,7 +3883,7 @@
     </row>
     <row r="175">
       <c r="A175">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B175" t="str">
         <v>Poni Wilds</v>
@@ -3895,7 +3895,7 @@
         <v>Druddigon</v>
       </c>
       <c r="E175" t="str">
-        <v>71-76</v>
+        <v>72-77</v>
       </c>
       <c r="F175" t="str">
         <v>20.00%</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="176">
       <c r="A176">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B176" t="str">
         <v>Poni Breaker Coast</v>
@@ -3915,7 +3915,7 @@
         <v>Wimpod</v>
       </c>
       <c r="E176" t="str">
-        <v>72-77</v>
+        <v>73-78</v>
       </c>
       <c r="F176" t="str">
         <v>20.00%</v>
@@ -3923,7 +3923,7 @@
     </row>
     <row r="177">
       <c r="A177">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B177" t="str">
         <v>Poni Breaker Coast</v>
@@ -3935,7 +3935,7 @@
         <v>Relicanth</v>
       </c>
       <c r="E177" t="str">
-        <v>72-77</v>
+        <v>73-78</v>
       </c>
       <c r="F177" t="str">
         <v>20.00%</v>
@@ -3943,7 +3943,7 @@
     </row>
     <row r="178">
       <c r="A178">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B178" t="str">
         <v>Poni Breaker Coast</v>
@@ -3955,7 +3955,7 @@
         <v>Wailmer</v>
       </c>
       <c r="E178" t="str">
-        <v>72-77</v>
+        <v>73-78</v>
       </c>
       <c r="F178" t="str">
         <v>20.00%</v>
@@ -3963,7 +3963,7 @@
     </row>
     <row r="179">
       <c r="A179">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B179" t="str">
         <v>Poni Breaker Coast</v>
@@ -3975,7 +3975,7 @@
         <v>Carvanha</v>
       </c>
       <c r="E179" t="str">
-        <v>72-77</v>
+        <v>73-78</v>
       </c>
       <c r="F179" t="str">
         <v>20.00%</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="180">
       <c r="A180">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B180" t="str">
         <v>Poni Breaker Coast</v>
@@ -3995,7 +3995,7 @@
         <v>Sharpedo</v>
       </c>
       <c r="E180" t="str">
-        <v>72-77</v>
+        <v>73-78</v>
       </c>
       <c r="F180" t="str">
         <v>20.00%</v>
@@ -4003,7 +4003,7 @@
     </row>
     <row r="181">
       <c r="A181">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B181" t="str">
         <v>Exeggutor Island</v>
@@ -4015,7 +4015,7 @@
         <v>Pelipper</v>
       </c>
       <c r="E181" t="str">
-        <v>73-78</v>
+        <v>75-80</v>
       </c>
       <c r="F181" t="str">
         <v>16.67%</v>
@@ -4023,7 +4023,7 @@
     </row>
     <row r="182">
       <c r="A182">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B182" t="str">
         <v>Exeggutor Island</v>
@@ -4035,7 +4035,7 @@
         <v>Pinsir</v>
       </c>
       <c r="E182" t="str">
-        <v>73-78</v>
+        <v>75-80</v>
       </c>
       <c r="F182" t="str">
         <v>16.67%</v>
@@ -4043,7 +4043,7 @@
     </row>
     <row r="183">
       <c r="A183">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B183" t="str">
         <v>Exeggutor Island</v>
@@ -4055,7 +4055,7 @@
         <v>Gastrodon</v>
       </c>
       <c r="E183" t="str">
-        <v>73-78</v>
+        <v>75-80</v>
       </c>
       <c r="F183" t="str">
         <v>16.67%</v>
@@ -4063,7 +4063,7 @@
     </row>
     <row r="184">
       <c r="A184">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B184" t="str">
         <v>Exeggutor Island</v>
@@ -4075,7 +4075,7 @@
         <v>Exeggcute</v>
       </c>
       <c r="E184" t="str">
-        <v>73-78</v>
+        <v>75-80</v>
       </c>
       <c r="F184" t="str">
         <v>16.67%</v>
@@ -4083,7 +4083,7 @@
     </row>
     <row r="185">
       <c r="A185">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B185" t="str">
         <v>Exeggutor Island</v>
@@ -4095,7 +4095,7 @@
         <v>Tropius</v>
       </c>
       <c r="E185" t="str">
-        <v>73-78</v>
+        <v>75-80</v>
       </c>
       <c r="F185" t="str">
         <v>16.67%</v>
@@ -4103,7 +4103,7 @@
     </row>
     <row r="186">
       <c r="A186">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B186" t="str">
         <v>Exeggutor Island</v>
@@ -4115,7 +4115,7 @@
         <v>Alolan Exeggutor</v>
       </c>
       <c r="E186" t="str">
-        <v>73-78</v>
+        <v>75-80</v>
       </c>
       <c r="F186" t="str">
         <v>16.67%</v>
@@ -4123,7 +4123,7 @@
     </row>
     <row r="187">
       <c r="A187">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B187" t="str">
         <v>Vast Poni Canyon</v>
@@ -4135,7 +4135,7 @@
         <v>Machoke</v>
       </c>
       <c r="E187" t="str">
-        <v>75-80</v>
+        <v>76-81</v>
       </c>
       <c r="F187" t="str">
         <v>33.33%</v>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="188">
       <c r="A188">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B188" t="str">
         <v>Vast Poni Canyon</v>
@@ -4155,7 +4155,7 @@
         <v>Mienfoo</v>
       </c>
       <c r="E188" t="str">
-        <v>75-80</v>
+        <v>76-81</v>
       </c>
       <c r="F188" t="str">
         <v>33.33%</v>
@@ -4163,7 +4163,7 @@
     </row>
     <row r="189">
       <c r="A189">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B189" t="str">
         <v>Vast Poni Canyon</v>
@@ -4175,7 +4175,7 @@
         <v>Jangmo-o</v>
       </c>
       <c r="E189" t="str">
-        <v>75-80</v>
+        <v>76-81</v>
       </c>
       <c r="F189" t="str">
         <v>33.33%</v>
@@ -4183,122 +4183,122 @@
     </row>
     <row r="190">
       <c r="A190">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B190" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Captain Kommo-o</v>
       </c>
       <c r="C190" t="str">
-        <v>Northwest (Hidden Area)</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D190" t="str">
-        <v>Corphish</v>
+        <v>Boss</v>
       </c>
       <c r="E190" t="str">
-        <v>77-82</v>
+        <v>79-84</v>
       </c>
       <c r="F190" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="191">
       <c r="A191">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B191" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Captain Mina</v>
       </c>
       <c r="C191" t="str">
-        <v>Northwest (Hidden Area)</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D191" t="str">
-        <v>Dratini</v>
+        <v>Boss</v>
       </c>
       <c r="E191" t="str">
-        <v>77-82</v>
+        <v>80-85</v>
       </c>
       <c r="F191" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="192">
       <c r="A192">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B192" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Kahuna Hapu</v>
       </c>
       <c r="C192" t="str">
-        <v>Northwest (Hidden Area)</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D192" t="str">
-        <v>Golduck</v>
+        <v>Boss</v>
       </c>
       <c r="E192" t="str">
-        <v>77-82</v>
+        <v>81-86</v>
       </c>
       <c r="F192" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="193">
       <c r="A193">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B193" t="str">
-        <v>Captain Kommo-o</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C193" t="str">
-        <v>Boss Battle</v>
+        <v>Cave</v>
       </c>
       <c r="D193" t="str">
-        <v>Boss</v>
+        <v>Drampa</v>
       </c>
       <c r="E193" t="str">
-        <v>79-84</v>
+        <v>83-88</v>
       </c>
       <c r="F193" t="str">
-        <v>-</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="194">
       <c r="A194">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B194" t="str">
-        <v>Captain Mina</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C194" t="str">
-        <v>Boss Battle</v>
+        <v>Cave</v>
       </c>
       <c r="D194" t="str">
-        <v>Boss</v>
+        <v>Glalie</v>
       </c>
       <c r="E194" t="str">
-        <v>80-85</v>
+        <v>83-88</v>
       </c>
       <c r="F194" t="str">
-        <v>-</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="195">
       <c r="A195">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B195" t="str">
-        <v>Kahuna Hapu</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C195" t="str">
-        <v>Boss Battle</v>
+        <v>Cave</v>
       </c>
       <c r="D195" t="str">
-        <v>Boss</v>
+        <v>Sneasel</v>
       </c>
       <c r="E195" t="str">
-        <v>81-86</v>
+        <v>83-88</v>
       </c>
       <c r="F195" t="str">
-        <v>-</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="196">
@@ -4312,7 +4312,7 @@
         <v>Cave</v>
       </c>
       <c r="D196" t="str">
-        <v>Drampa</v>
+        <v>Crabominable</v>
       </c>
       <c r="E196" t="str">
         <v>83-88</v>
@@ -4323,102 +4323,102 @@
     </row>
     <row r="197">
       <c r="A197">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B197" t="str">
-        <v>Mount Lanakila</v>
+        <v>Alola Pokemon League</v>
       </c>
       <c r="C197" t="str">
-        <v>Cave</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D197" t="str">
-        <v>Glalie</v>
+        <v>Boss</v>
       </c>
       <c r="E197" t="str">
-        <v>83-88</v>
+        <v>84-89</v>
       </c>
       <c r="F197" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="198">
       <c r="A198">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B198" t="str">
-        <v>Mount Lanakila</v>
+        <v>Champion Hau</v>
       </c>
       <c r="C198" t="str">
-        <v>Cave</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D198" t="str">
-        <v>Sneasel</v>
+        <v>Boss</v>
       </c>
       <c r="E198" t="str">
-        <v>83-88</v>
+        <v>85-90</v>
       </c>
       <c r="F198" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="199">
       <c r="A199">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B199" t="str">
-        <v>Mount Lanakila</v>
+        <v>Route 7</v>
       </c>
       <c r="C199" t="str">
-        <v>Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D199" t="str">
-        <v>Crabominable</v>
+        <v>Staryu</v>
       </c>
       <c r="E199" t="str">
-        <v>83-88</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F199" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="200">
       <c r="A200">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B200" t="str">
-        <v>Alola Pokemon League</v>
+        <v>Route 7</v>
       </c>
       <c r="C200" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D200" t="str">
-        <v>Boss</v>
+        <v>Pyukumuku</v>
       </c>
       <c r="E200" t="str">
-        <v>84-89</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F200" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="201">
       <c r="A201">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B201" t="str">
-        <v>Champion Hau</v>
+        <v>Route 7</v>
       </c>
       <c r="C201" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D201" t="str">
-        <v>Boss</v>
+        <v>Corsola</v>
       </c>
       <c r="E201" t="str">
-        <v>85-90</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F201" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="202">
@@ -4432,7 +4432,7 @@
         <v>Main Area</v>
       </c>
       <c r="D202" t="str">
-        <v>Staryu</v>
+        <v>Mareanie</v>
       </c>
       <c r="E202" t="str">
         <v>NaN-NaN</v>
@@ -4452,7 +4452,7 @@
         <v>Main Area</v>
       </c>
       <c r="D203" t="str">
-        <v>Pyukumuku</v>
+        <v>Bruxish</v>
       </c>
       <c r="E203" t="str">
         <v>NaN-NaN</v>
@@ -4463,142 +4463,142 @@
     </row>
     <row r="204">
       <c r="A204">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B204" t="str">
-        <v>Route 7</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C204" t="str">
-        <v>Main Area</v>
+        <v>Secret Lab</v>
       </c>
       <c r="D204" t="str">
-        <v>Corsola</v>
+        <v>Type: Null</v>
       </c>
       <c r="E204" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F204" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="205">
       <c r="A205">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B205" t="str">
-        <v>Route 7</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C205" t="str">
-        <v>Main Area</v>
+        <v>Secret Lab</v>
       </c>
       <c r="D205" t="str">
-        <v>Mareanie</v>
+        <v>Ditto</v>
       </c>
       <c r="E205" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F205" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="206">
       <c r="A206">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B206" t="str">
-        <v>Route 7</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C206" t="str">
-        <v>Main Area</v>
+        <v>Secret Lab</v>
       </c>
       <c r="D206" t="str">
-        <v>Bruxish</v>
+        <v>Porygon</v>
       </c>
       <c r="E206" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F206" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="207">
       <c r="A207">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B207" t="str">
-        <v>Aether Paradise</v>
+        <v>Memorial Hill</v>
       </c>
       <c r="C207" t="str">
-        <v>Labs</v>
+        <v>Main</v>
       </c>
       <c r="D207" t="str">
-        <v>Type: Null</v>
+        <v>Phantump</v>
       </c>
       <c r="E207" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F207" t="str">
-        <v>33.33%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="208">
       <c r="A208">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B208" t="str">
-        <v>Aether Paradise</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C208" t="str">
-        <v>Labs</v>
+        <v>Main Area</v>
       </c>
       <c r="D208" t="str">
-        <v>Ditto</v>
+        <v>Tapu Koko</v>
       </c>
       <c r="E208" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F208" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="209">
       <c r="A209">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B209" t="str">
-        <v>Aether Paradise</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C209" t="str">
-        <v>Labs</v>
+        <v>Main Area</v>
       </c>
       <c r="D209" t="str">
-        <v>Porygon</v>
+        <v>Tapu Lele</v>
       </c>
       <c r="E209" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F209" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="210">
       <c r="A210">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B210" t="str">
-        <v>Ruins of Conflict</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C210" t="str">
-        <v>Special Encounter</v>
+        <v>Main Area</v>
       </c>
       <c r="D210" t="str">
-        <v>Special Encounter</v>
+        <v>Tapu Bulu</v>
       </c>
       <c r="E210" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F210" t="str">
-        <v>100%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="211">
@@ -4612,7 +4612,7 @@
         <v>Main Area</v>
       </c>
       <c r="D211" t="str">
-        <v>Tapu Koko</v>
+        <v>Tapu Fini</v>
       </c>
       <c r="E211" t="str">
         <v>NaN-NaN</v>
@@ -4623,62 +4623,62 @@
     </row>
     <row r="212">
       <c r="A212">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B212" t="str">
-        <v>Sacred Shrine</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C212" t="str">
         <v>Main Area</v>
       </c>
       <c r="D212" t="str">
-        <v>Tapu Lele</v>
+        <v>Cosmog</v>
       </c>
       <c r="E212" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F212" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="213">
       <c r="A213">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B213" t="str">
-        <v>Sacred Shrine</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C213" t="str">
         <v>Main Area</v>
       </c>
       <c r="D213" t="str">
-        <v>Tapu Bulu</v>
+        <v>Cosmoem</v>
       </c>
       <c r="E213" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F213" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="214">
       <c r="A214">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B214" t="str">
-        <v>Sacred Shrine</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C214" t="str">
         <v>Main Area</v>
       </c>
       <c r="D214" t="str">
-        <v>Tapu Fini</v>
+        <v>Solgaleo</v>
       </c>
       <c r="E214" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F214" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="215">
@@ -4686,24 +4686,24 @@
         <v>57</v>
       </c>
       <c r="B215" t="str">
-        <v>Route 15</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C215" t="str">
         <v>Main Area</v>
       </c>
       <c r="D215" t="str">
-        <v>Special Encounter</v>
+        <v>Lunala</v>
       </c>
       <c r="E215" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F215" t="str">
-        <v>100%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="216">
       <c r="A216">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B216" t="str">
         <v>Obsidian Sphere</v>
@@ -4712,7 +4712,7 @@
         <v>Main Area</v>
       </c>
       <c r="D216" t="str">
-        <v>Cosmog</v>
+        <v>Necrozma</v>
       </c>
       <c r="E216" t="str">
         <v>NaN-NaN</v>
@@ -4726,13 +4726,13 @@
         <v>58</v>
       </c>
       <c r="B217" t="str">
-        <v>Obsidian Sphere</v>
+        <v>Route 3</v>
       </c>
       <c r="C217" t="str">
-        <v>Main Area</v>
+        <v>North</v>
       </c>
       <c r="D217" t="str">
-        <v>Cosmoem</v>
+        <v>Mankey</v>
       </c>
       <c r="E217" t="str">
         <v>NaN-NaN</v>
@@ -4746,13 +4746,13 @@
         <v>58</v>
       </c>
       <c r="B218" t="str">
-        <v>Obsidian Sphere</v>
+        <v>Route 3</v>
       </c>
       <c r="C218" t="str">
-        <v>Main Area</v>
+        <v>North</v>
       </c>
       <c r="D218" t="str">
-        <v>Solgaleo</v>
+        <v>Delibird</v>
       </c>
       <c r="E218" t="str">
         <v>NaN-NaN</v>
@@ -4766,13 +4766,13 @@
         <v>58</v>
       </c>
       <c r="B219" t="str">
-        <v>Obsidian Sphere</v>
+        <v>Route 3</v>
       </c>
       <c r="C219" t="str">
-        <v>Main Area</v>
+        <v>North</v>
       </c>
       <c r="D219" t="str">
-        <v>Lunala</v>
+        <v>Bagon</v>
       </c>
       <c r="E219" t="str">
         <v>NaN-NaN</v>
@@ -4786,13 +4786,13 @@
         <v>58</v>
       </c>
       <c r="B220" t="str">
-        <v>Obsidian Sphere</v>
+        <v>Route 3</v>
       </c>
       <c r="C220" t="str">
-        <v>Main Area</v>
+        <v>North</v>
       </c>
       <c r="D220" t="str">
-        <v>Necrozma</v>
+        <v>Oricorio</v>
       </c>
       <c r="E220" t="str">
         <v>NaN-NaN</v>
@@ -4803,7 +4803,7 @@
     </row>
     <row r="221">
       <c r="A221">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B221" t="str">
         <v>Route 3</v>
@@ -4812,7 +4812,7 @@
         <v>North</v>
       </c>
       <c r="D221" t="str">
-        <v>Mankey</v>
+        <v>Igglybuff</v>
       </c>
       <c r="E221" t="str">
         <v>NaN-NaN</v>
@@ -4826,79 +4826,79 @@
         <v>59</v>
       </c>
       <c r="B222" t="str">
-        <v>Route 3</v>
+        <v>Ten Carat Hill</v>
       </c>
       <c r="C222" t="str">
-        <v>North</v>
+        <v>Deepest Cave</v>
       </c>
       <c r="D222" t="str">
-        <v>Delibird</v>
+        <v>Marshadow</v>
       </c>
       <c r="E222" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F222" t="str">
-        <v>20.00%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="223">
       <c r="A223">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B223" t="str">
-        <v>Route 3</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C223" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D223" t="str">
-        <v>Bagon</v>
+        <v>Buneary</v>
       </c>
       <c r="E223" t="str">
-        <v>NaN-NaN</v>
+        <v>90-100</v>
       </c>
       <c r="F223" t="str">
-        <v>20.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="224">
       <c r="A224">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B224" t="str">
-        <v>Route 3</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C224" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D224" t="str">
-        <v>Oricorio</v>
+        <v>Granbull</v>
       </c>
       <c r="E224" t="str">
-        <v>NaN-NaN</v>
+        <v>90-100</v>
       </c>
       <c r="F224" t="str">
-        <v>20.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="225">
       <c r="A225">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B225" t="str">
-        <v>Route 3</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C225" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D225" t="str">
-        <v>Igglybuff</v>
+        <v>Zoroark</v>
       </c>
       <c r="E225" t="str">
-        <v>NaN-NaN</v>
+        <v>90-100</v>
       </c>
       <c r="F225" t="str">
-        <v>20.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="226">
@@ -4906,24 +4906,24 @@
         <v>60</v>
       </c>
       <c r="B226" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C226" t="str">
-        <v>Deepest Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D226" t="str">
-        <v>Special Encounter</v>
+        <v>Heracross</v>
       </c>
       <c r="E226" t="str">
-        <v>NaN-NaN</v>
+        <v>90-100</v>
       </c>
       <c r="F226" t="str">
-        <v>100%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="227">
       <c r="A227">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B227" t="str">
         <v>Poni Grove</v>
@@ -4932,7 +4932,7 @@
         <v>Main Area</v>
       </c>
       <c r="D227" t="str">
-        <v>Buneary</v>
+        <v>Riolu</v>
       </c>
       <c r="E227" t="str">
         <v>90-100</v>
@@ -4943,7 +4943,7 @@
     </row>
     <row r="228">
       <c r="A228">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B228" t="str">
         <v>Poni Grove</v>
@@ -4952,7 +4952,7 @@
         <v>Main Area</v>
       </c>
       <c r="D228" t="str">
-        <v>Granbull</v>
+        <v>Hariyama</v>
       </c>
       <c r="E228" t="str">
         <v>90-100</v>
@@ -4963,7 +4963,7 @@
     </row>
     <row r="229">
       <c r="A229">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B229" t="str">
         <v>Poni Grove</v>
@@ -4972,7 +4972,7 @@
         <v>Main Area</v>
       </c>
       <c r="D229" t="str">
-        <v>Zoroark</v>
+        <v>Mudsdale</v>
       </c>
       <c r="E229" t="str">
         <v>90-100</v>
@@ -4986,19 +4986,19 @@
         <v>61</v>
       </c>
       <c r="B230" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C230" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D230" t="str">
-        <v>Heracross</v>
+        <v>Nihilego</v>
       </c>
       <c r="E230" t="str">
         <v>90-100</v>
       </c>
       <c r="F230" t="str">
-        <v>14.29%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="231">
@@ -5006,19 +5006,19 @@
         <v>61</v>
       </c>
       <c r="B231" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C231" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D231" t="str">
-        <v>Riolu</v>
+        <v>Buzzwole</v>
       </c>
       <c r="E231" t="str">
         <v>90-100</v>
       </c>
       <c r="F231" t="str">
-        <v>14.29%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="232">
@@ -5026,19 +5026,19 @@
         <v>61</v>
       </c>
       <c r="B232" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C232" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D232" t="str">
-        <v>Hariyama</v>
+        <v>Pheromosa</v>
       </c>
       <c r="E232" t="str">
         <v>90-100</v>
       </c>
       <c r="F232" t="str">
-        <v>14.29%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="233">
@@ -5046,24 +5046,24 @@
         <v>61</v>
       </c>
       <c r="B233" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C233" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D233" t="str">
-        <v>Mudsdale</v>
+        <v>Xurkitree</v>
       </c>
       <c r="E233" t="str">
         <v>90-100</v>
       </c>
       <c r="F233" t="str">
-        <v>14.29%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="234">
       <c r="A234">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B234" t="str">
         <v>The Interdimensional Rift</v>
@@ -5072,7 +5072,7 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D234" t="str">
-        <v>Nihilego</v>
+        <v>Celesteela</v>
       </c>
       <c r="E234" t="str">
         <v>90-100</v>
@@ -5083,7 +5083,7 @@
     </row>
     <row r="235">
       <c r="A235">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B235" t="str">
         <v>The Interdimensional Rift</v>
@@ -5092,7 +5092,7 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D235" t="str">
-        <v>Buzzwole</v>
+        <v>Kartana</v>
       </c>
       <c r="E235" t="str">
         <v>90-100</v>
@@ -5103,7 +5103,7 @@
     </row>
     <row r="236">
       <c r="A236">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B236" t="str">
         <v>The Interdimensional Rift</v>
@@ -5112,7 +5112,7 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D236" t="str">
-        <v>Pheromosa</v>
+        <v>Guzzlord</v>
       </c>
       <c r="E236" t="str">
         <v>90-100</v>
@@ -5123,7 +5123,7 @@
     </row>
     <row r="237">
       <c r="A237">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B237" t="str">
         <v>The Interdimensional Rift</v>
@@ -5132,7 +5132,7 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D237" t="str">
-        <v>Xurkitree</v>
+        <v>Poipole</v>
       </c>
       <c r="E237" t="str">
         <v>90-100</v>
@@ -5143,7 +5143,7 @@
     </row>
     <row r="238">
       <c r="A238">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B238" t="str">
         <v>The Interdimensional Rift</v>
@@ -5152,7 +5152,7 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D238" t="str">
-        <v>Celesteela</v>
+        <v>Stakataka</v>
       </c>
       <c r="E238" t="str">
         <v>90-100</v>
@@ -5169,76 +5169,76 @@
         <v>The Interdimensional Rift</v>
       </c>
       <c r="C239" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area Part 2</v>
       </c>
       <c r="D239" t="str">
-        <v>Kartana</v>
+        <v>Blacephalon</v>
       </c>
       <c r="E239" t="str">
         <v>90-100</v>
       </c>
       <c r="F239" t="str">
-        <v>11.11%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="240">
       <c r="A240">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B240" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C240" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D240" t="str">
-        <v>Guzzlord</v>
+        <v>Caterpie</v>
       </c>
       <c r="E240" t="str">
         <v>90-100</v>
       </c>
       <c r="F240" t="str">
-        <v>11.11%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="241">
       <c r="A241">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B241" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C241" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D241" t="str">
-        <v>Poipole</v>
+        <v>Metapod</v>
       </c>
       <c r="E241" t="str">
         <v>90-100</v>
       </c>
       <c r="F241" t="str">
-        <v>11.11%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="242">
       <c r="A242">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B242" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C242" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D242" t="str">
-        <v>Stakataka</v>
+        <v>Cutiefly</v>
       </c>
       <c r="E242" t="str">
         <v>90-100</v>
       </c>
       <c r="F242" t="str">
-        <v>11.11%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="243">
@@ -5246,93 +5246,93 @@
         <v>63</v>
       </c>
       <c r="B243" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C243" t="str">
-        <v>Main Area Part 2</v>
+        <v>Main Area</v>
       </c>
       <c r="D243" t="str">
-        <v>Blacephalon</v>
+        <v>Butterfree</v>
       </c>
       <c r="E243" t="str">
         <v>90-100</v>
       </c>
       <c r="F243" t="str">
-        <v>100.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="244">
       <c r="A244">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B244" t="str">
-        <v>Poni Plains</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C244" t="str">
-        <v>Center</v>
+        <v>Main Area</v>
       </c>
       <c r="D244" t="str">
-        <v>Special Encounter</v>
+        <v>Flabébé</v>
       </c>
       <c r="E244" t="str">
         <v>90-100</v>
       </c>
       <c r="F244" t="str">
-        <v>100%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="245">
       <c r="A245">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B245" t="str">
-        <v>Resolution Cave</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C245" t="str">
         <v>Main Area</v>
       </c>
       <c r="D245" t="str">
-        <v>Special Encounter</v>
+        <v>Petilil</v>
       </c>
       <c r="E245" t="str">
         <v>90-100</v>
       </c>
       <c r="F245" t="str">
-        <v>100%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="246">
       <c r="A246">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B246" t="str">
-        <v>Shopping Mall Antiquities</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C246" t="str">
-        <v>Event</v>
+        <v>Main Area</v>
       </c>
       <c r="D246" t="str">
-        <v>Magearna</v>
+        <v>Cottonee</v>
       </c>
       <c r="E246" t="str">
         <v>90-100</v>
       </c>
       <c r="F246" t="str">
-        <v>100.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="247">
       <c r="A247">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B247" t="str">
-        <v>Aether Paradise</v>
+        <v>Shopping Mall Antiquities</v>
       </c>
       <c r="C247" t="str">
-        <v>Secret Lab</v>
+        <v>Event</v>
       </c>
       <c r="D247" t="str">
-        <v>Zeraora</v>
+        <v>Magearna</v>
       </c>
       <c r="E247" t="str">
         <v>90-100</v>
@@ -5341,16 +5341,36 @@
         <v>100.00%</v>
       </c>
     </row>
+    <row r="248">
+      <c r="A248">
+        <v>65</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Aether Paradise</v>
+      </c>
+      <c r="C248" t="str">
+        <v>Restricted Area</v>
+      </c>
+      <c r="D248" t="str">
+        <v>Zeraora</v>
+      </c>
+      <c r="E248" t="str">
+        <v>90-100</v>
+      </c>
+      <c r="F248" t="str">
+        <v>100.00%</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F247"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F248"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C70"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5371,7 +5391,7 @@
         <v>Start the game</v>
       </c>
       <c r="C2" t="str">
-        <v>Starter Professor Kukui</v>
+        <v>Unlocks Starter Professor Kukui</v>
       </c>
     </row>
     <row r="3">
@@ -5382,7 +5402,7 @@
         <v>Defeat 10 Pokemon in Starter Professor Kukui</v>
       </c>
       <c r="C3" t="str">
-        <v>Route 1 East</v>
+        <v>Unlocks Route 1 East</v>
       </c>
     </row>
     <row r="4">
@@ -5393,7 +5413,7 @@
         <v>Defeat 10 Pokemon in Route 1 East</v>
       </c>
       <c r="C4" t="str">
-        <v>Route 1 Hau'oli Outskirts</v>
+        <v>Unlocks Route 1 Hau'oli Outskirts</v>
       </c>
     </row>
     <row r="5">
@@ -5404,7 +5424,7 @@
         <v>Defeat 10 Pokemon in Route 1 Hau'oli Outskirts</v>
       </c>
       <c r="C5" t="str">
-        <v>Hau'oli City Shopping District</v>
+        <v>Unlocks Hau'oli City Shopping District</v>
       </c>
     </row>
     <row r="6">
@@ -5415,7 +5435,7 @@
         <v>Defeat 10 Pokemon in Hau'oli City Shopping District</v>
       </c>
       <c r="C6" t="str">
-        <v>Route 2 North</v>
+        <v>Unlocks Route 2 North</v>
       </c>
     </row>
     <row r="7">
@@ -5426,7 +5446,7 @@
         <v>Defeat 10 Pokemon in Route 2 North</v>
       </c>
       <c r="C7" t="str">
-        <v>Captain Ilima</v>
+        <v>Unlocks Captain Ilima</v>
       </c>
     </row>
     <row r="8">
@@ -5437,7 +5457,7 @@
         <v>Defeat Captain Ilima</v>
       </c>
       <c r="C8" t="str">
-        <v>Hau'oli Cemetery Main Area</v>
+        <v>Unlocks Hau'oli Cemetery Main Area</v>
       </c>
     </row>
     <row r="9">
@@ -5448,7 +5468,7 @@
         <v>Defeat 10 Pokemon in Hau'oli Cemetery Main Area</v>
       </c>
       <c r="C9" t="str">
-        <v>Ten Carat Hill Farthest Hollow</v>
+        <v>Unlocks Ten Carat Hill Farthest Hollow</v>
       </c>
     </row>
     <row r="10">
@@ -5459,7 +5479,7 @@
         <v>Defeat 10 Pokemon in Ten Carat Hill Farthest Hollow</v>
       </c>
       <c r="C10" t="str">
-        <v>Seaward Cave Main Area</v>
+        <v>Unlocks Seaward Cave Main Area</v>
       </c>
     </row>
     <row r="11">
@@ -5470,7 +5490,7 @@
         <v>Defeat 10 Pokemon in Seaward Cave Main Area</v>
       </c>
       <c r="C11" t="str">
-        <v>Route 3 North</v>
+        <v>Unlocks Route 3 North</v>
       </c>
     </row>
     <row r="12">
@@ -5481,7 +5501,7 @@
         <v>Defeat 10 Pokemon in Route 3 North</v>
       </c>
       <c r="C12" t="str">
-        <v>Kahuna Hala</v>
+        <v>Unlocks Kahuna Hala</v>
       </c>
     </row>
     <row r="13">
@@ -5492,7 +5512,7 @@
         <v>Defeat Kahuna Hala</v>
       </c>
       <c r="C13" t="str">
-        <v>Heahea Beach Main Area Part 1</v>
+        <v>Unlocks Heahea Beach Main Area Part 1</v>
       </c>
     </row>
     <row r="14">
@@ -5503,7 +5523,7 @@
         <v>Defeat Kahuna Hala</v>
       </c>
       <c r="C14" t="str">
-        <v>Heahea Beach Main Area Part 2</v>
+        <v>Unlocks Heahea Beach Main Area Part 2</v>
       </c>
     </row>
     <row r="15">
@@ -5514,7 +5534,7 @@
         <v>Defeat 10 Pokemon in Heahea Beach Main Area Part 2</v>
       </c>
       <c r="C15" t="str">
-        <v>Paniola Ranch Main Area</v>
+        <v>Unlocks Paniola Ranch Main Area</v>
       </c>
     </row>
     <row r="16">
@@ -5525,7 +5545,7 @@
         <v>Defeat 10 Pokemon in Paniola Ranch Main Area</v>
       </c>
       <c r="C16" t="str">
-        <v>Daycare NPC</v>
+        <v>Unlocks Daycare NPC</v>
       </c>
     </row>
     <row r="17">
@@ -5536,7 +5556,7 @@
         <v>Interact with Daycare</v>
       </c>
       <c r="C17" t="str">
-        <v>Route 5 Main Area</v>
+        <v>Unlocks Route 5 Main Area</v>
       </c>
     </row>
     <row r="18">
@@ -5547,7 +5567,7 @@
         <v>Defeat 10 Pokemon in Route 5 Main Area</v>
       </c>
       <c r="C18" t="str">
-        <v>Brooklet Hill South</v>
+        <v>Unlocks Brooklet Hill South</v>
       </c>
     </row>
     <row r="19">
@@ -5558,7 +5578,7 @@
         <v>Defeat 10 Pokemon in Brooklet Hill South</v>
       </c>
       <c r="C19" t="str">
-        <v>Captain Lana</v>
+        <v>Unlocks Captain Lana</v>
       </c>
     </row>
     <row r="20">
@@ -5569,7 +5589,7 @@
         <v>Defeat Captain Lana</v>
       </c>
       <c r="C20" t="str">
-        <v>Wela Volcano Park Main Area</v>
+        <v>Unlocks Wela Volcano Park Main Area</v>
       </c>
     </row>
     <row r="21">
@@ -5580,7 +5600,7 @@
         <v>Defeat 10 Pokemon in Wela Volcano Park Main Area</v>
       </c>
       <c r="C21" t="str">
-        <v>Captain Kiawe</v>
+        <v>Unlocks Captain Kiawe</v>
       </c>
     </row>
     <row r="22">
@@ -5591,7 +5611,7 @@
         <v>Defeat Captain Kiawe</v>
       </c>
       <c r="C22" t="str">
-        <v>Route 7 Main Area</v>
+        <v>Unlocks Route 7 Main Area</v>
       </c>
     </row>
     <row r="23">
@@ -5602,7 +5622,7 @@
         <v>Defeat 10 Pokemon in Route 7 Main Area</v>
       </c>
       <c r="C23" t="str">
-        <v>Route 8 Fossil Restoration Center Part 1</v>
+        <v>Unlocks Route 8 Fossil Restoration Center Part 1</v>
       </c>
     </row>
     <row r="24">
@@ -5613,7 +5633,7 @@
         <v>Defeat 10 Pokemon in Route 8 Fossil Restoration Center Part 1</v>
       </c>
       <c r="C24" t="str">
-        <v>Route 8 Fossil Restoration Center Part 2</v>
+        <v>Unlocks Route 8 Fossil Restoration Center Part 2</v>
       </c>
     </row>
     <row r="25">
@@ -5624,7 +5644,7 @@
         <v>Defeat 10 Pokemon in Route 8 Fossil Restoration Center Part 2</v>
       </c>
       <c r="C25" t="str">
-        <v>Lush Jungle North</v>
+        <v>Unlocks Lush Jungle North</v>
       </c>
     </row>
     <row r="26">
@@ -5635,7 +5655,7 @@
         <v>Defeat 10 Pokemon in Lush Jungle North</v>
       </c>
       <c r="C26" t="str">
-        <v>Lush Jungle East Cave</v>
+        <v>Unlocks Lush Jungle East Cave</v>
       </c>
     </row>
     <row r="27">
@@ -5646,7 +5666,7 @@
         <v>Defeat 10 Pokemon in Lush Jungle East Cave</v>
       </c>
       <c r="C27" t="str">
-        <v>Captain Mallow</v>
+        <v>Unlocks Captain Mallow</v>
       </c>
     </row>
     <row r="28">
@@ -5657,7 +5677,7 @@
         <v>Defeat Captain Mallow</v>
       </c>
       <c r="C28" t="str">
-        <v>Diglett's Tunnel Main Area</v>
+        <v>Unlocks Diglett's Tunnel Main Area</v>
       </c>
     </row>
     <row r="29">
@@ -5668,7 +5688,7 @@
         <v>Defeat 10 Pokemon in Diglett's Tunnel Main Area</v>
       </c>
       <c r="C29" t="str">
-        <v>Akala Outskirts Main Area</v>
+        <v>Unlocks Memorial Hill Main</v>
       </c>
     </row>
     <row r="30">
@@ -5676,10 +5696,10 @@
         <v>Challenge 29</v>
       </c>
       <c r="B30" t="str">
-        <v>Defeat 10 Pokemon in Akala Outskirts Main Area</v>
+        <v>Defeat 10 Pokemon in Memorial Hill Main</v>
       </c>
       <c r="C30" t="str">
-        <v>Kahuna Olivia</v>
+        <v>Unlocks Akala Outskirts Main Area</v>
       </c>
     </row>
     <row r="31">
@@ -5687,10 +5707,10 @@
         <v>Challenge 30</v>
       </c>
       <c r="B31" t="str">
-        <v>Defeat 10 Pokemon in Kahuna Olivia</v>
+        <v>Defeat 10 Pokemon in Akala Outskirts Main Area</v>
       </c>
       <c r="C31" t="str">
-        <v>Malie City Outer Cape</v>
+        <v>Unlocks Kahuna Olivia</v>
       </c>
     </row>
     <row r="32">
@@ -5698,10 +5718,10 @@
         <v>Challenge 31</v>
       </c>
       <c r="B32" t="str">
-        <v>Defeat 10 Pokemon in Malie City Outer Cape</v>
+        <v>Defeat 10 Pokemon in Kahuna Olivia</v>
       </c>
       <c r="C32" t="str">
-        <v>Route 10 Main Area</v>
+        <v>Unlocks Malie City Outer Cape</v>
       </c>
     </row>
     <row r="33">
@@ -5709,10 +5729,10 @@
         <v>Challenge 32</v>
       </c>
       <c r="B33" t="str">
-        <v>Defeat 10 Pokemon in Route 10 Main Area</v>
+        <v>Defeat 10 Pokemon in Malie City Outer Cape</v>
       </c>
       <c r="C33" t="str">
-        <v>Mount Hokulani East</v>
+        <v>Unlocks Route 10 Main Area</v>
       </c>
     </row>
     <row r="34">
@@ -5720,10 +5740,10 @@
         <v>Challenge 33</v>
       </c>
       <c r="B34" t="str">
-        <v>Defeat 10 Pokemon in Mount Hokulani East</v>
+        <v>Defeat 10 Pokemon in Route 10 Main Area</v>
       </c>
       <c r="C34" t="str">
-        <v>Captain Sophocles</v>
+        <v>Unlocks Mount Hokulani East</v>
       </c>
     </row>
     <row r="35">
@@ -5731,10 +5751,10 @@
         <v>Challenge 34</v>
       </c>
       <c r="B35" t="str">
-        <v>Defeat Captain Sophocles</v>
+        <v>Defeat 10 Pokemon in Mount Hokulani East</v>
       </c>
       <c r="C35" t="str">
-        <v>Route 11 Main Area</v>
+        <v>Unlocks Captain Sophocles</v>
       </c>
     </row>
     <row r="36">
@@ -5742,10 +5762,10 @@
         <v>Challenge 35</v>
       </c>
       <c r="B36" t="str">
-        <v>Defeat 10 Pokemon in Route 11 Main Area</v>
+        <v>Defeat Captain Sophocles</v>
       </c>
       <c r="C36" t="str">
-        <v>Blush Mountain Main Area</v>
+        <v>Unlocks Route 11 Main Area</v>
       </c>
     </row>
     <row r="37">
@@ -5753,10 +5773,10 @@
         <v>Challenge 36</v>
       </c>
       <c r="B37" t="str">
-        <v>Defeat 10 Pokemon in Blush Mountain Main Area</v>
+        <v>Defeat 10 Pokemon in Route 11 Main Area</v>
       </c>
       <c r="C37" t="str">
-        <v>Haina Desert Main Area</v>
+        <v>Unlocks Blush Mountain Main Area</v>
       </c>
     </row>
     <row r="38">
@@ -5764,10 +5784,10 @@
         <v>Challenge 37</v>
       </c>
       <c r="B38" t="str">
-        <v>Defeat 10 Pokemon in Haina Desert Main Area</v>
+        <v>Defeat 10 Pokemon in Blush Mountain Main Area</v>
       </c>
       <c r="C38" t="str">
-        <v>Tapu Village Main Area</v>
+        <v>Unlocks Haina Desert Main Area</v>
       </c>
     </row>
     <row r="39">
@@ -5775,10 +5795,10 @@
         <v>Challenge 38</v>
       </c>
       <c r="B39" t="str">
-        <v>Defeat 10 Pokemon in Tapu Village Main Area</v>
+        <v>Defeat 10 Pokemon in Haina Desert Main Area</v>
       </c>
       <c r="C39" t="str">
-        <v>Thrifty Megamart Abandoned Site</v>
+        <v>Unlocks Tapu Village Main Area</v>
       </c>
     </row>
     <row r="40">
@@ -5786,10 +5806,10 @@
         <v>Challenge 39</v>
       </c>
       <c r="B40" t="str">
-        <v>Defeat 10 Pokemon in Thrifty Megamart Abandoned Site</v>
+        <v>Defeat 10 Pokemon in Tapu Village Main Area</v>
       </c>
       <c r="C40" t="str">
-        <v>Captain Acerola</v>
+        <v>Unlocks Thrifty Megamart Abandoned Site</v>
       </c>
     </row>
     <row r="41">
@@ -5797,10 +5817,10 @@
         <v>Challenge 40</v>
       </c>
       <c r="B41" t="str">
-        <v>Defeat 10 Pokemon in Captain Acerola</v>
+        <v>Defeat 10 Pokemon in Thrifty Megamart Abandoned Site</v>
       </c>
       <c r="C41" t="str">
-        <v>Kahuna Nanu</v>
+        <v>Unlocks Captain Acerola</v>
       </c>
     </row>
     <row r="42">
@@ -5808,10 +5828,10 @@
         <v>Challenge 41</v>
       </c>
       <c r="B42" t="str">
-        <v>Defeat Kahuna Nanu</v>
+        <v>Defeat 10 Pokemon in Captain Acerola</v>
       </c>
       <c r="C42" t="str">
-        <v>Seafolk Village Main</v>
+        <v>Unlocks Kahuna Nanu</v>
       </c>
     </row>
     <row r="43">
@@ -5819,10 +5839,10 @@
         <v>Challenge 42</v>
       </c>
       <c r="B43" t="str">
-        <v>Defeat 10 Pokemon in Seafolk Village Main</v>
+        <v>Defeat Kahuna Nanu</v>
       </c>
       <c r="C43" t="str">
-        <v>Poni Wilds Main Area</v>
+        <v>Unlocks Seafolk Village Main</v>
       </c>
     </row>
     <row r="44">
@@ -5830,10 +5850,10 @@
         <v>Challenge 43</v>
       </c>
       <c r="B44" t="str">
-        <v>Defeat 10 Pokemon in Poni Wilds Main Area</v>
+        <v>Defeat 10 Pokemon in Seafolk Village Main</v>
       </c>
       <c r="C44" t="str">
-        <v>Poni Breaker Coast Main Area</v>
+        <v>Unlocks Poni Wilds Main Area</v>
       </c>
     </row>
     <row r="45">
@@ -5841,10 +5861,10 @@
         <v>Challenge 44</v>
       </c>
       <c r="B45" t="str">
-        <v>Defeat 10 Pokemon in Poni Breaker Coast Main Area</v>
+        <v>Defeat 10 Pokemon in Poni Wilds Main Area</v>
       </c>
       <c r="C45" t="str">
-        <v>Exeggutor Island Main Area</v>
+        <v>Unlocks Poni Breaker Coast Main Area</v>
       </c>
     </row>
     <row r="46">
@@ -5852,10 +5872,10 @@
         <v>Challenge 45</v>
       </c>
       <c r="B46" t="str">
-        <v>Defeat 10 Pokemon in Exeggutor Island Main Area</v>
+        <v>Defeat 10 Pokemon in Poni Breaker Coast Main Area</v>
       </c>
       <c r="C46" t="str">
-        <v>Vast Poni Canyon Outside</v>
+        <v>Unlocks Exeggutor Island Main Area</v>
       </c>
     </row>
     <row r="47">
@@ -5863,10 +5883,10 @@
         <v>Challenge 46</v>
       </c>
       <c r="B47" t="str">
-        <v>Defeat 10 Pokemon in Vast Poni Canyon Outside</v>
+        <v>Defeat 10 Pokemon in Exeggutor Island Main Area</v>
       </c>
       <c r="C47" t="str">
-        <v>Vast Poni Canyon Northwest (Hidden Area)</v>
+        <v>Unlocks Vast Poni Canyon Outside</v>
       </c>
     </row>
     <row r="48">
@@ -5874,10 +5894,10 @@
         <v>Challenge 47</v>
       </c>
       <c r="B48" t="str">
-        <v>Defeat 10 Pokemon in Vast Poni Canyon Northwest (Hidden Area)</v>
+        <v>Defeat 10 Pokemon in Vast Poni Canyon Outside</v>
       </c>
       <c r="C48" t="str">
-        <v>Captain Kommo-o</v>
+        <v>Unlocks Captain Kommo-o</v>
       </c>
     </row>
     <row r="49">
@@ -5888,7 +5908,7 @@
         <v>Defeat Captain Kommo-o</v>
       </c>
       <c r="C49" t="str">
-        <v>Captain Mina</v>
+        <v>Unlocks Captain Mina</v>
       </c>
     </row>
     <row r="50">
@@ -5899,7 +5919,7 @@
         <v>Defeat Captain Mina</v>
       </c>
       <c r="C50" t="str">
-        <v>Kahuna Hapu</v>
+        <v>Unlocks Kahuna Hapu</v>
       </c>
     </row>
     <row r="51">
@@ -5910,7 +5930,7 @@
         <v>Defeat Kahuna Hapu</v>
       </c>
       <c r="C51" t="str">
-        <v>Mount Lanakila Cave</v>
+        <v>Unlocks Mount Lanakila Cave</v>
       </c>
     </row>
     <row r="52">
@@ -5921,7 +5941,7 @@
         <v>Defeat 10 Pokemon in Mount Lanakila Cave</v>
       </c>
       <c r="C52" t="str">
-        <v>Alola Pokemon League</v>
+        <v>Unlocks Alola Pokemon League</v>
       </c>
     </row>
     <row r="53">
@@ -5932,7 +5952,7 @@
         <v>Defeat Alola Pokemon League</v>
       </c>
       <c r="C53" t="str">
-        <v>Champion Hau</v>
+        <v>Unlocks Champion Hau</v>
       </c>
     </row>
     <row r="54">
@@ -5943,7 +5963,7 @@
         <v>Defeat Kahuna Olivia</v>
       </c>
       <c r="C54" t="str">
-        <v>Route 7 Main Area</v>
+        <v>Unlocks Route 7 Main Area</v>
       </c>
     </row>
     <row r="55">
@@ -5954,7 +5974,7 @@
         <v>Defeat 15 Pokemon in Route 7 Main Area</v>
       </c>
       <c r="C55" t="str">
-        <v>Aether Paradise Labs</v>
+        <v>Unlocks Aether Paradise Secret Lab [Type: Null, Ditto, Porygon]</v>
       </c>
     </row>
     <row r="56">
@@ -5965,7 +5985,7 @@
         <v>Defeat Kahuna Hala</v>
       </c>
       <c r="C56" t="str">
-        <v>Ruins of Conflict Special Encounter</v>
+        <v>Unlocks Memorial Hill Main</v>
       </c>
     </row>
     <row r="57">
@@ -5973,10 +5993,10 @@
         <v>Extra Challenge $2-2</v>
       </c>
       <c r="B57" t="str">
-        <v>Defeat 15 Pokemon in Ruins of Conflict Special Encounter</v>
+        <v>Defeat 15 Pokemon in Memorial Hill Main</v>
       </c>
       <c r="C57" t="str">
-        <v>Sacred Shrine Main Area</v>
+        <v>Unlocks Sacred Shrine Main Area [Tapus (Koko, Lele, Bulu, Fini)]</v>
       </c>
     </row>
     <row r="58">
@@ -5987,7 +6007,7 @@
         <v>Defeat Kahuna Nanu</v>
       </c>
       <c r="C58" t="str">
-        <v>Route 15 Main Area</v>
+        <v>Unlocks Route 15 Main Area</v>
       </c>
     </row>
     <row r="59">
@@ -5998,7 +6018,7 @@
         <v>Defeat 15 Pokemon in Route 15 Main Area</v>
       </c>
       <c r="C59" t="str">
-        <v>Obsidian Sphere Main Area</v>
+        <v>Unlocks Obsidian Sphere Main Area [Cosmog, Solgaleo, Lunala, Necrozma]</v>
       </c>
     </row>
     <row r="60">
@@ -6009,7 +6029,7 @@
         <v>Defeat Captain Ilima</v>
       </c>
       <c r="C60" t="str">
-        <v>Route 3 North</v>
+        <v>Unlocks Route 3 North</v>
       </c>
     </row>
     <row r="61">
@@ -6020,7 +6040,7 @@
         <v>Defeat 15 Pokemon in Route 3 North</v>
       </c>
       <c r="C61" t="str">
-        <v>Ten Carat Hill Deepest Cave</v>
+        <v>Unlocks Ten Carat Hill Deepest Cave [Marshadow]</v>
       </c>
     </row>
     <row r="62">
@@ -6031,7 +6051,7 @@
         <v>Defeat Champion Hau</v>
       </c>
       <c r="C62" t="str">
-        <v>Poni Grove Main Area</v>
+        <v>Unlocks Poni Grove Main Area</v>
       </c>
     </row>
     <row r="63">
@@ -6042,7 +6062,7 @@
         <v>Defeat 15 Pokemon in Poni Grove Main Area</v>
       </c>
       <c r="C63" t="str">
-        <v>The Interdimensional Rift Main Area Part 1</v>
+        <v>Unlocks Poni Plains Center</v>
       </c>
     </row>
     <row r="64">
@@ -6050,59 +6070,81 @@
         <v>Extra Challenge $5-3</v>
       </c>
       <c r="B64" t="str">
-        <v>Defeat 15 Pokemon in The Interdimensional Rift Main Area Part 1</v>
+        <v>Defeat 15 Pokemon in Poni Plains Center</v>
       </c>
       <c r="C64" t="str">
-        <v>The Interdimensional Rift Main Area Part 2</v>
+        <v>Unlocks Resolution Cave Main Area</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Extra Challenge $6-1</v>
+        <v>Extra Challenge $5-4</v>
       </c>
       <c r="B65" t="str">
-        <v>Defeat Champion Hau</v>
+        <v>Defeat 15 Pokemon in Resolution Cave Main Area</v>
       </c>
       <c r="C65" t="str">
-        <v>Poni Plains Center</v>
+        <v>Unlocks The Interdimensional Rift Main Area Part 1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Extra Challenge $6-2</v>
+        <v>Extra Challenge $5-5</v>
       </c>
       <c r="B66" t="str">
-        <v>Defeat 15 Pokemon in Poni Plains Center</v>
+        <v>Defeat 15 Pokemon in The Interdimensional Rift Main Area Part 1</v>
       </c>
       <c r="C66" t="str">
-        <v>Resolution Cave Main Area</v>
+        <v>Unlocks The Interdimensional Rift Main Area Part 2 [All Ultra Beasts]</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Extra Challenge $6-3</v>
+        <v>Extra Challenge $6-1</v>
       </c>
       <c r="B67" t="str">
-        <v>Defeat 15 Pokemon in Resolution Cave Main Area</v>
+        <v>Defeat Champion Hau</v>
       </c>
       <c r="C67" t="str">
-        <v>Shopping Mall Antiquities Event</v>
+        <v>Unlocks Mahalo Trail Main Area</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
+        <v>Extra Challenge $6-2</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Defeat 15 Pokemon in Mahalo Trail Main Area</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Unlocks Melemele Meadow Main Area</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Extra Challenge $6-3</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Defeat 15 Pokemon in Melemele Meadow Main Area</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Unlocks Shopping Mall Antiquities Event [Magearna]</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
         <v>Extra Challenge $6-4</v>
       </c>
-      <c r="B68" t="str">
+      <c r="B70" t="str">
         <v>Defeat 15 Pokemon in Shopping Mall Antiquities Event</v>
       </c>
-      <c r="C68" t="str">
-        <v>Aether Paradise Secret Lab</v>
+      <c r="C70" t="str">
+        <v>Unlocks Aether Paradise Restricted Area [Zeraora]</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C68"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C70"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -6136,7 +6178,7 @@
         <v>Route 1 East</v>
       </c>
       <c r="D2" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="3">
@@ -6164,7 +6206,7 @@
         <v>Route 3 North</v>
       </c>
       <c r="D4" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="5">
@@ -6178,7 +6220,7 @@
         <v>Ten Carat Hill Inside</v>
       </c>
       <c r="D5" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="6">
@@ -6192,7 +6234,7 @@
         <v>Route 7 Main Area</v>
       </c>
       <c r="D6" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="7">
@@ -6206,7 +6248,7 @@
         <v>Route 7 Main Area</v>
       </c>
       <c r="D7" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="8">
@@ -6220,7 +6262,7 @@
         <v>Lush Jungle North</v>
       </c>
       <c r="D8" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="9">
@@ -6234,7 +6276,7 @@
         <v>Lush Jungle East Cave</v>
       </c>
       <c r="D9" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="10">
@@ -6248,7 +6290,7 @@
         <v>Lush Jungle East Cave</v>
       </c>
       <c r="D10" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="11">
@@ -6262,7 +6304,7 @@
         <v>Route 7 Main Area</v>
       </c>
       <c r="D11" t="str">
-        <v>Yes (Relocated)</v>
+        <v>Yes (Merged)</v>
       </c>
     </row>
     <row r="12">
@@ -6276,7 +6318,7 @@
         <v>Route 7 Main Area</v>
       </c>
       <c r="D12" t="str">
-        <v>Yes (Relocated)</v>
+        <v>Yes (Merged)</v>
       </c>
     </row>
     <row r="13">
@@ -6290,7 +6332,7 @@
         <v>Mount Hokulani East</v>
       </c>
       <c r="D13" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="14">
@@ -6304,7 +6346,7 @@
         <v>Route 14 Main Area</v>
       </c>
       <c r="D14" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="15">
@@ -6318,7 +6360,7 @@
         <v>Route 15 Main Area</v>
       </c>
       <c r="D15" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="16">
@@ -6332,7 +6374,7 @@
         <v>Route 16 Main Area</v>
       </c>
       <c r="D16" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="17">
@@ -6346,343 +6388,343 @@
         <v>Mount Lanakila Cave</v>
       </c>
       <c r="D17" t="str">
-        <v>Yes (Added)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Type: Null</v>
+        <v>Tapu Koko</v>
       </c>
       <c r="B18" t="str">
-        <v>Normal</v>
+        <v>Electric/Fairy</v>
       </c>
       <c r="C18" t="str">
-        <v>Aether Paradise Labs</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="D18" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Silvally</v>
+        <v>Tapu Lele</v>
       </c>
       <c r="B19" t="str">
-        <v>Normal</v>
+        <v>Psychic/Fairy</v>
       </c>
       <c r="C19" t="str">
-        <v>Aether Paradise Labs</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="D19" t="str">
-        <v>Yes (Evolution)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Ditto</v>
+        <v>Tapu Bulu</v>
       </c>
       <c r="B20" t="str">
-        <v>Normal</v>
+        <v>Grass/Fairy</v>
       </c>
       <c r="C20" t="str">
-        <v>Aether Paradise Labs</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="D20" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Porygon</v>
+        <v>Tapu Fini</v>
       </c>
       <c r="B21" t="str">
-        <v>Normal</v>
+        <v>Water/Fairy</v>
       </c>
       <c r="C21" t="str">
-        <v>Aether Paradise Labs</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="D21" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Tapu Koko</v>
+        <v>Cosmog</v>
       </c>
       <c r="B22" t="str">
-        <v>Electric/Fairy</v>
+        <v>Psychic</v>
       </c>
       <c r="C22" t="str">
-        <v>Sacred Shrine Main Area</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="D22" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Tapu Lele</v>
+        <v>Cosmoem</v>
       </c>
       <c r="B23" t="str">
-        <v>Psychic/Fairy</v>
+        <v>Psychic</v>
       </c>
       <c r="C23" t="str">
-        <v>Sacred Shrine Main Area</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="D23" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes (Evolution)</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Tapu Bulu</v>
+        <v>Solgaleo</v>
       </c>
       <c r="B24" t="str">
-        <v>Grass/Fairy</v>
+        <v>Psychic/Steel</v>
       </c>
       <c r="C24" t="str">
-        <v>Sacred Shrine Main Area</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="D24" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Tapu Fini</v>
+        <v>Lunala</v>
       </c>
       <c r="B25" t="str">
-        <v>Water/Fairy</v>
+        <v>Psychic/Ghost</v>
       </c>
       <c r="C25" t="str">
-        <v>Sacred Shrine Main Area</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="D25" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Cosmog</v>
+        <v>Necrozma</v>
       </c>
       <c r="B26" t="str">
         <v>Psychic</v>
       </c>
       <c r="C26" t="str">
-        <v>Obsidian Sphere Main Area</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="D26" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Cosmoem</v>
+        <v>Poipole</v>
       </c>
       <c r="B27" t="str">
-        <v>Psychic</v>
+        <v>Poison</v>
       </c>
       <c r="C27" t="str">
-        <v>Obsidian Sphere Main Area</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="D27" t="str">
-        <v>Yes (Evolution)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Solgaleo</v>
+        <v>Naganadel</v>
       </c>
       <c r="B28" t="str">
-        <v>Psychic/Steel</v>
+        <v>Poison/Dragon</v>
       </c>
       <c r="C28" t="str">
-        <v>Obsidian Sphere Main Area</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="D28" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes (Evolution)</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Lunala</v>
+        <v>Nihilego</v>
       </c>
       <c r="B29" t="str">
-        <v>Psychic/Ghost</v>
+        <v>Rock/Poison</v>
       </c>
       <c r="C29" t="str">
-        <v>Obsidian Sphere Main Area</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="D29" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Necrozma</v>
+        <v>Buzzwole</v>
       </c>
       <c r="B30" t="str">
-        <v>Psychic</v>
+        <v>Bug/Fighting</v>
       </c>
       <c r="C30" t="str">
-        <v>Obsidian Sphere Main Area</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="D30" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Poipole</v>
+        <v>Pheromosa</v>
       </c>
       <c r="B31" t="str">
-        <v>Poison</v>
+        <v>Bug/Fighting</v>
       </c>
       <c r="C31" t="str">
-        <v>The Interdimensional Rift Main Area</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="D31" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Naganadel</v>
+        <v>Xurkitree</v>
       </c>
       <c r="B32" t="str">
-        <v>Poison/Dragon</v>
+        <v>Electric</v>
       </c>
       <c r="C32" t="str">
-        <v>The Interdimensional Rift Main Area</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="D32" t="str">
-        <v>Yes (Evolution)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Nihilego</v>
+        <v>Celesteela</v>
       </c>
       <c r="B33" t="str">
-        <v>Rock/Poison</v>
+        <v>Steel/Flying</v>
       </c>
       <c r="C33" t="str">
-        <v>The Interdimensional Rift Main Area</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="D33" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Buzzwole</v>
+        <v>Kartana</v>
       </c>
       <c r="B34" t="str">
-        <v>Bug/Fighting</v>
+        <v>Grass/Steel</v>
       </c>
       <c r="C34" t="str">
-        <v>The Interdimensional Rift Main Area</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="D34" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Pheromosa</v>
+        <v>Guzzlord</v>
       </c>
       <c r="B35" t="str">
-        <v>Bug/Fighting</v>
+        <v>Dark/Dragon</v>
       </c>
       <c r="C35" t="str">
-        <v>The Interdimensional Rift Main Area</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="D35" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Xurkitree</v>
+        <v>Stakataka</v>
       </c>
       <c r="B36" t="str">
-        <v>Electric</v>
+        <v>Rock/Steel</v>
       </c>
       <c r="C36" t="str">
-        <v>The Interdimensional Rift Main Area</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="D36" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Celesteela</v>
+        <v>Blacephalon</v>
       </c>
       <c r="B37" t="str">
-        <v>Steel/Flying</v>
+        <v>Fire/Ghost</v>
       </c>
       <c r="C37" t="str">
-        <v>The Interdimensional Rift Main Area</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="D37" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Kartana</v>
+        <v>Type: Null</v>
       </c>
       <c r="B38" t="str">
-        <v>Grass/Steel</v>
+        <v>Normal</v>
       </c>
       <c r="C38" t="str">
-        <v>The Interdimensional Rift Main Area</v>
+        <v>Aether Paradise Secret Lab</v>
       </c>
       <c r="D38" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Guzzlord</v>
+        <v>Silvally</v>
       </c>
       <c r="B39" t="str">
-        <v>Dark/Dragon</v>
+        <v>Normal</v>
       </c>
       <c r="C39" t="str">
-        <v>The Interdimensional Rift Main Area</v>
+        <v>Aether Paradise Secret Lab</v>
       </c>
       <c r="D39" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes (Evolution)</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Stakataka</v>
+        <v>Ditto</v>
       </c>
       <c r="B40" t="str">
-        <v>Rock/Steel</v>
+        <v>Normal</v>
       </c>
       <c r="C40" t="str">
-        <v>The Interdimensional Rift Main Area</v>
+        <v>Aether Paradise Secret Lab</v>
       </c>
       <c r="D40" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Blacephalon</v>
+        <v>Porygon</v>
       </c>
       <c r="B41" t="str">
-        <v>Fire/Ghost</v>
+        <v>Normal</v>
       </c>
       <c r="C41" t="str">
-        <v>The Interdimensional Rift Main Area</v>
+        <v>Aether Paradise Secret Lab</v>
       </c>
       <c r="D41" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="42">
@@ -6696,7 +6738,7 @@
         <v>Shopping Mall Antiquities Event</v>
       </c>
       <c r="D42" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="43">
@@ -6710,7 +6752,7 @@
         <v>Ten Carat Hill Deepest Cave</v>
       </c>
       <c r="D43" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="44">
@@ -6721,10 +6763,10 @@
         <v>Electric</v>
       </c>
       <c r="C44" t="str">
-        <v>Aether Paradise Secret Lab</v>
+        <v>Aether Paradise Restricted Area</v>
       </c>
       <c r="D44" t="str">
-        <v>Yes (Added to Extra)</v>
+        <v>Yes</v>
       </c>
     </row>
   </sheetData>

--- a/Alola_Paths_and_Challenges.xlsx
+++ b/Alola_Paths_and_Challenges.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F248"/>
+  <dimension ref="A1:F256"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -426,19 +426,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Starter</v>
+        <v>Route 1</v>
       </c>
       <c r="C2" t="str">
-        <v>Professor Kukui</v>
+        <v>East</v>
       </c>
       <c r="D2" t="str">
-        <v>Rowlet</v>
+        <v>Pikipek</v>
       </c>
       <c r="E2" t="str">
         <v>2-7</v>
       </c>
       <c r="F2" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="3">
@@ -446,19 +446,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="str">
-        <v>Starter</v>
+        <v>Route 1</v>
       </c>
       <c r="C3" t="str">
-        <v>Professor Kukui</v>
+        <v>East</v>
       </c>
       <c r="D3" t="str">
-        <v>Litten</v>
+        <v>Yungoos</v>
       </c>
       <c r="E3" t="str">
         <v>2-7</v>
       </c>
       <c r="F3" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="4">
@@ -466,24 +466,24 @@
         <v>1</v>
       </c>
       <c r="B4" t="str">
-        <v>Starter</v>
+        <v>Route 1</v>
       </c>
       <c r="C4" t="str">
-        <v>Professor Kukui</v>
+        <v>East</v>
       </c>
       <c r="D4" t="str">
-        <v>Popplio</v>
+        <v>Alolan Rattata</v>
       </c>
       <c r="E4" t="str">
         <v>2-7</v>
       </c>
       <c r="F4" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="str">
         <v>Route 1</v>
@@ -492,10 +492,10 @@
         <v>East</v>
       </c>
       <c r="D5" t="str">
-        <v>Pikipek</v>
+        <v>Ledyba</v>
       </c>
       <c r="E5" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F5" t="str">
         <v>12.50%</v>
@@ -503,7 +503,7 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" t="str">
         <v>Route 1</v>
@@ -512,10 +512,10 @@
         <v>East</v>
       </c>
       <c r="D6" t="str">
-        <v>Yungoos</v>
+        <v>Spinarak</v>
       </c>
       <c r="E6" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F6" t="str">
         <v>12.50%</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="str">
         <v>Route 1</v>
@@ -532,10 +532,10 @@
         <v>East</v>
       </c>
       <c r="D7" t="str">
-        <v>Alolan Rattata</v>
+        <v>Grubbin</v>
       </c>
       <c r="E7" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F7" t="str">
         <v>12.50%</v>
@@ -543,7 +543,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="str">
         <v>Route 1</v>
@@ -552,10 +552,10 @@
         <v>East</v>
       </c>
       <c r="D8" t="str">
-        <v>Ledyba</v>
+        <v>Pichu</v>
       </c>
       <c r="E8" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F8" t="str">
         <v>12.50%</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="str">
         <v>Route 1</v>
@@ -572,10 +572,10 @@
         <v>East</v>
       </c>
       <c r="D9" t="str">
-        <v>Spinarak</v>
+        <v>Pikachu</v>
       </c>
       <c r="E9" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F9" t="str">
         <v>12.50%</v>
@@ -589,16 +589,16 @@
         <v>Route 1</v>
       </c>
       <c r="C10" t="str">
-        <v>East</v>
+        <v>Hau'oli Outskirts</v>
       </c>
       <c r="D10" t="str">
-        <v>Grubbin</v>
+        <v>Inkay</v>
       </c>
       <c r="E10" t="str">
         <v>3-8</v>
       </c>
       <c r="F10" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="11">
@@ -609,16 +609,16 @@
         <v>Route 1</v>
       </c>
       <c r="C11" t="str">
-        <v>East</v>
+        <v>Hau'oli Outskirts</v>
       </c>
       <c r="D11" t="str">
-        <v>Pichu</v>
+        <v>Slowpoke</v>
       </c>
       <c r="E11" t="str">
         <v>3-8</v>
       </c>
       <c r="F11" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="12">
@@ -629,21 +629,21 @@
         <v>Route 1</v>
       </c>
       <c r="C12" t="str">
-        <v>East</v>
+        <v>Hau'oli Outskirts</v>
       </c>
       <c r="D12" t="str">
-        <v>Pikachu</v>
+        <v>Alolan Meowth</v>
       </c>
       <c r="E12" t="str">
         <v>3-8</v>
       </c>
       <c r="F12" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" t="str">
         <v>Route 1</v>
@@ -652,10 +652,10 @@
         <v>Hau'oli Outskirts</v>
       </c>
       <c r="D13" t="str">
-        <v>Inkay</v>
+        <v>Tentacool</v>
       </c>
       <c r="E13" t="str">
-        <v>5-10</v>
+        <v>3-8</v>
       </c>
       <c r="F13" t="str">
         <v>20.00%</v>
@@ -663,7 +663,7 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" t="str">
         <v>Route 1</v>
@@ -672,10 +672,10 @@
         <v>Hau'oli Outskirts</v>
       </c>
       <c r="D14" t="str">
-        <v>Slowpoke</v>
+        <v>Finneon</v>
       </c>
       <c r="E14" t="str">
-        <v>5-10</v>
+        <v>3-8</v>
       </c>
       <c r="F14" t="str">
         <v>20.00%</v>
@@ -686,13 +686,13 @@
         <v>3</v>
       </c>
       <c r="B15" t="str">
-        <v>Route 1</v>
+        <v>Hau'oli City</v>
       </c>
       <c r="C15" t="str">
-        <v>Hau'oli Outskirts</v>
+        <v>Shopping District</v>
       </c>
       <c r="D15" t="str">
-        <v>Alolan Meowth</v>
+        <v>Furfrou</v>
       </c>
       <c r="E15" t="str">
         <v>5-10</v>
@@ -706,13 +706,13 @@
         <v>3</v>
       </c>
       <c r="B16" t="str">
-        <v>Route 1</v>
+        <v>Hau'oli City</v>
       </c>
       <c r="C16" t="str">
-        <v>Hau'oli Outskirts</v>
+        <v>Shopping District</v>
       </c>
       <c r="D16" t="str">
-        <v>Tentacool</v>
+        <v>Hypno</v>
       </c>
       <c r="E16" t="str">
         <v>5-10</v>
@@ -726,13 +726,13 @@
         <v>3</v>
       </c>
       <c r="B17" t="str">
-        <v>Route 1</v>
+        <v>Hau'oli City</v>
       </c>
       <c r="C17" t="str">
-        <v>Hau'oli Outskirts</v>
+        <v>Shopping District</v>
       </c>
       <c r="D17" t="str">
-        <v>Finneon</v>
+        <v>Abra</v>
       </c>
       <c r="E17" t="str">
         <v>5-10</v>
@@ -743,7 +743,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" t="str">
         <v>Hau'oli City</v>
@@ -752,10 +752,10 @@
         <v>Shopping District</v>
       </c>
       <c r="D18" t="str">
-        <v>Furfrou</v>
+        <v>Mime Jr.</v>
       </c>
       <c r="E18" t="str">
-        <v>6-11</v>
+        <v>5-10</v>
       </c>
       <c r="F18" t="str">
         <v>20.00%</v>
@@ -763,7 +763,7 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19" t="str">
         <v>Hau'oli City</v>
@@ -772,10 +772,10 @@
         <v>Shopping District</v>
       </c>
       <c r="D19" t="str">
-        <v>Hypno</v>
+        <v>Bewear</v>
       </c>
       <c r="E19" t="str">
-        <v>6-11</v>
+        <v>5-10</v>
       </c>
       <c r="F19" t="str">
         <v>20.00%</v>
@@ -786,19 +786,19 @@
         <v>4</v>
       </c>
       <c r="B20" t="str">
-        <v>Hau'oli City</v>
+        <v>Route 2</v>
       </c>
       <c r="C20" t="str">
-        <v>Shopping District</v>
+        <v>North</v>
       </c>
       <c r="D20" t="str">
-        <v>Abra</v>
+        <v>Drowzee</v>
       </c>
       <c r="E20" t="str">
         <v>6-11</v>
       </c>
       <c r="F20" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="21">
@@ -806,19 +806,19 @@
         <v>4</v>
       </c>
       <c r="B21" t="str">
-        <v>Hau'oli City</v>
+        <v>Route 2</v>
       </c>
       <c r="C21" t="str">
-        <v>Shopping District</v>
+        <v>North</v>
       </c>
       <c r="D21" t="str">
-        <v>Mime Jr.</v>
+        <v>Makuhita</v>
       </c>
       <c r="E21" t="str">
         <v>6-11</v>
       </c>
       <c r="F21" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="22">
@@ -826,24 +826,24 @@
         <v>4</v>
       </c>
       <c r="B22" t="str">
-        <v>Hau'oli City</v>
+        <v>Route 2</v>
       </c>
       <c r="C22" t="str">
-        <v>Shopping District</v>
+        <v>North</v>
       </c>
       <c r="D22" t="str">
-        <v>Bewear</v>
+        <v>Spearow</v>
       </c>
       <c r="E22" t="str">
         <v>6-11</v>
       </c>
       <c r="F22" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B23" t="str">
         <v>Route 2</v>
@@ -852,10 +852,10 @@
         <v>North</v>
       </c>
       <c r="D23" t="str">
-        <v>Drowzee</v>
+        <v>Ekans</v>
       </c>
       <c r="E23" t="str">
-        <v>7-12</v>
+        <v>6-11</v>
       </c>
       <c r="F23" t="str">
         <v>16.67%</v>
@@ -863,7 +863,7 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" t="str">
         <v>Route 2</v>
@@ -872,10 +872,10 @@
         <v>North</v>
       </c>
       <c r="D24" t="str">
-        <v>Makuhita</v>
+        <v>Growlithe</v>
       </c>
       <c r="E24" t="str">
-        <v>7-12</v>
+        <v>6-11</v>
       </c>
       <c r="F24" t="str">
         <v>16.67%</v>
@@ -883,7 +883,7 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B25" t="str">
         <v>Route 2</v>
@@ -892,10 +892,10 @@
         <v>North</v>
       </c>
       <c r="D25" t="str">
-        <v>Spearow</v>
+        <v>Smeargle</v>
       </c>
       <c r="E25" t="str">
-        <v>7-12</v>
+        <v>6-11</v>
       </c>
       <c r="F25" t="str">
         <v>16.67%</v>
@@ -906,59 +906,59 @@
         <v>5</v>
       </c>
       <c r="B26" t="str">
-        <v>Route 2</v>
+        <v>Captain Ilima</v>
       </c>
       <c r="C26" t="str">
-        <v>North</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D26" t="str">
-        <v>Ekans</v>
+        <v>Boss</v>
       </c>
       <c r="E26" t="str">
-        <v>7-12</v>
+        <v>8-13</v>
       </c>
       <c r="F26" t="str">
-        <v>16.67%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B27" t="str">
-        <v>Route 2</v>
+        <v>Hau'oli Cemetery</v>
       </c>
       <c r="C27" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D27" t="str">
-        <v>Growlithe</v>
+        <v>Gastly</v>
       </c>
       <c r="E27" t="str">
-        <v>7-12</v>
+        <v>9-14</v>
       </c>
       <c r="F27" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B28" t="str">
-        <v>Route 2</v>
+        <v>Hau'oli Cemetery</v>
       </c>
       <c r="C28" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D28" t="str">
-        <v>Smeargle</v>
+        <v>Drifloon</v>
       </c>
       <c r="E28" t="str">
-        <v>7-12</v>
+        <v>9-14</v>
       </c>
       <c r="F28" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="29">
@@ -966,24 +966,24 @@
         <v>6</v>
       </c>
       <c r="B29" t="str">
-        <v>Captain Ilima</v>
+        <v>Hau'oli Cemetery</v>
       </c>
       <c r="C29" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D29" t="str">
-        <v>Boss</v>
+        <v>Murkrow</v>
       </c>
       <c r="E29" t="str">
         <v>9-14</v>
       </c>
       <c r="F29" t="str">
-        <v>-</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B30" t="str">
         <v>Hau'oli Cemetery</v>
@@ -992,10 +992,10 @@
         <v>Main Area</v>
       </c>
       <c r="D30" t="str">
-        <v>Gastly</v>
+        <v>Misdreavus</v>
       </c>
       <c r="E30" t="str">
-        <v>10-15</v>
+        <v>9-14</v>
       </c>
       <c r="F30" t="str">
         <v>25.00%</v>
@@ -1006,19 +1006,19 @@
         <v>7</v>
       </c>
       <c r="B31" t="str">
-        <v>Hau'oli Cemetery</v>
+        <v>Ten Carat Hill</v>
       </c>
       <c r="C31" t="str">
-        <v>Main Area</v>
+        <v>Farthest Hollow</v>
       </c>
       <c r="D31" t="str">
-        <v>Drifloon</v>
+        <v>Roggenrola</v>
       </c>
       <c r="E31" t="str">
-        <v>10-15</v>
+        <v>14-19</v>
       </c>
       <c r="F31" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="32">
@@ -1026,19 +1026,19 @@
         <v>7</v>
       </c>
       <c r="B32" t="str">
-        <v>Hau'oli Cemetery</v>
+        <v>Ten Carat Hill</v>
       </c>
       <c r="C32" t="str">
-        <v>Main Area</v>
+        <v>Farthest Hollow</v>
       </c>
       <c r="D32" t="str">
-        <v>Murkrow</v>
+        <v>Carbink</v>
       </c>
       <c r="E32" t="str">
-        <v>10-15</v>
+        <v>14-19</v>
       </c>
       <c r="F32" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="33">
@@ -1046,24 +1046,24 @@
         <v>7</v>
       </c>
       <c r="B33" t="str">
-        <v>Hau'oli Cemetery</v>
+        <v>Ten Carat Hill</v>
       </c>
       <c r="C33" t="str">
-        <v>Main Area</v>
+        <v>Farthest Hollow</v>
       </c>
       <c r="D33" t="str">
-        <v>Misdreavus</v>
+        <v>Spinda</v>
       </c>
       <c r="E33" t="str">
-        <v>10-15</v>
+        <v>14-19</v>
       </c>
       <c r="F33" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B34" t="str">
         <v>Ten Carat Hill</v>
@@ -1072,7 +1072,7 @@
         <v>Farthest Hollow</v>
       </c>
       <c r="D34" t="str">
-        <v>Roggenrola</v>
+        <v>Mawile</v>
       </c>
       <c r="E34" t="str">
         <v>14-19</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B35" t="str">
         <v>Ten Carat Hill</v>
@@ -1092,7 +1092,7 @@
         <v>Farthest Hollow</v>
       </c>
       <c r="D35" t="str">
-        <v>Carbink</v>
+        <v>Lycanroc</v>
       </c>
       <c r="E35" t="str">
         <v>14-19</v>
@@ -1106,19 +1106,19 @@
         <v>8</v>
       </c>
       <c r="B36" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Seaward Cave</v>
       </c>
       <c r="C36" t="str">
-        <v>Farthest Hollow</v>
+        <v>Main Area</v>
       </c>
       <c r="D36" t="str">
-        <v>Spinda</v>
+        <v>Barboach</v>
       </c>
       <c r="E36" t="str">
-        <v>14-19</v>
+        <v>15-20</v>
       </c>
       <c r="F36" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="37">
@@ -1126,19 +1126,19 @@
         <v>8</v>
       </c>
       <c r="B37" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Seaward Cave</v>
       </c>
       <c r="C37" t="str">
-        <v>Farthest Hollow</v>
+        <v>Main Area</v>
       </c>
       <c r="D37" t="str">
-        <v>Mawile</v>
+        <v>Smoochum</v>
       </c>
       <c r="E37" t="str">
-        <v>14-19</v>
+        <v>15-20</v>
       </c>
       <c r="F37" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="38">
@@ -1146,19 +1146,19 @@
         <v>8</v>
       </c>
       <c r="B38" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Seaward Cave</v>
       </c>
       <c r="C38" t="str">
-        <v>Farthest Hollow</v>
+        <v>Main Area</v>
       </c>
       <c r="D38" t="str">
-        <v>Lycanroc</v>
+        <v>Seel</v>
       </c>
       <c r="E38" t="str">
-        <v>14-19</v>
+        <v>15-20</v>
       </c>
       <c r="F38" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="39">
@@ -1166,59 +1166,59 @@
         <v>9</v>
       </c>
       <c r="B39" t="str">
-        <v>Seaward Cave</v>
+        <v>Kahuna Hala</v>
       </c>
       <c r="C39" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D39" t="str">
-        <v>Barboach</v>
+        <v>Boss</v>
       </c>
       <c r="E39" t="str">
-        <v>16-21</v>
+        <v>17-22</v>
       </c>
       <c r="F39" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B40" t="str">
-        <v>Seaward Cave</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C40" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D40" t="str">
-        <v>Smoochum</v>
+        <v>Vikavolt</v>
       </c>
       <c r="E40" t="str">
-        <v>16-21</v>
+        <v>18-23</v>
       </c>
       <c r="F40" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B41" t="str">
-        <v>Seaward Cave</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C41" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D41" t="str">
-        <v>Seel</v>
+        <v>Ribombee</v>
       </c>
       <c r="E41" t="str">
-        <v>16-21</v>
+        <v>18-23</v>
       </c>
       <c r="F41" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="42">
@@ -1226,16 +1226,16 @@
         <v>10</v>
       </c>
       <c r="B42" t="str">
-        <v>Route 3</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C42" t="str">
-        <v>North</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D42" t="str">
-        <v>Mankey</v>
+        <v>Araquanid</v>
       </c>
       <c r="E42" t="str">
-        <v>17-22</v>
+        <v>18-23</v>
       </c>
       <c r="F42" t="str">
         <v>20.00%</v>
@@ -1246,16 +1246,16 @@
         <v>10</v>
       </c>
       <c r="B43" t="str">
-        <v>Route 3</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C43" t="str">
-        <v>North</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D43" t="str">
-        <v>Delibird</v>
+        <v>Lurantis</v>
       </c>
       <c r="E43" t="str">
-        <v>17-22</v>
+        <v>18-23</v>
       </c>
       <c r="F43" t="str">
         <v>20.00%</v>
@@ -1266,16 +1266,16 @@
         <v>10</v>
       </c>
       <c r="B44" t="str">
-        <v>Route 3</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C44" t="str">
-        <v>North</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D44" t="str">
-        <v>Bagon</v>
+        <v>Salazzle</v>
       </c>
       <c r="E44" t="str">
-        <v>17-22</v>
+        <v>18-23</v>
       </c>
       <c r="F44" t="str">
         <v>20.00%</v>
@@ -1283,19 +1283,19 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B45" t="str">
-        <v>Route 3</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C45" t="str">
-        <v>North</v>
+        <v>Main Area Part 2</v>
       </c>
       <c r="D45" t="str">
-        <v>Oricorio</v>
+        <v>Alolan Marowak</v>
       </c>
       <c r="E45" t="str">
-        <v>17-22</v>
+        <v>18-23</v>
       </c>
       <c r="F45" t="str">
         <v>20.00%</v>
@@ -1303,19 +1303,19 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B46" t="str">
-        <v>Route 3</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C46" t="str">
-        <v>North</v>
+        <v>Main Area Part 2</v>
       </c>
       <c r="D46" t="str">
-        <v>Igglybuff</v>
+        <v>Kommo-o</v>
       </c>
       <c r="E46" t="str">
-        <v>17-22</v>
+        <v>18-23</v>
       </c>
       <c r="F46" t="str">
         <v>20.00%</v>
@@ -1326,59 +1326,59 @@
         <v>11</v>
       </c>
       <c r="B47" t="str">
-        <v>Kahuna Hala</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C47" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area Part 2</v>
       </c>
       <c r="D47" t="str">
-        <v>Boss</v>
+        <v>Mimikyu</v>
       </c>
       <c r="E47" t="str">
         <v>18-23</v>
       </c>
       <c r="F47" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B48" t="str">
         <v>Heahea Beach</v>
       </c>
       <c r="C48" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area Part 2</v>
       </c>
       <c r="D48" t="str">
-        <v>Vikavolt</v>
+        <v>Poliwhirl</v>
       </c>
       <c r="E48" t="str">
-        <v>20-25</v>
+        <v>18-23</v>
       </c>
       <c r="F48" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B49" t="str">
         <v>Heahea Beach</v>
       </c>
       <c r="C49" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area Part 2</v>
       </c>
       <c r="D49" t="str">
-        <v>Ribombee</v>
+        <v>Ditto</v>
       </c>
       <c r="E49" t="str">
-        <v>20-25</v>
+        <v>18-23</v>
       </c>
       <c r="F49" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="50">
@@ -1386,19 +1386,19 @@
         <v>12</v>
       </c>
       <c r="B50" t="str">
-        <v>Heahea Beach</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C50" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D50" t="str">
-        <v>Araquanid</v>
+        <v>Eevee</v>
       </c>
       <c r="E50" t="str">
         <v>20-25</v>
       </c>
       <c r="F50" t="str">
-        <v>11.11%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="51">
@@ -1406,19 +1406,19 @@
         <v>12</v>
       </c>
       <c r="B51" t="str">
-        <v>Heahea Beach</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C51" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D51" t="str">
-        <v>Lurantis</v>
+        <v>Mareep</v>
       </c>
       <c r="E51" t="str">
         <v>20-25</v>
       </c>
       <c r="F51" t="str">
-        <v>11.11%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="52">
@@ -1426,19 +1426,19 @@
         <v>12</v>
       </c>
       <c r="B52" t="str">
-        <v>Heahea Beach</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C52" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D52" t="str">
-        <v>Salazzle</v>
+        <v>Tauros</v>
       </c>
       <c r="E52" t="str">
         <v>20-25</v>
       </c>
       <c r="F52" t="str">
-        <v>11.11%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="53">
@@ -1446,179 +1446,179 @@
         <v>12</v>
       </c>
       <c r="B53" t="str">
-        <v>Heahea Beach</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C53" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D53" t="str">
-        <v>Alolan Marowak</v>
+        <v>Miltank</v>
       </c>
       <c r="E53" t="str">
         <v>20-25</v>
       </c>
       <c r="F53" t="str">
-        <v>11.11%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B54" t="str">
-        <v>Heahea Beach</v>
+        <v>Daycare</v>
       </c>
       <c r="C54" t="str">
-        <v>Main Area Part 1</v>
+        <v>NPC</v>
       </c>
       <c r="D54" t="str">
-        <v>Kommo-o</v>
+        <v>NPC</v>
       </c>
       <c r="E54" t="str">
-        <v>20-25</v>
+        <v>-</v>
       </c>
       <c r="F54" t="str">
-        <v>11.11%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B55" t="str">
-        <v>Heahea Beach</v>
+        <v>Route 5</v>
       </c>
       <c r="C55" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D55" t="str">
-        <v>Mimikyu</v>
+        <v>Noibat</v>
       </c>
       <c r="E55" t="str">
-        <v>20-25</v>
+        <v>22-27</v>
       </c>
       <c r="F55" t="str">
-        <v>11.11%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B56" t="str">
-        <v>Heahea Beach</v>
+        <v>Route 5</v>
       </c>
       <c r="C56" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D56" t="str">
-        <v>Poliwhirl</v>
+        <v>Fomantis</v>
       </c>
       <c r="E56" t="str">
-        <v>20-25</v>
+        <v>22-27</v>
       </c>
       <c r="F56" t="str">
-        <v>11.11%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B57" t="str">
-        <v>Heahea Beach</v>
+        <v>Route 5</v>
       </c>
       <c r="C57" t="str">
-        <v>Main Area Part 2</v>
+        <v>Main Area</v>
       </c>
       <c r="D57" t="str">
-        <v>Ditto</v>
+        <v>Bounsweet</v>
       </c>
       <c r="E57" t="str">
-        <v>20-25</v>
+        <v>22-27</v>
       </c>
       <c r="F57" t="str">
-        <v>100.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B58" t="str">
-        <v>Paniola Ranch</v>
+        <v>Brooklet Hill</v>
       </c>
       <c r="C58" t="str">
-        <v>Main Area</v>
+        <v>South</v>
       </c>
       <c r="D58" t="str">
-        <v>Eevee</v>
+        <v>Wingull</v>
       </c>
       <c r="E58" t="str">
-        <v>21-26</v>
+        <v>24-29</v>
       </c>
       <c r="F58" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B59" t="str">
-        <v>Paniola Ranch</v>
+        <v>Brooklet Hill</v>
       </c>
       <c r="C59" t="str">
-        <v>Main Area</v>
+        <v>South</v>
       </c>
       <c r="D59" t="str">
-        <v>Mareep</v>
+        <v>Lillipup</v>
       </c>
       <c r="E59" t="str">
-        <v>21-26</v>
+        <v>24-29</v>
       </c>
       <c r="F59" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B60" t="str">
-        <v>Paniola Ranch</v>
+        <v>Brooklet Hill</v>
       </c>
       <c r="C60" t="str">
-        <v>Main Area</v>
+        <v>South</v>
       </c>
       <c r="D60" t="str">
-        <v>Tauros</v>
+        <v>Paras</v>
       </c>
       <c r="E60" t="str">
-        <v>21-26</v>
+        <v>24-29</v>
       </c>
       <c r="F60" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B61" t="str">
-        <v>Paniola Ranch</v>
+        <v>Brooklet Hill</v>
       </c>
       <c r="C61" t="str">
-        <v>Main Area</v>
+        <v>South</v>
       </c>
       <c r="D61" t="str">
-        <v>Miltank</v>
+        <v>Goldeen</v>
       </c>
       <c r="E61" t="str">
-        <v>21-26</v>
+        <v>24-29</v>
       </c>
       <c r="F61" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="62">
@@ -1626,19 +1626,19 @@
         <v>15</v>
       </c>
       <c r="B62" t="str">
-        <v>Daycare</v>
+        <v>Brooklet Hill</v>
       </c>
       <c r="C62" t="str">
-        <v>NPC</v>
+        <v>South</v>
       </c>
       <c r="D62" t="str">
-        <v>NPC</v>
+        <v>Feebas</v>
       </c>
       <c r="E62" t="str">
-        <v>-</v>
+        <v>24-29</v>
       </c>
       <c r="F62" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="63">
@@ -1646,36 +1646,36 @@
         <v>16</v>
       </c>
       <c r="B63" t="str">
-        <v>Route 5</v>
+        <v>Captain Lana</v>
       </c>
       <c r="C63" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D63" t="str">
-        <v>Noibat</v>
+        <v>Boss</v>
       </c>
       <c r="E63" t="str">
-        <v>24-29</v>
+        <v>25-30</v>
       </c>
       <c r="F63" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B64" t="str">
-        <v>Route 5</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C64" t="str">
         <v>Main Area</v>
       </c>
       <c r="D64" t="str">
-        <v>Fomantis</v>
+        <v>Cubone</v>
       </c>
       <c r="E64" t="str">
-        <v>24-29</v>
+        <v>27-32</v>
       </c>
       <c r="F64" t="str">
         <v>33.33%</v>
@@ -1683,19 +1683,19 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B65" t="str">
-        <v>Route 5</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C65" t="str">
         <v>Main Area</v>
       </c>
       <c r="D65" t="str">
-        <v>Bounsweet</v>
+        <v>Kangaskhan</v>
       </c>
       <c r="E65" t="str">
-        <v>24-29</v>
+        <v>27-32</v>
       </c>
       <c r="F65" t="str">
         <v>33.33%</v>
@@ -1706,56 +1706,56 @@
         <v>17</v>
       </c>
       <c r="B66" t="str">
-        <v>Brooklet Hill</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C66" t="str">
-        <v>South</v>
+        <v>Main Area</v>
       </c>
       <c r="D66" t="str">
-        <v>Wingull</v>
+        <v>Magby</v>
       </c>
       <c r="E66" t="str">
-        <v>25-30</v>
+        <v>27-32</v>
       </c>
       <c r="F66" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B67" t="str">
-        <v>Brooklet Hill</v>
+        <v>Captain Kiawe</v>
       </c>
       <c r="C67" t="str">
-        <v>South</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D67" t="str">
-        <v>Lillipup</v>
+        <v>Boss</v>
       </c>
       <c r="E67" t="str">
-        <v>25-30</v>
+        <v>28-33</v>
       </c>
       <c r="F67" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B68" t="str">
-        <v>Brooklet Hill</v>
+        <v>Route 7</v>
       </c>
       <c r="C68" t="str">
-        <v>South</v>
+        <v>Main Area</v>
       </c>
       <c r="D68" t="str">
-        <v>Paras</v>
+        <v>Staryu</v>
       </c>
       <c r="E68" t="str">
-        <v>25-30</v>
+        <v>30-35</v>
       </c>
       <c r="F68" t="str">
         <v>20.00%</v>
@@ -1763,19 +1763,19 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B69" t="str">
-        <v>Brooklet Hill</v>
+        <v>Route 7</v>
       </c>
       <c r="C69" t="str">
-        <v>South</v>
+        <v>Main Area</v>
       </c>
       <c r="D69" t="str">
-        <v>Goldeen</v>
+        <v>Pyukumuku</v>
       </c>
       <c r="E69" t="str">
-        <v>25-30</v>
+        <v>30-35</v>
       </c>
       <c r="F69" t="str">
         <v>20.00%</v>
@@ -1783,19 +1783,19 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B70" t="str">
-        <v>Brooklet Hill</v>
+        <v>Route 7</v>
       </c>
       <c r="C70" t="str">
-        <v>South</v>
+        <v>Main Area</v>
       </c>
       <c r="D70" t="str">
-        <v>Feebas</v>
+        <v>Corsola</v>
       </c>
       <c r="E70" t="str">
-        <v>25-30</v>
+        <v>30-35</v>
       </c>
       <c r="F70" t="str">
         <v>20.00%</v>
@@ -1803,22 +1803,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B71" t="str">
-        <v>Captain Lana</v>
+        <v>Route 7</v>
       </c>
       <c r="C71" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D71" t="str">
-        <v>Boss</v>
+        <v>Mareanie</v>
       </c>
       <c r="E71" t="str">
-        <v>27-32</v>
+        <v>30-35</v>
       </c>
       <c r="F71" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="72">
@@ -1826,59 +1826,59 @@
         <v>19</v>
       </c>
       <c r="B72" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Route 7</v>
       </c>
       <c r="C72" t="str">
         <v>Main Area</v>
       </c>
       <c r="D72" t="str">
-        <v>Cubone</v>
+        <v>Bruxish</v>
       </c>
       <c r="E72" t="str">
-        <v>28-33</v>
+        <v>30-35</v>
       </c>
       <c r="F72" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B73" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Route 8</v>
       </c>
       <c r="C73" t="str">
-        <v>Main Area</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D73" t="str">
-        <v>Kangaskhan</v>
+        <v>Omanyte</v>
       </c>
       <c r="E73" t="str">
-        <v>28-33</v>
+        <v>31-36</v>
       </c>
       <c r="F73" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B74" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Route 8</v>
       </c>
       <c r="C74" t="str">
-        <v>Main Area</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D74" t="str">
-        <v>Magby</v>
+        <v>Kabuto</v>
       </c>
       <c r="E74" t="str">
-        <v>28-33</v>
+        <v>31-36</v>
       </c>
       <c r="F74" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="75">
@@ -1886,33 +1886,33 @@
         <v>20</v>
       </c>
       <c r="B75" t="str">
-        <v>Captain Kiawe</v>
+        <v>Route 8</v>
       </c>
       <c r="C75" t="str">
-        <v>Boss Battle</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D75" t="str">
-        <v>Boss</v>
+        <v>Lileep</v>
       </c>
       <c r="E75" t="str">
-        <v>29-34</v>
+        <v>31-36</v>
       </c>
       <c r="F75" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B76" t="str">
-        <v>Route 7</v>
+        <v>Route 8</v>
       </c>
       <c r="C76" t="str">
-        <v>Main Area</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D76" t="str">
-        <v>Staryu</v>
+        <v>Anorith</v>
       </c>
       <c r="E76" t="str">
         <v>31-36</v>
@@ -1923,16 +1923,16 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B77" t="str">
-        <v>Route 7</v>
+        <v>Route 8</v>
       </c>
       <c r="C77" t="str">
-        <v>Main Area</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D77" t="str">
-        <v>Pyukumuku</v>
+        <v>Cranidos</v>
       </c>
       <c r="E77" t="str">
         <v>31-36</v>
@@ -1946,13 +1946,13 @@
         <v>21</v>
       </c>
       <c r="B78" t="str">
-        <v>Route 7</v>
+        <v>Route 8</v>
       </c>
       <c r="C78" t="str">
-        <v>Main Area</v>
+        <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D78" t="str">
-        <v>Corsola</v>
+        <v>Shieldon</v>
       </c>
       <c r="E78" t="str">
         <v>31-36</v>
@@ -1966,13 +1966,13 @@
         <v>21</v>
       </c>
       <c r="B79" t="str">
-        <v>Route 7</v>
+        <v>Route 8</v>
       </c>
       <c r="C79" t="str">
-        <v>Main Area</v>
+        <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D79" t="str">
-        <v>Mareanie</v>
+        <v>Archen</v>
       </c>
       <c r="E79" t="str">
         <v>31-36</v>
@@ -1986,13 +1986,13 @@
         <v>21</v>
       </c>
       <c r="B80" t="str">
-        <v>Route 7</v>
+        <v>Route 8</v>
       </c>
       <c r="C80" t="str">
-        <v>Main Area</v>
+        <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D80" t="str">
-        <v>Bruxish</v>
+        <v>Tirtouga</v>
       </c>
       <c r="E80" t="str">
         <v>31-36</v>
@@ -2003,42 +2003,42 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B81" t="str">
         <v>Route 8</v>
       </c>
       <c r="C81" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D81" t="str">
-        <v>Omanyte</v>
+        <v>Tyrunt</v>
       </c>
       <c r="E81" t="str">
-        <v>32-37</v>
+        <v>31-36</v>
       </c>
       <c r="F81" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B82" t="str">
         <v>Route 8</v>
       </c>
       <c r="C82" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D82" t="str">
-        <v>Kabuto</v>
+        <v>Amaura</v>
       </c>
       <c r="E82" t="str">
-        <v>32-37</v>
+        <v>31-36</v>
       </c>
       <c r="F82" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="83">
@@ -2046,19 +2046,19 @@
         <v>22</v>
       </c>
       <c r="B83" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C83" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>North</v>
       </c>
       <c r="D83" t="str">
-        <v>Lileep</v>
+        <v>Trumbeak</v>
       </c>
       <c r="E83" t="str">
-        <v>32-37</v>
+        <v>33-38</v>
       </c>
       <c r="F83" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="84">
@@ -2066,19 +2066,19 @@
         <v>22</v>
       </c>
       <c r="B84" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C84" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>North</v>
       </c>
       <c r="D84" t="str">
-        <v>Anorith</v>
+        <v>Steenee</v>
       </c>
       <c r="E84" t="str">
-        <v>32-37</v>
+        <v>33-38</v>
       </c>
       <c r="F84" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="85">
@@ -2086,19 +2086,19 @@
         <v>22</v>
       </c>
       <c r="B85" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C85" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>North</v>
       </c>
       <c r="D85" t="str">
-        <v>Cranidos</v>
+        <v>Comfey</v>
       </c>
       <c r="E85" t="str">
-        <v>32-37</v>
+        <v>33-38</v>
       </c>
       <c r="F85" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="86">
@@ -2106,19 +2106,19 @@
         <v>22</v>
       </c>
       <c r="B86" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C86" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>North</v>
       </c>
       <c r="D86" t="str">
-        <v>Shieldon</v>
+        <v>Hoothoot</v>
       </c>
       <c r="E86" t="str">
-        <v>32-37</v>
+        <v>33-38</v>
       </c>
       <c r="F86" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="87">
@@ -2126,19 +2126,19 @@
         <v>22</v>
       </c>
       <c r="B87" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C87" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>North</v>
       </c>
       <c r="D87" t="str">
-        <v>Archen</v>
+        <v>Oranguru</v>
       </c>
       <c r="E87" t="str">
-        <v>32-37</v>
+        <v>33-38</v>
       </c>
       <c r="F87" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="88">
@@ -2146,39 +2146,39 @@
         <v>22</v>
       </c>
       <c r="B88" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C88" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>North</v>
       </c>
       <c r="D88" t="str">
-        <v>Tirtouga</v>
+        <v>Bounsweet</v>
       </c>
       <c r="E88" t="str">
-        <v>32-37</v>
+        <v>33-38</v>
       </c>
       <c r="F88" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B89" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C89" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>East Cave</v>
       </c>
       <c r="D89" t="str">
-        <v>Tyrunt</v>
+        <v>Golbat</v>
       </c>
       <c r="E89" t="str">
-        <v>32-37</v>
+        <v>34-39</v>
       </c>
       <c r="F89" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="90">
@@ -2186,79 +2186,79 @@
         <v>23</v>
       </c>
       <c r="B90" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C90" t="str">
-        <v>Fossil Restoration Center Part 2</v>
+        <v>East Cave</v>
       </c>
       <c r="D90" t="str">
-        <v>Amaura</v>
+        <v>Salandit</v>
       </c>
       <c r="E90" t="str">
-        <v>32-37</v>
+        <v>34-39</v>
       </c>
       <c r="F90" t="str">
-        <v>100.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B91" t="str">
         <v>Lush Jungle</v>
       </c>
       <c r="C91" t="str">
-        <v>North</v>
+        <v>East Cave</v>
       </c>
       <c r="D91" t="str">
-        <v>Trumbeak</v>
+        <v>Larvesta</v>
       </c>
       <c r="E91" t="str">
-        <v>33-38</v>
+        <v>34-39</v>
       </c>
       <c r="F91" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B92" t="str">
         <v>Lush Jungle</v>
       </c>
       <c r="C92" t="str">
-        <v>North</v>
+        <v>East Cave</v>
       </c>
       <c r="D92" t="str">
-        <v>Steenee</v>
+        <v>Oranguru</v>
       </c>
       <c r="E92" t="str">
-        <v>33-38</v>
+        <v>34-39</v>
       </c>
       <c r="F92" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B93" t="str">
         <v>Lush Jungle</v>
       </c>
       <c r="C93" t="str">
-        <v>North</v>
+        <v>East Cave</v>
       </c>
       <c r="D93" t="str">
-        <v>Comfey</v>
+        <v>Passimian</v>
       </c>
       <c r="E93" t="str">
-        <v>33-38</v>
+        <v>34-39</v>
       </c>
       <c r="F93" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="94">
@@ -2266,59 +2266,59 @@
         <v>24</v>
       </c>
       <c r="B94" t="str">
-        <v>Lush Jungle</v>
+        <v>Captain Mallow</v>
       </c>
       <c r="C94" t="str">
-        <v>North</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D94" t="str">
-        <v>Hoothoot</v>
+        <v>Boss</v>
       </c>
       <c r="E94" t="str">
-        <v>33-38</v>
+        <v>36-41</v>
       </c>
       <c r="F94" t="str">
-        <v>16.67%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="95">
       <c r="A95">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B95" t="str">
-        <v>Lush Jungle</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C95" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D95" t="str">
-        <v>Oranguru</v>
+        <v>Zubat</v>
       </c>
       <c r="E95" t="str">
-        <v>33-38</v>
+        <v>37-42</v>
       </c>
       <c r="F95" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B96" t="str">
-        <v>Lush Jungle</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C96" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D96" t="str">
-        <v>Bounsweet</v>
+        <v>Alolan Diglett</v>
       </c>
       <c r="E96" t="str">
-        <v>33-38</v>
+        <v>37-42</v>
       </c>
       <c r="F96" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="97">
@@ -2326,19 +2326,19 @@
         <v>25</v>
       </c>
       <c r="B97" t="str">
-        <v>Lush Jungle</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C97" t="str">
-        <v>East Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D97" t="str">
-        <v>Golbat</v>
+        <v>Kecleon</v>
       </c>
       <c r="E97" t="str">
-        <v>35-40</v>
+        <v>37-42</v>
       </c>
       <c r="F97" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="98">
@@ -2346,79 +2346,79 @@
         <v>25</v>
       </c>
       <c r="B98" t="str">
-        <v>Lush Jungle</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C98" t="str">
-        <v>East Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D98" t="str">
-        <v>Salandit</v>
+        <v>Larvitar</v>
       </c>
       <c r="E98" t="str">
-        <v>35-40</v>
+        <v>37-42</v>
       </c>
       <c r="F98" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B99" t="str">
-        <v>Lush Jungle</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C99" t="str">
-        <v>East Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D99" t="str">
-        <v>Larvesta</v>
+        <v>Gumshoos</v>
       </c>
       <c r="E99" t="str">
-        <v>35-40</v>
+        <v>43-48</v>
       </c>
       <c r="F99" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="100">
       <c r="A100">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B100" t="str">
-        <v>Lush Jungle</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C100" t="str">
-        <v>East Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D100" t="str">
-        <v>Oranguru</v>
+        <v>Wingull</v>
       </c>
       <c r="E100" t="str">
-        <v>35-40</v>
+        <v>43-48</v>
       </c>
       <c r="F100" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="101">
       <c r="A101">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B101" t="str">
-        <v>Lush Jungle</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C101" t="str">
-        <v>East Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D101" t="str">
-        <v>Passimian</v>
+        <v>Magikarp</v>
       </c>
       <c r="E101" t="str">
-        <v>35-40</v>
+        <v>43-48</v>
       </c>
       <c r="F101" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="102">
@@ -2426,219 +2426,219 @@
         <v>26</v>
       </c>
       <c r="B102" t="str">
-        <v>Captain Mallow</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C102" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D102" t="str">
-        <v>Boss</v>
+        <v>Stufful</v>
       </c>
       <c r="E102" t="str">
-        <v>36-41</v>
+        <v>43-48</v>
       </c>
       <c r="F102" t="str">
-        <v>-</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="103">
       <c r="A103">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B103" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C103" t="str">
         <v>Main Area</v>
       </c>
       <c r="D103" t="str">
-        <v>Zubat</v>
+        <v>Chinchou</v>
       </c>
       <c r="E103" t="str">
-        <v>38-43</v>
+        <v>43-48</v>
       </c>
       <c r="F103" t="str">
-        <v>25.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="104">
       <c r="A104">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B104" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C104" t="str">
         <v>Main Area</v>
       </c>
       <c r="D104" t="str">
-        <v>Alolan Diglett</v>
+        <v>Alolan Raticate</v>
       </c>
       <c r="E104" t="str">
-        <v>38-43</v>
+        <v>43-48</v>
       </c>
       <c r="F104" t="str">
-        <v>25.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="105">
       <c r="A105">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B105" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C105" t="str">
         <v>Main Area</v>
       </c>
       <c r="D105" t="str">
-        <v>Kecleon</v>
+        <v>Natu</v>
       </c>
       <c r="E105" t="str">
-        <v>38-43</v>
+        <v>43-48</v>
       </c>
       <c r="F105" t="str">
-        <v>25.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="106">
       <c r="A106">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B106" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C106" t="str">
         <v>Main Area</v>
       </c>
       <c r="D106" t="str">
-        <v>Larvitar</v>
+        <v>Nosepass</v>
       </c>
       <c r="E106" t="str">
-        <v>38-43</v>
+        <v>43-48</v>
       </c>
       <c r="F106" t="str">
-        <v>25.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="107">
       <c r="A107">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B107" t="str">
-        <v>Memorial Hill</v>
+        <v>Kahuna Olivia</v>
       </c>
       <c r="C107" t="str">
-        <v>Main</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D107" t="str">
-        <v>Phantump</v>
+        <v>Boss</v>
       </c>
       <c r="E107" t="str">
-        <v>42-47</v>
+        <v>44-49</v>
       </c>
       <c r="F107" t="str">
-        <v>100.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="108">
       <c r="A108">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B108" t="str">
-        <v>Akala Outskirts</v>
+        <v>Malie City</v>
       </c>
       <c r="C108" t="str">
-        <v>Main Area</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D108" t="str">
-        <v>Gumshoos</v>
+        <v>Magnemite</v>
       </c>
       <c r="E108" t="str">
-        <v>43-48</v>
+        <v>47-52</v>
       </c>
       <c r="F108" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="109">
       <c r="A109">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B109" t="str">
-        <v>Akala Outskirts</v>
+        <v>Malie City</v>
       </c>
       <c r="C109" t="str">
-        <v>Main Area</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D109" t="str">
-        <v>Wingull</v>
+        <v>Alolan Grimer</v>
       </c>
       <c r="E109" t="str">
-        <v>43-48</v>
+        <v>47-52</v>
       </c>
       <c r="F109" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="110">
       <c r="A110">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B110" t="str">
-        <v>Akala Outskirts</v>
+        <v>Malie City</v>
       </c>
       <c r="C110" t="str">
-        <v>Main Area</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D110" t="str">
-        <v>Magikarp</v>
+        <v>Trubbish</v>
       </c>
       <c r="E110" t="str">
-        <v>43-48</v>
+        <v>47-52</v>
       </c>
       <c r="F110" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="111">
       <c r="A111">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B111" t="str">
-        <v>Akala Outskirts</v>
+        <v>Malie City</v>
       </c>
       <c r="C111" t="str">
-        <v>Main Area</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D111" t="str">
-        <v>Stufful</v>
+        <v>Minccino</v>
       </c>
       <c r="E111" t="str">
-        <v>43-48</v>
+        <v>47-52</v>
       </c>
       <c r="F111" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="112">
       <c r="A112">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B112" t="str">
-        <v>Akala Outskirts</v>
+        <v>Malie City</v>
       </c>
       <c r="C112" t="str">
-        <v>Main Area</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D112" t="str">
-        <v>Chinchou</v>
+        <v>Masquerain</v>
       </c>
       <c r="E112" t="str">
-        <v>43-48</v>
+        <v>47-52</v>
       </c>
       <c r="F112" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="113">
@@ -2646,19 +2646,19 @@
         <v>29</v>
       </c>
       <c r="B113" t="str">
-        <v>Akala Outskirts</v>
+        <v>Route 10</v>
       </c>
       <c r="C113" t="str">
         <v>Main Area</v>
       </c>
       <c r="D113" t="str">
-        <v>Alolan Raticate</v>
+        <v>Ledian</v>
       </c>
       <c r="E113" t="str">
-        <v>43-48</v>
+        <v>50-55</v>
       </c>
       <c r="F113" t="str">
-        <v>12.50%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="114">
@@ -2666,19 +2666,19 @@
         <v>29</v>
       </c>
       <c r="B114" t="str">
-        <v>Akala Outskirts</v>
+        <v>Route 10</v>
       </c>
       <c r="C114" t="str">
         <v>Main Area</v>
       </c>
       <c r="D114" t="str">
-        <v>Natu</v>
+        <v>Ariados</v>
       </c>
       <c r="E114" t="str">
-        <v>43-48</v>
+        <v>50-55</v>
       </c>
       <c r="F114" t="str">
-        <v>12.50%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="115">
@@ -2686,179 +2686,179 @@
         <v>29</v>
       </c>
       <c r="B115" t="str">
-        <v>Akala Outskirts</v>
+        <v>Route 10</v>
       </c>
       <c r="C115" t="str">
         <v>Main Area</v>
       </c>
       <c r="D115" t="str">
-        <v>Nosepass</v>
+        <v>Crabrawler</v>
       </c>
       <c r="E115" t="str">
-        <v>43-48</v>
+        <v>50-55</v>
       </c>
       <c r="F115" t="str">
-        <v>12.50%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="116">
       <c r="A116">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B116" t="str">
-        <v>Kahuna Olivia</v>
+        <v>Route 10</v>
       </c>
       <c r="C116" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D116" t="str">
-        <v>Boss</v>
+        <v>Fearow</v>
       </c>
       <c r="E116" t="str">
-        <v>44-49</v>
+        <v>50-55</v>
       </c>
       <c r="F116" t="str">
-        <v>-</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="117">
       <c r="A117">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B117" t="str">
-        <v>Malie City</v>
+        <v>Route 10</v>
       </c>
       <c r="C117" t="str">
-        <v>Outer Cape</v>
+        <v>Main Area</v>
       </c>
       <c r="D117" t="str">
-        <v>Magnemite</v>
+        <v>Skarmory</v>
       </c>
       <c r="E117" t="str">
-        <v>47-52</v>
+        <v>50-55</v>
       </c>
       <c r="F117" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="118">
       <c r="A118">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B118" t="str">
-        <v>Malie City</v>
+        <v>Route 10</v>
       </c>
       <c r="C118" t="str">
-        <v>Outer Cape</v>
+        <v>Main Area</v>
       </c>
       <c r="D118" t="str">
-        <v>Alolan Grimer</v>
+        <v>Pancham</v>
       </c>
       <c r="E118" t="str">
-        <v>47-52</v>
+        <v>50-55</v>
       </c>
       <c r="F118" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="119">
       <c r="A119">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B119" t="str">
-        <v>Malie City</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C119" t="str">
-        <v>Outer Cape</v>
+        <v>East</v>
       </c>
       <c r="D119" t="str">
-        <v>Trubbish</v>
+        <v>Cleffa</v>
       </c>
       <c r="E119" t="str">
-        <v>47-52</v>
+        <v>52-57</v>
       </c>
       <c r="F119" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="120">
       <c r="A120">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B120" t="str">
-        <v>Malie City</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C120" t="str">
-        <v>Outer Cape</v>
+        <v>East</v>
       </c>
       <c r="D120" t="str">
-        <v>Minccino</v>
+        <v>Elgyem</v>
       </c>
       <c r="E120" t="str">
-        <v>47-52</v>
+        <v>52-57</v>
       </c>
       <c r="F120" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="121">
       <c r="A121">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B121" t="str">
-        <v>Malie City</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C121" t="str">
-        <v>Outer Cape</v>
+        <v>East</v>
       </c>
       <c r="D121" t="str">
-        <v>Masquerain</v>
+        <v>Beldum</v>
       </c>
       <c r="E121" t="str">
-        <v>47-52</v>
+        <v>52-57</v>
       </c>
       <c r="F121" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="122">
       <c r="A122">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B122" t="str">
-        <v>Route 10</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C122" t="str">
-        <v>Main Area</v>
+        <v>East</v>
       </c>
       <c r="D122" t="str">
-        <v>Ledian</v>
+        <v>Minior</v>
       </c>
       <c r="E122" t="str">
-        <v>50-55</v>
+        <v>52-57</v>
       </c>
       <c r="F122" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="123">
       <c r="A123">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B123" t="str">
-        <v>Route 10</v>
+        <v>Captain Sophocles</v>
       </c>
       <c r="C123" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D123" t="str">
-        <v>Ariados</v>
+        <v>Boss</v>
       </c>
       <c r="E123" t="str">
-        <v>50-55</v>
+        <v>53-58</v>
       </c>
       <c r="F123" t="str">
-        <v>16.67%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="124">
@@ -2866,19 +2866,19 @@
         <v>32</v>
       </c>
       <c r="B124" t="str">
-        <v>Route 10</v>
+        <v>Route 11</v>
       </c>
       <c r="C124" t="str">
         <v>Main Area</v>
       </c>
       <c r="D124" t="str">
-        <v>Crabrawler</v>
+        <v>Shiinotic</v>
       </c>
       <c r="E124" t="str">
-        <v>50-55</v>
+        <v>55-60</v>
       </c>
       <c r="F124" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="125">
@@ -2886,19 +2886,19 @@
         <v>32</v>
       </c>
       <c r="B125" t="str">
-        <v>Route 10</v>
+        <v>Route 11</v>
       </c>
       <c r="C125" t="str">
         <v>Main Area</v>
       </c>
       <c r="D125" t="str">
-        <v>Fearow</v>
+        <v>Parasect</v>
       </c>
       <c r="E125" t="str">
-        <v>50-55</v>
+        <v>55-60</v>
       </c>
       <c r="F125" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="126">
@@ -2906,19 +2906,19 @@
         <v>32</v>
       </c>
       <c r="B126" t="str">
-        <v>Route 10</v>
+        <v>Route 11</v>
       </c>
       <c r="C126" t="str">
         <v>Main Area</v>
       </c>
       <c r="D126" t="str">
-        <v>Skarmory</v>
+        <v>Komala</v>
       </c>
       <c r="E126" t="str">
-        <v>50-55</v>
+        <v>55-60</v>
       </c>
       <c r="F126" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="127">
@@ -2926,419 +2926,419 @@
         <v>32</v>
       </c>
       <c r="B127" t="str">
-        <v>Route 10</v>
+        <v>Route 11</v>
       </c>
       <c r="C127" t="str">
         <v>Main Area</v>
       </c>
       <c r="D127" t="str">
-        <v>Pancham</v>
+        <v>Houndoom</v>
       </c>
       <c r="E127" t="str">
-        <v>50-55</v>
+        <v>55-60</v>
       </c>
       <c r="F127" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="128">
       <c r="A128">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B128" t="str">
-        <v>Mount Hokulani</v>
+        <v>Route 11</v>
       </c>
       <c r="C128" t="str">
-        <v>East</v>
+        <v>Main Area</v>
       </c>
       <c r="D128" t="str">
-        <v>Cleffa</v>
+        <v>Manectric</v>
       </c>
       <c r="E128" t="str">
-        <v>51-56</v>
+        <v>55-60</v>
       </c>
       <c r="F128" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="129">
       <c r="A129">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B129" t="str">
-        <v>Mount Hokulani</v>
+        <v>Route 11</v>
       </c>
       <c r="C129" t="str">
-        <v>East</v>
+        <v>Main Area</v>
       </c>
       <c r="D129" t="str">
-        <v>Elgyem</v>
+        <v>Scraggy</v>
       </c>
       <c r="E129" t="str">
-        <v>51-56</v>
+        <v>55-60</v>
       </c>
       <c r="F129" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="130">
       <c r="A130">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B130" t="str">
-        <v>Mount Hokulani</v>
+        <v>Route 11</v>
       </c>
       <c r="C130" t="str">
-        <v>East</v>
+        <v>Main Area</v>
       </c>
       <c r="D130" t="str">
-        <v>Beldum</v>
+        <v>Bisharp</v>
       </c>
       <c r="E130" t="str">
-        <v>51-56</v>
+        <v>55-60</v>
       </c>
       <c r="F130" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="131">
       <c r="A131">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B131" t="str">
-        <v>Mount Hokulani</v>
+        <v>Route 11</v>
       </c>
       <c r="C131" t="str">
-        <v>East</v>
+        <v>Main Area</v>
       </c>
       <c r="D131" t="str">
-        <v>Minior</v>
+        <v>Machop</v>
       </c>
       <c r="E131" t="str">
-        <v>51-56</v>
+        <v>55-60</v>
       </c>
       <c r="F131" t="str">
-        <v>25.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="132">
       <c r="A132">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B132" t="str">
-        <v>Captain Sophocles</v>
+        <v>Route 11</v>
       </c>
       <c r="C132" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D132" t="str">
-        <v>Boss</v>
+        <v>Hawlucha</v>
       </c>
       <c r="E132" t="str">
-        <v>53-58</v>
+        <v>55-60</v>
       </c>
       <c r="F132" t="str">
-        <v>-</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="133">
       <c r="A133">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B133" t="str">
-        <v>Route 11</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C133" t="str">
         <v>Main Area</v>
       </c>
       <c r="D133" t="str">
-        <v>Shiinotic</v>
+        <v>Alolan Dugtrio</v>
       </c>
       <c r="E133" t="str">
-        <v>54-59</v>
+        <v>58-63</v>
       </c>
       <c r="F133" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="134">
       <c r="A134">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B134" t="str">
-        <v>Route 11</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C134" t="str">
         <v>Main Area</v>
       </c>
       <c r="D134" t="str">
-        <v>Parasect</v>
+        <v>Sandile</v>
       </c>
       <c r="E134" t="str">
-        <v>54-59</v>
+        <v>58-63</v>
       </c>
       <c r="F134" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="135">
       <c r="A135">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B135" t="str">
-        <v>Route 11</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C135" t="str">
         <v>Main Area</v>
       </c>
       <c r="D135" t="str">
-        <v>Komala</v>
+        <v>Krokorok</v>
       </c>
       <c r="E135" t="str">
-        <v>54-59</v>
+        <v>58-63</v>
       </c>
       <c r="F135" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="136">
       <c r="A136">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B136" t="str">
-        <v>Route 11</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C136" t="str">
         <v>Main Area</v>
       </c>
       <c r="D136" t="str">
-        <v>Houndoom</v>
+        <v>Staryu</v>
       </c>
       <c r="E136" t="str">
-        <v>54-59</v>
+        <v>58-63</v>
       </c>
       <c r="F136" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="137">
       <c r="A137">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B137" t="str">
-        <v>Route 11</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C137" t="str">
         <v>Main Area</v>
       </c>
       <c r="D137" t="str">
-        <v>Manectric</v>
+        <v>Sandygast</v>
       </c>
       <c r="E137" t="str">
-        <v>54-59</v>
+        <v>58-63</v>
       </c>
       <c r="F137" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="138">
       <c r="A138">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B138" t="str">
-        <v>Route 11</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C138" t="str">
         <v>Main Area</v>
       </c>
       <c r="D138" t="str">
-        <v>Scraggy</v>
+        <v>Graveler</v>
       </c>
       <c r="E138" t="str">
-        <v>54-59</v>
+        <v>59-64</v>
       </c>
       <c r="F138" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="139">
       <c r="A139">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B139" t="str">
-        <v>Route 11</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C139" t="str">
         <v>Main Area</v>
       </c>
       <c r="D139" t="str">
-        <v>Bisharp</v>
+        <v>Bruxish</v>
       </c>
       <c r="E139" t="str">
-        <v>54-59</v>
+        <v>59-64</v>
       </c>
       <c r="F139" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="140">
       <c r="A140">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B140" t="str">
-        <v>Route 11</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C140" t="str">
         <v>Main Area</v>
       </c>
       <c r="D140" t="str">
-        <v>Machop</v>
+        <v>Absol</v>
       </c>
       <c r="E140" t="str">
-        <v>54-59</v>
+        <v>59-64</v>
       </c>
       <c r="F140" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="141">
       <c r="A141">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B141" t="str">
-        <v>Route 11</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C141" t="str">
         <v>Main Area</v>
       </c>
       <c r="D141" t="str">
-        <v>Hawlucha</v>
+        <v>Snorunt</v>
       </c>
       <c r="E141" t="str">
-        <v>54-59</v>
+        <v>59-64</v>
       </c>
       <c r="F141" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="142">
       <c r="A142">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B142" t="str">
-        <v>Blush Mountain</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C142" t="str">
         <v>Main Area</v>
       </c>
       <c r="D142" t="str">
-        <v>Mudbray</v>
+        <v>Alolan Sandshrew</v>
       </c>
       <c r="E142" t="str">
-        <v>57-62</v>
+        <v>59-64</v>
       </c>
       <c r="F142" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="143">
       <c r="A143">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B143" t="str">
-        <v>Blush Mountain</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C143" t="str">
         <v>Main Area</v>
       </c>
       <c r="D143" t="str">
-        <v>Torkoal</v>
+        <v>Alolan Vulpix</v>
       </c>
       <c r="E143" t="str">
-        <v>57-62</v>
+        <v>59-64</v>
       </c>
       <c r="F143" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="144">
       <c r="A144">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B144" t="str">
-        <v>Blush Mountain</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C144" t="str">
-        <v>Main Area</v>
+        <v>Abandoned Site</v>
       </c>
       <c r="D144" t="str">
-        <v>Togedemaru</v>
+        <v>Haunter</v>
       </c>
       <c r="E144" t="str">
-        <v>57-62</v>
+        <v>62-67</v>
       </c>
       <c r="F144" t="str">
-        <v>11.11%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="145">
       <c r="A145">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B145" t="str">
-        <v>Blush Mountain</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C145" t="str">
-        <v>Main Area</v>
+        <v>Abandoned Site</v>
       </c>
       <c r="D145" t="str">
-        <v>Elekid</v>
+        <v>Klefki</v>
       </c>
       <c r="E145" t="str">
-        <v>57-62</v>
+        <v>62-67</v>
       </c>
       <c r="F145" t="str">
-        <v>11.11%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="146">
       <c r="A146">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B146" t="str">
-        <v>Blush Mountain</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C146" t="str">
-        <v>Main Area</v>
+        <v>Abandoned Site</v>
       </c>
       <c r="D146" t="str">
-        <v>Alolan Geodude</v>
+        <v>Shuppet</v>
       </c>
       <c r="E146" t="str">
-        <v>57-62</v>
+        <v>62-67</v>
       </c>
       <c r="F146" t="str">
-        <v>11.11%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="147">
       <c r="A147">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B147" t="str">
-        <v>Blush Mountain</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C147" t="str">
-        <v>Main Area</v>
+        <v>Abandoned Site</v>
       </c>
       <c r="D147" t="str">
-        <v>Alolan Graveler</v>
+        <v>Boldore</v>
       </c>
       <c r="E147" t="str">
-        <v>57-62</v>
+        <v>62-67</v>
       </c>
       <c r="F147" t="str">
-        <v>11.11%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="148">
@@ -3346,116 +3346,116 @@
         <v>36</v>
       </c>
       <c r="B148" t="str">
-        <v>Blush Mountain</v>
+        <v>Captain Acerola</v>
       </c>
       <c r="C148" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D148" t="str">
-        <v>Charjabug</v>
+        <v>Boss</v>
       </c>
       <c r="E148" t="str">
-        <v>57-62</v>
+        <v>64-69</v>
       </c>
       <c r="F148" t="str">
-        <v>11.11%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="149">
       <c r="A149">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B149" t="str">
-        <v>Blush Mountain</v>
+        <v>Kahuna Nanu</v>
       </c>
       <c r="C149" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D149" t="str">
-        <v>Turtonator</v>
+        <v>Boss</v>
       </c>
       <c r="E149" t="str">
-        <v>57-62</v>
+        <v>68-73</v>
       </c>
       <c r="F149" t="str">
-        <v>11.11%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="150">
       <c r="A150">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B150" t="str">
-        <v>Blush Mountain</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C150" t="str">
-        <v>Main Area</v>
+        <v>Main</v>
       </c>
       <c r="D150" t="str">
-        <v>Dedenne</v>
+        <v>Steenee</v>
       </c>
       <c r="E150" t="str">
-        <v>57-62</v>
+        <v>69-74</v>
       </c>
       <c r="F150" t="str">
-        <v>11.11%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="151">
       <c r="A151">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B151" t="str">
-        <v>Haina Desert</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C151" t="str">
-        <v>Main Area</v>
+        <v>Main</v>
       </c>
       <c r="D151" t="str">
-        <v>Alolan Dugtrio</v>
+        <v>Shellos</v>
       </c>
       <c r="E151" t="str">
-        <v>58-63</v>
+        <v>69-74</v>
       </c>
       <c r="F151" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="152">
       <c r="A152">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B152" t="str">
-        <v>Haina Desert</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C152" t="str">
-        <v>Main Area</v>
+        <v>Main</v>
       </c>
       <c r="D152" t="str">
-        <v>Sandile</v>
+        <v>Dhelmise</v>
       </c>
       <c r="E152" t="str">
-        <v>58-63</v>
+        <v>69-74</v>
       </c>
       <c r="F152" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="153">
       <c r="A153">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B153" t="str">
-        <v>Haina Desert</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C153" t="str">
         <v>Main Area</v>
       </c>
       <c r="D153" t="str">
-        <v>Krokorok</v>
+        <v>Tentacruel</v>
       </c>
       <c r="E153" t="str">
-        <v>58-63</v>
+        <v>71-76</v>
       </c>
       <c r="F153" t="str">
         <v>20.00%</v>
@@ -3463,19 +3463,19 @@
     </row>
     <row r="154">
       <c r="A154">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B154" t="str">
-        <v>Haina Desert</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C154" t="str">
         <v>Main Area</v>
       </c>
       <c r="D154" t="str">
-        <v>Staryu</v>
+        <v>Lumineon</v>
       </c>
       <c r="E154" t="str">
-        <v>58-63</v>
+        <v>71-76</v>
       </c>
       <c r="F154" t="str">
         <v>20.00%</v>
@@ -3483,19 +3483,19 @@
     </row>
     <row r="155">
       <c r="A155">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B155" t="str">
-        <v>Haina Desert</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C155" t="str">
         <v>Main Area</v>
       </c>
       <c r="D155" t="str">
-        <v>Sandygast</v>
+        <v>Lapras</v>
       </c>
       <c r="E155" t="str">
-        <v>58-63</v>
+        <v>71-76</v>
       </c>
       <c r="F155" t="str">
         <v>20.00%</v>
@@ -3503,222 +3503,222 @@
     </row>
     <row r="156">
       <c r="A156">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B156" t="str">
-        <v>Tapu Village</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C156" t="str">
         <v>Main Area</v>
       </c>
       <c r="D156" t="str">
-        <v>Graveler</v>
+        <v>Noivern</v>
       </c>
       <c r="E156" t="str">
-        <v>59-64</v>
+        <v>71-76</v>
       </c>
       <c r="F156" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="157">
       <c r="A157">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B157" t="str">
-        <v>Tapu Village</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C157" t="str">
         <v>Main Area</v>
       </c>
       <c r="D157" t="str">
-        <v>Bruxish</v>
+        <v>Druddigon</v>
       </c>
       <c r="E157" t="str">
-        <v>59-64</v>
+        <v>71-76</v>
       </c>
       <c r="F157" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="158">
       <c r="A158">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B158" t="str">
-        <v>Tapu Village</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C158" t="str">
         <v>Main Area</v>
       </c>
       <c r="D158" t="str">
-        <v>Absol</v>
+        <v>Wimpod</v>
       </c>
       <c r="E158" t="str">
-        <v>59-64</v>
+        <v>72-77</v>
       </c>
       <c r="F158" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="159">
       <c r="A159">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B159" t="str">
-        <v>Tapu Village</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C159" t="str">
         <v>Main Area</v>
       </c>
       <c r="D159" t="str">
-        <v>Snorunt</v>
+        <v>Relicanth</v>
       </c>
       <c r="E159" t="str">
-        <v>59-64</v>
+        <v>72-77</v>
       </c>
       <c r="F159" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="160">
       <c r="A160">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B160" t="str">
-        <v>Tapu Village</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C160" t="str">
         <v>Main Area</v>
       </c>
       <c r="D160" t="str">
-        <v>Alolan Sandshrew</v>
+        <v>Wailmer</v>
       </c>
       <c r="E160" t="str">
-        <v>59-64</v>
+        <v>72-77</v>
       </c>
       <c r="F160" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="161">
       <c r="A161">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B161" t="str">
-        <v>Tapu Village</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C161" t="str">
         <v>Main Area</v>
       </c>
       <c r="D161" t="str">
-        <v>Alolan Vulpix</v>
+        <v>Carvanha</v>
       </c>
       <c r="E161" t="str">
-        <v>59-64</v>
+        <v>72-77</v>
       </c>
       <c r="F161" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="162">
       <c r="A162">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B162" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C162" t="str">
-        <v>Abandoned Site</v>
+        <v>Main Area</v>
       </c>
       <c r="D162" t="str">
-        <v>Haunter</v>
+        <v>Sharpedo</v>
       </c>
       <c r="E162" t="str">
-        <v>62-67</v>
+        <v>72-77</v>
       </c>
       <c r="F162" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="163">
       <c r="A163">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B163" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C163" t="str">
-        <v>Abandoned Site</v>
+        <v>Main Area</v>
       </c>
       <c r="D163" t="str">
-        <v>Klefki</v>
+        <v>Pelipper</v>
       </c>
       <c r="E163" t="str">
-        <v>62-67</v>
+        <v>74-79</v>
       </c>
       <c r="F163" t="str">
-        <v>25.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="164">
       <c r="A164">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B164" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C164" t="str">
-        <v>Abandoned Site</v>
+        <v>Main Area</v>
       </c>
       <c r="D164" t="str">
-        <v>Shuppet</v>
+        <v>Pinsir</v>
       </c>
       <c r="E164" t="str">
-        <v>62-67</v>
+        <v>74-79</v>
       </c>
       <c r="F164" t="str">
-        <v>25.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="165">
       <c r="A165">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B165" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C165" t="str">
-        <v>Abandoned Site</v>
+        <v>Main Area</v>
       </c>
       <c r="D165" t="str">
-        <v>Boldore</v>
+        <v>Gastrodon</v>
       </c>
       <c r="E165" t="str">
-        <v>62-67</v>
+        <v>74-79</v>
       </c>
       <c r="F165" t="str">
-        <v>25.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="166">
       <c r="A166">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B166" t="str">
-        <v>Captain Acerola</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C166" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D166" t="str">
-        <v>Boss</v>
+        <v>Exeggcute</v>
       </c>
       <c r="E166" t="str">
-        <v>64-69</v>
+        <v>74-79</v>
       </c>
       <c r="F166" t="str">
-        <v>-</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="167">
@@ -3726,39 +3726,39 @@
         <v>41</v>
       </c>
       <c r="B167" t="str">
-        <v>Kahuna Nanu</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C167" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D167" t="str">
-        <v>Boss</v>
+        <v>Tropius</v>
       </c>
       <c r="E167" t="str">
-        <v>69-74</v>
+        <v>74-79</v>
       </c>
       <c r="F167" t="str">
-        <v>-</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="168">
       <c r="A168">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B168" t="str">
-        <v>Seafolk Village</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C168" t="str">
-        <v>Main</v>
+        <v>Main Area</v>
       </c>
       <c r="D168" t="str">
-        <v>Steenee</v>
+        <v>Alolan Exeggutor</v>
       </c>
       <c r="E168" t="str">
-        <v>70-75</v>
+        <v>74-79</v>
       </c>
       <c r="F168" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="169">
@@ -3766,16 +3766,16 @@
         <v>42</v>
       </c>
       <c r="B169" t="str">
-        <v>Seafolk Village</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C169" t="str">
-        <v>Main</v>
+        <v>Outside</v>
       </c>
       <c r="D169" t="str">
-        <v>Shellos</v>
+        <v>Machoke</v>
       </c>
       <c r="E169" t="str">
-        <v>70-75</v>
+        <v>75-80</v>
       </c>
       <c r="F169" t="str">
         <v>33.33%</v>
@@ -3786,16 +3786,16 @@
         <v>42</v>
       </c>
       <c r="B170" t="str">
-        <v>Seafolk Village</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C170" t="str">
-        <v>Main</v>
+        <v>Outside</v>
       </c>
       <c r="D170" t="str">
-        <v>Dhelmise</v>
+        <v>Mienfoo</v>
       </c>
       <c r="E170" t="str">
-        <v>70-75</v>
+        <v>75-80</v>
       </c>
       <c r="F170" t="str">
         <v>33.33%</v>
@@ -3803,22 +3803,22 @@
     </row>
     <row r="171">
       <c r="A171">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B171" t="str">
-        <v>Poni Wilds</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C171" t="str">
-        <v>Main Area</v>
+        <v>Outside</v>
       </c>
       <c r="D171" t="str">
-        <v>Tentacruel</v>
+        <v>Jangmo-o</v>
       </c>
       <c r="E171" t="str">
-        <v>72-77</v>
+        <v>75-80</v>
       </c>
       <c r="F171" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="172">
@@ -3826,356 +3826,356 @@
         <v>43</v>
       </c>
       <c r="B172" t="str">
-        <v>Poni Wilds</v>
+        <v>Captain Kommo-o</v>
       </c>
       <c r="C172" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D172" t="str">
-        <v>Lumineon</v>
+        <v>Boss</v>
       </c>
       <c r="E172" t="str">
-        <v>72-77</v>
+        <v>78-83</v>
       </c>
       <c r="F172" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="173">
       <c r="A173">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B173" t="str">
-        <v>Poni Wilds</v>
+        <v>Captain Mina</v>
       </c>
       <c r="C173" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D173" t="str">
-        <v>Lapras</v>
+        <v>Boss</v>
       </c>
       <c r="E173" t="str">
-        <v>72-77</v>
+        <v>80-85</v>
       </c>
       <c r="F173" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="174">
       <c r="A174">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B174" t="str">
-        <v>Poni Wilds</v>
+        <v>Kahuna Hapu</v>
       </c>
       <c r="C174" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D174" t="str">
-        <v>Noivern</v>
+        <v>Boss</v>
       </c>
       <c r="E174" t="str">
-        <v>72-77</v>
+        <v>81-86</v>
       </c>
       <c r="F174" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="175">
       <c r="A175">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B175" t="str">
-        <v>Poni Wilds</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C175" t="str">
-        <v>Main Area</v>
+        <v>Cave</v>
       </c>
       <c r="D175" t="str">
-        <v>Druddigon</v>
+        <v>Drampa</v>
       </c>
       <c r="E175" t="str">
-        <v>72-77</v>
+        <v>83-88</v>
       </c>
       <c r="F175" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="176">
       <c r="A176">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B176" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C176" t="str">
-        <v>Main Area</v>
+        <v>Cave</v>
       </c>
       <c r="D176" t="str">
-        <v>Wimpod</v>
+        <v>Glalie</v>
       </c>
       <c r="E176" t="str">
-        <v>73-78</v>
+        <v>83-88</v>
       </c>
       <c r="F176" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="177">
       <c r="A177">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B177" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C177" t="str">
-        <v>Main Area</v>
+        <v>Cave</v>
       </c>
       <c r="D177" t="str">
-        <v>Relicanth</v>
+        <v>Sneasel</v>
       </c>
       <c r="E177" t="str">
-        <v>73-78</v>
+        <v>83-88</v>
       </c>
       <c r="F177" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="178">
       <c r="A178">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B178" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C178" t="str">
-        <v>Main Area</v>
+        <v>Cave</v>
       </c>
       <c r="D178" t="str">
-        <v>Wailmer</v>
+        <v>Crabominable</v>
       </c>
       <c r="E178" t="str">
-        <v>73-78</v>
+        <v>83-88</v>
       </c>
       <c r="F178" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="179">
       <c r="A179">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B179" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Alola Pokemon League</v>
       </c>
       <c r="C179" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D179" t="str">
-        <v>Carvanha</v>
+        <v>Boss</v>
       </c>
       <c r="E179" t="str">
-        <v>73-78</v>
+        <v>84-89</v>
       </c>
       <c r="F179" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="180">
       <c r="A180">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B180" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Champion Hau</v>
       </c>
       <c r="C180" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D180" t="str">
-        <v>Sharpedo</v>
+        <v>Boss</v>
       </c>
       <c r="E180" t="str">
-        <v>73-78</v>
+        <v>85-90</v>
       </c>
       <c r="F180" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="181">
       <c r="A181">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B181" t="str">
-        <v>Exeggutor Island</v>
+        <v>Route 6</v>
       </c>
       <c r="C181" t="str">
         <v>Main Area</v>
       </c>
       <c r="D181" t="str">
-        <v>Pelipper</v>
+        <v>Special Encounter</v>
       </c>
       <c r="E181" t="str">
-        <v>75-80</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F181" t="str">
-        <v>16.67%</v>
+        <v>100%</v>
       </c>
     </row>
     <row r="182">
       <c r="A182">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B182" t="str">
-        <v>Exeggutor Island</v>
+        <v>Royal Avenue</v>
       </c>
       <c r="C182" t="str">
         <v>Main Area</v>
       </c>
       <c r="D182" t="str">
-        <v>Pinsir</v>
+        <v>Oricorio</v>
       </c>
       <c r="E182" t="str">
-        <v>75-80</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F182" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="183">
       <c r="A183">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B183" t="str">
-        <v>Exeggutor Island</v>
+        <v>Royal Avenue</v>
       </c>
       <c r="C183" t="str">
         <v>Main Area</v>
       </c>
       <c r="D183" t="str">
-        <v>Gastrodon</v>
+        <v>Trumbeak</v>
       </c>
       <c r="E183" t="str">
-        <v>75-80</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F183" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="184">
       <c r="A184">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B184" t="str">
-        <v>Exeggutor Island</v>
+        <v>Royal Avenue</v>
       </c>
       <c r="C184" t="str">
         <v>Main Area</v>
       </c>
       <c r="D184" t="str">
-        <v>Exeggcute</v>
+        <v>Ribombee</v>
       </c>
       <c r="E184" t="str">
-        <v>75-80</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F184" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="185">
       <c r="A185">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B185" t="str">
-        <v>Exeggutor Island</v>
+        <v>Pikachu Valley</v>
       </c>
       <c r="C185" t="str">
         <v>Main Area</v>
       </c>
       <c r="D185" t="str">
-        <v>Tropius</v>
+        <v>Pikachu</v>
       </c>
       <c r="E185" t="str">
-        <v>75-80</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F185" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="186">
       <c r="A186">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B186" t="str">
-        <v>Exeggutor Island</v>
+        <v>Pikachu Valley</v>
       </c>
       <c r="C186" t="str">
         <v>Main Area</v>
       </c>
       <c r="D186" t="str">
-        <v>Alolan Exeggutor</v>
+        <v>Alolan Raichu</v>
       </c>
       <c r="E186" t="str">
-        <v>75-80</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F186" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="187">
       <c r="A187">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B187" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Pikachu Valley</v>
       </c>
       <c r="C187" t="str">
-        <v>Outside</v>
+        <v>Main Area</v>
       </c>
       <c r="D187" t="str">
-        <v>Machoke</v>
+        <v>Pichu</v>
       </c>
       <c r="E187" t="str">
-        <v>76-81</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F187" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="188">
       <c r="A188">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B188" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Pikachu Valley</v>
       </c>
       <c r="C188" t="str">
-        <v>Outside</v>
+        <v>Main Area</v>
       </c>
       <c r="D188" t="str">
-        <v>Mienfoo</v>
+        <v>Magnemite</v>
       </c>
       <c r="E188" t="str">
-        <v>76-81</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F188" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="189">
       <c r="A189">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B189" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Heahea Surf Spot</v>
       </c>
       <c r="C189" t="str">
-        <v>Outside</v>
+        <v>Main Area</v>
       </c>
       <c r="D189" t="str">
-        <v>Jangmo-o</v>
+        <v>Mantine</v>
       </c>
       <c r="E189" t="str">
-        <v>76-81</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F189" t="str">
         <v>33.33%</v>
@@ -4183,282 +4183,282 @@
     </row>
     <row r="190">
       <c r="A190">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B190" t="str">
-        <v>Captain Kommo-o</v>
+        <v>Heahea Surf Spot</v>
       </c>
       <c r="C190" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D190" t="str">
-        <v>Boss</v>
+        <v>Finneon</v>
       </c>
       <c r="E190" t="str">
-        <v>79-84</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F190" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="191">
       <c r="A191">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B191" t="str">
-        <v>Captain Mina</v>
+        <v>Heahea Surf Spot</v>
       </c>
       <c r="C191" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D191" t="str">
-        <v>Boss</v>
+        <v>Tentacool</v>
       </c>
       <c r="E191" t="str">
-        <v>80-85</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F191" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="192">
       <c r="A192">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B192" t="str">
-        <v>Kahuna Hapu</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C192" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D192" t="str">
-        <v>Boss</v>
+        <v>Rowlet</v>
       </c>
       <c r="E192" t="str">
-        <v>81-86</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F192" t="str">
-        <v>-</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="193">
       <c r="A193">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B193" t="str">
-        <v>Mount Lanakila</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C193" t="str">
-        <v>Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D193" t="str">
-        <v>Drampa</v>
+        <v>Dartrix</v>
       </c>
       <c r="E193" t="str">
-        <v>83-88</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F193" t="str">
-        <v>25.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="194">
       <c r="A194">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B194" t="str">
-        <v>Mount Lanakila</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C194" t="str">
-        <v>Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D194" t="str">
-        <v>Glalie</v>
+        <v>Litten</v>
       </c>
       <c r="E194" t="str">
-        <v>83-88</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F194" t="str">
-        <v>25.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="195">
       <c r="A195">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B195" t="str">
-        <v>Mount Lanakila</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C195" t="str">
-        <v>Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D195" t="str">
-        <v>Sneasel</v>
+        <v>Torracat</v>
       </c>
       <c r="E195" t="str">
-        <v>83-88</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F195" t="str">
-        <v>25.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="196">
       <c r="A196">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B196" t="str">
-        <v>Mount Lanakila</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C196" t="str">
-        <v>Cave</v>
+        <v>Main Area</v>
       </c>
       <c r="D196" t="str">
-        <v>Crabominable</v>
+        <v>Popplio</v>
       </c>
       <c r="E196" t="str">
-        <v>83-88</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F196" t="str">
-        <v>25.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="197">
       <c r="A197">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B197" t="str">
-        <v>Alola Pokemon League</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C197" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D197" t="str">
-        <v>Boss</v>
+        <v>Brionne</v>
       </c>
       <c r="E197" t="str">
-        <v>84-89</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F197" t="str">
-        <v>-</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="198">
       <c r="A198">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B198" t="str">
-        <v>Champion Hau</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C198" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D198" t="str">
-        <v>Boss</v>
+        <v>Mudbray</v>
       </c>
       <c r="E198" t="str">
-        <v>85-90</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F198" t="str">
-        <v>-</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="199">
       <c r="A199">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B199" t="str">
-        <v>Route 7</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C199" t="str">
         <v>Main Area</v>
       </c>
       <c r="D199" t="str">
-        <v>Staryu</v>
+        <v>Torkoal</v>
       </c>
       <c r="E199" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F199" t="str">
-        <v>20.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="200">
       <c r="A200">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B200" t="str">
-        <v>Route 7</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C200" t="str">
         <v>Main Area</v>
       </c>
       <c r="D200" t="str">
-        <v>Pyukumuku</v>
+        <v>Togedemaru</v>
       </c>
       <c r="E200" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F200" t="str">
-        <v>20.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="201">
       <c r="A201">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B201" t="str">
-        <v>Route 7</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C201" t="str">
         <v>Main Area</v>
       </c>
       <c r="D201" t="str">
-        <v>Corsola</v>
+        <v>Elekid</v>
       </c>
       <c r="E201" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F201" t="str">
-        <v>20.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="202">
       <c r="A202">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B202" t="str">
-        <v>Route 7</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C202" t="str">
         <v>Main Area</v>
       </c>
       <c r="D202" t="str">
-        <v>Mareanie</v>
+        <v>Alolan Geodude</v>
       </c>
       <c r="E202" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F202" t="str">
-        <v>20.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="203">
       <c r="A203">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B203" t="str">
-        <v>Route 7</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C203" t="str">
         <v>Main Area</v>
       </c>
       <c r="D203" t="str">
-        <v>Bruxish</v>
+        <v>Alolan Graveler</v>
       </c>
       <c r="E203" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F203" t="str">
-        <v>20.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="204">
@@ -4466,19 +4466,19 @@
         <v>54</v>
       </c>
       <c r="B204" t="str">
-        <v>Aether Paradise</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C204" t="str">
-        <v>Secret Lab</v>
+        <v>Main Area</v>
       </c>
       <c r="D204" t="str">
-        <v>Type: Null</v>
+        <v>Charjabug</v>
       </c>
       <c r="E204" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F204" t="str">
-        <v>33.33%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="205">
@@ -4486,19 +4486,19 @@
         <v>54</v>
       </c>
       <c r="B205" t="str">
-        <v>Aether Paradise</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C205" t="str">
-        <v>Secret Lab</v>
+        <v>Main Area</v>
       </c>
       <c r="D205" t="str">
-        <v>Ditto</v>
+        <v>Turtonator</v>
       </c>
       <c r="E205" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F205" t="str">
-        <v>33.33%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="206">
@@ -4506,19 +4506,19 @@
         <v>54</v>
       </c>
       <c r="B206" t="str">
-        <v>Aether Paradise</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C206" t="str">
-        <v>Secret Lab</v>
+        <v>Main Area</v>
       </c>
       <c r="D206" t="str">
-        <v>Porygon</v>
+        <v>Dedenne</v>
       </c>
       <c r="E206" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F206" t="str">
-        <v>33.33%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="207">
@@ -4526,59 +4526,59 @@
         <v>55</v>
       </c>
       <c r="B207" t="str">
-        <v>Memorial Hill</v>
+        <v>Ula'ula Meadow</v>
       </c>
       <c r="C207" t="str">
-        <v>Main</v>
+        <v>Main Area</v>
       </c>
       <c r="D207" t="str">
-        <v>Phantump</v>
+        <v>Ledian</v>
       </c>
       <c r="E207" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F207" t="str">
-        <v>100.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="208">
       <c r="A208">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B208" t="str">
-        <v>Sacred Shrine</v>
+        <v>Ula'ula Meadow</v>
       </c>
       <c r="C208" t="str">
         <v>Main Area</v>
       </c>
       <c r="D208" t="str">
-        <v>Tapu Koko</v>
+        <v>Ariados</v>
       </c>
       <c r="E208" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F208" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="209">
       <c r="A209">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B209" t="str">
-        <v>Sacred Shrine</v>
+        <v>Ula'ula Meadow</v>
       </c>
       <c r="C209" t="str">
         <v>Main Area</v>
       </c>
       <c r="D209" t="str">
-        <v>Tapu Lele</v>
+        <v>Oricorio</v>
       </c>
       <c r="E209" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F209" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="210">
@@ -4586,19 +4586,19 @@
         <v>56</v>
       </c>
       <c r="B210" t="str">
-        <v>Sacred Shrine</v>
+        <v>Lake of the Sunne</v>
       </c>
       <c r="C210" t="str">
         <v>Main Area</v>
       </c>
       <c r="D210" t="str">
-        <v>Tapu Bulu</v>
+        <v>Golbat</v>
       </c>
       <c r="E210" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F210" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="211">
@@ -4606,39 +4606,39 @@
         <v>56</v>
       </c>
       <c r="B211" t="str">
-        <v>Sacred Shrine</v>
+        <v>Lake of the Sunne</v>
       </c>
       <c r="C211" t="str">
         <v>Main Area</v>
       </c>
       <c r="D211" t="str">
-        <v>Tapu Fini</v>
+        <v>Gastly</v>
       </c>
       <c r="E211" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F211" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="212">
       <c r="A212">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B212" t="str">
-        <v>Obsidian Sphere</v>
+        <v>Lake of the Sunne</v>
       </c>
       <c r="C212" t="str">
         <v>Main Area</v>
       </c>
       <c r="D212" t="str">
-        <v>Cosmog</v>
+        <v>Haunter</v>
       </c>
       <c r="E212" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F212" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="213">
@@ -4652,7 +4652,7 @@
         <v>Main Area</v>
       </c>
       <c r="D213" t="str">
-        <v>Cosmoem</v>
+        <v>Cosmog</v>
       </c>
       <c r="E213" t="str">
         <v>NaN-NaN</v>
@@ -4672,7 +4672,7 @@
         <v>Main Area</v>
       </c>
       <c r="D214" t="str">
-        <v>Solgaleo</v>
+        <v>Cosmoem</v>
       </c>
       <c r="E214" t="str">
         <v>NaN-NaN</v>
@@ -4692,7 +4692,7 @@
         <v>Main Area</v>
       </c>
       <c r="D215" t="str">
-        <v>Lunala</v>
+        <v>Solgaleo</v>
       </c>
       <c r="E215" t="str">
         <v>NaN-NaN</v>
@@ -4712,7 +4712,7 @@
         <v>Main Area</v>
       </c>
       <c r="D216" t="str">
-        <v>Necrozma</v>
+        <v>Lunala</v>
       </c>
       <c r="E216" t="str">
         <v>NaN-NaN</v>
@@ -4723,16 +4723,16 @@
     </row>
     <row r="217">
       <c r="A217">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B217" t="str">
-        <v>Route 3</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C217" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D217" t="str">
-        <v>Mankey</v>
+        <v>Necrozma</v>
       </c>
       <c r="E217" t="str">
         <v>NaN-NaN</v>
@@ -4752,13 +4752,13 @@
         <v>North</v>
       </c>
       <c r="D218" t="str">
-        <v>Delibird</v>
+        <v>Mankey</v>
       </c>
       <c r="E218" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F218" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="219">
@@ -4772,13 +4772,13 @@
         <v>North</v>
       </c>
       <c r="D219" t="str">
-        <v>Bagon</v>
+        <v>Delibird</v>
       </c>
       <c r="E219" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F219" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="220">
@@ -4792,13 +4792,13 @@
         <v>North</v>
       </c>
       <c r="D220" t="str">
-        <v>Oricorio</v>
+        <v>Bagon</v>
       </c>
       <c r="E220" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F220" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="221">
@@ -4818,7 +4818,7 @@
         <v>NaN-NaN</v>
       </c>
       <c r="F221" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="222">
@@ -4826,19 +4826,19 @@
         <v>59</v>
       </c>
       <c r="B222" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Memorial Hill</v>
       </c>
       <c r="C222" t="str">
-        <v>Deepest Cave</v>
+        <v>Main</v>
       </c>
       <c r="D222" t="str">
-        <v>Marshadow</v>
+        <v>Special Encounter</v>
       </c>
       <c r="E222" t="str">
         <v>NaN-NaN</v>
       </c>
       <c r="F222" t="str">
-        <v>100.00%</v>
+        <v>100%</v>
       </c>
     </row>
     <row r="223">
@@ -4846,19 +4846,19 @@
         <v>60</v>
       </c>
       <c r="B223" t="str">
-        <v>Poni Grove</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C223" t="str">
         <v>Main Area</v>
       </c>
       <c r="D223" t="str">
-        <v>Buneary</v>
+        <v>Tapu Koko</v>
       </c>
       <c r="E223" t="str">
-        <v>90-100</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F223" t="str">
-        <v>14.29%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="224">
@@ -4866,19 +4866,19 @@
         <v>60</v>
       </c>
       <c r="B224" t="str">
-        <v>Poni Grove</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C224" t="str">
         <v>Main Area</v>
       </c>
       <c r="D224" t="str">
-        <v>Granbull</v>
+        <v>Tapu Lele</v>
       </c>
       <c r="E224" t="str">
-        <v>90-100</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F224" t="str">
-        <v>14.29%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="225">
@@ -4886,19 +4886,19 @@
         <v>60</v>
       </c>
       <c r="B225" t="str">
-        <v>Poni Grove</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C225" t="str">
         <v>Main Area</v>
       </c>
       <c r="D225" t="str">
-        <v>Zoroark</v>
+        <v>Tapu Bulu</v>
       </c>
       <c r="E225" t="str">
-        <v>90-100</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F225" t="str">
-        <v>14.29%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="226">
@@ -4906,471 +4906,631 @@
         <v>60</v>
       </c>
       <c r="B226" t="str">
-        <v>Poni Grove</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C226" t="str">
         <v>Main Area</v>
       </c>
       <c r="D226" t="str">
-        <v>Heracross</v>
+        <v>Tapu Fini</v>
       </c>
       <c r="E226" t="str">
-        <v>90-100</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F226" t="str">
-        <v>14.29%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="227">
       <c r="A227">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B227" t="str">
-        <v>Poni Grove</v>
+        <v>Route 15</v>
       </c>
       <c r="C227" t="str">
         <v>Main Area</v>
       </c>
       <c r="D227" t="str">
-        <v>Riolu</v>
+        <v>Special Encounter</v>
       </c>
       <c r="E227" t="str">
-        <v>90-100</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F227" t="str">
-        <v>14.29%</v>
+        <v>100%</v>
       </c>
     </row>
     <row r="228">
       <c r="A228">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B228" t="str">
-        <v>Poni Grove</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C228" t="str">
-        <v>Main Area</v>
+        <v>Labs</v>
       </c>
       <c r="D228" t="str">
-        <v>Hariyama</v>
+        <v>Special Encounter</v>
       </c>
       <c r="E228" t="str">
-        <v>90-100</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F228" t="str">
-        <v>14.29%</v>
+        <v>100%</v>
       </c>
     </row>
     <row r="229">
       <c r="A229">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B229" t="str">
-        <v>Poni Grove</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C229" t="str">
-        <v>Main Area</v>
+        <v>Secret Lab</v>
       </c>
       <c r="D229" t="str">
-        <v>Mudsdale</v>
+        <v>Type: Null</v>
       </c>
       <c r="E229" t="str">
-        <v>90-100</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F229" t="str">
-        <v>14.29%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="230">
       <c r="A230">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B230" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C230" t="str">
-        <v>Main Area Part 1</v>
+        <v>Secret Lab</v>
       </c>
       <c r="D230" t="str">
-        <v>Nihilego</v>
+        <v>Silvally</v>
       </c>
       <c r="E230" t="str">
-        <v>90-100</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F230" t="str">
-        <v>11.11%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="231">
       <c r="A231">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B231" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C231" t="str">
-        <v>Main Area Part 1</v>
+        <v>Secret Lab</v>
       </c>
       <c r="D231" t="str">
-        <v>Buzzwole</v>
+        <v>Porygon</v>
       </c>
       <c r="E231" t="str">
-        <v>90-100</v>
+        <v>NaN-NaN</v>
       </c>
       <c r="F231" t="str">
-        <v>11.11%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="232">
       <c r="A232">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B232" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C232" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D232" t="str">
-        <v>Pheromosa</v>
+        <v>Buneary</v>
       </c>
       <c r="E232" t="str">
         <v>90-100</v>
       </c>
       <c r="F232" t="str">
-        <v>11.11%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="233">
       <c r="A233">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B233" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C233" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D233" t="str">
-        <v>Xurkitree</v>
+        <v>Granbull</v>
       </c>
       <c r="E233" t="str">
         <v>90-100</v>
       </c>
       <c r="F233" t="str">
-        <v>11.11%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="234">
       <c r="A234">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B234" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C234" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D234" t="str">
-        <v>Celesteela</v>
+        <v>Zoroark</v>
       </c>
       <c r="E234" t="str">
         <v>90-100</v>
       </c>
       <c r="F234" t="str">
-        <v>11.11%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="235">
       <c r="A235">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B235" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C235" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D235" t="str">
-        <v>Kartana</v>
+        <v>Heracross</v>
       </c>
       <c r="E235" t="str">
         <v>90-100</v>
       </c>
       <c r="F235" t="str">
-        <v>11.11%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="236">
       <c r="A236">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B236" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C236" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D236" t="str">
-        <v>Guzzlord</v>
+        <v>Riolu</v>
       </c>
       <c r="E236" t="str">
         <v>90-100</v>
       </c>
       <c r="F236" t="str">
-        <v>11.11%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="237">
       <c r="A237">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B237" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C237" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D237" t="str">
-        <v>Poipole</v>
+        <v>Hariyama</v>
       </c>
       <c r="E237" t="str">
         <v>90-100</v>
       </c>
       <c r="F237" t="str">
-        <v>11.11%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="238">
       <c r="A238">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B238" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C238" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D238" t="str">
-        <v>Stakataka</v>
+        <v>Mudsdale</v>
       </c>
       <c r="E238" t="str">
         <v>90-100</v>
       </c>
       <c r="F238" t="str">
-        <v>11.11%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="239">
       <c r="A239">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B239" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Poni Plains</v>
       </c>
       <c r="C239" t="str">
-        <v>Main Area Part 2</v>
+        <v>Center</v>
       </c>
       <c r="D239" t="str">
-        <v>Blacephalon</v>
+        <v>Special Encounter</v>
       </c>
       <c r="E239" t="str">
         <v>90-100</v>
       </c>
       <c r="F239" t="str">
-        <v>100.00%</v>
+        <v>100%</v>
       </c>
     </row>
     <row r="240">
       <c r="A240">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B240" t="str">
-        <v>Melemele Meadow</v>
+        <v>Resolution Cave</v>
       </c>
       <c r="C240" t="str">
         <v>Main Area</v>
       </c>
       <c r="D240" t="str">
-        <v>Caterpie</v>
+        <v>Special Encounter</v>
       </c>
       <c r="E240" t="str">
         <v>90-100</v>
       </c>
       <c r="F240" t="str">
-        <v>14.29%</v>
+        <v>100%</v>
       </c>
     </row>
     <row r="241">
       <c r="A241">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B241" t="str">
-        <v>Melemele Meadow</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C241" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D241" t="str">
-        <v>Metapod</v>
+        <v>Nihilego</v>
       </c>
       <c r="E241" t="str">
         <v>90-100</v>
       </c>
       <c r="F241" t="str">
-        <v>14.29%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="242">
       <c r="A242">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B242" t="str">
-        <v>Melemele Meadow</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C242" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D242" t="str">
-        <v>Cutiefly</v>
+        <v>Buzzwole</v>
       </c>
       <c r="E242" t="str">
         <v>90-100</v>
       </c>
       <c r="F242" t="str">
-        <v>14.29%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="243">
       <c r="A243">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B243" t="str">
-        <v>Melemele Meadow</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C243" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D243" t="str">
-        <v>Butterfree</v>
+        <v>Pheromosa</v>
       </c>
       <c r="E243" t="str">
         <v>90-100</v>
       </c>
       <c r="F243" t="str">
-        <v>14.29%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="244">
       <c r="A244">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B244" t="str">
-        <v>Melemele Meadow</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C244" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D244" t="str">
-        <v>Flabébé</v>
+        <v>Xurkitree</v>
       </c>
       <c r="E244" t="str">
         <v>90-100</v>
       </c>
       <c r="F244" t="str">
-        <v>14.29%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="245">
       <c r="A245">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B245" t="str">
-        <v>Melemele Meadow</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C245" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D245" t="str">
-        <v>Petilil</v>
+        <v>Celesteela</v>
       </c>
       <c r="E245" t="str">
         <v>90-100</v>
       </c>
       <c r="F245" t="str">
-        <v>14.29%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="246">
       <c r="A246">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B246" t="str">
-        <v>Melemele Meadow</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C246" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 2</v>
       </c>
       <c r="D246" t="str">
-        <v>Cottonee</v>
+        <v>Kartana</v>
       </c>
       <c r="E246" t="str">
         <v>90-100</v>
       </c>
       <c r="F246" t="str">
-        <v>14.29%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="247">
       <c r="A247">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B247" t="str">
-        <v>Shopping Mall Antiquities</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C247" t="str">
-        <v>Event</v>
+        <v>Main Area Part 2</v>
       </c>
       <c r="D247" t="str">
-        <v>Magearna</v>
+        <v>Guzzlord</v>
       </c>
       <c r="E247" t="str">
         <v>90-100</v>
       </c>
       <c r="F247" t="str">
-        <v>100.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="248">
       <c r="A248">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B248" t="str">
-        <v>Aether Paradise</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C248" t="str">
-        <v>Restricted Area</v>
+        <v>Main Area Part 2</v>
       </c>
       <c r="D248" t="str">
-        <v>Zeraora</v>
+        <v>Poipole</v>
       </c>
       <c r="E248" t="str">
         <v>90-100</v>
       </c>
       <c r="F248" t="str">
-        <v>100.00%</v>
+        <v>20.00%</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>68</v>
+      </c>
+      <c r="B249" t="str">
+        <v>The Interdimensional Rift</v>
+      </c>
+      <c r="C249" t="str">
+        <v>Main Area Part 2</v>
+      </c>
+      <c r="D249" t="str">
+        <v>Stakataka</v>
+      </c>
+      <c r="E249" t="str">
+        <v>90-100</v>
+      </c>
+      <c r="F249" t="str">
+        <v>20.00%</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>68</v>
+      </c>
+      <c r="B250" t="str">
+        <v>The Interdimensional Rift</v>
+      </c>
+      <c r="C250" t="str">
+        <v>Main Area Part 2</v>
+      </c>
+      <c r="D250" t="str">
+        <v>Blacephalon</v>
+      </c>
+      <c r="E250" t="str">
+        <v>90-100</v>
+      </c>
+      <c r="F250" t="str">
+        <v>20.00%</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>69</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Poni Coast</v>
+      </c>
+      <c r="C251" t="str">
+        <v>Main Area</v>
+      </c>
+      <c r="D251" t="str">
+        <v>Alolan Dugtrio</v>
+      </c>
+      <c r="E251" t="str">
+        <v>90-100</v>
+      </c>
+      <c r="F251" t="str">
+        <v>33.33%</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>69</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Poni Coast</v>
+      </c>
+      <c r="C252" t="str">
+        <v>Main Area</v>
+      </c>
+      <c r="D252" t="str">
+        <v>Gastrodon</v>
+      </c>
+      <c r="E252" t="str">
+        <v>90-100</v>
+      </c>
+      <c r="F252" t="str">
+        <v>33.33%</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>69</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Poni Coast</v>
+      </c>
+      <c r="C253" t="str">
+        <v>Main Area</v>
+      </c>
+      <c r="D253" t="str">
+        <v>Exeggcute</v>
+      </c>
+      <c r="E253" t="str">
+        <v>90-100</v>
+      </c>
+      <c r="F253" t="str">
+        <v>33.33%</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>70</v>
+      </c>
+      <c r="B254" t="str">
+        <v>The Zenith Anomaly</v>
+      </c>
+      <c r="C254" t="str">
+        <v>Main Area</v>
+      </c>
+      <c r="D254" t="str">
+        <v>Magearna</v>
+      </c>
+      <c r="E254" t="str">
+        <v>90-100</v>
+      </c>
+      <c r="F254" t="str">
+        <v>33.33%</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>70</v>
+      </c>
+      <c r="B255" t="str">
+        <v>The Zenith Anomaly</v>
+      </c>
+      <c r="C255" t="str">
+        <v>Main Area</v>
+      </c>
+      <c r="D255" t="str">
+        <v>Marshadow</v>
+      </c>
+      <c r="E255" t="str">
+        <v>90-100</v>
+      </c>
+      <c r="F255" t="str">
+        <v>33.33%</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>70</v>
+      </c>
+      <c r="B256" t="str">
+        <v>The Zenith Anomaly</v>
+      </c>
+      <c r="C256" t="str">
+        <v>Main Area</v>
+      </c>
+      <c r="D256" t="str">
+        <v>Zeraora</v>
+      </c>
+      <c r="E256" t="str">
+        <v>90-100</v>
+      </c>
+      <c r="F256" t="str">
+        <v>33.33%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F248"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F256"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C71"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5391,7 +5551,7 @@
         <v>Start the game</v>
       </c>
       <c r="C2" t="str">
-        <v>Unlocks Starter Professor Kukui</v>
+        <v>Unlocks Route 1 East</v>
       </c>
     </row>
     <row r="3">
@@ -5399,10 +5559,10 @@
         <v>Challenge 2</v>
       </c>
       <c r="B3" t="str">
-        <v>Defeat 10 Pokemon in Starter Professor Kukui</v>
+        <v>Defeat 10 Pokemon in Route 1 East</v>
       </c>
       <c r="C3" t="str">
-        <v>Unlocks Route 1 East</v>
+        <v>Unlocks Route 1 Hau'oli Outskirts</v>
       </c>
     </row>
     <row r="4">
@@ -5410,10 +5570,10 @@
         <v>Challenge 3</v>
       </c>
       <c r="B4" t="str">
-        <v>Defeat 10 Pokemon in Route 1 East</v>
+        <v>Defeat 10 Pokemon in Route 1 Hau'oli Outskirts</v>
       </c>
       <c r="C4" t="str">
-        <v>Unlocks Route 1 Hau'oli Outskirts</v>
+        <v>Unlocks Hau'oli City Shopping District</v>
       </c>
     </row>
     <row r="5">
@@ -5421,10 +5581,10 @@
         <v>Challenge 4</v>
       </c>
       <c r="B5" t="str">
-        <v>Defeat 10 Pokemon in Route 1 Hau'oli Outskirts</v>
+        <v>Defeat 10 Pokemon in Hau'oli City Shopping District</v>
       </c>
       <c r="C5" t="str">
-        <v>Unlocks Hau'oli City Shopping District</v>
+        <v>Unlocks Route 2 North</v>
       </c>
     </row>
     <row r="6">
@@ -5432,10 +5592,10 @@
         <v>Challenge 5</v>
       </c>
       <c r="B6" t="str">
-        <v>Defeat 10 Pokemon in Hau'oli City Shopping District</v>
+        <v>Defeat 10 Pokemon in Route 2 North</v>
       </c>
       <c r="C6" t="str">
-        <v>Unlocks Route 2 North</v>
+        <v>Unlocks Captain Ilima</v>
       </c>
     </row>
     <row r="7">
@@ -5443,10 +5603,10 @@
         <v>Challenge 6</v>
       </c>
       <c r="B7" t="str">
-        <v>Defeat 10 Pokemon in Route 2 North</v>
+        <v>Defeat Captain Ilima</v>
       </c>
       <c r="C7" t="str">
-        <v>Unlocks Captain Ilima</v>
+        <v>Unlocks Hau'oli Cemetery Main Area</v>
       </c>
     </row>
     <row r="8">
@@ -5454,10 +5614,10 @@
         <v>Challenge 7</v>
       </c>
       <c r="B8" t="str">
-        <v>Defeat Captain Ilima</v>
+        <v>Defeat 10 Pokemon in Hau'oli Cemetery Main Area</v>
       </c>
       <c r="C8" t="str">
-        <v>Unlocks Hau'oli Cemetery Main Area</v>
+        <v>Unlocks Ten Carat Hill Farthest Hollow</v>
       </c>
     </row>
     <row r="9">
@@ -5465,10 +5625,10 @@
         <v>Challenge 8</v>
       </c>
       <c r="B9" t="str">
-        <v>Defeat 10 Pokemon in Hau'oli Cemetery Main Area</v>
+        <v>Defeat 10 Pokemon in Ten Carat Hill Farthest Hollow</v>
       </c>
       <c r="C9" t="str">
-        <v>Unlocks Ten Carat Hill Farthest Hollow</v>
+        <v>Unlocks Seaward Cave Main Area</v>
       </c>
     </row>
     <row r="10">
@@ -5476,10 +5636,10 @@
         <v>Challenge 9</v>
       </c>
       <c r="B10" t="str">
-        <v>Defeat 10 Pokemon in Ten Carat Hill Farthest Hollow</v>
+        <v>Defeat 10 Pokemon in Seaward Cave Main Area</v>
       </c>
       <c r="C10" t="str">
-        <v>Unlocks Seaward Cave Main Area</v>
+        <v>Unlocks Kahuna Hala</v>
       </c>
     </row>
     <row r="11">
@@ -5487,10 +5647,10 @@
         <v>Challenge 10</v>
       </c>
       <c r="B11" t="str">
-        <v>Defeat 10 Pokemon in Seaward Cave Main Area</v>
+        <v>Defeat Kahuna Hala</v>
       </c>
       <c r="C11" t="str">
-        <v>Unlocks Route 3 North</v>
+        <v>Unlocks Heahea Beach Main Area Part 1</v>
       </c>
     </row>
     <row r="12">
@@ -5498,10 +5658,10 @@
         <v>Challenge 11</v>
       </c>
       <c r="B12" t="str">
-        <v>Defeat 10 Pokemon in Route 3 North</v>
+        <v>Defeat Kahuna Hala</v>
       </c>
       <c r="C12" t="str">
-        <v>Unlocks Kahuna Hala</v>
+        <v>Unlocks Heahea Beach Main Area Part 2</v>
       </c>
     </row>
     <row r="13">
@@ -5509,10 +5669,10 @@
         <v>Challenge 12</v>
       </c>
       <c r="B13" t="str">
-        <v>Defeat Kahuna Hala</v>
+        <v>Defeat 10 Pokemon in Heahea Beach Main Area Part 2</v>
       </c>
       <c r="C13" t="str">
-        <v>Unlocks Heahea Beach Main Area Part 1</v>
+        <v>Unlocks Paniola Ranch Main Area</v>
       </c>
     </row>
     <row r="14">
@@ -5520,10 +5680,10 @@
         <v>Challenge 13</v>
       </c>
       <c r="B14" t="str">
-        <v>Defeat Kahuna Hala</v>
+        <v>Defeat 10 Pokemon in Paniola Ranch Main Area</v>
       </c>
       <c r="C14" t="str">
-        <v>Unlocks Heahea Beach Main Area Part 2</v>
+        <v>Unlocks Daycare NPC</v>
       </c>
     </row>
     <row r="15">
@@ -5531,10 +5691,10 @@
         <v>Challenge 14</v>
       </c>
       <c r="B15" t="str">
-        <v>Defeat 10 Pokemon in Heahea Beach Main Area Part 2</v>
+        <v>Interact with Daycare</v>
       </c>
       <c r="C15" t="str">
-        <v>Unlocks Paniola Ranch Main Area</v>
+        <v>Unlocks Route 5 Main Area</v>
       </c>
     </row>
     <row r="16">
@@ -5542,10 +5702,10 @@
         <v>Challenge 15</v>
       </c>
       <c r="B16" t="str">
-        <v>Defeat 10 Pokemon in Paniola Ranch Main Area</v>
+        <v>Defeat 10 Pokemon in Route 5 Main Area</v>
       </c>
       <c r="C16" t="str">
-        <v>Unlocks Daycare NPC</v>
+        <v>Unlocks Brooklet Hill South</v>
       </c>
     </row>
     <row r="17">
@@ -5553,10 +5713,10 @@
         <v>Challenge 16</v>
       </c>
       <c r="B17" t="str">
-        <v>Interact with Daycare</v>
+        <v>Defeat 10 Pokemon in Brooklet Hill South</v>
       </c>
       <c r="C17" t="str">
-        <v>Unlocks Route 5 Main Area</v>
+        <v>Unlocks Captain Lana</v>
       </c>
     </row>
     <row r="18">
@@ -5564,10 +5724,10 @@
         <v>Challenge 17</v>
       </c>
       <c r="B18" t="str">
-        <v>Defeat 10 Pokemon in Route 5 Main Area</v>
+        <v>Defeat Captain Lana</v>
       </c>
       <c r="C18" t="str">
-        <v>Unlocks Brooklet Hill South</v>
+        <v>Unlocks Wela Volcano Park Main Area</v>
       </c>
     </row>
     <row r="19">
@@ -5575,10 +5735,10 @@
         <v>Challenge 18</v>
       </c>
       <c r="B19" t="str">
-        <v>Defeat 10 Pokemon in Brooklet Hill South</v>
+        <v>Defeat 10 Pokemon in Wela Volcano Park Main Area</v>
       </c>
       <c r="C19" t="str">
-        <v>Unlocks Captain Lana</v>
+        <v>Unlocks Captain Kiawe</v>
       </c>
     </row>
     <row r="20">
@@ -5586,10 +5746,10 @@
         <v>Challenge 19</v>
       </c>
       <c r="B20" t="str">
-        <v>Defeat Captain Lana</v>
+        <v>Defeat Captain Kiawe</v>
       </c>
       <c r="C20" t="str">
-        <v>Unlocks Wela Volcano Park Main Area</v>
+        <v>Unlocks Route 7 Main Area</v>
       </c>
     </row>
     <row r="21">
@@ -5597,10 +5757,10 @@
         <v>Challenge 20</v>
       </c>
       <c r="B21" t="str">
-        <v>Defeat 10 Pokemon in Wela Volcano Park Main Area</v>
+        <v>Defeat 10 Pokemon in Route 7 Main Area</v>
       </c>
       <c r="C21" t="str">
-        <v>Unlocks Captain Kiawe</v>
+        <v>Unlocks Route 8 Fossil Restoration Center Part 1</v>
       </c>
     </row>
     <row r="22">
@@ -5608,10 +5768,10 @@
         <v>Challenge 21</v>
       </c>
       <c r="B22" t="str">
-        <v>Defeat Captain Kiawe</v>
+        <v>Defeat 10 Pokemon in Route 8 Fossil Restoration Center Part 1</v>
       </c>
       <c r="C22" t="str">
-        <v>Unlocks Route 7 Main Area</v>
+        <v>Unlocks Route 8 Fossil Restoration Center Part 2</v>
       </c>
     </row>
     <row r="23">
@@ -5619,10 +5779,10 @@
         <v>Challenge 22</v>
       </c>
       <c r="B23" t="str">
-        <v>Defeat 10 Pokemon in Route 7 Main Area</v>
+        <v>Defeat 10 Pokemon in Route 8 Fossil Restoration Center Part 2</v>
       </c>
       <c r="C23" t="str">
-        <v>Unlocks Route 8 Fossil Restoration Center Part 1</v>
+        <v>Unlocks Lush Jungle North</v>
       </c>
     </row>
     <row r="24">
@@ -5630,10 +5790,10 @@
         <v>Challenge 23</v>
       </c>
       <c r="B24" t="str">
-        <v>Defeat 10 Pokemon in Route 8 Fossil Restoration Center Part 1</v>
+        <v>Defeat 10 Pokemon in Lush Jungle North</v>
       </c>
       <c r="C24" t="str">
-        <v>Unlocks Route 8 Fossil Restoration Center Part 2</v>
+        <v>Unlocks Lush Jungle East Cave</v>
       </c>
     </row>
     <row r="25">
@@ -5641,10 +5801,10 @@
         <v>Challenge 24</v>
       </c>
       <c r="B25" t="str">
-        <v>Defeat 10 Pokemon in Route 8 Fossil Restoration Center Part 2</v>
+        <v>Defeat 10 Pokemon in Lush Jungle East Cave</v>
       </c>
       <c r="C25" t="str">
-        <v>Unlocks Lush Jungle North</v>
+        <v>Unlocks Captain Mallow</v>
       </c>
     </row>
     <row r="26">
@@ -5652,10 +5812,10 @@
         <v>Challenge 25</v>
       </c>
       <c r="B26" t="str">
-        <v>Defeat 10 Pokemon in Lush Jungle North</v>
+        <v>Defeat Captain Mallow</v>
       </c>
       <c r="C26" t="str">
-        <v>Unlocks Lush Jungle East Cave</v>
+        <v>Unlocks Diglett's Tunnel Main Area</v>
       </c>
     </row>
     <row r="27">
@@ -5663,10 +5823,10 @@
         <v>Challenge 26</v>
       </c>
       <c r="B27" t="str">
-        <v>Defeat 10 Pokemon in Lush Jungle East Cave</v>
+        <v>Defeat 10 Pokemon in Diglett's Tunnel Main Area</v>
       </c>
       <c r="C27" t="str">
-        <v>Unlocks Captain Mallow</v>
+        <v>Unlocks Akala Outskirts Main Area</v>
       </c>
     </row>
     <row r="28">
@@ -5674,10 +5834,10 @@
         <v>Challenge 27</v>
       </c>
       <c r="B28" t="str">
-        <v>Defeat Captain Mallow</v>
+        <v>Defeat 10 Pokemon in Akala Outskirts Main Area</v>
       </c>
       <c r="C28" t="str">
-        <v>Unlocks Diglett's Tunnel Main Area</v>
+        <v>Unlocks Kahuna Olivia</v>
       </c>
     </row>
     <row r="29">
@@ -5685,10 +5845,10 @@
         <v>Challenge 28</v>
       </c>
       <c r="B29" t="str">
-        <v>Defeat 10 Pokemon in Diglett's Tunnel Main Area</v>
+        <v>Defeat 10 Pokemon in Kahuna Olivia</v>
       </c>
       <c r="C29" t="str">
-        <v>Unlocks Memorial Hill Main</v>
+        <v>Unlocks Malie City Outer Cape</v>
       </c>
     </row>
     <row r="30">
@@ -5696,10 +5856,10 @@
         <v>Challenge 29</v>
       </c>
       <c r="B30" t="str">
-        <v>Defeat 10 Pokemon in Memorial Hill Main</v>
+        <v>Defeat 10 Pokemon in Malie City Outer Cape</v>
       </c>
       <c r="C30" t="str">
-        <v>Unlocks Akala Outskirts Main Area</v>
+        <v>Unlocks Route 10 Main Area</v>
       </c>
     </row>
     <row r="31">
@@ -5707,10 +5867,10 @@
         <v>Challenge 30</v>
       </c>
       <c r="B31" t="str">
-        <v>Defeat 10 Pokemon in Akala Outskirts Main Area</v>
+        <v>Defeat 10 Pokemon in Route 10 Main Area</v>
       </c>
       <c r="C31" t="str">
-        <v>Unlocks Kahuna Olivia</v>
+        <v>Unlocks Mount Hokulani East</v>
       </c>
     </row>
     <row r="32">
@@ -5718,10 +5878,10 @@
         <v>Challenge 31</v>
       </c>
       <c r="B32" t="str">
-        <v>Defeat 10 Pokemon in Kahuna Olivia</v>
+        <v>Defeat 10 Pokemon in Mount Hokulani East</v>
       </c>
       <c r="C32" t="str">
-        <v>Unlocks Malie City Outer Cape</v>
+        <v>Unlocks Captain Sophocles</v>
       </c>
     </row>
     <row r="33">
@@ -5729,10 +5889,10 @@
         <v>Challenge 32</v>
       </c>
       <c r="B33" t="str">
-        <v>Defeat 10 Pokemon in Malie City Outer Cape</v>
+        <v>Defeat Captain Sophocles</v>
       </c>
       <c r="C33" t="str">
-        <v>Unlocks Route 10 Main Area</v>
+        <v>Unlocks Route 11 Main Area</v>
       </c>
     </row>
     <row r="34">
@@ -5740,10 +5900,10 @@
         <v>Challenge 33</v>
       </c>
       <c r="B34" t="str">
-        <v>Defeat 10 Pokemon in Route 10 Main Area</v>
+        <v>Defeat 10 Pokemon in Route 11 Main Area</v>
       </c>
       <c r="C34" t="str">
-        <v>Unlocks Mount Hokulani East</v>
+        <v>Unlocks Haina Desert Main Area</v>
       </c>
     </row>
     <row r="35">
@@ -5751,10 +5911,10 @@
         <v>Challenge 34</v>
       </c>
       <c r="B35" t="str">
-        <v>Defeat 10 Pokemon in Mount Hokulani East</v>
+        <v>Defeat 10 Pokemon in Haina Desert Main Area</v>
       </c>
       <c r="C35" t="str">
-        <v>Unlocks Captain Sophocles</v>
+        <v>Unlocks Tapu Village Main Area</v>
       </c>
     </row>
     <row r="36">
@@ -5762,10 +5922,10 @@
         <v>Challenge 35</v>
       </c>
       <c r="B36" t="str">
-        <v>Defeat Captain Sophocles</v>
+        <v>Defeat 10 Pokemon in Tapu Village Main Area</v>
       </c>
       <c r="C36" t="str">
-        <v>Unlocks Route 11 Main Area</v>
+        <v>Unlocks Thrifty Megamart Abandoned Site</v>
       </c>
     </row>
     <row r="37">
@@ -5773,10 +5933,10 @@
         <v>Challenge 36</v>
       </c>
       <c r="B37" t="str">
-        <v>Defeat 10 Pokemon in Route 11 Main Area</v>
+        <v>Defeat 10 Pokemon in Thrifty Megamart Abandoned Site</v>
       </c>
       <c r="C37" t="str">
-        <v>Unlocks Blush Mountain Main Area</v>
+        <v>Unlocks Captain Acerola</v>
       </c>
     </row>
     <row r="38">
@@ -5784,10 +5944,10 @@
         <v>Challenge 37</v>
       </c>
       <c r="B38" t="str">
-        <v>Defeat 10 Pokemon in Blush Mountain Main Area</v>
+        <v>Defeat 10 Pokemon in Captain Acerola</v>
       </c>
       <c r="C38" t="str">
-        <v>Unlocks Haina Desert Main Area</v>
+        <v>Unlocks Kahuna Nanu</v>
       </c>
     </row>
     <row r="39">
@@ -5795,10 +5955,10 @@
         <v>Challenge 38</v>
       </c>
       <c r="B39" t="str">
-        <v>Defeat 10 Pokemon in Haina Desert Main Area</v>
+        <v>Defeat Kahuna Nanu</v>
       </c>
       <c r="C39" t="str">
-        <v>Unlocks Tapu Village Main Area</v>
+        <v>Unlocks Seafolk Village Main</v>
       </c>
     </row>
     <row r="40">
@@ -5806,10 +5966,10 @@
         <v>Challenge 39</v>
       </c>
       <c r="B40" t="str">
-        <v>Defeat 10 Pokemon in Tapu Village Main Area</v>
+        <v>Defeat 10 Pokemon in Seafolk Village Main</v>
       </c>
       <c r="C40" t="str">
-        <v>Unlocks Thrifty Megamart Abandoned Site</v>
+        <v>Unlocks Poni Wilds Main Area</v>
       </c>
     </row>
     <row r="41">
@@ -5817,10 +5977,10 @@
         <v>Challenge 40</v>
       </c>
       <c r="B41" t="str">
-        <v>Defeat 10 Pokemon in Thrifty Megamart Abandoned Site</v>
+        <v>Defeat 10 Pokemon in Poni Wilds Main Area</v>
       </c>
       <c r="C41" t="str">
-        <v>Unlocks Captain Acerola</v>
+        <v>Unlocks Poni Breaker Coast Main Area</v>
       </c>
     </row>
     <row r="42">
@@ -5828,10 +5988,10 @@
         <v>Challenge 41</v>
       </c>
       <c r="B42" t="str">
-        <v>Defeat 10 Pokemon in Captain Acerola</v>
+        <v>Defeat 10 Pokemon in Poni Breaker Coast Main Area</v>
       </c>
       <c r="C42" t="str">
-        <v>Unlocks Kahuna Nanu</v>
+        <v>Unlocks Exeggutor Island Main Area</v>
       </c>
     </row>
     <row r="43">
@@ -5839,10 +5999,10 @@
         <v>Challenge 42</v>
       </c>
       <c r="B43" t="str">
-        <v>Defeat Kahuna Nanu</v>
+        <v>Defeat 10 Pokemon in Exeggutor Island Main Area</v>
       </c>
       <c r="C43" t="str">
-        <v>Unlocks Seafolk Village Main</v>
+        <v>Unlocks Vast Poni Canyon Outside</v>
       </c>
     </row>
     <row r="44">
@@ -5850,10 +6010,10 @@
         <v>Challenge 43</v>
       </c>
       <c r="B44" t="str">
-        <v>Defeat 10 Pokemon in Seafolk Village Main</v>
+        <v>Defeat 10 Pokemon in Vast Poni Canyon Outside</v>
       </c>
       <c r="C44" t="str">
-        <v>Unlocks Poni Wilds Main Area</v>
+        <v>Unlocks Captain Kommo-o</v>
       </c>
     </row>
     <row r="45">
@@ -5861,10 +6021,10 @@
         <v>Challenge 44</v>
       </c>
       <c r="B45" t="str">
-        <v>Defeat 10 Pokemon in Poni Wilds Main Area</v>
+        <v>Defeat Captain Kommo-o</v>
       </c>
       <c r="C45" t="str">
-        <v>Unlocks Poni Breaker Coast Main Area</v>
+        <v>Unlocks Captain Mina</v>
       </c>
     </row>
     <row r="46">
@@ -5872,10 +6032,10 @@
         <v>Challenge 45</v>
       </c>
       <c r="B46" t="str">
-        <v>Defeat 10 Pokemon in Poni Breaker Coast Main Area</v>
+        <v>Defeat Captain Mina</v>
       </c>
       <c r="C46" t="str">
-        <v>Unlocks Exeggutor Island Main Area</v>
+        <v>Unlocks Kahuna Hapu</v>
       </c>
     </row>
     <row r="47">
@@ -5883,10 +6043,10 @@
         <v>Challenge 46</v>
       </c>
       <c r="B47" t="str">
-        <v>Defeat 10 Pokemon in Exeggutor Island Main Area</v>
+        <v>Defeat Kahuna Hapu</v>
       </c>
       <c r="C47" t="str">
-        <v>Unlocks Vast Poni Canyon Outside</v>
+        <v>Unlocks Mount Lanakila Cave</v>
       </c>
     </row>
     <row r="48">
@@ -5894,10 +6054,10 @@
         <v>Challenge 47</v>
       </c>
       <c r="B48" t="str">
-        <v>Defeat 10 Pokemon in Vast Poni Canyon Outside</v>
+        <v>Defeat 10 Pokemon in Mount Lanakila Cave</v>
       </c>
       <c r="C48" t="str">
-        <v>Unlocks Captain Kommo-o</v>
+        <v>Unlocks Alola Pokemon League</v>
       </c>
     </row>
     <row r="49">
@@ -5905,253 +6065,264 @@
         <v>Challenge 48</v>
       </c>
       <c r="B49" t="str">
-        <v>Defeat Captain Kommo-o</v>
+        <v>Defeat Alola Pokemon League</v>
       </c>
       <c r="C49" t="str">
-        <v>Unlocks Captain Mina</v>
+        <v>Unlocks Champion Hau</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Challenge 49</v>
+        <v>Extra Challenge $1-1</v>
       </c>
       <c r="B50" t="str">
-        <v>Defeat Captain Mina</v>
+        <v>Defeat Captain Lana</v>
       </c>
       <c r="C50" t="str">
-        <v>Unlocks Kahuna Hapu</v>
+        <v>Unlocks Route 6 Main Area</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Challenge 50</v>
+        <v>Extra Challenge $1-2</v>
       </c>
       <c r="B51" t="str">
-        <v>Defeat Kahuna Hapu</v>
+        <v>Defeat 15 Pokemon in Route 6 Main Area</v>
       </c>
       <c r="C51" t="str">
-        <v>Unlocks Mount Lanakila Cave</v>
+        <v>Unlocks Royal Avenue Main Area</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Challenge 51</v>
+        <v>Extra Challenge $1-3</v>
       </c>
       <c r="B52" t="str">
-        <v>Defeat 10 Pokemon in Mount Lanakila Cave</v>
+        <v>Defeat 15 Pokemon in Royal Avenue Main Area</v>
       </c>
       <c r="C52" t="str">
-        <v>Unlocks Alola Pokemon League</v>
+        <v>Unlocks Pikachu Valley Main Area</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Challenge 52</v>
+        <v>Extra Challenge $1-4</v>
       </c>
       <c r="B53" t="str">
-        <v>Defeat Alola Pokemon League</v>
+        <v>Defeat 15 Pokemon in Pikachu Valley Main Area</v>
       </c>
       <c r="C53" t="str">
-        <v>Unlocks Champion Hau</v>
+        <v>Unlocks Heahea Surf Spot Main Area</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Extra Challenge $1-1</v>
+        <v>Extra Challenge $1-5</v>
       </c>
       <c r="B54" t="str">
-        <v>Defeat Kahuna Olivia</v>
+        <v>Defeat 15 Pokemon in Heahea Surf Spot Main Area</v>
       </c>
       <c r="C54" t="str">
-        <v>Unlocks Route 7 Main Area</v>
+        <v>Unlocks Starter Depot Main Area</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Extra Challenge $1-2</v>
+        <v>Extra Challenge $2-1</v>
       </c>
       <c r="B55" t="str">
-        <v>Defeat 15 Pokemon in Route 7 Main Area</v>
+        <v>Defeat Captain Sophocles</v>
       </c>
       <c r="C55" t="str">
-        <v>Unlocks Aether Paradise Secret Lab [Type: Null, Ditto, Porygon]</v>
+        <v>Unlocks Blush Mountain Main Area</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Extra Challenge $2-1</v>
+        <v>Extra Challenge $2-2</v>
       </c>
       <c r="B56" t="str">
-        <v>Defeat Kahuna Hala</v>
+        <v>Defeat 15 Pokemon in Blush Mountain Main Area</v>
       </c>
       <c r="C56" t="str">
-        <v>Unlocks Memorial Hill Main</v>
+        <v>Unlocks Ula'ula Meadow Main Area</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Extra Challenge $2-2</v>
+        <v>Extra Challenge $2-3</v>
       </c>
       <c r="B57" t="str">
-        <v>Defeat 15 Pokemon in Memorial Hill Main</v>
+        <v>Defeat 15 Pokemon in Ula'ula Meadow Main Area</v>
       </c>
       <c r="C57" t="str">
-        <v>Unlocks Sacred Shrine Main Area [Tapus (Koko, Lele, Bulu, Fini)]</v>
+        <v>Unlocks Lake of the Sunne Main Area</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Extra Challenge $3-1</v>
+        <v>Extra Challenge $2-4</v>
       </c>
       <c r="B58" t="str">
-        <v>Defeat Kahuna Nanu</v>
+        <v>Defeat 15 Pokemon in Lake of the Sunne Main Area</v>
       </c>
       <c r="C58" t="str">
-        <v>Unlocks Route 15 Main Area</v>
+        <v>Unlocks Obsidian Sphere Main Area [Cosmog, Solgaleo, Lunala, Necrozma]</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Extra Challenge $3-2</v>
+        <v>Extra Challenge $3-1</v>
       </c>
       <c r="B59" t="str">
-        <v>Defeat 15 Pokemon in Route 15 Main Area</v>
+        <v>Defeat Kahuna Hala</v>
       </c>
       <c r="C59" t="str">
-        <v>Unlocks Obsidian Sphere Main Area [Cosmog, Solgaleo, Lunala, Necrozma]</v>
+        <v>Unlocks Route 3 North</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Extra Challenge $4-1</v>
+        <v>Extra Challenge $3-2</v>
       </c>
       <c r="B60" t="str">
-        <v>Defeat Captain Ilima</v>
+        <v>Defeat 15 Pokemon in Route 3 North</v>
       </c>
       <c r="C60" t="str">
-        <v>Unlocks Route 3 North</v>
+        <v>Unlocks Memorial Hill Main</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Extra Challenge $4-2</v>
+        <v>Extra Challenge $3-3</v>
       </c>
       <c r="B61" t="str">
-        <v>Defeat 15 Pokemon in Route 3 North</v>
+        <v>Defeat 15 Pokemon in Memorial Hill Main</v>
       </c>
       <c r="C61" t="str">
-        <v>Unlocks Ten Carat Hill Deepest Cave [Marshadow]</v>
+        <v>Unlocks Sacred Shrine Main Area [Tapus (Koko, Lele, Bulu, Fini)]</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Extra Challenge $5-1</v>
+        <v>Extra Challenge $4-1</v>
       </c>
       <c r="B62" t="str">
-        <v>Defeat Champion Hau</v>
+        <v>Defeat Kahuna Nanu</v>
       </c>
       <c r="C62" t="str">
-        <v>Unlocks Poni Grove Main Area</v>
+        <v>Unlocks Route 15 Main Area</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Extra Challenge $5-2</v>
+        <v>Extra Challenge $4-2</v>
       </c>
       <c r="B63" t="str">
-        <v>Defeat 15 Pokemon in Poni Grove Main Area</v>
+        <v>Defeat 15 Pokemon in Route 15 Main Area</v>
       </c>
       <c r="C63" t="str">
-        <v>Unlocks Poni Plains Center</v>
+        <v>Unlocks Aether Paradise Labs</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Extra Challenge $5-3</v>
+        <v>Extra Challenge $4-3</v>
       </c>
       <c r="B64" t="str">
-        <v>Defeat 15 Pokemon in Poni Plains Center</v>
+        <v>Defeat 15 Pokemon in Aether Paradise Labs</v>
       </c>
       <c r="C64" t="str">
-        <v>Unlocks Resolution Cave Main Area</v>
+        <v>Unlocks Aether Paradise Secret Lab [Type: Null, Porygon, Silvally]</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Extra Challenge $5-4</v>
+        <v>Extra Challenge $5-1</v>
       </c>
       <c r="B65" t="str">
-        <v>Defeat 15 Pokemon in Resolution Cave Main Area</v>
+        <v>Defeat Champion Hau</v>
       </c>
       <c r="C65" t="str">
-        <v>Unlocks The Interdimensional Rift Main Area Part 1</v>
+        <v>Unlocks Poni Grove Main Area</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Extra Challenge $5-5</v>
+        <v>Extra Challenge $5-2</v>
       </c>
       <c r="B66" t="str">
-        <v>Defeat 15 Pokemon in The Interdimensional Rift Main Area Part 1</v>
+        <v>Defeat 15 Pokemon in Poni Grove Main Area</v>
       </c>
       <c r="C66" t="str">
-        <v>Unlocks The Interdimensional Rift Main Area Part 2 [All Ultra Beasts]</v>
+        <v>Unlocks Poni Plains Center</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Extra Challenge $6-1</v>
+        <v>Extra Challenge $5-3</v>
       </c>
       <c r="B67" t="str">
-        <v>Defeat Champion Hau</v>
+        <v>Defeat 15 Pokemon in Poni Plains Center</v>
       </c>
       <c r="C67" t="str">
-        <v>Unlocks Mahalo Trail Main Area</v>
+        <v>Unlocks Resolution Cave Main Area</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Extra Challenge $6-2</v>
+        <v>Extra Challenge $5-4</v>
       </c>
       <c r="B68" t="str">
-        <v>Defeat 15 Pokemon in Mahalo Trail Main Area</v>
+        <v>Defeat 15 Pokemon in Resolution Cave Main Area</v>
       </c>
       <c r="C68" t="str">
-        <v>Unlocks Melemele Meadow Main Area</v>
+        <v>Unlocks The Interdimensional Rift Main Area Part 1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Extra Challenge $6-3</v>
+        <v>Extra Challenge $5-5</v>
       </c>
       <c r="B69" t="str">
-        <v>Defeat 15 Pokemon in Melemele Meadow Main Area</v>
+        <v>Defeat 15 Pokemon in The Interdimensional Rift Main Area Part 1</v>
       </c>
       <c r="C69" t="str">
-        <v>Unlocks Shopping Mall Antiquities Event [Magearna]</v>
+        <v>Unlocks The Interdimensional Rift Main Area Part 2 [All Ultra Beasts]</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Extra Challenge $6-4</v>
+        <v>Extra Challenge $6-1</v>
       </c>
       <c r="B70" t="str">
-        <v>Defeat 15 Pokemon in Shopping Mall Antiquities Event</v>
+        <v>Defeat 15 Pokemon in The Interdimensional Rift Main Area Part 2</v>
       </c>
       <c r="C70" t="str">
-        <v>Unlocks Aether Paradise Restricted Area [Zeraora]</v>
+        <v>Unlocks Poni Coast Main Area</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Extra Challenge $6-2</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Defeat 15 Pokemon in Poni Coast Main Area</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Unlocks The Zenith Anomaly Main Area [Magearna, Marshadow, Zeraora]</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C70"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C71"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6169,13 +6340,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Pikachu</v>
+        <v>Rowlet</v>
       </c>
       <c r="B2" t="str">
-        <v>Electric</v>
+        <v>Grass/Flying</v>
       </c>
       <c r="C2" t="str">
-        <v>Route 1 East</v>
+        <v>Starter Depot</v>
       </c>
       <c r="D2" t="str">
         <v>Yes</v>
@@ -6183,27 +6354,27 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Alolan Raichu</v>
+        <v>Dartrix</v>
       </c>
       <c r="B3" t="str">
-        <v>Electric/Psychic</v>
+        <v>Grass/Flying</v>
       </c>
       <c r="C3" t="str">
-        <v>Route 1 East</v>
+        <v>Starter Depot</v>
       </c>
       <c r="D3" t="str">
-        <v>Yes (Evolution)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Oricorio</v>
+        <v>Litten</v>
       </c>
       <c r="B4" t="str">
-        <v>Fire/Electric/Psychic/Ghost</v>
+        <v>Fire</v>
       </c>
       <c r="C4" t="str">
-        <v>Route 3 North</v>
+        <v>Starter Depot</v>
       </c>
       <c r="D4" t="str">
         <v>Yes</v>
@@ -6211,13 +6382,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Lycanroc</v>
+        <v>Torracat</v>
       </c>
       <c r="B5" t="str">
-        <v>Rock</v>
+        <v>Fire</v>
       </c>
       <c r="C5" t="str">
-        <v>Ten Carat Hill Inside</v>
+        <v>Starter Depot</v>
       </c>
       <c r="D5" t="str">
         <v>Yes</v>
@@ -6225,13 +6396,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Staryu</v>
+        <v>Popplio</v>
       </c>
       <c r="B6" t="str">
         <v>Water</v>
       </c>
       <c r="C6" t="str">
-        <v>Route 7 Main Area</v>
+        <v>Starter Depot</v>
       </c>
       <c r="D6" t="str">
         <v>Yes</v>
@@ -6239,13 +6410,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Pyukumuku</v>
+        <v>Brionne</v>
       </c>
       <c r="B7" t="str">
         <v>Water</v>
       </c>
       <c r="C7" t="str">
-        <v>Route 7 Main Area</v>
+        <v>Starter Depot</v>
       </c>
       <c r="D7" t="str">
         <v>Yes</v>
@@ -6253,13 +6424,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Bounsweet</v>
+        <v>Pikachu</v>
       </c>
       <c r="B8" t="str">
-        <v>Grass</v>
+        <v>Electric</v>
       </c>
       <c r="C8" t="str">
-        <v>Lush Jungle North</v>
+        <v>Route 1 East</v>
       </c>
       <c r="D8" t="str">
         <v>Yes</v>
@@ -6267,27 +6438,27 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Oranguru</v>
+        <v>Alolan Raichu</v>
       </c>
       <c r="B9" t="str">
-        <v>Normal/Psychic</v>
+        <v>Electric/Psychic</v>
       </c>
       <c r="C9" t="str">
-        <v>Lush Jungle East Cave</v>
+        <v>Route 1 East</v>
       </c>
       <c r="D9" t="str">
-        <v>Yes</v>
+        <v>Yes (Evolution)</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Passimian</v>
+        <v>Oricorio</v>
       </c>
       <c r="B10" t="str">
-        <v>Fighting</v>
+        <v>Fire/Electric/Psychic/Ghost</v>
       </c>
       <c r="C10" t="str">
-        <v>Lush Jungle East Cave</v>
+        <v>Route 3 North</v>
       </c>
       <c r="D10" t="str">
         <v>Yes</v>
@@ -6295,41 +6466,41 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Corsola</v>
+        <v>Lycanroc</v>
       </c>
       <c r="B11" t="str">
-        <v>Water/Rock</v>
+        <v>Rock</v>
       </c>
       <c r="C11" t="str">
-        <v>Route 7 Main Area</v>
+        <v>Ten Carat Hill Inside</v>
       </c>
       <c r="D11" t="str">
-        <v>Yes (Merged)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Mareanie</v>
+        <v>Staryu</v>
       </c>
       <c r="B12" t="str">
-        <v>Poison/Water</v>
+        <v>Water</v>
       </c>
       <c r="C12" t="str">
         <v>Route 7 Main Area</v>
       </c>
       <c r="D12" t="str">
-        <v>Yes (Merged)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Minior</v>
+        <v>Pyukumuku</v>
       </c>
       <c r="B13" t="str">
-        <v>Rock/Flying</v>
+        <v>Water</v>
       </c>
       <c r="C13" t="str">
-        <v>Mount Hokulani East</v>
+        <v>Route 7 Main Area</v>
       </c>
       <c r="D13" t="str">
         <v>Yes</v>
@@ -6337,13 +6508,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Bruxish</v>
+        <v>Bounsweet</v>
       </c>
       <c r="B14" t="str">
-        <v>Water/Psychic</v>
+        <v>Grass</v>
       </c>
       <c r="C14" t="str">
-        <v>Route 14 Main Area</v>
+        <v>Lush Jungle North</v>
       </c>
       <c r="D14" t="str">
         <v>Yes</v>
@@ -6351,13 +6522,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Sandygast</v>
+        <v>Oranguru</v>
       </c>
       <c r="B15" t="str">
-        <v>Ghost/Ground</v>
+        <v>Normal/Psychic</v>
       </c>
       <c r="C15" t="str">
-        <v>Route 15 Main Area</v>
+        <v>Lush Jungle East Cave</v>
       </c>
       <c r="D15" t="str">
         <v>Yes</v>
@@ -6365,13 +6536,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Klefki</v>
+        <v>Passimian</v>
       </c>
       <c r="B16" t="str">
-        <v>Steel/Fairy</v>
+        <v>Fighting</v>
       </c>
       <c r="C16" t="str">
-        <v>Route 16 Main Area</v>
+        <v>Lush Jungle East Cave</v>
       </c>
       <c r="D16" t="str">
         <v>Yes</v>
@@ -6379,13 +6550,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Crabominable</v>
+        <v>Corsola</v>
       </c>
       <c r="B17" t="str">
-        <v>Fighting/Ice</v>
+        <v>Water/Rock</v>
       </c>
       <c r="C17" t="str">
-        <v>Mount Lanakila Cave</v>
+        <v>Route 7 Main Area</v>
       </c>
       <c r="D17" t="str">
         <v>Yes</v>
@@ -6393,13 +6564,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Tapu Koko</v>
+        <v>Mareanie</v>
       </c>
       <c r="B18" t="str">
-        <v>Electric/Fairy</v>
+        <v>Poison/Water</v>
       </c>
       <c r="C18" t="str">
-        <v>Sacred Shrine</v>
+        <v>Route 7 Main Area</v>
       </c>
       <c r="D18" t="str">
         <v>Yes</v>
@@ -6407,13 +6578,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Tapu Lele</v>
+        <v>Minior</v>
       </c>
       <c r="B19" t="str">
-        <v>Psychic/Fairy</v>
+        <v>Rock/Flying</v>
       </c>
       <c r="C19" t="str">
-        <v>Sacred Shrine</v>
+        <v>Mount Hokulani East</v>
       </c>
       <c r="D19" t="str">
         <v>Yes</v>
@@ -6421,13 +6592,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Tapu Bulu</v>
+        <v>Bruxish</v>
       </c>
       <c r="B20" t="str">
-        <v>Grass/Fairy</v>
+        <v>Water/Psychic</v>
       </c>
       <c r="C20" t="str">
-        <v>Sacred Shrine</v>
+        <v>Route 14 Main Area</v>
       </c>
       <c r="D20" t="str">
         <v>Yes</v>
@@ -6435,13 +6606,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Tapu Fini</v>
+        <v>Sandygast</v>
       </c>
       <c r="B21" t="str">
-        <v>Water/Fairy</v>
+        <v>Ghost/Ground</v>
       </c>
       <c r="C21" t="str">
-        <v>Sacred Shrine</v>
+        <v>Route 15 Main Area</v>
       </c>
       <c r="D21" t="str">
         <v>Yes</v>
@@ -6449,13 +6620,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Cosmog</v>
+        <v>Klefki</v>
       </c>
       <c r="B22" t="str">
-        <v>Psychic</v>
+        <v>Steel/Fairy</v>
       </c>
       <c r="C22" t="str">
-        <v>Obsidian Sphere</v>
+        <v>Route 16 Main Area</v>
       </c>
       <c r="D22" t="str">
         <v>Yes</v>
@@ -6463,27 +6634,27 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Cosmoem</v>
+        <v>Crabominable</v>
       </c>
       <c r="B23" t="str">
-        <v>Psychic</v>
+        <v>Fighting/Ice</v>
       </c>
       <c r="C23" t="str">
-        <v>Obsidian Sphere</v>
+        <v>Mount Lanakila Cave</v>
       </c>
       <c r="D23" t="str">
-        <v>Yes (Evolution)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Solgaleo</v>
+        <v>Amaura</v>
       </c>
       <c r="B24" t="str">
-        <v>Psychic/Steel</v>
+        <v>Rock/Ice</v>
       </c>
       <c r="C24" t="str">
-        <v>Obsidian Sphere</v>
+        <v>Route 8 Fossil Restoration</v>
       </c>
       <c r="D24" t="str">
         <v>Yes</v>
@@ -6491,13 +6662,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Lunala</v>
+        <v>Ditto</v>
       </c>
       <c r="B25" t="str">
-        <v>Psychic/Ghost</v>
+        <v>Normal</v>
       </c>
       <c r="C25" t="str">
-        <v>Obsidian Sphere</v>
+        <v>Route 10</v>
       </c>
       <c r="D25" t="str">
         <v>Yes</v>
@@ -6505,13 +6676,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Necrozma</v>
+        <v>Tapu Koko</v>
       </c>
       <c r="B26" t="str">
-        <v>Psychic</v>
+        <v>Electric/Fairy</v>
       </c>
       <c r="C26" t="str">
-        <v>Obsidian Sphere</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="D26" t="str">
         <v>Yes</v>
@@ -6519,13 +6690,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Poipole</v>
+        <v>Tapu Lele</v>
       </c>
       <c r="B27" t="str">
-        <v>Poison</v>
+        <v>Psychic/Fairy</v>
       </c>
       <c r="C27" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="D27" t="str">
         <v>Yes</v>
@@ -6533,27 +6704,27 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Naganadel</v>
+        <v>Tapu Bulu</v>
       </c>
       <c r="B28" t="str">
-        <v>Poison/Dragon</v>
+        <v>Grass/Fairy</v>
       </c>
       <c r="C28" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="D28" t="str">
-        <v>Yes (Evolution)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Nihilego</v>
+        <v>Tapu Fini</v>
       </c>
       <c r="B29" t="str">
-        <v>Rock/Poison</v>
+        <v>Water/Fairy</v>
       </c>
       <c r="C29" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="D29" t="str">
         <v>Yes</v>
@@ -6561,13 +6732,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Buzzwole</v>
+        <v>Cosmog</v>
       </c>
       <c r="B30" t="str">
-        <v>Bug/Fighting</v>
+        <v>Psychic</v>
       </c>
       <c r="C30" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="D30" t="str">
         <v>Yes</v>
@@ -6575,13 +6746,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Pheromosa</v>
+        <v>Cosmoem</v>
       </c>
       <c r="B31" t="str">
-        <v>Bug/Fighting</v>
+        <v>Psychic</v>
       </c>
       <c r="C31" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="D31" t="str">
         <v>Yes</v>
@@ -6589,13 +6760,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Xurkitree</v>
+        <v>Solgaleo</v>
       </c>
       <c r="B32" t="str">
-        <v>Electric</v>
+        <v>Psychic/Steel</v>
       </c>
       <c r="C32" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="D32" t="str">
         <v>Yes</v>
@@ -6603,13 +6774,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Celesteela</v>
+        <v>Lunala</v>
       </c>
       <c r="B33" t="str">
-        <v>Steel/Flying</v>
+        <v>Psychic/Ghost</v>
       </c>
       <c r="C33" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="D33" t="str">
         <v>Yes</v>
@@ -6617,13 +6788,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Kartana</v>
+        <v>Necrozma</v>
       </c>
       <c r="B34" t="str">
-        <v>Grass/Steel</v>
+        <v>Psychic</v>
       </c>
       <c r="C34" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="D34" t="str">
         <v>Yes</v>
@@ -6631,10 +6802,10 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Guzzlord</v>
+        <v>Poipole</v>
       </c>
       <c r="B35" t="str">
-        <v>Dark/Dragon</v>
+        <v>Poison</v>
       </c>
       <c r="C35" t="str">
         <v>The Interdimensional Rift</v>
@@ -6645,24 +6816,24 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Stakataka</v>
+        <v>Naganadel</v>
       </c>
       <c r="B36" t="str">
-        <v>Rock/Steel</v>
+        <v>Poison/Dragon</v>
       </c>
       <c r="C36" t="str">
         <v>The Interdimensional Rift</v>
       </c>
       <c r="D36" t="str">
-        <v>Yes</v>
+        <v>Yes (Evolution)</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Blacephalon</v>
+        <v>Nihilego</v>
       </c>
       <c r="B37" t="str">
-        <v>Fire/Ghost</v>
+        <v>Rock/Poison</v>
       </c>
       <c r="C37" t="str">
         <v>The Interdimensional Rift</v>
@@ -6673,13 +6844,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Type: Null</v>
+        <v>Buzzwole</v>
       </c>
       <c r="B38" t="str">
-        <v>Normal</v>
+        <v>Bug/Fighting</v>
       </c>
       <c r="C38" t="str">
-        <v>Aether Paradise Secret Lab</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="D38" t="str">
         <v>Yes</v>
@@ -6687,27 +6858,27 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Silvally</v>
+        <v>Pheromosa</v>
       </c>
       <c r="B39" t="str">
-        <v>Normal</v>
+        <v>Bug/Fighting</v>
       </c>
       <c r="C39" t="str">
-        <v>Aether Paradise Secret Lab</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="D39" t="str">
-        <v>Yes (Evolution)</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Ditto</v>
+        <v>Xurkitree</v>
       </c>
       <c r="B40" t="str">
-        <v>Normal</v>
+        <v>Electric</v>
       </c>
       <c r="C40" t="str">
-        <v>Aether Paradise Secret Lab</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="D40" t="str">
         <v>Yes</v>
@@ -6715,13 +6886,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Porygon</v>
+        <v>Celesteela</v>
       </c>
       <c r="B41" t="str">
-        <v>Normal</v>
+        <v>Steel/Flying</v>
       </c>
       <c r="C41" t="str">
-        <v>Aether Paradise Secret Lab</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="D41" t="str">
         <v>Yes</v>
@@ -6729,13 +6900,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Magearna</v>
+        <v>Kartana</v>
       </c>
       <c r="B42" t="str">
-        <v>Steel/Fairy</v>
+        <v>Grass/Steel</v>
       </c>
       <c r="C42" t="str">
-        <v>Shopping Mall Antiquities Event</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="D42" t="str">
         <v>Yes</v>
@@ -6743,13 +6914,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Marshadow</v>
+        <v>Guzzlord</v>
       </c>
       <c r="B43" t="str">
-        <v>Ghost/Fighting</v>
+        <v>Dark/Dragon</v>
       </c>
       <c r="C43" t="str">
-        <v>Ten Carat Hill Deepest Cave</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="D43" t="str">
         <v>Yes</v>
@@ -6757,21 +6928,119 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Zeraora</v>
+        <v>Stakataka</v>
       </c>
       <c r="B44" t="str">
-        <v>Electric</v>
+        <v>Rock/Steel</v>
       </c>
       <c r="C44" t="str">
-        <v>Aether Paradise Restricted Area</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="D44" t="str">
         <v>Yes</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Blacephalon</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Fire/Ghost</v>
+      </c>
+      <c r="C45" t="str">
+        <v>The Interdimensional Rift</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Type: Null</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Aether Paradise Secret Lab</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Silvally</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Aether Paradise Secret Lab</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Porygon</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Aether Paradise Secret Lab</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Magearna</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Steel/Fairy</v>
+      </c>
+      <c r="C49" t="str">
+        <v>The Zenith Anomaly</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Marshadow</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Ghost/Fighting</v>
+      </c>
+      <c r="C50" t="str">
+        <v>The Zenith Anomaly</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Zeraora</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Electric</v>
+      </c>
+      <c r="C51" t="str">
+        <v>The Zenith Anomaly</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Alola_Paths_and_Challenges.xlsx
+++ b/Alola_Paths_and_Challenges.xlsx
@@ -5,7 +5,6 @@
   <sheets>
     <sheet name="Paths" sheetId="1" r:id="rId1"/>
     <sheet name="Challenges" sheetId="2" r:id="rId2"/>
-    <sheet name="Missing Pokemons" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -399,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F256"/>
+  <dimension ref="A1:F250"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -438,7 +437,7 @@
         <v>2-7</v>
       </c>
       <c r="F2" t="str">
-        <v>12.50%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="3">
@@ -458,7 +457,7 @@
         <v>2-7</v>
       </c>
       <c r="F3" t="str">
-        <v>12.50%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="4">
@@ -478,7 +477,7 @@
         <v>2-7</v>
       </c>
       <c r="F4" t="str">
-        <v>12.50%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="5">
@@ -498,7 +497,7 @@
         <v>2-7</v>
       </c>
       <c r="F5" t="str">
-        <v>12.50%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="6">
@@ -518,7 +517,7 @@
         <v>2-7</v>
       </c>
       <c r="F6" t="str">
-        <v>12.50%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="7">
@@ -538,7 +537,7 @@
         <v>2-7</v>
       </c>
       <c r="F7" t="str">
-        <v>12.50%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="8">
@@ -558,27 +557,27 @@
         <v>2-7</v>
       </c>
       <c r="F8" t="str">
-        <v>12.50%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" t="str">
         <v>Route 1</v>
       </c>
       <c r="C9" t="str">
-        <v>East</v>
+        <v>Hau'oli Outskirts</v>
       </c>
       <c r="D9" t="str">
-        <v>Pikachu</v>
+        <v>Inkay</v>
       </c>
       <c r="E9" t="str">
-        <v>2-7</v>
+        <v>3-8</v>
       </c>
       <c r="F9" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="10">
@@ -592,7 +591,7 @@
         <v>Hau'oli Outskirts</v>
       </c>
       <c r="D10" t="str">
-        <v>Inkay</v>
+        <v>Slowpoke</v>
       </c>
       <c r="E10" t="str">
         <v>3-8</v>
@@ -612,7 +611,7 @@
         <v>Hau'oli Outskirts</v>
       </c>
       <c r="D11" t="str">
-        <v>Slowpoke</v>
+        <v>Alolan Meowth</v>
       </c>
       <c r="E11" t="str">
         <v>3-8</v>
@@ -632,7 +631,7 @@
         <v>Hau'oli Outskirts</v>
       </c>
       <c r="D12" t="str">
-        <v>Alolan Meowth</v>
+        <v>Tentacool</v>
       </c>
       <c r="E12" t="str">
         <v>3-8</v>
@@ -652,7 +651,7 @@
         <v>Hau'oli Outskirts</v>
       </c>
       <c r="D13" t="str">
-        <v>Tentacool</v>
+        <v>Finneon</v>
       </c>
       <c r="E13" t="str">
         <v>3-8</v>
@@ -663,19 +662,19 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" t="str">
-        <v>Route 1</v>
+        <v>Hau'oli City</v>
       </c>
       <c r="C14" t="str">
-        <v>Hau'oli Outskirts</v>
+        <v>Shopping District</v>
       </c>
       <c r="D14" t="str">
-        <v>Finneon</v>
+        <v>Furfrou</v>
       </c>
       <c r="E14" t="str">
-        <v>3-8</v>
+        <v>5-10</v>
       </c>
       <c r="F14" t="str">
         <v>20.00%</v>
@@ -692,7 +691,7 @@
         <v>Shopping District</v>
       </c>
       <c r="D15" t="str">
-        <v>Furfrou</v>
+        <v>Hypno</v>
       </c>
       <c r="E15" t="str">
         <v>5-10</v>
@@ -712,7 +711,7 @@
         <v>Shopping District</v>
       </c>
       <c r="D16" t="str">
-        <v>Hypno</v>
+        <v>Abra</v>
       </c>
       <c r="E16" t="str">
         <v>5-10</v>
@@ -732,7 +731,7 @@
         <v>Shopping District</v>
       </c>
       <c r="D17" t="str">
-        <v>Abra</v>
+        <v>Mime Jr.</v>
       </c>
       <c r="E17" t="str">
         <v>5-10</v>
@@ -752,7 +751,7 @@
         <v>Shopping District</v>
       </c>
       <c r="D18" t="str">
-        <v>Mime Jr.</v>
+        <v>Bewear</v>
       </c>
       <c r="E18" t="str">
         <v>5-10</v>
@@ -763,22 +762,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B19" t="str">
-        <v>Hau'oli City</v>
+        <v>Route 2</v>
       </c>
       <c r="C19" t="str">
-        <v>Shopping District</v>
+        <v>North</v>
       </c>
       <c r="D19" t="str">
-        <v>Bewear</v>
+        <v>Drowzee</v>
       </c>
       <c r="E19" t="str">
-        <v>5-10</v>
+        <v>6-11</v>
       </c>
       <c r="F19" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="20">
@@ -792,7 +791,7 @@
         <v>North</v>
       </c>
       <c r="D20" t="str">
-        <v>Drowzee</v>
+        <v>Makuhita</v>
       </c>
       <c r="E20" t="str">
         <v>6-11</v>
@@ -812,7 +811,7 @@
         <v>North</v>
       </c>
       <c r="D21" t="str">
-        <v>Makuhita</v>
+        <v>Spearow</v>
       </c>
       <c r="E21" t="str">
         <v>6-11</v>
@@ -832,7 +831,7 @@
         <v>North</v>
       </c>
       <c r="D22" t="str">
-        <v>Spearow</v>
+        <v>Ekans</v>
       </c>
       <c r="E22" t="str">
         <v>6-11</v>
@@ -852,7 +851,7 @@
         <v>North</v>
       </c>
       <c r="D23" t="str">
-        <v>Ekans</v>
+        <v>Growlithe</v>
       </c>
       <c r="E23" t="str">
         <v>6-11</v>
@@ -872,7 +871,7 @@
         <v>North</v>
       </c>
       <c r="D24" t="str">
-        <v>Growlithe</v>
+        <v>Smeargle</v>
       </c>
       <c r="E24" t="str">
         <v>6-11</v>
@@ -883,42 +882,42 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B25" t="str">
-        <v>Route 2</v>
+        <v>Captain Ilima</v>
       </c>
       <c r="C25" t="str">
-        <v>North</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D25" t="str">
-        <v>Smeargle</v>
+        <v>Boss</v>
       </c>
       <c r="E25" t="str">
-        <v>6-11</v>
+        <v>8-13</v>
       </c>
       <c r="F25" t="str">
-        <v>16.67%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B26" t="str">
-        <v>Captain Ilima</v>
+        <v>Hau'oli Cemetery</v>
       </c>
       <c r="C26" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D26" t="str">
-        <v>Boss</v>
+        <v>Gastly</v>
       </c>
       <c r="E26" t="str">
-        <v>8-13</v>
+        <v>9-14</v>
       </c>
       <c r="F26" t="str">
-        <v>-</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="27">
@@ -932,7 +931,7 @@
         <v>Main Area</v>
       </c>
       <c r="D27" t="str">
-        <v>Gastly</v>
+        <v>Drifloon</v>
       </c>
       <c r="E27" t="str">
         <v>9-14</v>
@@ -952,7 +951,7 @@
         <v>Main Area</v>
       </c>
       <c r="D28" t="str">
-        <v>Drifloon</v>
+        <v>Murkrow</v>
       </c>
       <c r="E28" t="str">
         <v>9-14</v>
@@ -972,7 +971,7 @@
         <v>Main Area</v>
       </c>
       <c r="D29" t="str">
-        <v>Murkrow</v>
+        <v>Misdreavus</v>
       </c>
       <c r="E29" t="str">
         <v>9-14</v>
@@ -983,22 +982,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B30" t="str">
-        <v>Hau'oli Cemetery</v>
+        <v>Ten Carat Hill</v>
       </c>
       <c r="C30" t="str">
-        <v>Main Area</v>
+        <v>Farthest Hollow</v>
       </c>
       <c r="D30" t="str">
-        <v>Misdreavus</v>
+        <v>Roggenrola</v>
       </c>
       <c r="E30" t="str">
-        <v>9-14</v>
+        <v>14-19</v>
       </c>
       <c r="F30" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="31">
@@ -1012,7 +1011,7 @@
         <v>Farthest Hollow</v>
       </c>
       <c r="D31" t="str">
-        <v>Roggenrola</v>
+        <v>Carbink</v>
       </c>
       <c r="E31" t="str">
         <v>14-19</v>
@@ -1032,7 +1031,7 @@
         <v>Farthest Hollow</v>
       </c>
       <c r="D32" t="str">
-        <v>Carbink</v>
+        <v>Spinda</v>
       </c>
       <c r="E32" t="str">
         <v>14-19</v>
@@ -1052,7 +1051,7 @@
         <v>Farthest Hollow</v>
       </c>
       <c r="D33" t="str">
-        <v>Spinda</v>
+        <v>Mawile</v>
       </c>
       <c r="E33" t="str">
         <v>14-19</v>
@@ -1072,7 +1071,7 @@
         <v>Farthest Hollow</v>
       </c>
       <c r="D34" t="str">
-        <v>Mawile</v>
+        <v>Lycanroc</v>
       </c>
       <c r="E34" t="str">
         <v>14-19</v>
@@ -1083,22 +1082,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B35" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Seaward Cave</v>
       </c>
       <c r="C35" t="str">
-        <v>Farthest Hollow</v>
+        <v>Main Area</v>
       </c>
       <c r="D35" t="str">
-        <v>Lycanroc</v>
+        <v>Barboach</v>
       </c>
       <c r="E35" t="str">
-        <v>14-19</v>
+        <v>15-20</v>
       </c>
       <c r="F35" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="36">
@@ -1112,7 +1111,7 @@
         <v>Main Area</v>
       </c>
       <c r="D36" t="str">
-        <v>Barboach</v>
+        <v>Smoochum</v>
       </c>
       <c r="E36" t="str">
         <v>15-20</v>
@@ -1132,7 +1131,7 @@
         <v>Main Area</v>
       </c>
       <c r="D37" t="str">
-        <v>Smoochum</v>
+        <v>Seel</v>
       </c>
       <c r="E37" t="str">
         <v>15-20</v>
@@ -1143,42 +1142,42 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B38" t="str">
-        <v>Seaward Cave</v>
+        <v>Kahuna Hala</v>
       </c>
       <c r="C38" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D38" t="str">
-        <v>Seel</v>
+        <v>Boss</v>
       </c>
       <c r="E38" t="str">
-        <v>15-20</v>
+        <v>17-22</v>
       </c>
       <c r="F38" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B39" t="str">
-        <v>Kahuna Hala</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C39" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D39" t="str">
-        <v>Boss</v>
+        <v>Vikavolt</v>
       </c>
       <c r="E39" t="str">
-        <v>17-22</v>
+        <v>18-23</v>
       </c>
       <c r="F39" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="40">
@@ -1192,7 +1191,7 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D40" t="str">
-        <v>Vikavolt</v>
+        <v>Ribombee</v>
       </c>
       <c r="E40" t="str">
         <v>18-23</v>
@@ -1212,7 +1211,7 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D41" t="str">
-        <v>Ribombee</v>
+        <v>Araquanid</v>
       </c>
       <c r="E41" t="str">
         <v>18-23</v>
@@ -1232,7 +1231,7 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D42" t="str">
-        <v>Araquanid</v>
+        <v>Lurantis</v>
       </c>
       <c r="E42" t="str">
         <v>18-23</v>
@@ -1252,7 +1251,7 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D43" t="str">
-        <v>Lurantis</v>
+        <v>Salazzle</v>
       </c>
       <c r="E43" t="str">
         <v>18-23</v>
@@ -1263,16 +1262,16 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B44" t="str">
         <v>Heahea Beach</v>
       </c>
       <c r="C44" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area Part 2</v>
       </c>
       <c r="D44" t="str">
-        <v>Salazzle</v>
+        <v>Alolan Marowak</v>
       </c>
       <c r="E44" t="str">
         <v>18-23</v>
@@ -1292,7 +1291,7 @@
         <v>Main Area Part 2</v>
       </c>
       <c r="D45" t="str">
-        <v>Alolan Marowak</v>
+        <v>Kommo-o</v>
       </c>
       <c r="E45" t="str">
         <v>18-23</v>
@@ -1312,7 +1311,7 @@
         <v>Main Area Part 2</v>
       </c>
       <c r="D46" t="str">
-        <v>Kommo-o</v>
+        <v>Mimikyu</v>
       </c>
       <c r="E46" t="str">
         <v>18-23</v>
@@ -1332,7 +1331,7 @@
         <v>Main Area Part 2</v>
       </c>
       <c r="D47" t="str">
-        <v>Mimikyu</v>
+        <v>Poliwhirl</v>
       </c>
       <c r="E47" t="str">
         <v>18-23</v>
@@ -1352,7 +1351,7 @@
         <v>Main Area Part 2</v>
       </c>
       <c r="D48" t="str">
-        <v>Poliwhirl</v>
+        <v>Ditto</v>
       </c>
       <c r="E48" t="str">
         <v>18-23</v>
@@ -1363,22 +1362,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B49" t="str">
-        <v>Heahea Beach</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C49" t="str">
-        <v>Main Area Part 2</v>
+        <v>Main Area</v>
       </c>
       <c r="D49" t="str">
-        <v>Ditto</v>
+        <v>Eevee</v>
       </c>
       <c r="E49" t="str">
-        <v>18-23</v>
+        <v>20-25</v>
       </c>
       <c r="F49" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="50">
@@ -1392,7 +1391,7 @@
         <v>Main Area</v>
       </c>
       <c r="D50" t="str">
-        <v>Eevee</v>
+        <v>Mareep</v>
       </c>
       <c r="E50" t="str">
         <v>20-25</v>
@@ -1412,7 +1411,7 @@
         <v>Main Area</v>
       </c>
       <c r="D51" t="str">
-        <v>Mareep</v>
+        <v>Tauros</v>
       </c>
       <c r="E51" t="str">
         <v>20-25</v>
@@ -1432,7 +1431,7 @@
         <v>Main Area</v>
       </c>
       <c r="D52" t="str">
-        <v>Tauros</v>
+        <v>Miltank</v>
       </c>
       <c r="E52" t="str">
         <v>20-25</v>
@@ -1443,42 +1442,42 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B53" t="str">
-        <v>Paniola Ranch</v>
+        <v>Daycare</v>
       </c>
       <c r="C53" t="str">
-        <v>Main Area</v>
+        <v>NPC</v>
       </c>
       <c r="D53" t="str">
-        <v>Miltank</v>
+        <v>NPC</v>
       </c>
       <c r="E53" t="str">
-        <v>20-25</v>
+        <v>-</v>
       </c>
       <c r="F53" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B54" t="str">
-        <v>Daycare</v>
+        <v>Route 5</v>
       </c>
       <c r="C54" t="str">
-        <v>NPC</v>
+        <v>Main Area</v>
       </c>
       <c r="D54" t="str">
-        <v>NPC</v>
+        <v>Noibat</v>
       </c>
       <c r="E54" t="str">
-        <v>-</v>
+        <v>23-28</v>
       </c>
       <c r="F54" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="55">
@@ -1492,10 +1491,10 @@
         <v>Main Area</v>
       </c>
       <c r="D55" t="str">
-        <v>Noibat</v>
+        <v>Fomantis</v>
       </c>
       <c r="E55" t="str">
-        <v>22-27</v>
+        <v>23-28</v>
       </c>
       <c r="F55" t="str">
         <v>33.33%</v>
@@ -1512,10 +1511,10 @@
         <v>Main Area</v>
       </c>
       <c r="D56" t="str">
-        <v>Fomantis</v>
+        <v>Bounsweet</v>
       </c>
       <c r="E56" t="str">
-        <v>22-27</v>
+        <v>23-28</v>
       </c>
       <c r="F56" t="str">
         <v>33.33%</v>
@@ -1523,22 +1522,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B57" t="str">
-        <v>Route 5</v>
+        <v>Brooklet Hill</v>
       </c>
       <c r="C57" t="str">
-        <v>Main Area</v>
+        <v>South</v>
       </c>
       <c r="D57" t="str">
-        <v>Bounsweet</v>
+        <v>Wingull</v>
       </c>
       <c r="E57" t="str">
-        <v>22-27</v>
+        <v>24-29</v>
       </c>
       <c r="F57" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="58">
@@ -1552,7 +1551,7 @@
         <v>South</v>
       </c>
       <c r="D58" t="str">
-        <v>Wingull</v>
+        <v>Lillipup</v>
       </c>
       <c r="E58" t="str">
         <v>24-29</v>
@@ -1572,7 +1571,7 @@
         <v>South</v>
       </c>
       <c r="D59" t="str">
-        <v>Lillipup</v>
+        <v>Paras</v>
       </c>
       <c r="E59" t="str">
         <v>24-29</v>
@@ -1592,7 +1591,7 @@
         <v>South</v>
       </c>
       <c r="D60" t="str">
-        <v>Paras</v>
+        <v>Goldeen</v>
       </c>
       <c r="E60" t="str">
         <v>24-29</v>
@@ -1612,7 +1611,7 @@
         <v>South</v>
       </c>
       <c r="D61" t="str">
-        <v>Goldeen</v>
+        <v>Feebas</v>
       </c>
       <c r="E61" t="str">
         <v>24-29</v>
@@ -1623,42 +1622,42 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B62" t="str">
-        <v>Brooklet Hill</v>
+        <v>Captain Lana</v>
       </c>
       <c r="C62" t="str">
-        <v>South</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D62" t="str">
-        <v>Feebas</v>
+        <v>Boss</v>
       </c>
       <c r="E62" t="str">
-        <v>24-29</v>
+        <v>26-31</v>
       </c>
       <c r="F62" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B63" t="str">
-        <v>Captain Lana</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C63" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D63" t="str">
-        <v>Boss</v>
+        <v>Cubone</v>
       </c>
       <c r="E63" t="str">
-        <v>25-30</v>
+        <v>27-32</v>
       </c>
       <c r="F63" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="64">
@@ -1672,7 +1671,7 @@
         <v>Main Area</v>
       </c>
       <c r="D64" t="str">
-        <v>Cubone</v>
+        <v>Kangaskhan</v>
       </c>
       <c r="E64" t="str">
         <v>27-32</v>
@@ -1692,7 +1691,7 @@
         <v>Main Area</v>
       </c>
       <c r="D65" t="str">
-        <v>Kangaskhan</v>
+        <v>Magby</v>
       </c>
       <c r="E65" t="str">
         <v>27-32</v>
@@ -1703,42 +1702,42 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B66" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Captain Kiawe</v>
       </c>
       <c r="C66" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D66" t="str">
-        <v>Magby</v>
+        <v>Boss</v>
       </c>
       <c r="E66" t="str">
-        <v>27-32</v>
+        <v>29-34</v>
       </c>
       <c r="F66" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B67" t="str">
-        <v>Captain Kiawe</v>
+        <v>Route 7</v>
       </c>
       <c r="C67" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D67" t="str">
-        <v>Boss</v>
+        <v>Staryu</v>
       </c>
       <c r="E67" t="str">
-        <v>28-33</v>
+        <v>30-35</v>
       </c>
       <c r="F67" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="68">
@@ -1752,7 +1751,7 @@
         <v>Main Area</v>
       </c>
       <c r="D68" t="str">
-        <v>Staryu</v>
+        <v>Pyukumuku</v>
       </c>
       <c r="E68" t="str">
         <v>30-35</v>
@@ -1772,7 +1771,7 @@
         <v>Main Area</v>
       </c>
       <c r="D69" t="str">
-        <v>Pyukumuku</v>
+        <v>Corsola</v>
       </c>
       <c r="E69" t="str">
         <v>30-35</v>
@@ -1792,7 +1791,7 @@
         <v>Main Area</v>
       </c>
       <c r="D70" t="str">
-        <v>Corsola</v>
+        <v>Mareanie</v>
       </c>
       <c r="E70" t="str">
         <v>30-35</v>
@@ -1812,7 +1811,7 @@
         <v>Main Area</v>
       </c>
       <c r="D71" t="str">
-        <v>Mareanie</v>
+        <v>Bruxish</v>
       </c>
       <c r="E71" t="str">
         <v>30-35</v>
@@ -1823,19 +1822,19 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B72" t="str">
-        <v>Route 7</v>
+        <v>Route 8</v>
       </c>
       <c r="C72" t="str">
-        <v>Main Area</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D72" t="str">
-        <v>Bruxish</v>
+        <v>Omanyte</v>
       </c>
       <c r="E72" t="str">
-        <v>30-35</v>
+        <v>32-37</v>
       </c>
       <c r="F72" t="str">
         <v>20.00%</v>
@@ -1852,10 +1851,10 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D73" t="str">
-        <v>Omanyte</v>
+        <v>Kabuto</v>
       </c>
       <c r="E73" t="str">
-        <v>31-36</v>
+        <v>32-37</v>
       </c>
       <c r="F73" t="str">
         <v>20.00%</v>
@@ -1872,10 +1871,10 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D74" t="str">
-        <v>Kabuto</v>
+        <v>Lileep</v>
       </c>
       <c r="E74" t="str">
-        <v>31-36</v>
+        <v>32-37</v>
       </c>
       <c r="F74" t="str">
         <v>20.00%</v>
@@ -1892,10 +1891,10 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D75" t="str">
-        <v>Lileep</v>
+        <v>Anorith</v>
       </c>
       <c r="E75" t="str">
-        <v>31-36</v>
+        <v>32-37</v>
       </c>
       <c r="F75" t="str">
         <v>20.00%</v>
@@ -1912,10 +1911,10 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D76" t="str">
-        <v>Anorith</v>
+        <v>Cranidos</v>
       </c>
       <c r="E76" t="str">
-        <v>31-36</v>
+        <v>32-37</v>
       </c>
       <c r="F76" t="str">
         <v>20.00%</v>
@@ -1923,19 +1922,19 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B77" t="str">
         <v>Route 8</v>
       </c>
       <c r="C77" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D77" t="str">
-        <v>Cranidos</v>
+        <v>Shieldon</v>
       </c>
       <c r="E77" t="str">
-        <v>31-36</v>
+        <v>32-37</v>
       </c>
       <c r="F77" t="str">
         <v>20.00%</v>
@@ -1952,10 +1951,10 @@
         <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D78" t="str">
-        <v>Shieldon</v>
+        <v>Archen</v>
       </c>
       <c r="E78" t="str">
-        <v>31-36</v>
+        <v>32-37</v>
       </c>
       <c r="F78" t="str">
         <v>20.00%</v>
@@ -1972,10 +1971,10 @@
         <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D79" t="str">
-        <v>Archen</v>
+        <v>Tirtouga</v>
       </c>
       <c r="E79" t="str">
-        <v>31-36</v>
+        <v>32-37</v>
       </c>
       <c r="F79" t="str">
         <v>20.00%</v>
@@ -1992,10 +1991,10 @@
         <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D80" t="str">
-        <v>Tirtouga</v>
+        <v>Tyrunt</v>
       </c>
       <c r="E80" t="str">
-        <v>31-36</v>
+        <v>32-37</v>
       </c>
       <c r="F80" t="str">
         <v>20.00%</v>
@@ -2012,10 +2011,10 @@
         <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D81" t="str">
-        <v>Tyrunt</v>
+        <v>Amaura</v>
       </c>
       <c r="E81" t="str">
-        <v>31-36</v>
+        <v>32-37</v>
       </c>
       <c r="F81" t="str">
         <v>20.00%</v>
@@ -2023,22 +2022,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B82" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C82" t="str">
-        <v>Fossil Restoration Center Part 2</v>
+        <v>North</v>
       </c>
       <c r="D82" t="str">
-        <v>Amaura</v>
+        <v>Trumbeak</v>
       </c>
       <c r="E82" t="str">
-        <v>31-36</v>
+        <v>33-38</v>
       </c>
       <c r="F82" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="83">
@@ -2052,7 +2051,7 @@
         <v>North</v>
       </c>
       <c r="D83" t="str">
-        <v>Trumbeak</v>
+        <v>Steenee</v>
       </c>
       <c r="E83" t="str">
         <v>33-38</v>
@@ -2072,7 +2071,7 @@
         <v>North</v>
       </c>
       <c r="D84" t="str">
-        <v>Steenee</v>
+        <v>Comfey</v>
       </c>
       <c r="E84" t="str">
         <v>33-38</v>
@@ -2092,7 +2091,7 @@
         <v>North</v>
       </c>
       <c r="D85" t="str">
-        <v>Comfey</v>
+        <v>Hoothoot</v>
       </c>
       <c r="E85" t="str">
         <v>33-38</v>
@@ -2112,7 +2111,7 @@
         <v>North</v>
       </c>
       <c r="D86" t="str">
-        <v>Hoothoot</v>
+        <v>Oranguru</v>
       </c>
       <c r="E86" t="str">
         <v>33-38</v>
@@ -2132,7 +2131,7 @@
         <v>North</v>
       </c>
       <c r="D87" t="str">
-        <v>Oranguru</v>
+        <v>Bounsweet</v>
       </c>
       <c r="E87" t="str">
         <v>33-38</v>
@@ -2143,22 +2142,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B88" t="str">
         <v>Lush Jungle</v>
       </c>
       <c r="C88" t="str">
-        <v>North</v>
+        <v>East Cave</v>
       </c>
       <c r="D88" t="str">
-        <v>Bounsweet</v>
+        <v>Golbat</v>
       </c>
       <c r="E88" t="str">
-        <v>33-38</v>
+        <v>35-40</v>
       </c>
       <c r="F88" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="89">
@@ -2172,10 +2171,10 @@
         <v>East Cave</v>
       </c>
       <c r="D89" t="str">
-        <v>Golbat</v>
+        <v>Salandit</v>
       </c>
       <c r="E89" t="str">
-        <v>34-39</v>
+        <v>35-40</v>
       </c>
       <c r="F89" t="str">
         <v>20.00%</v>
@@ -2192,10 +2191,10 @@
         <v>East Cave</v>
       </c>
       <c r="D90" t="str">
-        <v>Salandit</v>
+        <v>Larvesta</v>
       </c>
       <c r="E90" t="str">
-        <v>34-39</v>
+        <v>35-40</v>
       </c>
       <c r="F90" t="str">
         <v>20.00%</v>
@@ -2212,10 +2211,10 @@
         <v>East Cave</v>
       </c>
       <c r="D91" t="str">
-        <v>Larvesta</v>
+        <v>Oranguru</v>
       </c>
       <c r="E91" t="str">
-        <v>34-39</v>
+        <v>35-40</v>
       </c>
       <c r="F91" t="str">
         <v>20.00%</v>
@@ -2232,10 +2231,10 @@
         <v>East Cave</v>
       </c>
       <c r="D92" t="str">
-        <v>Oranguru</v>
+        <v>Passimian</v>
       </c>
       <c r="E92" t="str">
-        <v>34-39</v>
+        <v>35-40</v>
       </c>
       <c r="F92" t="str">
         <v>20.00%</v>
@@ -2243,42 +2242,42 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B93" t="str">
-        <v>Lush Jungle</v>
+        <v>Captain Mallow</v>
       </c>
       <c r="C93" t="str">
-        <v>East Cave</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D93" t="str">
-        <v>Passimian</v>
+        <v>Boss</v>
       </c>
       <c r="E93" t="str">
-        <v>34-39</v>
+        <v>36-41</v>
       </c>
       <c r="F93" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B94" t="str">
-        <v>Captain Mallow</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C94" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D94" t="str">
-        <v>Boss</v>
+        <v>Zubat</v>
       </c>
       <c r="E94" t="str">
-        <v>36-41</v>
+        <v>38-43</v>
       </c>
       <c r="F94" t="str">
-        <v>-</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="95">
@@ -2292,10 +2291,10 @@
         <v>Main Area</v>
       </c>
       <c r="D95" t="str">
-        <v>Zubat</v>
+        <v>Alolan Diglett</v>
       </c>
       <c r="E95" t="str">
-        <v>37-42</v>
+        <v>38-43</v>
       </c>
       <c r="F95" t="str">
         <v>25.00%</v>
@@ -2312,10 +2311,10 @@
         <v>Main Area</v>
       </c>
       <c r="D96" t="str">
-        <v>Alolan Diglett</v>
+        <v>Kecleon</v>
       </c>
       <c r="E96" t="str">
-        <v>37-42</v>
+        <v>38-43</v>
       </c>
       <c r="F96" t="str">
         <v>25.00%</v>
@@ -2332,10 +2331,10 @@
         <v>Main Area</v>
       </c>
       <c r="D97" t="str">
-        <v>Kecleon</v>
+        <v>Larvitar</v>
       </c>
       <c r="E97" t="str">
-        <v>37-42</v>
+        <v>38-43</v>
       </c>
       <c r="F97" t="str">
         <v>25.00%</v>
@@ -2343,22 +2342,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B98" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C98" t="str">
         <v>Main Area</v>
       </c>
       <c r="D98" t="str">
-        <v>Larvitar</v>
+        <v>Gumshoos</v>
       </c>
       <c r="E98" t="str">
-        <v>37-42</v>
+        <v>42-47</v>
       </c>
       <c r="F98" t="str">
-        <v>25.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="99">
@@ -2372,10 +2371,10 @@
         <v>Main Area</v>
       </c>
       <c r="D99" t="str">
-        <v>Gumshoos</v>
+        <v>Wingull</v>
       </c>
       <c r="E99" t="str">
-        <v>43-48</v>
+        <v>42-47</v>
       </c>
       <c r="F99" t="str">
         <v>12.50%</v>
@@ -2392,10 +2391,10 @@
         <v>Main Area</v>
       </c>
       <c r="D100" t="str">
-        <v>Wingull</v>
+        <v>Magikarp</v>
       </c>
       <c r="E100" t="str">
-        <v>43-48</v>
+        <v>42-47</v>
       </c>
       <c r="F100" t="str">
         <v>12.50%</v>
@@ -2412,10 +2411,10 @@
         <v>Main Area</v>
       </c>
       <c r="D101" t="str">
-        <v>Magikarp</v>
+        <v>Stufful</v>
       </c>
       <c r="E101" t="str">
-        <v>43-48</v>
+        <v>42-47</v>
       </c>
       <c r="F101" t="str">
         <v>12.50%</v>
@@ -2432,10 +2431,10 @@
         <v>Main Area</v>
       </c>
       <c r="D102" t="str">
-        <v>Stufful</v>
+        <v>Chinchou</v>
       </c>
       <c r="E102" t="str">
-        <v>43-48</v>
+        <v>42-47</v>
       </c>
       <c r="F102" t="str">
         <v>12.50%</v>
@@ -2452,10 +2451,10 @@
         <v>Main Area</v>
       </c>
       <c r="D103" t="str">
-        <v>Chinchou</v>
+        <v>Alolan Raticate</v>
       </c>
       <c r="E103" t="str">
-        <v>43-48</v>
+        <v>42-47</v>
       </c>
       <c r="F103" t="str">
         <v>12.50%</v>
@@ -2472,10 +2471,10 @@
         <v>Main Area</v>
       </c>
       <c r="D104" t="str">
-        <v>Alolan Raticate</v>
+        <v>Natu</v>
       </c>
       <c r="E104" t="str">
-        <v>43-48</v>
+        <v>42-47</v>
       </c>
       <c r="F104" t="str">
         <v>12.50%</v>
@@ -2492,10 +2491,10 @@
         <v>Main Area</v>
       </c>
       <c r="D105" t="str">
-        <v>Natu</v>
+        <v>Nosepass</v>
       </c>
       <c r="E105" t="str">
-        <v>43-48</v>
+        <v>42-47</v>
       </c>
       <c r="F105" t="str">
         <v>12.50%</v>
@@ -2503,42 +2502,42 @@
     </row>
     <row r="106">
       <c r="A106">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B106" t="str">
-        <v>Akala Outskirts</v>
+        <v>Kahuna Olivia</v>
       </c>
       <c r="C106" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D106" t="str">
-        <v>Nosepass</v>
+        <v>Boss</v>
       </c>
       <c r="E106" t="str">
-        <v>43-48</v>
+        <v>44-49</v>
       </c>
       <c r="F106" t="str">
-        <v>12.50%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="107">
       <c r="A107">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B107" t="str">
-        <v>Kahuna Olivia</v>
+        <v>Malie City</v>
       </c>
       <c r="C107" t="str">
-        <v>Boss Battle</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D107" t="str">
-        <v>Boss</v>
+        <v>Magnemite</v>
       </c>
       <c r="E107" t="str">
-        <v>44-49</v>
+        <v>47-52</v>
       </c>
       <c r="F107" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="108">
@@ -2552,7 +2551,7 @@
         <v>Outer Cape</v>
       </c>
       <c r="D108" t="str">
-        <v>Magnemite</v>
+        <v>Alolan Grimer</v>
       </c>
       <c r="E108" t="str">
         <v>47-52</v>
@@ -2572,7 +2571,7 @@
         <v>Outer Cape</v>
       </c>
       <c r="D109" t="str">
-        <v>Alolan Grimer</v>
+        <v>Trubbish</v>
       </c>
       <c r="E109" t="str">
         <v>47-52</v>
@@ -2592,7 +2591,7 @@
         <v>Outer Cape</v>
       </c>
       <c r="D110" t="str">
-        <v>Trubbish</v>
+        <v>Minccino</v>
       </c>
       <c r="E110" t="str">
         <v>47-52</v>
@@ -2612,7 +2611,7 @@
         <v>Outer Cape</v>
       </c>
       <c r="D111" t="str">
-        <v>Minccino</v>
+        <v>Masquerain</v>
       </c>
       <c r="E111" t="str">
         <v>47-52</v>
@@ -2623,22 +2622,22 @@
     </row>
     <row r="112">
       <c r="A112">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B112" t="str">
-        <v>Malie City</v>
+        <v>Route 10</v>
       </c>
       <c r="C112" t="str">
-        <v>Outer Cape</v>
+        <v>Main Area</v>
       </c>
       <c r="D112" t="str">
-        <v>Masquerain</v>
+        <v>Ledian</v>
       </c>
       <c r="E112" t="str">
-        <v>47-52</v>
+        <v>50-55</v>
       </c>
       <c r="F112" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="113">
@@ -2652,7 +2651,7 @@
         <v>Main Area</v>
       </c>
       <c r="D113" t="str">
-        <v>Ledian</v>
+        <v>Ariados</v>
       </c>
       <c r="E113" t="str">
         <v>50-55</v>
@@ -2672,7 +2671,7 @@
         <v>Main Area</v>
       </c>
       <c r="D114" t="str">
-        <v>Ariados</v>
+        <v>Crabrawler</v>
       </c>
       <c r="E114" t="str">
         <v>50-55</v>
@@ -2692,7 +2691,7 @@
         <v>Main Area</v>
       </c>
       <c r="D115" t="str">
-        <v>Crabrawler</v>
+        <v>Fearow</v>
       </c>
       <c r="E115" t="str">
         <v>50-55</v>
@@ -2712,7 +2711,7 @@
         <v>Main Area</v>
       </c>
       <c r="D116" t="str">
-        <v>Fearow</v>
+        <v>Skarmory</v>
       </c>
       <c r="E116" t="str">
         <v>50-55</v>
@@ -2732,7 +2731,7 @@
         <v>Main Area</v>
       </c>
       <c r="D117" t="str">
-        <v>Skarmory</v>
+        <v>Pancham</v>
       </c>
       <c r="E117" t="str">
         <v>50-55</v>
@@ -2743,22 +2742,22 @@
     </row>
     <row r="118">
       <c r="A118">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B118" t="str">
-        <v>Route 10</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C118" t="str">
-        <v>Main Area</v>
+        <v>East</v>
       </c>
       <c r="D118" t="str">
-        <v>Pancham</v>
+        <v>Cleffa</v>
       </c>
       <c r="E118" t="str">
-        <v>50-55</v>
+        <v>51-56</v>
       </c>
       <c r="F118" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="119">
@@ -2772,10 +2771,10 @@
         <v>East</v>
       </c>
       <c r="D119" t="str">
-        <v>Cleffa</v>
+        <v>Elgyem</v>
       </c>
       <c r="E119" t="str">
-        <v>52-57</v>
+        <v>51-56</v>
       </c>
       <c r="F119" t="str">
         <v>25.00%</v>
@@ -2792,10 +2791,10 @@
         <v>East</v>
       </c>
       <c r="D120" t="str">
-        <v>Elgyem</v>
+        <v>Beldum</v>
       </c>
       <c r="E120" t="str">
-        <v>52-57</v>
+        <v>51-56</v>
       </c>
       <c r="F120" t="str">
         <v>25.00%</v>
@@ -2812,10 +2811,10 @@
         <v>East</v>
       </c>
       <c r="D121" t="str">
-        <v>Beldum</v>
+        <v>Minior</v>
       </c>
       <c r="E121" t="str">
-        <v>52-57</v>
+        <v>51-56</v>
       </c>
       <c r="F121" t="str">
         <v>25.00%</v>
@@ -2823,42 +2822,42 @@
     </row>
     <row r="122">
       <c r="A122">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B122" t="str">
-        <v>Mount Hokulani</v>
+        <v>Captain Sophocles</v>
       </c>
       <c r="C122" t="str">
-        <v>East</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D122" t="str">
-        <v>Minior</v>
+        <v>Boss</v>
       </c>
       <c r="E122" t="str">
-        <v>52-57</v>
+        <v>53-58</v>
       </c>
       <c r="F122" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="123">
       <c r="A123">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B123" t="str">
-        <v>Captain Sophocles</v>
+        <v>Route 11</v>
       </c>
       <c r="C123" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D123" t="str">
-        <v>Boss</v>
+        <v>Shiinotic</v>
       </c>
       <c r="E123" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="F123" t="str">
-        <v>-</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="124">
@@ -2872,10 +2871,10 @@
         <v>Main Area</v>
       </c>
       <c r="D124" t="str">
-        <v>Shiinotic</v>
+        <v>Parasect</v>
       </c>
       <c r="E124" t="str">
-        <v>55-60</v>
+        <v>54-59</v>
       </c>
       <c r="F124" t="str">
         <v>11.11%</v>
@@ -2892,10 +2891,10 @@
         <v>Main Area</v>
       </c>
       <c r="D125" t="str">
-        <v>Parasect</v>
+        <v>Komala</v>
       </c>
       <c r="E125" t="str">
-        <v>55-60</v>
+        <v>54-59</v>
       </c>
       <c r="F125" t="str">
         <v>11.11%</v>
@@ -2912,10 +2911,10 @@
         <v>Main Area</v>
       </c>
       <c r="D126" t="str">
-        <v>Komala</v>
+        <v>Houndoom</v>
       </c>
       <c r="E126" t="str">
-        <v>55-60</v>
+        <v>54-59</v>
       </c>
       <c r="F126" t="str">
         <v>11.11%</v>
@@ -2932,10 +2931,10 @@
         <v>Main Area</v>
       </c>
       <c r="D127" t="str">
-        <v>Houndoom</v>
+        <v>Manectric</v>
       </c>
       <c r="E127" t="str">
-        <v>55-60</v>
+        <v>54-59</v>
       </c>
       <c r="F127" t="str">
         <v>11.11%</v>
@@ -2952,10 +2951,10 @@
         <v>Main Area</v>
       </c>
       <c r="D128" t="str">
-        <v>Manectric</v>
+        <v>Scraggy</v>
       </c>
       <c r="E128" t="str">
-        <v>55-60</v>
+        <v>54-59</v>
       </c>
       <c r="F128" t="str">
         <v>11.11%</v>
@@ -2972,10 +2971,10 @@
         <v>Main Area</v>
       </c>
       <c r="D129" t="str">
-        <v>Scraggy</v>
+        <v>Bisharp</v>
       </c>
       <c r="E129" t="str">
-        <v>55-60</v>
+        <v>54-59</v>
       </c>
       <c r="F129" t="str">
         <v>11.11%</v>
@@ -2992,10 +2991,10 @@
         <v>Main Area</v>
       </c>
       <c r="D130" t="str">
-        <v>Bisharp</v>
+        <v>Machop</v>
       </c>
       <c r="E130" t="str">
-        <v>55-60</v>
+        <v>54-59</v>
       </c>
       <c r="F130" t="str">
         <v>11.11%</v>
@@ -3012,10 +3011,10 @@
         <v>Main Area</v>
       </c>
       <c r="D131" t="str">
-        <v>Machop</v>
+        <v>Hawlucha</v>
       </c>
       <c r="E131" t="str">
-        <v>55-60</v>
+        <v>54-59</v>
       </c>
       <c r="F131" t="str">
         <v>11.11%</v>
@@ -3023,22 +3022,22 @@
     </row>
     <row r="132">
       <c r="A132">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B132" t="str">
-        <v>Route 11</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C132" t="str">
         <v>Main Area</v>
       </c>
       <c r="D132" t="str">
-        <v>Hawlucha</v>
+        <v>Alolan Dugtrio</v>
       </c>
       <c r="E132" t="str">
-        <v>55-60</v>
+        <v>57-62</v>
       </c>
       <c r="F132" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="133">
@@ -3052,10 +3051,10 @@
         <v>Main Area</v>
       </c>
       <c r="D133" t="str">
-        <v>Alolan Dugtrio</v>
+        <v>Sandile</v>
       </c>
       <c r="E133" t="str">
-        <v>58-63</v>
+        <v>57-62</v>
       </c>
       <c r="F133" t="str">
         <v>20.00%</v>
@@ -3072,10 +3071,10 @@
         <v>Main Area</v>
       </c>
       <c r="D134" t="str">
-        <v>Sandile</v>
+        <v>Krokorok</v>
       </c>
       <c r="E134" t="str">
-        <v>58-63</v>
+        <v>57-62</v>
       </c>
       <c r="F134" t="str">
         <v>20.00%</v>
@@ -3092,10 +3091,10 @@
         <v>Main Area</v>
       </c>
       <c r="D135" t="str">
-        <v>Krokorok</v>
+        <v>Staryu</v>
       </c>
       <c r="E135" t="str">
-        <v>58-63</v>
+        <v>57-62</v>
       </c>
       <c r="F135" t="str">
         <v>20.00%</v>
@@ -3112,10 +3111,10 @@
         <v>Main Area</v>
       </c>
       <c r="D136" t="str">
-        <v>Staryu</v>
+        <v>Sandygast</v>
       </c>
       <c r="E136" t="str">
-        <v>58-63</v>
+        <v>57-62</v>
       </c>
       <c r="F136" t="str">
         <v>20.00%</v>
@@ -3123,22 +3122,22 @@
     </row>
     <row r="137">
       <c r="A137">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B137" t="str">
-        <v>Haina Desert</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C137" t="str">
         <v>Main Area</v>
       </c>
       <c r="D137" t="str">
-        <v>Sandygast</v>
+        <v>Graveler</v>
       </c>
       <c r="E137" t="str">
-        <v>58-63</v>
+        <v>59-64</v>
       </c>
       <c r="F137" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="138">
@@ -3152,7 +3151,7 @@
         <v>Main Area</v>
       </c>
       <c r="D138" t="str">
-        <v>Graveler</v>
+        <v>Bruxish</v>
       </c>
       <c r="E138" t="str">
         <v>59-64</v>
@@ -3172,7 +3171,7 @@
         <v>Main Area</v>
       </c>
       <c r="D139" t="str">
-        <v>Bruxish</v>
+        <v>Absol</v>
       </c>
       <c r="E139" t="str">
         <v>59-64</v>
@@ -3192,7 +3191,7 @@
         <v>Main Area</v>
       </c>
       <c r="D140" t="str">
-        <v>Absol</v>
+        <v>Snorunt</v>
       </c>
       <c r="E140" t="str">
         <v>59-64</v>
@@ -3212,7 +3211,7 @@
         <v>Main Area</v>
       </c>
       <c r="D141" t="str">
-        <v>Snorunt</v>
+        <v>Alolan Sandshrew</v>
       </c>
       <c r="E141" t="str">
         <v>59-64</v>
@@ -3232,7 +3231,7 @@
         <v>Main Area</v>
       </c>
       <c r="D142" t="str">
-        <v>Alolan Sandshrew</v>
+        <v>Alolan Vulpix</v>
       </c>
       <c r="E142" t="str">
         <v>59-64</v>
@@ -3243,22 +3242,22 @@
     </row>
     <row r="143">
       <c r="A143">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B143" t="str">
-        <v>Tapu Village</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C143" t="str">
-        <v>Main Area</v>
+        <v>Abandoned Site</v>
       </c>
       <c r="D143" t="str">
-        <v>Alolan Vulpix</v>
+        <v>Haunter</v>
       </c>
       <c r="E143" t="str">
-        <v>59-64</v>
+        <v>62-67</v>
       </c>
       <c r="F143" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="144">
@@ -3272,7 +3271,7 @@
         <v>Abandoned Site</v>
       </c>
       <c r="D144" t="str">
-        <v>Haunter</v>
+        <v>Klefki</v>
       </c>
       <c r="E144" t="str">
         <v>62-67</v>
@@ -3292,7 +3291,7 @@
         <v>Abandoned Site</v>
       </c>
       <c r="D145" t="str">
-        <v>Klefki</v>
+        <v>Shuppet</v>
       </c>
       <c r="E145" t="str">
         <v>62-67</v>
@@ -3312,7 +3311,7 @@
         <v>Abandoned Site</v>
       </c>
       <c r="D146" t="str">
-        <v>Shuppet</v>
+        <v>Boldore</v>
       </c>
       <c r="E146" t="str">
         <v>62-67</v>
@@ -3323,30 +3322,30 @@
     </row>
     <row r="147">
       <c r="A147">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B147" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Captain Acerola</v>
       </c>
       <c r="C147" t="str">
-        <v>Abandoned Site</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D147" t="str">
-        <v>Boldore</v>
+        <v>Boss</v>
       </c>
       <c r="E147" t="str">
-        <v>62-67</v>
+        <v>63-68</v>
       </c>
       <c r="F147" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="148">
       <c r="A148">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B148" t="str">
-        <v>Captain Acerola</v>
+        <v>Kahuna Nanu</v>
       </c>
       <c r="C148" t="str">
         <v>Boss Battle</v>
@@ -3355,7 +3354,7 @@
         <v>Boss</v>
       </c>
       <c r="E148" t="str">
-        <v>64-69</v>
+        <v>68-73</v>
       </c>
       <c r="F148" t="str">
         <v>-</v>
@@ -3363,22 +3362,22 @@
     </row>
     <row r="149">
       <c r="A149">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B149" t="str">
-        <v>Kahuna Nanu</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C149" t="str">
-        <v>Boss Battle</v>
+        <v>Main</v>
       </c>
       <c r="D149" t="str">
-        <v>Boss</v>
+        <v>Steenee</v>
       </c>
       <c r="E149" t="str">
-        <v>68-73</v>
+        <v>69-74</v>
       </c>
       <c r="F149" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="150">
@@ -3392,7 +3391,7 @@
         <v>Main</v>
       </c>
       <c r="D150" t="str">
-        <v>Steenee</v>
+        <v>Shellos</v>
       </c>
       <c r="E150" t="str">
         <v>69-74</v>
@@ -3412,7 +3411,7 @@
         <v>Main</v>
       </c>
       <c r="D151" t="str">
-        <v>Shellos</v>
+        <v>Dhelmise</v>
       </c>
       <c r="E151" t="str">
         <v>69-74</v>
@@ -3423,22 +3422,22 @@
     </row>
     <row r="152">
       <c r="A152">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B152" t="str">
-        <v>Seafolk Village</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C152" t="str">
-        <v>Main</v>
+        <v>Main Area</v>
       </c>
       <c r="D152" t="str">
-        <v>Dhelmise</v>
+        <v>Tentacruel</v>
       </c>
       <c r="E152" t="str">
-        <v>69-74</v>
+        <v>71-76</v>
       </c>
       <c r="F152" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="153">
@@ -3452,7 +3451,7 @@
         <v>Main Area</v>
       </c>
       <c r="D153" t="str">
-        <v>Tentacruel</v>
+        <v>Lumineon</v>
       </c>
       <c r="E153" t="str">
         <v>71-76</v>
@@ -3472,7 +3471,7 @@
         <v>Main Area</v>
       </c>
       <c r="D154" t="str">
-        <v>Lumineon</v>
+        <v>Lapras</v>
       </c>
       <c r="E154" t="str">
         <v>71-76</v>
@@ -3492,7 +3491,7 @@
         <v>Main Area</v>
       </c>
       <c r="D155" t="str">
-        <v>Lapras</v>
+        <v>Noivern</v>
       </c>
       <c r="E155" t="str">
         <v>71-76</v>
@@ -3512,7 +3511,7 @@
         <v>Main Area</v>
       </c>
       <c r="D156" t="str">
-        <v>Noivern</v>
+        <v>Druddigon</v>
       </c>
       <c r="E156" t="str">
         <v>71-76</v>
@@ -3523,19 +3522,19 @@
     </row>
     <row r="157">
       <c r="A157">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B157" t="str">
-        <v>Poni Wilds</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C157" t="str">
         <v>Main Area</v>
       </c>
       <c r="D157" t="str">
-        <v>Druddigon</v>
+        <v>Wimpod</v>
       </c>
       <c r="E157" t="str">
-        <v>71-76</v>
+        <v>72-77</v>
       </c>
       <c r="F157" t="str">
         <v>20.00%</v>
@@ -3552,7 +3551,7 @@
         <v>Main Area</v>
       </c>
       <c r="D158" t="str">
-        <v>Wimpod</v>
+        <v>Relicanth</v>
       </c>
       <c r="E158" t="str">
         <v>72-77</v>
@@ -3572,7 +3571,7 @@
         <v>Main Area</v>
       </c>
       <c r="D159" t="str">
-        <v>Relicanth</v>
+        <v>Wailmer</v>
       </c>
       <c r="E159" t="str">
         <v>72-77</v>
@@ -3592,7 +3591,7 @@
         <v>Main Area</v>
       </c>
       <c r="D160" t="str">
-        <v>Wailmer</v>
+        <v>Carvanha</v>
       </c>
       <c r="E160" t="str">
         <v>72-77</v>
@@ -3612,7 +3611,7 @@
         <v>Main Area</v>
       </c>
       <c r="D161" t="str">
-        <v>Carvanha</v>
+        <v>Sharpedo</v>
       </c>
       <c r="E161" t="str">
         <v>72-77</v>
@@ -3623,22 +3622,22 @@
     </row>
     <row r="162">
       <c r="A162">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B162" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C162" t="str">
         <v>Main Area</v>
       </c>
       <c r="D162" t="str">
-        <v>Sharpedo</v>
+        <v>Pelipper</v>
       </c>
       <c r="E162" t="str">
-        <v>72-77</v>
+        <v>74-79</v>
       </c>
       <c r="F162" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="163">
@@ -3652,7 +3651,7 @@
         <v>Main Area</v>
       </c>
       <c r="D163" t="str">
-        <v>Pelipper</v>
+        <v>Pinsir</v>
       </c>
       <c r="E163" t="str">
         <v>74-79</v>
@@ -3672,7 +3671,7 @@
         <v>Main Area</v>
       </c>
       <c r="D164" t="str">
-        <v>Pinsir</v>
+        <v>Gastrodon</v>
       </c>
       <c r="E164" t="str">
         <v>74-79</v>
@@ -3692,7 +3691,7 @@
         <v>Main Area</v>
       </c>
       <c r="D165" t="str">
-        <v>Gastrodon</v>
+        <v>Exeggcute</v>
       </c>
       <c r="E165" t="str">
         <v>74-79</v>
@@ -3712,7 +3711,7 @@
         <v>Main Area</v>
       </c>
       <c r="D166" t="str">
-        <v>Exeggcute</v>
+        <v>Tropius</v>
       </c>
       <c r="E166" t="str">
         <v>74-79</v>
@@ -3732,7 +3731,7 @@
         <v>Main Area</v>
       </c>
       <c r="D167" t="str">
-        <v>Tropius</v>
+        <v>Alolan Exeggutor</v>
       </c>
       <c r="E167" t="str">
         <v>74-79</v>
@@ -3743,22 +3742,22 @@
     </row>
     <row r="168">
       <c r="A168">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B168" t="str">
-        <v>Exeggutor Island</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C168" t="str">
-        <v>Main Area</v>
+        <v>Outside</v>
       </c>
       <c r="D168" t="str">
-        <v>Alolan Exeggutor</v>
+        <v>Machoke</v>
       </c>
       <c r="E168" t="str">
-        <v>74-79</v>
+        <v>75-80</v>
       </c>
       <c r="F168" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="169">
@@ -3772,7 +3771,7 @@
         <v>Outside</v>
       </c>
       <c r="D169" t="str">
-        <v>Machoke</v>
+        <v>Mienfoo</v>
       </c>
       <c r="E169" t="str">
         <v>75-80</v>
@@ -3792,7 +3791,7 @@
         <v>Outside</v>
       </c>
       <c r="D170" t="str">
-        <v>Mienfoo</v>
+        <v>Jangmo-o</v>
       </c>
       <c r="E170" t="str">
         <v>75-80</v>
@@ -3803,30 +3802,30 @@
     </row>
     <row r="171">
       <c r="A171">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B171" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Captain Kommo-o</v>
       </c>
       <c r="C171" t="str">
-        <v>Outside</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D171" t="str">
-        <v>Jangmo-o</v>
+        <v>Boss</v>
       </c>
       <c r="E171" t="str">
-        <v>75-80</v>
+        <v>78-83</v>
       </c>
       <c r="F171" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="172">
       <c r="A172">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B172" t="str">
-        <v>Captain Kommo-o</v>
+        <v>Captain Mina</v>
       </c>
       <c r="C172" t="str">
         <v>Boss Battle</v>
@@ -3835,7 +3834,7 @@
         <v>Boss</v>
       </c>
       <c r="E172" t="str">
-        <v>78-83</v>
+        <v>80-85</v>
       </c>
       <c r="F172" t="str">
         <v>-</v>
@@ -3843,10 +3842,10 @@
     </row>
     <row r="173">
       <c r="A173">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B173" t="str">
-        <v>Captain Mina</v>
+        <v>Kahuna Hapu</v>
       </c>
       <c r="C173" t="str">
         <v>Boss Battle</v>
@@ -3855,7 +3854,7 @@
         <v>Boss</v>
       </c>
       <c r="E173" t="str">
-        <v>80-85</v>
+        <v>81-86</v>
       </c>
       <c r="F173" t="str">
         <v>-</v>
@@ -3863,22 +3862,22 @@
     </row>
     <row r="174">
       <c r="A174">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B174" t="str">
-        <v>Kahuna Hapu</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C174" t="str">
-        <v>Boss Battle</v>
+        <v>Cave</v>
       </c>
       <c r="D174" t="str">
-        <v>Boss</v>
+        <v>Drampa</v>
       </c>
       <c r="E174" t="str">
-        <v>81-86</v>
+        <v>83-88</v>
       </c>
       <c r="F174" t="str">
-        <v>-</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="175">
@@ -3892,7 +3891,7 @@
         <v>Cave</v>
       </c>
       <c r="D175" t="str">
-        <v>Drampa</v>
+        <v>Glalie</v>
       </c>
       <c r="E175" t="str">
         <v>83-88</v>
@@ -3912,7 +3911,7 @@
         <v>Cave</v>
       </c>
       <c r="D176" t="str">
-        <v>Glalie</v>
+        <v>Sneasel</v>
       </c>
       <c r="E176" t="str">
         <v>83-88</v>
@@ -3932,7 +3931,7 @@
         <v>Cave</v>
       </c>
       <c r="D177" t="str">
-        <v>Sneasel</v>
+        <v>Crabominable</v>
       </c>
       <c r="E177" t="str">
         <v>83-88</v>
@@ -3943,30 +3942,30 @@
     </row>
     <row r="178">
       <c r="A178">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B178" t="str">
-        <v>Mount Lanakila</v>
+        <v>Alola Pokemon League</v>
       </c>
       <c r="C178" t="str">
-        <v>Cave</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D178" t="str">
-        <v>Crabominable</v>
+        <v>Boss</v>
       </c>
       <c r="E178" t="str">
-        <v>83-88</v>
+        <v>84-89</v>
       </c>
       <c r="F178" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="179">
       <c r="A179">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B179" t="str">
-        <v>Alola Pokemon League</v>
+        <v>Champion Hau</v>
       </c>
       <c r="C179" t="str">
         <v>Boss Battle</v>
@@ -3975,7 +3974,7 @@
         <v>Boss</v>
       </c>
       <c r="E179" t="str">
-        <v>84-89</v>
+        <v>85-90</v>
       </c>
       <c r="F179" t="str">
         <v>-</v>
@@ -3983,22 +3982,22 @@
     </row>
     <row r="180">
       <c r="A180">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B180" t="str">
-        <v>Champion Hau</v>
+        <v>Route 6</v>
       </c>
       <c r="C180" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D180" t="str">
-        <v>Boss</v>
+        <v>Eevee</v>
       </c>
       <c r="E180" t="str">
         <v>85-90</v>
       </c>
       <c r="F180" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="181">
@@ -4012,30 +4011,30 @@
         <v>Main Area</v>
       </c>
       <c r="D181" t="str">
-        <v>Special Encounter</v>
+        <v>Mudbray</v>
       </c>
       <c r="E181" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F181" t="str">
-        <v>100%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="182">
       <c r="A182">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B182" t="str">
-        <v>Royal Avenue</v>
+        <v>Route 6</v>
       </c>
       <c r="C182" t="str">
         <v>Main Area</v>
       </c>
       <c r="D182" t="str">
-        <v>Oricorio</v>
+        <v>Igglybuff</v>
       </c>
       <c r="E182" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F182" t="str">
         <v>33.33%</v>
@@ -4052,10 +4051,10 @@
         <v>Main Area</v>
       </c>
       <c r="D183" t="str">
-        <v>Trumbeak</v>
+        <v>Oricorio</v>
       </c>
       <c r="E183" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F183" t="str">
         <v>33.33%</v>
@@ -4072,10 +4071,10 @@
         <v>Main Area</v>
       </c>
       <c r="D184" t="str">
-        <v>Ribombee</v>
+        <v>Trumbeak</v>
       </c>
       <c r="E184" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F184" t="str">
         <v>33.33%</v>
@@ -4083,22 +4082,22 @@
     </row>
     <row r="185">
       <c r="A185">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B185" t="str">
-        <v>Pikachu Valley</v>
+        <v>Royal Avenue</v>
       </c>
       <c r="C185" t="str">
         <v>Main Area</v>
       </c>
       <c r="D185" t="str">
-        <v>Pikachu</v>
+        <v>Ribombee</v>
       </c>
       <c r="E185" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F185" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="186">
@@ -4112,13 +4111,13 @@
         <v>Main Area</v>
       </c>
       <c r="D186" t="str">
-        <v>Alolan Raichu</v>
+        <v>Pikachu</v>
       </c>
       <c r="E186" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F186" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="187">
@@ -4132,13 +4131,13 @@
         <v>Main Area</v>
       </c>
       <c r="D187" t="str">
-        <v>Pichu</v>
+        <v>Alolan Raichu</v>
       </c>
       <c r="E187" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F187" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="188">
@@ -4152,13 +4151,13 @@
         <v>Main Area</v>
       </c>
       <c r="D188" t="str">
-        <v>Magnemite</v>
+        <v>Pichu</v>
       </c>
       <c r="E188" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F188" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="189">
@@ -4166,19 +4165,19 @@
         <v>52</v>
       </c>
       <c r="B189" t="str">
-        <v>Heahea Surf Spot</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C189" t="str">
         <v>Main Area</v>
       </c>
       <c r="D189" t="str">
-        <v>Mantine</v>
+        <v>Rowlet</v>
       </c>
       <c r="E189" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F189" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="190">
@@ -4186,19 +4185,19 @@
         <v>52</v>
       </c>
       <c r="B190" t="str">
-        <v>Heahea Surf Spot</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C190" t="str">
         <v>Main Area</v>
       </c>
       <c r="D190" t="str">
-        <v>Finneon</v>
+        <v>Dartrix</v>
       </c>
       <c r="E190" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F190" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="191">
@@ -4206,24 +4205,24 @@
         <v>52</v>
       </c>
       <c r="B191" t="str">
-        <v>Heahea Surf Spot</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C191" t="str">
         <v>Main Area</v>
       </c>
       <c r="D191" t="str">
-        <v>Tentacool</v>
+        <v>Litten</v>
       </c>
       <c r="E191" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F191" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="192">
       <c r="A192">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B192" t="str">
         <v>Starter Depot</v>
@@ -4232,10 +4231,10 @@
         <v>Main Area</v>
       </c>
       <c r="D192" t="str">
-        <v>Rowlet</v>
+        <v>Torracat</v>
       </c>
       <c r="E192" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F192" t="str">
         <v>16.67%</v>
@@ -4243,7 +4242,7 @@
     </row>
     <row r="193">
       <c r="A193">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B193" t="str">
         <v>Starter Depot</v>
@@ -4252,10 +4251,10 @@
         <v>Main Area</v>
       </c>
       <c r="D193" t="str">
-        <v>Dartrix</v>
+        <v>Popplio</v>
       </c>
       <c r="E193" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F193" t="str">
         <v>16.67%</v>
@@ -4263,7 +4262,7 @@
     </row>
     <row r="194">
       <c r="A194">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B194" t="str">
         <v>Starter Depot</v>
@@ -4272,10 +4271,10 @@
         <v>Main Area</v>
       </c>
       <c r="D194" t="str">
-        <v>Litten</v>
+        <v>Brionne</v>
       </c>
       <c r="E194" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F194" t="str">
         <v>16.67%</v>
@@ -4286,19 +4285,19 @@
         <v>53</v>
       </c>
       <c r="B195" t="str">
-        <v>Starter Depot</v>
+        <v>Poni Coast</v>
       </c>
       <c r="C195" t="str">
         <v>Main Area</v>
       </c>
       <c r="D195" t="str">
-        <v>Torracat</v>
+        <v>Alolan Dugtrio</v>
       </c>
       <c r="E195" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F195" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="196">
@@ -4306,19 +4305,19 @@
         <v>53</v>
       </c>
       <c r="B196" t="str">
-        <v>Starter Depot</v>
+        <v>Poni Coast</v>
       </c>
       <c r="C196" t="str">
         <v>Main Area</v>
       </c>
       <c r="D196" t="str">
-        <v>Popplio</v>
+        <v>Gastrodon</v>
       </c>
       <c r="E196" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F196" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="197">
@@ -4326,19 +4325,19 @@
         <v>53</v>
       </c>
       <c r="B197" t="str">
-        <v>Starter Depot</v>
+        <v>Poni Coast</v>
       </c>
       <c r="C197" t="str">
         <v>Main Area</v>
       </c>
       <c r="D197" t="str">
-        <v>Brionne</v>
+        <v>Exeggcute</v>
       </c>
       <c r="E197" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F197" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="198">
@@ -4346,19 +4345,19 @@
         <v>54</v>
       </c>
       <c r="B198" t="str">
-        <v>Blush Mountain</v>
+        <v>Shopping Mall Antiquities</v>
       </c>
       <c r="C198" t="str">
-        <v>Main Area</v>
+        <v>Event</v>
       </c>
       <c r="D198" t="str">
-        <v>Mudbray</v>
+        <v>Klefki</v>
       </c>
       <c r="E198" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F198" t="str">
-        <v>11.11%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="199">
@@ -4366,396 +4365,396 @@
         <v>54</v>
       </c>
       <c r="B199" t="str">
-        <v>Blush Mountain</v>
+        <v>Shopping Mall Antiquities</v>
       </c>
       <c r="C199" t="str">
-        <v>Main Area</v>
+        <v>Event</v>
       </c>
       <c r="D199" t="str">
-        <v>Torkoal</v>
+        <v>Haunter</v>
       </c>
       <c r="E199" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F199" t="str">
-        <v>11.11%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="200">
       <c r="A200">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B200" t="str">
-        <v>Blush Mountain</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C200" t="str">
-        <v>Main Area</v>
+        <v>Restricted Area</v>
       </c>
       <c r="D200" t="str">
-        <v>Togedemaru</v>
+        <v>Porygon-Z</v>
       </c>
       <c r="E200" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F200" t="str">
-        <v>11.11%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="201">
       <c r="A201">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B201" t="str">
-        <v>Blush Mountain</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C201" t="str">
-        <v>Main Area</v>
+        <v>Restricted Area</v>
       </c>
       <c r="D201" t="str">
-        <v>Elekid</v>
+        <v>Silvally</v>
       </c>
       <c r="E201" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F201" t="str">
-        <v>11.11%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="202">
       <c r="A202">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B202" t="str">
-        <v>Blush Mountain</v>
+        <v>The Zenith Anomaly</v>
       </c>
       <c r="C202" t="str">
         <v>Main Area</v>
       </c>
       <c r="D202" t="str">
-        <v>Alolan Geodude</v>
+        <v>Magearna</v>
       </c>
       <c r="E202" t="str">
-        <v>NaN-NaN</v>
+        <v>95-100</v>
       </c>
       <c r="F202" t="str">
-        <v>11.11%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="203">
       <c r="A203">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B203" t="str">
-        <v>Blush Mountain</v>
+        <v>The Zenith Anomaly</v>
       </c>
       <c r="C203" t="str">
         <v>Main Area</v>
       </c>
       <c r="D203" t="str">
-        <v>Alolan Graveler</v>
+        <v>Marshadow</v>
       </c>
       <c r="E203" t="str">
-        <v>NaN-NaN</v>
+        <v>95-100</v>
       </c>
       <c r="F203" t="str">
-        <v>11.11%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="204">
       <c r="A204">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B204" t="str">
-        <v>Blush Mountain</v>
+        <v>The Zenith Anomaly</v>
       </c>
       <c r="C204" t="str">
         <v>Main Area</v>
       </c>
       <c r="D204" t="str">
-        <v>Charjabug</v>
+        <v>Zeraora</v>
       </c>
       <c r="E204" t="str">
-        <v>NaN-NaN</v>
+        <v>95-100</v>
       </c>
       <c r="F204" t="str">
-        <v>11.11%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="205">
       <c r="A205">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B205" t="str">
-        <v>Blush Mountain</v>
+        <v>Mahalo Trail</v>
       </c>
       <c r="C205" t="str">
         <v>Main Area</v>
       </c>
       <c r="D205" t="str">
-        <v>Turtonator</v>
+        <v>Spearow</v>
       </c>
       <c r="E205" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F205" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="206">
       <c r="A206">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B206" t="str">
-        <v>Blush Mountain</v>
+        <v>Mahalo Trail</v>
       </c>
       <c r="C206" t="str">
         <v>Main Area</v>
       </c>
       <c r="D206" t="str">
-        <v>Dedenne</v>
+        <v>Rufflet</v>
       </c>
       <c r="E206" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F206" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="207">
       <c r="A207">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B207" t="str">
-        <v>Ula'ula Meadow</v>
+        <v>Mahalo Trail</v>
       </c>
       <c r="C207" t="str">
         <v>Main Area</v>
       </c>
       <c r="D207" t="str">
-        <v>Ledian</v>
+        <v>Vullaby</v>
       </c>
       <c r="E207" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F207" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="208">
       <c r="A208">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B208" t="str">
-        <v>Ula'ula Meadow</v>
+        <v>Mahalo Trail</v>
       </c>
       <c r="C208" t="str">
         <v>Main Area</v>
       </c>
       <c r="D208" t="str">
-        <v>Ariados</v>
+        <v>Machop</v>
       </c>
       <c r="E208" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F208" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="209">
       <c r="A209">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B209" t="str">
-        <v>Ula'ula Meadow</v>
+        <v>Mahalo Trail</v>
       </c>
       <c r="C209" t="str">
         <v>Main Area</v>
       </c>
       <c r="D209" t="str">
-        <v>Oricorio</v>
+        <v>Hawlucha</v>
       </c>
       <c r="E209" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F209" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="210">
       <c r="A210">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B210" t="str">
-        <v>Lake of the Sunne</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C210" t="str">
         <v>Main Area</v>
       </c>
       <c r="D210" t="str">
-        <v>Golbat</v>
+        <v>Caterpie</v>
       </c>
       <c r="E210" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F210" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="211">
       <c r="A211">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B211" t="str">
-        <v>Lake of the Sunne</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C211" t="str">
         <v>Main Area</v>
       </c>
       <c r="D211" t="str">
-        <v>Gastly</v>
+        <v>Metapod</v>
       </c>
       <c r="E211" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F211" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="212">
       <c r="A212">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B212" t="str">
-        <v>Lake of the Sunne</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C212" t="str">
         <v>Main Area</v>
       </c>
       <c r="D212" t="str">
-        <v>Haunter</v>
+        <v>Cutiefly</v>
       </c>
       <c r="E212" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F212" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="213">
       <c r="A213">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B213" t="str">
-        <v>Obsidian Sphere</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C213" t="str">
         <v>Main Area</v>
       </c>
       <c r="D213" t="str">
-        <v>Cosmog</v>
+        <v>Butterfree</v>
       </c>
       <c r="E213" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F213" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="214">
       <c r="A214">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B214" t="str">
-        <v>Obsidian Sphere</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C214" t="str">
         <v>Main Area</v>
       </c>
       <c r="D214" t="str">
-        <v>Cosmoem</v>
+        <v>Flabébé</v>
       </c>
       <c r="E214" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F214" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="215">
       <c r="A215">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B215" t="str">
-        <v>Obsidian Sphere</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C215" t="str">
         <v>Main Area</v>
       </c>
       <c r="D215" t="str">
-        <v>Solgaleo</v>
+        <v>Petilil</v>
       </c>
       <c r="E215" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F215" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="216">
       <c r="A216">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B216" t="str">
-        <v>Obsidian Sphere</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C216" t="str">
         <v>Main Area</v>
       </c>
       <c r="D216" t="str">
-        <v>Lunala</v>
+        <v>Cottonee</v>
       </c>
       <c r="E216" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F216" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="217">
       <c r="A217">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B217" t="str">
-        <v>Obsidian Sphere</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C217" t="str">
         <v>Main Area</v>
       </c>
       <c r="D217" t="str">
-        <v>Necrozma</v>
+        <v>Phantump</v>
       </c>
       <c r="E217" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F217" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="218">
       <c r="A218">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B218" t="str">
-        <v>Route 3</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C218" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D218" t="str">
-        <v>Mankey</v>
+        <v>Tapu Koko</v>
       </c>
       <c r="E218" t="str">
-        <v>NaN-NaN</v>
+        <v>100</v>
       </c>
       <c r="F218" t="str">
         <v>25.00%</v>
@@ -4763,19 +4762,19 @@
     </row>
     <row r="219">
       <c r="A219">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B219" t="str">
-        <v>Route 3</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C219" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D219" t="str">
-        <v>Delibird</v>
+        <v>Tapu Lele</v>
       </c>
       <c r="E219" t="str">
-        <v>NaN-NaN</v>
+        <v>100</v>
       </c>
       <c r="F219" t="str">
         <v>25.00%</v>
@@ -4783,19 +4782,19 @@
     </row>
     <row r="220">
       <c r="A220">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B220" t="str">
-        <v>Route 3</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C220" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D220" t="str">
-        <v>Bagon</v>
+        <v>Tapu Bulu</v>
       </c>
       <c r="E220" t="str">
-        <v>NaN-NaN</v>
+        <v>100</v>
       </c>
       <c r="F220" t="str">
         <v>25.00%</v>
@@ -4803,19 +4802,19 @@
     </row>
     <row r="221">
       <c r="A221">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B221" t="str">
-        <v>Route 3</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C221" t="str">
-        <v>North</v>
+        <v>Main Area</v>
       </c>
       <c r="D221" t="str">
-        <v>Igglybuff</v>
+        <v>Tapu Fini</v>
       </c>
       <c r="E221" t="str">
-        <v>NaN-NaN</v>
+        <v>100</v>
       </c>
       <c r="F221" t="str">
         <v>25.00%</v>
@@ -4823,22 +4822,22 @@
     </row>
     <row r="222">
       <c r="A222">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B222" t="str">
-        <v>Memorial Hill</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C222" t="str">
-        <v>Main</v>
+        <v>Main Area</v>
       </c>
       <c r="D222" t="str">
-        <v>Special Encounter</v>
+        <v>Buneary</v>
       </c>
       <c r="E222" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F222" t="str">
-        <v>100%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="223">
@@ -4846,19 +4845,19 @@
         <v>60</v>
       </c>
       <c r="B223" t="str">
-        <v>Sacred Shrine</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C223" t="str">
         <v>Main Area</v>
       </c>
       <c r="D223" t="str">
-        <v>Tapu Koko</v>
+        <v>Granbull</v>
       </c>
       <c r="E223" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F223" t="str">
-        <v>25.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="224">
@@ -4866,19 +4865,19 @@
         <v>60</v>
       </c>
       <c r="B224" t="str">
-        <v>Sacred Shrine</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C224" t="str">
         <v>Main Area</v>
       </c>
       <c r="D224" t="str">
-        <v>Tapu Lele</v>
+        <v>Zoroark</v>
       </c>
       <c r="E224" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F224" t="str">
-        <v>25.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="225">
@@ -4886,19 +4885,19 @@
         <v>60</v>
       </c>
       <c r="B225" t="str">
-        <v>Sacred Shrine</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C225" t="str">
         <v>Main Area</v>
       </c>
       <c r="D225" t="str">
-        <v>Tapu Bulu</v>
+        <v>Heracross</v>
       </c>
       <c r="E225" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F225" t="str">
-        <v>25.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="226">
@@ -4906,416 +4905,416 @@
         <v>60</v>
       </c>
       <c r="B226" t="str">
-        <v>Sacred Shrine</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C226" t="str">
         <v>Main Area</v>
       </c>
       <c r="D226" t="str">
-        <v>Tapu Fini</v>
+        <v>Riolu</v>
       </c>
       <c r="E226" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F226" t="str">
-        <v>25.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="227">
       <c r="A227">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B227" t="str">
-        <v>Route 15</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C227" t="str">
         <v>Main Area</v>
       </c>
       <c r="D227" t="str">
-        <v>Special Encounter</v>
+        <v>Hariyama</v>
       </c>
       <c r="E227" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F227" t="str">
-        <v>100%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="228">
       <c r="A228">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B228" t="str">
-        <v>Aether Paradise</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C228" t="str">
-        <v>Labs</v>
+        <v>Main Area</v>
       </c>
       <c r="D228" t="str">
-        <v>Special Encounter</v>
+        <v>Mudsdale</v>
       </c>
       <c r="E228" t="str">
-        <v>NaN-NaN</v>
+        <v>85-90</v>
       </c>
       <c r="F228" t="str">
-        <v>100%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="229">
       <c r="A229">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B229" t="str">
-        <v>Aether Paradise</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C229" t="str">
-        <v>Secret Lab</v>
+        <v>Main Area</v>
       </c>
       <c r="D229" t="str">
-        <v>Type: Null</v>
+        <v>Nihilego</v>
       </c>
       <c r="E229" t="str">
-        <v>NaN-NaN</v>
+        <v>110</v>
       </c>
       <c r="F229" t="str">
-        <v>33.33%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="230">
       <c r="A230">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B230" t="str">
-        <v>Aether Paradise</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C230" t="str">
-        <v>Secret Lab</v>
+        <v>Main Area</v>
       </c>
       <c r="D230" t="str">
-        <v>Silvally</v>
+        <v>Buzzwole</v>
       </c>
       <c r="E230" t="str">
-        <v>NaN-NaN</v>
+        <v>110</v>
       </c>
       <c r="F230" t="str">
-        <v>33.33%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="231">
       <c r="A231">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B231" t="str">
-        <v>Aether Paradise</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C231" t="str">
-        <v>Secret Lab</v>
+        <v>Main Area</v>
       </c>
       <c r="D231" t="str">
-        <v>Porygon</v>
+        <v>Pheromosa</v>
       </c>
       <c r="E231" t="str">
-        <v>NaN-NaN</v>
+        <v>110</v>
       </c>
       <c r="F231" t="str">
-        <v>33.33%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="232">
       <c r="A232">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B232" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C232" t="str">
         <v>Main Area</v>
       </c>
       <c r="D232" t="str">
-        <v>Buneary</v>
+        <v>Xurkitree</v>
       </c>
       <c r="E232" t="str">
-        <v>90-100</v>
+        <v>110</v>
       </c>
       <c r="F232" t="str">
-        <v>14.29%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="233">
       <c r="A233">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B233" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C233" t="str">
         <v>Main Area</v>
       </c>
       <c r="D233" t="str">
-        <v>Granbull</v>
+        <v>Celesteela</v>
       </c>
       <c r="E233" t="str">
-        <v>90-100</v>
+        <v>110</v>
       </c>
       <c r="F233" t="str">
-        <v>14.29%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="234">
       <c r="A234">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B234" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C234" t="str">
         <v>Main Area</v>
       </c>
       <c r="D234" t="str">
-        <v>Zoroark</v>
+        <v>Kartana</v>
       </c>
       <c r="E234" t="str">
-        <v>90-100</v>
+        <v>110</v>
       </c>
       <c r="F234" t="str">
-        <v>14.29%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="235">
       <c r="A235">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B235" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C235" t="str">
         <v>Main Area</v>
       </c>
       <c r="D235" t="str">
-        <v>Heracross</v>
+        <v>Guzzlord</v>
       </c>
       <c r="E235" t="str">
-        <v>90-100</v>
+        <v>110</v>
       </c>
       <c r="F235" t="str">
-        <v>14.29%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="236">
       <c r="A236">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B236" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C236" t="str">
         <v>Main Area</v>
       </c>
       <c r="D236" t="str">
-        <v>Riolu</v>
+        <v>Poipole</v>
       </c>
       <c r="E236" t="str">
-        <v>90-100</v>
+        <v>110</v>
       </c>
       <c r="F236" t="str">
-        <v>14.29%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="237">
       <c r="A237">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B237" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C237" t="str">
         <v>Main Area</v>
       </c>
       <c r="D237" t="str">
-        <v>Hariyama</v>
+        <v>Stakataka</v>
       </c>
       <c r="E237" t="str">
-        <v>90-100</v>
+        <v>110</v>
       </c>
       <c r="F237" t="str">
-        <v>14.29%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="238">
       <c r="A238">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B238" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C238" t="str">
         <v>Main Area</v>
       </c>
       <c r="D238" t="str">
-        <v>Mudsdale</v>
+        <v>Blacephalon</v>
       </c>
       <c r="E238" t="str">
-        <v>90-100</v>
+        <v>110</v>
       </c>
       <c r="F238" t="str">
-        <v>14.29%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="239">
       <c r="A239">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B239" t="str">
-        <v>Poni Plains</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C239" t="str">
-        <v>Center</v>
+        <v>Labs</v>
       </c>
       <c r="D239" t="str">
-        <v>Special Encounter</v>
+        <v>Ditto</v>
       </c>
       <c r="E239" t="str">
-        <v>90-100</v>
+        <v>85-90</v>
       </c>
       <c r="F239" t="str">
-        <v>100%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="240">
       <c r="A240">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B240" t="str">
-        <v>Resolution Cave</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C240" t="str">
-        <v>Main Area</v>
+        <v>Labs</v>
       </c>
       <c r="D240" t="str">
-        <v>Special Encounter</v>
+        <v>Porygon2</v>
       </c>
       <c r="E240" t="str">
-        <v>90-100</v>
+        <v>85-90</v>
       </c>
       <c r="F240" t="str">
-        <v>100%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="241">
       <c r="A241">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B241" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C241" t="str">
-        <v>Main Area Part 1</v>
+        <v>Secret Lab</v>
       </c>
       <c r="D241" t="str">
-        <v>Nihilego</v>
+        <v>Type: Null</v>
       </c>
       <c r="E241" t="str">
-        <v>90-100</v>
+        <v>85-90</v>
       </c>
       <c r="F241" t="str">
-        <v>20.00%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="242">
       <c r="A242">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B242" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C242" t="str">
-        <v>Main Area Part 1</v>
+        <v>Secret Lab</v>
       </c>
       <c r="D242" t="str">
-        <v>Buzzwole</v>
+        <v>Porygon</v>
       </c>
       <c r="E242" t="str">
-        <v>90-100</v>
+        <v>85-90</v>
       </c>
       <c r="F242" t="str">
-        <v>20.00%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="243">
       <c r="A243">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B243" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C243" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D243" t="str">
-        <v>Pheromosa</v>
+        <v>Solgaleo</v>
       </c>
       <c r="E243" t="str">
-        <v>90-100</v>
+        <v>120</v>
       </c>
       <c r="F243" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="244">
       <c r="A244">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B244" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C244" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D244" t="str">
-        <v>Xurkitree</v>
+        <v>Lunala</v>
       </c>
       <c r="E244" t="str">
-        <v>90-100</v>
+        <v>120</v>
       </c>
       <c r="F244" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="245">
       <c r="A245">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B245" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C245" t="str">
-        <v>Main Area Part 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D245" t="str">
-        <v>Celesteela</v>
+        <v>Necrozma</v>
       </c>
       <c r="E245" t="str">
-        <v>90-100</v>
+        <v>120</v>
       </c>
       <c r="F245" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="246">
       <c r="A246">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B246" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Obsidian Tesseract</v>
       </c>
       <c r="C246" t="str">
-        <v>Main Area Part 2</v>
+        <v>Main Area</v>
       </c>
       <c r="D246" t="str">
-        <v>Kartana</v>
+        <v>Cosmog</v>
       </c>
       <c r="E246" t="str">
-        <v>90-100</v>
+        <v>100</v>
       </c>
       <c r="F246" t="str">
         <v>20.00%</v>
@@ -5323,19 +5322,19 @@
     </row>
     <row r="247">
       <c r="A247">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B247" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Obsidian Tesseract</v>
       </c>
       <c r="C247" t="str">
-        <v>Main Area Part 2</v>
+        <v>Main Area</v>
       </c>
       <c r="D247" t="str">
-        <v>Guzzlord</v>
+        <v>Cosmoem</v>
       </c>
       <c r="E247" t="str">
-        <v>90-100</v>
+        <v>100</v>
       </c>
       <c r="F247" t="str">
         <v>20.00%</v>
@@ -5343,19 +5342,19 @@
     </row>
     <row r="248">
       <c r="A248">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B248" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Obsidian Tesseract</v>
       </c>
       <c r="C248" t="str">
-        <v>Main Area Part 2</v>
+        <v>Main Area</v>
       </c>
       <c r="D248" t="str">
-        <v>Poipole</v>
+        <v>Solgaleo</v>
       </c>
       <c r="E248" t="str">
-        <v>90-100</v>
+        <v>120</v>
       </c>
       <c r="F248" t="str">
         <v>20.00%</v>
@@ -5363,19 +5362,19 @@
     </row>
     <row r="249">
       <c r="A249">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B249" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Obsidian Tesseract</v>
       </c>
       <c r="C249" t="str">
-        <v>Main Area Part 2</v>
+        <v>Main Area</v>
       </c>
       <c r="D249" t="str">
-        <v>Stakataka</v>
+        <v>Lunala</v>
       </c>
       <c r="E249" t="str">
-        <v>90-100</v>
+        <v>120</v>
       </c>
       <c r="F249" t="str">
         <v>20.00%</v>
@@ -5383,154 +5382,34 @@
     </row>
     <row r="250">
       <c r="A250">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B250" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Obsidian Tesseract</v>
       </c>
       <c r="C250" t="str">
-        <v>Main Area Part 2</v>
+        <v>Main Area</v>
       </c>
       <c r="D250" t="str">
-        <v>Blacephalon</v>
+        <v>Necrozma</v>
       </c>
       <c r="E250" t="str">
-        <v>90-100</v>
+        <v>120</v>
       </c>
       <c r="F250" t="str">
         <v>20.00%</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251">
-        <v>69</v>
-      </c>
-      <c r="B251" t="str">
-        <v>Poni Coast</v>
-      </c>
-      <c r="C251" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D251" t="str">
-        <v>Alolan Dugtrio</v>
-      </c>
-      <c r="E251" t="str">
-        <v>90-100</v>
-      </c>
-      <c r="F251" t="str">
-        <v>33.33%</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252">
-        <v>69</v>
-      </c>
-      <c r="B252" t="str">
-        <v>Poni Coast</v>
-      </c>
-      <c r="C252" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D252" t="str">
-        <v>Gastrodon</v>
-      </c>
-      <c r="E252" t="str">
-        <v>90-100</v>
-      </c>
-      <c r="F252" t="str">
-        <v>33.33%</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253">
-        <v>69</v>
-      </c>
-      <c r="B253" t="str">
-        <v>Poni Coast</v>
-      </c>
-      <c r="C253" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D253" t="str">
-        <v>Exeggcute</v>
-      </c>
-      <c r="E253" t="str">
-        <v>90-100</v>
-      </c>
-      <c r="F253" t="str">
-        <v>33.33%</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254">
-        <v>70</v>
-      </c>
-      <c r="B254" t="str">
-        <v>The Zenith Anomaly</v>
-      </c>
-      <c r="C254" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D254" t="str">
-        <v>Magearna</v>
-      </c>
-      <c r="E254" t="str">
-        <v>90-100</v>
-      </c>
-      <c r="F254" t="str">
-        <v>33.33%</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255">
-        <v>70</v>
-      </c>
-      <c r="B255" t="str">
-        <v>The Zenith Anomaly</v>
-      </c>
-      <c r="C255" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D255" t="str">
-        <v>Marshadow</v>
-      </c>
-      <c r="E255" t="str">
-        <v>90-100</v>
-      </c>
-      <c r="F255" t="str">
-        <v>33.33%</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256">
-        <v>70</v>
-      </c>
-      <c r="B256" t="str">
-        <v>The Zenith Anomaly</v>
-      </c>
-      <c r="C256" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D256" t="str">
-        <v>Zeraora</v>
-      </c>
-      <c r="E256" t="str">
-        <v>90-100</v>
-      </c>
-      <c r="F256" t="str">
-        <v>33.33%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F256"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F250"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C73"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6073,7 +5952,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Extra Challenge $1-1</v>
+        <v>Extra Challenge A-1</v>
       </c>
       <c r="B50" t="str">
         <v>Defeat Captain Lana</v>
@@ -6084,7 +5963,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Extra Challenge $1-2</v>
+        <v>Extra Challenge A-2</v>
       </c>
       <c r="B51" t="str">
         <v>Defeat 15 Pokemon in Route 6 Main Area</v>
@@ -6095,7 +5974,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Extra Challenge $1-3</v>
+        <v>Extra Challenge A-3</v>
       </c>
       <c r="B52" t="str">
         <v>Defeat 15 Pokemon in Royal Avenue Main Area</v>
@@ -6106,941 +5985,238 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Extra Challenge $1-4</v>
+        <v>Extra Challenge A-4</v>
       </c>
       <c r="B53" t="str">
         <v>Defeat 15 Pokemon in Pikachu Valley Main Area</v>
       </c>
       <c r="C53" t="str">
-        <v>Unlocks Heahea Surf Spot Main Area</v>
+        <v>Unlocks Starter Depot Main Area</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Extra Challenge $1-5</v>
+        <v>Extra Challenge B-1</v>
       </c>
       <c r="B54" t="str">
-        <v>Defeat 15 Pokemon in Heahea Surf Spot Main Area</v>
+        <v>Defeat Champion Hau</v>
       </c>
       <c r="C54" t="str">
-        <v>Unlocks Starter Depot Main Area</v>
+        <v>Unlocks Poni Coast Main Area</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Extra Challenge $2-1</v>
+        <v>Extra Challenge B-2</v>
       </c>
       <c r="B55" t="str">
-        <v>Defeat Captain Sophocles</v>
+        <v>Defeat 15 Pokemon in Poni Coast Main Area</v>
       </c>
       <c r="C55" t="str">
-        <v>Unlocks Blush Mountain Main Area</v>
+        <v>Unlocks Shopping Mall Antiquities Event</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Extra Challenge $2-2</v>
+        <v>Extra Challenge B-3</v>
       </c>
       <c r="B56" t="str">
-        <v>Defeat 15 Pokemon in Blush Mountain Main Area</v>
+        <v>Defeat 15 Pokemon in Shopping Mall Antiquities Event</v>
       </c>
       <c r="C56" t="str">
-        <v>Unlocks Ula'ula Meadow Main Area</v>
+        <v>Unlocks Aether Paradise Restricted Area</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Extra Challenge $2-3</v>
+        <v>Extra Challenge B-4</v>
       </c>
       <c r="B57" t="str">
-        <v>Defeat 15 Pokemon in Ula'ula Meadow Main Area</v>
+        <v>Defeat 15 Pokemon in Aether Paradise Restricted Area</v>
       </c>
       <c r="C57" t="str">
-        <v>Unlocks Lake of the Sunne Main Area</v>
+        <v>Unlocks The Zenith Anomaly Main Area</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Extra Challenge $2-4</v>
+        <v>Extra Challenge C-1</v>
       </c>
       <c r="B58" t="str">
-        <v>Defeat 15 Pokemon in Lake of the Sunne Main Area</v>
+        <v>Defeat Champion Hau</v>
       </c>
       <c r="C58" t="str">
-        <v>Unlocks Obsidian Sphere Main Area [Cosmog, Solgaleo, Lunala, Necrozma]</v>
+        <v>Unlocks Mahalo Trail Main Area</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Extra Challenge $3-1</v>
+        <v>Extra Challenge C-2</v>
       </c>
       <c r="B59" t="str">
-        <v>Defeat Kahuna Hala</v>
+        <v>Defeat 15 Pokemon in Mahalo Trail Main Area</v>
       </c>
       <c r="C59" t="str">
-        <v>Unlocks Route 3 North</v>
+        <v>Unlocks Melemele Meadow Main Area</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Extra Challenge $3-2</v>
+        <v>Extra Challenge C-3</v>
       </c>
       <c r="B60" t="str">
-        <v>Defeat 15 Pokemon in Route 3 North</v>
+        <v>Defeat 15 Pokemon in Melemele Meadow Main Area</v>
       </c>
       <c r="C60" t="str">
-        <v>Unlocks Memorial Hill Main</v>
+        <v>Unlocks Ruins of Conflict Special Encounter</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Extra Challenge $3-3</v>
+        <v>Extra Challenge C-4</v>
       </c>
       <c r="B61" t="str">
-        <v>Defeat 15 Pokemon in Memorial Hill Main</v>
+        <v>Defeat 15 Pokemon in Ruins of Conflict Special Encounter</v>
       </c>
       <c r="C61" t="str">
-        <v>Unlocks Sacred Shrine Main Area [Tapus (Koko, Lele, Bulu, Fini)]</v>
+        <v>Unlocks Memorial Hill Main</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Extra Challenge $4-1</v>
+        <v>Extra Challenge C-5</v>
       </c>
       <c r="B62" t="str">
-        <v>Defeat Kahuna Nanu</v>
+        <v>Defeat 15 Pokemon in Memorial Hill Main</v>
       </c>
       <c r="C62" t="str">
-        <v>Unlocks Route 15 Main Area</v>
+        <v>Unlocks Sacred Shrine Main Area</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Extra Challenge $4-2</v>
+        <v>Extra Challenge D-1</v>
       </c>
       <c r="B63" t="str">
-        <v>Defeat 15 Pokemon in Route 15 Main Area</v>
+        <v>Defeat Champion Hau</v>
       </c>
       <c r="C63" t="str">
-        <v>Unlocks Aether Paradise Labs</v>
+        <v>Unlocks Poni Grove Main Area</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Extra Challenge $4-3</v>
+        <v>Extra Challenge D-2</v>
       </c>
       <c r="B64" t="str">
-        <v>Defeat 15 Pokemon in Aether Paradise Labs</v>
+        <v>Defeat 15 Pokemon in Poni Grove Main Area</v>
       </c>
       <c r="C64" t="str">
-        <v>Unlocks Aether Paradise Secret Lab [Type: Null, Porygon, Silvally]</v>
+        <v>Unlocks Poni Plains Center</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Extra Challenge $5-1</v>
+        <v>Extra Challenge D-3</v>
       </c>
       <c r="B65" t="str">
-        <v>Defeat Champion Hau</v>
+        <v>Defeat 15 Pokemon in Poni Plains Center</v>
       </c>
       <c r="C65" t="str">
-        <v>Unlocks Poni Grove Main Area</v>
+        <v>Unlocks Resolution Cave Main Area</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Extra Challenge $5-2</v>
+        <v>Extra Challenge D-4</v>
       </c>
       <c r="B66" t="str">
-        <v>Defeat 15 Pokemon in Poni Grove Main Area</v>
+        <v>Defeat 15 Pokemon in Resolution Cave Main Area</v>
       </c>
       <c r="C66" t="str">
-        <v>Unlocks Poni Plains Center</v>
+        <v>Unlocks Ruins of Hope Special Encounter</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Extra Challenge $5-3</v>
+        <v>Extra Challenge D-5</v>
       </c>
       <c r="B67" t="str">
-        <v>Defeat 15 Pokemon in Poni Plains Center</v>
+        <v>Defeat 15 Pokemon in Ruins of Hope Special Encounter</v>
       </c>
       <c r="C67" t="str">
-        <v>Unlocks Resolution Cave Main Area</v>
+        <v>Unlocks The Interdimensional Rift Main Area</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Extra Challenge $5-4</v>
+        <v>Extra Challenge E-1</v>
       </c>
       <c r="B68" t="str">
-        <v>Defeat 15 Pokemon in Resolution Cave Main Area</v>
+        <v>Defeat Champion Hau</v>
       </c>
       <c r="C68" t="str">
-        <v>Unlocks The Interdimensional Rift Main Area Part 1</v>
+        <v>Unlocks Route 15 Main Area</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Extra Challenge $5-5</v>
+        <v>Extra Challenge E-2</v>
       </c>
       <c r="B69" t="str">
-        <v>Defeat 15 Pokemon in The Interdimensional Rift Main Area Part 1</v>
+        <v>Defeat 15 Pokemon in Route 15 Main Area</v>
       </c>
       <c r="C69" t="str">
-        <v>Unlocks The Interdimensional Rift Main Area Part 2 [All Ultra Beasts]</v>
+        <v>Unlocks Aether Paradise Labs</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Extra Challenge $6-1</v>
+        <v>Extra Challenge E-3</v>
       </c>
       <c r="B70" t="str">
-        <v>Defeat 15 Pokemon in The Interdimensional Rift Main Area Part 2</v>
+        <v>Defeat 15 Pokemon in Aether Paradise Labs</v>
       </c>
       <c r="C70" t="str">
-        <v>Unlocks Poni Coast Main Area</v>
+        <v>Unlocks Aether Paradise Secret Lab</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Extra Challenge $6-2</v>
+        <v>Extra Challenge E-4</v>
       </c>
       <c r="B71" t="str">
-        <v>Defeat 15 Pokemon in Poni Coast Main Area</v>
+        <v>Defeat 15 Pokemon in Aether Paradise Secret Lab</v>
       </c>
       <c r="C71" t="str">
-        <v>Unlocks The Zenith Anomaly Main Area [Magearna, Marshadow, Zeraora]</v>
+        <v>Unlocks Lake of the Sunne Main Area</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Extra Challenge E-5</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Defeat 15 Pokemon in Lake of the Sunne Main Area</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Unlocks Obsidian Sphere Main Area</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Extra Challenge E-6</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Defeat 15 Pokemon in Obsidian Sphere Main Area</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Transforms Obsidian Sphere into Obsidian Tesseract</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C71"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D51"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Pokemon Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Pokemon Type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Path to be include</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Obtained?</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Rowlet</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Grass/Flying</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Starter Depot</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Dartrix</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Grass/Flying</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Starter Depot</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Litten</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Fire</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Starter Depot</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Torracat</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Fire</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Starter Depot</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Popplio</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Water</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Starter Depot</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Brionne</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Water</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Starter Depot</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Pikachu</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Electric</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Route 1 East</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Alolan Raichu</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Electric/Psychic</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Route 1 East</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Yes (Evolution)</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Oricorio</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Fire/Electric/Psychic/Ghost</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Route 3 North</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Lycanroc</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Rock</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Ten Carat Hill Inside</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Staryu</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Water</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Route 7 Main Area</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Pyukumuku</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Water</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Route 7 Main Area</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Bounsweet</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Grass</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Lush Jungle North</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Oranguru</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Normal/Psychic</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Lush Jungle East Cave</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Passimian</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Fighting</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Lush Jungle East Cave</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Corsola</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Water/Rock</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Route 7 Main Area</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Mareanie</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Poison/Water</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Route 7 Main Area</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Minior</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Rock/Flying</v>
-      </c>
-      <c r="C19" t="str">
-        <v>Mount Hokulani East</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Bruxish</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Water/Psychic</v>
-      </c>
-      <c r="C20" t="str">
-        <v>Route 14 Main Area</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>Sandygast</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Ghost/Ground</v>
-      </c>
-      <c r="C21" t="str">
-        <v>Route 15 Main Area</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>Klefki</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Steel/Fairy</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Route 16 Main Area</v>
-      </c>
-      <c r="D22" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>Crabominable</v>
-      </c>
-      <c r="B23" t="str">
-        <v>Fighting/Ice</v>
-      </c>
-      <c r="C23" t="str">
-        <v>Mount Lanakila Cave</v>
-      </c>
-      <c r="D23" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>Amaura</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Rock/Ice</v>
-      </c>
-      <c r="C24" t="str">
-        <v>Route 8 Fossil Restoration</v>
-      </c>
-      <c r="D24" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Ditto</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="C25" t="str">
-        <v>Route 10</v>
-      </c>
-      <c r="D25" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Tapu Koko</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Electric/Fairy</v>
-      </c>
-      <c r="C26" t="str">
-        <v>Sacred Shrine</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>Tapu Lele</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Psychic/Fairy</v>
-      </c>
-      <c r="C27" t="str">
-        <v>Sacred Shrine</v>
-      </c>
-      <c r="D27" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Tapu Bulu</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Grass/Fairy</v>
-      </c>
-      <c r="C28" t="str">
-        <v>Sacred Shrine</v>
-      </c>
-      <c r="D28" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>Tapu Fini</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Water/Fairy</v>
-      </c>
-      <c r="C29" t="str">
-        <v>Sacred Shrine</v>
-      </c>
-      <c r="D29" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>Cosmog</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Psychic</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Obsidian Sphere</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>Cosmoem</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Psychic</v>
-      </c>
-      <c r="C31" t="str">
-        <v>Obsidian Sphere</v>
-      </c>
-      <c r="D31" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>Solgaleo</v>
-      </c>
-      <c r="B32" t="str">
-        <v>Psychic/Steel</v>
-      </c>
-      <c r="C32" t="str">
-        <v>Obsidian Sphere</v>
-      </c>
-      <c r="D32" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>Lunala</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Psychic/Ghost</v>
-      </c>
-      <c r="C33" t="str">
-        <v>Obsidian Sphere</v>
-      </c>
-      <c r="D33" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>Necrozma</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Psychic</v>
-      </c>
-      <c r="C34" t="str">
-        <v>Obsidian Sphere</v>
-      </c>
-      <c r="D34" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Poipole</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Poison</v>
-      </c>
-      <c r="C35" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="D35" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>Naganadel</v>
-      </c>
-      <c r="B36" t="str">
-        <v>Poison/Dragon</v>
-      </c>
-      <c r="C36" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="D36" t="str">
-        <v>Yes (Evolution)</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>Nihilego</v>
-      </c>
-      <c r="B37" t="str">
-        <v>Rock/Poison</v>
-      </c>
-      <c r="C37" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="D37" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>Buzzwole</v>
-      </c>
-      <c r="B38" t="str">
-        <v>Bug/Fighting</v>
-      </c>
-      <c r="C38" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="D38" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>Pheromosa</v>
-      </c>
-      <c r="B39" t="str">
-        <v>Bug/Fighting</v>
-      </c>
-      <c r="C39" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="D39" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>Xurkitree</v>
-      </c>
-      <c r="B40" t="str">
-        <v>Electric</v>
-      </c>
-      <c r="C40" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="D40" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>Celesteela</v>
-      </c>
-      <c r="B41" t="str">
-        <v>Steel/Flying</v>
-      </c>
-      <c r="C41" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="D41" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>Kartana</v>
-      </c>
-      <c r="B42" t="str">
-        <v>Grass/Steel</v>
-      </c>
-      <c r="C42" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="D42" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>Guzzlord</v>
-      </c>
-      <c r="B43" t="str">
-        <v>Dark/Dragon</v>
-      </c>
-      <c r="C43" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="D43" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>Stakataka</v>
-      </c>
-      <c r="B44" t="str">
-        <v>Rock/Steel</v>
-      </c>
-      <c r="C44" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="D44" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>Blacephalon</v>
-      </c>
-      <c r="B45" t="str">
-        <v>Fire/Ghost</v>
-      </c>
-      <c r="C45" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="D45" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>Type: Null</v>
-      </c>
-      <c r="B46" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="C46" t="str">
-        <v>Aether Paradise Secret Lab</v>
-      </c>
-      <c r="D46" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>Silvally</v>
-      </c>
-      <c r="B47" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="C47" t="str">
-        <v>Aether Paradise Secret Lab</v>
-      </c>
-      <c r="D47" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>Porygon</v>
-      </c>
-      <c r="B48" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="C48" t="str">
-        <v>Aether Paradise Secret Lab</v>
-      </c>
-      <c r="D48" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>Magearna</v>
-      </c>
-      <c r="B49" t="str">
-        <v>Steel/Fairy</v>
-      </c>
-      <c r="C49" t="str">
-        <v>The Zenith Anomaly</v>
-      </c>
-      <c r="D49" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>Marshadow</v>
-      </c>
-      <c r="B50" t="str">
-        <v>Ghost/Fighting</v>
-      </c>
-      <c r="C50" t="str">
-        <v>The Zenith Anomaly</v>
-      </c>
-      <c r="D50" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>Zeraora</v>
-      </c>
-      <c r="B51" t="str">
-        <v>Electric</v>
-      </c>
-      <c r="C51" t="str">
-        <v>The Zenith Anomaly</v>
-      </c>
-      <c r="D51" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C73"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Alola_Paths_and_Challenges.xlsx
+++ b/Alola_Paths_and_Challenges.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="Paths" sheetId="1" r:id="rId1"/>
     <sheet name="Challenges" sheetId="2" r:id="rId2"/>
+    <sheet name="Missing Pokemons" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -398,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F250"/>
+  <dimension ref="A1:F239"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -434,10 +435,10 @@
         <v>Pikipek</v>
       </c>
       <c r="E2" t="str">
-        <v>2-7</v>
+        <v>3-8</v>
       </c>
       <c r="F2" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="3">
@@ -454,10 +455,10 @@
         <v>Yungoos</v>
       </c>
       <c r="E3" t="str">
-        <v>2-7</v>
+        <v>3-8</v>
       </c>
       <c r="F3" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="4">
@@ -474,10 +475,10 @@
         <v>Alolan Rattata</v>
       </c>
       <c r="E4" t="str">
-        <v>2-7</v>
+        <v>3-8</v>
       </c>
       <c r="F4" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="5">
@@ -494,10 +495,10 @@
         <v>Ledyba</v>
       </c>
       <c r="E5" t="str">
-        <v>2-7</v>
+        <v>3-8</v>
       </c>
       <c r="F5" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="6">
@@ -514,10 +515,10 @@
         <v>Spinarak</v>
       </c>
       <c r="E6" t="str">
-        <v>2-7</v>
+        <v>3-8</v>
       </c>
       <c r="F6" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="7">
@@ -534,10 +535,10 @@
         <v>Grubbin</v>
       </c>
       <c r="E7" t="str">
-        <v>2-7</v>
+        <v>3-8</v>
       </c>
       <c r="F7" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="8">
@@ -554,30 +555,30 @@
         <v>Pichu</v>
       </c>
       <c r="E8" t="str">
-        <v>2-7</v>
+        <v>3-8</v>
       </c>
       <c r="F8" t="str">
-        <v>14.29%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="str">
         <v>Route 1</v>
       </c>
       <c r="C9" t="str">
-        <v>Hau'oli Outskirts</v>
+        <v>East</v>
       </c>
       <c r="D9" t="str">
-        <v>Inkay</v>
+        <v>Pikachu</v>
       </c>
       <c r="E9" t="str">
         <v>3-8</v>
       </c>
       <c r="F9" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="10">
@@ -591,10 +592,10 @@
         <v>Hau'oli Outskirts</v>
       </c>
       <c r="D10" t="str">
-        <v>Slowpoke</v>
+        <v>Inkay</v>
       </c>
       <c r="E10" t="str">
-        <v>3-8</v>
+        <v>5-10</v>
       </c>
       <c r="F10" t="str">
         <v>20.00%</v>
@@ -611,10 +612,10 @@
         <v>Hau'oli Outskirts</v>
       </c>
       <c r="D11" t="str">
-        <v>Alolan Meowth</v>
+        <v>Slowpoke</v>
       </c>
       <c r="E11" t="str">
-        <v>3-8</v>
+        <v>5-10</v>
       </c>
       <c r="F11" t="str">
         <v>20.00%</v>
@@ -631,10 +632,10 @@
         <v>Hau'oli Outskirts</v>
       </c>
       <c r="D12" t="str">
-        <v>Tentacool</v>
+        <v>Alolan Meowth</v>
       </c>
       <c r="E12" t="str">
-        <v>3-8</v>
+        <v>5-10</v>
       </c>
       <c r="F12" t="str">
         <v>20.00%</v>
@@ -651,10 +652,10 @@
         <v>Hau'oli Outskirts</v>
       </c>
       <c r="D13" t="str">
-        <v>Finneon</v>
+        <v>Tentacool</v>
       </c>
       <c r="E13" t="str">
-        <v>3-8</v>
+        <v>5-10</v>
       </c>
       <c r="F13" t="str">
         <v>20.00%</v>
@@ -662,16 +663,16 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" t="str">
-        <v>Hau'oli City</v>
+        <v>Route 1</v>
       </c>
       <c r="C14" t="str">
-        <v>Shopping District</v>
+        <v>Hau'oli Outskirts</v>
       </c>
       <c r="D14" t="str">
-        <v>Furfrou</v>
+        <v>Finneon</v>
       </c>
       <c r="E14" t="str">
         <v>5-10</v>
@@ -691,10 +692,10 @@
         <v>Shopping District</v>
       </c>
       <c r="D15" t="str">
-        <v>Hypno</v>
+        <v>Furfrou</v>
       </c>
       <c r="E15" t="str">
-        <v>5-10</v>
+        <v>6-11</v>
       </c>
       <c r="F15" t="str">
         <v>20.00%</v>
@@ -711,10 +712,10 @@
         <v>Shopping District</v>
       </c>
       <c r="D16" t="str">
-        <v>Abra</v>
+        <v>Hypno</v>
       </c>
       <c r="E16" t="str">
-        <v>5-10</v>
+        <v>6-11</v>
       </c>
       <c r="F16" t="str">
         <v>20.00%</v>
@@ -731,10 +732,10 @@
         <v>Shopping District</v>
       </c>
       <c r="D17" t="str">
-        <v>Mime Jr.</v>
+        <v>Abra</v>
       </c>
       <c r="E17" t="str">
-        <v>5-10</v>
+        <v>6-11</v>
       </c>
       <c r="F17" t="str">
         <v>20.00%</v>
@@ -751,10 +752,10 @@
         <v>Shopping District</v>
       </c>
       <c r="D18" t="str">
-        <v>Bewear</v>
+        <v>Mime Jr.</v>
       </c>
       <c r="E18" t="str">
-        <v>5-10</v>
+        <v>6-11</v>
       </c>
       <c r="F18" t="str">
         <v>20.00%</v>
@@ -762,22 +763,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19" t="str">
-        <v>Route 2</v>
+        <v>Hau'oli City</v>
       </c>
       <c r="C19" t="str">
-        <v>North</v>
+        <v>Shopping District</v>
       </c>
       <c r="D19" t="str">
-        <v>Drowzee</v>
+        <v>Bewear</v>
       </c>
       <c r="E19" t="str">
         <v>6-11</v>
       </c>
       <c r="F19" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="20">
@@ -791,10 +792,10 @@
         <v>North</v>
       </c>
       <c r="D20" t="str">
-        <v>Makuhita</v>
+        <v>Drowzee</v>
       </c>
       <c r="E20" t="str">
-        <v>6-11</v>
+        <v>8-13</v>
       </c>
       <c r="F20" t="str">
         <v>16.67%</v>
@@ -811,10 +812,10 @@
         <v>North</v>
       </c>
       <c r="D21" t="str">
-        <v>Spearow</v>
+        <v>Makuhita</v>
       </c>
       <c r="E21" t="str">
-        <v>6-11</v>
+        <v>8-13</v>
       </c>
       <c r="F21" t="str">
         <v>16.67%</v>
@@ -831,10 +832,10 @@
         <v>North</v>
       </c>
       <c r="D22" t="str">
-        <v>Ekans</v>
+        <v>Spearow</v>
       </c>
       <c r="E22" t="str">
-        <v>6-11</v>
+        <v>8-13</v>
       </c>
       <c r="F22" t="str">
         <v>16.67%</v>
@@ -851,10 +852,10 @@
         <v>North</v>
       </c>
       <c r="D23" t="str">
-        <v>Growlithe</v>
+        <v>Ekans</v>
       </c>
       <c r="E23" t="str">
-        <v>6-11</v>
+        <v>8-13</v>
       </c>
       <c r="F23" t="str">
         <v>16.67%</v>
@@ -871,10 +872,10 @@
         <v>North</v>
       </c>
       <c r="D24" t="str">
-        <v>Smeargle</v>
+        <v>Growlithe</v>
       </c>
       <c r="E24" t="str">
-        <v>6-11</v>
+        <v>8-13</v>
       </c>
       <c r="F24" t="str">
         <v>16.67%</v>
@@ -882,42 +883,42 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B25" t="str">
-        <v>Captain Ilima</v>
+        <v>Route 2</v>
       </c>
       <c r="C25" t="str">
-        <v>Boss Battle</v>
+        <v>North</v>
       </c>
       <c r="D25" t="str">
-        <v>Boss</v>
+        <v>Smeargle</v>
       </c>
       <c r="E25" t="str">
         <v>8-13</v>
       </c>
       <c r="F25" t="str">
-        <v>-</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B26" t="str">
-        <v>Hau'oli Cemetery</v>
+        <v>Captain Ilima</v>
       </c>
       <c r="C26" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D26" t="str">
-        <v>Gastly</v>
+        <v>Boss</v>
       </c>
       <c r="E26" t="str">
         <v>9-14</v>
       </c>
       <c r="F26" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="27">
@@ -931,10 +932,10 @@
         <v>Main Area</v>
       </c>
       <c r="D27" t="str">
-        <v>Drifloon</v>
+        <v>Gastly</v>
       </c>
       <c r="E27" t="str">
-        <v>9-14</v>
+        <v>11-16</v>
       </c>
       <c r="F27" t="str">
         <v>25.00%</v>
@@ -951,10 +952,10 @@
         <v>Main Area</v>
       </c>
       <c r="D28" t="str">
-        <v>Murkrow</v>
+        <v>Drifloon</v>
       </c>
       <c r="E28" t="str">
-        <v>9-14</v>
+        <v>11-16</v>
       </c>
       <c r="F28" t="str">
         <v>25.00%</v>
@@ -971,10 +972,10 @@
         <v>Main Area</v>
       </c>
       <c r="D29" t="str">
-        <v>Misdreavus</v>
+        <v>Murkrow</v>
       </c>
       <c r="E29" t="str">
-        <v>9-14</v>
+        <v>11-16</v>
       </c>
       <c r="F29" t="str">
         <v>25.00%</v>
@@ -982,22 +983,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B30" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Hau'oli Cemetery</v>
       </c>
       <c r="C30" t="str">
-        <v>Farthest Hollow</v>
+        <v>Main Area</v>
       </c>
       <c r="D30" t="str">
-        <v>Roggenrola</v>
+        <v>Misdreavus</v>
       </c>
       <c r="E30" t="str">
-        <v>14-19</v>
+        <v>11-16</v>
       </c>
       <c r="F30" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="31">
@@ -1011,10 +1012,10 @@
         <v>Farthest Hollow</v>
       </c>
       <c r="D31" t="str">
-        <v>Carbink</v>
+        <v>Roggenrola</v>
       </c>
       <c r="E31" t="str">
-        <v>14-19</v>
+        <v>15-20</v>
       </c>
       <c r="F31" t="str">
         <v>20.00%</v>
@@ -1031,10 +1032,10 @@
         <v>Farthest Hollow</v>
       </c>
       <c r="D32" t="str">
-        <v>Spinda</v>
+        <v>Carbink</v>
       </c>
       <c r="E32" t="str">
-        <v>14-19</v>
+        <v>15-20</v>
       </c>
       <c r="F32" t="str">
         <v>20.00%</v>
@@ -1051,10 +1052,10 @@
         <v>Farthest Hollow</v>
       </c>
       <c r="D33" t="str">
-        <v>Mawile</v>
+        <v>Spinda</v>
       </c>
       <c r="E33" t="str">
-        <v>14-19</v>
+        <v>15-20</v>
       </c>
       <c r="F33" t="str">
         <v>20.00%</v>
@@ -1071,10 +1072,10 @@
         <v>Farthest Hollow</v>
       </c>
       <c r="D34" t="str">
-        <v>Lycanroc</v>
+        <v>Mawile</v>
       </c>
       <c r="E34" t="str">
-        <v>14-19</v>
+        <v>15-20</v>
       </c>
       <c r="F34" t="str">
         <v>20.00%</v>
@@ -1082,22 +1083,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B35" t="str">
-        <v>Seaward Cave</v>
+        <v>Ten Carat Hill</v>
       </c>
       <c r="C35" t="str">
-        <v>Main Area</v>
+        <v>Farthest Hollow</v>
       </c>
       <c r="D35" t="str">
-        <v>Barboach</v>
+        <v>Lycanroc</v>
       </c>
       <c r="E35" t="str">
         <v>15-20</v>
       </c>
       <c r="F35" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="36">
@@ -1111,10 +1112,10 @@
         <v>Main Area</v>
       </c>
       <c r="D36" t="str">
-        <v>Smoochum</v>
+        <v>Barboach</v>
       </c>
       <c r="E36" t="str">
-        <v>15-20</v>
+        <v>17-22</v>
       </c>
       <c r="F36" t="str">
         <v>33.33%</v>
@@ -1131,10 +1132,10 @@
         <v>Main Area</v>
       </c>
       <c r="D37" t="str">
-        <v>Seel</v>
+        <v>Smoochum</v>
       </c>
       <c r="E37" t="str">
-        <v>15-20</v>
+        <v>17-22</v>
       </c>
       <c r="F37" t="str">
         <v>33.33%</v>
@@ -1142,42 +1143,42 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B38" t="str">
-        <v>Kahuna Hala</v>
+        <v>Seaward Cave</v>
       </c>
       <c r="C38" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D38" t="str">
-        <v>Boss</v>
+        <v>Seel</v>
       </c>
       <c r="E38" t="str">
         <v>17-22</v>
       </c>
       <c r="F38" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B39" t="str">
-        <v>Heahea Beach</v>
+        <v>Kahuna Hala</v>
       </c>
       <c r="C39" t="str">
-        <v>Main Area Part 1</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D39" t="str">
-        <v>Vikavolt</v>
+        <v>Boss</v>
       </c>
       <c r="E39" t="str">
         <v>18-23</v>
       </c>
       <c r="F39" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="40">
@@ -1191,10 +1192,10 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D40" t="str">
-        <v>Ribombee</v>
+        <v>Vikavolt</v>
       </c>
       <c r="E40" t="str">
-        <v>18-23</v>
+        <v>20-25</v>
       </c>
       <c r="F40" t="str">
         <v>20.00%</v>
@@ -1211,10 +1212,10 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D41" t="str">
-        <v>Araquanid</v>
+        <v>Ribombee</v>
       </c>
       <c r="E41" t="str">
-        <v>18-23</v>
+        <v>20-25</v>
       </c>
       <c r="F41" t="str">
         <v>20.00%</v>
@@ -1231,10 +1232,10 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D42" t="str">
-        <v>Lurantis</v>
+        <v>Araquanid</v>
       </c>
       <c r="E42" t="str">
-        <v>18-23</v>
+        <v>20-25</v>
       </c>
       <c r="F42" t="str">
         <v>20.00%</v>
@@ -1251,10 +1252,10 @@
         <v>Main Area Part 1</v>
       </c>
       <c r="D43" t="str">
-        <v>Salazzle</v>
+        <v>Lurantis</v>
       </c>
       <c r="E43" t="str">
-        <v>18-23</v>
+        <v>20-25</v>
       </c>
       <c r="F43" t="str">
         <v>20.00%</v>
@@ -1262,19 +1263,19 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B44" t="str">
         <v>Heahea Beach</v>
       </c>
       <c r="C44" t="str">
-        <v>Main Area Part 2</v>
+        <v>Main Area Part 1</v>
       </c>
       <c r="D44" t="str">
-        <v>Alolan Marowak</v>
+        <v>Salazzle</v>
       </c>
       <c r="E44" t="str">
-        <v>18-23</v>
+        <v>20-25</v>
       </c>
       <c r="F44" t="str">
         <v>20.00%</v>
@@ -1291,10 +1292,10 @@
         <v>Main Area Part 2</v>
       </c>
       <c r="D45" t="str">
-        <v>Kommo-o</v>
+        <v>Alolan Marowak</v>
       </c>
       <c r="E45" t="str">
-        <v>18-23</v>
+        <v>20-25</v>
       </c>
       <c r="F45" t="str">
         <v>20.00%</v>
@@ -1311,10 +1312,10 @@
         <v>Main Area Part 2</v>
       </c>
       <c r="D46" t="str">
-        <v>Mimikyu</v>
+        <v>Kommo-o</v>
       </c>
       <c r="E46" t="str">
-        <v>18-23</v>
+        <v>20-25</v>
       </c>
       <c r="F46" t="str">
         <v>20.00%</v>
@@ -1331,10 +1332,10 @@
         <v>Main Area Part 2</v>
       </c>
       <c r="D47" t="str">
-        <v>Poliwhirl</v>
+        <v>Mimikyu</v>
       </c>
       <c r="E47" t="str">
-        <v>18-23</v>
+        <v>20-25</v>
       </c>
       <c r="F47" t="str">
         <v>20.00%</v>
@@ -1351,10 +1352,10 @@
         <v>Main Area Part 2</v>
       </c>
       <c r="D48" t="str">
-        <v>Ditto</v>
+        <v>Poliwhirl</v>
       </c>
       <c r="E48" t="str">
-        <v>18-23</v>
+        <v>20-25</v>
       </c>
       <c r="F48" t="str">
         <v>20.00%</v>
@@ -1362,22 +1363,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B49" t="str">
-        <v>Paniola Ranch</v>
+        <v>Heahea Beach</v>
       </c>
       <c r="C49" t="str">
-        <v>Main Area</v>
+        <v>Main Area Part 2</v>
       </c>
       <c r="D49" t="str">
-        <v>Eevee</v>
+        <v>Ditto</v>
       </c>
       <c r="E49" t="str">
         <v>20-25</v>
       </c>
       <c r="F49" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="50">
@@ -1391,10 +1392,10 @@
         <v>Main Area</v>
       </c>
       <c r="D50" t="str">
-        <v>Mareep</v>
+        <v>Eevee</v>
       </c>
       <c r="E50" t="str">
-        <v>20-25</v>
+        <v>21-26</v>
       </c>
       <c r="F50" t="str">
         <v>25.00%</v>
@@ -1411,10 +1412,10 @@
         <v>Main Area</v>
       </c>
       <c r="D51" t="str">
-        <v>Tauros</v>
+        <v>Mareep</v>
       </c>
       <c r="E51" t="str">
-        <v>20-25</v>
+        <v>21-26</v>
       </c>
       <c r="F51" t="str">
         <v>25.00%</v>
@@ -1431,10 +1432,10 @@
         <v>Main Area</v>
       </c>
       <c r="D52" t="str">
-        <v>Miltank</v>
+        <v>Tauros</v>
       </c>
       <c r="E52" t="str">
-        <v>20-25</v>
+        <v>21-26</v>
       </c>
       <c r="F52" t="str">
         <v>25.00%</v>
@@ -1442,42 +1443,42 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B53" t="str">
-        <v>Daycare</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C53" t="str">
-        <v>NPC</v>
+        <v>Main Area</v>
       </c>
       <c r="D53" t="str">
-        <v>NPC</v>
+        <v>Miltank</v>
       </c>
       <c r="E53" t="str">
-        <v>-</v>
+        <v>21-26</v>
       </c>
       <c r="F53" t="str">
-        <v>-</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B54" t="str">
-        <v>Route 5</v>
+        <v>Daycare</v>
       </c>
       <c r="C54" t="str">
-        <v>Main Area</v>
+        <v>NPC</v>
       </c>
       <c r="D54" t="str">
-        <v>Noibat</v>
+        <v>NPC</v>
       </c>
       <c r="E54" t="str">
-        <v>23-28</v>
+        <v>-</v>
       </c>
       <c r="F54" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="55">
@@ -1491,10 +1492,10 @@
         <v>Main Area</v>
       </c>
       <c r="D55" t="str">
-        <v>Fomantis</v>
+        <v>Noibat</v>
       </c>
       <c r="E55" t="str">
-        <v>23-28</v>
+        <v>24-29</v>
       </c>
       <c r="F55" t="str">
         <v>33.33%</v>
@@ -1511,10 +1512,10 @@
         <v>Main Area</v>
       </c>
       <c r="D56" t="str">
-        <v>Bounsweet</v>
+        <v>Fomantis</v>
       </c>
       <c r="E56" t="str">
-        <v>23-28</v>
+        <v>24-29</v>
       </c>
       <c r="F56" t="str">
         <v>33.33%</v>
@@ -1522,22 +1523,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B57" t="str">
-        <v>Brooklet Hill</v>
+        <v>Route 5</v>
       </c>
       <c r="C57" t="str">
-        <v>South</v>
+        <v>Main Area</v>
       </c>
       <c r="D57" t="str">
-        <v>Wingull</v>
+        <v>Bounsweet</v>
       </c>
       <c r="E57" t="str">
         <v>24-29</v>
       </c>
       <c r="F57" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="58">
@@ -1551,10 +1552,10 @@
         <v>South</v>
       </c>
       <c r="D58" t="str">
-        <v>Lillipup</v>
+        <v>Wingull</v>
       </c>
       <c r="E58" t="str">
-        <v>24-29</v>
+        <v>25-30</v>
       </c>
       <c r="F58" t="str">
         <v>20.00%</v>
@@ -1571,10 +1572,10 @@
         <v>South</v>
       </c>
       <c r="D59" t="str">
-        <v>Paras</v>
+        <v>Lillipup</v>
       </c>
       <c r="E59" t="str">
-        <v>24-29</v>
+        <v>25-30</v>
       </c>
       <c r="F59" t="str">
         <v>20.00%</v>
@@ -1591,10 +1592,10 @@
         <v>South</v>
       </c>
       <c r="D60" t="str">
-        <v>Goldeen</v>
+        <v>Paras</v>
       </c>
       <c r="E60" t="str">
-        <v>24-29</v>
+        <v>25-30</v>
       </c>
       <c r="F60" t="str">
         <v>20.00%</v>
@@ -1611,10 +1612,10 @@
         <v>South</v>
       </c>
       <c r="D61" t="str">
-        <v>Feebas</v>
+        <v>Goldeen</v>
       </c>
       <c r="E61" t="str">
-        <v>24-29</v>
+        <v>25-30</v>
       </c>
       <c r="F61" t="str">
         <v>20.00%</v>
@@ -1622,42 +1623,42 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B62" t="str">
-        <v>Captain Lana</v>
+        <v>Brooklet Hill</v>
       </c>
       <c r="C62" t="str">
-        <v>Boss Battle</v>
+        <v>South</v>
       </c>
       <c r="D62" t="str">
-        <v>Boss</v>
+        <v>Feebas</v>
       </c>
       <c r="E62" t="str">
-        <v>26-31</v>
+        <v>25-30</v>
       </c>
       <c r="F62" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B63" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Captain Lana</v>
       </c>
       <c r="C63" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D63" t="str">
-        <v>Cubone</v>
+        <v>Boss</v>
       </c>
       <c r="E63" t="str">
         <v>27-32</v>
       </c>
       <c r="F63" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="64">
@@ -1671,10 +1672,10 @@
         <v>Main Area</v>
       </c>
       <c r="D64" t="str">
-        <v>Kangaskhan</v>
+        <v>Cubone</v>
       </c>
       <c r="E64" t="str">
-        <v>27-32</v>
+        <v>28-33</v>
       </c>
       <c r="F64" t="str">
         <v>33.33%</v>
@@ -1691,10 +1692,10 @@
         <v>Main Area</v>
       </c>
       <c r="D65" t="str">
-        <v>Magby</v>
+        <v>Kangaskhan</v>
       </c>
       <c r="E65" t="str">
-        <v>27-32</v>
+        <v>28-33</v>
       </c>
       <c r="F65" t="str">
         <v>33.33%</v>
@@ -1702,42 +1703,42 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B66" t="str">
-        <v>Captain Kiawe</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C66" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D66" t="str">
-        <v>Boss</v>
+        <v>Magby</v>
       </c>
       <c r="E66" t="str">
-        <v>29-34</v>
+        <v>28-33</v>
       </c>
       <c r="F66" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B67" t="str">
-        <v>Route 7</v>
+        <v>Captain Kiawe</v>
       </c>
       <c r="C67" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D67" t="str">
-        <v>Staryu</v>
+        <v>Boss</v>
       </c>
       <c r="E67" t="str">
         <v>30-35</v>
       </c>
       <c r="F67" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="68">
@@ -1751,10 +1752,10 @@
         <v>Main Area</v>
       </c>
       <c r="D68" t="str">
-        <v>Pyukumuku</v>
+        <v>Staryu</v>
       </c>
       <c r="E68" t="str">
-        <v>30-35</v>
+        <v>31-36</v>
       </c>
       <c r="F68" t="str">
         <v>20.00%</v>
@@ -1771,10 +1772,10 @@
         <v>Main Area</v>
       </c>
       <c r="D69" t="str">
-        <v>Corsola</v>
+        <v>Pyukumuku</v>
       </c>
       <c r="E69" t="str">
-        <v>30-35</v>
+        <v>31-36</v>
       </c>
       <c r="F69" t="str">
         <v>20.00%</v>
@@ -1791,10 +1792,10 @@
         <v>Main Area</v>
       </c>
       <c r="D70" t="str">
-        <v>Mareanie</v>
+        <v>Corsola</v>
       </c>
       <c r="E70" t="str">
-        <v>30-35</v>
+        <v>31-36</v>
       </c>
       <c r="F70" t="str">
         <v>20.00%</v>
@@ -1811,10 +1812,10 @@
         <v>Main Area</v>
       </c>
       <c r="D71" t="str">
-        <v>Bruxish</v>
+        <v>Mareanie</v>
       </c>
       <c r="E71" t="str">
-        <v>30-35</v>
+        <v>31-36</v>
       </c>
       <c r="F71" t="str">
         <v>20.00%</v>
@@ -1822,19 +1823,19 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B72" t="str">
-        <v>Route 8</v>
+        <v>Route 7</v>
       </c>
       <c r="C72" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>Main Area</v>
       </c>
       <c r="D72" t="str">
-        <v>Omanyte</v>
+        <v>Bruxish</v>
       </c>
       <c r="E72" t="str">
-        <v>32-37</v>
+        <v>31-36</v>
       </c>
       <c r="F72" t="str">
         <v>20.00%</v>
@@ -1851,10 +1852,10 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D73" t="str">
-        <v>Kabuto</v>
+        <v>Omanyte</v>
       </c>
       <c r="E73" t="str">
-        <v>32-37</v>
+        <v>33-38</v>
       </c>
       <c r="F73" t="str">
         <v>20.00%</v>
@@ -1871,10 +1872,10 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D74" t="str">
-        <v>Lileep</v>
+        <v>Kabuto</v>
       </c>
       <c r="E74" t="str">
-        <v>32-37</v>
+        <v>33-38</v>
       </c>
       <c r="F74" t="str">
         <v>20.00%</v>
@@ -1891,10 +1892,10 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D75" t="str">
-        <v>Anorith</v>
+        <v>Lileep</v>
       </c>
       <c r="E75" t="str">
-        <v>32-37</v>
+        <v>33-38</v>
       </c>
       <c r="F75" t="str">
         <v>20.00%</v>
@@ -1911,10 +1912,10 @@
         <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D76" t="str">
-        <v>Cranidos</v>
+        <v>Anorith</v>
       </c>
       <c r="E76" t="str">
-        <v>32-37</v>
+        <v>33-38</v>
       </c>
       <c r="F76" t="str">
         <v>20.00%</v>
@@ -1922,19 +1923,19 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B77" t="str">
         <v>Route 8</v>
       </c>
       <c r="C77" t="str">
-        <v>Fossil Restoration Center Part 2</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D77" t="str">
-        <v>Shieldon</v>
+        <v>Cranidos</v>
       </c>
       <c r="E77" t="str">
-        <v>32-37</v>
+        <v>33-38</v>
       </c>
       <c r="F77" t="str">
         <v>20.00%</v>
@@ -1951,10 +1952,10 @@
         <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D78" t="str">
-        <v>Archen</v>
+        <v>Shieldon</v>
       </c>
       <c r="E78" t="str">
-        <v>32-37</v>
+        <v>33-38</v>
       </c>
       <c r="F78" t="str">
         <v>20.00%</v>
@@ -1971,10 +1972,10 @@
         <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D79" t="str">
-        <v>Tirtouga</v>
+        <v>Archen</v>
       </c>
       <c r="E79" t="str">
-        <v>32-37</v>
+        <v>33-38</v>
       </c>
       <c r="F79" t="str">
         <v>20.00%</v>
@@ -1991,10 +1992,10 @@
         <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D80" t="str">
-        <v>Tyrunt</v>
+        <v>Tirtouga</v>
       </c>
       <c r="E80" t="str">
-        <v>32-37</v>
+        <v>33-38</v>
       </c>
       <c r="F80" t="str">
         <v>20.00%</v>
@@ -2011,10 +2012,10 @@
         <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D81" t="str">
-        <v>Amaura</v>
+        <v>Tyrunt</v>
       </c>
       <c r="E81" t="str">
-        <v>32-37</v>
+        <v>33-38</v>
       </c>
       <c r="F81" t="str">
         <v>20.00%</v>
@@ -2022,22 +2023,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B82" t="str">
-        <v>Lush Jungle</v>
+        <v>Route 8</v>
       </c>
       <c r="C82" t="str">
-        <v>North</v>
+        <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D82" t="str">
-        <v>Trumbeak</v>
+        <v>Amaura</v>
       </c>
       <c r="E82" t="str">
         <v>33-38</v>
       </c>
       <c r="F82" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="83">
@@ -2051,10 +2052,10 @@
         <v>North</v>
       </c>
       <c r="D83" t="str">
-        <v>Steenee</v>
+        <v>Trumbeak</v>
       </c>
       <c r="E83" t="str">
-        <v>33-38</v>
+        <v>34-39</v>
       </c>
       <c r="F83" t="str">
         <v>16.67%</v>
@@ -2071,10 +2072,10 @@
         <v>North</v>
       </c>
       <c r="D84" t="str">
-        <v>Comfey</v>
+        <v>Steenee</v>
       </c>
       <c r="E84" t="str">
-        <v>33-38</v>
+        <v>34-39</v>
       </c>
       <c r="F84" t="str">
         <v>16.67%</v>
@@ -2091,10 +2092,10 @@
         <v>North</v>
       </c>
       <c r="D85" t="str">
-        <v>Hoothoot</v>
+        <v>Comfey</v>
       </c>
       <c r="E85" t="str">
-        <v>33-38</v>
+        <v>34-39</v>
       </c>
       <c r="F85" t="str">
         <v>16.67%</v>
@@ -2111,10 +2112,10 @@
         <v>North</v>
       </c>
       <c r="D86" t="str">
-        <v>Oranguru</v>
+        <v>Hoothoot</v>
       </c>
       <c r="E86" t="str">
-        <v>33-38</v>
+        <v>34-39</v>
       </c>
       <c r="F86" t="str">
         <v>16.67%</v>
@@ -2131,10 +2132,10 @@
         <v>North</v>
       </c>
       <c r="D87" t="str">
-        <v>Bounsweet</v>
+        <v>Oranguru</v>
       </c>
       <c r="E87" t="str">
-        <v>33-38</v>
+        <v>34-39</v>
       </c>
       <c r="F87" t="str">
         <v>16.67%</v>
@@ -2142,22 +2143,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B88" t="str">
         <v>Lush Jungle</v>
       </c>
       <c r="C88" t="str">
-        <v>East Cave</v>
+        <v>North</v>
       </c>
       <c r="D88" t="str">
-        <v>Golbat</v>
+        <v>Bounsweet</v>
       </c>
       <c r="E88" t="str">
-        <v>35-40</v>
+        <v>34-39</v>
       </c>
       <c r="F88" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="89">
@@ -2171,10 +2172,10 @@
         <v>East Cave</v>
       </c>
       <c r="D89" t="str">
-        <v>Salandit</v>
+        <v>Golbat</v>
       </c>
       <c r="E89" t="str">
-        <v>35-40</v>
+        <v>36-41</v>
       </c>
       <c r="F89" t="str">
         <v>20.00%</v>
@@ -2191,10 +2192,10 @@
         <v>East Cave</v>
       </c>
       <c r="D90" t="str">
-        <v>Larvesta</v>
+        <v>Salandit</v>
       </c>
       <c r="E90" t="str">
-        <v>35-40</v>
+        <v>36-41</v>
       </c>
       <c r="F90" t="str">
         <v>20.00%</v>
@@ -2211,10 +2212,10 @@
         <v>East Cave</v>
       </c>
       <c r="D91" t="str">
-        <v>Oranguru</v>
+        <v>Larvesta</v>
       </c>
       <c r="E91" t="str">
-        <v>35-40</v>
+        <v>36-41</v>
       </c>
       <c r="F91" t="str">
         <v>20.00%</v>
@@ -2231,10 +2232,10 @@
         <v>East Cave</v>
       </c>
       <c r="D92" t="str">
-        <v>Passimian</v>
+        <v>Oranguru</v>
       </c>
       <c r="E92" t="str">
-        <v>35-40</v>
+        <v>36-41</v>
       </c>
       <c r="F92" t="str">
         <v>20.00%</v>
@@ -2242,42 +2243,42 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B93" t="str">
-        <v>Captain Mallow</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C93" t="str">
-        <v>Boss Battle</v>
+        <v>East Cave</v>
       </c>
       <c r="D93" t="str">
-        <v>Boss</v>
+        <v>Passimian</v>
       </c>
       <c r="E93" t="str">
         <v>36-41</v>
       </c>
       <c r="F93" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B94" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Captain Mallow</v>
       </c>
       <c r="C94" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D94" t="str">
-        <v>Zubat</v>
+        <v>Boss</v>
       </c>
       <c r="E94" t="str">
-        <v>38-43</v>
+        <v>37-42</v>
       </c>
       <c r="F94" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="95">
@@ -2291,10 +2292,10 @@
         <v>Main Area</v>
       </c>
       <c r="D95" t="str">
-        <v>Alolan Diglett</v>
+        <v>Zubat</v>
       </c>
       <c r="E95" t="str">
-        <v>38-43</v>
+        <v>39-44</v>
       </c>
       <c r="F95" t="str">
         <v>25.00%</v>
@@ -2311,10 +2312,10 @@
         <v>Main Area</v>
       </c>
       <c r="D96" t="str">
-        <v>Kecleon</v>
+        <v>Alolan Diglett</v>
       </c>
       <c r="E96" t="str">
-        <v>38-43</v>
+        <v>39-44</v>
       </c>
       <c r="F96" t="str">
         <v>25.00%</v>
@@ -2331,10 +2332,10 @@
         <v>Main Area</v>
       </c>
       <c r="D97" t="str">
-        <v>Larvitar</v>
+        <v>Kecleon</v>
       </c>
       <c r="E97" t="str">
-        <v>38-43</v>
+        <v>39-44</v>
       </c>
       <c r="F97" t="str">
         <v>25.00%</v>
@@ -2342,22 +2343,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B98" t="str">
-        <v>Akala Outskirts</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C98" t="str">
         <v>Main Area</v>
       </c>
       <c r="D98" t="str">
-        <v>Gumshoos</v>
+        <v>Larvitar</v>
       </c>
       <c r="E98" t="str">
-        <v>42-47</v>
+        <v>39-44</v>
       </c>
       <c r="F98" t="str">
-        <v>12.50%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="99">
@@ -2371,10 +2372,10 @@
         <v>Main Area</v>
       </c>
       <c r="D99" t="str">
-        <v>Wingull</v>
+        <v>Gumshoos</v>
       </c>
       <c r="E99" t="str">
-        <v>42-47</v>
+        <v>43-48</v>
       </c>
       <c r="F99" t="str">
         <v>12.50%</v>
@@ -2391,10 +2392,10 @@
         <v>Main Area</v>
       </c>
       <c r="D100" t="str">
-        <v>Magikarp</v>
+        <v>Wingull</v>
       </c>
       <c r="E100" t="str">
-        <v>42-47</v>
+        <v>43-48</v>
       </c>
       <c r="F100" t="str">
         <v>12.50%</v>
@@ -2411,10 +2412,10 @@
         <v>Main Area</v>
       </c>
       <c r="D101" t="str">
-        <v>Stufful</v>
+        <v>Magikarp</v>
       </c>
       <c r="E101" t="str">
-        <v>42-47</v>
+        <v>43-48</v>
       </c>
       <c r="F101" t="str">
         <v>12.50%</v>
@@ -2431,10 +2432,10 @@
         <v>Main Area</v>
       </c>
       <c r="D102" t="str">
-        <v>Chinchou</v>
+        <v>Stufful</v>
       </c>
       <c r="E102" t="str">
-        <v>42-47</v>
+        <v>43-48</v>
       </c>
       <c r="F102" t="str">
         <v>12.50%</v>
@@ -2451,10 +2452,10 @@
         <v>Main Area</v>
       </c>
       <c r="D103" t="str">
-        <v>Alolan Raticate</v>
+        <v>Chinchou</v>
       </c>
       <c r="E103" t="str">
-        <v>42-47</v>
+        <v>43-48</v>
       </c>
       <c r="F103" t="str">
         <v>12.50%</v>
@@ -2471,10 +2472,10 @@
         <v>Main Area</v>
       </c>
       <c r="D104" t="str">
-        <v>Natu</v>
+        <v>Alolan Raticate</v>
       </c>
       <c r="E104" t="str">
-        <v>42-47</v>
+        <v>43-48</v>
       </c>
       <c r="F104" t="str">
         <v>12.50%</v>
@@ -2491,10 +2492,10 @@
         <v>Main Area</v>
       </c>
       <c r="D105" t="str">
-        <v>Nosepass</v>
+        <v>Natu</v>
       </c>
       <c r="E105" t="str">
-        <v>42-47</v>
+        <v>43-48</v>
       </c>
       <c r="F105" t="str">
         <v>12.50%</v>
@@ -2502,42 +2503,42 @@
     </row>
     <row r="106">
       <c r="A106">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B106" t="str">
-        <v>Kahuna Olivia</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C106" t="str">
-        <v>Boss Battle</v>
+        <v>Main Area</v>
       </c>
       <c r="D106" t="str">
-        <v>Boss</v>
+        <v>Nosepass</v>
       </c>
       <c r="E106" t="str">
-        <v>44-49</v>
+        <v>43-48</v>
       </c>
       <c r="F106" t="str">
-        <v>-</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="107">
       <c r="A107">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B107" t="str">
-        <v>Malie City</v>
+        <v>Kahuna Olivia</v>
       </c>
       <c r="C107" t="str">
-        <v>Outer Cape</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D107" t="str">
-        <v>Magnemite</v>
+        <v>Boss</v>
       </c>
       <c r="E107" t="str">
-        <v>47-52</v>
+        <v>44-49</v>
       </c>
       <c r="F107" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="108">
@@ -2551,7 +2552,7 @@
         <v>Outer Cape</v>
       </c>
       <c r="D108" t="str">
-        <v>Alolan Grimer</v>
+        <v>Magnemite</v>
       </c>
       <c r="E108" t="str">
         <v>47-52</v>
@@ -2571,7 +2572,7 @@
         <v>Outer Cape</v>
       </c>
       <c r="D109" t="str">
-        <v>Trubbish</v>
+        <v>Alolan Grimer</v>
       </c>
       <c r="E109" t="str">
         <v>47-52</v>
@@ -2591,7 +2592,7 @@
         <v>Outer Cape</v>
       </c>
       <c r="D110" t="str">
-        <v>Minccino</v>
+        <v>Trubbish</v>
       </c>
       <c r="E110" t="str">
         <v>47-52</v>
@@ -2611,7 +2612,7 @@
         <v>Outer Cape</v>
       </c>
       <c r="D111" t="str">
-        <v>Masquerain</v>
+        <v>Minccino</v>
       </c>
       <c r="E111" t="str">
         <v>47-52</v>
@@ -2622,22 +2623,22 @@
     </row>
     <row r="112">
       <c r="A112">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B112" t="str">
-        <v>Route 10</v>
+        <v>Malie City</v>
       </c>
       <c r="C112" t="str">
-        <v>Main Area</v>
+        <v>Outer Cape</v>
       </c>
       <c r="D112" t="str">
-        <v>Ledian</v>
+        <v>Masquerain</v>
       </c>
       <c r="E112" t="str">
-        <v>50-55</v>
+        <v>47-52</v>
       </c>
       <c r="F112" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="113">
@@ -2651,7 +2652,7 @@
         <v>Main Area</v>
       </c>
       <c r="D113" t="str">
-        <v>Ariados</v>
+        <v>Ledian</v>
       </c>
       <c r="E113" t="str">
         <v>50-55</v>
@@ -2671,7 +2672,7 @@
         <v>Main Area</v>
       </c>
       <c r="D114" t="str">
-        <v>Crabrawler</v>
+        <v>Ariados</v>
       </c>
       <c r="E114" t="str">
         <v>50-55</v>
@@ -2691,7 +2692,7 @@
         <v>Main Area</v>
       </c>
       <c r="D115" t="str">
-        <v>Fearow</v>
+        <v>Crabrawler</v>
       </c>
       <c r="E115" t="str">
         <v>50-55</v>
@@ -2711,7 +2712,7 @@
         <v>Main Area</v>
       </c>
       <c r="D116" t="str">
-        <v>Skarmory</v>
+        <v>Fearow</v>
       </c>
       <c r="E116" t="str">
         <v>50-55</v>
@@ -2731,7 +2732,7 @@
         <v>Main Area</v>
       </c>
       <c r="D117" t="str">
-        <v>Pancham</v>
+        <v>Skarmory</v>
       </c>
       <c r="E117" t="str">
         <v>50-55</v>
@@ -2742,22 +2743,22 @@
     </row>
     <row r="118">
       <c r="A118">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B118" t="str">
-        <v>Mount Hokulani</v>
+        <v>Route 10</v>
       </c>
       <c r="C118" t="str">
-        <v>East</v>
+        <v>Main Area</v>
       </c>
       <c r="D118" t="str">
-        <v>Cleffa</v>
+        <v>Pancham</v>
       </c>
       <c r="E118" t="str">
-        <v>51-56</v>
+        <v>50-55</v>
       </c>
       <c r="F118" t="str">
-        <v>25.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="119">
@@ -2771,10 +2772,10 @@
         <v>East</v>
       </c>
       <c r="D119" t="str">
-        <v>Elgyem</v>
+        <v>Cleffa</v>
       </c>
       <c r="E119" t="str">
-        <v>51-56</v>
+        <v>52-57</v>
       </c>
       <c r="F119" t="str">
         <v>25.00%</v>
@@ -2791,10 +2792,10 @@
         <v>East</v>
       </c>
       <c r="D120" t="str">
-        <v>Beldum</v>
+        <v>Elgyem</v>
       </c>
       <c r="E120" t="str">
-        <v>51-56</v>
+        <v>52-57</v>
       </c>
       <c r="F120" t="str">
         <v>25.00%</v>
@@ -2811,10 +2812,10 @@
         <v>East</v>
       </c>
       <c r="D121" t="str">
-        <v>Minior</v>
+        <v>Beldum</v>
       </c>
       <c r="E121" t="str">
-        <v>51-56</v>
+        <v>52-57</v>
       </c>
       <c r="F121" t="str">
         <v>25.00%</v>
@@ -2822,42 +2823,42 @@
     </row>
     <row r="122">
       <c r="A122">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B122" t="str">
-        <v>Captain Sophocles</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C122" t="str">
-        <v>Boss Battle</v>
+        <v>East</v>
       </c>
       <c r="D122" t="str">
-        <v>Boss</v>
+        <v>Minior</v>
       </c>
       <c r="E122" t="str">
-        <v>53-58</v>
+        <v>52-57</v>
       </c>
       <c r="F122" t="str">
-        <v>-</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="123">
       <c r="A123">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B123" t="str">
-        <v>Route 11</v>
+        <v>Captain Sophocles</v>
       </c>
       <c r="C123" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D123" t="str">
-        <v>Shiinotic</v>
+        <v>Boss</v>
       </c>
       <c r="E123" t="str">
-        <v>54-59</v>
+        <v>53-58</v>
       </c>
       <c r="F123" t="str">
-        <v>11.11%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="124">
@@ -2871,10 +2872,10 @@
         <v>Main Area</v>
       </c>
       <c r="D124" t="str">
-        <v>Parasect</v>
+        <v>Shiinotic</v>
       </c>
       <c r="E124" t="str">
-        <v>54-59</v>
+        <v>55-60</v>
       </c>
       <c r="F124" t="str">
         <v>11.11%</v>
@@ -2891,10 +2892,10 @@
         <v>Main Area</v>
       </c>
       <c r="D125" t="str">
-        <v>Komala</v>
+        <v>Parasect</v>
       </c>
       <c r="E125" t="str">
-        <v>54-59</v>
+        <v>55-60</v>
       </c>
       <c r="F125" t="str">
         <v>11.11%</v>
@@ -2911,10 +2912,10 @@
         <v>Main Area</v>
       </c>
       <c r="D126" t="str">
-        <v>Houndoom</v>
+        <v>Komala</v>
       </c>
       <c r="E126" t="str">
-        <v>54-59</v>
+        <v>55-60</v>
       </c>
       <c r="F126" t="str">
         <v>11.11%</v>
@@ -2931,10 +2932,10 @@
         <v>Main Area</v>
       </c>
       <c r="D127" t="str">
-        <v>Manectric</v>
+        <v>Houndoom</v>
       </c>
       <c r="E127" t="str">
-        <v>54-59</v>
+        <v>55-60</v>
       </c>
       <c r="F127" t="str">
         <v>11.11%</v>
@@ -2951,10 +2952,10 @@
         <v>Main Area</v>
       </c>
       <c r="D128" t="str">
-        <v>Scraggy</v>
+        <v>Manectric</v>
       </c>
       <c r="E128" t="str">
-        <v>54-59</v>
+        <v>55-60</v>
       </c>
       <c r="F128" t="str">
         <v>11.11%</v>
@@ -2971,10 +2972,10 @@
         <v>Main Area</v>
       </c>
       <c r="D129" t="str">
-        <v>Bisharp</v>
+        <v>Scraggy</v>
       </c>
       <c r="E129" t="str">
-        <v>54-59</v>
+        <v>55-60</v>
       </c>
       <c r="F129" t="str">
         <v>11.11%</v>
@@ -2991,10 +2992,10 @@
         <v>Main Area</v>
       </c>
       <c r="D130" t="str">
-        <v>Machop</v>
+        <v>Bisharp</v>
       </c>
       <c r="E130" t="str">
-        <v>54-59</v>
+        <v>55-60</v>
       </c>
       <c r="F130" t="str">
         <v>11.11%</v>
@@ -3011,10 +3012,10 @@
         <v>Main Area</v>
       </c>
       <c r="D131" t="str">
-        <v>Hawlucha</v>
+        <v>Machop</v>
       </c>
       <c r="E131" t="str">
-        <v>54-59</v>
+        <v>55-60</v>
       </c>
       <c r="F131" t="str">
         <v>11.11%</v>
@@ -3022,22 +3023,22 @@
     </row>
     <row r="132">
       <c r="A132">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B132" t="str">
-        <v>Haina Desert</v>
+        <v>Route 11</v>
       </c>
       <c r="C132" t="str">
         <v>Main Area</v>
       </c>
       <c r="D132" t="str">
-        <v>Alolan Dugtrio</v>
+        <v>Hawlucha</v>
       </c>
       <c r="E132" t="str">
-        <v>57-62</v>
+        <v>55-60</v>
       </c>
       <c r="F132" t="str">
-        <v>20.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="133">
@@ -3051,10 +3052,10 @@
         <v>Main Area</v>
       </c>
       <c r="D133" t="str">
-        <v>Sandile</v>
+        <v>Alolan Dugtrio</v>
       </c>
       <c r="E133" t="str">
-        <v>57-62</v>
+        <v>58-63</v>
       </c>
       <c r="F133" t="str">
         <v>20.00%</v>
@@ -3071,10 +3072,10 @@
         <v>Main Area</v>
       </c>
       <c r="D134" t="str">
-        <v>Krokorok</v>
+        <v>Sandile</v>
       </c>
       <c r="E134" t="str">
-        <v>57-62</v>
+        <v>58-63</v>
       </c>
       <c r="F134" t="str">
         <v>20.00%</v>
@@ -3091,10 +3092,10 @@
         <v>Main Area</v>
       </c>
       <c r="D135" t="str">
-        <v>Staryu</v>
+        <v>Krokorok</v>
       </c>
       <c r="E135" t="str">
-        <v>57-62</v>
+        <v>58-63</v>
       </c>
       <c r="F135" t="str">
         <v>20.00%</v>
@@ -3111,10 +3112,10 @@
         <v>Main Area</v>
       </c>
       <c r="D136" t="str">
-        <v>Sandygast</v>
+        <v>Staryu</v>
       </c>
       <c r="E136" t="str">
-        <v>57-62</v>
+        <v>58-63</v>
       </c>
       <c r="F136" t="str">
         <v>20.00%</v>
@@ -3122,22 +3123,22 @@
     </row>
     <row r="137">
       <c r="A137">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B137" t="str">
-        <v>Tapu Village</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C137" t="str">
         <v>Main Area</v>
       </c>
       <c r="D137" t="str">
-        <v>Graveler</v>
+        <v>Sandygast</v>
       </c>
       <c r="E137" t="str">
-        <v>59-64</v>
+        <v>58-63</v>
       </c>
       <c r="F137" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="138">
@@ -3151,7 +3152,7 @@
         <v>Main Area</v>
       </c>
       <c r="D138" t="str">
-        <v>Bruxish</v>
+        <v>Graveler</v>
       </c>
       <c r="E138" t="str">
         <v>59-64</v>
@@ -3171,7 +3172,7 @@
         <v>Main Area</v>
       </c>
       <c r="D139" t="str">
-        <v>Absol</v>
+        <v>Bruxish</v>
       </c>
       <c r="E139" t="str">
         <v>59-64</v>
@@ -3191,7 +3192,7 @@
         <v>Main Area</v>
       </c>
       <c r="D140" t="str">
-        <v>Snorunt</v>
+        <v>Absol</v>
       </c>
       <c r="E140" t="str">
         <v>59-64</v>
@@ -3211,7 +3212,7 @@
         <v>Main Area</v>
       </c>
       <c r="D141" t="str">
-        <v>Alolan Sandshrew</v>
+        <v>Snorunt</v>
       </c>
       <c r="E141" t="str">
         <v>59-64</v>
@@ -3231,7 +3232,7 @@
         <v>Main Area</v>
       </c>
       <c r="D142" t="str">
-        <v>Alolan Vulpix</v>
+        <v>Alolan Sandshrew</v>
       </c>
       <c r="E142" t="str">
         <v>59-64</v>
@@ -3242,22 +3243,22 @@
     </row>
     <row r="143">
       <c r="A143">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B143" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C143" t="str">
-        <v>Abandoned Site</v>
+        <v>Main Area</v>
       </c>
       <c r="D143" t="str">
-        <v>Haunter</v>
+        <v>Alolan Vulpix</v>
       </c>
       <c r="E143" t="str">
-        <v>62-67</v>
+        <v>59-64</v>
       </c>
       <c r="F143" t="str">
-        <v>25.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="144">
@@ -3271,7 +3272,7 @@
         <v>Abandoned Site</v>
       </c>
       <c r="D144" t="str">
-        <v>Klefki</v>
+        <v>Haunter</v>
       </c>
       <c r="E144" t="str">
         <v>62-67</v>
@@ -3291,7 +3292,7 @@
         <v>Abandoned Site</v>
       </c>
       <c r="D145" t="str">
-        <v>Shuppet</v>
+        <v>Klefki</v>
       </c>
       <c r="E145" t="str">
         <v>62-67</v>
@@ -3311,7 +3312,7 @@
         <v>Abandoned Site</v>
       </c>
       <c r="D146" t="str">
-        <v>Boldore</v>
+        <v>Shuppet</v>
       </c>
       <c r="E146" t="str">
         <v>62-67</v>
@@ -3322,30 +3323,30 @@
     </row>
     <row r="147">
       <c r="A147">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B147" t="str">
-        <v>Captain Acerola</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C147" t="str">
-        <v>Boss Battle</v>
+        <v>Abandoned Site</v>
       </c>
       <c r="D147" t="str">
-        <v>Boss</v>
+        <v>Boldore</v>
       </c>
       <c r="E147" t="str">
-        <v>63-68</v>
+        <v>62-67</v>
       </c>
       <c r="F147" t="str">
-        <v>-</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="148">
       <c r="A148">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B148" t="str">
-        <v>Kahuna Nanu</v>
+        <v>Captain Acerola</v>
       </c>
       <c r="C148" t="str">
         <v>Boss Battle</v>
@@ -3354,7 +3355,7 @@
         <v>Boss</v>
       </c>
       <c r="E148" t="str">
-        <v>68-73</v>
+        <v>64-69</v>
       </c>
       <c r="F148" t="str">
         <v>-</v>
@@ -3362,22 +3363,22 @@
     </row>
     <row r="149">
       <c r="A149">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B149" t="str">
-        <v>Seafolk Village</v>
+        <v>Kahuna Nanu</v>
       </c>
       <c r="C149" t="str">
-        <v>Main</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D149" t="str">
-        <v>Steenee</v>
+        <v>Boss</v>
       </c>
       <c r="E149" t="str">
-        <v>69-74</v>
+        <v>68-73</v>
       </c>
       <c r="F149" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="150">
@@ -3391,7 +3392,7 @@
         <v>Main</v>
       </c>
       <c r="D150" t="str">
-        <v>Shellos</v>
+        <v>Steenee</v>
       </c>
       <c r="E150" t="str">
         <v>69-74</v>
@@ -3411,7 +3412,7 @@
         <v>Main</v>
       </c>
       <c r="D151" t="str">
-        <v>Dhelmise</v>
+        <v>Shellos</v>
       </c>
       <c r="E151" t="str">
         <v>69-74</v>
@@ -3422,22 +3423,22 @@
     </row>
     <row r="152">
       <c r="A152">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B152" t="str">
-        <v>Poni Wilds</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C152" t="str">
-        <v>Main Area</v>
+        <v>Main</v>
       </c>
       <c r="D152" t="str">
-        <v>Tentacruel</v>
+        <v>Dhelmise</v>
       </c>
       <c r="E152" t="str">
-        <v>71-76</v>
+        <v>69-74</v>
       </c>
       <c r="F152" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="153">
@@ -3451,7 +3452,7 @@
         <v>Main Area</v>
       </c>
       <c r="D153" t="str">
-        <v>Lumineon</v>
+        <v>Tentacruel</v>
       </c>
       <c r="E153" t="str">
         <v>71-76</v>
@@ -3471,7 +3472,7 @@
         <v>Main Area</v>
       </c>
       <c r="D154" t="str">
-        <v>Lapras</v>
+        <v>Lumineon</v>
       </c>
       <c r="E154" t="str">
         <v>71-76</v>
@@ -3491,7 +3492,7 @@
         <v>Main Area</v>
       </c>
       <c r="D155" t="str">
-        <v>Noivern</v>
+        <v>Lapras</v>
       </c>
       <c r="E155" t="str">
         <v>71-76</v>
@@ -3511,7 +3512,7 @@
         <v>Main Area</v>
       </c>
       <c r="D156" t="str">
-        <v>Druddigon</v>
+        <v>Noivern</v>
       </c>
       <c r="E156" t="str">
         <v>71-76</v>
@@ -3522,19 +3523,19 @@
     </row>
     <row r="157">
       <c r="A157">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B157" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C157" t="str">
         <v>Main Area</v>
       </c>
       <c r="D157" t="str">
-        <v>Wimpod</v>
+        <v>Druddigon</v>
       </c>
       <c r="E157" t="str">
-        <v>72-77</v>
+        <v>71-76</v>
       </c>
       <c r="F157" t="str">
         <v>20.00%</v>
@@ -3551,7 +3552,7 @@
         <v>Main Area</v>
       </c>
       <c r="D158" t="str">
-        <v>Relicanth</v>
+        <v>Wimpod</v>
       </c>
       <c r="E158" t="str">
         <v>72-77</v>
@@ -3571,7 +3572,7 @@
         <v>Main Area</v>
       </c>
       <c r="D159" t="str">
-        <v>Wailmer</v>
+        <v>Relicanth</v>
       </c>
       <c r="E159" t="str">
         <v>72-77</v>
@@ -3591,7 +3592,7 @@
         <v>Main Area</v>
       </c>
       <c r="D160" t="str">
-        <v>Carvanha</v>
+        <v>Wailmer</v>
       </c>
       <c r="E160" t="str">
         <v>72-77</v>
@@ -3611,7 +3612,7 @@
         <v>Main Area</v>
       </c>
       <c r="D161" t="str">
-        <v>Sharpedo</v>
+        <v>Carvanha</v>
       </c>
       <c r="E161" t="str">
         <v>72-77</v>
@@ -3622,22 +3623,22 @@
     </row>
     <row r="162">
       <c r="A162">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B162" t="str">
-        <v>Exeggutor Island</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C162" t="str">
         <v>Main Area</v>
       </c>
       <c r="D162" t="str">
-        <v>Pelipper</v>
+        <v>Sharpedo</v>
       </c>
       <c r="E162" t="str">
-        <v>74-79</v>
+        <v>72-77</v>
       </c>
       <c r="F162" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="163">
@@ -3651,7 +3652,7 @@
         <v>Main Area</v>
       </c>
       <c r="D163" t="str">
-        <v>Pinsir</v>
+        <v>Pelipper</v>
       </c>
       <c r="E163" t="str">
         <v>74-79</v>
@@ -3671,7 +3672,7 @@
         <v>Main Area</v>
       </c>
       <c r="D164" t="str">
-        <v>Gastrodon</v>
+        <v>Pinsir</v>
       </c>
       <c r="E164" t="str">
         <v>74-79</v>
@@ -3691,7 +3692,7 @@
         <v>Main Area</v>
       </c>
       <c r="D165" t="str">
-        <v>Exeggcute</v>
+        <v>Gastrodon</v>
       </c>
       <c r="E165" t="str">
         <v>74-79</v>
@@ -3711,7 +3712,7 @@
         <v>Main Area</v>
       </c>
       <c r="D166" t="str">
-        <v>Tropius</v>
+        <v>Exeggcute</v>
       </c>
       <c r="E166" t="str">
         <v>74-79</v>
@@ -3731,7 +3732,7 @@
         <v>Main Area</v>
       </c>
       <c r="D167" t="str">
-        <v>Alolan Exeggutor</v>
+        <v>Tropius</v>
       </c>
       <c r="E167" t="str">
         <v>74-79</v>
@@ -3742,22 +3743,22 @@
     </row>
     <row r="168">
       <c r="A168">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B168" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C168" t="str">
-        <v>Outside</v>
+        <v>Main Area</v>
       </c>
       <c r="D168" t="str">
-        <v>Machoke</v>
+        <v>Alolan Exeggutor</v>
       </c>
       <c r="E168" t="str">
-        <v>75-80</v>
+        <v>74-79</v>
       </c>
       <c r="F168" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="169">
@@ -3771,7 +3772,7 @@
         <v>Outside</v>
       </c>
       <c r="D169" t="str">
-        <v>Mienfoo</v>
+        <v>Machoke</v>
       </c>
       <c r="E169" t="str">
         <v>75-80</v>
@@ -3791,7 +3792,7 @@
         <v>Outside</v>
       </c>
       <c r="D170" t="str">
-        <v>Jangmo-o</v>
+        <v>Mienfoo</v>
       </c>
       <c r="E170" t="str">
         <v>75-80</v>
@@ -3802,30 +3803,30 @@
     </row>
     <row r="171">
       <c r="A171">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B171" t="str">
-        <v>Captain Kommo-o</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C171" t="str">
-        <v>Boss Battle</v>
+        <v>Outside</v>
       </c>
       <c r="D171" t="str">
-        <v>Boss</v>
+        <v>Jangmo-o</v>
       </c>
       <c r="E171" t="str">
-        <v>78-83</v>
+        <v>75-80</v>
       </c>
       <c r="F171" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="172">
       <c r="A172">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B172" t="str">
-        <v>Captain Mina</v>
+        <v>Captain Kommo-o</v>
       </c>
       <c r="C172" t="str">
         <v>Boss Battle</v>
@@ -3834,7 +3835,7 @@
         <v>Boss</v>
       </c>
       <c r="E172" t="str">
-        <v>80-85</v>
+        <v>78-83</v>
       </c>
       <c r="F172" t="str">
         <v>-</v>
@@ -3842,10 +3843,10 @@
     </row>
     <row r="173">
       <c r="A173">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B173" t="str">
-        <v>Kahuna Hapu</v>
+        <v>Captain Mina</v>
       </c>
       <c r="C173" t="str">
         <v>Boss Battle</v>
@@ -3854,7 +3855,7 @@
         <v>Boss</v>
       </c>
       <c r="E173" t="str">
-        <v>81-86</v>
+        <v>80-85</v>
       </c>
       <c r="F173" t="str">
         <v>-</v>
@@ -3862,22 +3863,22 @@
     </row>
     <row r="174">
       <c r="A174">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B174" t="str">
-        <v>Mount Lanakila</v>
+        <v>Kahuna Hapu</v>
       </c>
       <c r="C174" t="str">
-        <v>Cave</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D174" t="str">
-        <v>Drampa</v>
+        <v>Boss</v>
       </c>
       <c r="E174" t="str">
-        <v>83-88</v>
+        <v>81-86</v>
       </c>
       <c r="F174" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="175">
@@ -3891,7 +3892,7 @@
         <v>Cave</v>
       </c>
       <c r="D175" t="str">
-        <v>Glalie</v>
+        <v>Drampa</v>
       </c>
       <c r="E175" t="str">
         <v>83-88</v>
@@ -3911,7 +3912,7 @@
         <v>Cave</v>
       </c>
       <c r="D176" t="str">
-        <v>Sneasel</v>
+        <v>Glalie</v>
       </c>
       <c r="E176" t="str">
         <v>83-88</v>
@@ -3931,7 +3932,7 @@
         <v>Cave</v>
       </c>
       <c r="D177" t="str">
-        <v>Crabominable</v>
+        <v>Sneasel</v>
       </c>
       <c r="E177" t="str">
         <v>83-88</v>
@@ -3942,30 +3943,30 @@
     </row>
     <row r="178">
       <c r="A178">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B178" t="str">
-        <v>Alola Pokemon League</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C178" t="str">
-        <v>Boss Battle</v>
+        <v>Cave</v>
       </c>
       <c r="D178" t="str">
-        <v>Boss</v>
+        <v>Crabominable</v>
       </c>
       <c r="E178" t="str">
-        <v>84-89</v>
+        <v>83-88</v>
       </c>
       <c r="F178" t="str">
-        <v>-</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="179">
       <c r="A179">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B179" t="str">
-        <v>Champion Hau</v>
+        <v>Alola Pokemon League</v>
       </c>
       <c r="C179" t="str">
         <v>Boss Battle</v>
@@ -3974,7 +3975,7 @@
         <v>Boss</v>
       </c>
       <c r="E179" t="str">
-        <v>85-90</v>
+        <v>84-89</v>
       </c>
       <c r="F179" t="str">
         <v>-</v>
@@ -3982,22 +3983,22 @@
     </row>
     <row r="180">
       <c r="A180">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B180" t="str">
-        <v>Route 6</v>
+        <v>Champion Hau</v>
       </c>
       <c r="C180" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D180" t="str">
-        <v>Eevee</v>
+        <v>Boss</v>
       </c>
       <c r="E180" t="str">
         <v>85-90</v>
       </c>
       <c r="F180" t="str">
-        <v>33.33%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="181">
@@ -4005,13 +4006,13 @@
         <v>49</v>
       </c>
       <c r="B181" t="str">
-        <v>Route 6</v>
+        <v>Royal Avenue</v>
       </c>
       <c r="C181" t="str">
         <v>Main Area</v>
       </c>
       <c r="D181" t="str">
-        <v>Mudbray</v>
+        <v>Oricorio</v>
       </c>
       <c r="E181" t="str">
         <v>85-90</v>
@@ -4025,13 +4026,13 @@
         <v>49</v>
       </c>
       <c r="B182" t="str">
-        <v>Route 6</v>
+        <v>Royal Avenue</v>
       </c>
       <c r="C182" t="str">
         <v>Main Area</v>
       </c>
       <c r="D182" t="str">
-        <v>Igglybuff</v>
+        <v>Trumbeak</v>
       </c>
       <c r="E182" t="str">
         <v>85-90</v>
@@ -4042,7 +4043,7 @@
     </row>
     <row r="183">
       <c r="A183">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B183" t="str">
         <v>Royal Avenue</v>
@@ -4051,7 +4052,7 @@
         <v>Main Area</v>
       </c>
       <c r="D183" t="str">
-        <v>Oricorio</v>
+        <v>Ribombee</v>
       </c>
       <c r="E183" t="str">
         <v>85-90</v>
@@ -4065,19 +4066,19 @@
         <v>50</v>
       </c>
       <c r="B184" t="str">
-        <v>Royal Avenue</v>
+        <v>Pikachu Valley</v>
       </c>
       <c r="C184" t="str">
         <v>Main Area</v>
       </c>
       <c r="D184" t="str">
-        <v>Trumbeak</v>
+        <v>Pikachu</v>
       </c>
       <c r="E184" t="str">
         <v>85-90</v>
       </c>
       <c r="F184" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="185">
@@ -4085,24 +4086,24 @@
         <v>50</v>
       </c>
       <c r="B185" t="str">
-        <v>Royal Avenue</v>
+        <v>Pikachu Valley</v>
       </c>
       <c r="C185" t="str">
         <v>Main Area</v>
       </c>
       <c r="D185" t="str">
-        <v>Ribombee</v>
+        <v>Alolan Raichu</v>
       </c>
       <c r="E185" t="str">
         <v>85-90</v>
       </c>
       <c r="F185" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="186">
       <c r="A186">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B186" t="str">
         <v>Pikachu Valley</v>
@@ -4111,18 +4112,18 @@
         <v>Main Area</v>
       </c>
       <c r="D186" t="str">
-        <v>Pikachu</v>
+        <v>Pichu</v>
       </c>
       <c r="E186" t="str">
         <v>85-90</v>
       </c>
       <c r="F186" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="187">
       <c r="A187">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B187" t="str">
         <v>Pikachu Valley</v>
@@ -4131,13 +4132,13 @@
         <v>Main Area</v>
       </c>
       <c r="D187" t="str">
-        <v>Alolan Raichu</v>
+        <v>Magnemite</v>
       </c>
       <c r="E187" t="str">
         <v>85-90</v>
       </c>
       <c r="F187" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="188">
@@ -4145,24 +4146,24 @@
         <v>51</v>
       </c>
       <c r="B188" t="str">
-        <v>Pikachu Valley</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C188" t="str">
         <v>Main Area</v>
       </c>
       <c r="D188" t="str">
-        <v>Pichu</v>
+        <v>Rowlet</v>
       </c>
       <c r="E188" t="str">
         <v>85-90</v>
       </c>
       <c r="F188" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="189">
       <c r="A189">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B189" t="str">
         <v>Starter Depot</v>
@@ -4171,7 +4172,7 @@
         <v>Main Area</v>
       </c>
       <c r="D189" t="str">
-        <v>Rowlet</v>
+        <v>Dartrix</v>
       </c>
       <c r="E189" t="str">
         <v>85-90</v>
@@ -4182,7 +4183,7 @@
     </row>
     <row r="190">
       <c r="A190">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B190" t="str">
         <v>Starter Depot</v>
@@ -4191,7 +4192,7 @@
         <v>Main Area</v>
       </c>
       <c r="D190" t="str">
-        <v>Dartrix</v>
+        <v>Litten</v>
       </c>
       <c r="E190" t="str">
         <v>85-90</v>
@@ -4202,7 +4203,7 @@
     </row>
     <row r="191">
       <c r="A191">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B191" t="str">
         <v>Starter Depot</v>
@@ -4211,7 +4212,7 @@
         <v>Main Area</v>
       </c>
       <c r="D191" t="str">
-        <v>Litten</v>
+        <v>Torracat</v>
       </c>
       <c r="E191" t="str">
         <v>85-90</v>
@@ -4222,7 +4223,7 @@
     </row>
     <row r="192">
       <c r="A192">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B192" t="str">
         <v>Starter Depot</v>
@@ -4231,7 +4232,7 @@
         <v>Main Area</v>
       </c>
       <c r="D192" t="str">
-        <v>Torracat</v>
+        <v>Popplio</v>
       </c>
       <c r="E192" t="str">
         <v>85-90</v>
@@ -4242,7 +4243,7 @@
     </row>
     <row r="193">
       <c r="A193">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B193" t="str">
         <v>Starter Depot</v>
@@ -4251,7 +4252,7 @@
         <v>Main Area</v>
       </c>
       <c r="D193" t="str">
-        <v>Popplio</v>
+        <v>Brionne</v>
       </c>
       <c r="E193" t="str">
         <v>85-90</v>
@@ -4265,24 +4266,24 @@
         <v>52</v>
       </c>
       <c r="B194" t="str">
-        <v>Starter Depot</v>
+        <v>Poni Coast</v>
       </c>
       <c r="C194" t="str">
         <v>Main Area</v>
       </c>
       <c r="D194" t="str">
-        <v>Brionne</v>
+        <v>Alolan Dugtrio</v>
       </c>
       <c r="E194" t="str">
         <v>85-90</v>
       </c>
       <c r="F194" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="195">
       <c r="A195">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B195" t="str">
         <v>Poni Coast</v>
@@ -4291,7 +4292,7 @@
         <v>Main Area</v>
       </c>
       <c r="D195" t="str">
-        <v>Alolan Dugtrio</v>
+        <v>Gastrodon</v>
       </c>
       <c r="E195" t="str">
         <v>85-90</v>
@@ -4302,7 +4303,7 @@
     </row>
     <row r="196">
       <c r="A196">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B196" t="str">
         <v>Poni Coast</v>
@@ -4311,7 +4312,7 @@
         <v>Main Area</v>
       </c>
       <c r="D196" t="str">
-        <v>Gastrodon</v>
+        <v>Exeggcute</v>
       </c>
       <c r="E196" t="str">
         <v>85-90</v>
@@ -4325,16 +4326,16 @@
         <v>53</v>
       </c>
       <c r="B197" t="str">
-        <v>Poni Coast</v>
+        <v>The Zenith Anomaly</v>
       </c>
       <c r="C197" t="str">
         <v>Main Area</v>
       </c>
       <c r="D197" t="str">
-        <v>Exeggcute</v>
+        <v>Magearna</v>
       </c>
       <c r="E197" t="str">
-        <v>85-90</v>
+        <v>95-100</v>
       </c>
       <c r="F197" t="str">
         <v>33.33%</v>
@@ -4342,1074 +4343,854 @@
     </row>
     <row r="198">
       <c r="A198">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B198" t="str">
-        <v>Shopping Mall Antiquities</v>
+        <v>The Zenith Anomaly</v>
       </c>
       <c r="C198" t="str">
-        <v>Event</v>
+        <v>Main Area</v>
       </c>
       <c r="D198" t="str">
-        <v>Klefki</v>
+        <v>Marshadow</v>
       </c>
       <c r="E198" t="str">
-        <v>85-90</v>
+        <v>95-100</v>
       </c>
       <c r="F198" t="str">
-        <v>50.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="199">
       <c r="A199">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B199" t="str">
-        <v>Shopping Mall Antiquities</v>
+        <v>The Zenith Anomaly</v>
       </c>
       <c r="C199" t="str">
-        <v>Event</v>
+        <v>Main Area</v>
       </c>
       <c r="D199" t="str">
-        <v>Haunter</v>
+        <v>Zeraora</v>
       </c>
       <c r="E199" t="str">
-        <v>85-90</v>
+        <v>95-100</v>
       </c>
       <c r="F199" t="str">
-        <v>50.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="200">
       <c r="A200">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B200" t="str">
-        <v>Aether Paradise</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C200" t="str">
-        <v>Restricted Area</v>
+        <v>Main Area</v>
       </c>
       <c r="D200" t="str">
-        <v>Porygon-Z</v>
+        <v>Caterpie</v>
       </c>
       <c r="E200" t="str">
         <v>85-90</v>
       </c>
       <c r="F200" t="str">
-        <v>50.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="201">
       <c r="A201">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B201" t="str">
-        <v>Aether Paradise</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C201" t="str">
-        <v>Restricted Area</v>
+        <v>Main Area</v>
       </c>
       <c r="D201" t="str">
-        <v>Silvally</v>
+        <v>Metapod</v>
       </c>
       <c r="E201" t="str">
         <v>85-90</v>
       </c>
       <c r="F201" t="str">
-        <v>50.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="202">
       <c r="A202">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B202" t="str">
-        <v>The Zenith Anomaly</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C202" t="str">
         <v>Main Area</v>
       </c>
       <c r="D202" t="str">
-        <v>Magearna</v>
+        <v>Cutiefly</v>
       </c>
       <c r="E202" t="str">
-        <v>95-100</v>
+        <v>85-90</v>
       </c>
       <c r="F202" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="203">
       <c r="A203">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B203" t="str">
-        <v>The Zenith Anomaly</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C203" t="str">
         <v>Main Area</v>
       </c>
       <c r="D203" t="str">
-        <v>Marshadow</v>
+        <v>Butterfree</v>
       </c>
       <c r="E203" t="str">
-        <v>95-100</v>
+        <v>85-90</v>
       </c>
       <c r="F203" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="204">
       <c r="A204">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B204" t="str">
-        <v>The Zenith Anomaly</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C204" t="str">
         <v>Main Area</v>
       </c>
       <c r="D204" t="str">
-        <v>Zeraora</v>
+        <v>Flabébé</v>
       </c>
       <c r="E204" t="str">
-        <v>95-100</v>
+        <v>85-90</v>
       </c>
       <c r="F204" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="205">
       <c r="A205">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B205" t="str">
-        <v>Mahalo Trail</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C205" t="str">
         <v>Main Area</v>
       </c>
       <c r="D205" t="str">
-        <v>Spearow</v>
+        <v>Petilil</v>
       </c>
       <c r="E205" t="str">
         <v>85-90</v>
       </c>
       <c r="F205" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="206">
       <c r="A206">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B206" t="str">
-        <v>Mahalo Trail</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C206" t="str">
         <v>Main Area</v>
       </c>
       <c r="D206" t="str">
-        <v>Rufflet</v>
+        <v>Cottonee</v>
       </c>
       <c r="E206" t="str">
         <v>85-90</v>
       </c>
       <c r="F206" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="207">
       <c r="A207">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B207" t="str">
-        <v>Mahalo Trail</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C207" t="str">
         <v>Main Area</v>
       </c>
       <c r="D207" t="str">
-        <v>Vullaby</v>
+        <v>Phantump</v>
       </c>
       <c r="E207" t="str">
         <v>85-90</v>
       </c>
       <c r="F207" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="208">
       <c r="A208">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B208" t="str">
-        <v>Mahalo Trail</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C208" t="str">
         <v>Main Area</v>
       </c>
       <c r="D208" t="str">
-        <v>Machop</v>
+        <v>Tapu Koko</v>
       </c>
       <c r="E208" t="str">
-        <v>85-90</v>
+        <v>100</v>
       </c>
       <c r="F208" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="209">
       <c r="A209">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B209" t="str">
-        <v>Mahalo Trail</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C209" t="str">
         <v>Main Area</v>
       </c>
       <c r="D209" t="str">
-        <v>Hawlucha</v>
+        <v>Tapu Lele</v>
       </c>
       <c r="E209" t="str">
-        <v>85-90</v>
+        <v>100</v>
       </c>
       <c r="F209" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="210">
       <c r="A210">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B210" t="str">
-        <v>Melemele Meadow</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C210" t="str">
         <v>Main Area</v>
       </c>
       <c r="D210" t="str">
-        <v>Caterpie</v>
+        <v>Tapu Bulu</v>
       </c>
       <c r="E210" t="str">
-        <v>85-90</v>
+        <v>100</v>
       </c>
       <c r="F210" t="str">
-        <v>12.50%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="211">
       <c r="A211">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B211" t="str">
-        <v>Melemele Meadow</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C211" t="str">
         <v>Main Area</v>
       </c>
       <c r="D211" t="str">
-        <v>Metapod</v>
+        <v>Tapu Fini</v>
       </c>
       <c r="E211" t="str">
-        <v>85-90</v>
+        <v>100</v>
       </c>
       <c r="F211" t="str">
-        <v>12.50%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="212">
       <c r="A212">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B212" t="str">
-        <v>Melemele Meadow</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C212" t="str">
         <v>Main Area</v>
       </c>
       <c r="D212" t="str">
-        <v>Cutiefly</v>
+        <v>Buneary</v>
       </c>
       <c r="E212" t="str">
         <v>85-90</v>
       </c>
       <c r="F212" t="str">
-        <v>12.50%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="213">
       <c r="A213">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B213" t="str">
-        <v>Melemele Meadow</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C213" t="str">
         <v>Main Area</v>
       </c>
       <c r="D213" t="str">
-        <v>Butterfree</v>
+        <v>Granbull</v>
       </c>
       <c r="E213" t="str">
         <v>85-90</v>
       </c>
       <c r="F213" t="str">
-        <v>12.50%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="214">
       <c r="A214">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B214" t="str">
-        <v>Melemele Meadow</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C214" t="str">
         <v>Main Area</v>
       </c>
       <c r="D214" t="str">
-        <v>Flabébé</v>
+        <v>Zoroark</v>
       </c>
       <c r="E214" t="str">
         <v>85-90</v>
       </c>
       <c r="F214" t="str">
-        <v>12.50%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="215">
       <c r="A215">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B215" t="str">
-        <v>Melemele Meadow</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C215" t="str">
         <v>Main Area</v>
       </c>
       <c r="D215" t="str">
-        <v>Petilil</v>
+        <v>Heracross</v>
       </c>
       <c r="E215" t="str">
         <v>85-90</v>
       </c>
       <c r="F215" t="str">
-        <v>12.50%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="216">
       <c r="A216">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B216" t="str">
-        <v>Melemele Meadow</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C216" t="str">
         <v>Main Area</v>
       </c>
       <c r="D216" t="str">
-        <v>Cottonee</v>
+        <v>Riolu</v>
       </c>
       <c r="E216" t="str">
         <v>85-90</v>
       </c>
       <c r="F216" t="str">
-        <v>12.50%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="217">
       <c r="A217">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B217" t="str">
-        <v>Melemele Meadow</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C217" t="str">
         <v>Main Area</v>
       </c>
       <c r="D217" t="str">
-        <v>Phantump</v>
+        <v>Hariyama</v>
       </c>
       <c r="E217" t="str">
         <v>85-90</v>
       </c>
       <c r="F217" t="str">
-        <v>12.50%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="218">
       <c r="A218">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B218" t="str">
-        <v>Sacred Shrine</v>
+        <v>Poni Grove</v>
       </c>
       <c r="C218" t="str">
         <v>Main Area</v>
       </c>
       <c r="D218" t="str">
-        <v>Tapu Koko</v>
+        <v>Mudsdale</v>
       </c>
       <c r="E218" t="str">
-        <v>100</v>
+        <v>85-90</v>
       </c>
       <c r="F218" t="str">
-        <v>25.00%</v>
+        <v>14.29%</v>
       </c>
     </row>
     <row r="219">
       <c r="A219">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B219" t="str">
-        <v>Sacred Shrine</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C219" t="str">
         <v>Main Area</v>
       </c>
       <c r="D219" t="str">
-        <v>Tapu Lele</v>
+        <v>Nihilego</v>
       </c>
       <c r="E219" t="str">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F219" t="str">
-        <v>25.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="220">
       <c r="A220">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B220" t="str">
-        <v>Sacred Shrine</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C220" t="str">
         <v>Main Area</v>
       </c>
       <c r="D220" t="str">
-        <v>Tapu Bulu</v>
+        <v>Buzzwole</v>
       </c>
       <c r="E220" t="str">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F220" t="str">
-        <v>25.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="221">
       <c r="A221">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B221" t="str">
-        <v>Sacred Shrine</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C221" t="str">
         <v>Main Area</v>
       </c>
       <c r="D221" t="str">
-        <v>Tapu Fini</v>
+        <v>Pheromosa</v>
       </c>
       <c r="E221" t="str">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F221" t="str">
-        <v>25.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="222">
       <c r="A222">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B222" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C222" t="str">
         <v>Main Area</v>
       </c>
       <c r="D222" t="str">
-        <v>Buneary</v>
+        <v>Xurkitree</v>
       </c>
       <c r="E222" t="str">
-        <v>85-90</v>
+        <v>110</v>
       </c>
       <c r="F222" t="str">
-        <v>14.29%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="223">
       <c r="A223">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B223" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C223" t="str">
         <v>Main Area</v>
       </c>
       <c r="D223" t="str">
-        <v>Granbull</v>
+        <v>Celesteela</v>
       </c>
       <c r="E223" t="str">
-        <v>85-90</v>
+        <v>110</v>
       </c>
       <c r="F223" t="str">
-        <v>14.29%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="224">
       <c r="A224">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B224" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C224" t="str">
         <v>Main Area</v>
       </c>
       <c r="D224" t="str">
-        <v>Zoroark</v>
+        <v>Kartana</v>
       </c>
       <c r="E224" t="str">
-        <v>85-90</v>
+        <v>110</v>
       </c>
       <c r="F224" t="str">
-        <v>14.29%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="225">
       <c r="A225">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B225" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C225" t="str">
         <v>Main Area</v>
       </c>
       <c r="D225" t="str">
-        <v>Heracross</v>
+        <v>Guzzlord</v>
       </c>
       <c r="E225" t="str">
-        <v>85-90</v>
+        <v>110</v>
       </c>
       <c r="F225" t="str">
-        <v>14.29%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="226">
       <c r="A226">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B226" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C226" t="str">
         <v>Main Area</v>
       </c>
       <c r="D226" t="str">
-        <v>Riolu</v>
+        <v>Poipole</v>
       </c>
       <c r="E226" t="str">
-        <v>85-90</v>
+        <v>110</v>
       </c>
       <c r="F226" t="str">
-        <v>14.29%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="227">
       <c r="A227">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B227" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C227" t="str">
         <v>Main Area</v>
       </c>
       <c r="D227" t="str">
-        <v>Hariyama</v>
+        <v>Stakataka</v>
       </c>
       <c r="E227" t="str">
-        <v>85-90</v>
+        <v>110</v>
       </c>
       <c r="F227" t="str">
-        <v>14.29%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="228">
       <c r="A228">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B228" t="str">
-        <v>Poni Grove</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C228" t="str">
         <v>Main Area</v>
       </c>
       <c r="D228" t="str">
-        <v>Mudsdale</v>
+        <v>Blacephalon</v>
       </c>
       <c r="E228" t="str">
-        <v>85-90</v>
+        <v>110</v>
       </c>
       <c r="F228" t="str">
-        <v>14.29%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="229">
       <c r="A229">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B229" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C229" t="str">
-        <v>Main Area</v>
+        <v>Secret Lab</v>
       </c>
       <c r="D229" t="str">
-        <v>Nihilego</v>
+        <v>Type: Null</v>
       </c>
       <c r="E229" t="str">
-        <v>110</v>
+        <v>85-90</v>
       </c>
       <c r="F229" t="str">
-        <v>10.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="230">
       <c r="A230">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B230" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C230" t="str">
-        <v>Main Area</v>
+        <v>Secret Lab</v>
       </c>
       <c r="D230" t="str">
-        <v>Buzzwole</v>
+        <v>Silvally</v>
       </c>
       <c r="E230" t="str">
-        <v>110</v>
+        <v>85-90</v>
       </c>
       <c r="F230" t="str">
-        <v>10.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="231">
       <c r="A231">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B231" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C231" t="str">
-        <v>Main Area</v>
+        <v>Secret Lab</v>
       </c>
       <c r="D231" t="str">
-        <v>Pheromosa</v>
+        <v>Porygon</v>
       </c>
       <c r="E231" t="str">
-        <v>110</v>
+        <v>85-90</v>
       </c>
       <c r="F231" t="str">
-        <v>10.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="232">
       <c r="A232">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B232" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Lake of the Sunne</v>
       </c>
       <c r="C232" t="str">
         <v>Main Area</v>
       </c>
       <c r="D232" t="str">
-        <v>Xurkitree</v>
+        <v>Golbat</v>
       </c>
       <c r="E232" t="str">
-        <v>110</v>
+        <v>85-90</v>
       </c>
       <c r="F232" t="str">
-        <v>10.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="233">
       <c r="A233">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B233" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Lake of the Sunne</v>
       </c>
       <c r="C233" t="str">
         <v>Main Area</v>
       </c>
       <c r="D233" t="str">
-        <v>Celesteela</v>
+        <v>Gastly</v>
       </c>
       <c r="E233" t="str">
-        <v>110</v>
+        <v>85-90</v>
       </c>
       <c r="F233" t="str">
-        <v>10.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="234">
       <c r="A234">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B234" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Lake of the Sunne</v>
       </c>
       <c r="C234" t="str">
         <v>Main Area</v>
       </c>
       <c r="D234" t="str">
-        <v>Kartana</v>
+        <v>Haunter</v>
       </c>
       <c r="E234" t="str">
-        <v>110</v>
+        <v>85-90</v>
       </c>
       <c r="F234" t="str">
-        <v>10.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="235">
       <c r="A235">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B235" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C235" t="str">
         <v>Main Area</v>
       </c>
       <c r="D235" t="str">
-        <v>Guzzlord</v>
+        <v>Cosmog</v>
       </c>
       <c r="E235" t="str">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F235" t="str">
-        <v>10.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="236">
       <c r="A236">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B236" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C236" t="str">
         <v>Main Area</v>
       </c>
       <c r="D236" t="str">
-        <v>Poipole</v>
+        <v>Cosmoem</v>
       </c>
       <c r="E236" t="str">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F236" t="str">
-        <v>10.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="237">
       <c r="A237">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B237" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C237" t="str">
         <v>Main Area</v>
       </c>
       <c r="D237" t="str">
-        <v>Stakataka</v>
+        <v>Solgaleo</v>
       </c>
       <c r="E237" t="str">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F237" t="str">
-        <v>10.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="238">
       <c r="A238">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B238" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C238" t="str">
         <v>Main Area</v>
       </c>
       <c r="D238" t="str">
-        <v>Blacephalon</v>
+        <v>Lunala</v>
       </c>
       <c r="E238" t="str">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F238" t="str">
-        <v>10.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="239">
       <c r="A239">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B239" t="str">
-        <v>Aether Paradise</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C239" t="str">
-        <v>Labs</v>
+        <v>Main Area</v>
       </c>
       <c r="D239" t="str">
-        <v>Ditto</v>
+        <v>Necrozma</v>
       </c>
       <c r="E239" t="str">
-        <v>85-90</v>
+        <v>120</v>
       </c>
       <c r="F239" t="str">
-        <v>50.00%</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240">
-        <v>62</v>
-      </c>
-      <c r="B240" t="str">
-        <v>Aether Paradise</v>
-      </c>
-      <c r="C240" t="str">
-        <v>Labs</v>
-      </c>
-      <c r="D240" t="str">
-        <v>Porygon2</v>
-      </c>
-      <c r="E240" t="str">
-        <v>85-90</v>
-      </c>
-      <c r="F240" t="str">
-        <v>50.00%</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241">
-        <v>63</v>
-      </c>
-      <c r="B241" t="str">
-        <v>Aether Paradise</v>
-      </c>
-      <c r="C241" t="str">
-        <v>Secret Lab</v>
-      </c>
-      <c r="D241" t="str">
-        <v>Type: Null</v>
-      </c>
-      <c r="E241" t="str">
-        <v>85-90</v>
-      </c>
-      <c r="F241" t="str">
-        <v>50.00%</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242">
-        <v>63</v>
-      </c>
-      <c r="B242" t="str">
-        <v>Aether Paradise</v>
-      </c>
-      <c r="C242" t="str">
-        <v>Secret Lab</v>
-      </c>
-      <c r="D242" t="str">
-        <v>Porygon</v>
-      </c>
-      <c r="E242" t="str">
-        <v>85-90</v>
-      </c>
-      <c r="F242" t="str">
-        <v>50.00%</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243">
-        <v>64</v>
-      </c>
-      <c r="B243" t="str">
-        <v>Obsidian Sphere</v>
-      </c>
-      <c r="C243" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D243" t="str">
-        <v>Solgaleo</v>
-      </c>
-      <c r="E243" t="str">
-        <v>120</v>
-      </c>
-      <c r="F243" t="str">
-        <v>33.33%</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244">
-        <v>64</v>
-      </c>
-      <c r="B244" t="str">
-        <v>Obsidian Sphere</v>
-      </c>
-      <c r="C244" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D244" t="str">
-        <v>Lunala</v>
-      </c>
-      <c r="E244" t="str">
-        <v>120</v>
-      </c>
-      <c r="F244" t="str">
-        <v>33.33%</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245">
-        <v>64</v>
-      </c>
-      <c r="B245" t="str">
-        <v>Obsidian Sphere</v>
-      </c>
-      <c r="C245" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D245" t="str">
-        <v>Necrozma</v>
-      </c>
-      <c r="E245" t="str">
-        <v>120</v>
-      </c>
-      <c r="F245" t="str">
-        <v>33.33%</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246">
-        <v>65</v>
-      </c>
-      <c r="B246" t="str">
-        <v>Obsidian Tesseract</v>
-      </c>
-      <c r="C246" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D246" t="str">
-        <v>Cosmog</v>
-      </c>
-      <c r="E246" t="str">
-        <v>100</v>
-      </c>
-      <c r="F246" t="str">
-        <v>20.00%</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247">
-        <v>65</v>
-      </c>
-      <c r="B247" t="str">
-        <v>Obsidian Tesseract</v>
-      </c>
-      <c r="C247" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D247" t="str">
-        <v>Cosmoem</v>
-      </c>
-      <c r="E247" t="str">
-        <v>100</v>
-      </c>
-      <c r="F247" t="str">
-        <v>20.00%</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248">
-        <v>65</v>
-      </c>
-      <c r="B248" t="str">
-        <v>Obsidian Tesseract</v>
-      </c>
-      <c r="C248" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D248" t="str">
-        <v>Solgaleo</v>
-      </c>
-      <c r="E248" t="str">
-        <v>120</v>
-      </c>
-      <c r="F248" t="str">
-        <v>20.00%</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249">
-        <v>65</v>
-      </c>
-      <c r="B249" t="str">
-        <v>Obsidian Tesseract</v>
-      </c>
-      <c r="C249" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D249" t="str">
-        <v>Lunala</v>
-      </c>
-      <c r="E249" t="str">
-        <v>120</v>
-      </c>
-      <c r="F249" t="str">
-        <v>20.00%</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250">
-        <v>65</v>
-      </c>
-      <c r="B250" t="str">
-        <v>Obsidian Tesseract</v>
-      </c>
-      <c r="C250" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D250" t="str">
-        <v>Necrozma</v>
-      </c>
-      <c r="E250" t="str">
-        <v>120</v>
-      </c>
-      <c r="F250" t="str">
         <v>20.00%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F250"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F239"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C71"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5427,10 +5208,10 @@
         <v>Challenge 1</v>
       </c>
       <c r="B2" t="str">
-        <v>Start the game</v>
+        <v>Defeat 10 Pokemon in Route 1 East</v>
       </c>
       <c r="C2" t="str">
-        <v>Unlocks Route 1 East</v>
+        <v>Unlocks Route 1 Hau'oli Outskirts</v>
       </c>
     </row>
     <row r="3">
@@ -5438,10 +5219,10 @@
         <v>Challenge 2</v>
       </c>
       <c r="B3" t="str">
-        <v>Defeat 10 Pokemon in Route 1 East</v>
+        <v>Defeat 10 Pokemon in Route 1 Hau'oli Outskirts</v>
       </c>
       <c r="C3" t="str">
-        <v>Unlocks Route 1 Hau'oli Outskirts</v>
+        <v>Unlocks Hau'oli City Shopping District</v>
       </c>
     </row>
     <row r="4">
@@ -5449,10 +5230,10 @@
         <v>Challenge 3</v>
       </c>
       <c r="B4" t="str">
-        <v>Defeat 10 Pokemon in Route 1 Hau'oli Outskirts</v>
+        <v>Defeat 10 Pokemon in Hau'oli City Shopping District</v>
       </c>
       <c r="C4" t="str">
-        <v>Unlocks Hau'oli City Shopping District</v>
+        <v>Unlocks Route 2 North</v>
       </c>
     </row>
     <row r="5">
@@ -5460,10 +5241,10 @@
         <v>Challenge 4</v>
       </c>
       <c r="B5" t="str">
-        <v>Defeat 10 Pokemon in Hau'oli City Shopping District</v>
+        <v>Defeat 10 Pokemon in Route 2 North</v>
       </c>
       <c r="C5" t="str">
-        <v>Unlocks Route 2 North</v>
+        <v>Unlocks Captain Ilima</v>
       </c>
     </row>
     <row r="6">
@@ -5471,10 +5252,10 @@
         <v>Challenge 5</v>
       </c>
       <c r="B6" t="str">
-        <v>Defeat 10 Pokemon in Route 2 North</v>
+        <v>Defeat Captain Ilima</v>
       </c>
       <c r="C6" t="str">
-        <v>Unlocks Captain Ilima</v>
+        <v>Unlocks Hau'oli Cemetery Main Area</v>
       </c>
     </row>
     <row r="7">
@@ -5482,10 +5263,10 @@
         <v>Challenge 6</v>
       </c>
       <c r="B7" t="str">
-        <v>Defeat Captain Ilima</v>
+        <v>Defeat 10 Pokemon in Hau'oli Cemetery Main Area</v>
       </c>
       <c r="C7" t="str">
-        <v>Unlocks Hau'oli Cemetery Main Area</v>
+        <v>Unlocks Ten Carat Hill Farthest Hollow</v>
       </c>
     </row>
     <row r="8">
@@ -5493,10 +5274,10 @@
         <v>Challenge 7</v>
       </c>
       <c r="B8" t="str">
-        <v>Defeat 10 Pokemon in Hau'oli Cemetery Main Area</v>
+        <v>Defeat 10 Pokemon in Ten Carat Hill Farthest Hollow</v>
       </c>
       <c r="C8" t="str">
-        <v>Unlocks Ten Carat Hill Farthest Hollow</v>
+        <v>Unlocks Seaward Cave Main Area</v>
       </c>
     </row>
     <row r="9">
@@ -5504,10 +5285,10 @@
         <v>Challenge 8</v>
       </c>
       <c r="B9" t="str">
-        <v>Defeat 10 Pokemon in Ten Carat Hill Farthest Hollow</v>
+        <v>Defeat 10 Pokemon in Seaward Cave Main Area</v>
       </c>
       <c r="C9" t="str">
-        <v>Unlocks Seaward Cave Main Area</v>
+        <v>Unlocks Kahuna Hala</v>
       </c>
     </row>
     <row r="10">
@@ -5515,10 +5296,10 @@
         <v>Challenge 9</v>
       </c>
       <c r="B10" t="str">
-        <v>Defeat 10 Pokemon in Seaward Cave Main Area</v>
+        <v>Defeat Kahuna Hala</v>
       </c>
       <c r="C10" t="str">
-        <v>Unlocks Kahuna Hala</v>
+        <v>Unlocks Heahea Beach Main Area Part 1</v>
       </c>
     </row>
     <row r="11">
@@ -5529,7 +5310,7 @@
         <v>Defeat Kahuna Hala</v>
       </c>
       <c r="C11" t="str">
-        <v>Unlocks Heahea Beach Main Area Part 1</v>
+        <v>Unlocks Heahea Beach Main Area Part 2</v>
       </c>
     </row>
     <row r="12">
@@ -5537,10 +5318,10 @@
         <v>Challenge 11</v>
       </c>
       <c r="B12" t="str">
-        <v>Defeat Kahuna Hala</v>
+        <v>Defeat 10 Pokemon in Heahea Beach Main Area Part 2</v>
       </c>
       <c r="C12" t="str">
-        <v>Unlocks Heahea Beach Main Area Part 2</v>
+        <v>Unlocks Paniola Ranch Main Area</v>
       </c>
     </row>
     <row r="13">
@@ -5548,10 +5329,10 @@
         <v>Challenge 12</v>
       </c>
       <c r="B13" t="str">
-        <v>Defeat 10 Pokemon in Heahea Beach Main Area Part 2</v>
+        <v>Defeat 10 Pokemon in Paniola Ranch Main Area</v>
       </c>
       <c r="C13" t="str">
-        <v>Unlocks Paniola Ranch Main Area</v>
+        <v>Unlocks Daycare NPC</v>
       </c>
     </row>
     <row r="14">
@@ -5559,10 +5340,10 @@
         <v>Challenge 13</v>
       </c>
       <c r="B14" t="str">
-        <v>Defeat 10 Pokemon in Paniola Ranch Main Area</v>
+        <v>Interact with Daycare</v>
       </c>
       <c r="C14" t="str">
-        <v>Unlocks Daycare NPC</v>
+        <v>Unlocks Route 5 Main Area</v>
       </c>
     </row>
     <row r="15">
@@ -5570,10 +5351,10 @@
         <v>Challenge 14</v>
       </c>
       <c r="B15" t="str">
-        <v>Interact with Daycare</v>
+        <v>Defeat 10 Pokemon in Route 5 Main Area</v>
       </c>
       <c r="C15" t="str">
-        <v>Unlocks Route 5 Main Area</v>
+        <v>Unlocks Brooklet Hill South</v>
       </c>
     </row>
     <row r="16">
@@ -5581,10 +5362,10 @@
         <v>Challenge 15</v>
       </c>
       <c r="B16" t="str">
-        <v>Defeat 10 Pokemon in Route 5 Main Area</v>
+        <v>Defeat 10 Pokemon in Brooklet Hill South</v>
       </c>
       <c r="C16" t="str">
-        <v>Unlocks Brooklet Hill South</v>
+        <v>Unlocks Captain Lana</v>
       </c>
     </row>
     <row r="17">
@@ -5592,10 +5373,10 @@
         <v>Challenge 16</v>
       </c>
       <c r="B17" t="str">
-        <v>Defeat 10 Pokemon in Brooklet Hill South</v>
+        <v>Defeat Captain Lana</v>
       </c>
       <c r="C17" t="str">
-        <v>Unlocks Captain Lana</v>
+        <v>Unlocks Captain Lana and Wela Volcano Park Main Area</v>
       </c>
     </row>
     <row r="18">
@@ -5603,10 +5384,10 @@
         <v>Challenge 17</v>
       </c>
       <c r="B18" t="str">
-        <v>Defeat Captain Lana</v>
+        <v>Defeat Captain Kiawe</v>
       </c>
       <c r="C18" t="str">
-        <v>Unlocks Wela Volcano Park Main Area</v>
+        <v>Unlocks Route 7 Main Area</v>
       </c>
     </row>
     <row r="19">
@@ -5614,10 +5395,10 @@
         <v>Challenge 18</v>
       </c>
       <c r="B19" t="str">
-        <v>Defeat 10 Pokemon in Wela Volcano Park Main Area</v>
+        <v>Defeat 10 Pokemon in Route 7 Main Area</v>
       </c>
       <c r="C19" t="str">
-        <v>Unlocks Captain Kiawe</v>
+        <v>Unlocks Route 8 Fossil Restoration Center Part 1</v>
       </c>
     </row>
     <row r="20">
@@ -5625,10 +5406,10 @@
         <v>Challenge 19</v>
       </c>
       <c r="B20" t="str">
-        <v>Defeat Captain Kiawe</v>
+        <v>Defeat 10 Pokemon in Route 8 Fossil Restoration Center Part 1</v>
       </c>
       <c r="C20" t="str">
-        <v>Unlocks Route 7 Main Area</v>
+        <v>Unlocks Route 8 Fossil Restoration Center Part 2</v>
       </c>
     </row>
     <row r="21">
@@ -5636,10 +5417,10 @@
         <v>Challenge 20</v>
       </c>
       <c r="B21" t="str">
-        <v>Defeat 10 Pokemon in Route 7 Main Area</v>
+        <v>Defeat 10 Pokemon in Route 8 Fossil Restoration Center Part 2</v>
       </c>
       <c r="C21" t="str">
-        <v>Unlocks Route 8 Fossil Restoration Center Part 1</v>
+        <v>Unlocks Lush Jungle North</v>
       </c>
     </row>
     <row r="22">
@@ -5647,10 +5428,10 @@
         <v>Challenge 21</v>
       </c>
       <c r="B22" t="str">
-        <v>Defeat 10 Pokemon in Route 8 Fossil Restoration Center Part 1</v>
+        <v>Defeat 10 Pokemon in Lush Jungle North</v>
       </c>
       <c r="C22" t="str">
-        <v>Unlocks Route 8 Fossil Restoration Center Part 2</v>
+        <v>Unlocks Lush Jungle East Cave</v>
       </c>
     </row>
     <row r="23">
@@ -5658,10 +5439,10 @@
         <v>Challenge 22</v>
       </c>
       <c r="B23" t="str">
-        <v>Defeat 10 Pokemon in Route 8 Fossil Restoration Center Part 2</v>
+        <v>Defeat 10 Pokemon in Lush Jungle East Cave</v>
       </c>
       <c r="C23" t="str">
-        <v>Unlocks Lush Jungle North</v>
+        <v>Unlocks Captain Mallow</v>
       </c>
     </row>
     <row r="24">
@@ -5669,10 +5450,10 @@
         <v>Challenge 23</v>
       </c>
       <c r="B24" t="str">
-        <v>Defeat 10 Pokemon in Lush Jungle North</v>
+        <v>Defeat Captain Mallow</v>
       </c>
       <c r="C24" t="str">
-        <v>Unlocks Lush Jungle East Cave</v>
+        <v>Unlocks Diglett's Tunnel Main Area</v>
       </c>
     </row>
     <row r="25">
@@ -5680,10 +5461,10 @@
         <v>Challenge 24</v>
       </c>
       <c r="B25" t="str">
-        <v>Defeat 10 Pokemon in Lush Jungle East Cave</v>
+        <v>Defeat 10 Pokemon in Diglett's Tunnel Main Area</v>
       </c>
       <c r="C25" t="str">
-        <v>Unlocks Captain Mallow</v>
+        <v>Unlocks Akala Outskirts Main Area</v>
       </c>
     </row>
     <row r="26">
@@ -5691,10 +5472,10 @@
         <v>Challenge 25</v>
       </c>
       <c r="B26" t="str">
-        <v>Defeat Captain Mallow</v>
+        <v>Defeat 10 Pokemon in Akala Outskirts Main Area</v>
       </c>
       <c r="C26" t="str">
-        <v>Unlocks Diglett's Tunnel Main Area</v>
+        <v>Unlocks Kahuna Olivia</v>
       </c>
     </row>
     <row r="27">
@@ -5702,10 +5483,10 @@
         <v>Challenge 26</v>
       </c>
       <c r="B27" t="str">
-        <v>Defeat 10 Pokemon in Diglett's Tunnel Main Area</v>
+        <v>Defeat 10 Pokemon in Kahuna Olivia</v>
       </c>
       <c r="C27" t="str">
-        <v>Unlocks Akala Outskirts Main Area</v>
+        <v>Unlocks Malie City Outer Cape</v>
       </c>
     </row>
     <row r="28">
@@ -5713,10 +5494,10 @@
         <v>Challenge 27</v>
       </c>
       <c r="B28" t="str">
-        <v>Defeat 10 Pokemon in Akala Outskirts Main Area</v>
+        <v>Defeat 10 Pokemon in Malie City Outer Cape</v>
       </c>
       <c r="C28" t="str">
-        <v>Unlocks Kahuna Olivia</v>
+        <v>Unlocks Route 10 Main Area</v>
       </c>
     </row>
     <row r="29">
@@ -5724,10 +5505,10 @@
         <v>Challenge 28</v>
       </c>
       <c r="B29" t="str">
-        <v>Defeat 10 Pokemon in Kahuna Olivia</v>
+        <v>Defeat 10 Pokemon in Route 10 Main Area</v>
       </c>
       <c r="C29" t="str">
-        <v>Unlocks Malie City Outer Cape</v>
+        <v>Unlocks Mount Hokulani East</v>
       </c>
     </row>
     <row r="30">
@@ -5735,10 +5516,10 @@
         <v>Challenge 29</v>
       </c>
       <c r="B30" t="str">
-        <v>Defeat 10 Pokemon in Malie City Outer Cape</v>
+        <v>Defeat 10 Pokemon in Mount Hokulani East</v>
       </c>
       <c r="C30" t="str">
-        <v>Unlocks Route 10 Main Area</v>
+        <v>Unlocks Captain Sophocles</v>
       </c>
     </row>
     <row r="31">
@@ -5746,10 +5527,10 @@
         <v>Challenge 30</v>
       </c>
       <c r="B31" t="str">
-        <v>Defeat 10 Pokemon in Route 10 Main Area</v>
+        <v>Defeat Captain Sophocles</v>
       </c>
       <c r="C31" t="str">
-        <v>Unlocks Mount Hokulani East</v>
+        <v>Unlocks Route 11 Main Area</v>
       </c>
     </row>
     <row r="32">
@@ -5757,10 +5538,10 @@
         <v>Challenge 31</v>
       </c>
       <c r="B32" t="str">
-        <v>Defeat 10 Pokemon in Mount Hokulani East</v>
+        <v>Defeat 10 Pokemon in Route 11 Main Area</v>
       </c>
       <c r="C32" t="str">
-        <v>Unlocks Captain Sophocles</v>
+        <v>Unlocks Haina Desert Main Area</v>
       </c>
     </row>
     <row r="33">
@@ -5768,10 +5549,10 @@
         <v>Challenge 32</v>
       </c>
       <c r="B33" t="str">
-        <v>Defeat Captain Sophocles</v>
+        <v>Defeat 10 Pokemon in Haina Desert Main Area</v>
       </c>
       <c r="C33" t="str">
-        <v>Unlocks Route 11 Main Area</v>
+        <v>Unlocks Tapu Village Main Area</v>
       </c>
     </row>
     <row r="34">
@@ -5779,10 +5560,10 @@
         <v>Challenge 33</v>
       </c>
       <c r="B34" t="str">
-        <v>Defeat 10 Pokemon in Route 11 Main Area</v>
+        <v>Defeat 10 Pokemon in Tapu Village Main Area</v>
       </c>
       <c r="C34" t="str">
-        <v>Unlocks Haina Desert Main Area</v>
+        <v>Unlocks Thrifty Megamart Abandoned Site</v>
       </c>
     </row>
     <row r="35">
@@ -5790,10 +5571,10 @@
         <v>Challenge 34</v>
       </c>
       <c r="B35" t="str">
-        <v>Defeat 10 Pokemon in Haina Desert Main Area</v>
+        <v>Defeat 10 Pokemon in Thrifty Megamart Abandoned Site</v>
       </c>
       <c r="C35" t="str">
-        <v>Unlocks Tapu Village Main Area</v>
+        <v>Unlocks Captain Acerola</v>
       </c>
     </row>
     <row r="36">
@@ -5801,10 +5582,10 @@
         <v>Challenge 35</v>
       </c>
       <c r="B36" t="str">
-        <v>Defeat 10 Pokemon in Tapu Village Main Area</v>
+        <v>Defeat 10 Pokemon in Captain Acerola</v>
       </c>
       <c r="C36" t="str">
-        <v>Unlocks Thrifty Megamart Abandoned Site</v>
+        <v>Unlocks Kahuna Nanu</v>
       </c>
     </row>
     <row r="37">
@@ -5812,10 +5593,10 @@
         <v>Challenge 36</v>
       </c>
       <c r="B37" t="str">
-        <v>Defeat 10 Pokemon in Thrifty Megamart Abandoned Site</v>
+        <v>Defeat Kahuna Nanu</v>
       </c>
       <c r="C37" t="str">
-        <v>Unlocks Captain Acerola</v>
+        <v>Unlocks Seafolk Village Main</v>
       </c>
     </row>
     <row r="38">
@@ -5823,10 +5604,10 @@
         <v>Challenge 37</v>
       </c>
       <c r="B38" t="str">
-        <v>Defeat 10 Pokemon in Captain Acerola</v>
+        <v>Defeat 10 Pokemon in Seafolk Village Main</v>
       </c>
       <c r="C38" t="str">
-        <v>Unlocks Kahuna Nanu</v>
+        <v>Unlocks Poni Wilds Main Area</v>
       </c>
     </row>
     <row r="39">
@@ -5834,10 +5615,10 @@
         <v>Challenge 38</v>
       </c>
       <c r="B39" t="str">
-        <v>Defeat Kahuna Nanu</v>
+        <v>Defeat 10 Pokemon in Poni Wilds Main Area</v>
       </c>
       <c r="C39" t="str">
-        <v>Unlocks Seafolk Village Main</v>
+        <v>Unlocks Poni Breaker Coast Main Area</v>
       </c>
     </row>
     <row r="40">
@@ -5845,10 +5626,10 @@
         <v>Challenge 39</v>
       </c>
       <c r="B40" t="str">
-        <v>Defeat 10 Pokemon in Seafolk Village Main</v>
+        <v>Defeat 10 Pokemon in Poni Breaker Coast Main Area</v>
       </c>
       <c r="C40" t="str">
-        <v>Unlocks Poni Wilds Main Area</v>
+        <v>Unlocks Exeggutor Island Main Area</v>
       </c>
     </row>
     <row r="41">
@@ -5856,10 +5637,10 @@
         <v>Challenge 40</v>
       </c>
       <c r="B41" t="str">
-        <v>Defeat 10 Pokemon in Poni Wilds Main Area</v>
+        <v>Defeat 10 Pokemon in Exeggutor Island Main Area</v>
       </c>
       <c r="C41" t="str">
-        <v>Unlocks Poni Breaker Coast Main Area</v>
+        <v>Unlocks Vast Poni Canyon Outside</v>
       </c>
     </row>
     <row r="42">
@@ -5867,10 +5648,10 @@
         <v>Challenge 41</v>
       </c>
       <c r="B42" t="str">
-        <v>Defeat 10 Pokemon in Poni Breaker Coast Main Area</v>
+        <v>Defeat 10 Pokemon in Vast Poni Canyon Outside</v>
       </c>
       <c r="C42" t="str">
-        <v>Unlocks Exeggutor Island Main Area</v>
+        <v>Unlocks Captain Kommo-o</v>
       </c>
     </row>
     <row r="43">
@@ -5878,10 +5659,10 @@
         <v>Challenge 42</v>
       </c>
       <c r="B43" t="str">
-        <v>Defeat 10 Pokemon in Exeggutor Island Main Area</v>
+        <v>Defeat Captain Kommo-o</v>
       </c>
       <c r="C43" t="str">
-        <v>Unlocks Vast Poni Canyon Outside</v>
+        <v>Unlocks Captain Mina</v>
       </c>
     </row>
     <row r="44">
@@ -5889,10 +5670,10 @@
         <v>Challenge 43</v>
       </c>
       <c r="B44" t="str">
-        <v>Defeat 10 Pokemon in Vast Poni Canyon Outside</v>
+        <v>Defeat Captain Mina</v>
       </c>
       <c r="C44" t="str">
-        <v>Unlocks Captain Kommo-o</v>
+        <v>Unlocks Kahuna Hapu</v>
       </c>
     </row>
     <row r="45">
@@ -5900,10 +5681,10 @@
         <v>Challenge 44</v>
       </c>
       <c r="B45" t="str">
-        <v>Defeat Captain Kommo-o</v>
+        <v>Defeat Kahuna Hapu</v>
       </c>
       <c r="C45" t="str">
-        <v>Unlocks Captain Mina</v>
+        <v>Unlocks Mount Lanakila Cave</v>
       </c>
     </row>
     <row r="46">
@@ -5911,10 +5692,10 @@
         <v>Challenge 45</v>
       </c>
       <c r="B46" t="str">
-        <v>Defeat Captain Mina</v>
+        <v>Defeat 10 Pokemon in Mount Lanakila Cave</v>
       </c>
       <c r="C46" t="str">
-        <v>Unlocks Kahuna Hapu</v>
+        <v>Unlocks Alola Pokemon League</v>
       </c>
     </row>
     <row r="47">
@@ -5922,301 +5703,1004 @@
         <v>Challenge 46</v>
       </c>
       <c r="B47" t="str">
-        <v>Defeat Kahuna Hapu</v>
+        <v>Defeat Alola Pokemon League</v>
       </c>
       <c r="C47" t="str">
-        <v>Unlocks Mount Lanakila Cave</v>
+        <v>Unlocks Champion Hau</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Challenge 47</v>
+        <v>Extra Challenge A-1</v>
       </c>
       <c r="B48" t="str">
-        <v>Defeat 10 Pokemon in Mount Lanakila Cave</v>
+        <v>Defeat 15 Pokemon in Route 1 East</v>
       </c>
       <c r="C48" t="str">
-        <v>Unlocks Alola Pokemon League</v>
+        <v>Unlocks Route 6 Main Area</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Challenge 48</v>
+        <v>Extra Challenge A-2</v>
       </c>
       <c r="B49" t="str">
-        <v>Defeat Alola Pokemon League</v>
+        <v>Defeat 15 Pokemon in Route 6 Main Area</v>
       </c>
       <c r="C49" t="str">
-        <v>Unlocks Champion Hau</v>
+        <v>Unlocks Royal Avenue Main Area</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Extra Challenge A-1</v>
+        <v>Extra Challenge A-3</v>
       </c>
       <c r="B50" t="str">
-        <v>Defeat Captain Lana</v>
+        <v>Defeat 15 Pokemon in Royal Avenue Main Area</v>
       </c>
       <c r="C50" t="str">
-        <v>Unlocks Route 6 Main Area</v>
+        <v>Unlocks Pikachu Valley Main Area</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Extra Challenge A-2</v>
+        <v>Extra Challenge A-4</v>
       </c>
       <c r="B51" t="str">
-        <v>Defeat 15 Pokemon in Route 6 Main Area</v>
+        <v>Defeat 15 Pokemon in Pikachu Valley Main Area</v>
       </c>
       <c r="C51" t="str">
-        <v>Unlocks Royal Avenue Main Area</v>
+        <v>Unlocks Starter Depot Main Area</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Extra Challenge A-3</v>
+        <v>Extra Challenge B-1</v>
       </c>
       <c r="B52" t="str">
-        <v>Defeat 15 Pokemon in Royal Avenue Main Area</v>
+        <v>Defeat Champion Hau</v>
       </c>
       <c r="C52" t="str">
-        <v>Unlocks Pikachu Valley Main Area</v>
+        <v>Unlocks Poni Coast Main Area</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Extra Challenge A-4</v>
+        <v>Extra Challenge B-2</v>
       </c>
       <c r="B53" t="str">
-        <v>Defeat 15 Pokemon in Pikachu Valley Main Area</v>
+        <v>Defeat 15 Pokemon in Poni Coast Main Area</v>
       </c>
       <c r="C53" t="str">
-        <v>Unlocks Starter Depot Main Area</v>
+        <v>Unlocks Shopping Mall Antiquities Event</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Extra Challenge B-1</v>
+        <v>Extra Challenge B-3</v>
       </c>
       <c r="B54" t="str">
-        <v>Defeat Champion Hau</v>
+        <v>Defeat 15 Pokemon in Shopping Mall Antiquities Event</v>
       </c>
       <c r="C54" t="str">
-        <v>Unlocks Poni Coast Main Area</v>
+        <v>Unlocks Aether Paradise Restricted Area</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Extra Challenge B-2</v>
+        <v>Extra Challenge B-4</v>
       </c>
       <c r="B55" t="str">
-        <v>Defeat 15 Pokemon in Poni Coast Main Area</v>
+        <v>Defeat 15 Pokemon in Aether Paradise Restricted Area</v>
       </c>
       <c r="C55" t="str">
-        <v>Unlocks Shopping Mall Antiquities Event</v>
+        <v>Unlocks The Zenith Anomaly Main Area</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Extra Challenge B-3</v>
+        <v>Extra Challenge C-1</v>
       </c>
       <c r="B56" t="str">
-        <v>Defeat 15 Pokemon in Shopping Mall Antiquities Event</v>
+        <v>Defeat Champion Hau</v>
       </c>
       <c r="C56" t="str">
-        <v>Unlocks Aether Paradise Restricted Area</v>
+        <v>Unlocks Mahalo Trail Main Area</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Extra Challenge B-4</v>
+        <v>Extra Challenge C-2</v>
       </c>
       <c r="B57" t="str">
-        <v>Defeat 15 Pokemon in Aether Paradise Restricted Area</v>
+        <v>Defeat 15 Pokemon in Mahalo Trail Main Area</v>
       </c>
       <c r="C57" t="str">
-        <v>Unlocks The Zenith Anomaly Main Area</v>
+        <v>Unlocks Melemele Meadow Main Area</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Extra Challenge C-1</v>
+        <v>Extra Challenge C-3</v>
       </c>
       <c r="B58" t="str">
-        <v>Defeat Champion Hau</v>
+        <v>Defeat 15 Pokemon in Melemele Meadow Main Area</v>
       </c>
       <c r="C58" t="str">
-        <v>Unlocks Mahalo Trail Main Area</v>
+        <v>Unlocks Ruins of Conflict Special Encounter</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Extra Challenge C-2</v>
+        <v>Extra Challenge C-4</v>
       </c>
       <c r="B59" t="str">
-        <v>Defeat 15 Pokemon in Mahalo Trail Main Area</v>
+        <v>Defeat 15 Pokemon in Ruins of Conflict Special Encounter</v>
       </c>
       <c r="C59" t="str">
-        <v>Unlocks Melemele Meadow Main Area</v>
+        <v>Unlocks Memorial Hill Main</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Extra Challenge C-3</v>
+        <v>Extra Challenge C-5</v>
       </c>
       <c r="B60" t="str">
-        <v>Defeat 15 Pokemon in Melemele Meadow Main Area</v>
+        <v>Defeat 15 Pokemon in Memorial Hill Main</v>
       </c>
       <c r="C60" t="str">
-        <v>Unlocks Ruins of Conflict Special Encounter</v>
+        <v>Unlocks Sacred Shrine Main Area</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Extra Challenge C-4</v>
+        <v>Extra Challenge D-1</v>
       </c>
       <c r="B61" t="str">
-        <v>Defeat 15 Pokemon in Ruins of Conflict Special Encounter</v>
+        <v>Defeat Champion Hau</v>
       </c>
       <c r="C61" t="str">
-        <v>Unlocks Memorial Hill Main</v>
+        <v>Unlocks Poni Grove Main Area</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Extra Challenge C-5</v>
+        <v>Extra Challenge D-2</v>
       </c>
       <c r="B62" t="str">
-        <v>Defeat 15 Pokemon in Memorial Hill Main</v>
+        <v>Defeat 15 Pokemon in Poni Grove Main Area</v>
       </c>
       <c r="C62" t="str">
-        <v>Unlocks Sacred Shrine Main Area</v>
+        <v>Unlocks Poni Plains Center</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Extra Challenge D-1</v>
+        <v>Extra Challenge D-3</v>
       </c>
       <c r="B63" t="str">
-        <v>Defeat Champion Hau</v>
+        <v>Defeat 15 Pokemon in Poni Plains Center</v>
       </c>
       <c r="C63" t="str">
-        <v>Unlocks Poni Grove Main Area</v>
+        <v>Unlocks Resolution Cave Main Area</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Extra Challenge D-2</v>
+        <v>Extra Challenge D-4</v>
       </c>
       <c r="B64" t="str">
-        <v>Defeat 15 Pokemon in Poni Grove Main Area</v>
+        <v>Defeat 15 Pokemon in Resolution Cave Main Area</v>
       </c>
       <c r="C64" t="str">
-        <v>Unlocks Poni Plains Center</v>
+        <v>Unlocks Ruins of Hope Special Encounter</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Extra Challenge D-3</v>
+        <v>Extra Challenge D-5</v>
       </c>
       <c r="B65" t="str">
-        <v>Defeat 15 Pokemon in Poni Plains Center</v>
+        <v>Defeat 15 Pokemon in Ruins of Hope Special Encounter</v>
       </c>
       <c r="C65" t="str">
-        <v>Unlocks Resolution Cave Main Area</v>
+        <v>Unlocks The Interdimensional Rift Main Area</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Extra Challenge D-4</v>
+        <v>Extra Challenge E-1</v>
       </c>
       <c r="B66" t="str">
-        <v>Defeat 15 Pokemon in Resolution Cave Main Area</v>
+        <v>Defeat Champion Hau</v>
       </c>
       <c r="C66" t="str">
-        <v>Unlocks Ruins of Hope Special Encounter</v>
+        <v>Unlocks Route 15 Main Area</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Extra Challenge D-5</v>
+        <v>Extra Challenge E-2</v>
       </c>
       <c r="B67" t="str">
-        <v>Defeat 15 Pokemon in Ruins of Hope Special Encounter</v>
+        <v>Defeat 15 Pokemon in Route 15 Main Area</v>
       </c>
       <c r="C67" t="str">
-        <v>Unlocks The Interdimensional Rift Main Area</v>
+        <v>Unlocks Aether Paradise Labs</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Extra Challenge E-1</v>
+        <v>Extra Challenge E-3</v>
       </c>
       <c r="B68" t="str">
-        <v>Defeat Champion Hau</v>
+        <v>Defeat 15 Pokemon in Aether Paradise Labs</v>
       </c>
       <c r="C68" t="str">
-        <v>Unlocks Route 15 Main Area</v>
+        <v>Unlocks Aether Paradise Secret Lab</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Extra Challenge E-2</v>
+        <v>Extra Challenge E-4</v>
       </c>
       <c r="B69" t="str">
-        <v>Defeat 15 Pokemon in Route 15 Main Area</v>
+        <v>Defeat 15 Pokemon in Aether Paradise Secret Lab</v>
       </c>
       <c r="C69" t="str">
-        <v>Unlocks Aether Paradise Labs</v>
+        <v>Unlocks Lake of the Sunne Main Area</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Extra Challenge E-3</v>
+        <v>Extra Challenge E-5</v>
       </c>
       <c r="B70" t="str">
-        <v>Defeat 15 Pokemon in Aether Paradise Labs</v>
+        <v>Defeat 15 Pokemon in Lake of the Sunne Main Area</v>
       </c>
       <c r="C70" t="str">
-        <v>Unlocks Aether Paradise Secret Lab</v>
+        <v>Unlocks Obsidian Sphere Main Area</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Extra Challenge E-4</v>
+        <v>Extra Challenge E-6</v>
       </c>
       <c r="B71" t="str">
-        <v>Defeat 15 Pokemon in Aether Paradise Secret Lab</v>
+        <v>Defeat 15 Pokemon in Obsidian Sphere Main Area</v>
       </c>
       <c r="C71" t="str">
-        <v>Unlocks Lake of the Sunne Main Area</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>Extra Challenge E-5</v>
-      </c>
-      <c r="B72" t="str">
-        <v>Defeat 15 Pokemon in Lake of the Sunne Main Area</v>
-      </c>
-      <c r="C72" t="str">
-        <v>Unlocks Obsidian Sphere Main Area</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>Extra Challenge E-6</v>
-      </c>
-      <c r="B73" t="str">
-        <v>Defeat 15 Pokemon in Obsidian Sphere Main Area</v>
-      </c>
-      <c r="C73" t="str">
         <v>Transforms Obsidian Sphere into Obsidian Tesseract</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C73"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C71"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D51"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Pokemon Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Pokemon Type</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Path to be include</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Obtained?</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Rowlet</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Grass/Flying</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Starter Depot</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Dartrix</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Grass/Flying</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Starter Depot</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Litten</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Fire</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Starter Depot</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Torracat</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Fire</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Starter Depot</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Popplio</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Water</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Starter Depot</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Brionne</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Water</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Starter Depot</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Pikachu</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Electric</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Route 1 East</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Alolan Raichu</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Electric/Psychic</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Route 1 East</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Yes (Evolution)</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Oricorio</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Fire/Electric/Psychic/Ghost</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Route 3 North</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Lycanroc</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Rock</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Ten Carat Hill Inside</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Staryu</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Water</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Route 7 Main Area</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Pyukumuku</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Water</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Route 7 Main Area</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Bounsweet</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Lush Jungle North</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Oranguru</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Normal/Psychic</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Lush Jungle East Cave</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Passimian</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Fighting</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Lush Jungle East Cave</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Corsola</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Water/Rock</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Route 7 Main Area</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Mareanie</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Poison/Water</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Route 7 Main Area</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Minior</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Rock/Flying</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Mount Hokulani East</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Bruxish</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Water/Psychic</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Route 14 Main Area</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Sandygast</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Ghost/Ground</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Route 15 Main Area</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Klefki</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Steel/Fairy</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Route 16 Main Area</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Crabominable</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Fighting/Ice</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Mount Lanakila Cave</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Amaura</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Rock/Ice</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Route 8 Fossil Restoration</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Ditto</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Route 10</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Tapu Koko</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Electric/Fairy</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Sacred Shrine</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Tapu Lele</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Psychic/Fairy</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Sacred Shrine</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Tapu Bulu</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Grass/Fairy</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Sacred Shrine</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Tapu Fini</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Water/Fairy</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Sacred Shrine</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Cosmog</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Psychic</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Obsidian Sphere</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Cosmoem</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Psychic</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Obsidian Sphere</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Solgaleo</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Psychic/Steel</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Obsidian Sphere</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Lunala</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Psychic/Ghost</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Obsidian Sphere</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Necrozma</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Psychic</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Obsidian Sphere</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Poipole</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Poison</v>
+      </c>
+      <c r="C35" t="str">
+        <v>The Interdimensional Rift</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Naganadel</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Poison/Dragon</v>
+      </c>
+      <c r="C36" t="str">
+        <v>The Interdimensional Rift</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Yes (Evolution)</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Nihilego</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Rock/Poison</v>
+      </c>
+      <c r="C37" t="str">
+        <v>The Interdimensional Rift</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Buzzwole</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Bug/Fighting</v>
+      </c>
+      <c r="C38" t="str">
+        <v>The Interdimensional Rift</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Pheromosa</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Bug/Fighting</v>
+      </c>
+      <c r="C39" t="str">
+        <v>The Interdimensional Rift</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Xurkitree</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Electric</v>
+      </c>
+      <c r="C40" t="str">
+        <v>The Interdimensional Rift</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Celesteela</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Steel/Flying</v>
+      </c>
+      <c r="C41" t="str">
+        <v>The Interdimensional Rift</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Kartana</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Grass/Steel</v>
+      </c>
+      <c r="C42" t="str">
+        <v>The Interdimensional Rift</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Guzzlord</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Dark/Dragon</v>
+      </c>
+      <c r="C43" t="str">
+        <v>The Interdimensional Rift</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Stakataka</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Rock/Steel</v>
+      </c>
+      <c r="C44" t="str">
+        <v>The Interdimensional Rift</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Blacephalon</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Fire/Ghost</v>
+      </c>
+      <c r="C45" t="str">
+        <v>The Interdimensional Rift</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Type: Null</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Aether Paradise Secret Lab</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Silvally</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Aether Paradise Secret Lab</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Porygon</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Aether Paradise Secret Lab</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Magearna</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Steel/Fairy</v>
+      </c>
+      <c r="C49" t="str">
+        <v>The Zenith Anomaly</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Marshadow</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Ghost/Fighting</v>
+      </c>
+      <c r="C50" t="str">
+        <v>The Zenith Anomaly</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Zeraora</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Electric</v>
+      </c>
+      <c r="C51" t="str">
+        <v>The Zenith Anomaly</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Alola_Paths_and_Challenges.xlsx
+++ b/Alola_Paths_and_Challenges.xlsx
@@ -435,7 +435,7 @@
         <v>Pikipek</v>
       </c>
       <c r="E2" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F2" t="str">
         <v>12.50%</v>
@@ -455,7 +455,7 @@
         <v>Yungoos</v>
       </c>
       <c r="E3" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F3" t="str">
         <v>12.50%</v>
@@ -475,7 +475,7 @@
         <v>Alolan Rattata</v>
       </c>
       <c r="E4" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F4" t="str">
         <v>12.50%</v>
@@ -495,7 +495,7 @@
         <v>Ledyba</v>
       </c>
       <c r="E5" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F5" t="str">
         <v>12.50%</v>
@@ -515,7 +515,7 @@
         <v>Spinarak</v>
       </c>
       <c r="E6" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F6" t="str">
         <v>12.50%</v>
@@ -535,7 +535,7 @@
         <v>Grubbin</v>
       </c>
       <c r="E7" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F7" t="str">
         <v>12.50%</v>
@@ -555,7 +555,7 @@
         <v>Pichu</v>
       </c>
       <c r="E8" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F8" t="str">
         <v>12.50%</v>
@@ -575,7 +575,7 @@
         <v>Pikachu</v>
       </c>
       <c r="E9" t="str">
-        <v>3-8</v>
+        <v>2-7</v>
       </c>
       <c r="F9" t="str">
         <v>12.50%</v>
@@ -595,7 +595,7 @@
         <v>Inkay</v>
       </c>
       <c r="E10" t="str">
-        <v>5-10</v>
+        <v>3-8</v>
       </c>
       <c r="F10" t="str">
         <v>20.00%</v>
@@ -615,7 +615,7 @@
         <v>Slowpoke</v>
       </c>
       <c r="E11" t="str">
-        <v>5-10</v>
+        <v>3-8</v>
       </c>
       <c r="F11" t="str">
         <v>20.00%</v>
@@ -635,7 +635,7 @@
         <v>Alolan Meowth</v>
       </c>
       <c r="E12" t="str">
-        <v>5-10</v>
+        <v>3-8</v>
       </c>
       <c r="F12" t="str">
         <v>20.00%</v>
@@ -655,7 +655,7 @@
         <v>Tentacool</v>
       </c>
       <c r="E13" t="str">
-        <v>5-10</v>
+        <v>3-8</v>
       </c>
       <c r="F13" t="str">
         <v>20.00%</v>
@@ -675,7 +675,7 @@
         <v>Finneon</v>
       </c>
       <c r="E14" t="str">
-        <v>5-10</v>
+        <v>3-8</v>
       </c>
       <c r="F14" t="str">
         <v>20.00%</v>
@@ -695,7 +695,7 @@
         <v>Furfrou</v>
       </c>
       <c r="E15" t="str">
-        <v>6-11</v>
+        <v>5-10</v>
       </c>
       <c r="F15" t="str">
         <v>20.00%</v>
@@ -715,7 +715,7 @@
         <v>Hypno</v>
       </c>
       <c r="E16" t="str">
-        <v>6-11</v>
+        <v>5-10</v>
       </c>
       <c r="F16" t="str">
         <v>20.00%</v>
@@ -735,7 +735,7 @@
         <v>Abra</v>
       </c>
       <c r="E17" t="str">
-        <v>6-11</v>
+        <v>5-10</v>
       </c>
       <c r="F17" t="str">
         <v>20.00%</v>
@@ -755,7 +755,7 @@
         <v>Mime Jr.</v>
       </c>
       <c r="E18" t="str">
-        <v>6-11</v>
+        <v>5-10</v>
       </c>
       <c r="F18" t="str">
         <v>20.00%</v>
@@ -775,7 +775,7 @@
         <v>Bewear</v>
       </c>
       <c r="E19" t="str">
-        <v>6-11</v>
+        <v>5-10</v>
       </c>
       <c r="F19" t="str">
         <v>20.00%</v>
@@ -795,7 +795,7 @@
         <v>Drowzee</v>
       </c>
       <c r="E20" t="str">
-        <v>8-13</v>
+        <v>6-11</v>
       </c>
       <c r="F20" t="str">
         <v>16.67%</v>
@@ -815,7 +815,7 @@
         <v>Makuhita</v>
       </c>
       <c r="E21" t="str">
-        <v>8-13</v>
+        <v>6-11</v>
       </c>
       <c r="F21" t="str">
         <v>16.67%</v>
@@ -835,7 +835,7 @@
         <v>Spearow</v>
       </c>
       <c r="E22" t="str">
-        <v>8-13</v>
+        <v>6-11</v>
       </c>
       <c r="F22" t="str">
         <v>16.67%</v>
@@ -855,7 +855,7 @@
         <v>Ekans</v>
       </c>
       <c r="E23" t="str">
-        <v>8-13</v>
+        <v>6-11</v>
       </c>
       <c r="F23" t="str">
         <v>16.67%</v>
@@ -875,7 +875,7 @@
         <v>Growlithe</v>
       </c>
       <c r="E24" t="str">
-        <v>8-13</v>
+        <v>6-11</v>
       </c>
       <c r="F24" t="str">
         <v>16.67%</v>
@@ -895,7 +895,7 @@
         <v>Smeargle</v>
       </c>
       <c r="E25" t="str">
-        <v>8-13</v>
+        <v>6-11</v>
       </c>
       <c r="F25" t="str">
         <v>16.67%</v>
@@ -915,7 +915,7 @@
         <v>Boss</v>
       </c>
       <c r="E26" t="str">
-        <v>9-14</v>
+        <v>8-13</v>
       </c>
       <c r="F26" t="str">
         <v>-</v>
@@ -935,7 +935,7 @@
         <v>Gastly</v>
       </c>
       <c r="E27" t="str">
-        <v>11-16</v>
+        <v>9-14</v>
       </c>
       <c r="F27" t="str">
         <v>25.00%</v>
@@ -955,7 +955,7 @@
         <v>Drifloon</v>
       </c>
       <c r="E28" t="str">
-        <v>11-16</v>
+        <v>9-14</v>
       </c>
       <c r="F28" t="str">
         <v>25.00%</v>
@@ -975,7 +975,7 @@
         <v>Murkrow</v>
       </c>
       <c r="E29" t="str">
-        <v>11-16</v>
+        <v>9-14</v>
       </c>
       <c r="F29" t="str">
         <v>25.00%</v>
@@ -995,7 +995,7 @@
         <v>Misdreavus</v>
       </c>
       <c r="E30" t="str">
-        <v>11-16</v>
+        <v>9-14</v>
       </c>
       <c r="F30" t="str">
         <v>25.00%</v>
@@ -1015,7 +1015,7 @@
         <v>Roggenrola</v>
       </c>
       <c r="E31" t="str">
-        <v>15-20</v>
+        <v>14-19</v>
       </c>
       <c r="F31" t="str">
         <v>20.00%</v>
@@ -1035,7 +1035,7 @@
         <v>Carbink</v>
       </c>
       <c r="E32" t="str">
-        <v>15-20</v>
+        <v>14-19</v>
       </c>
       <c r="F32" t="str">
         <v>20.00%</v>
@@ -1055,7 +1055,7 @@
         <v>Spinda</v>
       </c>
       <c r="E33" t="str">
-        <v>15-20</v>
+        <v>14-19</v>
       </c>
       <c r="F33" t="str">
         <v>20.00%</v>
@@ -1075,7 +1075,7 @@
         <v>Mawile</v>
       </c>
       <c r="E34" t="str">
-        <v>15-20</v>
+        <v>14-19</v>
       </c>
       <c r="F34" t="str">
         <v>20.00%</v>
@@ -1095,7 +1095,7 @@
         <v>Lycanroc</v>
       </c>
       <c r="E35" t="str">
-        <v>15-20</v>
+        <v>14-19</v>
       </c>
       <c r="F35" t="str">
         <v>20.00%</v>
@@ -1115,7 +1115,7 @@
         <v>Barboach</v>
       </c>
       <c r="E36" t="str">
-        <v>17-22</v>
+        <v>15-20</v>
       </c>
       <c r="F36" t="str">
         <v>33.33%</v>
@@ -1135,7 +1135,7 @@
         <v>Smoochum</v>
       </c>
       <c r="E37" t="str">
-        <v>17-22</v>
+        <v>15-20</v>
       </c>
       <c r="F37" t="str">
         <v>33.33%</v>
@@ -1155,7 +1155,7 @@
         <v>Seel</v>
       </c>
       <c r="E38" t="str">
-        <v>17-22</v>
+        <v>15-20</v>
       </c>
       <c r="F38" t="str">
         <v>33.33%</v>
@@ -1175,7 +1175,7 @@
         <v>Boss</v>
       </c>
       <c r="E39" t="str">
-        <v>18-23</v>
+        <v>17-22</v>
       </c>
       <c r="F39" t="str">
         <v>-</v>
@@ -1195,7 +1195,7 @@
         <v>Vikavolt</v>
       </c>
       <c r="E40" t="str">
-        <v>20-25</v>
+        <v>18-23</v>
       </c>
       <c r="F40" t="str">
         <v>20.00%</v>
@@ -1215,7 +1215,7 @@
         <v>Ribombee</v>
       </c>
       <c r="E41" t="str">
-        <v>20-25</v>
+        <v>18-23</v>
       </c>
       <c r="F41" t="str">
         <v>20.00%</v>
@@ -1235,7 +1235,7 @@
         <v>Araquanid</v>
       </c>
       <c r="E42" t="str">
-        <v>20-25</v>
+        <v>18-23</v>
       </c>
       <c r="F42" t="str">
         <v>20.00%</v>
@@ -1255,7 +1255,7 @@
         <v>Lurantis</v>
       </c>
       <c r="E43" t="str">
-        <v>20-25</v>
+        <v>18-23</v>
       </c>
       <c r="F43" t="str">
         <v>20.00%</v>
@@ -1275,7 +1275,7 @@
         <v>Salazzle</v>
       </c>
       <c r="E44" t="str">
-        <v>20-25</v>
+        <v>18-23</v>
       </c>
       <c r="F44" t="str">
         <v>20.00%</v>
@@ -1295,7 +1295,7 @@
         <v>Alolan Marowak</v>
       </c>
       <c r="E45" t="str">
-        <v>20-25</v>
+        <v>18-23</v>
       </c>
       <c r="F45" t="str">
         <v>20.00%</v>
@@ -1315,7 +1315,7 @@
         <v>Kommo-o</v>
       </c>
       <c r="E46" t="str">
-        <v>20-25</v>
+        <v>18-23</v>
       </c>
       <c r="F46" t="str">
         <v>20.00%</v>
@@ -1335,7 +1335,7 @@
         <v>Mimikyu</v>
       </c>
       <c r="E47" t="str">
-        <v>20-25</v>
+        <v>18-23</v>
       </c>
       <c r="F47" t="str">
         <v>20.00%</v>
@@ -1355,7 +1355,7 @@
         <v>Poliwhirl</v>
       </c>
       <c r="E48" t="str">
-        <v>20-25</v>
+        <v>18-23</v>
       </c>
       <c r="F48" t="str">
         <v>20.00%</v>
@@ -1375,7 +1375,7 @@
         <v>Ditto</v>
       </c>
       <c r="E49" t="str">
-        <v>20-25</v>
+        <v>18-23</v>
       </c>
       <c r="F49" t="str">
         <v>20.00%</v>
@@ -1395,7 +1395,7 @@
         <v>Eevee</v>
       </c>
       <c r="E50" t="str">
-        <v>21-26</v>
+        <v>20-25</v>
       </c>
       <c r="F50" t="str">
         <v>25.00%</v>
@@ -1415,7 +1415,7 @@
         <v>Mareep</v>
       </c>
       <c r="E51" t="str">
-        <v>21-26</v>
+        <v>20-25</v>
       </c>
       <c r="F51" t="str">
         <v>25.00%</v>
@@ -1435,7 +1435,7 @@
         <v>Tauros</v>
       </c>
       <c r="E52" t="str">
-        <v>21-26</v>
+        <v>20-25</v>
       </c>
       <c r="F52" t="str">
         <v>25.00%</v>
@@ -1455,7 +1455,7 @@
         <v>Miltank</v>
       </c>
       <c r="E53" t="str">
-        <v>21-26</v>
+        <v>20-25</v>
       </c>
       <c r="F53" t="str">
         <v>25.00%</v>
@@ -1495,7 +1495,7 @@
         <v>Noibat</v>
       </c>
       <c r="E55" t="str">
-        <v>24-29</v>
+        <v>23-28</v>
       </c>
       <c r="F55" t="str">
         <v>33.33%</v>
@@ -1515,7 +1515,7 @@
         <v>Fomantis</v>
       </c>
       <c r="E56" t="str">
-        <v>24-29</v>
+        <v>23-28</v>
       </c>
       <c r="F56" t="str">
         <v>33.33%</v>
@@ -1535,7 +1535,7 @@
         <v>Bounsweet</v>
       </c>
       <c r="E57" t="str">
-        <v>24-29</v>
+        <v>23-28</v>
       </c>
       <c r="F57" t="str">
         <v>33.33%</v>
@@ -1555,7 +1555,7 @@
         <v>Wingull</v>
       </c>
       <c r="E58" t="str">
-        <v>25-30</v>
+        <v>24-29</v>
       </c>
       <c r="F58" t="str">
         <v>20.00%</v>
@@ -1575,7 +1575,7 @@
         <v>Lillipup</v>
       </c>
       <c r="E59" t="str">
-        <v>25-30</v>
+        <v>24-29</v>
       </c>
       <c r="F59" t="str">
         <v>20.00%</v>
@@ -1595,7 +1595,7 @@
         <v>Paras</v>
       </c>
       <c r="E60" t="str">
-        <v>25-30</v>
+        <v>24-29</v>
       </c>
       <c r="F60" t="str">
         <v>20.00%</v>
@@ -1615,7 +1615,7 @@
         <v>Goldeen</v>
       </c>
       <c r="E61" t="str">
-        <v>25-30</v>
+        <v>24-29</v>
       </c>
       <c r="F61" t="str">
         <v>20.00%</v>
@@ -1635,7 +1635,7 @@
         <v>Feebas</v>
       </c>
       <c r="E62" t="str">
-        <v>25-30</v>
+        <v>24-29</v>
       </c>
       <c r="F62" t="str">
         <v>20.00%</v>
@@ -1655,7 +1655,7 @@
         <v>Boss</v>
       </c>
       <c r="E63" t="str">
-        <v>27-32</v>
+        <v>26-31</v>
       </c>
       <c r="F63" t="str">
         <v>-</v>
@@ -1675,7 +1675,7 @@
         <v>Cubone</v>
       </c>
       <c r="E64" t="str">
-        <v>28-33</v>
+        <v>27-32</v>
       </c>
       <c r="F64" t="str">
         <v>33.33%</v>
@@ -1695,7 +1695,7 @@
         <v>Kangaskhan</v>
       </c>
       <c r="E65" t="str">
-        <v>28-33</v>
+        <v>27-32</v>
       </c>
       <c r="F65" t="str">
         <v>33.33%</v>
@@ -1715,7 +1715,7 @@
         <v>Magby</v>
       </c>
       <c r="E66" t="str">
-        <v>28-33</v>
+        <v>27-32</v>
       </c>
       <c r="F66" t="str">
         <v>33.33%</v>
@@ -1735,7 +1735,7 @@
         <v>Boss</v>
       </c>
       <c r="E67" t="str">
-        <v>30-35</v>
+        <v>29-34</v>
       </c>
       <c r="F67" t="str">
         <v>-</v>
@@ -1755,7 +1755,7 @@
         <v>Staryu</v>
       </c>
       <c r="E68" t="str">
-        <v>31-36</v>
+        <v>30-35</v>
       </c>
       <c r="F68" t="str">
         <v>20.00%</v>
@@ -1775,7 +1775,7 @@
         <v>Pyukumuku</v>
       </c>
       <c r="E69" t="str">
-        <v>31-36</v>
+        <v>30-35</v>
       </c>
       <c r="F69" t="str">
         <v>20.00%</v>
@@ -1795,7 +1795,7 @@
         <v>Corsola</v>
       </c>
       <c r="E70" t="str">
-        <v>31-36</v>
+        <v>30-35</v>
       </c>
       <c r="F70" t="str">
         <v>20.00%</v>
@@ -1815,7 +1815,7 @@
         <v>Mareanie</v>
       </c>
       <c r="E71" t="str">
-        <v>31-36</v>
+        <v>30-35</v>
       </c>
       <c r="F71" t="str">
         <v>20.00%</v>
@@ -1835,7 +1835,7 @@
         <v>Bruxish</v>
       </c>
       <c r="E72" t="str">
-        <v>31-36</v>
+        <v>30-35</v>
       </c>
       <c r="F72" t="str">
         <v>20.00%</v>
@@ -1855,7 +1855,7 @@
         <v>Omanyte</v>
       </c>
       <c r="E73" t="str">
-        <v>33-38</v>
+        <v>32-37</v>
       </c>
       <c r="F73" t="str">
         <v>20.00%</v>
@@ -1875,7 +1875,7 @@
         <v>Kabuto</v>
       </c>
       <c r="E74" t="str">
-        <v>33-38</v>
+        <v>32-37</v>
       </c>
       <c r="F74" t="str">
         <v>20.00%</v>
@@ -1895,7 +1895,7 @@
         <v>Lileep</v>
       </c>
       <c r="E75" t="str">
-        <v>33-38</v>
+        <v>32-37</v>
       </c>
       <c r="F75" t="str">
         <v>20.00%</v>
@@ -1915,7 +1915,7 @@
         <v>Anorith</v>
       </c>
       <c r="E76" t="str">
-        <v>33-38</v>
+        <v>32-37</v>
       </c>
       <c r="F76" t="str">
         <v>20.00%</v>
@@ -1935,7 +1935,7 @@
         <v>Cranidos</v>
       </c>
       <c r="E77" t="str">
-        <v>33-38</v>
+        <v>32-37</v>
       </c>
       <c r="F77" t="str">
         <v>20.00%</v>
@@ -1955,7 +1955,7 @@
         <v>Shieldon</v>
       </c>
       <c r="E78" t="str">
-        <v>33-38</v>
+        <v>32-37</v>
       </c>
       <c r="F78" t="str">
         <v>20.00%</v>
@@ -1975,7 +1975,7 @@
         <v>Archen</v>
       </c>
       <c r="E79" t="str">
-        <v>33-38</v>
+        <v>32-37</v>
       </c>
       <c r="F79" t="str">
         <v>20.00%</v>
@@ -1995,7 +1995,7 @@
         <v>Tirtouga</v>
       </c>
       <c r="E80" t="str">
-        <v>33-38</v>
+        <v>32-37</v>
       </c>
       <c r="F80" t="str">
         <v>20.00%</v>
@@ -2015,7 +2015,7 @@
         <v>Tyrunt</v>
       </c>
       <c r="E81" t="str">
-        <v>33-38</v>
+        <v>32-37</v>
       </c>
       <c r="F81" t="str">
         <v>20.00%</v>
@@ -2035,7 +2035,7 @@
         <v>Amaura</v>
       </c>
       <c r="E82" t="str">
-        <v>33-38</v>
+        <v>32-37</v>
       </c>
       <c r="F82" t="str">
         <v>20.00%</v>
@@ -2055,7 +2055,7 @@
         <v>Trumbeak</v>
       </c>
       <c r="E83" t="str">
-        <v>34-39</v>
+        <v>33-38</v>
       </c>
       <c r="F83" t="str">
         <v>16.67%</v>
@@ -2075,7 +2075,7 @@
         <v>Steenee</v>
       </c>
       <c r="E84" t="str">
-        <v>34-39</v>
+        <v>33-38</v>
       </c>
       <c r="F84" t="str">
         <v>16.67%</v>
@@ -2095,7 +2095,7 @@
         <v>Comfey</v>
       </c>
       <c r="E85" t="str">
-        <v>34-39</v>
+        <v>33-38</v>
       </c>
       <c r="F85" t="str">
         <v>16.67%</v>
@@ -2115,7 +2115,7 @@
         <v>Hoothoot</v>
       </c>
       <c r="E86" t="str">
-        <v>34-39</v>
+        <v>33-38</v>
       </c>
       <c r="F86" t="str">
         <v>16.67%</v>
@@ -2135,7 +2135,7 @@
         <v>Oranguru</v>
       </c>
       <c r="E87" t="str">
-        <v>34-39</v>
+        <v>33-38</v>
       </c>
       <c r="F87" t="str">
         <v>16.67%</v>
@@ -2155,7 +2155,7 @@
         <v>Bounsweet</v>
       </c>
       <c r="E88" t="str">
-        <v>34-39</v>
+        <v>33-38</v>
       </c>
       <c r="F88" t="str">
         <v>16.67%</v>
@@ -2175,7 +2175,7 @@
         <v>Golbat</v>
       </c>
       <c r="E89" t="str">
-        <v>36-41</v>
+        <v>35-40</v>
       </c>
       <c r="F89" t="str">
         <v>20.00%</v>
@@ -2195,7 +2195,7 @@
         <v>Salandit</v>
       </c>
       <c r="E90" t="str">
-        <v>36-41</v>
+        <v>35-40</v>
       </c>
       <c r="F90" t="str">
         <v>20.00%</v>
@@ -2215,7 +2215,7 @@
         <v>Larvesta</v>
       </c>
       <c r="E91" t="str">
-        <v>36-41</v>
+        <v>35-40</v>
       </c>
       <c r="F91" t="str">
         <v>20.00%</v>
@@ -2235,7 +2235,7 @@
         <v>Oranguru</v>
       </c>
       <c r="E92" t="str">
-        <v>36-41</v>
+        <v>35-40</v>
       </c>
       <c r="F92" t="str">
         <v>20.00%</v>
@@ -2255,7 +2255,7 @@
         <v>Passimian</v>
       </c>
       <c r="E93" t="str">
-        <v>36-41</v>
+        <v>35-40</v>
       </c>
       <c r="F93" t="str">
         <v>20.00%</v>
@@ -2275,7 +2275,7 @@
         <v>Boss</v>
       </c>
       <c r="E94" t="str">
-        <v>37-42</v>
+        <v>36-41</v>
       </c>
       <c r="F94" t="str">
         <v>-</v>
@@ -2295,7 +2295,7 @@
         <v>Zubat</v>
       </c>
       <c r="E95" t="str">
-        <v>39-44</v>
+        <v>38-43</v>
       </c>
       <c r="F95" t="str">
         <v>25.00%</v>
@@ -2315,7 +2315,7 @@
         <v>Alolan Diglett</v>
       </c>
       <c r="E96" t="str">
-        <v>39-44</v>
+        <v>38-43</v>
       </c>
       <c r="F96" t="str">
         <v>25.00%</v>
@@ -2335,7 +2335,7 @@
         <v>Kecleon</v>
       </c>
       <c r="E97" t="str">
-        <v>39-44</v>
+        <v>38-43</v>
       </c>
       <c r="F97" t="str">
         <v>25.00%</v>
@@ -2355,7 +2355,7 @@
         <v>Larvitar</v>
       </c>
       <c r="E98" t="str">
-        <v>39-44</v>
+        <v>38-43</v>
       </c>
       <c r="F98" t="str">
         <v>25.00%</v>
@@ -2375,7 +2375,7 @@
         <v>Gumshoos</v>
       </c>
       <c r="E99" t="str">
-        <v>43-48</v>
+        <v>42-47</v>
       </c>
       <c r="F99" t="str">
         <v>12.50%</v>
@@ -2395,7 +2395,7 @@
         <v>Wingull</v>
       </c>
       <c r="E100" t="str">
-        <v>43-48</v>
+        <v>42-47</v>
       </c>
       <c r="F100" t="str">
         <v>12.50%</v>
@@ -2415,7 +2415,7 @@
         <v>Magikarp</v>
       </c>
       <c r="E101" t="str">
-        <v>43-48</v>
+        <v>42-47</v>
       </c>
       <c r="F101" t="str">
         <v>12.50%</v>
@@ -2435,7 +2435,7 @@
         <v>Stufful</v>
       </c>
       <c r="E102" t="str">
-        <v>43-48</v>
+        <v>42-47</v>
       </c>
       <c r="F102" t="str">
         <v>12.50%</v>
@@ -2455,7 +2455,7 @@
         <v>Chinchou</v>
       </c>
       <c r="E103" t="str">
-        <v>43-48</v>
+        <v>42-47</v>
       </c>
       <c r="F103" t="str">
         <v>12.50%</v>
@@ -2475,7 +2475,7 @@
         <v>Alolan Raticate</v>
       </c>
       <c r="E104" t="str">
-        <v>43-48</v>
+        <v>42-47</v>
       </c>
       <c r="F104" t="str">
         <v>12.50%</v>
@@ -2495,7 +2495,7 @@
         <v>Natu</v>
       </c>
       <c r="E105" t="str">
-        <v>43-48</v>
+        <v>42-47</v>
       </c>
       <c r="F105" t="str">
         <v>12.50%</v>
@@ -2515,7 +2515,7 @@
         <v>Nosepass</v>
       </c>
       <c r="E106" t="str">
-        <v>43-48</v>
+        <v>42-47</v>
       </c>
       <c r="F106" t="str">
         <v>12.50%</v>
@@ -2775,7 +2775,7 @@
         <v>Cleffa</v>
       </c>
       <c r="E119" t="str">
-        <v>52-57</v>
+        <v>51-56</v>
       </c>
       <c r="F119" t="str">
         <v>25.00%</v>
@@ -2795,7 +2795,7 @@
         <v>Elgyem</v>
       </c>
       <c r="E120" t="str">
-        <v>52-57</v>
+        <v>51-56</v>
       </c>
       <c r="F120" t="str">
         <v>25.00%</v>
@@ -2815,7 +2815,7 @@
         <v>Beldum</v>
       </c>
       <c r="E121" t="str">
-        <v>52-57</v>
+        <v>51-56</v>
       </c>
       <c r="F121" t="str">
         <v>25.00%</v>
@@ -2835,7 +2835,7 @@
         <v>Minior</v>
       </c>
       <c r="E122" t="str">
-        <v>52-57</v>
+        <v>51-56</v>
       </c>
       <c r="F122" t="str">
         <v>25.00%</v>
@@ -2875,7 +2875,7 @@
         <v>Shiinotic</v>
       </c>
       <c r="E124" t="str">
-        <v>55-60</v>
+        <v>54-59</v>
       </c>
       <c r="F124" t="str">
         <v>11.11%</v>
@@ -2895,7 +2895,7 @@
         <v>Parasect</v>
       </c>
       <c r="E125" t="str">
-        <v>55-60</v>
+        <v>54-59</v>
       </c>
       <c r="F125" t="str">
         <v>11.11%</v>
@@ -2915,7 +2915,7 @@
         <v>Komala</v>
       </c>
       <c r="E126" t="str">
-        <v>55-60</v>
+        <v>54-59</v>
       </c>
       <c r="F126" t="str">
         <v>11.11%</v>
@@ -2935,7 +2935,7 @@
         <v>Houndoom</v>
       </c>
       <c r="E127" t="str">
-        <v>55-60</v>
+        <v>54-59</v>
       </c>
       <c r="F127" t="str">
         <v>11.11%</v>
@@ -2955,7 +2955,7 @@
         <v>Manectric</v>
       </c>
       <c r="E128" t="str">
-        <v>55-60</v>
+        <v>54-59</v>
       </c>
       <c r="F128" t="str">
         <v>11.11%</v>
@@ -2975,7 +2975,7 @@
         <v>Scraggy</v>
       </c>
       <c r="E129" t="str">
-        <v>55-60</v>
+        <v>54-59</v>
       </c>
       <c r="F129" t="str">
         <v>11.11%</v>
@@ -2995,7 +2995,7 @@
         <v>Bisharp</v>
       </c>
       <c r="E130" t="str">
-        <v>55-60</v>
+        <v>54-59</v>
       </c>
       <c r="F130" t="str">
         <v>11.11%</v>
@@ -3015,7 +3015,7 @@
         <v>Machop</v>
       </c>
       <c r="E131" t="str">
-        <v>55-60</v>
+        <v>54-59</v>
       </c>
       <c r="F131" t="str">
         <v>11.11%</v>
@@ -3035,7 +3035,7 @@
         <v>Hawlucha</v>
       </c>
       <c r="E132" t="str">
-        <v>55-60</v>
+        <v>54-59</v>
       </c>
       <c r="F132" t="str">
         <v>11.11%</v>
@@ -3055,7 +3055,7 @@
         <v>Alolan Dugtrio</v>
       </c>
       <c r="E133" t="str">
-        <v>58-63</v>
+        <v>57-62</v>
       </c>
       <c r="F133" t="str">
         <v>20.00%</v>
@@ -3075,7 +3075,7 @@
         <v>Sandile</v>
       </c>
       <c r="E134" t="str">
-        <v>58-63</v>
+        <v>57-62</v>
       </c>
       <c r="F134" t="str">
         <v>20.00%</v>
@@ -3095,7 +3095,7 @@
         <v>Krokorok</v>
       </c>
       <c r="E135" t="str">
-        <v>58-63</v>
+        <v>57-62</v>
       </c>
       <c r="F135" t="str">
         <v>20.00%</v>
@@ -3115,7 +3115,7 @@
         <v>Staryu</v>
       </c>
       <c r="E136" t="str">
-        <v>58-63</v>
+        <v>57-62</v>
       </c>
       <c r="F136" t="str">
         <v>20.00%</v>
@@ -3135,7 +3135,7 @@
         <v>Sandygast</v>
       </c>
       <c r="E137" t="str">
-        <v>58-63</v>
+        <v>57-62</v>
       </c>
       <c r="F137" t="str">
         <v>20.00%</v>
@@ -3355,7 +3355,7 @@
         <v>Boss</v>
       </c>
       <c r="E148" t="str">
-        <v>64-69</v>
+        <v>63-68</v>
       </c>
       <c r="F148" t="str">
         <v>-</v>
@@ -5208,7 +5208,7 @@
         <v>Challenge 1</v>
       </c>
       <c r="B2" t="str">
-        <v>Defeat 10 Pokemon in Route 1 East</v>
+        <v>Defeat 15 Pokemon in Route 1 East</v>
       </c>
       <c r="C2" t="str">
         <v>Unlocks Route 1 Hau'oli Outskirts</v>
@@ -5219,7 +5219,7 @@
         <v>Challenge 2</v>
       </c>
       <c r="B3" t="str">
-        <v>Defeat 10 Pokemon in Route 1 Hau'oli Outskirts</v>
+        <v>Catch 3 Dark type Pokemon in Route 1 Hau'oli Outskirts</v>
       </c>
       <c r="C3" t="str">
         <v>Unlocks Hau'oli City Shopping District</v>
@@ -5230,7 +5230,7 @@
         <v>Challenge 3</v>
       </c>
       <c r="B4" t="str">
-        <v>Defeat 10 Pokemon in Hau'oli City Shopping District</v>
+        <v>Catch 5 Pokemon of Uncommon or better rarity in Hau'oli City Shopping District</v>
       </c>
       <c r="C4" t="str">
         <v>Unlocks Route 2 North</v>
@@ -5241,7 +5241,7 @@
         <v>Challenge 4</v>
       </c>
       <c r="B5" t="str">
-        <v>Defeat 10 Pokemon in Route 2 North</v>
+        <v>Catch 2 Pokemon of Rare or better rarity in Route 2 North</v>
       </c>
       <c r="C5" t="str">
         <v>Unlocks Captain Ilima</v>
@@ -5263,7 +5263,7 @@
         <v>Challenge 6</v>
       </c>
       <c r="B7" t="str">
-        <v>Defeat 10 Pokemon in Hau'oli Cemetery Main Area</v>
+        <v>Catch 1 Epic rarity Pokemon in Hau'oli Cemetery Main Area</v>
       </c>
       <c r="C7" t="str">
         <v>Unlocks Ten Carat Hill Farthest Hollow</v>
@@ -5274,7 +5274,7 @@
         <v>Challenge 7</v>
       </c>
       <c r="B8" t="str">
-        <v>Defeat 10 Pokemon in Ten Carat Hill Farthest Hollow</v>
+        <v>Defeat 5 specific Rock type Pokemon</v>
       </c>
       <c r="C8" t="str">
         <v>Unlocks Seaward Cave Main Area</v>
@@ -5285,7 +5285,7 @@
         <v>Challenge 8</v>
       </c>
       <c r="B9" t="str">
-        <v>Defeat 10 Pokemon in Seaward Cave Main Area</v>
+        <v>Catch 10 Pokemon in Seaward Cave Main Area</v>
       </c>
       <c r="C9" t="str">
         <v>Unlocks Kahuna Hala</v>
@@ -5318,7 +5318,7 @@
         <v>Challenge 11</v>
       </c>
       <c r="B12" t="str">
-        <v>Defeat 10 Pokemon in Heahea Beach Main Area Part 2</v>
+        <v>Defeat 15 Pokemon in Heahea Beach Main Area Part 2</v>
       </c>
       <c r="C12" t="str">
         <v>Unlocks Paniola Ranch Main Area</v>
@@ -5329,7 +5329,7 @@
         <v>Challenge 12</v>
       </c>
       <c r="B13" t="str">
-        <v>Defeat 10 Pokemon in Paniola Ranch Main Area</v>
+        <v>Catch 3 Normal type Pokemon in Paniola Ranch Main Area</v>
       </c>
       <c r="C13" t="str">
         <v>Unlocks Daycare NPC</v>
@@ -5351,7 +5351,7 @@
         <v>Challenge 14</v>
       </c>
       <c r="B15" t="str">
-        <v>Defeat 10 Pokemon in Route 5 Main Area</v>
+        <v>Catch 5 Pokemon of Uncommon or better rarity in Route 5 Main Area</v>
       </c>
       <c r="C15" t="str">
         <v>Unlocks Brooklet Hill South</v>
@@ -5362,7 +5362,7 @@
         <v>Challenge 15</v>
       </c>
       <c r="B16" t="str">
-        <v>Defeat 10 Pokemon in Brooklet Hill South</v>
+        <v>Catch 2 Pokemon of Rare or better rarity in Brooklet Hill South</v>
       </c>
       <c r="C16" t="str">
         <v>Unlocks Captain Lana</v>
@@ -5395,7 +5395,7 @@
         <v>Challenge 18</v>
       </c>
       <c r="B19" t="str">
-        <v>Defeat 10 Pokemon in Route 7 Main Area</v>
+        <v>Defeat 5 specific Water type Pokemon</v>
       </c>
       <c r="C19" t="str">
         <v>Unlocks Route 8 Fossil Restoration Center Part 1</v>
@@ -5406,7 +5406,7 @@
         <v>Challenge 19</v>
       </c>
       <c r="B20" t="str">
-        <v>Defeat 10 Pokemon in Route 8 Fossil Restoration Center Part 1</v>
+        <v>Catch 10 Pokemon in Route 8 Fossil Restoration Center Part 1</v>
       </c>
       <c r="C20" t="str">
         <v>Unlocks Route 8 Fossil Restoration Center Part 2</v>
@@ -5417,7 +5417,7 @@
         <v>Challenge 20</v>
       </c>
       <c r="B21" t="str">
-        <v>Defeat 10 Pokemon in Route 8 Fossil Restoration Center Part 2</v>
+        <v>Catch 2 specific Pokemon species in Route 8 Fossil Restoration Center Part 2</v>
       </c>
       <c r="C21" t="str">
         <v>Unlocks Lush Jungle North</v>
@@ -5428,7 +5428,7 @@
         <v>Challenge 21</v>
       </c>
       <c r="B22" t="str">
-        <v>Defeat 10 Pokemon in Lush Jungle North</v>
+        <v>Defeat 15 Pokemon in Lush Jungle North</v>
       </c>
       <c r="C22" t="str">
         <v>Unlocks Lush Jungle East Cave</v>
@@ -5439,7 +5439,7 @@
         <v>Challenge 22</v>
       </c>
       <c r="B23" t="str">
-        <v>Defeat 10 Pokemon in Lush Jungle East Cave</v>
+        <v>Catch 3 Poison type Pokemon in Lush Jungle East Cave</v>
       </c>
       <c r="C23" t="str">
         <v>Unlocks Captain Mallow</v>
@@ -5461,7 +5461,7 @@
         <v>Challenge 24</v>
       </c>
       <c r="B25" t="str">
-        <v>Defeat 10 Pokemon in Diglett's Tunnel Main Area</v>
+        <v>Catch 5 Pokemon of Uncommon or better rarity in Diglett's Tunnel Main Area</v>
       </c>
       <c r="C25" t="str">
         <v>Unlocks Akala Outskirts Main Area</v>
@@ -5472,7 +5472,7 @@
         <v>Challenge 25</v>
       </c>
       <c r="B26" t="str">
-        <v>Defeat 10 Pokemon in Akala Outskirts Main Area</v>
+        <v>Catch 2 Pokemon of Rare or better rarity in Akala Outskirts Main Area</v>
       </c>
       <c r="C26" t="str">
         <v>Unlocks Kahuna Olivia</v>
@@ -5494,7 +5494,7 @@
         <v>Challenge 27</v>
       </c>
       <c r="B28" t="str">
-        <v>Defeat 10 Pokemon in Malie City Outer Cape</v>
+        <v>Catch 1 Epic rarity Pokemon in Malie City Outer Cape</v>
       </c>
       <c r="C28" t="str">
         <v>Unlocks Route 10 Main Area</v>
@@ -5505,7 +5505,7 @@
         <v>Challenge 28</v>
       </c>
       <c r="B29" t="str">
-        <v>Defeat 10 Pokemon in Route 10 Main Area</v>
+        <v>Defeat 5 specific Bug type Pokemon</v>
       </c>
       <c r="C29" t="str">
         <v>Unlocks Mount Hokulani East</v>
@@ -5516,7 +5516,7 @@
         <v>Challenge 29</v>
       </c>
       <c r="B30" t="str">
-        <v>Defeat 10 Pokemon in Mount Hokulani East</v>
+        <v>Catch 10 Pokemon in Mount Hokulani East</v>
       </c>
       <c r="C30" t="str">
         <v>Unlocks Captain Sophocles</v>
@@ -5538,7 +5538,7 @@
         <v>Challenge 31</v>
       </c>
       <c r="B32" t="str">
-        <v>Defeat 10 Pokemon in Route 11 Main Area</v>
+        <v>Catch 2 specific Pokemon species in Route 11 Main Area</v>
       </c>
       <c r="C32" t="str">
         <v>Unlocks Haina Desert Main Area</v>
@@ -5549,7 +5549,7 @@
         <v>Challenge 32</v>
       </c>
       <c r="B33" t="str">
-        <v>Defeat 10 Pokemon in Haina Desert Main Area</v>
+        <v>Defeat 15 Pokemon in Haina Desert Main Area</v>
       </c>
       <c r="C33" t="str">
         <v>Unlocks Tapu Village Main Area</v>
@@ -5560,7 +5560,7 @@
         <v>Challenge 33</v>
       </c>
       <c r="B34" t="str">
-        <v>Defeat 10 Pokemon in Tapu Village Main Area</v>
+        <v>Catch 3 Rock type Pokemon in Tapu Village Main Area</v>
       </c>
       <c r="C34" t="str">
         <v>Unlocks Thrifty Megamart Abandoned Site</v>
@@ -5571,7 +5571,7 @@
         <v>Challenge 34</v>
       </c>
       <c r="B35" t="str">
-        <v>Defeat 10 Pokemon in Thrifty Megamart Abandoned Site</v>
+        <v>Catch 5 Pokemon of Uncommon or better rarity in Thrifty Megamart Abandoned Site</v>
       </c>
       <c r="C35" t="str">
         <v>Unlocks Captain Acerola</v>
@@ -5604,7 +5604,7 @@
         <v>Challenge 37</v>
       </c>
       <c r="B38" t="str">
-        <v>Defeat 10 Pokemon in Seafolk Village Main</v>
+        <v>Catch 2 Pokemon of Rare or better rarity in Seafolk Village Main</v>
       </c>
       <c r="C38" t="str">
         <v>Unlocks Poni Wilds Main Area</v>
@@ -5615,7 +5615,7 @@
         <v>Challenge 38</v>
       </c>
       <c r="B39" t="str">
-        <v>Defeat 10 Pokemon in Poni Wilds Main Area</v>
+        <v>Catch 1 Epic rarity Pokemon in Poni Wilds Main Area</v>
       </c>
       <c r="C39" t="str">
         <v>Unlocks Poni Breaker Coast Main Area</v>
@@ -5626,7 +5626,7 @@
         <v>Challenge 39</v>
       </c>
       <c r="B40" t="str">
-        <v>Defeat 10 Pokemon in Poni Breaker Coast Main Area</v>
+        <v>Defeat 5 specific Bug type Pokemon</v>
       </c>
       <c r="C40" t="str">
         <v>Unlocks Exeggutor Island Main Area</v>
@@ -5637,7 +5637,7 @@
         <v>Challenge 40</v>
       </c>
       <c r="B41" t="str">
-        <v>Defeat 10 Pokemon in Exeggutor Island Main Area</v>
+        <v>Catch 10 Pokemon in Exeggutor Island Main Area</v>
       </c>
       <c r="C41" t="str">
         <v>Unlocks Vast Poni Canyon Outside</v>
@@ -5648,7 +5648,7 @@
         <v>Challenge 41</v>
       </c>
       <c r="B42" t="str">
-        <v>Defeat 10 Pokemon in Vast Poni Canyon Outside</v>
+        <v>Catch 2 specific Pokemon species in Vast Poni Canyon Outside</v>
       </c>
       <c r="C42" t="str">
         <v>Unlocks Captain Kommo-o</v>
@@ -5692,7 +5692,7 @@
         <v>Challenge 45</v>
       </c>
       <c r="B46" t="str">
-        <v>Defeat 10 Pokemon in Mount Lanakila Cave</v>
+        <v>Defeat 15 Pokemon in Mount Lanakila Cave</v>
       </c>
       <c r="C46" t="str">
         <v>Unlocks Alola Pokemon League</v>
@@ -5714,7 +5714,7 @@
         <v>Extra Challenge A-1</v>
       </c>
       <c r="B48" t="str">
-        <v>Defeat 15 Pokemon in Route 1 East</v>
+        <v>Defeat Captain Lana</v>
       </c>
       <c r="C48" t="str">
         <v>Unlocks Route 6 Main Area</v>
@@ -5725,7 +5725,7 @@
         <v>Extra Challenge A-2</v>
       </c>
       <c r="B49" t="str">
-        <v>Defeat 15 Pokemon in Route 6 Main Area</v>
+        <v>Defeat 10 Pokemon in Route 6 Main Area</v>
       </c>
       <c r="C49" t="str">
         <v>Unlocks Royal Avenue Main Area</v>
@@ -5736,7 +5736,7 @@
         <v>Extra Challenge A-3</v>
       </c>
       <c r="B50" t="str">
-        <v>Defeat 15 Pokemon in Royal Avenue Main Area</v>
+        <v>Catch 3 Fire type Pokemon in Royal Avenue Main Area</v>
       </c>
       <c r="C50" t="str">
         <v>Unlocks Pikachu Valley Main Area</v>
@@ -5747,7 +5747,7 @@
         <v>Extra Challenge A-4</v>
       </c>
       <c r="B51" t="str">
-        <v>Defeat 15 Pokemon in Pikachu Valley Main Area</v>
+        <v>Catch 5 Pokemon of Uncommon or better rarity in Pikachu Valley Main Area</v>
       </c>
       <c r="C51" t="str">
         <v>Unlocks Starter Depot Main Area</v>
@@ -5769,7 +5769,7 @@
         <v>Extra Challenge B-2</v>
       </c>
       <c r="B53" t="str">
-        <v>Defeat 15 Pokemon in Poni Coast Main Area</v>
+        <v>Catch 2 Pokemon of Rare or better rarity in Poni Coast Main Area</v>
       </c>
       <c r="C53" t="str">
         <v>Unlocks Shopping Mall Antiquities Event</v>
@@ -5780,7 +5780,7 @@
         <v>Extra Challenge B-3</v>
       </c>
       <c r="B54" t="str">
-        <v>Defeat 15 Pokemon in Shopping Mall Antiquities Event</v>
+        <v>Defeat 10 Pokemon in Shopping Mall Antiquities Event</v>
       </c>
       <c r="C54" t="str">
         <v>Unlocks Aether Paradise Restricted Area</v>
@@ -5791,7 +5791,7 @@
         <v>Extra Challenge B-4</v>
       </c>
       <c r="B55" t="str">
-        <v>Defeat 15 Pokemon in Aether Paradise Restricted Area</v>
+        <v>Defeat 10 Pokemon in Aether Paradise Restricted Area</v>
       </c>
       <c r="C55" t="str">
         <v>Unlocks The Zenith Anomaly Main Area</v>
@@ -5813,7 +5813,7 @@
         <v>Extra Challenge C-2</v>
       </c>
       <c r="B57" t="str">
-        <v>Defeat 15 Pokemon in Mahalo Trail Main Area</v>
+        <v>Defeat 10 Pokemon in Mahalo Trail Main Area</v>
       </c>
       <c r="C57" t="str">
         <v>Unlocks Melemele Meadow Main Area</v>
@@ -5824,7 +5824,7 @@
         <v>Extra Challenge C-3</v>
       </c>
       <c r="B58" t="str">
-        <v>Defeat 15 Pokemon in Melemele Meadow Main Area</v>
+        <v>Catch 1 Epic rarity Pokemon in Melemele Meadow Main Area</v>
       </c>
       <c r="C58" t="str">
         <v>Unlocks Ruins of Conflict Special Encounter</v>
@@ -5835,7 +5835,7 @@
         <v>Extra Challenge C-4</v>
       </c>
       <c r="B59" t="str">
-        <v>Defeat 15 Pokemon in Ruins of Conflict Special Encounter</v>
+        <v>Defeat 10 Pokemon in Ruins of Conflict Special Encounter</v>
       </c>
       <c r="C59" t="str">
         <v>Unlocks Memorial Hill Main</v>
@@ -5846,7 +5846,7 @@
         <v>Extra Challenge C-5</v>
       </c>
       <c r="B60" t="str">
-        <v>Defeat 15 Pokemon in Memorial Hill Main</v>
+        <v>Defeat 10 Pokemon in Memorial Hill Main</v>
       </c>
       <c r="C60" t="str">
         <v>Unlocks Sacred Shrine Main Area</v>
@@ -5868,7 +5868,7 @@
         <v>Extra Challenge D-2</v>
       </c>
       <c r="B62" t="str">
-        <v>Defeat 15 Pokemon in Poni Grove Main Area</v>
+        <v>Defeat 5 specific Normal type Pokemon</v>
       </c>
       <c r="C62" t="str">
         <v>Unlocks Poni Plains Center</v>
@@ -5879,7 +5879,7 @@
         <v>Extra Challenge D-3</v>
       </c>
       <c r="B63" t="str">
-        <v>Defeat 15 Pokemon in Poni Plains Center</v>
+        <v>Defeat 10 Pokemon in Poni Plains Center</v>
       </c>
       <c r="C63" t="str">
         <v>Unlocks Resolution Cave Main Area</v>
@@ -5890,7 +5890,7 @@
         <v>Extra Challenge D-4</v>
       </c>
       <c r="B64" t="str">
-        <v>Defeat 15 Pokemon in Resolution Cave Main Area</v>
+        <v>Defeat 10 Pokemon in Resolution Cave Main Area</v>
       </c>
       <c r="C64" t="str">
         <v>Unlocks Ruins of Hope Special Encounter</v>
@@ -5901,7 +5901,7 @@
         <v>Extra Challenge D-5</v>
       </c>
       <c r="B65" t="str">
-        <v>Defeat 15 Pokemon in Ruins of Hope Special Encounter</v>
+        <v>Defeat 10 Pokemon in Ruins of Hope Special Encounter</v>
       </c>
       <c r="C65" t="str">
         <v>Unlocks The Interdimensional Rift Main Area</v>
@@ -5923,7 +5923,7 @@
         <v>Extra Challenge E-2</v>
       </c>
       <c r="B67" t="str">
-        <v>Defeat 15 Pokemon in Route 15 Main Area</v>
+        <v>Defeat 10 Pokemon in Route 15 Main Area</v>
       </c>
       <c r="C67" t="str">
         <v>Unlocks Aether Paradise Labs</v>
@@ -5934,7 +5934,7 @@
         <v>Extra Challenge E-3</v>
       </c>
       <c r="B68" t="str">
-        <v>Defeat 15 Pokemon in Aether Paradise Labs</v>
+        <v>Defeat 10 Pokemon in Aether Paradise Labs</v>
       </c>
       <c r="C68" t="str">
         <v>Unlocks Aether Paradise Secret Lab</v>
@@ -5945,7 +5945,7 @@
         <v>Extra Challenge E-4</v>
       </c>
       <c r="B69" t="str">
-        <v>Defeat 15 Pokemon in Aether Paradise Secret Lab</v>
+        <v>Catch 10 Pokemon in Aether Paradise Secret Lab</v>
       </c>
       <c r="C69" t="str">
         <v>Unlocks Lake of the Sunne Main Area</v>
@@ -5956,7 +5956,7 @@
         <v>Extra Challenge E-5</v>
       </c>
       <c r="B70" t="str">
-        <v>Defeat 15 Pokemon in Lake of the Sunne Main Area</v>
+        <v>Catch 2 specific Pokemon species in Lake of the Sunne Main Area</v>
       </c>
       <c r="C70" t="str">
         <v>Unlocks Obsidian Sphere Main Area</v>

--- a/Alola_Paths_and_Challenges.xlsx
+++ b/Alola_Paths_and_Challenges.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F239"/>
+  <dimension ref="A1:F212"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -595,7 +595,7 @@
         <v>Inkay</v>
       </c>
       <c r="E10" t="str">
-        <v>3-8</v>
+        <v>4-9</v>
       </c>
       <c r="F10" t="str">
         <v>20.00%</v>
@@ -615,7 +615,7 @@
         <v>Slowpoke</v>
       </c>
       <c r="E11" t="str">
-        <v>3-8</v>
+        <v>4-9</v>
       </c>
       <c r="F11" t="str">
         <v>20.00%</v>
@@ -635,7 +635,7 @@
         <v>Alolan Meowth</v>
       </c>
       <c r="E12" t="str">
-        <v>3-8</v>
+        <v>4-9</v>
       </c>
       <c r="F12" t="str">
         <v>20.00%</v>
@@ -655,7 +655,7 @@
         <v>Tentacool</v>
       </c>
       <c r="E13" t="str">
-        <v>3-8</v>
+        <v>4-9</v>
       </c>
       <c r="F13" t="str">
         <v>20.00%</v>
@@ -675,7 +675,7 @@
         <v>Finneon</v>
       </c>
       <c r="E14" t="str">
-        <v>3-8</v>
+        <v>4-9</v>
       </c>
       <c r="F14" t="str">
         <v>20.00%</v>
@@ -686,19 +686,19 @@
         <v>3</v>
       </c>
       <c r="B15" t="str">
-        <v>Hau'oli City</v>
+        <v>Route 2</v>
       </c>
       <c r="C15" t="str">
-        <v>Shopping District</v>
+        <v>North</v>
       </c>
       <c r="D15" t="str">
-        <v>Furfrou</v>
+        <v>Drowzee</v>
       </c>
       <c r="E15" t="str">
-        <v>5-10</v>
+        <v>7-12</v>
       </c>
       <c r="F15" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="16">
@@ -706,19 +706,19 @@
         <v>3</v>
       </c>
       <c r="B16" t="str">
-        <v>Hau'oli City</v>
+        <v>Route 2</v>
       </c>
       <c r="C16" t="str">
-        <v>Shopping District</v>
+        <v>North</v>
       </c>
       <c r="D16" t="str">
-        <v>Hypno</v>
+        <v>Makuhita</v>
       </c>
       <c r="E16" t="str">
-        <v>5-10</v>
+        <v>7-12</v>
       </c>
       <c r="F16" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="17">
@@ -726,19 +726,19 @@
         <v>3</v>
       </c>
       <c r="B17" t="str">
-        <v>Hau'oli City</v>
+        <v>Route 2</v>
       </c>
       <c r="C17" t="str">
-        <v>Shopping District</v>
+        <v>North</v>
       </c>
       <c r="D17" t="str">
-        <v>Abra</v>
+        <v>Spearow</v>
       </c>
       <c r="E17" t="str">
-        <v>5-10</v>
+        <v>7-12</v>
       </c>
       <c r="F17" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="18">
@@ -746,19 +746,19 @@
         <v>3</v>
       </c>
       <c r="B18" t="str">
-        <v>Hau'oli City</v>
+        <v>Route 2</v>
       </c>
       <c r="C18" t="str">
-        <v>Shopping District</v>
+        <v>North</v>
       </c>
       <c r="D18" t="str">
-        <v>Mime Jr.</v>
+        <v>Ekans</v>
       </c>
       <c r="E18" t="str">
-        <v>5-10</v>
+        <v>7-12</v>
       </c>
       <c r="F18" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="19">
@@ -766,24 +766,24 @@
         <v>3</v>
       </c>
       <c r="B19" t="str">
-        <v>Hau'oli City</v>
+        <v>Route 2</v>
       </c>
       <c r="C19" t="str">
-        <v>Shopping District</v>
+        <v>North</v>
       </c>
       <c r="D19" t="str">
-        <v>Bewear</v>
+        <v>Growlithe</v>
       </c>
       <c r="E19" t="str">
-        <v>5-10</v>
+        <v>7-12</v>
       </c>
       <c r="F19" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B20" t="str">
         <v>Route 2</v>
@@ -792,10 +792,10 @@
         <v>North</v>
       </c>
       <c r="D20" t="str">
-        <v>Drowzee</v>
+        <v>Smeargle</v>
       </c>
       <c r="E20" t="str">
-        <v>6-11</v>
+        <v>7-12</v>
       </c>
       <c r="F20" t="str">
         <v>16.67%</v>
@@ -806,119 +806,119 @@
         <v>4</v>
       </c>
       <c r="B21" t="str">
-        <v>Route 2</v>
+        <v>Captain Ilima</v>
       </c>
       <c r="C21" t="str">
-        <v>North</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D21" t="str">
-        <v>Makuhita</v>
+        <v>Boss</v>
       </c>
       <c r="E21" t="str">
-        <v>6-11</v>
+        <v>8-13</v>
       </c>
       <c r="F21" t="str">
-        <v>16.67%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B22" t="str">
-        <v>Route 2</v>
+        <v>Hau'oli Cemetery</v>
       </c>
       <c r="C22" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D22" t="str">
-        <v>Spearow</v>
+        <v>Gastly</v>
       </c>
       <c r="E22" t="str">
-        <v>6-11</v>
+        <v>10-15</v>
       </c>
       <c r="F22" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B23" t="str">
-        <v>Route 2</v>
+        <v>Hau'oli Cemetery</v>
       </c>
       <c r="C23" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D23" t="str">
-        <v>Ekans</v>
+        <v>Drifloon</v>
       </c>
       <c r="E23" t="str">
-        <v>6-11</v>
+        <v>10-15</v>
       </c>
       <c r="F23" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B24" t="str">
-        <v>Route 2</v>
+        <v>Hau'oli Cemetery</v>
       </c>
       <c r="C24" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D24" t="str">
-        <v>Growlithe</v>
+        <v>Murkrow</v>
       </c>
       <c r="E24" t="str">
-        <v>6-11</v>
+        <v>10-15</v>
       </c>
       <c r="F24" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B25" t="str">
-        <v>Route 2</v>
+        <v>Hau'oli Cemetery</v>
       </c>
       <c r="C25" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D25" t="str">
-        <v>Smeargle</v>
+        <v>Misdreavus</v>
       </c>
       <c r="E25" t="str">
-        <v>6-11</v>
+        <v>10-15</v>
       </c>
       <c r="F25" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B26" t="str">
-        <v>Captain Ilima</v>
+        <v>Ten Carat Hill</v>
       </c>
       <c r="C26" t="str">
-        <v>Boss Battle</v>
+        <v>Farthest Hollow</v>
       </c>
       <c r="D26" t="str">
-        <v>Boss</v>
+        <v>Roggenrola</v>
       </c>
       <c r="E26" t="str">
-        <v>8-13</v>
+        <v>14-19</v>
       </c>
       <c r="F26" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="27">
@@ -926,19 +926,19 @@
         <v>6</v>
       </c>
       <c r="B27" t="str">
-        <v>Hau'oli Cemetery</v>
+        <v>Ten Carat Hill</v>
       </c>
       <c r="C27" t="str">
-        <v>Main Area</v>
+        <v>Farthest Hollow</v>
       </c>
       <c r="D27" t="str">
-        <v>Gastly</v>
+        <v>Carbink</v>
       </c>
       <c r="E27" t="str">
-        <v>9-14</v>
+        <v>14-19</v>
       </c>
       <c r="F27" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="28">
@@ -946,19 +946,19 @@
         <v>6</v>
       </c>
       <c r="B28" t="str">
-        <v>Hau'oli Cemetery</v>
+        <v>Ten Carat Hill</v>
       </c>
       <c r="C28" t="str">
-        <v>Main Area</v>
+        <v>Farthest Hollow</v>
       </c>
       <c r="D28" t="str">
-        <v>Drifloon</v>
+        <v>Spinda</v>
       </c>
       <c r="E28" t="str">
-        <v>9-14</v>
+        <v>14-19</v>
       </c>
       <c r="F28" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="29">
@@ -966,19 +966,19 @@
         <v>6</v>
       </c>
       <c r="B29" t="str">
-        <v>Hau'oli Cemetery</v>
+        <v>Ten Carat Hill</v>
       </c>
       <c r="C29" t="str">
-        <v>Main Area</v>
+        <v>Farthest Hollow</v>
       </c>
       <c r="D29" t="str">
-        <v>Murkrow</v>
+        <v>Mawile</v>
       </c>
       <c r="E29" t="str">
-        <v>9-14</v>
+        <v>14-19</v>
       </c>
       <c r="F29" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="30">
@@ -986,19 +986,19 @@
         <v>6</v>
       </c>
       <c r="B30" t="str">
-        <v>Hau'oli Cemetery</v>
+        <v>Ten Carat Hill</v>
       </c>
       <c r="C30" t="str">
-        <v>Main Area</v>
+        <v>Farthest Hollow</v>
       </c>
       <c r="D30" t="str">
-        <v>Misdreavus</v>
+        <v>Lycanroc</v>
       </c>
       <c r="E30" t="str">
-        <v>9-14</v>
+        <v>14-19</v>
       </c>
       <c r="F30" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="31">
@@ -1006,19 +1006,19 @@
         <v>7</v>
       </c>
       <c r="B31" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Seaward Cave</v>
       </c>
       <c r="C31" t="str">
-        <v>Farthest Hollow</v>
+        <v/>
       </c>
       <c r="D31" t="str">
-        <v>Roggenrola</v>
+        <v>Barboach</v>
       </c>
       <c r="E31" t="str">
-        <v>14-19</v>
+        <v>16-21</v>
       </c>
       <c r="F31" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="32">
@@ -1026,19 +1026,19 @@
         <v>7</v>
       </c>
       <c r="B32" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Seaward Cave</v>
       </c>
       <c r="C32" t="str">
-        <v>Farthest Hollow</v>
+        <v/>
       </c>
       <c r="D32" t="str">
-        <v>Carbink</v>
+        <v>Smoochum</v>
       </c>
       <c r="E32" t="str">
-        <v>14-19</v>
+        <v>16-21</v>
       </c>
       <c r="F32" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="33">
@@ -1046,136 +1046,136 @@
         <v>7</v>
       </c>
       <c r="B33" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Seaward Cave</v>
       </c>
       <c r="C33" t="str">
-        <v>Farthest Hollow</v>
+        <v/>
       </c>
       <c r="D33" t="str">
-        <v>Spinda</v>
+        <v>Seel</v>
       </c>
       <c r="E33" t="str">
-        <v>14-19</v>
+        <v>16-21</v>
       </c>
       <c r="F33" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B34" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Kahuna Hala</v>
       </c>
       <c r="C34" t="str">
-        <v>Farthest Hollow</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D34" t="str">
-        <v>Mawile</v>
+        <v>Boss</v>
       </c>
       <c r="E34" t="str">
-        <v>14-19</v>
+        <v>17-22</v>
       </c>
       <c r="F34" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B35" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C35" t="str">
-        <v>Farthest Hollow</v>
+        <v/>
       </c>
       <c r="D35" t="str">
-        <v>Lycanroc</v>
+        <v>Eevee</v>
       </c>
       <c r="E35" t="str">
-        <v>14-19</v>
+        <v>20-25</v>
       </c>
       <c r="F35" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B36" t="str">
-        <v>Seaward Cave</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C36" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D36" t="str">
-        <v>Barboach</v>
+        <v>Mareep</v>
       </c>
       <c r="E36" t="str">
-        <v>15-20</v>
+        <v>20-25</v>
       </c>
       <c r="F36" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B37" t="str">
-        <v>Seaward Cave</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C37" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D37" t="str">
-        <v>Smoochum</v>
+        <v>Tauros</v>
       </c>
       <c r="E37" t="str">
-        <v>15-20</v>
+        <v>20-25</v>
       </c>
       <c r="F37" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B38" t="str">
-        <v>Seaward Cave</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C38" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D38" t="str">
-        <v>Seel</v>
+        <v>Miltank</v>
       </c>
       <c r="E38" t="str">
-        <v>15-20</v>
+        <v>20-25</v>
       </c>
       <c r="F38" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B39" t="str">
-        <v>Kahuna Hala</v>
+        <v>Daycare</v>
       </c>
       <c r="C39" t="str">
-        <v>Boss Battle</v>
+        <v>NPC</v>
       </c>
       <c r="D39" t="str">
-        <v>Boss</v>
+        <v>NPC</v>
       </c>
       <c r="E39" t="str">
-        <v>17-22</v>
+        <v>-</v>
       </c>
       <c r="F39" t="str">
         <v>-</v>
@@ -1183,179 +1183,179 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B40" t="str">
-        <v>Heahea Beach</v>
+        <v>Route 5</v>
       </c>
       <c r="C40" t="str">
-        <v>Main Area Part 1</v>
+        <v/>
       </c>
       <c r="D40" t="str">
-        <v>Vikavolt</v>
+        <v>Noibat</v>
       </c>
       <c r="E40" t="str">
-        <v>18-23</v>
+        <v>23-28</v>
       </c>
       <c r="F40" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B41" t="str">
-        <v>Heahea Beach</v>
+        <v>Route 5</v>
       </c>
       <c r="C41" t="str">
-        <v>Main Area Part 1</v>
+        <v/>
       </c>
       <c r="D41" t="str">
-        <v>Ribombee</v>
+        <v>Fomantis</v>
       </c>
       <c r="E41" t="str">
-        <v>18-23</v>
+        <v>23-28</v>
       </c>
       <c r="F41" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B42" t="str">
-        <v>Heahea Beach</v>
+        <v>Route 5</v>
       </c>
       <c r="C42" t="str">
-        <v>Main Area Part 1</v>
+        <v/>
       </c>
       <c r="D42" t="str">
-        <v>Araquanid</v>
+        <v>Bounsweet</v>
       </c>
       <c r="E42" t="str">
-        <v>18-23</v>
+        <v>23-28</v>
       </c>
       <c r="F42" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B43" t="str">
-        <v>Heahea Beach</v>
+        <v>Captain Lana</v>
       </c>
       <c r="C43" t="str">
-        <v>Main Area Part 1</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D43" t="str">
-        <v>Lurantis</v>
+        <v>Boss</v>
       </c>
       <c r="E43" t="str">
-        <v>18-23</v>
+        <v>26-31</v>
       </c>
       <c r="F43" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B44" t="str">
-        <v>Heahea Beach</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C44" t="str">
-        <v>Main Area Part 1</v>
+        <v/>
       </c>
       <c r="D44" t="str">
-        <v>Salazzle</v>
+        <v>Cubone</v>
       </c>
       <c r="E44" t="str">
-        <v>18-23</v>
+        <v>28-33</v>
       </c>
       <c r="F44" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B45" t="str">
-        <v>Heahea Beach</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C45" t="str">
-        <v>Main Area Part 2</v>
+        <v/>
       </c>
       <c r="D45" t="str">
-        <v>Alolan Marowak</v>
+        <v>Kangaskhan</v>
       </c>
       <c r="E45" t="str">
-        <v>18-23</v>
+        <v>28-33</v>
       </c>
       <c r="F45" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B46" t="str">
-        <v>Heahea Beach</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C46" t="str">
-        <v>Main Area Part 2</v>
+        <v/>
       </c>
       <c r="D46" t="str">
-        <v>Kommo-o</v>
+        <v>Magby</v>
       </c>
       <c r="E46" t="str">
-        <v>18-23</v>
+        <v>28-33</v>
       </c>
       <c r="F46" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B47" t="str">
-        <v>Heahea Beach</v>
+        <v>Captain Kiawe</v>
       </c>
       <c r="C47" t="str">
-        <v>Main Area Part 2</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D47" t="str">
-        <v>Mimikyu</v>
+        <v>Boss</v>
       </c>
       <c r="E47" t="str">
-        <v>18-23</v>
+        <v>29-34</v>
       </c>
       <c r="F47" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B48" t="str">
-        <v>Heahea Beach</v>
+        <v>Route 7</v>
       </c>
       <c r="C48" t="str">
-        <v>Main Area Part 2</v>
+        <v/>
       </c>
       <c r="D48" t="str">
-        <v>Poliwhirl</v>
+        <v>Staryu</v>
       </c>
       <c r="E48" t="str">
-        <v>18-23</v>
+        <v>31-36</v>
       </c>
       <c r="F48" t="str">
         <v>20.00%</v>
@@ -1363,19 +1363,19 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B49" t="str">
-        <v>Heahea Beach</v>
+        <v>Route 7</v>
       </c>
       <c r="C49" t="str">
-        <v>Main Area Part 2</v>
+        <v/>
       </c>
       <c r="D49" t="str">
-        <v>Ditto</v>
+        <v>Pyukumuku</v>
       </c>
       <c r="E49" t="str">
-        <v>18-23</v>
+        <v>31-36</v>
       </c>
       <c r="F49" t="str">
         <v>20.00%</v>
@@ -1383,179 +1383,179 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B50" t="str">
-        <v>Paniola Ranch</v>
+        <v>Route 7</v>
       </c>
       <c r="C50" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D50" t="str">
-        <v>Eevee</v>
+        <v>Corsola</v>
       </c>
       <c r="E50" t="str">
-        <v>20-25</v>
+        <v>31-36</v>
       </c>
       <c r="F50" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B51" t="str">
-        <v>Paniola Ranch</v>
+        <v>Route 7</v>
       </c>
       <c r="C51" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D51" t="str">
-        <v>Mareep</v>
+        <v>Mareanie</v>
       </c>
       <c r="E51" t="str">
-        <v>20-25</v>
+        <v>31-36</v>
       </c>
       <c r="F51" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B52" t="str">
-        <v>Paniola Ranch</v>
+        <v>Route 7</v>
       </c>
       <c r="C52" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D52" t="str">
-        <v>Tauros</v>
+        <v>Bruxish</v>
       </c>
       <c r="E52" t="str">
-        <v>20-25</v>
+        <v>31-36</v>
       </c>
       <c r="F52" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B53" t="str">
-        <v>Paniola Ranch</v>
+        <v>Route 8</v>
       </c>
       <c r="C53" t="str">
-        <v>Main Area</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D53" t="str">
-        <v>Miltank</v>
+        <v>Omanyte</v>
       </c>
       <c r="E53" t="str">
-        <v>20-25</v>
+        <v>32-37</v>
       </c>
       <c r="F53" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B54" t="str">
-        <v>Daycare</v>
+        <v>Route 8</v>
       </c>
       <c r="C54" t="str">
-        <v>NPC</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D54" t="str">
-        <v>NPC</v>
+        <v>Kabuto</v>
       </c>
       <c r="E54" t="str">
-        <v>-</v>
+        <v>32-37</v>
       </c>
       <c r="F54" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B55" t="str">
-        <v>Route 5</v>
+        <v>Route 8</v>
       </c>
       <c r="C55" t="str">
-        <v>Main Area</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D55" t="str">
-        <v>Noibat</v>
+        <v>Lileep</v>
       </c>
       <c r="E55" t="str">
-        <v>23-28</v>
+        <v>32-37</v>
       </c>
       <c r="F55" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B56" t="str">
-        <v>Route 5</v>
+        <v>Route 8</v>
       </c>
       <c r="C56" t="str">
-        <v>Main Area</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D56" t="str">
-        <v>Fomantis</v>
+        <v>Anorith</v>
       </c>
       <c r="E56" t="str">
-        <v>23-28</v>
+        <v>32-37</v>
       </c>
       <c r="F56" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B57" t="str">
-        <v>Route 5</v>
+        <v>Route 8</v>
       </c>
       <c r="C57" t="str">
-        <v>Main Area</v>
+        <v>Fossil Restoration Center Part 1</v>
       </c>
       <c r="D57" t="str">
-        <v>Bounsweet</v>
+        <v>Cranidos</v>
       </c>
       <c r="E57" t="str">
-        <v>23-28</v>
+        <v>32-37</v>
       </c>
       <c r="F57" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B58" t="str">
-        <v>Brooklet Hill</v>
+        <v>Route 8</v>
       </c>
       <c r="C58" t="str">
-        <v>South</v>
+        <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D58" t="str">
-        <v>Wingull</v>
+        <v>Shieldon</v>
       </c>
       <c r="E58" t="str">
-        <v>24-29</v>
+        <v>32-37</v>
       </c>
       <c r="F58" t="str">
         <v>20.00%</v>
@@ -1563,19 +1563,19 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B59" t="str">
-        <v>Brooklet Hill</v>
+        <v>Route 8</v>
       </c>
       <c r="C59" t="str">
-        <v>South</v>
+        <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D59" t="str">
-        <v>Lillipup</v>
+        <v>Archen</v>
       </c>
       <c r="E59" t="str">
-        <v>24-29</v>
+        <v>32-37</v>
       </c>
       <c r="F59" t="str">
         <v>20.00%</v>
@@ -1583,19 +1583,19 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B60" t="str">
-        <v>Brooklet Hill</v>
+        <v>Route 8</v>
       </c>
       <c r="C60" t="str">
-        <v>South</v>
+        <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D60" t="str">
-        <v>Paras</v>
+        <v>Tirtouga</v>
       </c>
       <c r="E60" t="str">
-        <v>24-29</v>
+        <v>32-37</v>
       </c>
       <c r="F60" t="str">
         <v>20.00%</v>
@@ -1603,19 +1603,19 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B61" t="str">
-        <v>Brooklet Hill</v>
+        <v>Route 8</v>
       </c>
       <c r="C61" t="str">
-        <v>South</v>
+        <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D61" t="str">
-        <v>Goldeen</v>
+        <v>Tyrunt</v>
       </c>
       <c r="E61" t="str">
-        <v>24-29</v>
+        <v>32-37</v>
       </c>
       <c r="F61" t="str">
         <v>20.00%</v>
@@ -1623,19 +1623,19 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B62" t="str">
-        <v>Brooklet Hill</v>
+        <v>Route 8</v>
       </c>
       <c r="C62" t="str">
-        <v>South</v>
+        <v>Fossil Restoration Center Part 2</v>
       </c>
       <c r="D62" t="str">
-        <v>Feebas</v>
+        <v>Amaura</v>
       </c>
       <c r="E62" t="str">
-        <v>24-29</v>
+        <v>32-37</v>
       </c>
       <c r="F62" t="str">
         <v>20.00%</v>
@@ -1643,82 +1643,82 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B63" t="str">
-        <v>Captain Lana</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C63" t="str">
-        <v>Boss Battle</v>
+        <v>North</v>
       </c>
       <c r="D63" t="str">
-        <v>Boss</v>
+        <v>Trumbeak</v>
       </c>
       <c r="E63" t="str">
-        <v>26-31</v>
+        <v>34-39</v>
       </c>
       <c r="F63" t="str">
-        <v>-</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B64" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C64" t="str">
-        <v>Main Area</v>
+        <v>North</v>
       </c>
       <c r="D64" t="str">
-        <v>Cubone</v>
+        <v>Steenee</v>
       </c>
       <c r="E64" t="str">
-        <v>27-32</v>
+        <v>34-39</v>
       </c>
       <c r="F64" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B65" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C65" t="str">
-        <v>Main Area</v>
+        <v>North</v>
       </c>
       <c r="D65" t="str">
-        <v>Kangaskhan</v>
+        <v>Comfey</v>
       </c>
       <c r="E65" t="str">
-        <v>27-32</v>
+        <v>34-39</v>
       </c>
       <c r="F65" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B66" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C66" t="str">
-        <v>Main Area</v>
+        <v>North</v>
       </c>
       <c r="D66" t="str">
-        <v>Magby</v>
+        <v>Hoothoot</v>
       </c>
       <c r="E66" t="str">
-        <v>27-32</v>
+        <v>34-39</v>
       </c>
       <c r="F66" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="67">
@@ -1726,39 +1726,39 @@
         <v>18</v>
       </c>
       <c r="B67" t="str">
-        <v>Captain Kiawe</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C67" t="str">
-        <v>Boss Battle</v>
+        <v>North</v>
       </c>
       <c r="D67" t="str">
-        <v>Boss</v>
+        <v>Oranguru</v>
       </c>
       <c r="E67" t="str">
-        <v>29-34</v>
+        <v>34-39</v>
       </c>
       <c r="F67" t="str">
-        <v>-</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B68" t="str">
-        <v>Route 7</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C68" t="str">
-        <v>Main Area</v>
+        <v>North</v>
       </c>
       <c r="D68" t="str">
-        <v>Staryu</v>
+        <v>Bounsweet</v>
       </c>
       <c r="E68" t="str">
-        <v>30-35</v>
+        <v>34-39</v>
       </c>
       <c r="F68" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="69">
@@ -1766,16 +1766,16 @@
         <v>19</v>
       </c>
       <c r="B69" t="str">
-        <v>Route 7</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C69" t="str">
-        <v>Main Area</v>
+        <v>East Cave</v>
       </c>
       <c r="D69" t="str">
-        <v>Pyukumuku</v>
+        <v>Golbat</v>
       </c>
       <c r="E69" t="str">
-        <v>30-35</v>
+        <v>35-40</v>
       </c>
       <c r="F69" t="str">
         <v>20.00%</v>
@@ -1786,16 +1786,16 @@
         <v>19</v>
       </c>
       <c r="B70" t="str">
-        <v>Route 7</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C70" t="str">
-        <v>Main Area</v>
+        <v>East Cave</v>
       </c>
       <c r="D70" t="str">
-        <v>Corsola</v>
+        <v>Salandit</v>
       </c>
       <c r="E70" t="str">
-        <v>30-35</v>
+        <v>35-40</v>
       </c>
       <c r="F70" t="str">
         <v>20.00%</v>
@@ -1806,16 +1806,16 @@
         <v>19</v>
       </c>
       <c r="B71" t="str">
-        <v>Route 7</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C71" t="str">
-        <v>Main Area</v>
+        <v>East Cave</v>
       </c>
       <c r="D71" t="str">
-        <v>Mareanie</v>
+        <v>Larvesta</v>
       </c>
       <c r="E71" t="str">
-        <v>30-35</v>
+        <v>35-40</v>
       </c>
       <c r="F71" t="str">
         <v>20.00%</v>
@@ -1826,16 +1826,16 @@
         <v>19</v>
       </c>
       <c r="B72" t="str">
-        <v>Route 7</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C72" t="str">
-        <v>Main Area</v>
+        <v>East Cave</v>
       </c>
       <c r="D72" t="str">
-        <v>Bruxish</v>
+        <v>Oranguru</v>
       </c>
       <c r="E72" t="str">
-        <v>30-35</v>
+        <v>35-40</v>
       </c>
       <c r="F72" t="str">
         <v>20.00%</v>
@@ -1843,19 +1843,19 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B73" t="str">
-        <v>Route 8</v>
+        <v>Lush Jungle</v>
       </c>
       <c r="C73" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>East Cave</v>
       </c>
       <c r="D73" t="str">
-        <v>Omanyte</v>
+        <v>Passimian</v>
       </c>
       <c r="E73" t="str">
-        <v>32-37</v>
+        <v>35-40</v>
       </c>
       <c r="F73" t="str">
         <v>20.00%</v>
@@ -1866,79 +1866,79 @@
         <v>20</v>
       </c>
       <c r="B74" t="str">
-        <v>Route 8</v>
+        <v>Captain Mallow</v>
       </c>
       <c r="C74" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D74" t="str">
-        <v>Kabuto</v>
+        <v>Boss</v>
       </c>
       <c r="E74" t="str">
-        <v>32-37</v>
+        <v>37-42</v>
       </c>
       <c r="F74" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B75" t="str">
-        <v>Route 8</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C75" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v/>
       </c>
       <c r="D75" t="str">
-        <v>Lileep</v>
+        <v>Zubat</v>
       </c>
       <c r="E75" t="str">
-        <v>32-37</v>
+        <v>38-43</v>
       </c>
       <c r="F75" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B76" t="str">
-        <v>Route 8</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C76" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v/>
       </c>
       <c r="D76" t="str">
-        <v>Anorith</v>
+        <v>Alolan Diglett</v>
       </c>
       <c r="E76" t="str">
-        <v>32-37</v>
+        <v>38-43</v>
       </c>
       <c r="F76" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B77" t="str">
-        <v>Route 8</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C77" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v/>
       </c>
       <c r="D77" t="str">
-        <v>Cranidos</v>
+        <v>Kecleon</v>
       </c>
       <c r="E77" t="str">
-        <v>32-37</v>
+        <v>38-43</v>
       </c>
       <c r="F77" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="78">
@@ -1946,99 +1946,99 @@
         <v>21</v>
       </c>
       <c r="B78" t="str">
-        <v>Route 8</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C78" t="str">
-        <v>Fossil Restoration Center Part 2</v>
+        <v/>
       </c>
       <c r="D78" t="str">
-        <v>Shieldon</v>
+        <v>Larvitar</v>
       </c>
       <c r="E78" t="str">
-        <v>32-37</v>
+        <v>38-43</v>
       </c>
       <c r="F78" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B79" t="str">
-        <v>Route 8</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C79" t="str">
-        <v>Fossil Restoration Center Part 2</v>
+        <v/>
       </c>
       <c r="D79" t="str">
-        <v>Archen</v>
+        <v>Gumshoos</v>
       </c>
       <c r="E79" t="str">
-        <v>32-37</v>
+        <v>43-48</v>
       </c>
       <c r="F79" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B80" t="str">
-        <v>Route 8</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C80" t="str">
-        <v>Fossil Restoration Center Part 2</v>
+        <v/>
       </c>
       <c r="D80" t="str">
-        <v>Tirtouga</v>
+        <v>Wingull</v>
       </c>
       <c r="E80" t="str">
-        <v>32-37</v>
+        <v>43-48</v>
       </c>
       <c r="F80" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B81" t="str">
-        <v>Route 8</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C81" t="str">
-        <v>Fossil Restoration Center Part 2</v>
+        <v/>
       </c>
       <c r="D81" t="str">
-        <v>Tyrunt</v>
+        <v>Magikarp</v>
       </c>
       <c r="E81" t="str">
-        <v>32-37</v>
+        <v>43-48</v>
       </c>
       <c r="F81" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B82" t="str">
-        <v>Route 8</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C82" t="str">
-        <v>Fossil Restoration Center Part 2</v>
+        <v/>
       </c>
       <c r="D82" t="str">
-        <v>Amaura</v>
+        <v>Stufful</v>
       </c>
       <c r="E82" t="str">
-        <v>32-37</v>
+        <v>43-48</v>
       </c>
       <c r="F82" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="83">
@@ -2046,19 +2046,19 @@
         <v>22</v>
       </c>
       <c r="B83" t="str">
-        <v>Lush Jungle</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C83" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D83" t="str">
-        <v>Trumbeak</v>
+        <v>Chinchou</v>
       </c>
       <c r="E83" t="str">
-        <v>33-38</v>
+        <v>43-48</v>
       </c>
       <c r="F83" t="str">
-        <v>16.67%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="84">
@@ -2066,19 +2066,19 @@
         <v>22</v>
       </c>
       <c r="B84" t="str">
-        <v>Lush Jungle</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C84" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D84" t="str">
-        <v>Steenee</v>
+        <v>Alolan Raticate</v>
       </c>
       <c r="E84" t="str">
-        <v>33-38</v>
+        <v>43-48</v>
       </c>
       <c r="F84" t="str">
-        <v>16.67%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="85">
@@ -2086,19 +2086,19 @@
         <v>22</v>
       </c>
       <c r="B85" t="str">
-        <v>Lush Jungle</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C85" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D85" t="str">
-        <v>Comfey</v>
+        <v>Natu</v>
       </c>
       <c r="E85" t="str">
-        <v>33-38</v>
+        <v>43-48</v>
       </c>
       <c r="F85" t="str">
-        <v>16.67%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="86">
@@ -2106,76 +2106,76 @@
         <v>22</v>
       </c>
       <c r="B86" t="str">
-        <v>Lush Jungle</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C86" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D86" t="str">
-        <v>Hoothoot</v>
+        <v>Nosepass</v>
       </c>
       <c r="E86" t="str">
-        <v>33-38</v>
+        <v>43-48</v>
       </c>
       <c r="F86" t="str">
-        <v>16.67%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B87" t="str">
-        <v>Lush Jungle</v>
+        <v>Kahuna Olivia</v>
       </c>
       <c r="C87" t="str">
-        <v>North</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D87" t="str">
-        <v>Oranguru</v>
+        <v>Boss</v>
       </c>
       <c r="E87" t="str">
-        <v>33-38</v>
+        <v>45-50</v>
       </c>
       <c r="F87" t="str">
-        <v>16.67%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="88">
       <c r="A88">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B88" t="str">
-        <v>Lush Jungle</v>
+        <v>Malie City</v>
       </c>
       <c r="C88" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D88" t="str">
-        <v>Bounsweet</v>
+        <v>Magnemite</v>
       </c>
       <c r="E88" t="str">
-        <v>33-38</v>
+        <v>48-53</v>
       </c>
       <c r="F88" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B89" t="str">
-        <v>Lush Jungle</v>
+        <v>Malie City</v>
       </c>
       <c r="C89" t="str">
-        <v>East Cave</v>
+        <v/>
       </c>
       <c r="D89" t="str">
-        <v>Golbat</v>
+        <v>Alolan Grimer</v>
       </c>
       <c r="E89" t="str">
-        <v>35-40</v>
+        <v>48-53</v>
       </c>
       <c r="F89" t="str">
         <v>20.00%</v>
@@ -2183,19 +2183,19 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B90" t="str">
-        <v>Lush Jungle</v>
+        <v>Malie City</v>
       </c>
       <c r="C90" t="str">
-        <v>East Cave</v>
+        <v/>
       </c>
       <c r="D90" t="str">
-        <v>Salandit</v>
+        <v>Trubbish</v>
       </c>
       <c r="E90" t="str">
-        <v>35-40</v>
+        <v>48-53</v>
       </c>
       <c r="F90" t="str">
         <v>20.00%</v>
@@ -2203,19 +2203,19 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B91" t="str">
-        <v>Lush Jungle</v>
+        <v>Malie City</v>
       </c>
       <c r="C91" t="str">
-        <v>East Cave</v>
+        <v/>
       </c>
       <c r="D91" t="str">
-        <v>Larvesta</v>
+        <v>Minccino</v>
       </c>
       <c r="E91" t="str">
-        <v>35-40</v>
+        <v>48-53</v>
       </c>
       <c r="F91" t="str">
         <v>20.00%</v>
@@ -2223,19 +2223,19 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B92" t="str">
-        <v>Lush Jungle</v>
+        <v>Malie City</v>
       </c>
       <c r="C92" t="str">
-        <v>East Cave</v>
+        <v/>
       </c>
       <c r="D92" t="str">
-        <v>Oranguru</v>
+        <v>Masquerain</v>
       </c>
       <c r="E92" t="str">
-        <v>35-40</v>
+        <v>48-53</v>
       </c>
       <c r="F92" t="str">
         <v>20.00%</v>
@@ -2243,42 +2243,42 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B93" t="str">
-        <v>Lush Jungle</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C93" t="str">
-        <v>East Cave</v>
+        <v>East</v>
       </c>
       <c r="D93" t="str">
-        <v>Passimian</v>
+        <v>Cleffa</v>
       </c>
       <c r="E93" t="str">
-        <v>35-40</v>
+        <v>52-57</v>
       </c>
       <c r="F93" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B94" t="str">
-        <v>Captain Mallow</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C94" t="str">
-        <v>Boss Battle</v>
+        <v>East</v>
       </c>
       <c r="D94" t="str">
-        <v>Boss</v>
+        <v>Elgyem</v>
       </c>
       <c r="E94" t="str">
-        <v>36-41</v>
+        <v>52-57</v>
       </c>
       <c r="F94" t="str">
-        <v>-</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="95">
@@ -2286,16 +2286,16 @@
         <v>25</v>
       </c>
       <c r="B95" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C95" t="str">
-        <v>Main Area</v>
+        <v>East</v>
       </c>
       <c r="D95" t="str">
-        <v>Zubat</v>
+        <v>Beldum</v>
       </c>
       <c r="E95" t="str">
-        <v>38-43</v>
+        <v>52-57</v>
       </c>
       <c r="F95" t="str">
         <v>25.00%</v>
@@ -2306,16 +2306,16 @@
         <v>25</v>
       </c>
       <c r="B96" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Mount Hokulani</v>
       </c>
       <c r="C96" t="str">
-        <v>Main Area</v>
+        <v>East</v>
       </c>
       <c r="D96" t="str">
-        <v>Alolan Diglett</v>
+        <v>Minior</v>
       </c>
       <c r="E96" t="str">
-        <v>38-43</v>
+        <v>52-57</v>
       </c>
       <c r="F96" t="str">
         <v>25.00%</v>
@@ -2323,222 +2323,222 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B97" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Captain Sophocles</v>
       </c>
       <c r="C97" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D97" t="str">
-        <v>Kecleon</v>
+        <v>Boss</v>
       </c>
       <c r="E97" t="str">
-        <v>38-43</v>
+        <v>54-59</v>
       </c>
       <c r="F97" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B98" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C98" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D98" t="str">
-        <v>Larvitar</v>
+        <v>Alolan Dugtrio</v>
       </c>
       <c r="E98" t="str">
-        <v>38-43</v>
+        <v>58-63</v>
       </c>
       <c r="F98" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B99" t="str">
-        <v>Akala Outskirts</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C99" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D99" t="str">
-        <v>Gumshoos</v>
+        <v>Sandile</v>
       </c>
       <c r="E99" t="str">
-        <v>42-47</v>
+        <v>58-63</v>
       </c>
       <c r="F99" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="100">
       <c r="A100">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B100" t="str">
-        <v>Akala Outskirts</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C100" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D100" t="str">
-        <v>Wingull</v>
+        <v>Krokorok</v>
       </c>
       <c r="E100" t="str">
-        <v>42-47</v>
+        <v>58-63</v>
       </c>
       <c r="F100" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="101">
       <c r="A101">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B101" t="str">
-        <v>Akala Outskirts</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C101" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D101" t="str">
-        <v>Magikarp</v>
+        <v>Staryu</v>
       </c>
       <c r="E101" t="str">
-        <v>42-47</v>
+        <v>58-63</v>
       </c>
       <c r="F101" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="102">
       <c r="A102">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B102" t="str">
-        <v>Akala Outskirts</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C102" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D102" t="str">
-        <v>Stufful</v>
+        <v>Sandygast</v>
       </c>
       <c r="E102" t="str">
-        <v>42-47</v>
+        <v>58-63</v>
       </c>
       <c r="F102" t="str">
-        <v>12.50%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="103">
       <c r="A103">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B103" t="str">
-        <v>Akala Outskirts</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C103" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D103" t="str">
-        <v>Chinchou</v>
+        <v>Graveler</v>
       </c>
       <c r="E103" t="str">
-        <v>42-47</v>
+        <v>60-65</v>
       </c>
       <c r="F103" t="str">
-        <v>12.50%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="104">
       <c r="A104">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B104" t="str">
-        <v>Akala Outskirts</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C104" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D104" t="str">
-        <v>Alolan Raticate</v>
+        <v>Bruxish</v>
       </c>
       <c r="E104" t="str">
-        <v>42-47</v>
+        <v>60-65</v>
       </c>
       <c r="F104" t="str">
-        <v>12.50%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="105">
       <c r="A105">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B105" t="str">
-        <v>Akala Outskirts</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C105" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D105" t="str">
-        <v>Natu</v>
+        <v>Absol</v>
       </c>
       <c r="E105" t="str">
-        <v>42-47</v>
+        <v>60-65</v>
       </c>
       <c r="F105" t="str">
-        <v>12.50%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="106">
       <c r="A106">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B106" t="str">
-        <v>Akala Outskirts</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C106" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D106" t="str">
-        <v>Nosepass</v>
+        <v>Snorunt</v>
       </c>
       <c r="E106" t="str">
-        <v>42-47</v>
+        <v>60-65</v>
       </c>
       <c r="F106" t="str">
-        <v>12.50%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="107">
       <c r="A107">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B107" t="str">
-        <v>Kahuna Olivia</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C107" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D107" t="str">
-        <v>Boss</v>
+        <v>Alolan Sandshrew</v>
       </c>
       <c r="E107" t="str">
-        <v>44-49</v>
+        <v>60-65</v>
       </c>
       <c r="F107" t="str">
-        <v>-</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="108">
@@ -2546,1276 +2546,1276 @@
         <v>28</v>
       </c>
       <c r="B108" t="str">
-        <v>Malie City</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C108" t="str">
-        <v>Outer Cape</v>
+        <v/>
       </c>
       <c r="D108" t="str">
-        <v>Magnemite</v>
+        <v>Alolan Vulpix</v>
       </c>
       <c r="E108" t="str">
-        <v>47-52</v>
+        <v>60-65</v>
       </c>
       <c r="F108" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="109">
       <c r="A109">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B109" t="str">
-        <v>Malie City</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C109" t="str">
-        <v>Outer Cape</v>
+        <v/>
       </c>
       <c r="D109" t="str">
-        <v>Alolan Grimer</v>
+        <v>Haunter</v>
       </c>
       <c r="E109" t="str">
-        <v>47-52</v>
+        <v>63-68</v>
       </c>
       <c r="F109" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="110">
       <c r="A110">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B110" t="str">
-        <v>Malie City</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C110" t="str">
-        <v>Outer Cape</v>
+        <v/>
       </c>
       <c r="D110" t="str">
-        <v>Trubbish</v>
+        <v>Klefki</v>
       </c>
       <c r="E110" t="str">
-        <v>47-52</v>
+        <v>63-68</v>
       </c>
       <c r="F110" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="111">
       <c r="A111">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B111" t="str">
-        <v>Malie City</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C111" t="str">
-        <v>Outer Cape</v>
+        <v/>
       </c>
       <c r="D111" t="str">
-        <v>Minccino</v>
+        <v>Shuppet</v>
       </c>
       <c r="E111" t="str">
-        <v>47-52</v>
+        <v>63-68</v>
       </c>
       <c r="F111" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="112">
       <c r="A112">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B112" t="str">
-        <v>Malie City</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C112" t="str">
-        <v>Outer Cape</v>
+        <v/>
       </c>
       <c r="D112" t="str">
-        <v>Masquerain</v>
+        <v>Boldore</v>
       </c>
       <c r="E112" t="str">
-        <v>47-52</v>
+        <v>63-68</v>
       </c>
       <c r="F112" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="113">
       <c r="A113">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B113" t="str">
-        <v>Route 10</v>
+        <v>Captain Acerola</v>
       </c>
       <c r="C113" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D113" t="str">
-        <v>Ledian</v>
+        <v>Boss</v>
       </c>
       <c r="E113" t="str">
-        <v>50-55</v>
+        <v>64-69</v>
       </c>
       <c r="F113" t="str">
-        <v>16.67%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="114">
       <c r="A114">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B114" t="str">
-        <v>Route 10</v>
+        <v>Kahuna Nanu</v>
       </c>
       <c r="C114" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D114" t="str">
-        <v>Ariados</v>
+        <v>Boss</v>
       </c>
       <c r="E114" t="str">
-        <v>50-55</v>
+        <v>67-72</v>
       </c>
       <c r="F114" t="str">
-        <v>16.67%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="115">
       <c r="A115">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B115" t="str">
-        <v>Route 10</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C115" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D115" t="str">
-        <v>Crabrawler</v>
+        <v>Steenee</v>
       </c>
       <c r="E115" t="str">
-        <v>50-55</v>
+        <v>69-74</v>
       </c>
       <c r="F115" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="116">
       <c r="A116">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B116" t="str">
-        <v>Route 10</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C116" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D116" t="str">
-        <v>Fearow</v>
+        <v>Shellos</v>
       </c>
       <c r="E116" t="str">
-        <v>50-55</v>
+        <v>69-74</v>
       </c>
       <c r="F116" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="117">
       <c r="A117">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B117" t="str">
-        <v>Route 10</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C117" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D117" t="str">
-        <v>Skarmory</v>
+        <v>Dhelmise</v>
       </c>
       <c r="E117" t="str">
-        <v>50-55</v>
+        <v>69-74</v>
       </c>
       <c r="F117" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="118">
       <c r="A118">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B118" t="str">
-        <v>Route 10</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C118" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D118" t="str">
-        <v>Pancham</v>
+        <v>Tentacruel</v>
       </c>
       <c r="E118" t="str">
-        <v>50-55</v>
+        <v>70-75</v>
       </c>
       <c r="F118" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="119">
       <c r="A119">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B119" t="str">
-        <v>Mount Hokulani</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C119" t="str">
-        <v>East</v>
+        <v/>
       </c>
       <c r="D119" t="str">
-        <v>Cleffa</v>
+        <v>Lumineon</v>
       </c>
       <c r="E119" t="str">
-        <v>51-56</v>
+        <v>70-75</v>
       </c>
       <c r="F119" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="120">
       <c r="A120">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B120" t="str">
-        <v>Mount Hokulani</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C120" t="str">
-        <v>East</v>
+        <v/>
       </c>
       <c r="D120" t="str">
-        <v>Elgyem</v>
+        <v>Lapras</v>
       </c>
       <c r="E120" t="str">
-        <v>51-56</v>
+        <v>70-75</v>
       </c>
       <c r="F120" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="121">
       <c r="A121">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B121" t="str">
-        <v>Mount Hokulani</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C121" t="str">
-        <v>East</v>
+        <v/>
       </c>
       <c r="D121" t="str">
-        <v>Beldum</v>
+        <v>Noivern</v>
       </c>
       <c r="E121" t="str">
-        <v>51-56</v>
+        <v>70-75</v>
       </c>
       <c r="F121" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="122">
       <c r="A122">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B122" t="str">
-        <v>Mount Hokulani</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C122" t="str">
-        <v>East</v>
+        <v/>
       </c>
       <c r="D122" t="str">
-        <v>Minior</v>
+        <v>Druddigon</v>
       </c>
       <c r="E122" t="str">
-        <v>51-56</v>
+        <v>70-75</v>
       </c>
       <c r="F122" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="123">
       <c r="A123">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B123" t="str">
-        <v>Captain Sophocles</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C123" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D123" t="str">
-        <v>Boss</v>
+        <v>Wimpod</v>
       </c>
       <c r="E123" t="str">
-        <v>53-58</v>
+        <v>72-77</v>
       </c>
       <c r="F123" t="str">
-        <v>-</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="124">
       <c r="A124">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B124" t="str">
-        <v>Route 11</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C124" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D124" t="str">
-        <v>Shiinotic</v>
+        <v>Relicanth</v>
       </c>
       <c r="E124" t="str">
-        <v>54-59</v>
+        <v>72-77</v>
       </c>
       <c r="F124" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="125">
       <c r="A125">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B125" t="str">
-        <v>Route 11</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C125" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D125" t="str">
-        <v>Parasect</v>
+        <v>Wailmer</v>
       </c>
       <c r="E125" t="str">
-        <v>54-59</v>
+        <v>72-77</v>
       </c>
       <c r="F125" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="126">
       <c r="A126">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B126" t="str">
-        <v>Route 11</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C126" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D126" t="str">
-        <v>Komala</v>
+        <v>Carvanha</v>
       </c>
       <c r="E126" t="str">
-        <v>54-59</v>
+        <v>72-77</v>
       </c>
       <c r="F126" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="127">
       <c r="A127">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B127" t="str">
-        <v>Route 11</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C127" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D127" t="str">
-        <v>Houndoom</v>
+        <v>Sharpedo</v>
       </c>
       <c r="E127" t="str">
-        <v>54-59</v>
+        <v>72-77</v>
       </c>
       <c r="F127" t="str">
-        <v>11.11%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="128">
       <c r="A128">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B128" t="str">
-        <v>Route 11</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C128" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D128" t="str">
-        <v>Manectric</v>
+        <v>Pelipper</v>
       </c>
       <c r="E128" t="str">
-        <v>54-59</v>
+        <v>73-78</v>
       </c>
       <c r="F128" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="129">
       <c r="A129">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B129" t="str">
-        <v>Route 11</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C129" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D129" t="str">
-        <v>Scraggy</v>
+        <v>Pinsir</v>
       </c>
       <c r="E129" t="str">
-        <v>54-59</v>
+        <v>73-78</v>
       </c>
       <c r="F129" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="130">
       <c r="A130">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B130" t="str">
-        <v>Route 11</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C130" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D130" t="str">
-        <v>Bisharp</v>
+        <v>Gastrodon</v>
       </c>
       <c r="E130" t="str">
-        <v>54-59</v>
+        <v>73-78</v>
       </c>
       <c r="F130" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="131">
       <c r="A131">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B131" t="str">
-        <v>Route 11</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C131" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D131" t="str">
-        <v>Machop</v>
+        <v>Exeggcute</v>
       </c>
       <c r="E131" t="str">
-        <v>54-59</v>
+        <v>73-78</v>
       </c>
       <c r="F131" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="132">
       <c r="A132">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B132" t="str">
-        <v>Route 11</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C132" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D132" t="str">
-        <v>Hawlucha</v>
+        <v>Tropius</v>
       </c>
       <c r="E132" t="str">
-        <v>54-59</v>
+        <v>73-78</v>
       </c>
       <c r="F132" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="133">
       <c r="A133">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B133" t="str">
-        <v>Haina Desert</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C133" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D133" t="str">
-        <v>Alolan Dugtrio</v>
+        <v>Alolan Exeggutor</v>
       </c>
       <c r="E133" t="str">
-        <v>57-62</v>
+        <v>73-78</v>
       </c>
       <c r="F133" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="134">
       <c r="A134">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B134" t="str">
-        <v>Haina Desert</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C134" t="str">
-        <v>Main Area</v>
+        <v>Outside</v>
       </c>
       <c r="D134" t="str">
-        <v>Sandile</v>
+        <v>Machoke</v>
       </c>
       <c r="E134" t="str">
-        <v>57-62</v>
+        <v>75-80</v>
       </c>
       <c r="F134" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="135">
       <c r="A135">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B135" t="str">
-        <v>Haina Desert</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C135" t="str">
-        <v>Main Area</v>
+        <v>Outside</v>
       </c>
       <c r="D135" t="str">
-        <v>Krokorok</v>
+        <v>Mienfoo</v>
       </c>
       <c r="E135" t="str">
-        <v>57-62</v>
+        <v>75-80</v>
       </c>
       <c r="F135" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="136">
       <c r="A136">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B136" t="str">
-        <v>Haina Desert</v>
+        <v>Vast Poni Canyon</v>
       </c>
       <c r="C136" t="str">
-        <v>Main Area</v>
+        <v>Outside</v>
       </c>
       <c r="D136" t="str">
-        <v>Staryu</v>
+        <v>Jangmo-o</v>
       </c>
       <c r="E136" t="str">
-        <v>57-62</v>
+        <v>75-80</v>
       </c>
       <c r="F136" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="137">
       <c r="A137">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B137" t="str">
-        <v>Haina Desert</v>
+        <v>Captain Kommo-o</v>
       </c>
       <c r="C137" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D137" t="str">
-        <v>Sandygast</v>
+        <v>Boss</v>
       </c>
       <c r="E137" t="str">
-        <v>57-62</v>
+        <v>78-83</v>
       </c>
       <c r="F137" t="str">
-        <v>20.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="138">
       <c r="A138">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B138" t="str">
-        <v>Tapu Village</v>
+        <v>Captain Mina</v>
       </c>
       <c r="C138" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D138" t="str">
-        <v>Graveler</v>
+        <v>Boss</v>
       </c>
       <c r="E138" t="str">
-        <v>59-64</v>
+        <v>79-84</v>
       </c>
       <c r="F138" t="str">
-        <v>16.67%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="139">
       <c r="A139">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B139" t="str">
-        <v>Tapu Village</v>
+        <v>Kahuna Hapu</v>
       </c>
       <c r="C139" t="str">
-        <v>Main Area</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D139" t="str">
-        <v>Bruxish</v>
+        <v>Boss</v>
       </c>
       <c r="E139" t="str">
-        <v>59-64</v>
+        <v>81-86</v>
       </c>
       <c r="F139" t="str">
-        <v>16.67%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="140">
       <c r="A140">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B140" t="str">
-        <v>Tapu Village</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C140" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D140" t="str">
-        <v>Absol</v>
+        <v>Drampa</v>
       </c>
       <c r="E140" t="str">
-        <v>59-64</v>
+        <v>82-87</v>
       </c>
       <c r="F140" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="141">
       <c r="A141">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B141" t="str">
-        <v>Tapu Village</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C141" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D141" t="str">
-        <v>Snorunt</v>
+        <v>Glalie</v>
       </c>
       <c r="E141" t="str">
-        <v>59-64</v>
+        <v>82-87</v>
       </c>
       <c r="F141" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="142">
       <c r="A142">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B142" t="str">
-        <v>Tapu Village</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C142" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D142" t="str">
-        <v>Alolan Sandshrew</v>
+        <v>Sneasel</v>
       </c>
       <c r="E142" t="str">
-        <v>59-64</v>
+        <v>82-87</v>
       </c>
       <c r="F142" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="143">
       <c r="A143">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B143" t="str">
-        <v>Tapu Village</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C143" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D143" t="str">
-        <v>Alolan Vulpix</v>
+        <v>Crabominable</v>
       </c>
       <c r="E143" t="str">
-        <v>59-64</v>
+        <v>82-87</v>
       </c>
       <c r="F143" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="144">
       <c r="A144">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B144" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Alola Pokemon League</v>
       </c>
       <c r="C144" t="str">
-        <v>Abandoned Site</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D144" t="str">
-        <v>Haunter</v>
+        <v>Boss</v>
       </c>
       <c r="E144" t="str">
-        <v>62-67</v>
+        <v>84-89</v>
       </c>
       <c r="F144" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="145">
       <c r="A145">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B145" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Champion Hau</v>
       </c>
       <c r="C145" t="str">
-        <v>Abandoned Site</v>
+        <v>Boss Battle</v>
       </c>
       <c r="D145" t="str">
-        <v>Klefki</v>
+        <v>Boss</v>
       </c>
       <c r="E145" t="str">
-        <v>62-67</v>
+        <v>85-90</v>
       </c>
       <c r="F145" t="str">
-        <v>25.00%</v>
+        <v>-</v>
       </c>
     </row>
     <row r="146">
       <c r="A146">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B146" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Royal Avenue</v>
       </c>
       <c r="C146" t="str">
-        <v>Abandoned Site</v>
+        <v/>
       </c>
       <c r="D146" t="str">
-        <v>Shuppet</v>
+        <v>Oricorio</v>
       </c>
       <c r="E146" t="str">
-        <v>62-67</v>
+        <v>85-90</v>
       </c>
       <c r="F146" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="147">
       <c r="A147">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B147" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Royal Avenue</v>
       </c>
       <c r="C147" t="str">
-        <v>Abandoned Site</v>
+        <v/>
       </c>
       <c r="D147" t="str">
-        <v>Boldore</v>
+        <v>Trumbeak</v>
       </c>
       <c r="E147" t="str">
-        <v>62-67</v>
+        <v>85-90</v>
       </c>
       <c r="F147" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="148">
       <c r="A148">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B148" t="str">
-        <v>Captain Acerola</v>
+        <v>Royal Avenue</v>
       </c>
       <c r="C148" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D148" t="str">
-        <v>Boss</v>
+        <v>Ribombee</v>
       </c>
       <c r="E148" t="str">
-        <v>63-68</v>
+        <v>85-90</v>
       </c>
       <c r="F148" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="149">
       <c r="A149">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B149" t="str">
-        <v>Kahuna Nanu</v>
+        <v>Pikachu Valley</v>
       </c>
       <c r="C149" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D149" t="str">
-        <v>Boss</v>
+        <v>Pikachu</v>
       </c>
       <c r="E149" t="str">
-        <v>68-73</v>
+        <v>85-90</v>
       </c>
       <c r="F149" t="str">
-        <v>-</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="150">
       <c r="A150">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B150" t="str">
-        <v>Seafolk Village</v>
+        <v>Pikachu Valley</v>
       </c>
       <c r="C150" t="str">
-        <v>Main</v>
+        <v/>
       </c>
       <c r="D150" t="str">
-        <v>Steenee</v>
+        <v>Alolan Raichu</v>
       </c>
       <c r="E150" t="str">
-        <v>69-74</v>
+        <v>85-90</v>
       </c>
       <c r="F150" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="151">
       <c r="A151">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B151" t="str">
-        <v>Seafolk Village</v>
+        <v>Pikachu Valley</v>
       </c>
       <c r="C151" t="str">
-        <v>Main</v>
+        <v/>
       </c>
       <c r="D151" t="str">
-        <v>Shellos</v>
+        <v>Pichu</v>
       </c>
       <c r="E151" t="str">
-        <v>69-74</v>
+        <v>85-90</v>
       </c>
       <c r="F151" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="152">
       <c r="A152">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B152" t="str">
-        <v>Seafolk Village</v>
+        <v>Pikachu Valley</v>
       </c>
       <c r="C152" t="str">
-        <v>Main</v>
+        <v/>
       </c>
       <c r="D152" t="str">
-        <v>Dhelmise</v>
+        <v>Magnemite</v>
       </c>
       <c r="E152" t="str">
-        <v>69-74</v>
+        <v>85-90</v>
       </c>
       <c r="F152" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="153">
       <c r="A153">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B153" t="str">
-        <v>Poni Wilds</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C153" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D153" t="str">
-        <v>Tentacruel</v>
+        <v>Rowlet</v>
       </c>
       <c r="E153" t="str">
-        <v>71-76</v>
+        <v>85-90</v>
       </c>
       <c r="F153" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="154">
       <c r="A154">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B154" t="str">
-        <v>Poni Wilds</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C154" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D154" t="str">
-        <v>Lumineon</v>
+        <v>Dartrix</v>
       </c>
       <c r="E154" t="str">
-        <v>71-76</v>
+        <v>85-90</v>
       </c>
       <c r="F154" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="155">
       <c r="A155">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B155" t="str">
-        <v>Poni Wilds</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C155" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D155" t="str">
-        <v>Lapras</v>
+        <v>Litten</v>
       </c>
       <c r="E155" t="str">
-        <v>71-76</v>
+        <v>85-90</v>
       </c>
       <c r="F155" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="156">
       <c r="A156">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B156" t="str">
-        <v>Poni Wilds</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C156" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D156" t="str">
-        <v>Noivern</v>
+        <v>Torracat</v>
       </c>
       <c r="E156" t="str">
-        <v>71-76</v>
+        <v>85-90</v>
       </c>
       <c r="F156" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="157">
       <c r="A157">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B157" t="str">
-        <v>Poni Wilds</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C157" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D157" t="str">
-        <v>Druddigon</v>
+        <v>Popplio</v>
       </c>
       <c r="E157" t="str">
-        <v>71-76</v>
+        <v>85-90</v>
       </c>
       <c r="F157" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="158">
       <c r="A158">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B158" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C158" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D158" t="str">
-        <v>Wimpod</v>
+        <v>Brionne</v>
       </c>
       <c r="E158" t="str">
-        <v>72-77</v>
+        <v>85-90</v>
       </c>
       <c r="F158" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
     </row>
     <row r="159">
       <c r="A159">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B159" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Ula'ula Meadow</v>
       </c>
       <c r="C159" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D159" t="str">
-        <v>Relicanth</v>
+        <v>Ledian</v>
       </c>
       <c r="E159" t="str">
-        <v>72-77</v>
+        <v>85-90</v>
       </c>
       <c r="F159" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="160">
       <c r="A160">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B160" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Ula'ula Meadow</v>
       </c>
       <c r="C160" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D160" t="str">
-        <v>Wailmer</v>
+        <v>Ariados</v>
       </c>
       <c r="E160" t="str">
-        <v>72-77</v>
+        <v>85-90</v>
       </c>
       <c r="F160" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="161">
       <c r="A161">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B161" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Ula'ula Meadow</v>
       </c>
       <c r="C161" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D161" t="str">
-        <v>Carvanha</v>
+        <v>Oricorio</v>
       </c>
       <c r="E161" t="str">
-        <v>72-77</v>
+        <v>85-90</v>
       </c>
       <c r="F161" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="162">
       <c r="A162">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B162" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C162" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D162" t="str">
-        <v>Sharpedo</v>
+        <v>Mudbray</v>
       </c>
       <c r="E162" t="str">
-        <v>72-77</v>
+        <v>85-90</v>
       </c>
       <c r="F162" t="str">
-        <v>20.00%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="163">
       <c r="A163">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B163" t="str">
-        <v>Exeggutor Island</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C163" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D163" t="str">
-        <v>Pelipper</v>
+        <v>Torkoal</v>
       </c>
       <c r="E163" t="str">
-        <v>74-79</v>
+        <v>85-90</v>
       </c>
       <c r="F163" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="164">
       <c r="A164">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B164" t="str">
-        <v>Exeggutor Island</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C164" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D164" t="str">
-        <v>Pinsir</v>
+        <v>Togedemaru</v>
       </c>
       <c r="E164" t="str">
-        <v>74-79</v>
+        <v>85-90</v>
       </c>
       <c r="F164" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="165">
       <c r="A165">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B165" t="str">
-        <v>Exeggutor Island</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C165" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D165" t="str">
-        <v>Gastrodon</v>
+        <v>Elekid</v>
       </c>
       <c r="E165" t="str">
-        <v>74-79</v>
+        <v>85-90</v>
       </c>
       <c r="F165" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="166">
       <c r="A166">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B166" t="str">
-        <v>Exeggutor Island</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C166" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D166" t="str">
-        <v>Exeggcute</v>
+        <v>Alolan Geodude</v>
       </c>
       <c r="E166" t="str">
-        <v>74-79</v>
+        <v>85-90</v>
       </c>
       <c r="F166" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="167">
       <c r="A167">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B167" t="str">
-        <v>Exeggutor Island</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C167" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D167" t="str">
-        <v>Tropius</v>
+        <v>Alolan Graveler</v>
       </c>
       <c r="E167" t="str">
-        <v>74-79</v>
+        <v>85-90</v>
       </c>
       <c r="F167" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="168">
       <c r="A168">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B168" t="str">
-        <v>Exeggutor Island</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C168" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D168" t="str">
-        <v>Alolan Exeggutor</v>
+        <v>Charjabug</v>
       </c>
       <c r="E168" t="str">
-        <v>74-79</v>
+        <v>85-90</v>
       </c>
       <c r="F168" t="str">
-        <v>16.67%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="169">
       <c r="A169">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B169" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C169" t="str">
-        <v>Outside</v>
+        <v/>
       </c>
       <c r="D169" t="str">
-        <v>Machoke</v>
+        <v>Turtonator</v>
       </c>
       <c r="E169" t="str">
-        <v>75-80</v>
+        <v>85-90</v>
       </c>
       <c r="F169" t="str">
-        <v>33.33%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="170">
       <c r="A170">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B170" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C170" t="str">
-        <v>Outside</v>
+        <v/>
       </c>
       <c r="D170" t="str">
-        <v>Mienfoo</v>
+        <v>Dedenne</v>
       </c>
       <c r="E170" t="str">
-        <v>75-80</v>
+        <v>85-90</v>
       </c>
       <c r="F170" t="str">
-        <v>33.33%</v>
+        <v>11.11%</v>
       </c>
     </row>
     <row r="171">
       <c r="A171">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B171" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>The Zenith Anomaly</v>
       </c>
       <c r="C171" t="str">
-        <v>Outside</v>
+        <v/>
       </c>
       <c r="D171" t="str">
-        <v>Jangmo-o</v>
+        <v>Magearna</v>
       </c>
       <c r="E171" t="str">
-        <v>75-80</v>
+        <v>95-100</v>
       </c>
       <c r="F171" t="str">
         <v>33.33%</v>
@@ -3823,182 +3823,182 @@
     </row>
     <row r="172">
       <c r="A172">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B172" t="str">
-        <v>Captain Kommo-o</v>
+        <v>The Zenith Anomaly</v>
       </c>
       <c r="C172" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D172" t="str">
-        <v>Boss</v>
+        <v>Marshadow</v>
       </c>
       <c r="E172" t="str">
-        <v>78-83</v>
+        <v>95-100</v>
       </c>
       <c r="F172" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="173">
       <c r="A173">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B173" t="str">
-        <v>Captain Mina</v>
+        <v>The Zenith Anomaly</v>
       </c>
       <c r="C173" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D173" t="str">
-        <v>Boss</v>
+        <v>Zeraora</v>
       </c>
       <c r="E173" t="str">
-        <v>80-85</v>
+        <v>95-100</v>
       </c>
       <c r="F173" t="str">
-        <v>-</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="174">
       <c r="A174">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B174" t="str">
-        <v>Kahuna Hapu</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C174" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D174" t="str">
-        <v>Boss</v>
+        <v>Caterpie</v>
       </c>
       <c r="E174" t="str">
-        <v>81-86</v>
+        <v>85-90</v>
       </c>
       <c r="F174" t="str">
-        <v>-</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="175">
       <c r="A175">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B175" t="str">
-        <v>Mount Lanakila</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C175" t="str">
-        <v>Cave</v>
+        <v/>
       </c>
       <c r="D175" t="str">
-        <v>Drampa</v>
+        <v>Metapod</v>
       </c>
       <c r="E175" t="str">
-        <v>83-88</v>
+        <v>85-90</v>
       </c>
       <c r="F175" t="str">
-        <v>25.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="176">
       <c r="A176">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B176" t="str">
-        <v>Mount Lanakila</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C176" t="str">
-        <v>Cave</v>
+        <v/>
       </c>
       <c r="D176" t="str">
-        <v>Glalie</v>
+        <v>Cutiefly</v>
       </c>
       <c r="E176" t="str">
-        <v>83-88</v>
+        <v>85-90</v>
       </c>
       <c r="F176" t="str">
-        <v>25.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="177">
       <c r="A177">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B177" t="str">
-        <v>Mount Lanakila</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C177" t="str">
-        <v>Cave</v>
+        <v/>
       </c>
       <c r="D177" t="str">
-        <v>Sneasel</v>
+        <v>Butterfree</v>
       </c>
       <c r="E177" t="str">
-        <v>83-88</v>
+        <v>85-90</v>
       </c>
       <c r="F177" t="str">
-        <v>25.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="178">
       <c r="A178">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B178" t="str">
-        <v>Mount Lanakila</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C178" t="str">
-        <v>Cave</v>
+        <v/>
       </c>
       <c r="D178" t="str">
-        <v>Crabominable</v>
+        <v>Flabébé</v>
       </c>
       <c r="E178" t="str">
-        <v>83-88</v>
+        <v>85-90</v>
       </c>
       <c r="F178" t="str">
-        <v>25.00%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="179">
       <c r="A179">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B179" t="str">
-        <v>Alola Pokemon League</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C179" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D179" t="str">
-        <v>Boss</v>
+        <v>Petilil</v>
       </c>
       <c r="E179" t="str">
-        <v>84-89</v>
+        <v>85-90</v>
       </c>
       <c r="F179" t="str">
-        <v>-</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="180">
       <c r="A180">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B180" t="str">
-        <v>Champion Hau</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C180" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D180" t="str">
-        <v>Boss</v>
+        <v>Cottonee</v>
       </c>
       <c r="E180" t="str">
         <v>85-90</v>
       </c>
       <c r="F180" t="str">
-        <v>-</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="181">
@@ -4006,33 +4006,33 @@
         <v>49</v>
       </c>
       <c r="B181" t="str">
-        <v>Royal Avenue</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C181" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D181" t="str">
-        <v>Oricorio</v>
+        <v>Phantump</v>
       </c>
       <c r="E181" t="str">
         <v>85-90</v>
       </c>
       <c r="F181" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
     </row>
     <row r="182">
       <c r="A182">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B182" t="str">
-        <v>Royal Avenue</v>
+        <v>Kala'e Bay</v>
       </c>
       <c r="C182" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D182" t="str">
-        <v>Trumbeak</v>
+        <v>Shellder</v>
       </c>
       <c r="E182" t="str">
         <v>85-90</v>
@@ -4043,16 +4043,16 @@
     </row>
     <row r="183">
       <c r="A183">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B183" t="str">
-        <v>Royal Avenue</v>
+        <v>Kala'e Bay</v>
       </c>
       <c r="C183" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D183" t="str">
-        <v>Ribombee</v>
+        <v>Slowpoke</v>
       </c>
       <c r="E183" t="str">
         <v>85-90</v>
@@ -4066,36 +4066,36 @@
         <v>50</v>
       </c>
       <c r="B184" t="str">
-        <v>Pikachu Valley</v>
+        <v>Kala'e Bay</v>
       </c>
       <c r="C184" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D184" t="str">
-        <v>Pikachu</v>
+        <v>Finneon</v>
       </c>
       <c r="E184" t="str">
         <v>85-90</v>
       </c>
       <c r="F184" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="185">
       <c r="A185">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B185" t="str">
-        <v>Pikachu Valley</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C185" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D185" t="str">
-        <v>Alolan Raichu</v>
+        <v>Tapu Koko</v>
       </c>
       <c r="E185" t="str">
-        <v>85-90</v>
+        <v>100</v>
       </c>
       <c r="F185" t="str">
         <v>25.00%</v>
@@ -4103,19 +4103,19 @@
     </row>
     <row r="186">
       <c r="A186">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B186" t="str">
-        <v>Pikachu Valley</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C186" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D186" t="str">
-        <v>Pichu</v>
+        <v>Tapu Lele</v>
       </c>
       <c r="E186" t="str">
-        <v>85-90</v>
+        <v>100</v>
       </c>
       <c r="F186" t="str">
         <v>25.00%</v>
@@ -4123,19 +4123,19 @@
     </row>
     <row r="187">
       <c r="A187">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B187" t="str">
-        <v>Pikachu Valley</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C187" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D187" t="str">
-        <v>Magnemite</v>
+        <v>Tapu Bulu</v>
       </c>
       <c r="E187" t="str">
-        <v>85-90</v>
+        <v>100</v>
       </c>
       <c r="F187" t="str">
         <v>25.00%</v>
@@ -4146,179 +4146,179 @@
         <v>51</v>
       </c>
       <c r="B188" t="str">
-        <v>Starter Depot</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C188" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D188" t="str">
-        <v>Rowlet</v>
+        <v>Tapu Fini</v>
       </c>
       <c r="E188" t="str">
-        <v>85-90</v>
+        <v>100</v>
       </c>
       <c r="F188" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="189">
       <c r="A189">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B189" t="str">
-        <v>Starter Depot</v>
+        <v>Poni Coast</v>
       </c>
       <c r="C189" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D189" t="str">
-        <v>Dartrix</v>
+        <v>Alolan Dugtrio</v>
       </c>
       <c r="E189" t="str">
         <v>85-90</v>
       </c>
       <c r="F189" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="190">
       <c r="A190">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B190" t="str">
-        <v>Starter Depot</v>
+        <v>Poni Coast</v>
       </c>
       <c r="C190" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D190" t="str">
-        <v>Litten</v>
+        <v>Gastrodon</v>
       </c>
       <c r="E190" t="str">
         <v>85-90</v>
       </c>
       <c r="F190" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="191">
       <c r="A191">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B191" t="str">
-        <v>Starter Depot</v>
+        <v>Poni Coast</v>
       </c>
       <c r="C191" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D191" t="str">
-        <v>Torracat</v>
+        <v>Exeggcute</v>
       </c>
       <c r="E191" t="str">
         <v>85-90</v>
       </c>
       <c r="F191" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="192">
       <c r="A192">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B192" t="str">
-        <v>Starter Depot</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C192" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D192" t="str">
-        <v>Popplio</v>
+        <v>Nihilego</v>
       </c>
       <c r="E192" t="str">
-        <v>85-90</v>
+        <v>110</v>
       </c>
       <c r="F192" t="str">
-        <v>16.67%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="193">
       <c r="A193">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B193" t="str">
-        <v>Starter Depot</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C193" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D193" t="str">
-        <v>Brionne</v>
+        <v>Buzzwole</v>
       </c>
       <c r="E193" t="str">
-        <v>85-90</v>
+        <v>110</v>
       </c>
       <c r="F193" t="str">
-        <v>16.67%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="194">
       <c r="A194">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B194" t="str">
-        <v>Poni Coast</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C194" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D194" t="str">
-        <v>Alolan Dugtrio</v>
+        <v>Pheromosa</v>
       </c>
       <c r="E194" t="str">
-        <v>85-90</v>
+        <v>110</v>
       </c>
       <c r="F194" t="str">
-        <v>33.33%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="195">
       <c r="A195">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B195" t="str">
-        <v>Poni Coast</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C195" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D195" t="str">
-        <v>Gastrodon</v>
+        <v>Xurkitree</v>
       </c>
       <c r="E195" t="str">
-        <v>85-90</v>
+        <v>110</v>
       </c>
       <c r="F195" t="str">
-        <v>33.33%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="196">
       <c r="A196">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B196" t="str">
-        <v>Poni Coast</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C196" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D196" t="str">
-        <v>Exeggcute</v>
+        <v>Celesteela</v>
       </c>
       <c r="E196" t="str">
-        <v>85-90</v>
+        <v>110</v>
       </c>
       <c r="F196" t="str">
-        <v>33.33%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="197">
@@ -4326,19 +4326,19 @@
         <v>53</v>
       </c>
       <c r="B197" t="str">
-        <v>The Zenith Anomaly</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C197" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D197" t="str">
-        <v>Magearna</v>
+        <v>Kartana</v>
       </c>
       <c r="E197" t="str">
-        <v>95-100</v>
+        <v>110</v>
       </c>
       <c r="F197" t="str">
-        <v>33.33%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="198">
@@ -4346,19 +4346,19 @@
         <v>53</v>
       </c>
       <c r="B198" t="str">
-        <v>The Zenith Anomaly</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C198" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D198" t="str">
-        <v>Marshadow</v>
+        <v>Guzzlord</v>
       </c>
       <c r="E198" t="str">
-        <v>95-100</v>
+        <v>110</v>
       </c>
       <c r="F198" t="str">
-        <v>33.33%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="199">
@@ -4366,59 +4366,59 @@
         <v>53</v>
       </c>
       <c r="B199" t="str">
-        <v>The Zenith Anomaly</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C199" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D199" t="str">
-        <v>Zeraora</v>
+        <v>Poipole</v>
       </c>
       <c r="E199" t="str">
-        <v>95-100</v>
+        <v>110</v>
       </c>
       <c r="F199" t="str">
-        <v>33.33%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="200">
       <c r="A200">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B200" t="str">
-        <v>Melemele Meadow</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C200" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D200" t="str">
-        <v>Caterpie</v>
+        <v>Stakataka</v>
       </c>
       <c r="E200" t="str">
-        <v>85-90</v>
+        <v>110</v>
       </c>
       <c r="F200" t="str">
-        <v>12.50%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="201">
       <c r="A201">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B201" t="str">
-        <v>Melemele Meadow</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C201" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D201" t="str">
-        <v>Metapod</v>
+        <v>Blacephalon</v>
       </c>
       <c r="E201" t="str">
-        <v>85-90</v>
+        <v>110</v>
       </c>
       <c r="F201" t="str">
-        <v>12.50%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="202">
@@ -4426,19 +4426,19 @@
         <v>54</v>
       </c>
       <c r="B202" t="str">
-        <v>Melemele Meadow</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C202" t="str">
-        <v>Main Area</v>
+        <v>Labs</v>
       </c>
       <c r="D202" t="str">
-        <v>Cutiefly</v>
+        <v>Type: Null</v>
       </c>
       <c r="E202" t="str">
         <v>85-90</v>
       </c>
       <c r="F202" t="str">
-        <v>12.50%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="203">
@@ -4446,751 +4446,211 @@
         <v>54</v>
       </c>
       <c r="B203" t="str">
-        <v>Melemele Meadow</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C203" t="str">
-        <v>Main Area</v>
+        <v>Labs</v>
       </c>
       <c r="D203" t="str">
-        <v>Butterfree</v>
+        <v>Porygon</v>
       </c>
       <c r="E203" t="str">
         <v>85-90</v>
       </c>
       <c r="F203" t="str">
-        <v>12.50%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="204">
       <c r="A204">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B204" t="str">
-        <v>Melemele Meadow</v>
+        <v>Aether Paradise</v>
       </c>
       <c r="C204" t="str">
-        <v>Main Area</v>
+        <v>Secret Lab</v>
       </c>
       <c r="D204" t="str">
-        <v>Flabébé</v>
+        <v>Silvally</v>
       </c>
       <c r="E204" t="str">
         <v>85-90</v>
       </c>
       <c r="F204" t="str">
-        <v>12.50%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="205">
       <c r="A205">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B205" t="str">
-        <v>Melemele Meadow</v>
+        <v>Lake of the Sunne</v>
       </c>
       <c r="C205" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D205" t="str">
-        <v>Petilil</v>
+        <v>Golbat</v>
       </c>
       <c r="E205" t="str">
         <v>85-90</v>
       </c>
       <c r="F205" t="str">
-        <v>12.50%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="206">
       <c r="A206">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B206" t="str">
-        <v>Melemele Meadow</v>
+        <v>Lake of the Sunne</v>
       </c>
       <c r="C206" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D206" t="str">
-        <v>Cottonee</v>
+        <v>Gastly</v>
       </c>
       <c r="E206" t="str">
         <v>85-90</v>
       </c>
       <c r="F206" t="str">
-        <v>12.50%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="207">
       <c r="A207">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B207" t="str">
-        <v>Melemele Meadow</v>
+        <v>Lake of the Sunne</v>
       </c>
       <c r="C207" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D207" t="str">
-        <v>Phantump</v>
+        <v>Haunter</v>
       </c>
       <c r="E207" t="str">
         <v>85-90</v>
       </c>
       <c r="F207" t="str">
-        <v>12.50%</v>
+        <v>33.33%</v>
       </c>
     </row>
     <row r="208">
       <c r="A208">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B208" t="str">
-        <v>Sacred Shrine</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C208" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D208" t="str">
-        <v>Tapu Koko</v>
+        <v>Cosmog</v>
       </c>
       <c r="E208" t="str">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F208" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="209">
       <c r="A209">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B209" t="str">
-        <v>Sacred Shrine</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C209" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D209" t="str">
-        <v>Tapu Lele</v>
+        <v>Cosmoem</v>
       </c>
       <c r="E209" t="str">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F209" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="210">
       <c r="A210">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B210" t="str">
-        <v>Sacred Shrine</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C210" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D210" t="str">
-        <v>Tapu Bulu</v>
+        <v>Solgaleo</v>
       </c>
       <c r="E210" t="str">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F210" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="211">
       <c r="A211">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B211" t="str">
-        <v>Sacred Shrine</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C211" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D211" t="str">
-        <v>Tapu Fini</v>
+        <v>Lunala</v>
       </c>
       <c r="E211" t="str">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F211" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="212">
       <c r="A212">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B212" t="str">
-        <v>Poni Grove</v>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="C212" t="str">
-        <v>Main Area</v>
+        <v/>
       </c>
       <c r="D212" t="str">
-        <v>Buneary</v>
+        <v>Necrozma</v>
       </c>
       <c r="E212" t="str">
-        <v>85-90</v>
+        <v>120</v>
       </c>
       <c r="F212" t="str">
-        <v>14.29%</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213">
-        <v>56</v>
-      </c>
-      <c r="B213" t="str">
-        <v>Poni Grove</v>
-      </c>
-      <c r="C213" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D213" t="str">
-        <v>Granbull</v>
-      </c>
-      <c r="E213" t="str">
-        <v>85-90</v>
-      </c>
-      <c r="F213" t="str">
-        <v>14.29%</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214">
-        <v>56</v>
-      </c>
-      <c r="B214" t="str">
-        <v>Poni Grove</v>
-      </c>
-      <c r="C214" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D214" t="str">
-        <v>Zoroark</v>
-      </c>
-      <c r="E214" t="str">
-        <v>85-90</v>
-      </c>
-      <c r="F214" t="str">
-        <v>14.29%</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215">
-        <v>56</v>
-      </c>
-      <c r="B215" t="str">
-        <v>Poni Grove</v>
-      </c>
-      <c r="C215" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D215" t="str">
-        <v>Heracross</v>
-      </c>
-      <c r="E215" t="str">
-        <v>85-90</v>
-      </c>
-      <c r="F215" t="str">
-        <v>14.29%</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216">
-        <v>56</v>
-      </c>
-      <c r="B216" t="str">
-        <v>Poni Grove</v>
-      </c>
-      <c r="C216" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D216" t="str">
-        <v>Riolu</v>
-      </c>
-      <c r="E216" t="str">
-        <v>85-90</v>
-      </c>
-      <c r="F216" t="str">
-        <v>14.29%</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217">
-        <v>56</v>
-      </c>
-      <c r="B217" t="str">
-        <v>Poni Grove</v>
-      </c>
-      <c r="C217" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D217" t="str">
-        <v>Hariyama</v>
-      </c>
-      <c r="E217" t="str">
-        <v>85-90</v>
-      </c>
-      <c r="F217" t="str">
-        <v>14.29%</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218">
-        <v>56</v>
-      </c>
-      <c r="B218" t="str">
-        <v>Poni Grove</v>
-      </c>
-      <c r="C218" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D218" t="str">
-        <v>Mudsdale</v>
-      </c>
-      <c r="E218" t="str">
-        <v>85-90</v>
-      </c>
-      <c r="F218" t="str">
-        <v>14.29%</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219">
-        <v>57</v>
-      </c>
-      <c r="B219" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="C219" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D219" t="str">
-        <v>Nihilego</v>
-      </c>
-      <c r="E219" t="str">
-        <v>110</v>
-      </c>
-      <c r="F219" t="str">
-        <v>10.00%</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220">
-        <v>57</v>
-      </c>
-      <c r="B220" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="C220" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D220" t="str">
-        <v>Buzzwole</v>
-      </c>
-      <c r="E220" t="str">
-        <v>110</v>
-      </c>
-      <c r="F220" t="str">
-        <v>10.00%</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221">
-        <v>57</v>
-      </c>
-      <c r="B221" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="C221" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D221" t="str">
-        <v>Pheromosa</v>
-      </c>
-      <c r="E221" t="str">
-        <v>110</v>
-      </c>
-      <c r="F221" t="str">
-        <v>10.00%</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222">
-        <v>57</v>
-      </c>
-      <c r="B222" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="C222" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D222" t="str">
-        <v>Xurkitree</v>
-      </c>
-      <c r="E222" t="str">
-        <v>110</v>
-      </c>
-      <c r="F222" t="str">
-        <v>10.00%</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223">
-        <v>57</v>
-      </c>
-      <c r="B223" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="C223" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D223" t="str">
-        <v>Celesteela</v>
-      </c>
-      <c r="E223" t="str">
-        <v>110</v>
-      </c>
-      <c r="F223" t="str">
-        <v>10.00%</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224">
-        <v>57</v>
-      </c>
-      <c r="B224" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="C224" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D224" t="str">
-        <v>Kartana</v>
-      </c>
-      <c r="E224" t="str">
-        <v>110</v>
-      </c>
-      <c r="F224" t="str">
-        <v>10.00%</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225">
-        <v>57</v>
-      </c>
-      <c r="B225" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="C225" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D225" t="str">
-        <v>Guzzlord</v>
-      </c>
-      <c r="E225" t="str">
-        <v>110</v>
-      </c>
-      <c r="F225" t="str">
-        <v>10.00%</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226">
-        <v>57</v>
-      </c>
-      <c r="B226" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="C226" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D226" t="str">
-        <v>Poipole</v>
-      </c>
-      <c r="E226" t="str">
-        <v>110</v>
-      </c>
-      <c r="F226" t="str">
-        <v>10.00%</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227">
-        <v>57</v>
-      </c>
-      <c r="B227" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="C227" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D227" t="str">
-        <v>Stakataka</v>
-      </c>
-      <c r="E227" t="str">
-        <v>110</v>
-      </c>
-      <c r="F227" t="str">
-        <v>10.00%</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228">
-        <v>57</v>
-      </c>
-      <c r="B228" t="str">
-        <v>The Interdimensional Rift</v>
-      </c>
-      <c r="C228" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D228" t="str">
-        <v>Blacephalon</v>
-      </c>
-      <c r="E228" t="str">
-        <v>110</v>
-      </c>
-      <c r="F228" t="str">
-        <v>10.00%</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229">
-        <v>58</v>
-      </c>
-      <c r="B229" t="str">
-        <v>Aether Paradise</v>
-      </c>
-      <c r="C229" t="str">
-        <v>Secret Lab</v>
-      </c>
-      <c r="D229" t="str">
-        <v>Type: Null</v>
-      </c>
-      <c r="E229" t="str">
-        <v>85-90</v>
-      </c>
-      <c r="F229" t="str">
-        <v>33.33%</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230">
-        <v>58</v>
-      </c>
-      <c r="B230" t="str">
-        <v>Aether Paradise</v>
-      </c>
-      <c r="C230" t="str">
-        <v>Secret Lab</v>
-      </c>
-      <c r="D230" t="str">
-        <v>Silvally</v>
-      </c>
-      <c r="E230" t="str">
-        <v>85-90</v>
-      </c>
-      <c r="F230" t="str">
-        <v>33.33%</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231">
-        <v>58</v>
-      </c>
-      <c r="B231" t="str">
-        <v>Aether Paradise</v>
-      </c>
-      <c r="C231" t="str">
-        <v>Secret Lab</v>
-      </c>
-      <c r="D231" t="str">
-        <v>Porygon</v>
-      </c>
-      <c r="E231" t="str">
-        <v>85-90</v>
-      </c>
-      <c r="F231" t="str">
-        <v>33.33%</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232">
-        <v>59</v>
-      </c>
-      <c r="B232" t="str">
-        <v>Lake of the Sunne</v>
-      </c>
-      <c r="C232" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D232" t="str">
-        <v>Golbat</v>
-      </c>
-      <c r="E232" t="str">
-        <v>85-90</v>
-      </c>
-      <c r="F232" t="str">
-        <v>33.33%</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233">
-        <v>59</v>
-      </c>
-      <c r="B233" t="str">
-        <v>Lake of the Sunne</v>
-      </c>
-      <c r="C233" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D233" t="str">
-        <v>Gastly</v>
-      </c>
-      <c r="E233" t="str">
-        <v>85-90</v>
-      </c>
-      <c r="F233" t="str">
-        <v>33.33%</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234">
-        <v>59</v>
-      </c>
-      <c r="B234" t="str">
-        <v>Lake of the Sunne</v>
-      </c>
-      <c r="C234" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D234" t="str">
-        <v>Haunter</v>
-      </c>
-      <c r="E234" t="str">
-        <v>85-90</v>
-      </c>
-      <c r="F234" t="str">
-        <v>33.33%</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235">
-        <v>60</v>
-      </c>
-      <c r="B235" t="str">
-        <v>Obsidian Sphere</v>
-      </c>
-      <c r="C235" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D235" t="str">
-        <v>Cosmog</v>
-      </c>
-      <c r="E235" t="str">
-        <v>120</v>
-      </c>
-      <c r="F235" t="str">
-        <v>20.00%</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236">
-        <v>60</v>
-      </c>
-      <c r="B236" t="str">
-        <v>Obsidian Sphere</v>
-      </c>
-      <c r="C236" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D236" t="str">
-        <v>Cosmoem</v>
-      </c>
-      <c r="E236" t="str">
-        <v>120</v>
-      </c>
-      <c r="F236" t="str">
-        <v>20.00%</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237">
-        <v>60</v>
-      </c>
-      <c r="B237" t="str">
-        <v>Obsidian Sphere</v>
-      </c>
-      <c r="C237" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D237" t="str">
-        <v>Solgaleo</v>
-      </c>
-      <c r="E237" t="str">
-        <v>120</v>
-      </c>
-      <c r="F237" t="str">
-        <v>20.00%</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238">
-        <v>60</v>
-      </c>
-      <c r="B238" t="str">
-        <v>Obsidian Sphere</v>
-      </c>
-      <c r="C238" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D238" t="str">
-        <v>Lunala</v>
-      </c>
-      <c r="E238" t="str">
-        <v>120</v>
-      </c>
-      <c r="F238" t="str">
-        <v>20.00%</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239">
-        <v>60</v>
-      </c>
-      <c r="B239" t="str">
-        <v>Obsidian Sphere</v>
-      </c>
-      <c r="C239" t="str">
-        <v>Main Area</v>
-      </c>
-      <c r="D239" t="str">
-        <v>Necrozma</v>
-      </c>
-      <c r="E239" t="str">
-        <v>120</v>
-      </c>
-      <c r="F239" t="str">
         <v>20.00%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F239"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F212"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C65"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5222,7 +4682,7 @@
         <v>Catch 3 Dark type Pokemon in Route 1 Hau'oli Outskirts</v>
       </c>
       <c r="C3" t="str">
-        <v>Unlocks Hau'oli City Shopping District</v>
+        <v>Unlocks Route 2 North</v>
       </c>
     </row>
     <row r="4">
@@ -5230,10 +4690,10 @@
         <v>Challenge 3</v>
       </c>
       <c r="B4" t="str">
-        <v>Catch 5 Pokemon of Uncommon or better rarity in Hau'oli City Shopping District</v>
+        <v>Catch 5 Pokemon of Uncommon or better rarity in Route 2 North</v>
       </c>
       <c r="C4" t="str">
-        <v>Unlocks Route 2 North</v>
+        <v>Unlocks Captain Ilima</v>
       </c>
     </row>
     <row r="5">
@@ -5241,10 +4701,10 @@
         <v>Challenge 4</v>
       </c>
       <c r="B5" t="str">
-        <v>Catch 2 Pokemon of Rare or better rarity in Route 2 North</v>
+        <v>Defeat Captain Ilima</v>
       </c>
       <c r="C5" t="str">
-        <v>Unlocks Captain Ilima</v>
+        <v>Unlocks Hau'oli Cemetery</v>
       </c>
     </row>
     <row r="6">
@@ -5252,10 +4712,10 @@
         <v>Challenge 5</v>
       </c>
       <c r="B6" t="str">
-        <v>Defeat Captain Ilima</v>
+        <v>Catch 2 Pokemon of Rare or better rarity in Hau'oli Cemetery</v>
       </c>
       <c r="C6" t="str">
-        <v>Unlocks Hau'oli Cemetery Main Area</v>
+        <v>Unlocks Ten Carat Hill Farthest Hollow</v>
       </c>
     </row>
     <row r="7">
@@ -5263,10 +4723,10 @@
         <v>Challenge 6</v>
       </c>
       <c r="B7" t="str">
-        <v>Catch 1 Epic rarity Pokemon in Hau'oli Cemetery Main Area</v>
+        <v>Catch 1 Epic rarity Pokemon in Ten Carat Hill Farthest Hollow</v>
       </c>
       <c r="C7" t="str">
-        <v>Unlocks Ten Carat Hill Farthest Hollow</v>
+        <v>Unlocks Seaward Cave</v>
       </c>
     </row>
     <row r="8">
@@ -5274,10 +4734,10 @@
         <v>Challenge 7</v>
       </c>
       <c r="B8" t="str">
-        <v>Defeat 5 specific Rock type Pokemon</v>
+        <v>Defeat 5 specific Water type Pokemon</v>
       </c>
       <c r="C8" t="str">
-        <v>Unlocks Seaward Cave Main Area</v>
+        <v>Unlocks Kahuna Hala</v>
       </c>
     </row>
     <row r="9">
@@ -5285,10 +4745,10 @@
         <v>Challenge 8</v>
       </c>
       <c r="B9" t="str">
-        <v>Catch 10 Pokemon in Seaward Cave Main Area</v>
+        <v>Defeat 10 Pokemon in Kahuna Hala</v>
       </c>
       <c r="C9" t="str">
-        <v>Unlocks Kahuna Hala</v>
+        <v>Unlocks Paniola Ranch</v>
       </c>
     </row>
     <row r="10">
@@ -5296,10 +4756,10 @@
         <v>Challenge 9</v>
       </c>
       <c r="B10" t="str">
-        <v>Defeat Kahuna Hala</v>
+        <v>Catch 10 Pokemon in Paniola Ranch</v>
       </c>
       <c r="C10" t="str">
-        <v>Unlocks Heahea Beach Main Area Part 1</v>
+        <v>Unlocks Daycare NPC</v>
       </c>
     </row>
     <row r="11">
@@ -5307,10 +4767,10 @@
         <v>Challenge 10</v>
       </c>
       <c r="B11" t="str">
-        <v>Defeat Kahuna Hala</v>
+        <v>Interact with Daycare</v>
       </c>
       <c r="C11" t="str">
-        <v>Unlocks Heahea Beach Main Area Part 2</v>
+        <v>Unlocks Route 5</v>
       </c>
     </row>
     <row r="12">
@@ -5318,10 +4778,10 @@
         <v>Challenge 11</v>
       </c>
       <c r="B12" t="str">
-        <v>Defeat 15 Pokemon in Heahea Beach Main Area Part 2</v>
+        <v>Catch 2 specific Pokemon species in Route 5</v>
       </c>
       <c r="C12" t="str">
-        <v>Unlocks Paniola Ranch Main Area</v>
+        <v>Unlocks Captain Lana</v>
       </c>
     </row>
     <row r="13">
@@ -5329,10 +4789,10 @@
         <v>Challenge 12</v>
       </c>
       <c r="B13" t="str">
-        <v>Catch 3 Normal type Pokemon in Paniola Ranch Main Area</v>
+        <v>Defeat Captain Lana</v>
       </c>
       <c r="C13" t="str">
-        <v>Unlocks Daycare NPC</v>
+        <v>Unlocks Wela Volcano Park</v>
       </c>
     </row>
     <row r="14">
@@ -5340,10 +4800,10 @@
         <v>Challenge 13</v>
       </c>
       <c r="B14" t="str">
-        <v>Interact with Daycare</v>
+        <v>Defeat 15 Pokemon in Wela Volcano Park</v>
       </c>
       <c r="C14" t="str">
-        <v>Unlocks Route 5 Main Area</v>
+        <v>Unlocks Captain Kiawe</v>
       </c>
     </row>
     <row r="15">
@@ -5351,10 +4811,10 @@
         <v>Challenge 14</v>
       </c>
       <c r="B15" t="str">
-        <v>Catch 5 Pokemon of Uncommon or better rarity in Route 5 Main Area</v>
+        <v>Defeat Captain Kiawe</v>
       </c>
       <c r="C15" t="str">
-        <v>Unlocks Brooklet Hill South</v>
+        <v>Unlocks Route 7</v>
       </c>
     </row>
     <row r="16">
@@ -5362,10 +4822,10 @@
         <v>Challenge 15</v>
       </c>
       <c r="B16" t="str">
-        <v>Catch 2 Pokemon of Rare or better rarity in Brooklet Hill South</v>
+        <v>Catch 3 Water type Pokemon in Route 7</v>
       </c>
       <c r="C16" t="str">
-        <v>Unlocks Captain Lana</v>
+        <v>Unlocks Route 8 Fossil Restoration Center Part 1</v>
       </c>
     </row>
     <row r="17">
@@ -5373,10 +4833,10 @@
         <v>Challenge 16</v>
       </c>
       <c r="B17" t="str">
-        <v>Defeat Captain Lana</v>
+        <v>Catch 5 Pokemon of Uncommon or better rarity in Route 8 Fossil Restoration Center Part 1</v>
       </c>
       <c r="C17" t="str">
-        <v>Unlocks Captain Lana and Wela Volcano Park Main Area</v>
+        <v>Unlocks Captain Lana and Wela Volcano Park</v>
       </c>
     </row>
     <row r="18">
@@ -5384,10 +4844,10 @@
         <v>Challenge 17</v>
       </c>
       <c r="B18" t="str">
-        <v>Defeat Captain Kiawe</v>
+        <v>Catch 1 Epic rarity Pokemon in Lush Jungle North</v>
       </c>
       <c r="C18" t="str">
-        <v>Unlocks Route 7 Main Area</v>
+        <v>Unlocks Lush Jungle East Cave</v>
       </c>
     </row>
     <row r="19">
@@ -5395,10 +4855,10 @@
         <v>Challenge 18</v>
       </c>
       <c r="B19" t="str">
-        <v>Defeat 5 specific Water type Pokemon</v>
+        <v>Defeat 5 specific Poison type Pokemon</v>
       </c>
       <c r="C19" t="str">
-        <v>Unlocks Route 8 Fossil Restoration Center Part 1</v>
+        <v>Unlocks Captain Mallow</v>
       </c>
     </row>
     <row r="20">
@@ -5406,10 +4866,10 @@
         <v>Challenge 19</v>
       </c>
       <c r="B20" t="str">
-        <v>Catch 10 Pokemon in Route 8 Fossil Restoration Center Part 1</v>
+        <v>Defeat Captain Mallow</v>
       </c>
       <c r="C20" t="str">
-        <v>Unlocks Route 8 Fossil Restoration Center Part 2</v>
+        <v>Unlocks Diglett's Tunnel</v>
       </c>
     </row>
     <row r="21">
@@ -5417,10 +4877,10 @@
         <v>Challenge 20</v>
       </c>
       <c r="B21" t="str">
-        <v>Catch 2 specific Pokemon species in Route 8 Fossil Restoration Center Part 2</v>
+        <v>Catch 10 Pokemon in Diglett's Tunnel</v>
       </c>
       <c r="C21" t="str">
-        <v>Unlocks Lush Jungle North</v>
+        <v>Unlocks Akala Outskirts</v>
       </c>
     </row>
     <row r="22">
@@ -5428,10 +4888,10 @@
         <v>Challenge 21</v>
       </c>
       <c r="B22" t="str">
-        <v>Defeat 15 Pokemon in Lush Jungle North</v>
+        <v>Catch 2 specific Pokemon species in Akala Outskirts</v>
       </c>
       <c r="C22" t="str">
-        <v>Unlocks Lush Jungle East Cave</v>
+        <v>Unlocks Kahuna Olivia</v>
       </c>
     </row>
     <row r="23">
@@ -5439,10 +4899,10 @@
         <v>Challenge 22</v>
       </c>
       <c r="B23" t="str">
-        <v>Catch 3 Poison type Pokemon in Lush Jungle East Cave</v>
+        <v>Defeat 10 Pokemon in Kahuna Olivia</v>
       </c>
       <c r="C23" t="str">
-        <v>Unlocks Captain Mallow</v>
+        <v>Unlocks Malie City</v>
       </c>
     </row>
     <row r="24">
@@ -5450,10 +4910,10 @@
         <v>Challenge 23</v>
       </c>
       <c r="B24" t="str">
-        <v>Defeat Captain Mallow</v>
+        <v>Defeat 15 Pokemon in Malie City</v>
       </c>
       <c r="C24" t="str">
-        <v>Unlocks Diglett's Tunnel Main Area</v>
+        <v>Unlocks Mount Hokulani East</v>
       </c>
     </row>
     <row r="25">
@@ -5461,10 +4921,10 @@
         <v>Challenge 24</v>
       </c>
       <c r="B25" t="str">
-        <v>Catch 5 Pokemon of Uncommon or better rarity in Diglett's Tunnel Main Area</v>
+        <v>Catch 3 Fairy type Pokemon in Mount Hokulani East</v>
       </c>
       <c r="C25" t="str">
-        <v>Unlocks Akala Outskirts Main Area</v>
+        <v>Unlocks Captain Sophocles</v>
       </c>
     </row>
     <row r="26">
@@ -5472,10 +4932,10 @@
         <v>Challenge 25</v>
       </c>
       <c r="B26" t="str">
-        <v>Catch 2 Pokemon of Rare or better rarity in Akala Outskirts Main Area</v>
+        <v>Defeat 10 Pokemon in Captain Sophocles</v>
       </c>
       <c r="C26" t="str">
-        <v>Unlocks Kahuna Olivia</v>
+        <v>Unlocks Haina Desert</v>
       </c>
     </row>
     <row r="27">
@@ -5483,10 +4943,10 @@
         <v>Challenge 26</v>
       </c>
       <c r="B27" t="str">
-        <v>Defeat 10 Pokemon in Kahuna Olivia</v>
+        <v>Catch 5 Pokemon of Uncommon or better rarity in Haina Desert</v>
       </c>
       <c r="C27" t="str">
-        <v>Unlocks Malie City Outer Cape</v>
+        <v>Unlocks Tapu Village</v>
       </c>
     </row>
     <row r="28">
@@ -5494,10 +4954,10 @@
         <v>Challenge 27</v>
       </c>
       <c r="B28" t="str">
-        <v>Catch 1 Epic rarity Pokemon in Malie City Outer Cape</v>
+        <v>Catch 2 Pokemon of Rare or better rarity in Tapu Village</v>
       </c>
       <c r="C28" t="str">
-        <v>Unlocks Route 10 Main Area</v>
+        <v>Unlocks Thrifty Megamart</v>
       </c>
     </row>
     <row r="29">
@@ -5505,10 +4965,10 @@
         <v>Challenge 28</v>
       </c>
       <c r="B29" t="str">
-        <v>Defeat 5 specific Bug type Pokemon</v>
+        <v>Catch 1 Epic rarity Pokemon in Thrifty Megamart</v>
       </c>
       <c r="C29" t="str">
-        <v>Unlocks Mount Hokulani East</v>
+        <v>Unlocks Captain Acerola</v>
       </c>
     </row>
     <row r="30">
@@ -5516,10 +4976,10 @@
         <v>Challenge 29</v>
       </c>
       <c r="B30" t="str">
-        <v>Catch 10 Pokemon in Mount Hokulani East</v>
+        <v>Defeat 10 Pokemon in Captain Acerola</v>
       </c>
       <c r="C30" t="str">
-        <v>Unlocks Captain Sophocles</v>
+        <v>Unlocks Kahuna Nanu</v>
       </c>
     </row>
     <row r="31">
@@ -5527,10 +4987,10 @@
         <v>Challenge 30</v>
       </c>
       <c r="B31" t="str">
-        <v>Defeat Captain Sophocles</v>
+        <v>Defeat Kahuna Nanu</v>
       </c>
       <c r="C31" t="str">
-        <v>Unlocks Route 11 Main Area</v>
+        <v>Unlocks Seafolk Village</v>
       </c>
     </row>
     <row r="32">
@@ -5538,10 +4998,10 @@
         <v>Challenge 31</v>
       </c>
       <c r="B32" t="str">
-        <v>Catch 2 specific Pokemon species in Route 11 Main Area</v>
+        <v>Defeat 5 specific Grass type Pokemon</v>
       </c>
       <c r="C32" t="str">
-        <v>Unlocks Haina Desert Main Area</v>
+        <v>Unlocks Poni Wilds</v>
       </c>
     </row>
     <row r="33">
@@ -5549,10 +5009,10 @@
         <v>Challenge 32</v>
       </c>
       <c r="B33" t="str">
-        <v>Defeat 15 Pokemon in Haina Desert Main Area</v>
+        <v>Catch 10 Pokemon in Poni Wilds</v>
       </c>
       <c r="C33" t="str">
-        <v>Unlocks Tapu Village Main Area</v>
+        <v>Unlocks Poni Breaker Coast</v>
       </c>
     </row>
     <row r="34">
@@ -5560,10 +5020,10 @@
         <v>Challenge 33</v>
       </c>
       <c r="B34" t="str">
-        <v>Catch 3 Rock type Pokemon in Tapu Village Main Area</v>
+        <v>Catch 2 specific Pokemon species in Poni Breaker Coast</v>
       </c>
       <c r="C34" t="str">
-        <v>Unlocks Thrifty Megamart Abandoned Site</v>
+        <v>Unlocks Exeggutor Island</v>
       </c>
     </row>
     <row r="35">
@@ -5571,10 +5031,10 @@
         <v>Challenge 34</v>
       </c>
       <c r="B35" t="str">
-        <v>Catch 5 Pokemon of Uncommon or better rarity in Thrifty Megamart Abandoned Site</v>
+        <v>Defeat 15 Pokemon in Exeggutor Island</v>
       </c>
       <c r="C35" t="str">
-        <v>Unlocks Captain Acerola</v>
+        <v>Unlocks Vast Poni Canyon Outside</v>
       </c>
     </row>
     <row r="36">
@@ -5582,10 +5042,10 @@
         <v>Challenge 35</v>
       </c>
       <c r="B36" t="str">
-        <v>Defeat 10 Pokemon in Captain Acerola</v>
+        <v>Catch 3 Fighting type Pokemon in Vast Poni Canyon Outside</v>
       </c>
       <c r="C36" t="str">
-        <v>Unlocks Kahuna Nanu</v>
+        <v>Unlocks Captain Kommo-o</v>
       </c>
     </row>
     <row r="37">
@@ -5593,10 +5053,10 @@
         <v>Challenge 36</v>
       </c>
       <c r="B37" t="str">
-        <v>Defeat Kahuna Nanu</v>
+        <v>Defeat Captain Kommo-o</v>
       </c>
       <c r="C37" t="str">
-        <v>Unlocks Seafolk Village Main</v>
+        <v>Unlocks Captain Mina</v>
       </c>
     </row>
     <row r="38">
@@ -5604,10 +5064,10 @@
         <v>Challenge 37</v>
       </c>
       <c r="B38" t="str">
-        <v>Catch 2 Pokemon of Rare or better rarity in Seafolk Village Main</v>
+        <v>Defeat Captain Mina</v>
       </c>
       <c r="C38" t="str">
-        <v>Unlocks Poni Wilds Main Area</v>
+        <v>Unlocks Kahuna Hapu</v>
       </c>
     </row>
     <row r="39">
@@ -5615,10 +5075,10 @@
         <v>Challenge 38</v>
       </c>
       <c r="B39" t="str">
-        <v>Catch 1 Epic rarity Pokemon in Poni Wilds Main Area</v>
+        <v>Defeat Kahuna Hapu</v>
       </c>
       <c r="C39" t="str">
-        <v>Unlocks Poni Breaker Coast Main Area</v>
+        <v>Unlocks Mount Lanakila</v>
       </c>
     </row>
     <row r="40">
@@ -5626,10 +5086,10 @@
         <v>Challenge 39</v>
       </c>
       <c r="B40" t="str">
-        <v>Defeat 5 specific Bug type Pokemon</v>
+        <v>Catch 5 Pokemon of Uncommon or better rarity in Mount Lanakila</v>
       </c>
       <c r="C40" t="str">
-        <v>Unlocks Exeggutor Island Main Area</v>
+        <v>Unlocks Alola Pokemon League</v>
       </c>
     </row>
     <row r="41">
@@ -5637,345 +5097,279 @@
         <v>Challenge 40</v>
       </c>
       <c r="B41" t="str">
-        <v>Catch 10 Pokemon in Exeggutor Island Main Area</v>
+        <v>Defeat Alola Pokemon League</v>
       </c>
       <c r="C41" t="str">
-        <v>Unlocks Vast Poni Canyon Outside</v>
+        <v>Unlocks Champion Hau</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Challenge 41</v>
+        <v>Extra Challenge A-1</v>
       </c>
       <c r="B42" t="str">
-        <v>Catch 2 specific Pokemon species in Vast Poni Canyon Outside</v>
+        <v>Defeat Captain Lana</v>
       </c>
       <c r="C42" t="str">
-        <v>Unlocks Captain Kommo-o</v>
+        <v>Unlocks Route 6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Challenge 42</v>
+        <v>Extra Challenge A-2</v>
       </c>
       <c r="B43" t="str">
-        <v>Defeat Captain Kommo-o</v>
+        <v>Defeat 10 Pokemon in Route 6</v>
       </c>
       <c r="C43" t="str">
-        <v>Unlocks Captain Mina</v>
+        <v>Unlocks Royal Avenue</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Challenge 43</v>
+        <v>Extra Challenge A-3</v>
       </c>
       <c r="B44" t="str">
-        <v>Defeat Captain Mina</v>
+        <v>Catch 2 Pokemon of Rare or better rarity in Royal Avenue</v>
       </c>
       <c r="C44" t="str">
-        <v>Unlocks Kahuna Hapu</v>
+        <v>Unlocks Pikachu Valley</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Challenge 44</v>
+        <v>Extra Challenge A-4</v>
       </c>
       <c r="B45" t="str">
-        <v>Defeat Kahuna Hapu</v>
+        <v>Catch 1 Epic rarity Pokemon in Pikachu Valley</v>
       </c>
       <c r="C45" t="str">
-        <v>Unlocks Mount Lanakila Cave</v>
+        <v>Unlocks Starter Depot</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Challenge 45</v>
+        <v>Extra Challenge B-1</v>
       </c>
       <c r="B46" t="str">
-        <v>Defeat 15 Pokemon in Mount Lanakila Cave</v>
+        <v>Defeat Champion Hau</v>
       </c>
       <c r="C46" t="str">
-        <v>Unlocks Alola Pokemon League</v>
+        <v>Unlocks Ula'ula Meadow</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Challenge 46</v>
+        <v>Extra Challenge B-2</v>
       </c>
       <c r="B47" t="str">
-        <v>Defeat Alola Pokemon League</v>
+        <v>Defeat 5 specific Bug type Pokemon</v>
       </c>
       <c r="C47" t="str">
-        <v>Unlocks Champion Hau</v>
+        <v>Unlocks Blush Mountain</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Extra Challenge A-1</v>
+        <v>Extra Challenge B-3</v>
       </c>
       <c r="B48" t="str">
-        <v>Defeat Captain Lana</v>
+        <v>Catch 10 Pokemon in Blush Mountain</v>
       </c>
       <c r="C48" t="str">
-        <v>Unlocks Route 6 Main Area</v>
+        <v>Unlocks Shopping Mall Antiquities</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Extra Challenge A-2</v>
+        <v>Extra Challenge B-4</v>
       </c>
       <c r="B49" t="str">
-        <v>Defeat 10 Pokemon in Route 6 Main Area</v>
+        <v>Defeat 10 Pokemon in Shopping Mall Antiquities</v>
       </c>
       <c r="C49" t="str">
-        <v>Unlocks Royal Avenue Main Area</v>
+        <v>Unlocks The Zenith Anomaly</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Extra Challenge A-3</v>
+        <v>Extra Challenge C-1</v>
       </c>
       <c r="B50" t="str">
-        <v>Catch 3 Fire type Pokemon in Royal Avenue Main Area</v>
+        <v>Defeat Mahalo Trail</v>
       </c>
       <c r="C50" t="str">
-        <v>Unlocks Pikachu Valley Main Area</v>
+        <v>Unlocks Melemele Meadow</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Extra Challenge A-4</v>
+        <v>Extra Challenge C-2</v>
       </c>
       <c r="B51" t="str">
-        <v>Catch 5 Pokemon of Uncommon or better rarity in Pikachu Valley Main Area</v>
+        <v>Catch 2 specific Pokemon species in Melemele Meadow</v>
       </c>
       <c r="C51" t="str">
-        <v>Unlocks Starter Depot Main Area</v>
+        <v>Unlocks Ruins of Conflict</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Extra Challenge B-1</v>
+        <v>Extra Challenge C-3</v>
       </c>
       <c r="B52" t="str">
-        <v>Defeat Champion Hau</v>
+        <v>Defeat 10 Pokemon in Ruins of Conflict</v>
       </c>
       <c r="C52" t="str">
-        <v>Unlocks Poni Coast Main Area</v>
+        <v>Unlocks Ten Carat Hill Deepest Cave</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Extra Challenge B-2</v>
+        <v>Extra Challenge C-4</v>
       </c>
       <c r="B53" t="str">
-        <v>Catch 2 Pokemon of Rare or better rarity in Poni Coast Main Area</v>
+        <v>Defeat 10 Pokemon in Ten Carat Hill Deepest Cave</v>
       </c>
       <c r="C53" t="str">
-        <v>Unlocks Shopping Mall Antiquities Event</v>
+        <v>Unlocks Kala'e Bay</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Extra Challenge B-3</v>
+        <v>Extra Challenge C-5</v>
       </c>
       <c r="B54" t="str">
-        <v>Defeat 10 Pokemon in Shopping Mall Antiquities Event</v>
+        <v>Defeat 15 Pokemon in Kala'e Bay</v>
       </c>
       <c r="C54" t="str">
-        <v>Unlocks Aether Paradise Restricted Area</v>
+        <v>Unlocks Sacred Shrine</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Extra Challenge B-4</v>
+        <v>Extra Challenge D-1</v>
       </c>
       <c r="B55" t="str">
-        <v>Defeat 10 Pokemon in Aether Paradise Restricted Area</v>
+        <v>Defeat Poni Grove</v>
       </c>
       <c r="C55" t="str">
-        <v>Unlocks The Zenith Anomaly Main Area</v>
+        <v>Unlocks Poni Plains</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Extra Challenge C-1</v>
+        <v>Extra Challenge D-2</v>
       </c>
       <c r="B56" t="str">
-        <v>Defeat Champion Hau</v>
+        <v>Defeat 10 Pokemon in Poni Plains</v>
       </c>
       <c r="C56" t="str">
-        <v>Unlocks Mahalo Trail Main Area</v>
+        <v>Unlocks Poni Coast</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Extra Challenge C-2</v>
+        <v>Extra Challenge D-3</v>
       </c>
       <c r="B57" t="str">
-        <v>Defeat 10 Pokemon in Mahalo Trail Main Area</v>
+        <v>Catch 3 Normal type Pokemon in Poni Coast</v>
       </c>
       <c r="C57" t="str">
-        <v>Unlocks Melemele Meadow Main Area</v>
+        <v>Unlocks Resolution Cave</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Extra Challenge C-3</v>
+        <v>Extra Challenge D-4</v>
       </c>
       <c r="B58" t="str">
-        <v>Catch 1 Epic rarity Pokemon in Melemele Meadow Main Area</v>
+        <v>Defeat 10 Pokemon in Resolution Cave</v>
       </c>
       <c r="C58" t="str">
-        <v>Unlocks Ruins of Conflict Special Encounter</v>
+        <v>Unlocks Ruins of Hope</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Extra Challenge C-4</v>
+        <v>Extra Challenge D-5</v>
       </c>
       <c r="B59" t="str">
-        <v>Defeat 10 Pokemon in Ruins of Conflict Special Encounter</v>
+        <v>Defeat 10 Pokemon in Ruins of Hope</v>
       </c>
       <c r="C59" t="str">
-        <v>Unlocks Memorial Hill Main</v>
+        <v>Unlocks The Interdimensional Rift</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Extra Challenge C-5</v>
+        <v>Extra Challenge E-1</v>
       </c>
       <c r="B60" t="str">
-        <v>Defeat 10 Pokemon in Memorial Hill Main</v>
+        <v>Defeat Route 15</v>
       </c>
       <c r="C60" t="str">
-        <v>Unlocks Sacred Shrine Main Area</v>
+        <v>Unlocks Route 16</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Extra Challenge D-1</v>
+        <v>Extra Challenge E-2</v>
       </c>
       <c r="B61" t="str">
-        <v>Defeat Champion Hau</v>
+        <v>Defeat 10 Pokemon in Route 16</v>
       </c>
       <c r="C61" t="str">
-        <v>Unlocks Poni Grove Main Area</v>
+        <v>Unlocks Aether Paradise Labs</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Extra Challenge D-2</v>
+        <v>Extra Challenge E-3</v>
       </c>
       <c r="B62" t="str">
-        <v>Defeat 5 specific Normal type Pokemon</v>
+        <v>Catch 5 Pokemon of Uncommon or better rarity in Aether Paradise Labs</v>
       </c>
       <c r="C62" t="str">
-        <v>Unlocks Poni Plains Center</v>
+        <v>Unlocks Aether Paradise Secret Lab</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Extra Challenge D-3</v>
+        <v>Extra Challenge E-4</v>
       </c>
       <c r="B63" t="str">
-        <v>Defeat 10 Pokemon in Poni Plains Center</v>
+        <v>Catch 2 Pokemon of Rare or better rarity in Aether Paradise Secret Lab</v>
       </c>
       <c r="C63" t="str">
-        <v>Unlocks Resolution Cave Main Area</v>
+        <v>Unlocks Lake of the Sunne</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Extra Challenge D-4</v>
+        <v>Extra Challenge E-5</v>
       </c>
       <c r="B64" t="str">
-        <v>Defeat 10 Pokemon in Resolution Cave Main Area</v>
+        <v>Catch 1 Epic rarity Pokemon in Lake of the Sunne</v>
       </c>
       <c r="C64" t="str">
-        <v>Unlocks Ruins of Hope Special Encounter</v>
+        <v>Unlocks Obsidian Sphere</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Extra Challenge D-5</v>
+        <v>Extra Challenge E-6</v>
       </c>
       <c r="B65" t="str">
-        <v>Defeat 10 Pokemon in Ruins of Hope Special Encounter</v>
+        <v>Defeat 5 specific Psychic type Pokemon</v>
       </c>
       <c r="C65" t="str">
-        <v>Unlocks The Interdimensional Rift Main Area</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>Extra Challenge E-1</v>
-      </c>
-      <c r="B66" t="str">
-        <v>Defeat Champion Hau</v>
-      </c>
-      <c r="C66" t="str">
-        <v>Unlocks Route 15 Main Area</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>Extra Challenge E-2</v>
-      </c>
-      <c r="B67" t="str">
-        <v>Defeat 10 Pokemon in Route 15 Main Area</v>
-      </c>
-      <c r="C67" t="str">
-        <v>Unlocks Aether Paradise Labs</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>Extra Challenge E-3</v>
-      </c>
-      <c r="B68" t="str">
-        <v>Defeat 10 Pokemon in Aether Paradise Labs</v>
-      </c>
-      <c r="C68" t="str">
-        <v>Unlocks Aether Paradise Secret Lab</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>Extra Challenge E-4</v>
-      </c>
-      <c r="B69" t="str">
-        <v>Catch 10 Pokemon in Aether Paradise Secret Lab</v>
-      </c>
-      <c r="C69" t="str">
-        <v>Unlocks Lake of the Sunne Main Area</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>Extra Challenge E-5</v>
-      </c>
-      <c r="B70" t="str">
-        <v>Catch 2 specific Pokemon species in Lake of the Sunne Main Area</v>
-      </c>
-      <c r="C70" t="str">
-        <v>Unlocks Obsidian Sphere Main Area</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>Extra Challenge E-6</v>
-      </c>
-      <c r="B71" t="str">
-        <v>Defeat 15 Pokemon in Obsidian Sphere Main Area</v>
-      </c>
-      <c r="C71" t="str">
         <v>Transforms Obsidian Sphere into Obsidian Tesseract</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C71"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C65"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -6146,7 +5540,7 @@
         <v>Water</v>
       </c>
       <c r="C12" t="str">
-        <v>Route 7 Main Area</v>
+        <v>Route 7</v>
       </c>
       <c r="D12" t="str">
         <v>Yes</v>
@@ -6160,7 +5554,7 @@
         <v>Water</v>
       </c>
       <c r="C13" t="str">
-        <v>Route 7 Main Area</v>
+        <v>Route 7</v>
       </c>
       <c r="D13" t="str">
         <v>Yes</v>
@@ -6216,7 +5610,7 @@
         <v>Water/Rock</v>
       </c>
       <c r="C17" t="str">
-        <v>Route 7 Main Area</v>
+        <v>Route 7</v>
       </c>
       <c r="D17" t="str">
         <v>Yes</v>
@@ -6230,7 +5624,7 @@
         <v>Poison/Water</v>
       </c>
       <c r="C18" t="str">
-        <v>Route 7 Main Area</v>
+        <v>Route 7</v>
       </c>
       <c r="D18" t="str">
         <v>Yes</v>
@@ -6258,7 +5652,7 @@
         <v>Water/Psychic</v>
       </c>
       <c r="C20" t="str">
-        <v>Route 14 Main Area</v>
+        <v>Route 14</v>
       </c>
       <c r="D20" t="str">
         <v>Yes</v>
@@ -6272,7 +5666,7 @@
         <v>Ghost/Ground</v>
       </c>
       <c r="C21" t="str">
-        <v>Route 15 Main Area</v>
+        <v>Route 15</v>
       </c>
       <c r="D21" t="str">
         <v>Yes</v>
@@ -6286,7 +5680,7 @@
         <v>Steel/Fairy</v>
       </c>
       <c r="C22" t="str">
-        <v>Route 16 Main Area</v>
+        <v>Route 16</v>
       </c>
       <c r="D22" t="str">
         <v>Yes</v>
